--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,12 +163,12 @@
     <t>No</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
   </si>
   <si>
-    <t>DOWN</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
@@ -190,16 +190,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>52.5 → 49.9</t>
+    <t>54.4 → 41.9</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>52.5</t>
-  </si>
-  <si>
-    <t>49.9</t>
+    <t>54.4</t>
+  </si>
+  <si>
+    <t>41.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -924,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1075.2</v>
+        <v>1031.8</v>
       </c>
       <c r="D2">
-        <v>-1.38</v>
+        <v>-4.04</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -936,46 +936,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-13.41</v>
+        <v>-16.9</v>
       </c>
       <c r="H2">
-        <v>43.68</v>
+        <v>37.88</v>
       </c>
       <c r="I2">
-        <v>-4.9</v>
+        <v>-6.54</v>
       </c>
       <c r="J2">
-        <v>-9.24</v>
+        <v>-10.4</v>
       </c>
       <c r="K2">
-        <v>0.87</v>
+        <v>-3.16</v>
       </c>
       <c r="L2">
-        <v>10.61</v>
+        <v>5.21</v>
       </c>
       <c r="M2">
-        <v>3.65</v>
+        <v>2.66</v>
       </c>
       <c r="N2">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O2">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="P2">
-        <v>1091.88</v>
+        <v>1077.44</v>
       </c>
       <c r="Q2">
-        <v>1107.22</v>
+        <v>1102.68</v>
       </c>
       <c r="R2">
-        <v>1097.92</v>
+        <v>1095.66</v>
       </c>
       <c r="S2">
-        <v>955.41</v>
+        <v>956.1900000000001</v>
       </c>
       <c r="T2">
-        <v>12.54</v>
+        <v>7.91</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,43 +990,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>44.19</v>
+        <v>37.32</v>
       </c>
       <c r="Z2">
-        <v>-5.23</v>
+        <v>-10.07</v>
       </c>
       <c r="AA2">
-        <v>-1.26</v>
+        <v>-3.02</v>
       </c>
       <c r="AB2">
-        <v>-3.97</v>
+        <v>-7.05</v>
       </c>
       <c r="AC2">
-        <v>25.52</v>
+        <v>15.75</v>
       </c>
       <c r="AD2">
-        <v>30.4</v>
+        <v>24.5</v>
       </c>
       <c r="AE2">
-        <v>41.15</v>
+        <v>42.78</v>
       </c>
       <c r="AF2">
-        <v>-48.5</v>
+        <v>-12.79</v>
       </c>
       <c r="AG2">
-        <v>1154.27</v>
+        <v>1159.9</v>
       </c>
       <c r="AH2">
-        <v>1060.18</v>
+        <v>1045.46</v>
       </c>
       <c r="AI2">
-        <v>1042.8</v>
+        <v>1181.33</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>20.97</v>
+        <v>21.33</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>909</v>
+        <v>858</v>
       </c>
       <c r="D3">
-        <v>-0.61</v>
+        <v>-5.61</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1049,46 +1049,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-6.91</v>
+        <v>-12.14</v>
       </c>
       <c r="H3">
-        <v>71.68000000000001</v>
+        <v>62.05</v>
       </c>
       <c r="I3">
-        <v>2.02</v>
+        <v>-4.13</v>
       </c>
       <c r="J3">
-        <v>2.53</v>
+        <v>-3.61</v>
       </c>
       <c r="K3">
-        <v>-2.83</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L3">
-        <v>23.09</v>
+        <v>11.83</v>
       </c>
       <c r="M3">
-        <v>59.54</v>
+        <v>57.73</v>
       </c>
       <c r="N3">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="O3">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="P3">
-        <v>911.24</v>
+        <v>903.84</v>
       </c>
       <c r="Q3">
-        <v>891.4400000000001</v>
+        <v>889.4</v>
       </c>
       <c r="R3">
-        <v>889.78</v>
+        <v>888.4400000000001</v>
       </c>
       <c r="S3">
-        <v>780.99</v>
+        <v>781.84</v>
       </c>
       <c r="T3">
-        <v>16.39</v>
+        <v>9.74</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1103,43 +1103,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>54.39</v>
+        <v>41.91</v>
       </c>
       <c r="Z3">
-        <v>7.13</v>
+        <v>3.15</v>
       </c>
       <c r="AA3">
-        <v>3.57</v>
+        <v>3.48</v>
       </c>
       <c r="AB3">
-        <v>3.56</v>
+        <v>-0.34</v>
       </c>
       <c r="AC3">
-        <v>79.31</v>
+        <v>45.98</v>
       </c>
       <c r="AD3">
-        <v>82.61</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="AE3">
-        <v>22.78</v>
+        <v>24.96</v>
       </c>
       <c r="AF3">
-        <v>-9.960000000000001</v>
+        <v>42.44</v>
       </c>
       <c r="AG3">
-        <v>927.35</v>
+        <v>928.08</v>
       </c>
       <c r="AH3">
-        <v>855.53</v>
+        <v>850.72</v>
       </c>
       <c r="AI3">
         <v>853.38</v>
       </c>
       <c r="AJ3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK3">
-        <v>36.33</v>
+        <v>34.49</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1845.9</v>
+        <v>1791.6</v>
       </c>
       <c r="D4">
-        <v>-0.7</v>
+        <v>-2.94</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1162,46 +1162,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-4.85</v>
+        <v>-7.65</v>
       </c>
       <c r="H4">
-        <v>36.26</v>
+        <v>32.25</v>
       </c>
       <c r="I4">
-        <v>0.38</v>
+        <v>-3.06</v>
       </c>
       <c r="J4">
-        <v>-4.25</v>
+        <v>-5.43</v>
       </c>
       <c r="K4">
-        <v>11.63</v>
+        <v>6.62</v>
       </c>
       <c r="L4">
-        <v>22.57</v>
+        <v>17.77</v>
       </c>
       <c r="M4">
-        <v>26.12</v>
+        <v>25.53</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P4">
-        <v>1841.1</v>
+        <v>1829.78</v>
       </c>
       <c r="Q4">
-        <v>1855.28</v>
+        <v>1850.14</v>
       </c>
       <c r="R4">
-        <v>1837.17</v>
+        <v>1836</v>
       </c>
       <c r="S4">
-        <v>1681.53</v>
+        <v>1681.93</v>
       </c>
       <c r="T4">
-        <v>9.779999999999999</v>
+        <v>6.52</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1216,43 +1216,43 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>49.94</v>
+        <v>41.1</v>
       </c>
       <c r="Z4">
-        <v>-0.28</v>
+        <v>-4.65</v>
       </c>
       <c r="AA4">
-        <v>3.98</v>
+        <v>2.25</v>
       </c>
       <c r="AB4">
-        <v>-4.26</v>
+        <v>-6.9</v>
       </c>
       <c r="AC4">
-        <v>58.62</v>
+        <v>48.78</v>
       </c>
       <c r="AD4">
-        <v>44.37</v>
+        <v>50.23</v>
       </c>
       <c r="AE4">
-        <v>46.57</v>
+        <v>47.65</v>
       </c>
       <c r="AF4">
-        <v>54.69</v>
+        <v>70.39</v>
       </c>
       <c r="AG4">
-        <v>1898.57</v>
+        <v>1898.04</v>
       </c>
       <c r="AH4">
-        <v>1811.99</v>
+        <v>1802.24</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
       </c>
       <c r="AJ4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK4">
-        <v>16.78</v>
+        <v>16.26</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1929</v>
+        <v>1939.1</v>
       </c>
       <c r="D5">
-        <v>-1.68</v>
+        <v>0.52</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1275,46 +1275,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-19.58</v>
+        <v>-19.16</v>
       </c>
       <c r="H5">
-        <v>10.51</v>
+        <v>11.09</v>
       </c>
       <c r="I5">
-        <v>-0.51</v>
+        <v>-1.8</v>
       </c>
       <c r="J5">
-        <v>-7.65</v>
+        <v>-7.45</v>
       </c>
       <c r="K5">
-        <v>-2.88</v>
+        <v>-5.86</v>
       </c>
       <c r="L5">
-        <v>-12.62</v>
+        <v>-12.26</v>
       </c>
       <c r="M5">
-        <v>19.24</v>
+        <v>19.45</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="P5">
-        <v>1955.86</v>
+        <v>1948.76</v>
       </c>
       <c r="Q5">
-        <v>1961.09</v>
+        <v>1953.28</v>
       </c>
       <c r="R5">
-        <v>2018.22</v>
+        <v>2015.9</v>
       </c>
       <c r="S5">
-        <v>2084.33</v>
+        <v>2082.58</v>
       </c>
       <c r="T5">
-        <v>-7.45</v>
+        <v>-6.89</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,43 +1329,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>41.03</v>
+        <v>43.27</v>
       </c>
       <c r="Z5">
-        <v>-22.45</v>
+        <v>-21.77</v>
       </c>
       <c r="AA5">
-        <v>-25.1</v>
+        <v>-24.43</v>
       </c>
       <c r="AB5">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="AC5">
-        <v>80.47</v>
+        <v>72.55</v>
       </c>
       <c r="AD5">
-        <v>85.68000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AE5">
-        <v>44.43</v>
+        <v>43.47</v>
       </c>
       <c r="AF5">
-        <v>-20.94</v>
+        <v>-27.5</v>
       </c>
       <c r="AG5">
-        <v>2067.37</v>
+        <v>2039.01</v>
       </c>
       <c r="AH5">
-        <v>1854.81</v>
+        <v>1867.55</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
       </c>
       <c r="AJ5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK5">
-        <v>19.31</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,58 +1376,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>721.05</v>
+        <v>702.75</v>
       </c>
       <c r="D6">
-        <v>-1.76</v>
+        <v>-2.54</v>
       </c>
       <c r="E6">
         <v>1095.8</v>
       </c>
       <c r="F6">
-        <v>704.1</v>
+        <v>702.75</v>
       </c>
       <c r="G6">
-        <v>-34.2</v>
+        <v>-35.87</v>
       </c>
       <c r="H6">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>-7.72</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="J6">
-        <v>-7.59</v>
+        <v>-9.35</v>
       </c>
       <c r="K6">
-        <v>-0.63</v>
+        <v>-4.36</v>
       </c>
       <c r="L6">
-        <v>-32.64</v>
+        <v>-35.29</v>
       </c>
       <c r="M6">
-        <v>12.18</v>
+        <v>11.58</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P6">
-        <v>750.62</v>
+        <v>735.63</v>
       </c>
       <c r="Q6">
-        <v>785.34</v>
+        <v>780.88</v>
       </c>
       <c r="R6">
-        <v>778.03</v>
+        <v>776.74</v>
       </c>
       <c r="S6">
-        <v>845.05</v>
+        <v>843.4</v>
       </c>
       <c r="T6">
-        <v>-14.67</v>
+        <v>-16.68</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,16 +1442,16 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>31.16</v>
+        <v>27.72</v>
       </c>
       <c r="Z6">
-        <v>-10.03</v>
+        <v>-14.37</v>
       </c>
       <c r="AA6">
-        <v>-0.9</v>
+        <v>-3.59</v>
       </c>
       <c r="AB6">
-        <v>-9.140000000000001</v>
+        <v>-10.78</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -1460,25 +1460,25 @@
         <v>0</v>
       </c>
       <c r="AE6">
-        <v>24.77</v>
+        <v>24.5</v>
       </c>
       <c r="AF6">
-        <v>-60.92</v>
+        <v>-59.38</v>
       </c>
       <c r="AG6">
-        <v>836.22</v>
+        <v>843.58</v>
       </c>
       <c r="AH6">
-        <v>734.47</v>
+        <v>718.1799999999999</v>
       </c>
       <c r="AI6">
-        <v>800.48</v>
+        <v>784.02</v>
       </c>
       <c r="AJ6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK6">
-        <v>29.36</v>
+        <v>31.31</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3250.2</v>
+        <v>3128.6</v>
       </c>
       <c r="D7">
-        <v>2.95</v>
+        <v>-3.74</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1501,46 +1501,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-5.92</v>
+        <v>-9.44</v>
       </c>
       <c r="H7">
-        <v>71.84</v>
+        <v>65.41</v>
       </c>
       <c r="I7">
-        <v>1.74</v>
+        <v>-1.19</v>
       </c>
       <c r="J7">
-        <v>12.56</v>
+        <v>1.29</v>
       </c>
       <c r="K7">
-        <v>28.4</v>
+        <v>22.45</v>
       </c>
       <c r="L7">
-        <v>33.65</v>
+        <v>25.46</v>
       </c>
       <c r="M7">
-        <v>32.47</v>
+        <v>28.98</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P7">
-        <v>3176.98</v>
+        <v>3169.42</v>
       </c>
       <c r="Q7">
-        <v>3254.27</v>
+        <v>3255.84</v>
       </c>
       <c r="R7">
-        <v>2861.73</v>
+        <v>2874.41</v>
       </c>
       <c r="S7">
-        <v>2454.62</v>
+        <v>2458.06</v>
       </c>
       <c r="T7">
-        <v>32.41</v>
+        <v>27.28</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1555,43 +1555,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>60.92</v>
+        <v>51.3</v>
       </c>
       <c r="Z7">
-        <v>89.04000000000001</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="AA7">
-        <v>124.51</v>
+        <v>114.87</v>
       </c>
       <c r="AB7">
-        <v>-35.47</v>
+        <v>-38.55</v>
       </c>
       <c r="AC7">
-        <v>12.94</v>
+        <v>10.32</v>
       </c>
       <c r="AD7">
-        <v>6.43</v>
+        <v>9</v>
       </c>
       <c r="AE7">
-        <v>138.33</v>
+        <v>138.94</v>
       </c>
       <c r="AF7">
-        <v>-53.76</v>
+        <v>-70.5</v>
       </c>
       <c r="AG7">
-        <v>3454.24</v>
+        <v>3451.05</v>
       </c>
       <c r="AH7">
-        <v>3054.29</v>
+        <v>3060.62</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
       </c>
       <c r="AJ7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK7">
-        <v>27.79</v>
+        <v>26.8</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,58 +1602,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8812.5</v>
+        <v>8580</v>
       </c>
       <c r="D8">
-        <v>1.65</v>
+        <v>-2.64</v>
       </c>
       <c r="E8">
-        <v>9788.280000000001</v>
+        <v>9697.559999999999</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-9.970000000000001</v>
+        <v>-11.52</v>
       </c>
       <c r="H8">
-        <v>48.75</v>
+        <v>44.82</v>
       </c>
       <c r="I8">
-        <v>8</v>
+        <v>2.88</v>
       </c>
       <c r="J8">
-        <v>10.36</v>
+        <v>8.17</v>
       </c>
       <c r="K8">
-        <v>10.72</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="L8">
-        <v>-10.17</v>
+        <v>-12.34</v>
       </c>
       <c r="M8">
-        <v>14.27</v>
+        <v>13.77</v>
       </c>
       <c r="N8">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="O8">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="P8">
-        <v>8494.299999999999</v>
+        <v>8542.299999999999</v>
       </c>
       <c r="Q8">
-        <v>8234.75</v>
+        <v>8267.15</v>
       </c>
       <c r="R8">
-        <v>8051.27</v>
+        <v>8061.28</v>
       </c>
       <c r="S8">
-        <v>7407.67</v>
+        <v>7409.49</v>
       </c>
       <c r="T8">
-        <v>18.96</v>
+        <v>15.8</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1668,43 +1668,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>65.81999999999999</v>
+        <v>58.54</v>
       </c>
       <c r="Z8">
-        <v>142.33</v>
+        <v>148.39</v>
       </c>
       <c r="AA8">
-        <v>93.70999999999999</v>
+        <v>104.64</v>
       </c>
       <c r="AB8">
-        <v>48.62</v>
+        <v>43.74</v>
       </c>
       <c r="AC8">
-        <v>79.12</v>
+        <v>87.17</v>
       </c>
       <c r="AD8">
-        <v>70.48999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="AE8">
-        <v>293.49</v>
+        <v>313.89</v>
       </c>
       <c r="AF8">
-        <v>128.26</v>
+        <v>178.63</v>
       </c>
       <c r="AG8">
-        <v>8671.190000000001</v>
+        <v>8705.17</v>
       </c>
       <c r="AH8">
-        <v>7798.31</v>
+        <v>7829.13</v>
       </c>
       <c r="AI8">
-        <v>7800.02</v>
+        <v>7868.84</v>
       </c>
       <c r="AJ8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK8">
-        <v>43.26</v>
+        <v>46.81</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1885,7 +1885,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1937,13 +1937,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-5.54</v>
+        <v>-9.24</v>
       </c>
       <c r="D7" s="6">
-        <v>-9.24</v>
+        <v>-10.4</v>
       </c>
       <c r="E7" s="7">
-        <v>-3.7</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1954,13 +1954,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>2.99</v>
+        <v>2.53</v>
       </c>
       <c r="D8" s="6">
-        <v>2.53</v>
+        <v>-3.61</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.46</v>
+        <v>-6.14</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1971,13 +1971,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-3.06</v>
+        <v>-4.25</v>
       </c>
       <c r="D9" s="6">
-        <v>-4.25</v>
+        <v>-5.43</v>
       </c>
       <c r="E9" s="7">
-        <v>-1.19</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1988,13 +1988,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-5.37</v>
+        <v>-7.65</v>
       </c>
       <c r="D10" s="6">
-        <v>-7.65</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-2.28</v>
+        <v>-7.45</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.2</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2005,13 +2005,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-4.99</v>
+        <v>-7.59</v>
       </c>
       <c r="D11" s="6">
-        <v>-7.59</v>
+        <v>-9.35</v>
       </c>
       <c r="E11" s="7">
-        <v>-2.6</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2022,13 +2022,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>9.69</v>
+        <v>12.56</v>
       </c>
       <c r="D12" s="6">
-        <v>12.56</v>
-      </c>
-      <c r="E12" s="8">
-        <v>2.87</v>
+        <v>1.29</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-11.27</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2039,13 +2039,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>8.99</v>
+        <v>10.36</v>
       </c>
       <c r="D13" s="6">
-        <v>10.36</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1.37</v>
+        <v>8.17</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2056,13 +2056,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>1.13</v>
+        <v>-4.9</v>
       </c>
       <c r="D14" s="6">
-        <v>-4.9</v>
+        <v>-6.54</v>
       </c>
       <c r="E14" s="7">
-        <v>-6.03</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2073,13 +2073,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="D15" s="6">
-        <v>2.02</v>
+        <v>-4.13</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.16</v>
+        <v>-6.15</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2090,13 +2090,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>0.52</v>
+        <v>0.38</v>
       </c>
       <c r="D16" s="6">
-        <v>0.38</v>
+        <v>-3.06</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.14</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2107,13 +2107,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>1.58</v>
+        <v>-0.51</v>
       </c>
       <c r="D17" s="6">
-        <v>-0.51</v>
+        <v>-1.8</v>
       </c>
       <c r="E17" s="7">
-        <v>-2.09</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2124,13 +2124,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-5.69</v>
+        <v>-7.72</v>
       </c>
       <c r="D18" s="6">
-        <v>-7.72</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="E18" s="7">
-        <v>-2.03</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2141,13 +2141,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-3.38</v>
+        <v>1.74</v>
       </c>
       <c r="D19" s="6">
-        <v>1.74</v>
-      </c>
-      <c r="E19" s="8">
-        <v>5.12</v>
+        <v>-1.19</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.93</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2158,13 +2158,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>4.36</v>
+        <v>8</v>
       </c>
       <c r="D20" s="6">
-        <v>8</v>
-      </c>
-      <c r="E20" s="8">
-        <v>3.64</v>
+        <v>2.88</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-5.12</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2175,13 +2175,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>13.14</v>
+        <v>10.61</v>
       </c>
       <c r="D21" s="6">
-        <v>10.61</v>
+        <v>5.21</v>
       </c>
       <c r="E21" s="7">
-        <v>-2.53</v>
+        <v>-5.4</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2192,13 +2192,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>22.81</v>
+        <v>23.09</v>
       </c>
       <c r="D22" s="6">
-        <v>23.09</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.28</v>
+        <v>11.83</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-11.26</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2209,13 +2209,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>24.52</v>
+        <v>22.57</v>
       </c>
       <c r="D23" s="6">
-        <v>22.57</v>
+        <v>17.77</v>
       </c>
       <c r="E23" s="7">
-        <v>-1.95</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2226,13 +2226,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-9.859999999999999</v>
+        <v>-12.62</v>
       </c>
       <c r="D24" s="6">
-        <v>-12.62</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.76</v>
+        <v>-12.26</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.36</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2243,13 +2243,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-31.23</v>
+        <v>-32.64</v>
       </c>
       <c r="D25" s="6">
-        <v>-32.64</v>
+        <v>-35.29</v>
       </c>
       <c r="E25" s="7">
-        <v>-1.41</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2260,13 +2260,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>29.59</v>
+        <v>33.65</v>
       </c>
       <c r="D26" s="6">
-        <v>33.65</v>
-      </c>
-      <c r="E26" s="8">
-        <v>4.06</v>
+        <v>25.46</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-8.19</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2277,13 +2277,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-11.87</v>
+        <v>-10.17</v>
       </c>
       <c r="D27" s="6">
-        <v>-10.17</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.7</v>
+        <v>-12.34</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2294,13 +2294,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>3.52</v>
+        <v>0.87</v>
       </c>
       <c r="D28" s="6">
-        <v>0.87</v>
+        <v>-3.16</v>
       </c>
       <c r="E28" s="7">
-        <v>-2.65</v>
+        <v>-4.03</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2311,13 +2311,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>0.01</v>
+        <v>-2.83</v>
       </c>
       <c r="D29" s="6">
-        <v>-2.83</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="E29" s="7">
-        <v>-2.84</v>
+        <v>-5.96</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2328,13 +2328,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>18.55</v>
+        <v>11.63</v>
       </c>
       <c r="D30" s="6">
-        <v>11.63</v>
+        <v>6.62</v>
       </c>
       <c r="E30" s="7">
-        <v>-6.92</v>
+        <v>-5.01</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2345,13 +2345,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>2.36</v>
+        <v>-2.88</v>
       </c>
       <c r="D31" s="6">
-        <v>-2.88</v>
+        <v>-5.86</v>
       </c>
       <c r="E31" s="7">
-        <v>-5.24</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2362,13 +2362,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>0.6</v>
+        <v>-0.63</v>
       </c>
       <c r="D32" s="6">
-        <v>-0.63</v>
+        <v>-4.36</v>
       </c>
       <c r="E32" s="7">
-        <v>-1.23</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2379,13 +2379,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>25.86</v>
+        <v>28.4</v>
       </c>
       <c r="D33" s="6">
-        <v>28.4</v>
-      </c>
-      <c r="E33" s="8">
-        <v>2.54</v>
+        <v>22.45</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-5.95</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2396,13 +2396,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>12.86</v>
+        <v>10.72</v>
       </c>
       <c r="D34" s="6">
-        <v>10.72</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E34" s="7">
-        <v>-2.14</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2413,13 +2413,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-12.2</v>
+        <v>-13.41</v>
       </c>
       <c r="D35" s="6">
-        <v>-13.41</v>
+        <v>-16.9</v>
       </c>
       <c r="E35" s="7">
-        <v>-1.21</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2430,13 +2430,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-6.34</v>
+        <v>-6.91</v>
       </c>
       <c r="D36" s="6">
-        <v>-6.91</v>
+        <v>-12.14</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.57</v>
+        <v>-5.23</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2447,13 +2447,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-4.18</v>
+        <v>-4.85</v>
       </c>
       <c r="D37" s="6">
-        <v>-4.85</v>
+        <v>-7.65</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.67</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2464,13 +2464,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-18.21</v>
+        <v>-19.58</v>
       </c>
       <c r="D38" s="6">
-        <v>-19.58</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-1.37</v>
+        <v>-19.16</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.42</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2481,13 +2481,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-33.02</v>
+        <v>-34.2</v>
       </c>
       <c r="D39" s="6">
-        <v>-34.2</v>
+        <v>-35.87</v>
       </c>
       <c r="E39" s="7">
-        <v>-1.18</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2498,13 +2498,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-8.619999999999999</v>
+        <v>-5.92</v>
       </c>
       <c r="D40" s="6">
-        <v>-5.92</v>
-      </c>
-      <c r="E40" s="8">
-        <v>2.7</v>
+        <v>-9.44</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-3.52</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2515,13 +2515,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-11.62</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="D41" s="6">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="E41" s="8">
-        <v>1.65</v>
+        <v>-11.52</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2532,13 +2532,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>1090.2</v>
+        <v>1075.2</v>
       </c>
       <c r="D42" s="6">
-        <v>1075.2</v>
+        <v>1031.8</v>
       </c>
       <c r="E42" s="7">
-        <v>-15</v>
+        <v>-43.4</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2549,13 +2549,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>914.55</v>
+        <v>909</v>
       </c>
       <c r="D43" s="6">
-        <v>909</v>
+        <v>858</v>
       </c>
       <c r="E43" s="7">
-        <v>-5.55</v>
+        <v>-51</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2566,13 +2566,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>1859</v>
+        <v>1845.9</v>
       </c>
       <c r="D44" s="6">
-        <v>1845.9</v>
+        <v>1791.6</v>
       </c>
       <c r="E44" s="7">
-        <v>-13.1</v>
+        <v>-54.3</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2583,13 +2583,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>1961.9</v>
+        <v>1929</v>
       </c>
       <c r="D45" s="6">
-        <v>1929</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-32.9</v>
+        <v>1939.1</v>
+      </c>
+      <c r="E45" s="8">
+        <v>10.1</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2600,13 +2600,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>733.95</v>
+        <v>721.05</v>
       </c>
       <c r="D46" s="6">
-        <v>721.05</v>
+        <v>702.75</v>
       </c>
       <c r="E46" s="7">
-        <v>-12.9</v>
+        <v>-18.3</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2617,13 +2617,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>3157.1</v>
+        <v>3250.2</v>
       </c>
       <c r="D47" s="6">
-        <v>3250.2</v>
-      </c>
-      <c r="E47" s="8">
-        <v>93.09999999999999</v>
+        <v>3128.6</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-121.6</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2634,13 +2634,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>8669.5</v>
+        <v>8812.5</v>
       </c>
       <c r="D48" s="6">
-        <v>8812.5</v>
-      </c>
-      <c r="E48" s="8">
-        <v>143</v>
+        <v>8580</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-232.5</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2648,16 +2648,16 @@
         <v>37</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C49" s="6">
-        <v>46.96</v>
+        <v>57</v>
       </c>
       <c r="D49" s="6">
-        <v>44.19</v>
+        <v>43</v>
       </c>
       <c r="E49" s="7">
-        <v>-2.77</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2665,220 +2665,271 @@
         <v>38</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C50" s="6">
-        <v>56.07</v>
+        <v>71</v>
       </c>
       <c r="D50" s="6">
-        <v>54.39</v>
+        <v>57</v>
       </c>
       <c r="E50" s="7">
-        <v>-1.68</v>
+        <v>-14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C51" s="6">
-        <v>52.47</v>
+        <v>43</v>
       </c>
       <c r="D51" s="6">
-        <v>49.94</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-2.53</v>
+        <v>71</v>
+      </c>
+      <c r="E51" s="8">
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>46.58</v>
+        <v>44.19</v>
       </c>
       <c r="D52" s="6">
-        <v>41.03</v>
+        <v>37.32</v>
       </c>
       <c r="E52" s="7">
-        <v>-5.55</v>
+        <v>-6.87</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>33.92</v>
+        <v>54.39</v>
       </c>
       <c r="D53" s="6">
-        <v>31.16</v>
+        <v>41.91</v>
       </c>
       <c r="E53" s="7">
-        <v>-2.76</v>
+        <v>-12.48</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>54.91</v>
+        <v>49.94</v>
       </c>
       <c r="D54" s="6">
-        <v>60.92</v>
-      </c>
-      <c r="E54" s="8">
-        <v>6.01</v>
+        <v>41.1</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-8.84</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>63.21</v>
+        <v>41.03</v>
       </c>
       <c r="D55" s="6">
-        <v>65.81999999999999</v>
+        <v>43.27</v>
       </c>
       <c r="E55" s="8">
-        <v>2.61</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>-6.42</v>
+        <v>31.16</v>
       </c>
       <c r="D56" s="6">
-        <v>-48.5</v>
+        <v>27.72</v>
       </c>
       <c r="E56" s="7">
-        <v>-42.08</v>
+        <v>-3.44</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>-16.76</v>
+        <v>60.92</v>
       </c>
       <c r="D57" s="6">
-        <v>-9.960000000000001</v>
-      </c>
-      <c r="E57" s="8">
-        <v>6.8</v>
+        <v>51.3</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-9.619999999999999</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>207.75</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="D58" s="6">
-        <v>54.69</v>
+        <v>58.54</v>
       </c>
       <c r="E58" s="7">
-        <v>-153.06</v>
+        <v>-7.28</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>-70.14</v>
+        <v>-48.5</v>
       </c>
       <c r="D59" s="6">
-        <v>-20.94</v>
+        <v>-12.79</v>
       </c>
       <c r="E59" s="8">
-        <v>49.2</v>
+        <v>35.71</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>-59.91</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="D60" s="6">
-        <v>-60.92</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-1.01</v>
+        <v>42.44</v>
+      </c>
+      <c r="E60" s="8">
+        <v>52.4</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>-52.82</v>
+        <v>54.69</v>
       </c>
       <c r="D61" s="6">
-        <v>-53.76</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-0.9399999999999999</v>
+        <v>70.39</v>
+      </c>
+      <c r="E61" s="8">
+        <v>15.7</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>1130.31</v>
+        <v>-20.94</v>
       </c>
       <c r="D62" s="6">
+        <v>-27.5</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-6.56</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-60.92</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-59.38</v>
+      </c>
+      <c r="E63" s="8">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>-53.76</v>
+      </c>
+      <c r="D64" s="6">
+        <v>-70.5</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-16.74</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
         <v>128.26</v>
       </c>
-      <c r="E62" s="7">
-        <v>-1002.05</v>
+      <c r="D65" s="6">
+        <v>178.63</v>
+      </c>
+      <c r="E65" s="8">
+        <v>50.37</v>
       </c>
     </row>
   </sheetData>
@@ -2943,16 +2994,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>49.6</v>
+        <v>43</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>-0.5</v>
+        <v>-3.8</v>
       </c>
       <c r="G2" s="11">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3083,25 +3134,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.5954</v>
+        <v>0.5772999999999999</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3247</v>
+        <v>0.2898</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2612</v>
+        <v>0.2553</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1924</v>
+        <v>0.1945</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1427</v>
+        <v>0.1377</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1218</v>
+        <v>0.1158</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0365</v>
+        <v>0.0266</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,34 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>54.4 → 41.9</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>54.4</t>
-  </si>
-  <si>
-    <t>41.9</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,15 +374,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -924,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1031.8</v>
+        <v>1051.6</v>
       </c>
       <c r="D2">
-        <v>-4.04</v>
+        <v>1.92</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -936,46 +908,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-16.9</v>
+        <v>-15.31</v>
       </c>
       <c r="H2">
-        <v>37.88</v>
+        <v>40.52</v>
       </c>
       <c r="I2">
-        <v>-6.54</v>
+        <v>-4.04</v>
       </c>
       <c r="J2">
-        <v>-10.4</v>
+        <v>-6.33</v>
       </c>
       <c r="K2">
-        <v>-3.16</v>
+        <v>-6.96</v>
       </c>
       <c r="L2">
-        <v>5.21</v>
+        <v>6.85</v>
       </c>
       <c r="M2">
-        <v>2.66</v>
+        <v>3.89</v>
       </c>
       <c r="N2">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="O2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P2">
-        <v>1077.44</v>
+        <v>1068.58</v>
       </c>
       <c r="Q2">
-        <v>1102.68</v>
+        <v>1098.96</v>
       </c>
       <c r="R2">
-        <v>1095.66</v>
+        <v>1094.57</v>
       </c>
       <c r="S2">
-        <v>956.1900000000001</v>
+        <v>957.12</v>
       </c>
       <c r="T2">
-        <v>7.91</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,43 +962,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>37.32</v>
+        <v>41.77</v>
       </c>
       <c r="Z2">
-        <v>-10.07</v>
+        <v>-12.17</v>
       </c>
       <c r="AA2">
-        <v>-3.02</v>
+        <v>-4.85</v>
       </c>
       <c r="AB2">
-        <v>-7.05</v>
+        <v>-7.32</v>
       </c>
       <c r="AC2">
-        <v>15.75</v>
+        <v>12.57</v>
       </c>
       <c r="AD2">
-        <v>24.5</v>
+        <v>17.95</v>
       </c>
       <c r="AE2">
-        <v>42.78</v>
+        <v>42.39</v>
       </c>
       <c r="AF2">
-        <v>-12.79</v>
+        <v>-54.63</v>
       </c>
       <c r="AG2">
-        <v>1159.9</v>
+        <v>1159.38</v>
       </c>
       <c r="AH2">
-        <v>1045.46</v>
+        <v>1038.54</v>
       </c>
       <c r="AI2">
-        <v>1181.33</v>
+        <v>1163.98</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>21.33</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>858</v>
+        <v>851.55</v>
       </c>
       <c r="D3">
-        <v>-5.61</v>
+        <v>-0.75</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1049,46 +1021,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-12.14</v>
+        <v>-12.8</v>
       </c>
       <c r="H3">
-        <v>62.05</v>
+        <v>60.83</v>
       </c>
       <c r="I3">
-        <v>-4.13</v>
+        <v>-6.5</v>
       </c>
       <c r="J3">
-        <v>-3.61</v>
+        <v>-5.26</v>
       </c>
       <c r="K3">
-        <v>-8.789999999999999</v>
+        <v>-11.64</v>
       </c>
       <c r="L3">
-        <v>11.83</v>
+        <v>8.69</v>
       </c>
       <c r="M3">
-        <v>57.73</v>
+        <v>57.49</v>
       </c>
       <c r="N3">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O3">
         <v>58</v>
       </c>
       <c r="P3">
-        <v>903.84</v>
+        <v>892.01</v>
       </c>
       <c r="Q3">
-        <v>889.4</v>
+        <v>887.26</v>
       </c>
       <c r="R3">
-        <v>888.4400000000001</v>
+        <v>887.26</v>
       </c>
       <c r="S3">
-        <v>781.84</v>
+        <v>782.71</v>
       </c>
       <c r="T3">
-        <v>9.74</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1103,43 +1075,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>41.91</v>
+        <v>40.64</v>
       </c>
       <c r="Z3">
-        <v>3.15</v>
+        <v>-0.53</v>
       </c>
       <c r="AA3">
-        <v>3.48</v>
+        <v>2.68</v>
       </c>
       <c r="AB3">
-        <v>-0.34</v>
+        <v>-3.21</v>
       </c>
       <c r="AC3">
-        <v>45.98</v>
+        <v>21.13</v>
       </c>
       <c r="AD3">
-        <v>70.65000000000001</v>
+        <v>48.81</v>
       </c>
       <c r="AE3">
-        <v>24.96</v>
+        <v>25.01</v>
       </c>
       <c r="AF3">
-        <v>42.44</v>
+        <v>-25.63</v>
       </c>
       <c r="AG3">
-        <v>928.08</v>
+        <v>929.38</v>
       </c>
       <c r="AH3">
-        <v>850.72</v>
+        <v>845.15</v>
       </c>
       <c r="AI3">
-        <v>853.38</v>
+        <v>926.39</v>
       </c>
       <c r="AJ3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK3">
-        <v>34.49</v>
+        <v>34.93</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1791.6</v>
+        <v>1765.6</v>
       </c>
       <c r="D4">
-        <v>-2.94</v>
+        <v>-1.45</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1162,46 +1134,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-7.65</v>
+        <v>-8.99</v>
       </c>
       <c r="H4">
-        <v>32.25</v>
+        <v>30.33</v>
       </c>
       <c r="I4">
-        <v>-3.06</v>
+        <v>-3.17</v>
       </c>
       <c r="J4">
-        <v>-5.43</v>
+        <v>-6.8</v>
       </c>
       <c r="K4">
-        <v>6.62</v>
+        <v>5.15</v>
       </c>
       <c r="L4">
-        <v>17.77</v>
+        <v>18.13</v>
       </c>
       <c r="M4">
-        <v>25.53</v>
+        <v>23.93</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="P4">
-        <v>1829.78</v>
+        <v>1818.22</v>
       </c>
       <c r="Q4">
-        <v>1850.14</v>
+        <v>1845.02</v>
       </c>
       <c r="R4">
-        <v>1836</v>
+        <v>1834.24</v>
       </c>
       <c r="S4">
-        <v>1681.93</v>
+        <v>1682.14</v>
       </c>
       <c r="T4">
-        <v>6.52</v>
+        <v>4.96</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1216,34 +1188,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>41.1</v>
+        <v>37.66</v>
       </c>
       <c r="Z4">
-        <v>-4.65</v>
+        <v>-10.09</v>
       </c>
       <c r="AA4">
-        <v>2.25</v>
+        <v>-0.22</v>
       </c>
       <c r="AB4">
-        <v>-6.9</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="AC4">
-        <v>48.78</v>
+        <v>20.28</v>
       </c>
       <c r="AD4">
-        <v>50.23</v>
+        <v>42.56</v>
       </c>
       <c r="AE4">
-        <v>47.65</v>
+        <v>47.42</v>
       </c>
       <c r="AF4">
-        <v>70.39</v>
+        <v>24.5</v>
       </c>
       <c r="AG4">
-        <v>1898.04</v>
+        <v>1905.2</v>
       </c>
       <c r="AH4">
-        <v>1802.24</v>
+        <v>1784.84</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1252,7 +1224,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>16.26</v>
+        <v>18.27</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1939.1</v>
+        <v>1937.8</v>
       </c>
       <c r="D5">
-        <v>0.52</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1275,46 +1247,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-19.16</v>
+        <v>-19.22</v>
       </c>
       <c r="H5">
-        <v>11.09</v>
+        <v>11.01</v>
       </c>
       <c r="I5">
-        <v>-1.8</v>
+        <v>-0.68</v>
       </c>
       <c r="J5">
-        <v>-7.45</v>
+        <v>-7.52</v>
       </c>
       <c r="K5">
-        <v>-5.86</v>
+        <v>-4.82</v>
       </c>
       <c r="L5">
-        <v>-12.26</v>
+        <v>-12.89</v>
       </c>
       <c r="M5">
-        <v>19.45</v>
+        <v>19.37</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P5">
-        <v>1948.76</v>
+        <v>1946.1</v>
       </c>
       <c r="Q5">
-        <v>1953.28</v>
+        <v>1947.03</v>
       </c>
       <c r="R5">
-        <v>2015.9</v>
+        <v>2013.17</v>
       </c>
       <c r="S5">
-        <v>2082.58</v>
+        <v>2080.48</v>
       </c>
       <c r="T5">
-        <v>-6.89</v>
+        <v>-6.86</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,34 +1301,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>43.27</v>
+        <v>43.04</v>
       </c>
       <c r="Z5">
-        <v>-21.77</v>
+        <v>-21.09</v>
       </c>
       <c r="AA5">
-        <v>-24.43</v>
+        <v>-23.76</v>
       </c>
       <c r="AB5">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="AC5">
-        <v>72.55</v>
+        <v>64.41</v>
       </c>
       <c r="AD5">
-        <v>79.90000000000001</v>
+        <v>72.48</v>
       </c>
       <c r="AE5">
-        <v>43.47</v>
+        <v>42.87</v>
       </c>
       <c r="AF5">
-        <v>-27.5</v>
+        <v>-31.44</v>
       </c>
       <c r="AG5">
-        <v>2039.01</v>
+        <v>2015.7</v>
       </c>
       <c r="AH5">
-        <v>1867.55</v>
+        <v>1878.37</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1365,7 +1337,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>19.76</v>
+        <v>21.01</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>702.75</v>
+        <v>703.05</v>
       </c>
       <c r="D6">
-        <v>-2.54</v>
+        <v>0.04</v>
       </c>
       <c r="E6">
         <v>1095.8</v>
@@ -1388,46 +1360,46 @@
         <v>702.75</v>
       </c>
       <c r="G6">
-        <v>-35.87</v>
+        <v>-35.84</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I6">
-        <v>-9.640000000000001</v>
+        <v>-7.94</v>
       </c>
       <c r="J6">
-        <v>-9.35</v>
+        <v>-11.24</v>
       </c>
       <c r="K6">
-        <v>-4.36</v>
+        <v>-4.03</v>
       </c>
       <c r="L6">
-        <v>-35.29</v>
+        <v>-35.15</v>
       </c>
       <c r="M6">
-        <v>11.58</v>
+        <v>10.7</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P6">
-        <v>735.63</v>
+        <v>723.5</v>
       </c>
       <c r="Q6">
-        <v>780.88</v>
+        <v>777</v>
       </c>
       <c r="R6">
-        <v>776.74</v>
+        <v>775.79</v>
       </c>
       <c r="S6">
-        <v>843.4</v>
+        <v>841.76</v>
       </c>
       <c r="T6">
-        <v>-16.68</v>
+        <v>-16.48</v>
       </c>
       <c r="U6" t="s">
         <v>45</v>
@@ -1442,43 +1414,43 @@
         <v>1</v>
       </c>
       <c r="Y6">
-        <v>27.72</v>
+        <v>27.86</v>
       </c>
       <c r="Z6">
-        <v>-14.37</v>
+        <v>-17.57</v>
       </c>
       <c r="AA6">
-        <v>-3.59</v>
+        <v>-6.39</v>
       </c>
       <c r="AB6">
-        <v>-10.78</v>
+        <v>-11.19</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AE6">
-        <v>24.5</v>
+        <v>24.28</v>
       </c>
       <c r="AF6">
-        <v>-59.38</v>
+        <v>-62.23</v>
       </c>
       <c r="AG6">
-        <v>843.58</v>
+        <v>848.72</v>
       </c>
       <c r="AH6">
-        <v>718.1799999999999</v>
+        <v>705.29</v>
       </c>
       <c r="AI6">
-        <v>784.02</v>
+        <v>769.1</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>31.31</v>
+        <v>34.17</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3128.6</v>
+        <v>3114.2</v>
       </c>
       <c r="D7">
-        <v>-3.74</v>
+        <v>-0.46</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1501,46 +1473,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-9.44</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="H7">
-        <v>65.41</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="I7">
-        <v>-1.19</v>
+        <v>-0.85</v>
       </c>
       <c r="J7">
-        <v>1.29</v>
+        <v>0.55</v>
       </c>
       <c r="K7">
-        <v>22.45</v>
+        <v>24.2</v>
       </c>
       <c r="L7">
-        <v>25.46</v>
+        <v>24.25</v>
       </c>
       <c r="M7">
-        <v>28.98</v>
+        <v>29.65</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="P7">
-        <v>3169.42</v>
+        <v>3164.06</v>
       </c>
       <c r="Q7">
-        <v>3255.84</v>
+        <v>3247.54</v>
       </c>
       <c r="R7">
-        <v>2874.41</v>
+        <v>2885.99</v>
       </c>
       <c r="S7">
-        <v>2458.06</v>
+        <v>2461.74</v>
       </c>
       <c r="T7">
-        <v>27.28</v>
+        <v>26.5</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1555,34 +1527,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>51.3</v>
+        <v>50.28</v>
       </c>
       <c r="Z7">
-        <v>76.31999999999999</v>
+        <v>64.34</v>
       </c>
       <c r="AA7">
-        <v>114.87</v>
+        <v>104.77</v>
       </c>
       <c r="AB7">
-        <v>-38.55</v>
+        <v>-40.43</v>
       </c>
       <c r="AC7">
-        <v>10.32</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="AD7">
-        <v>9</v>
+        <v>10.82</v>
       </c>
       <c r="AE7">
-        <v>138.94</v>
+        <v>141.84</v>
       </c>
       <c r="AF7">
-        <v>-70.5</v>
+        <v>-27.29</v>
       </c>
       <c r="AG7">
-        <v>3451.05</v>
+        <v>3452.28</v>
       </c>
       <c r="AH7">
-        <v>3060.62</v>
+        <v>3042.79</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1591,7 +1563,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>26.8</v>
+        <v>25.49</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,58 +1574,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8580</v>
+        <v>8663.5</v>
       </c>
       <c r="D8">
-        <v>-2.64</v>
+        <v>0.97</v>
       </c>
       <c r="E8">
-        <v>9697.559999999999</v>
+        <v>9694.08</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-11.52</v>
+        <v>-10.63</v>
       </c>
       <c r="H8">
-        <v>44.82</v>
+        <v>46.23</v>
       </c>
       <c r="I8">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="J8">
-        <v>8.17</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="K8">
-        <v>9.960000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="L8">
-        <v>-12.34</v>
+        <v>-10.66</v>
       </c>
       <c r="M8">
-        <v>13.77</v>
+        <v>14.45</v>
       </c>
       <c r="N8">
         <v>71</v>
       </c>
       <c r="O8">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P8">
-        <v>8542.299999999999</v>
+        <v>8591.200000000001</v>
       </c>
       <c r="Q8">
-        <v>8267.15</v>
+        <v>8297.58</v>
       </c>
       <c r="R8">
-        <v>8061.28</v>
+        <v>8076.47</v>
       </c>
       <c r="S8">
-        <v>7409.49</v>
+        <v>7411.98</v>
       </c>
       <c r="T8">
-        <v>15.8</v>
+        <v>16.89</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1668,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>58.54</v>
+        <v>60.24</v>
       </c>
       <c r="Z8">
-        <v>148.39</v>
+        <v>158.1</v>
       </c>
       <c r="AA8">
-        <v>104.64</v>
+        <v>115.33</v>
       </c>
       <c r="AB8">
-        <v>43.74</v>
+        <v>42.77</v>
       </c>
       <c r="AC8">
-        <v>87.17</v>
+        <v>77.33</v>
       </c>
       <c r="AD8">
-        <v>79.40000000000001</v>
+        <v>81.20999999999999</v>
       </c>
       <c r="AE8">
-        <v>313.89</v>
+        <v>327.61</v>
       </c>
       <c r="AF8">
-        <v>178.63</v>
+        <v>6.19</v>
       </c>
       <c r="AG8">
-        <v>8705.17</v>
+        <v>8757.530000000001</v>
       </c>
       <c r="AH8">
-        <v>7829.13</v>
+        <v>7837.62</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
@@ -1704,7 +1676,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>46.81</v>
+        <v>46.48</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1865,47 +1837,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1913,1023 +1850,1006 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-9.24</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-10.4</v>
       </c>
-      <c r="E7" s="7">
-        <v>-1.16</v>
+      <c r="D7" s="5">
+        <v>-6.33</v>
+      </c>
+      <c r="E7" s="6">
+        <v>4.07</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>2.53</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-3.61</v>
       </c>
+      <c r="D8" s="5">
+        <v>-5.26</v>
+      </c>
       <c r="E8" s="7">
-        <v>-6.14</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-4.25</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-5.43</v>
       </c>
+      <c r="D9" s="5">
+        <v>-6.8</v>
+      </c>
       <c r="E9" s="7">
-        <v>-1.18</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
+        <v>-7.45</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-7.52</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-9.35</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-11.24</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>1.29</v>
+      </c>
+      <c r="D12" s="5">
+        <v>0.55</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>8.17</v>
+      </c>
+      <c r="D13" s="5">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="E13" s="6">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-6.54</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-4.04</v>
+      </c>
+      <c r="E14" s="6">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-4.13</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-6.5</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-2.37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-3.06</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-3.17</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-1.8</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-0.68</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-9.640000000000001</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-7.94</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-1.19</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-0.85</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>2.88</v>
+      </c>
+      <c r="D20" s="5">
+        <v>2.9</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>5.21</v>
+      </c>
+      <c r="D21" s="5">
+        <v>6.85</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>11.83</v>
+      </c>
+      <c r="D22" s="5">
+        <v>8.69</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-3.14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>17.77</v>
+      </c>
+      <c r="D23" s="5">
+        <v>18.13</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-12.26</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-12.89</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-35.29</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-35.15</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>25.46</v>
+      </c>
+      <c r="D26" s="5">
+        <v>24.25</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-12.34</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-10.66</v>
+      </c>
+      <c r="E27" s="6">
+        <v>1.68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-3.16</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-6.96</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-3.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-8.789999999999999</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-11.64</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-2.85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>6.62</v>
+      </c>
+      <c r="D30" s="5">
+        <v>5.15</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-5.86</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-4.82</v>
+      </c>
+      <c r="E31" s="6">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-4.36</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-4.03</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>22.45</v>
+      </c>
+      <c r="D33" s="5">
+        <v>24.2</v>
+      </c>
+      <c r="E33" s="6">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="D34" s="5">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-16.9</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-15.31</v>
+      </c>
+      <c r="E35" s="6">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-12.14</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-12.8</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
         <v>-7.65</v>
       </c>
-      <c r="D10" s="6">
-        <v>-7.45</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D37" s="5">
+        <v>-8.99</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-19.16</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-19.22</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-7.59</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-9.35</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-35.87</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-35.84</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>12.56</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1.29</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-11.27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-9.44</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>10.36</v>
-      </c>
-      <c r="D13" s="6">
-        <v>8.17</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-2.19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-11.52</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-10.63</v>
+      </c>
+      <c r="E41" s="6">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-4.9</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-6.54</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1031.8</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1051.6</v>
+      </c>
+      <c r="E42" s="6">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>2.02</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-4.13</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-6.15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>858</v>
+      </c>
+      <c r="D43" s="5">
+        <v>851.55</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-6.45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.38</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.06</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1791.6</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1765.6</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-0.51</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-1.8</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1939.1</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1937.8</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-7.72</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-9.640000000000001</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>702.75</v>
+      </c>
+      <c r="D46" s="5">
+        <v>703.05</v>
+      </c>
+      <c r="E46" s="6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>1.74</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.19</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.93</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>3128.6</v>
+      </c>
+      <c r="D47" s="5">
+        <v>3114.2</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-14.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>8</v>
-      </c>
-      <c r="D20" s="6">
-        <v>2.88</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-5.12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>8580</v>
+      </c>
+      <c r="D48" s="5">
+        <v>8663.5</v>
+      </c>
+      <c r="E48" s="6">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>10.61</v>
-      </c>
-      <c r="D21" s="6">
-        <v>5.21</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-5.4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="5">
+        <v>43</v>
+      </c>
+      <c r="D49" s="5">
+        <v>57</v>
+      </c>
+      <c r="E49" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>23.09</v>
-      </c>
-      <c r="D22" s="6">
-        <v>11.83</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-11.26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>22.57</v>
-      </c>
-      <c r="D23" s="6">
-        <v>17.77</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-12.62</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-12.26</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-32.64</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-35.29</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-2.65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>33.65</v>
-      </c>
-      <c r="D26" s="6">
-        <v>25.46</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-8.19</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="5">
+        <v>57</v>
+      </c>
+      <c r="D50" s="5">
         <v>43</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-10.17</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-12.34</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>0.87</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-3.16</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-4.03</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-2.83</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-5.96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>11.63</v>
-      </c>
-      <c r="D30" s="6">
-        <v>6.62</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-5.01</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-2.88</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-5.86</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-2.98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-0.63</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-4.36</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-3.73</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>28.4</v>
-      </c>
-      <c r="D33" s="6">
-        <v>22.45</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-5.95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>10.72</v>
-      </c>
-      <c r="D34" s="6">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-13.41</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-16.9</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-3.49</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-6.91</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-12.14</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-5.23</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-4.85</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-7.65</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-19.58</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-19.16</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-34.2</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-35.87</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-5.92</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-9.44</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-3.52</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-11.52</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1075.2</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1031.8</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-43.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>909</v>
-      </c>
-      <c r="D43" s="6">
-        <v>858</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-51</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1845.9</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1791.6</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-54.3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1929</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1939.1</v>
-      </c>
-      <c r="E45" s="8">
-        <v>10.1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>721.05</v>
-      </c>
-      <c r="D46" s="6">
-        <v>702.75</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-18.3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>3250.2</v>
-      </c>
-      <c r="D47" s="6">
-        <v>3128.6</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-121.6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>8812.5</v>
-      </c>
-      <c r="D48" s="6">
-        <v>8580</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-232.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="6">
-        <v>57</v>
-      </c>
-      <c r="D49" s="6">
-        <v>43</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="6">
-        <v>71</v>
-      </c>
-      <c r="D50" s="6">
-        <v>57</v>
       </c>
       <c r="E50" s="7">
         <v>-14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>37.32</v>
+      </c>
+      <c r="D51" s="5">
+        <v>41.77</v>
+      </c>
+      <c r="E51" s="6">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>41.91</v>
+      </c>
+      <c r="D52" s="5">
+        <v>40.64</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>41.1</v>
+      </c>
+      <c r="D53" s="5">
+        <v>37.66</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-3.44</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>43.27</v>
+      </c>
+      <c r="D54" s="5">
+        <v>43.04</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>27.72</v>
+      </c>
+      <c r="D55" s="5">
+        <v>27.86</v>
+      </c>
+      <c r="E55" s="6">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>51.3</v>
+      </c>
+      <c r="D56" s="5">
+        <v>50.28</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-1.02</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="6">
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>58.54</v>
+      </c>
+      <c r="D57" s="5">
+        <v>60.24</v>
+      </c>
+      <c r="E57" s="6">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-12.79</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-54.63</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-41.84</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>42.44</v>
+      </c>
+      <c r="D59" s="5">
+        <v>-25.63</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-68.06999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>70.39</v>
+      </c>
+      <c r="D60" s="5">
+        <v>24.5</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-45.89</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-27.5</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-31.44</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-3.94</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="5">
+        <v>-59.38</v>
+      </c>
+      <c r="D62" s="5">
+        <v>-62.23</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-2.85</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>-70.5</v>
+      </c>
+      <c r="D63" s="5">
+        <v>-27.29</v>
+      </c>
+      <c r="E63" s="6">
+        <v>43.21</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D51" s="6">
-        <v>71</v>
-      </c>
-      <c r="E51" s="8">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>44.19</v>
-      </c>
-      <c r="D52" s="6">
-        <v>37.32</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-6.87</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>54.39</v>
-      </c>
-      <c r="D53" s="6">
-        <v>41.91</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-12.48</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>49.94</v>
-      </c>
-      <c r="D54" s="6">
-        <v>41.1</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-8.84</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>41.03</v>
-      </c>
-      <c r="D55" s="6">
-        <v>43.27</v>
-      </c>
-      <c r="E55" s="8">
-        <v>2.24</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>31.16</v>
-      </c>
-      <c r="D56" s="6">
-        <v>27.72</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>60.92</v>
-      </c>
-      <c r="D57" s="6">
-        <v>51.3</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-9.619999999999999</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>65.81999999999999</v>
-      </c>
-      <c r="D58" s="6">
-        <v>58.54</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-7.28</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="5" t="s">
+      <c r="B64" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="6">
-        <v>-48.5</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-12.79</v>
-      </c>
-      <c r="E59" s="8">
-        <v>35.71</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-9.960000000000001</v>
-      </c>
-      <c r="D60" s="6">
-        <v>42.44</v>
-      </c>
-      <c r="E60" s="8">
-        <v>52.4</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>54.69</v>
-      </c>
-      <c r="D61" s="6">
-        <v>70.39</v>
-      </c>
-      <c r="E61" s="8">
-        <v>15.7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-20.94</v>
-      </c>
-      <c r="D62" s="6">
-        <v>-27.5</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-6.56</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-60.92</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-59.38</v>
-      </c>
-      <c r="E63" s="8">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-53.76</v>
-      </c>
-      <c r="D64" s="6">
-        <v>-70.5</v>
+      <c r="C64" s="5">
+        <v>178.63</v>
+      </c>
+      <c r="D64" s="5">
+        <v>6.19</v>
       </c>
       <c r="E64" s="7">
-        <v>-16.74</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>128.26</v>
-      </c>
-      <c r="D65" s="6">
-        <v>178.63</v>
-      </c>
-      <c r="E65" s="8">
-        <v>50.37</v>
+        <v>-172.44</v>
       </c>
     </row>
   </sheetData>
@@ -2955,60 +2875,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="11">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10">
+        <v>43.1</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="11">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="12">
-        <v>7</v>
-      </c>
-      <c r="D2" s="11">
-        <v>43</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-3.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>2.4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-3.9</v>
+      </c>
+      <c r="G2" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>70</v>
       </c>
     </row>
@@ -3110,49 +3030,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.5772999999999999</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2898</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2553</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1945</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1377</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1158</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0266</v>
+      <c r="A2" s="13">
+        <v>0.5749</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2965</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.2393</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1937</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1445</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.107</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.0389</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,40 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>50.3 → 45.9</t>
+  </si>
+  <si>
+    <t>50.3</t>
+  </si>
+  <si>
+    <t>45.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -258,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -298,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,17 +407,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -896,10 +930,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1051.6</v>
+        <v>1083.6</v>
       </c>
       <c r="D2">
-        <v>1.92</v>
+        <v>3.04</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -908,46 +942,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-15.31</v>
+        <v>-12.73</v>
       </c>
       <c r="H2">
-        <v>40.52</v>
+        <v>44.8</v>
       </c>
       <c r="I2">
-        <v>-4.04</v>
+        <v>-0.96</v>
       </c>
       <c r="J2">
-        <v>-6.33</v>
+        <v>-3.77</v>
       </c>
       <c r="K2">
-        <v>-6.96</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L2">
-        <v>6.85</v>
+        <v>9.32</v>
       </c>
       <c r="M2">
-        <v>3.89</v>
+        <v>5.1</v>
       </c>
       <c r="N2">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O2">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="P2">
-        <v>1068.58</v>
+        <v>1066.48</v>
       </c>
       <c r="Q2">
-        <v>1098.96</v>
+        <v>1098.78</v>
       </c>
       <c r="R2">
-        <v>1094.57</v>
+        <v>1094.63</v>
       </c>
       <c r="S2">
-        <v>957.12</v>
+        <v>958.26</v>
       </c>
       <c r="T2">
-        <v>9.869999999999999</v>
+        <v>13.08</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,34 +996,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>41.77</v>
+        <v>48.17</v>
       </c>
       <c r="Z2">
-        <v>-12.17</v>
+        <v>-11.13</v>
       </c>
       <c r="AA2">
-        <v>-4.85</v>
+        <v>-6.11</v>
       </c>
       <c r="AB2">
-        <v>-7.32</v>
+        <v>-5.02</v>
       </c>
       <c r="AC2">
-        <v>12.57</v>
+        <v>30.43</v>
       </c>
       <c r="AD2">
-        <v>17.95</v>
+        <v>19.58</v>
       </c>
       <c r="AE2">
-        <v>42.39</v>
+        <v>42.92</v>
       </c>
       <c r="AF2">
-        <v>-54.63</v>
+        <v>7.21</v>
       </c>
       <c r="AG2">
-        <v>1159.38</v>
+        <v>1159.37</v>
       </c>
       <c r="AH2">
-        <v>1038.54</v>
+        <v>1038.19</v>
       </c>
       <c r="AI2">
         <v>1163.98</v>
@@ -998,7 +1032,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>21.87</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1043,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>851.55</v>
+        <v>880</v>
       </c>
       <c r="D3">
-        <v>-0.75</v>
+        <v>3.34</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1021,46 +1055,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-12.8</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="H3">
-        <v>60.83</v>
+        <v>66.2</v>
       </c>
       <c r="I3">
-        <v>-6.5</v>
+        <v>-5.06</v>
       </c>
       <c r="J3">
-        <v>-5.26</v>
+        <v>-1.59</v>
       </c>
       <c r="K3">
-        <v>-11.64</v>
+        <v>-7.8</v>
       </c>
       <c r="L3">
-        <v>8.69</v>
+        <v>12.29</v>
       </c>
       <c r="M3">
-        <v>57.49</v>
+        <v>57.45</v>
       </c>
       <c r="N3">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="O3">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="P3">
-        <v>892.01</v>
+        <v>882.62</v>
       </c>
       <c r="Q3">
-        <v>887.26</v>
+        <v>888.11</v>
       </c>
       <c r="R3">
-        <v>887.26</v>
+        <v>886.7</v>
       </c>
       <c r="S3">
-        <v>782.71</v>
+        <v>783.76</v>
       </c>
       <c r="T3">
-        <v>8.789999999999999</v>
+        <v>12.28</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1075,34 +1109,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>40.64</v>
+        <v>48.11</v>
       </c>
       <c r="Z3">
-        <v>-0.53</v>
+        <v>-1.13</v>
       </c>
       <c r="AA3">
-        <v>2.68</v>
+        <v>1.92</v>
       </c>
       <c r="AB3">
-        <v>-3.21</v>
+        <v>-3.05</v>
       </c>
       <c r="AC3">
-        <v>21.13</v>
+        <v>12.91</v>
       </c>
       <c r="AD3">
-        <v>48.81</v>
+        <v>26.67</v>
       </c>
       <c r="AE3">
-        <v>25.01</v>
+        <v>25.49</v>
       </c>
       <c r="AF3">
-        <v>-25.63</v>
+        <v>-7.15</v>
       </c>
       <c r="AG3">
-        <v>929.38</v>
+        <v>928.84</v>
       </c>
       <c r="AH3">
-        <v>845.15</v>
+        <v>847.39</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1111,7 +1145,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>34.93</v>
+        <v>31.95</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1156,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1765.6</v>
+        <v>1764.5</v>
       </c>
       <c r="D4">
-        <v>-1.45</v>
+        <v>-0.06</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1134,46 +1168,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-8.99</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="H4">
-        <v>30.33</v>
+        <v>30.25</v>
       </c>
       <c r="I4">
-        <v>-3.17</v>
+        <v>-3.53</v>
       </c>
       <c r="J4">
-        <v>-6.8</v>
+        <v>-5.54</v>
       </c>
       <c r="K4">
-        <v>5.15</v>
+        <v>4.48</v>
       </c>
       <c r="L4">
-        <v>18.13</v>
+        <v>16.76</v>
       </c>
       <c r="M4">
-        <v>23.93</v>
+        <v>24.02</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P4">
-        <v>1818.22</v>
+        <v>1805.32</v>
       </c>
       <c r="Q4">
-        <v>1845.02</v>
+        <v>1839.57</v>
       </c>
       <c r="R4">
-        <v>1834.24</v>
+        <v>1834.14</v>
       </c>
       <c r="S4">
-        <v>1682.14</v>
+        <v>1682.29</v>
       </c>
       <c r="T4">
-        <v>4.96</v>
+        <v>4.89</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1188,34 +1222,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>37.66</v>
+        <v>37.52</v>
       </c>
       <c r="Z4">
-        <v>-10.09</v>
+        <v>-14.33</v>
       </c>
       <c r="AA4">
-        <v>-0.22</v>
+        <v>-3.04</v>
       </c>
       <c r="AB4">
-        <v>-9.869999999999999</v>
+        <v>-11.29</v>
       </c>
       <c r="AC4">
-        <v>20.28</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>42.56</v>
+        <v>23.02</v>
       </c>
       <c r="AE4">
-        <v>47.42</v>
+        <v>47.29</v>
       </c>
       <c r="AF4">
-        <v>24.5</v>
+        <v>66.97</v>
       </c>
       <c r="AG4">
-        <v>1905.2</v>
+        <v>1908.06</v>
       </c>
       <c r="AH4">
-        <v>1784.84</v>
+        <v>1771.08</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1224,7 +1258,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>18.27</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1269,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1937.8</v>
+        <v>1929.8</v>
       </c>
       <c r="D5">
-        <v>-0.07000000000000001</v>
+        <v>-0.41</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1247,46 +1281,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-19.22</v>
+        <v>-19.55</v>
       </c>
       <c r="H5">
-        <v>11.01</v>
+        <v>10.55</v>
       </c>
       <c r="I5">
-        <v>-0.68</v>
+        <v>-1.68</v>
       </c>
       <c r="J5">
-        <v>-7.52</v>
+        <v>-6.44</v>
       </c>
       <c r="K5">
-        <v>-4.82</v>
+        <v>-6.69</v>
       </c>
       <c r="L5">
-        <v>-12.89</v>
+        <v>-13.07</v>
       </c>
       <c r="M5">
-        <v>19.37</v>
+        <v>20.02</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="P5">
-        <v>1946.1</v>
+        <v>1939.52</v>
       </c>
       <c r="Q5">
-        <v>1947.03</v>
+        <v>1941.62</v>
       </c>
       <c r="R5">
-        <v>2013.17</v>
+        <v>2011.58</v>
       </c>
       <c r="S5">
-        <v>2080.48</v>
+        <v>2078.27</v>
       </c>
       <c r="T5">
-        <v>-6.86</v>
+        <v>-7.14</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1301,34 +1335,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>43.04</v>
+        <v>41.6</v>
       </c>
       <c r="Z5">
-        <v>-21.09</v>
+        <v>-20.95</v>
       </c>
       <c r="AA5">
-        <v>-23.76</v>
+        <v>-23.2</v>
       </c>
       <c r="AB5">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AC5">
-        <v>64.41</v>
+        <v>63.32</v>
       </c>
       <c r="AD5">
-        <v>72.48</v>
+        <v>66.76000000000001</v>
       </c>
       <c r="AE5">
-        <v>42.87</v>
+        <v>41.61</v>
       </c>
       <c r="AF5">
-        <v>-31.44</v>
+        <v>-6.77</v>
       </c>
       <c r="AG5">
-        <v>2015.7</v>
+        <v>1995.55</v>
       </c>
       <c r="AH5">
-        <v>1878.37</v>
+        <v>1887.69</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1337,7 +1371,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>21.01</v>
+        <v>21.68</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1382,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>703.05</v>
+        <v>703.1</v>
       </c>
       <c r="D6">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="E6">
         <v>1095.8</v>
@@ -1363,46 +1397,46 @@
         <v>-35.84</v>
       </c>
       <c r="H6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="I6">
-        <v>-7.94</v>
+        <v>-7.08</v>
       </c>
       <c r="J6">
-        <v>-11.24</v>
+        <v>-9.93</v>
       </c>
       <c r="K6">
-        <v>-4.03</v>
+        <v>-2.54</v>
       </c>
       <c r="L6">
-        <v>-35.15</v>
+        <v>-34.45</v>
       </c>
       <c r="M6">
-        <v>10.7</v>
+        <v>11.24</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P6">
-        <v>723.5</v>
+        <v>712.78</v>
       </c>
       <c r="Q6">
-        <v>777</v>
+        <v>772.8</v>
       </c>
       <c r="R6">
-        <v>775.79</v>
+        <v>775.42</v>
       </c>
       <c r="S6">
-        <v>841.76</v>
+        <v>840.13</v>
       </c>
       <c r="T6">
-        <v>-16.48</v>
+        <v>-16.31</v>
       </c>
       <c r="U6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V6" t="s">
         <v>46</v>
@@ -1411,37 +1445,37 @@
         <v>46</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>27.86</v>
+        <v>27.88</v>
       </c>
       <c r="Z6">
-        <v>-17.57</v>
+        <v>-19.88</v>
       </c>
       <c r="AA6">
-        <v>-6.39</v>
+        <v>-9.09</v>
       </c>
       <c r="AB6">
-        <v>-11.19</v>
+        <v>-10.8</v>
       </c>
       <c r="AC6">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="AD6">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="AE6">
-        <v>24.28</v>
+        <v>23.1</v>
       </c>
       <c r="AF6">
-        <v>-62.23</v>
+        <v>-80.59999999999999</v>
       </c>
       <c r="AG6">
-        <v>848.72</v>
+        <v>851.53</v>
       </c>
       <c r="AH6">
-        <v>705.29</v>
+        <v>694.08</v>
       </c>
       <c r="AI6">
         <v>769.1</v>
@@ -1450,7 +1484,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>34.17</v>
+        <v>36.66</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1495,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3114.2</v>
+        <v>3049.7</v>
       </c>
       <c r="D7">
-        <v>-0.46</v>
+        <v>-2.07</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1473,46 +1507,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-9.859999999999999</v>
+        <v>-11.73</v>
       </c>
       <c r="H7">
-        <v>64.65000000000001</v>
+        <v>61.24</v>
       </c>
       <c r="I7">
-        <v>-0.85</v>
+        <v>-3.8</v>
       </c>
       <c r="J7">
-        <v>0.55</v>
+        <v>-7.03</v>
       </c>
       <c r="K7">
-        <v>24.2</v>
+        <v>21.4</v>
       </c>
       <c r="L7">
-        <v>24.25</v>
+        <v>23.79</v>
       </c>
       <c r="M7">
-        <v>29.65</v>
+        <v>29.23</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P7">
-        <v>3164.06</v>
+        <v>3139.96</v>
       </c>
       <c r="Q7">
-        <v>3247.54</v>
+        <v>3243.65</v>
       </c>
       <c r="R7">
-        <v>2885.99</v>
+        <v>2896.69</v>
       </c>
       <c r="S7">
-        <v>2461.74</v>
+        <v>2465.22</v>
       </c>
       <c r="T7">
-        <v>26.5</v>
+        <v>23.71</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,34 +1561,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>50.28</v>
+        <v>45.91</v>
       </c>
       <c r="Z7">
-        <v>64.34</v>
+        <v>49.07</v>
       </c>
       <c r="AA7">
-        <v>104.77</v>
+        <v>93.63</v>
       </c>
       <c r="AB7">
-        <v>-40.43</v>
+        <v>-44.56</v>
       </c>
       <c r="AC7">
-        <v>9.210000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>10.82</v>
+        <v>6.51</v>
       </c>
       <c r="AE7">
-        <v>141.84</v>
+        <v>142.01</v>
       </c>
       <c r="AF7">
-        <v>-27.29</v>
+        <v>-6.35</v>
       </c>
       <c r="AG7">
-        <v>3452.28</v>
+        <v>3460.58</v>
       </c>
       <c r="AH7">
-        <v>3042.79</v>
+        <v>3026.71</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1563,7 +1597,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>25.49</v>
+        <v>24.35</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1608,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8663.5</v>
+        <v>8765</v>
       </c>
       <c r="D8">
-        <v>0.97</v>
+        <v>1.17</v>
       </c>
       <c r="E8">
         <v>9694.08</v>
@@ -1586,46 +1620,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-10.63</v>
+        <v>-9.58</v>
       </c>
       <c r="H8">
-        <v>46.23</v>
+        <v>47.94</v>
       </c>
       <c r="I8">
-        <v>2.9</v>
+        <v>6.49</v>
       </c>
       <c r="J8">
-        <v>9.220000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="K8">
-        <v>9.949999999999999</v>
+        <v>11.3</v>
       </c>
       <c r="L8">
-        <v>-10.66</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="M8">
-        <v>14.45</v>
+        <v>15.11</v>
       </c>
       <c r="N8">
         <v>71</v>
       </c>
       <c r="O8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P8">
-        <v>8591.200000000001</v>
+        <v>8698.1</v>
       </c>
       <c r="Q8">
-        <v>8297.58</v>
+        <v>8337.450000000001</v>
       </c>
       <c r="R8">
-        <v>8076.47</v>
+        <v>8098.48</v>
       </c>
       <c r="S8">
-        <v>7411.98</v>
+        <v>7415.66</v>
       </c>
       <c r="T8">
-        <v>16.89</v>
+        <v>18.2</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1640,34 +1674,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>60.24</v>
+        <v>62.27</v>
       </c>
       <c r="Z8">
-        <v>158.1</v>
+        <v>172.01</v>
       </c>
       <c r="AA8">
-        <v>115.33</v>
+        <v>126.67</v>
       </c>
       <c r="AB8">
-        <v>42.77</v>
+        <v>45.34</v>
       </c>
       <c r="AC8">
-        <v>77.33</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="AD8">
-        <v>81.20999999999999</v>
+        <v>78.52</v>
       </c>
       <c r="AE8">
-        <v>327.61</v>
+        <v>325.24</v>
       </c>
       <c r="AF8">
-        <v>6.19</v>
+        <v>-33.29</v>
       </c>
       <c r="AG8">
-        <v>8757.530000000001</v>
+        <v>8814.860000000001</v>
       </c>
       <c r="AH8">
-        <v>7837.62</v>
+        <v>7860.04</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
@@ -1676,7 +1710,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>46.48</v>
+        <v>46.54</v>
       </c>
     </row>
   </sheetData>
@@ -1837,1025 +1871,1063 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-10.4</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>-6.33</v>
       </c>
-      <c r="E7" s="6">
-        <v>4.07</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>-3.77</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-3.61</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-5.26</v>
       </c>
-      <c r="E8" s="7">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>-1.59</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3.67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-5.43</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-6.8</v>
       </c>
-      <c r="E9" s="7">
+      <c r="D10" s="6">
+        <v>-5.54</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-7.52</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-6.44</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-11.24</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-9.93</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.55</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-7.03</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-7.58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="6">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="D14" s="6">
+        <v>8.81</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-4.04</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-0.96</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-6.5</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-5.06</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-3.17</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-3.53</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-0.68</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-1.68</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-7.94</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-7.08</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-0.85</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-3.8</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>2.9</v>
+      </c>
+      <c r="D21" s="6">
+        <v>6.49</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>6.85</v>
+      </c>
+      <c r="D22" s="6">
+        <v>9.32</v>
+      </c>
+      <c r="E22" s="7">
+        <v>2.47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>8.69</v>
+      </c>
+      <c r="D23" s="6">
+        <v>12.29</v>
+      </c>
+      <c r="E23" s="7">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>18.13</v>
+      </c>
+      <c r="D24" s="6">
+        <v>16.76</v>
+      </c>
+      <c r="E24" s="8">
         <v>-1.37</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-7.45</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-7.52</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-12.89</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-13.07</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-9.35</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-11.24</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.89</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-35.15</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-34.45</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>1.29</v>
-      </c>
-      <c r="D12" s="5">
-        <v>0.55</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>24.25</v>
+      </c>
+      <c r="D27" s="6">
+        <v>23.79</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>8.17</v>
-      </c>
-      <c r="D13" s="5">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="E13" s="6">
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-10.66</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-8.880000000000001</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-6.96</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-9.109999999999999</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-2.15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-11.64</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-7.8</v>
+      </c>
+      <c r="E30" s="7">
+        <v>3.84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>5.15</v>
+      </c>
+      <c r="D31" s="6">
+        <v>4.48</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-4.82</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-6.69</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-4.03</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-2.54</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>24.2</v>
+      </c>
+      <c r="D34" s="6">
+        <v>21.4</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="D35" s="6">
+        <v>11.3</v>
+      </c>
+      <c r="E35" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-15.31</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-12.73</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-12.8</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-9.880000000000001</v>
+      </c>
+      <c r="E37" s="7">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-8.99</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-19.22</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-19.55</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-11.73</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.87</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-10.63</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-9.58</v>
+      </c>
+      <c r="E41" s="7">
         <v>1.05</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-6.54</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-4.04</v>
-      </c>
-      <c r="E14" s="6">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1051.6</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1083.6</v>
+      </c>
+      <c r="E42" s="7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-4.13</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-6.5</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-2.37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>851.55</v>
+      </c>
+      <c r="D43" s="6">
+        <v>880</v>
+      </c>
+      <c r="E43" s="7">
+        <v>28.45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-3.06</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-3.17</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>1765.6</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1764.5</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-1.8</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-0.68</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1.12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1937.8</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1929.8</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-9.640000000000001</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-7.94</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>703.05</v>
+      </c>
+      <c r="D46" s="6">
+        <v>703.1</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-1.19</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-0.85</v>
-      </c>
-      <c r="E19" s="6">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>3114.2</v>
+      </c>
+      <c r="D47" s="6">
+        <v>3049.7</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-64.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>2.88</v>
-      </c>
-      <c r="D20" s="5">
-        <v>2.9</v>
-      </c>
-      <c r="E20" s="6">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>8663.5</v>
+      </c>
+      <c r="D48" s="6">
+        <v>8765</v>
+      </c>
+      <c r="E48" s="7">
+        <v>101.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="6">
+        <v>57</v>
+      </c>
+      <c r="D49" s="6">
+        <v>43</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="6">
+        <v>43</v>
+      </c>
+      <c r="D50" s="6">
+        <v>57</v>
+      </c>
+      <c r="E50" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>41.77</v>
+      </c>
+      <c r="D51" s="6">
+        <v>48.17</v>
+      </c>
+      <c r="E51" s="7">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>40.64</v>
+      </c>
+      <c r="D52" s="6">
+        <v>48.11</v>
+      </c>
+      <c r="E52" s="7">
+        <v>7.47</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>37.66</v>
+      </c>
+      <c r="D53" s="6">
+        <v>37.52</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>43.04</v>
+      </c>
+      <c r="D54" s="6">
+        <v>41.6</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>27.86</v>
+      </c>
+      <c r="D55" s="6">
+        <v>27.88</v>
+      </c>
+      <c r="E55" s="7">
         <v>0.02</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>50.28</v>
+      </c>
+      <c r="D56" s="6">
+        <v>45.91</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-4.37</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>60.24</v>
+      </c>
+      <c r="D57" s="6">
+        <v>62.27</v>
+      </c>
+      <c r="E57" s="7">
+        <v>2.03</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>5.21</v>
-      </c>
-      <c r="D21" s="5">
-        <v>6.85</v>
-      </c>
-      <c r="E21" s="6">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-54.63</v>
+      </c>
+      <c r="D58" s="6">
+        <v>7.21</v>
+      </c>
+      <c r="E58" s="7">
+        <v>61.84</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>11.83</v>
-      </c>
-      <c r="D22" s="5">
-        <v>8.69</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-3.14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>-25.63</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-7.15</v>
+      </c>
+      <c r="E59" s="7">
+        <v>18.48</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>17.77</v>
-      </c>
-      <c r="D23" s="5">
-        <v>18.13</v>
-      </c>
-      <c r="E23" s="6">
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>24.5</v>
+      </c>
+      <c r="D60" s="6">
+        <v>66.97</v>
+      </c>
+      <c r="E60" s="7">
+        <v>42.47</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-12.26</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-12.89</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-31.44</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-6.77</v>
+      </c>
+      <c r="E61" s="7">
+        <v>24.67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-35.29</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-35.15</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
+        <v>-62.23</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-80.59999999999999</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-18.37</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>25.46</v>
-      </c>
-      <c r="D26" s="5">
-        <v>24.25</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-27.29</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-6.35</v>
+      </c>
+      <c r="E63" s="7">
+        <v>20.94</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-12.34</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-10.66</v>
-      </c>
-      <c r="E27" s="6">
-        <v>1.68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-3.16</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-6.96</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-3.8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-8.789999999999999</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-11.64</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>6.62</v>
-      </c>
-      <c r="D30" s="5">
-        <v>5.15</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-5.86</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-4.82</v>
-      </c>
-      <c r="E31" s="6">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-4.36</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-4.03</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>22.45</v>
-      </c>
-      <c r="D33" s="5">
-        <v>24.2</v>
-      </c>
-      <c r="E33" s="6">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>9.960000000000001</v>
-      </c>
-      <c r="D34" s="5">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-16.9</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-15.31</v>
-      </c>
-      <c r="E35" s="6">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-12.14</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-12.8</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-7.65</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-8.99</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-1.34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-19.16</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-19.22</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-35.87</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-35.84</v>
-      </c>
-      <c r="E39" s="6">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-9.44</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-9.859999999999999</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-11.52</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-10.63</v>
-      </c>
-      <c r="E41" s="6">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1031.8</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1051.6</v>
-      </c>
-      <c r="E42" s="6">
-        <v>19.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>858</v>
-      </c>
-      <c r="D43" s="5">
-        <v>851.55</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-6.45</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>1791.6</v>
-      </c>
-      <c r="D44" s="5">
-        <v>1765.6</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-26</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1939.1</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1937.8</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>702.75</v>
-      </c>
-      <c r="D46" s="5">
-        <v>703.05</v>
-      </c>
-      <c r="E46" s="6">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>3128.6</v>
-      </c>
-      <c r="D47" s="5">
-        <v>3114.2</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-14.4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>8580</v>
-      </c>
-      <c r="D48" s="5">
-        <v>8663.5</v>
-      </c>
-      <c r="E48" s="6">
-        <v>83.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="5">
-        <v>43</v>
-      </c>
-      <c r="D49" s="5">
-        <v>57</v>
-      </c>
-      <c r="E49" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="5">
-        <v>57</v>
-      </c>
-      <c r="D50" s="5">
-        <v>43</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>37.32</v>
-      </c>
-      <c r="D51" s="5">
-        <v>41.77</v>
-      </c>
-      <c r="E51" s="6">
-        <v>4.45</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>41.91</v>
-      </c>
-      <c r="D52" s="5">
-        <v>40.64</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>41.1</v>
-      </c>
-      <c r="D53" s="5">
-        <v>37.66</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>43.27</v>
-      </c>
-      <c r="D54" s="5">
-        <v>43.04</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>27.72</v>
-      </c>
-      <c r="D55" s="5">
-        <v>27.86</v>
-      </c>
-      <c r="E55" s="6">
-        <v>0.14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>51.3</v>
-      </c>
-      <c r="D56" s="5">
-        <v>50.28</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-1.02</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>58.54</v>
-      </c>
-      <c r="D57" s="5">
-        <v>60.24</v>
-      </c>
-      <c r="E57" s="6">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="3" t="s">
+      <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="5">
-        <v>-12.79</v>
-      </c>
-      <c r="D58" s="5">
-        <v>-54.63</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-41.84</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>42.44</v>
-      </c>
-      <c r="D59" s="5">
-        <v>-25.63</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-68.06999999999999</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>70.39</v>
-      </c>
-      <c r="D60" s="5">
-        <v>24.5</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-45.89</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>-27.5</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-31.44</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-3.94</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-59.38</v>
-      </c>
-      <c r="D62" s="5">
-        <v>-62.23</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>-70.5</v>
-      </c>
-      <c r="D63" s="5">
-        <v>-27.29</v>
-      </c>
-      <c r="E63" s="6">
-        <v>43.21</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>178.63</v>
-      </c>
-      <c r="D64" s="5">
+      <c r="C64" s="6">
         <v>6.19</v>
       </c>
-      <c r="E64" s="7">
-        <v>-172.44</v>
+      <c r="D64" s="6">
+        <v>-33.29</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-39.48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2875,60 +2947,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>44.5</v>
+      </c>
+      <c r="E2" s="11">
+        <v>70</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-3.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>1.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>43.1</v>
-      </c>
-      <c r="E2" s="10">
-        <v>70</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-3.9</v>
-      </c>
-      <c r="G2" s="10">
-        <v>1.7</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>70</v>
       </c>
     </row>
@@ -3030,49 +3102,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.5749</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2965</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2393</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1937</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1445</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.107</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0389</v>
+      <c r="A2" s="14">
+        <v>0.5745</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2923</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2402</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2002</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1511</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1124</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.051</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,25 +187,37 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.3 → 45.9</t>
-  </si>
-  <si>
-    <t>50.3</t>
-  </si>
-  <si>
-    <t>45.9</t>
+    <t>48.2 → 55.0</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.2</t>
+  </si>
+  <si>
+    <t>55.0</t>
+  </si>
+  <si>
+    <t>48.1 → 50.9</t>
+  </si>
+  <si>
+    <t>48.1</t>
+  </si>
+  <si>
+    <t>50.9</t>
+  </si>
+  <si>
+    <t>41.6 → 55.5</t>
+  </si>
+  <si>
+    <t>41.6</t>
+  </si>
+  <si>
+    <t>55.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -291,14 +303,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,13 +343,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,8 +429,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,10 +942,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1083.6</v>
+        <v>1124.4</v>
       </c>
       <c r="D2">
-        <v>3.04</v>
+        <v>3.77</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -942,46 +954,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-12.73</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="H2">
-        <v>44.8</v>
+        <v>50.25</v>
       </c>
       <c r="I2">
-        <v>-0.96</v>
+        <v>3.14</v>
       </c>
       <c r="J2">
-        <v>-3.77</v>
+        <v>3.42</v>
       </c>
       <c r="K2">
-        <v>-9.109999999999999</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="L2">
-        <v>9.32</v>
+        <v>15.03</v>
       </c>
       <c r="M2">
-        <v>5.1</v>
+        <v>6.11</v>
       </c>
       <c r="N2">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="O2">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="P2">
-        <v>1066.48</v>
+        <v>1073.32</v>
       </c>
       <c r="Q2">
-        <v>1098.78</v>
+        <v>1098.12</v>
       </c>
       <c r="R2">
-        <v>1094.63</v>
+        <v>1095.33</v>
       </c>
       <c r="S2">
-        <v>958.26</v>
+        <v>959.48</v>
       </c>
       <c r="T2">
-        <v>13.08</v>
+        <v>17.19</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -996,34 +1008,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>48.17</v>
+        <v>54.96</v>
       </c>
       <c r="Z2">
-        <v>-11.13</v>
+        <v>-6.92</v>
       </c>
       <c r="AA2">
-        <v>-6.11</v>
+        <v>-6.27</v>
       </c>
       <c r="AB2">
-        <v>-5.02</v>
+        <v>-0.65</v>
       </c>
       <c r="AC2">
-        <v>30.43</v>
+        <v>63.76</v>
       </c>
       <c r="AD2">
-        <v>19.58</v>
+        <v>35.59</v>
       </c>
       <c r="AE2">
-        <v>42.92</v>
+        <v>44.35</v>
       </c>
       <c r="AF2">
-        <v>7.21</v>
+        <v>170.12</v>
       </c>
       <c r="AG2">
-        <v>1159.37</v>
+        <v>1157.2</v>
       </c>
       <c r="AH2">
-        <v>1038.19</v>
+        <v>1039.04</v>
       </c>
       <c r="AI2">
         <v>1163.98</v>
@@ -1032,7 +1044,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>19.99</v>
+        <v>21.61</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1055,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="D3">
-        <v>3.34</v>
+        <v>1.36</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1055,46 +1067,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-9.880000000000001</v>
+        <v>-8.65</v>
       </c>
       <c r="H3">
-        <v>66.2</v>
+        <v>68.47</v>
       </c>
       <c r="I3">
-        <v>-5.06</v>
+        <v>-2.47</v>
       </c>
       <c r="J3">
-        <v>-1.59</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
-        <v>-7.8</v>
+        <v>-7.44</v>
       </c>
       <c r="L3">
-        <v>12.29</v>
+        <v>12.97</v>
       </c>
       <c r="M3">
-        <v>57.45</v>
+        <v>58.01</v>
       </c>
       <c r="N3">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O3">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P3">
-        <v>882.62</v>
+        <v>878.11</v>
       </c>
       <c r="Q3">
-        <v>888.11</v>
+        <v>888.9</v>
       </c>
       <c r="R3">
-        <v>886.7</v>
+        <v>886.3200000000001</v>
       </c>
       <c r="S3">
-        <v>783.76</v>
+        <v>784.87</v>
       </c>
       <c r="T3">
-        <v>12.28</v>
+        <v>13.65</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1109,34 +1121,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>48.11</v>
+        <v>50.91</v>
       </c>
       <c r="Z3">
-        <v>-1.13</v>
+        <v>-0.63</v>
       </c>
       <c r="AA3">
-        <v>1.92</v>
+        <v>1.41</v>
       </c>
       <c r="AB3">
-        <v>-3.05</v>
+        <v>-2.04</v>
       </c>
       <c r="AC3">
-        <v>12.91</v>
+        <v>30.66</v>
       </c>
       <c r="AD3">
-        <v>26.67</v>
+        <v>21.57</v>
       </c>
       <c r="AE3">
-        <v>25.49</v>
+        <v>25.89</v>
       </c>
       <c r="AF3">
-        <v>-7.15</v>
+        <v>21.7</v>
       </c>
       <c r="AG3">
-        <v>928.84</v>
+        <v>929.27</v>
       </c>
       <c r="AH3">
-        <v>847.39</v>
+        <v>848.53</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1145,7 +1157,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>31.95</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1168,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1764.5</v>
+        <v>1800</v>
       </c>
       <c r="D4">
-        <v>-0.06</v>
+        <v>2.01</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1168,46 +1180,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-9.050000000000001</v>
+        <v>-7.22</v>
       </c>
       <c r="H4">
-        <v>30.25</v>
+        <v>32.87</v>
       </c>
       <c r="I4">
-        <v>-3.53</v>
+        <v>-3.17</v>
       </c>
       <c r="J4">
-        <v>-5.54</v>
+        <v>-3.92</v>
       </c>
       <c r="K4">
-        <v>4.48</v>
+        <v>6.3</v>
       </c>
       <c r="L4">
-        <v>16.76</v>
+        <v>18.69</v>
       </c>
       <c r="M4">
-        <v>24.02</v>
+        <v>25.36</v>
       </c>
       <c r="N4">
         <v>85</v>
       </c>
       <c r="O4">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="P4">
-        <v>1805.32</v>
+        <v>1793.52</v>
       </c>
       <c r="Q4">
-        <v>1839.57</v>
+        <v>1835.12</v>
       </c>
       <c r="R4">
-        <v>1834.14</v>
+        <v>1834.3</v>
       </c>
       <c r="S4">
-        <v>1682.29</v>
+        <v>1682.67</v>
       </c>
       <c r="T4">
-        <v>4.89</v>
+        <v>6.97</v>
       </c>
       <c r="U4" t="s">
         <v>45</v>
@@ -1222,34 +1234,34 @@
         <v>3</v>
       </c>
       <c r="Y4">
-        <v>37.52</v>
+        <v>44.8</v>
       </c>
       <c r="Z4">
-        <v>-14.33</v>
+        <v>-14.65</v>
       </c>
       <c r="AA4">
-        <v>-3.04</v>
+        <v>-5.36</v>
       </c>
       <c r="AB4">
-        <v>-11.29</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>16.24</v>
       </c>
       <c r="AD4">
-        <v>23.02</v>
+        <v>12.17</v>
       </c>
       <c r="AE4">
-        <v>47.29</v>
+        <v>46.76</v>
       </c>
       <c r="AF4">
-        <v>66.97</v>
+        <v>32.41</v>
       </c>
       <c r="AG4">
-        <v>1908.06</v>
+        <v>1901.64</v>
       </c>
       <c r="AH4">
-        <v>1771.08</v>
+        <v>1768.61</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1258,7 +1270,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>20.65</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1281,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1929.8</v>
+        <v>1999.5</v>
       </c>
       <c r="D5">
-        <v>-0.41</v>
+        <v>3.61</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1281,46 +1293,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-19.55</v>
+        <v>-16.64</v>
       </c>
       <c r="H5">
-        <v>10.55</v>
+        <v>14.55</v>
       </c>
       <c r="I5">
-        <v>-1.68</v>
+        <v>1.92</v>
       </c>
       <c r="J5">
-        <v>-6.44</v>
+        <v>-1.89</v>
       </c>
       <c r="K5">
-        <v>-6.69</v>
+        <v>-0.78</v>
       </c>
       <c r="L5">
-        <v>-13.07</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="M5">
-        <v>20.02</v>
+        <v>21.33</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="P5">
-        <v>1939.52</v>
+        <v>1947.04</v>
       </c>
       <c r="Q5">
-        <v>1941.62</v>
+        <v>1941.35</v>
       </c>
       <c r="R5">
-        <v>2011.58</v>
+        <v>2011.29</v>
       </c>
       <c r="S5">
-        <v>2078.27</v>
+        <v>2076.35</v>
       </c>
       <c r="T5">
-        <v>-7.14</v>
+        <v>-3.7</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1335,34 +1347,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>41.6</v>
+        <v>55.55</v>
       </c>
       <c r="Z5">
-        <v>-20.95</v>
+        <v>-15.05</v>
       </c>
       <c r="AA5">
-        <v>-23.2</v>
+        <v>-21.57</v>
       </c>
       <c r="AB5">
-        <v>2.25</v>
+        <v>6.52</v>
       </c>
       <c r="AC5">
-        <v>63.32</v>
+        <v>74.2</v>
       </c>
       <c r="AD5">
-        <v>66.76000000000001</v>
+        <v>67.31</v>
       </c>
       <c r="AE5">
-        <v>41.61</v>
+        <v>45.81</v>
       </c>
       <c r="AF5">
-        <v>-6.77</v>
+        <v>129.32</v>
       </c>
       <c r="AG5">
-        <v>1995.55</v>
+        <v>1994.01</v>
       </c>
       <c r="AH5">
-        <v>1887.69</v>
+        <v>1888.7</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1371,7 +1383,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>21.68</v>
+        <v>23.23</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,37 +1394,37 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>703.1</v>
+        <v>700.7</v>
       </c>
       <c r="D6">
-        <v>0.01</v>
+        <v>-0.34</v>
       </c>
       <c r="E6">
         <v>1095.8</v>
       </c>
       <c r="F6">
-        <v>702.75</v>
+        <v>700.7</v>
       </c>
       <c r="G6">
-        <v>-35.84</v>
+        <v>-36.06</v>
       </c>
       <c r="H6">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>-7.08</v>
+        <v>-4.53</v>
       </c>
       <c r="J6">
-        <v>-9.93</v>
+        <v>-10.97</v>
       </c>
       <c r="K6">
-        <v>-2.54</v>
+        <v>-0.48</v>
       </c>
       <c r="L6">
-        <v>-34.45</v>
+        <v>-34.84</v>
       </c>
       <c r="M6">
-        <v>11.24</v>
+        <v>11.95</v>
       </c>
       <c r="N6">
         <v>15</v>
@@ -1421,19 +1433,19 @@
         <v>24</v>
       </c>
       <c r="P6">
-        <v>712.78</v>
+        <v>706.13</v>
       </c>
       <c r="Q6">
-        <v>772.8</v>
+        <v>767.33</v>
       </c>
       <c r="R6">
-        <v>775.42</v>
+        <v>774.45</v>
       </c>
       <c r="S6">
-        <v>840.13</v>
+        <v>838.54</v>
       </c>
       <c r="T6">
-        <v>-16.31</v>
+        <v>-16.44</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1448,43 +1460,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>27.88</v>
+        <v>27.39</v>
       </c>
       <c r="Z6">
-        <v>-19.88</v>
+        <v>-21.66</v>
       </c>
       <c r="AA6">
-        <v>-9.09</v>
+        <v>-11.6</v>
       </c>
       <c r="AB6">
-        <v>-10.8</v>
+        <v>-10.06</v>
       </c>
       <c r="AC6">
         <v>0.37</v>
       </c>
       <c r="AD6">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="AE6">
-        <v>23.1</v>
+        <v>23.26</v>
       </c>
       <c r="AF6">
-        <v>-80.59999999999999</v>
+        <v>5.86</v>
       </c>
       <c r="AG6">
-        <v>851.53</v>
+        <v>850.22</v>
       </c>
       <c r="AH6">
-        <v>694.08</v>
+        <v>684.4400000000001</v>
       </c>
       <c r="AI6">
-        <v>769.1</v>
+        <v>765.23</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>36.66</v>
+        <v>40.01</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1507,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3049.7</v>
+        <v>3054.1</v>
       </c>
       <c r="D7">
-        <v>-2.07</v>
+        <v>0.14</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1507,46 +1519,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-11.73</v>
+        <v>-11.6</v>
       </c>
       <c r="H7">
-        <v>61.24</v>
+        <v>61.47</v>
       </c>
       <c r="I7">
-        <v>-3.8</v>
+        <v>-3.26</v>
       </c>
       <c r="J7">
-        <v>-7.03</v>
+        <v>-2.35</v>
       </c>
       <c r="K7">
-        <v>21.4</v>
+        <v>16.72</v>
       </c>
       <c r="L7">
-        <v>23.79</v>
+        <v>25.22</v>
       </c>
       <c r="M7">
-        <v>29.23</v>
+        <v>30.64</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P7">
-        <v>3139.96</v>
+        <v>3119.36</v>
       </c>
       <c r="Q7">
-        <v>3243.65</v>
+        <v>3236.34</v>
       </c>
       <c r="R7">
-        <v>2896.69</v>
+        <v>2907.77</v>
       </c>
       <c r="S7">
-        <v>2465.22</v>
+        <v>2468.89</v>
       </c>
       <c r="T7">
-        <v>23.71</v>
+        <v>23.7</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1561,34 +1573,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>45.91</v>
+        <v>46.25</v>
       </c>
       <c r="Z7">
-        <v>49.07</v>
+        <v>36.9</v>
       </c>
       <c r="AA7">
-        <v>93.63</v>
+        <v>82.28</v>
       </c>
       <c r="AB7">
-        <v>-44.56</v>
+        <v>-45.38</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="AD7">
-        <v>6.51</v>
+        <v>3.26</v>
       </c>
       <c r="AE7">
-        <v>142.01</v>
+        <v>138.47</v>
       </c>
       <c r="AF7">
-        <v>-6.35</v>
+        <v>-18.29</v>
       </c>
       <c r="AG7">
-        <v>3460.58</v>
+        <v>3468.73</v>
       </c>
       <c r="AH7">
-        <v>3026.71</v>
+        <v>3003.95</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
@@ -1597,7 +1609,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>24.35</v>
+        <v>23.36</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,10 +1620,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8765</v>
+        <v>8767.5</v>
       </c>
       <c r="D8">
-        <v>1.17</v>
+        <v>0.03</v>
       </c>
       <c r="E8">
         <v>9694.08</v>
@@ -1620,46 +1632,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-9.58</v>
+        <v>-9.56</v>
       </c>
       <c r="H8">
-        <v>47.94</v>
+        <v>47.99</v>
       </c>
       <c r="I8">
-        <v>6.49</v>
+        <v>1.13</v>
       </c>
       <c r="J8">
-        <v>8.81</v>
+        <v>10.04</v>
       </c>
       <c r="K8">
-        <v>11.3</v>
+        <v>10.85</v>
       </c>
       <c r="L8">
-        <v>-8.880000000000001</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="M8">
-        <v>15.11</v>
+        <v>15.48</v>
       </c>
       <c r="N8">
         <v>71</v>
       </c>
       <c r="O8">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P8">
-        <v>8698.1</v>
+        <v>8717.700000000001</v>
       </c>
       <c r="Q8">
-        <v>8337.450000000001</v>
+        <v>8370.35</v>
       </c>
       <c r="R8">
-        <v>8098.48</v>
+        <v>8119.7</v>
       </c>
       <c r="S8">
-        <v>7415.66</v>
+        <v>7418.83</v>
       </c>
       <c r="T8">
-        <v>18.2</v>
+        <v>18.18</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1674,34 +1686,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>62.27</v>
+        <v>62.32</v>
       </c>
       <c r="Z8">
-        <v>172.01</v>
+        <v>181.15</v>
       </c>
       <c r="AA8">
-        <v>126.67</v>
+        <v>137.57</v>
       </c>
       <c r="AB8">
-        <v>45.34</v>
+        <v>43.58</v>
       </c>
       <c r="AC8">
-        <v>71.06999999999999</v>
+        <v>77.73</v>
       </c>
       <c r="AD8">
-        <v>78.52</v>
+        <v>75.38</v>
       </c>
       <c r="AE8">
-        <v>325.24</v>
+        <v>325.05</v>
       </c>
       <c r="AF8">
-        <v>-33.29</v>
+        <v>0.36</v>
       </c>
       <c r="AG8">
-        <v>8814.860000000001</v>
+        <v>8871.709999999999</v>
       </c>
       <c r="AH8">
-        <v>7860.04</v>
+        <v>7868.99</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
@@ -1710,7 +1722,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>46.54</v>
+        <v>46.9</v>
       </c>
     </row>
   </sheetData>
@@ -1851,7 +1863,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1891,7 +1903,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1903,787 +1915,790 @@
         <v>57</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-6.33</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-3.77</v>
-      </c>
-      <c r="E8" s="7">
-        <v>2.56</v>
+      <c r="B8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-5.26</v>
+        <v>-3.77</v>
       </c>
       <c r="D9" s="6">
-        <v>-1.59</v>
+        <v>3.42</v>
       </c>
       <c r="E9" s="7">
-        <v>3.67</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-6.8</v>
+        <v>-1.59</v>
       </c>
       <c r="D10" s="6">
-        <v>-5.54</v>
+        <v>3.35</v>
       </c>
       <c r="E10" s="7">
-        <v>1.26</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-7.52</v>
+        <v>-5.54</v>
       </c>
       <c r="D11" s="6">
-        <v>-6.44</v>
+        <v>-3.92</v>
       </c>
       <c r="E11" s="7">
-        <v>1.08</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-11.24</v>
+        <v>-6.44</v>
       </c>
       <c r="D12" s="6">
-        <v>-9.93</v>
+        <v>-1.89</v>
       </c>
       <c r="E12" s="7">
-        <v>1.31</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>0.55</v>
+        <v>-9.93</v>
       </c>
       <c r="D13" s="6">
-        <v>-7.03</v>
+        <v>-10.97</v>
       </c>
       <c r="E13" s="8">
-        <v>-7.58</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>9.220000000000001</v>
+        <v>-7.03</v>
       </c>
       <c r="D14" s="6">
-        <v>8.81</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.41</v>
+        <v>-2.35</v>
+      </c>
+      <c r="E14" s="7">
+        <v>4.68</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.04</v>
+        <v>8.81</v>
       </c>
       <c r="D15" s="6">
-        <v>-0.96</v>
+        <v>10.04</v>
       </c>
       <c r="E15" s="7">
-        <v>3.08</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-6.5</v>
+        <v>-0.96</v>
       </c>
       <c r="D16" s="6">
-        <v>-5.06</v>
+        <v>3.14</v>
       </c>
       <c r="E16" s="7">
-        <v>1.44</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-3.17</v>
+        <v>-5.06</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.53</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.36</v>
+        <v>-2.47</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.59</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.68</v>
+        <v>-3.53</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.68</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1</v>
+        <v>-3.17</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.36</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-7.94</v>
+        <v>-1.68</v>
       </c>
       <c r="D19" s="6">
-        <v>-7.08</v>
+        <v>1.92</v>
       </c>
       <c r="E19" s="7">
-        <v>0.86</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-0.85</v>
+        <v>-7.08</v>
       </c>
       <c r="D20" s="6">
-        <v>-3.8</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-2.95</v>
+        <v>-4.53</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.55</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>2.9</v>
+        <v>-3.8</v>
       </c>
       <c r="D21" s="6">
-        <v>6.49</v>
+        <v>-3.26</v>
       </c>
       <c r="E21" s="7">
-        <v>3.59</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>6.85</v>
+        <v>6.49</v>
       </c>
       <c r="D22" s="6">
-        <v>9.32</v>
-      </c>
-      <c r="E22" s="7">
-        <v>2.47</v>
+        <v>1.13</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-5.36</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>8.69</v>
+        <v>9.32</v>
       </c>
       <c r="D23" s="6">
-        <v>12.29</v>
+        <v>15.03</v>
       </c>
       <c r="E23" s="7">
-        <v>3.6</v>
+        <v>5.71</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>18.13</v>
+        <v>12.29</v>
       </c>
       <c r="D24" s="6">
-        <v>16.76</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.37</v>
+        <v>12.97</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.68</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-12.89</v>
+        <v>16.76</v>
       </c>
       <c r="D25" s="6">
-        <v>-13.07</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.18</v>
+        <v>18.69</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.93</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-35.15</v>
+        <v>-13.07</v>
       </c>
       <c r="D26" s="6">
-        <v>-34.45</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="E26" s="7">
-        <v>0.7</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>24.25</v>
+        <v>-34.45</v>
       </c>
       <c r="D27" s="6">
-        <v>23.79</v>
+        <v>-34.84</v>
       </c>
       <c r="E27" s="8">
-        <v>-0.46</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>-10.66</v>
+        <v>23.79</v>
       </c>
       <c r="D28" s="6">
-        <v>-8.880000000000001</v>
+        <v>25.22</v>
       </c>
       <c r="E28" s="7">
-        <v>1.78</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-6.96</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="D29" s="6">
-        <v>-9.109999999999999</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-2.15</v>
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.35</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-11.64</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="D30" s="6">
-        <v>-7.8</v>
-      </c>
-      <c r="E30" s="7">
-        <v>3.84</v>
+        <v>-9.449999999999999</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>5.15</v>
+        <v>-7.8</v>
       </c>
       <c r="D31" s="6">
-        <v>4.48</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.67</v>
+        <v>-7.44</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.36</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-4.82</v>
+        <v>4.48</v>
       </c>
       <c r="D32" s="6">
-        <v>-6.69</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.87</v>
+        <v>6.3</v>
+      </c>
+      <c r="E32" s="7">
+        <v>1.82</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>-4.03</v>
+        <v>-6.69</v>
       </c>
       <c r="D33" s="6">
-        <v>-2.54</v>
+        <v>-0.78</v>
       </c>
       <c r="E33" s="7">
-        <v>1.49</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>24.2</v>
+        <v>-2.54</v>
       </c>
       <c r="D34" s="6">
-        <v>21.4</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-2.8</v>
+        <v>-0.48</v>
+      </c>
+      <c r="E34" s="7">
+        <v>2.06</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>9.949999999999999</v>
+        <v>21.4</v>
       </c>
       <c r="D35" s="6">
-        <v>11.3</v>
-      </c>
-      <c r="E35" s="7">
-        <v>1.35</v>
+        <v>16.72</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-4.68</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>-15.31</v>
+        <v>11.3</v>
       </c>
       <c r="D36" s="6">
-        <v>-12.73</v>
-      </c>
-      <c r="E36" s="7">
-        <v>2.58</v>
+        <v>10.85</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-12.8</v>
+        <v>-12.73</v>
       </c>
       <c r="D37" s="6">
-        <v>-9.880000000000001</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="E37" s="7">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-8.99</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="D38" s="6">
-        <v>-9.050000000000001</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.06</v>
+        <v>-8.65</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.23</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-19.22</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="D39" s="6">
-        <v>-19.55</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.33</v>
+        <v>-7.22</v>
+      </c>
+      <c r="E39" s="7">
+        <v>1.83</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-9.859999999999999</v>
+        <v>-19.55</v>
       </c>
       <c r="D40" s="6">
-        <v>-11.73</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.87</v>
+        <v>-16.64</v>
+      </c>
+      <c r="E40" s="7">
+        <v>2.91</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-10.63</v>
+        <v>-35.84</v>
       </c>
       <c r="D41" s="6">
-        <v>-9.58</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.05</v>
+        <v>-36.06</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>1051.6</v>
+        <v>-11.73</v>
       </c>
       <c r="D42" s="6">
-        <v>1083.6</v>
+        <v>-11.6</v>
       </c>
       <c r="E42" s="7">
-        <v>32</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>851.55</v>
+        <v>-9.58</v>
       </c>
       <c r="D43" s="6">
-        <v>880</v>
+        <v>-9.56</v>
       </c>
       <c r="E43" s="7">
-        <v>28.45</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>1765.6</v>
+        <v>1083.6</v>
       </c>
       <c r="D44" s="6">
-        <v>1764.5</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-1.1</v>
+        <v>1124.4</v>
+      </c>
+      <c r="E44" s="7">
+        <v>40.8</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>1937.8</v>
+        <v>880</v>
       </c>
       <c r="D45" s="6">
-        <v>1929.8</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-8</v>
+        <v>892</v>
+      </c>
+      <c r="E45" s="7">
+        <v>12</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>703.05</v>
+        <v>1764.5</v>
       </c>
       <c r="D46" s="6">
-        <v>703.1</v>
+        <v>1800</v>
       </c>
       <c r="E46" s="7">
-        <v>0.05</v>
+        <v>35.5</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>3114.2</v>
+        <v>1929.8</v>
       </c>
       <c r="D47" s="6">
-        <v>3049.7</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-64.5</v>
+        <v>1999.5</v>
+      </c>
+      <c r="E47" s="7">
+        <v>69.7</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>8663.5</v>
+        <v>703.1</v>
       </c>
       <c r="D48" s="6">
-        <v>8765</v>
-      </c>
-      <c r="E48" s="7">
-        <v>101.5</v>
+        <v>700.7</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-2.4</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>57</v>
+        <v>3049.7</v>
       </c>
       <c r="D49" s="6">
-        <v>43</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-14</v>
+        <v>3054.1</v>
+      </c>
+      <c r="E49" s="7">
+        <v>4.4</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C50" s="6">
-        <v>43</v>
+        <v>8765</v>
       </c>
       <c r="D50" s="6">
-        <v>57</v>
+        <v>8767.5</v>
       </c>
       <c r="E50" s="7">
-        <v>14</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2691,16 +2706,16 @@
         <v>37</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C51" s="6">
-        <v>41.77</v>
+        <v>43</v>
       </c>
       <c r="D51" s="6">
-        <v>48.17</v>
+        <v>57</v>
       </c>
       <c r="E51" s="7">
-        <v>6.4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2708,226 +2723,260 @@
         <v>38</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C52" s="6">
-        <v>40.64</v>
+        <v>57</v>
       </c>
       <c r="D52" s="6">
-        <v>48.11</v>
-      </c>
-      <c r="E52" s="7">
-        <v>7.47</v>
+        <v>43</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-14</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>37.66</v>
+        <v>48.17</v>
       </c>
       <c r="D53" s="6">
-        <v>37.52</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.14</v>
+        <v>54.96</v>
+      </c>
+      <c r="E53" s="7">
+        <v>6.79</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>43.04</v>
+        <v>48.11</v>
       </c>
       <c r="D54" s="6">
-        <v>41.6</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-1.44</v>
+        <v>50.91</v>
+      </c>
+      <c r="E54" s="7">
+        <v>2.8</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>27.86</v>
+        <v>37.52</v>
       </c>
       <c r="D55" s="6">
-        <v>27.88</v>
+        <v>44.8</v>
       </c>
       <c r="E55" s="7">
-        <v>0.02</v>
+        <v>7.28</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>50.28</v>
+        <v>41.6</v>
       </c>
       <c r="D56" s="6">
-        <v>45.91</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-4.37</v>
+        <v>55.55</v>
+      </c>
+      <c r="E56" s="7">
+        <v>13.95</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>60.24</v>
+        <v>27.88</v>
       </c>
       <c r="D57" s="6">
-        <v>62.27</v>
-      </c>
-      <c r="E57" s="7">
-        <v>2.03</v>
+        <v>27.39</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>-54.63</v>
+        <v>45.91</v>
       </c>
       <c r="D58" s="6">
-        <v>7.21</v>
+        <v>46.25</v>
       </c>
       <c r="E58" s="7">
-        <v>61.84</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>-25.63</v>
+        <v>62.27</v>
       </c>
       <c r="D59" s="6">
-        <v>-7.15</v>
+        <v>62.32</v>
       </c>
       <c r="E59" s="7">
-        <v>18.48</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>24.5</v>
+        <v>7.21</v>
       </c>
       <c r="D60" s="6">
-        <v>66.97</v>
+        <v>170.12</v>
       </c>
       <c r="E60" s="7">
-        <v>42.47</v>
+        <v>162.91</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>-31.44</v>
+        <v>-7.15</v>
       </c>
       <c r="D61" s="6">
-        <v>-6.77</v>
+        <v>21.7</v>
       </c>
       <c r="E61" s="7">
-        <v>24.67</v>
+        <v>28.85</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>-62.23</v>
+        <v>66.97</v>
       </c>
       <c r="D62" s="6">
-        <v>-80.59999999999999</v>
+        <v>32.41</v>
       </c>
       <c r="E62" s="8">
-        <v>-18.37</v>
+        <v>-34.56</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C63" s="6">
-        <v>-27.29</v>
+        <v>-6.77</v>
       </c>
       <c r="D63" s="6">
-        <v>-6.35</v>
+        <v>129.32</v>
       </c>
       <c r="E63" s="7">
-        <v>20.94</v>
+        <v>136.09</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C64" s="6">
-        <v>6.19</v>
+        <v>-80.59999999999999</v>
       </c>
       <c r="D64" s="6">
+        <v>5.86</v>
+      </c>
+      <c r="E64" s="7">
+        <v>86.45999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>-6.35</v>
+      </c>
+      <c r="D65" s="6">
+        <v>-18.29</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-11.94</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
         <v>-33.29</v>
       </c>
-      <c r="E64" s="8">
-        <v>-39.48</v>
+      <c r="D66" s="6">
+        <v>0.36</v>
+      </c>
+      <c r="E66" s="7">
+        <v>33.65</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2951,28 +3000,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2986,16 +3035,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>44.5</v>
+        <v>48.9</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.6</v>
+        <v>-0.3</v>
       </c>
       <c r="G2" s="11">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3126,25 +3175,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.5745</v>
+        <v>0.5800999999999999</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2923</v>
+        <v>0.3064</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2402</v>
+        <v>0.2536</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2002</v>
+        <v>0.2133</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1511</v>
+        <v>0.1548</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1124</v>
+        <v>0.1195</v>
       </c>
       <c r="G2" s="14">
-        <v>0.051</v>
+        <v>0.0611</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,12 +163,12 @@
     <t>No</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
@@ -187,37 +187,25 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>48.2 → 55.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.2</t>
-  </si>
-  <si>
-    <t>55.0</t>
-  </si>
-  <si>
-    <t>48.1 → 50.9</t>
-  </si>
-  <si>
-    <t>48.1</t>
-  </si>
-  <si>
-    <t>50.9</t>
-  </si>
-  <si>
-    <t>41.6 → 55.5</t>
-  </si>
-  <si>
-    <t>41.6</t>
+    <t>55.5 → 45.7</t>
   </si>
   <si>
     <t>55.5</t>
+  </si>
+  <si>
+    <t>45.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -303,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -343,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,8 +417,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -942,10 +930,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1124.4</v>
+        <v>1178.9</v>
       </c>
       <c r="D2">
-        <v>3.77</v>
+        <v>4.85</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -954,46 +942,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-9.449999999999999</v>
+        <v>-5.06</v>
       </c>
       <c r="H2">
-        <v>50.25</v>
+        <v>57.53</v>
       </c>
       <c r="I2">
-        <v>3.14</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="J2">
-        <v>3.42</v>
+        <v>3.63</v>
       </c>
       <c r="K2">
-        <v>-9.449999999999999</v>
+        <v>-2.68</v>
       </c>
       <c r="L2">
-        <v>15.03</v>
+        <v>17.92</v>
       </c>
       <c r="M2">
-        <v>6.11</v>
+        <v>6.97</v>
       </c>
       <c r="N2">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="O2">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="P2">
-        <v>1073.32</v>
+        <v>1094.06</v>
       </c>
       <c r="Q2">
-        <v>1098.12</v>
+        <v>1098.57</v>
       </c>
       <c r="R2">
-        <v>1095.33</v>
+        <v>1097.08</v>
       </c>
       <c r="S2">
-        <v>959.48</v>
+        <v>960.95</v>
       </c>
       <c r="T2">
-        <v>17.19</v>
+        <v>22.68</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1008,43 +996,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>54.96</v>
+        <v>62.11</v>
       </c>
       <c r="Z2">
-        <v>-6.92</v>
+        <v>0.79</v>
       </c>
       <c r="AA2">
-        <v>-6.27</v>
+        <v>-4.86</v>
       </c>
       <c r="AB2">
-        <v>-0.65</v>
+        <v>5.65</v>
       </c>
       <c r="AC2">
-        <v>63.76</v>
+        <v>88.25</v>
       </c>
       <c r="AD2">
-        <v>35.59</v>
+        <v>60.81</v>
       </c>
       <c r="AE2">
-        <v>44.35</v>
+        <v>48.65</v>
       </c>
       <c r="AF2">
-        <v>170.12</v>
+        <v>1652.37</v>
       </c>
       <c r="AG2">
-        <v>1157.2</v>
+        <v>1160.07</v>
       </c>
       <c r="AH2">
-        <v>1039.04</v>
+        <v>1037.08</v>
       </c>
       <c r="AI2">
-        <v>1163.98</v>
+        <v>1044.34</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>21.61</v>
+        <v>26.33</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1055,10 +1043,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>892</v>
+        <v>910</v>
       </c>
       <c r="D3">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1067,46 +1055,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-8.65</v>
+        <v>-6.81</v>
       </c>
       <c r="H3">
-        <v>68.47</v>
+        <v>71.87</v>
       </c>
       <c r="I3">
-        <v>-2.47</v>
+        <v>0.11</v>
       </c>
       <c r="J3">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="K3">
-        <v>-7.44</v>
+        <v>-5.46</v>
       </c>
       <c r="L3">
-        <v>12.97</v>
+        <v>15.12</v>
       </c>
       <c r="M3">
-        <v>58.01</v>
+        <v>57.03</v>
       </c>
       <c r="N3">
-        <v>43</v>
+        <v>71</v>
       </c>
       <c r="O3">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>878.11</v>
+        <v>878.3099999999999</v>
       </c>
       <c r="Q3">
-        <v>888.9</v>
+        <v>891.05</v>
       </c>
       <c r="R3">
-        <v>886.3200000000001</v>
+        <v>886.1900000000001</v>
       </c>
       <c r="S3">
-        <v>784.87</v>
+        <v>786.13</v>
       </c>
       <c r="T3">
-        <v>13.65</v>
+        <v>15.76</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1121,43 +1109,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>50.91</v>
+        <v>54.86</v>
       </c>
       <c r="Z3">
-        <v>-0.63</v>
+        <v>1.21</v>
       </c>
       <c r="AA3">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AB3">
-        <v>-2.04</v>
+        <v>-0.16</v>
       </c>
       <c r="AC3">
-        <v>30.66</v>
+        <v>55.22</v>
       </c>
       <c r="AD3">
-        <v>21.57</v>
+        <v>32.93</v>
       </c>
       <c r="AE3">
-        <v>25.89</v>
+        <v>26.02</v>
       </c>
       <c r="AF3">
-        <v>21.7</v>
+        <v>19.31</v>
       </c>
       <c r="AG3">
-        <v>929.27</v>
+        <v>931.08</v>
       </c>
       <c r="AH3">
-        <v>848.53</v>
+        <v>851.01</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
       </c>
       <c r="AJ3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK3">
-        <v>29.5</v>
+        <v>28.28</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1168,10 +1156,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1800</v>
+        <v>1764</v>
       </c>
       <c r="D4">
-        <v>2.01</v>
+        <v>-2</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1180,97 +1168,97 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-7.22</v>
+        <v>-9.07</v>
       </c>
       <c r="H4">
-        <v>32.87</v>
+        <v>30.21</v>
       </c>
       <c r="I4">
-        <v>-3.17</v>
+        <v>-4.44</v>
       </c>
       <c r="J4">
-        <v>-3.92</v>
+        <v>-6.61</v>
       </c>
       <c r="K4">
-        <v>6.3</v>
+        <v>2.63</v>
       </c>
       <c r="L4">
-        <v>18.69</v>
+        <v>11.51</v>
       </c>
       <c r="M4">
-        <v>25.36</v>
+        <v>25.21</v>
       </c>
       <c r="N4">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="O4">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P4">
-        <v>1793.52</v>
+        <v>1777.14</v>
       </c>
       <c r="Q4">
-        <v>1835.12</v>
+        <v>1830.18</v>
       </c>
       <c r="R4">
-        <v>1834.3</v>
+        <v>1833.43</v>
       </c>
       <c r="S4">
-        <v>1682.67</v>
+        <v>1682.94</v>
       </c>
       <c r="T4">
-        <v>6.97</v>
+        <v>4.82</v>
       </c>
       <c r="U4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V4" t="s">
         <v>45</v>
       </c>
       <c r="W4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y4">
-        <v>44.8</v>
+        <v>39.74</v>
       </c>
       <c r="Z4">
-        <v>-14.65</v>
+        <v>-17.61</v>
       </c>
       <c r="AA4">
-        <v>-5.36</v>
+        <v>-7.81</v>
       </c>
       <c r="AB4">
-        <v>-9.289999999999999</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="AC4">
-        <v>16.24</v>
+        <v>21.2</v>
       </c>
       <c r="AD4">
-        <v>12.17</v>
+        <v>12.48</v>
       </c>
       <c r="AE4">
-        <v>46.76</v>
+        <v>46.46</v>
       </c>
       <c r="AF4">
-        <v>32.41</v>
+        <v>-22.17</v>
       </c>
       <c r="AG4">
-        <v>1901.64</v>
+        <v>1902.46</v>
       </c>
       <c r="AH4">
-        <v>1768.61</v>
+        <v>1757.9</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
       </c>
       <c r="AJ4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK4">
-        <v>20.99</v>
+        <v>21.53</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1281,10 +1269,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1999.5</v>
+        <v>1940.8</v>
       </c>
       <c r="D5">
-        <v>3.61</v>
+        <v>-2.94</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1293,46 +1281,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-16.64</v>
+        <v>-19.09</v>
       </c>
       <c r="H5">
-        <v>14.55</v>
+        <v>11.18</v>
       </c>
       <c r="I5">
-        <v>1.92</v>
+        <v>0.61</v>
       </c>
       <c r="J5">
-        <v>-1.89</v>
+        <v>-3.19</v>
       </c>
       <c r="K5">
-        <v>-0.78</v>
+        <v>-2.36</v>
       </c>
       <c r="L5">
-        <v>-9.369999999999999</v>
+        <v>-14</v>
       </c>
       <c r="M5">
-        <v>21.33</v>
+        <v>20.2</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="P5">
-        <v>1947.04</v>
+        <v>1949.4</v>
       </c>
       <c r="Q5">
-        <v>1941.35</v>
+        <v>1938.59</v>
       </c>
       <c r="R5">
-        <v>2011.29</v>
+        <v>2008.75</v>
       </c>
       <c r="S5">
-        <v>2076.35</v>
+        <v>2074.39</v>
       </c>
       <c r="T5">
-        <v>-3.7</v>
+        <v>-6.44</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1347,43 +1335,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>55.55</v>
+        <v>45.66</v>
       </c>
       <c r="Z5">
-        <v>-15.05</v>
+        <v>-14.94</v>
       </c>
       <c r="AA5">
-        <v>-21.57</v>
+        <v>-20.24</v>
       </c>
       <c r="AB5">
-        <v>6.52</v>
+        <v>5.31</v>
       </c>
       <c r="AC5">
-        <v>74.2</v>
+        <v>69.09</v>
       </c>
       <c r="AD5">
-        <v>67.31</v>
+        <v>68.87</v>
       </c>
       <c r="AE5">
-        <v>45.81</v>
+        <v>47.07</v>
       </c>
       <c r="AF5">
-        <v>129.32</v>
+        <v>-38.94</v>
       </c>
       <c r="AG5">
-        <v>1994.01</v>
+        <v>1984.52</v>
       </c>
       <c r="AH5">
-        <v>1888.7</v>
+        <v>1892.66</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
       </c>
       <c r="AJ5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK5">
-        <v>23.23</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1394,10 +1382,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>700.7</v>
+        <v>700.9</v>
       </c>
       <c r="D6">
-        <v>-0.34</v>
+        <v>0.03</v>
       </c>
       <c r="E6">
         <v>1095.8</v>
@@ -1406,46 +1394,46 @@
         <v>700.7</v>
       </c>
       <c r="G6">
-        <v>-36.06</v>
+        <v>-36.04</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I6">
-        <v>-4.53</v>
+        <v>-2.79</v>
       </c>
       <c r="J6">
-        <v>-10.97</v>
+        <v>-13.5</v>
       </c>
       <c r="K6">
-        <v>-0.48</v>
+        <v>-2.1</v>
       </c>
       <c r="L6">
-        <v>-34.84</v>
+        <v>-35.58</v>
       </c>
       <c r="M6">
-        <v>11.95</v>
+        <v>11.61</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P6">
-        <v>706.13</v>
+        <v>702.1</v>
       </c>
       <c r="Q6">
-        <v>767.33</v>
+        <v>762.51</v>
       </c>
       <c r="R6">
-        <v>774.45</v>
+        <v>773.29</v>
       </c>
       <c r="S6">
-        <v>838.54</v>
+        <v>836.84</v>
       </c>
       <c r="T6">
-        <v>-16.44</v>
+        <v>-16.24</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1460,43 +1448,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>27.39</v>
+        <v>27.51</v>
       </c>
       <c r="Z6">
-        <v>-21.66</v>
+        <v>-22.78</v>
       </c>
       <c r="AA6">
-        <v>-11.6</v>
+        <v>-13.84</v>
       </c>
       <c r="AB6">
-        <v>-10.06</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="AC6">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="AD6">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AE6">
-        <v>23.26</v>
+        <v>22.52</v>
       </c>
       <c r="AF6">
-        <v>5.86</v>
+        <v>-72.62</v>
       </c>
       <c r="AG6">
-        <v>850.22</v>
+        <v>849.1799999999999</v>
       </c>
       <c r="AH6">
-        <v>684.4400000000001</v>
+        <v>675.83</v>
       </c>
       <c r="AI6">
         <v>765.23</v>
       </c>
       <c r="AJ6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK6">
-        <v>40.01</v>
+        <v>42.92</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1507,10 +1495,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3054.1</v>
+        <v>3043.4</v>
       </c>
       <c r="D7">
-        <v>0.14</v>
+        <v>-0.35</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1519,46 +1507,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-11.6</v>
+        <v>-11.91</v>
       </c>
       <c r="H7">
-        <v>61.47</v>
+        <v>60.9</v>
       </c>
       <c r="I7">
-        <v>-3.26</v>
+        <v>-6.36</v>
       </c>
       <c r="J7">
-        <v>-2.35</v>
+        <v>-4.9</v>
       </c>
       <c r="K7">
-        <v>16.72</v>
+        <v>17.68</v>
       </c>
       <c r="L7">
-        <v>25.22</v>
+        <v>25.02</v>
       </c>
       <c r="M7">
-        <v>30.64</v>
+        <v>30.42</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P7">
-        <v>3119.36</v>
+        <v>3078</v>
       </c>
       <c r="Q7">
-        <v>3236.34</v>
+        <v>3222.57</v>
       </c>
       <c r="R7">
-        <v>2907.77</v>
+        <v>2919.06</v>
       </c>
       <c r="S7">
-        <v>2468.89</v>
+        <v>2472.61</v>
       </c>
       <c r="T7">
-        <v>23.7</v>
+        <v>23.08</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1573,43 +1561,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>46.25</v>
+        <v>45.5</v>
       </c>
       <c r="Z7">
-        <v>36.9</v>
+        <v>26.09</v>
       </c>
       <c r="AA7">
-        <v>82.28</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="AB7">
-        <v>-45.38</v>
+        <v>-44.95</v>
       </c>
       <c r="AC7">
         <v>0.58</v>
       </c>
       <c r="AD7">
-        <v>3.26</v>
+        <v>0.38</v>
       </c>
       <c r="AE7">
-        <v>138.47</v>
+        <v>132.8</v>
       </c>
       <c r="AF7">
-        <v>-18.29</v>
+        <v>-67.75</v>
       </c>
       <c r="AG7">
-        <v>3468.73</v>
+        <v>3466.72</v>
       </c>
       <c r="AH7">
-        <v>3003.95</v>
+        <v>2978.42</v>
       </c>
       <c r="AI7">
         <v>3037.42</v>
       </c>
       <c r="AJ7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK7">
-        <v>23.36</v>
+        <v>22.51</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1620,58 +1608,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8767.5</v>
+        <v>8640.5</v>
       </c>
       <c r="D8">
-        <v>0.03</v>
+        <v>-1.45</v>
       </c>
       <c r="E8">
-        <v>9694.08</v>
+        <v>9635.76</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-9.56</v>
+        <v>-10.33</v>
       </c>
       <c r="H8">
-        <v>47.99</v>
+        <v>45.84</v>
       </c>
       <c r="I8">
-        <v>1.13</v>
+        <v>-1.95</v>
       </c>
       <c r="J8">
-        <v>10.04</v>
+        <v>6.55</v>
       </c>
       <c r="K8">
-        <v>10.85</v>
+        <v>11.18</v>
       </c>
       <c r="L8">
-        <v>-8.529999999999999</v>
+        <v>-10.87</v>
       </c>
       <c r="M8">
-        <v>15.48</v>
+        <v>15.09</v>
       </c>
       <c r="N8">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="O8">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P8">
-        <v>8717.700000000001</v>
+        <v>8683.299999999999</v>
       </c>
       <c r="Q8">
-        <v>8370.35</v>
+        <v>8393.25</v>
       </c>
       <c r="R8">
-        <v>8119.7</v>
+        <v>8135.67</v>
       </c>
       <c r="S8">
-        <v>7418.83</v>
+        <v>7421.2</v>
       </c>
       <c r="T8">
-        <v>18.18</v>
+        <v>16.43</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1686,43 +1674,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>62.32</v>
+        <v>58.03</v>
       </c>
       <c r="Z8">
-        <v>181.15</v>
+        <v>176.11</v>
       </c>
       <c r="AA8">
-        <v>137.57</v>
+        <v>145.27</v>
       </c>
       <c r="AB8">
-        <v>43.58</v>
+        <v>30.84</v>
       </c>
       <c r="AC8">
-        <v>77.73</v>
+        <v>73.84</v>
       </c>
       <c r="AD8">
-        <v>75.38</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="AE8">
-        <v>325.05</v>
+        <v>321.37</v>
       </c>
       <c r="AF8">
-        <v>0.36</v>
+        <v>-64.73</v>
       </c>
       <c r="AG8">
-        <v>8871.709999999999</v>
+        <v>8900.290000000001</v>
       </c>
       <c r="AH8">
-        <v>7868.99</v>
+        <v>7886.21</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
       </c>
       <c r="AJ8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK8">
-        <v>46.9</v>
+        <v>47.03</v>
       </c>
     </row>
   </sheetData>
@@ -1863,7 +1851,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1903,42 +1891,42 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="E3" s="4" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>62</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1946,24 +1934,24 @@
         <v>40</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
@@ -1975,16 +1963,16 @@
         <v>0</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1995,13 +1983,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-3.77</v>
+        <v>3.42</v>
       </c>
       <c r="D9" s="6">
-        <v>3.42</v>
+        <v>3.63</v>
       </c>
       <c r="E9" s="7">
-        <v>7.19</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2012,13 +2000,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-1.59</v>
+        <v>3.35</v>
       </c>
       <c r="D10" s="6">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="E10" s="7">
-        <v>4.94</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2029,13 +2017,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.54</v>
+        <v>-3.92</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.92</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.62</v>
+        <v>-6.61</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-2.69</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2046,13 +2034,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-6.44</v>
+        <v>-1.89</v>
       </c>
       <c r="D12" s="6">
-        <v>-1.89</v>
-      </c>
-      <c r="E12" s="7">
-        <v>4.55</v>
+        <v>-3.19</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2063,13 +2051,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-9.93</v>
+        <v>-10.97</v>
       </c>
       <c r="D13" s="6">
-        <v>-10.97</v>
+        <v>-13.5</v>
       </c>
       <c r="E13" s="8">
-        <v>-1.04</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2080,13 +2068,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>-7.03</v>
+        <v>-2.35</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.35</v>
-      </c>
-      <c r="E14" s="7">
-        <v>4.68</v>
+        <v>-4.9</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-2.55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2097,13 +2085,13 @@
         <v>9</v>
       </c>
       <c r="C15" s="6">
-        <v>8.81</v>
+        <v>10.04</v>
       </c>
       <c r="D15" s="6">
-        <v>10.04</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.23</v>
+        <v>6.55</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-3.49</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2114,13 +2102,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-0.96</v>
+        <v>3.14</v>
       </c>
       <c r="D16" s="6">
-        <v>3.14</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="E16" s="7">
-        <v>4.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2131,13 +2119,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-5.06</v>
+        <v>-2.47</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.47</v>
+        <v>0.11</v>
       </c>
       <c r="E17" s="7">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2148,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-3.53</v>
+        <v>-3.17</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.17</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.36</v>
+        <v>-4.44</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2165,13 +2153,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.68</v>
+        <v>1.92</v>
       </c>
       <c r="D19" s="6">
-        <v>1.92</v>
-      </c>
-      <c r="E19" s="7">
-        <v>3.6</v>
+        <v>0.61</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2182,13 +2170,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-7.08</v>
+        <v>-4.53</v>
       </c>
       <c r="D20" s="6">
-        <v>-4.53</v>
+        <v>-2.79</v>
       </c>
       <c r="E20" s="7">
-        <v>2.55</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2199,13 +2187,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-3.8</v>
+        <v>-3.26</v>
       </c>
       <c r="D21" s="6">
-        <v>-3.26</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.54</v>
+        <v>-6.36</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-3.1</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2216,13 +2204,13 @@
         <v>8</v>
       </c>
       <c r="C22" s="6">
-        <v>6.49</v>
+        <v>1.13</v>
       </c>
       <c r="D22" s="6">
-        <v>1.13</v>
+        <v>-1.95</v>
       </c>
       <c r="E22" s="8">
-        <v>-5.36</v>
+        <v>-3.08</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2233,13 +2221,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>9.32</v>
+        <v>15.03</v>
       </c>
       <c r="D23" s="6">
-        <v>15.03</v>
+        <v>17.92</v>
       </c>
       <c r="E23" s="7">
-        <v>5.71</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2250,13 +2238,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>12.29</v>
+        <v>12.97</v>
       </c>
       <c r="D24" s="6">
-        <v>12.97</v>
+        <v>15.12</v>
       </c>
       <c r="E24" s="7">
-        <v>0.68</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2267,13 +2255,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>16.76</v>
+        <v>18.69</v>
       </c>
       <c r="D25" s="6">
-        <v>18.69</v>
-      </c>
-      <c r="E25" s="7">
-        <v>1.93</v>
+        <v>11.51</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-7.18</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2284,13 +2272,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-13.07</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="D26" s="6">
-        <v>-9.369999999999999</v>
-      </c>
-      <c r="E26" s="7">
-        <v>3.7</v>
+        <v>-14</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-4.63</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2301,13 +2289,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-34.45</v>
+        <v>-34.84</v>
       </c>
       <c r="D27" s="6">
-        <v>-34.84</v>
+        <v>-35.58</v>
       </c>
       <c r="E27" s="8">
-        <v>-0.39</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2318,13 +2306,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>23.79</v>
+        <v>25.22</v>
       </c>
       <c r="D28" s="6">
-        <v>25.22</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.43</v>
+        <v>25.02</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2335,13 +2323,13 @@
         <v>11</v>
       </c>
       <c r="C29" s="6">
-        <v>-8.880000000000001</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="D29" s="6">
-        <v>-8.529999999999999</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.35</v>
+        <v>-10.87</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-2.34</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2352,13 +2340,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-9.109999999999999</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="D30" s="6">
-        <v>-9.449999999999999</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.34</v>
+        <v>-2.68</v>
+      </c>
+      <c r="E30" s="7">
+        <v>6.77</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2369,13 +2357,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-7.8</v>
+        <v>-7.44</v>
       </c>
       <c r="D31" s="6">
-        <v>-7.44</v>
+        <v>-5.46</v>
       </c>
       <c r="E31" s="7">
-        <v>0.36</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2386,13 +2374,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>4.48</v>
+        <v>6.3</v>
       </c>
       <c r="D32" s="6">
-        <v>6.3</v>
-      </c>
-      <c r="E32" s="7">
-        <v>1.82</v>
+        <v>2.63</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-3.67</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2403,13 +2391,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>-6.69</v>
+        <v>-0.78</v>
       </c>
       <c r="D33" s="6">
-        <v>-0.78</v>
-      </c>
-      <c r="E33" s="7">
-        <v>5.91</v>
+        <v>-2.36</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-1.58</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2420,13 +2408,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-2.54</v>
+        <v>-0.48</v>
       </c>
       <c r="D34" s="6">
-        <v>-0.48</v>
-      </c>
-      <c r="E34" s="7">
-        <v>2.06</v>
+        <v>-2.1</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2437,13 +2425,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>21.4</v>
+        <v>16.72</v>
       </c>
       <c r="D35" s="6">
-        <v>16.72</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-4.68</v>
+        <v>17.68</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.96</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2454,13 +2442,13 @@
         <v>10</v>
       </c>
       <c r="C36" s="6">
-        <v>11.3</v>
+        <v>10.85</v>
       </c>
       <c r="D36" s="6">
-        <v>10.85</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.45</v>
+        <v>11.18</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.33</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2471,13 +2459,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-12.73</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="D37" s="6">
-        <v>-9.449999999999999</v>
+        <v>-5.06</v>
       </c>
       <c r="E37" s="7">
-        <v>3.28</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2488,13 +2476,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-9.880000000000001</v>
+        <v>-8.65</v>
       </c>
       <c r="D38" s="6">
-        <v>-8.65</v>
+        <v>-6.81</v>
       </c>
       <c r="E38" s="7">
-        <v>1.23</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2505,13 +2493,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-9.050000000000001</v>
+        <v>-7.22</v>
       </c>
       <c r="D39" s="6">
-        <v>-7.22</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1.83</v>
+        <v>-9.07</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2522,13 +2510,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-19.55</v>
+        <v>-16.64</v>
       </c>
       <c r="D40" s="6">
-        <v>-16.64</v>
-      </c>
-      <c r="E40" s="7">
-        <v>2.91</v>
+        <v>-19.09</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-2.45</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2539,13 +2527,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-35.84</v>
+        <v>-36.06</v>
       </c>
       <c r="D41" s="6">
-        <v>-36.06</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.22</v>
+        <v>-36.04</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2556,13 +2544,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>-11.73</v>
+        <v>-11.6</v>
       </c>
       <c r="D42" s="6">
-        <v>-11.6</v>
-      </c>
-      <c r="E42" s="7">
-        <v>0.13</v>
+        <v>-11.91</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2573,13 +2561,13 @@
         <v>6</v>
       </c>
       <c r="C43" s="6">
-        <v>-9.58</v>
+        <v>-9.56</v>
       </c>
       <c r="D43" s="6">
-        <v>-9.56</v>
-      </c>
-      <c r="E43" s="7">
-        <v>0.02</v>
+        <v>-10.33</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2590,13 +2578,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>1083.6</v>
+        <v>1124.4</v>
       </c>
       <c r="D44" s="6">
-        <v>1124.4</v>
+        <v>1178.9</v>
       </c>
       <c r="E44" s="7">
-        <v>40.8</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2607,13 +2595,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>880</v>
+        <v>892</v>
       </c>
       <c r="D45" s="6">
-        <v>892</v>
+        <v>910</v>
       </c>
       <c r="E45" s="7">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2624,13 +2612,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>1764.5</v>
+        <v>1800</v>
       </c>
       <c r="D46" s="6">
-        <v>1800</v>
-      </c>
-      <c r="E46" s="7">
-        <v>35.5</v>
+        <v>1764</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-36</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2641,13 +2629,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>1929.8</v>
+        <v>1999.5</v>
       </c>
       <c r="D47" s="6">
-        <v>1999.5</v>
-      </c>
-      <c r="E47" s="7">
-        <v>69.7</v>
+        <v>1940.8</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-58.7</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2658,13 +2646,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>703.1</v>
+        <v>700.7</v>
       </c>
       <c r="D48" s="6">
-        <v>700.7</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-2.4</v>
+        <v>700.9</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.2</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2675,13 +2663,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>3049.7</v>
+        <v>3054.1</v>
       </c>
       <c r="D49" s="6">
-        <v>3054.1</v>
-      </c>
-      <c r="E49" s="7">
-        <v>4.4</v>
+        <v>3043.4</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-10.7</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2692,13 +2680,13 @@
         <v>2</v>
       </c>
       <c r="C50" s="6">
-        <v>8765</v>
+        <v>8767.5</v>
       </c>
       <c r="D50" s="6">
-        <v>8767.5</v>
-      </c>
-      <c r="E50" s="7">
-        <v>2.5</v>
+        <v>8640.5</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-127</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2709,13 +2697,13 @@
         <v>13</v>
       </c>
       <c r="C51" s="6">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D51" s="6">
-        <v>57</v>
+        <v>85</v>
       </c>
       <c r="E51" s="7">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2726,251 +2714,285 @@
         <v>13</v>
       </c>
       <c r="C52" s="6">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="D52" s="6">
-        <v>43</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-14</v>
+        <v>71</v>
+      </c>
+      <c r="E52" s="7">
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C53" s="6">
-        <v>48.17</v>
+        <v>85</v>
       </c>
       <c r="D53" s="6">
-        <v>54.96</v>
-      </c>
-      <c r="E53" s="7">
-        <v>6.79</v>
+        <v>57</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-28</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C54" s="6">
-        <v>48.11</v>
+        <v>71</v>
       </c>
       <c r="D54" s="6">
-        <v>50.91</v>
-      </c>
-      <c r="E54" s="7">
-        <v>2.8</v>
+        <v>43</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-28</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>37.52</v>
+        <v>54.96</v>
       </c>
       <c r="D55" s="6">
-        <v>44.8</v>
+        <v>62.11</v>
       </c>
       <c r="E55" s="7">
-        <v>7.28</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>41.6</v>
+        <v>50.91</v>
       </c>
       <c r="D56" s="6">
-        <v>55.55</v>
+        <v>54.86</v>
       </c>
       <c r="E56" s="7">
-        <v>13.95</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>27.88</v>
+        <v>44.8</v>
       </c>
       <c r="D57" s="6">
-        <v>27.39</v>
+        <v>39.74</v>
       </c>
       <c r="E57" s="8">
-        <v>-0.49</v>
+        <v>-5.06</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>45.91</v>
+        <v>55.55</v>
       </c>
       <c r="D58" s="6">
-        <v>46.25</v>
-      </c>
-      <c r="E58" s="7">
-        <v>0.34</v>
+        <v>45.66</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-9.890000000000001</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C59" s="6">
-        <v>62.27</v>
+        <v>27.39</v>
       </c>
       <c r="D59" s="6">
-        <v>62.32</v>
+        <v>27.51</v>
       </c>
       <c r="E59" s="7">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C60" s="6">
-        <v>7.21</v>
+        <v>46.25</v>
       </c>
       <c r="D60" s="6">
-        <v>170.12</v>
-      </c>
-      <c r="E60" s="7">
-        <v>162.91</v>
+        <v>45.5</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C61" s="6">
-        <v>-7.15</v>
+        <v>62.32</v>
       </c>
       <c r="D61" s="6">
-        <v>21.7</v>
-      </c>
-      <c r="E61" s="7">
-        <v>28.85</v>
+        <v>58.03</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-4.29</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>66.97</v>
+        <v>170.12</v>
       </c>
       <c r="D62" s="6">
-        <v>32.41</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-34.56</v>
+        <v>1652.37</v>
+      </c>
+      <c r="E62" s="7">
+        <v>1482.25</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C63" s="6">
-        <v>-6.77</v>
+        <v>21.7</v>
       </c>
       <c r="D63" s="6">
-        <v>129.32</v>
-      </c>
-      <c r="E63" s="7">
-        <v>136.09</v>
+        <v>19.31</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-2.39</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C64" s="6">
-        <v>-80.59999999999999</v>
+        <v>32.41</v>
       </c>
       <c r="D64" s="6">
-        <v>5.86</v>
-      </c>
-      <c r="E64" s="7">
-        <v>86.45999999999999</v>
+        <v>-22.17</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-54.58</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C65" s="6">
-        <v>-6.35</v>
+        <v>129.32</v>
       </c>
       <c r="D65" s="6">
-        <v>-18.29</v>
+        <v>-38.94</v>
       </c>
       <c r="E65" s="8">
-        <v>-11.94</v>
+        <v>-168.26</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C66" s="6">
-        <v>-33.29</v>
+        <v>5.86</v>
       </c>
       <c r="D66" s="6">
+        <v>-72.62</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-78.48</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="6">
+        <v>-18.29</v>
+      </c>
+      <c r="D67" s="6">
+        <v>-67.75</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-49.46</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="6">
         <v>0.36</v>
       </c>
-      <c r="E66" s="7">
-        <v>33.65</v>
+      <c r="D68" s="6">
+        <v>-64.73</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-65.09</v>
       </c>
     </row>
   </sheetData>
@@ -3000,28 +3022,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>74</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3035,22 +3057,22 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>48.9</v>
+        <v>47.6</v>
       </c>
       <c r="E2" s="11">
         <v>70</v>
       </c>
       <c r="F2" s="11">
-        <v>-0.3</v>
+        <v>-2</v>
       </c>
       <c r="G2" s="11">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
       </c>
       <c r="I2" s="11">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -3175,25 +3197,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.5800999999999999</v>
+        <v>0.5703</v>
       </c>
       <c r="B2" s="14">
-        <v>0.3064</v>
+        <v>0.3042</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2536</v>
+        <v>0.2521</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2133</v>
+        <v>0.202</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1548</v>
+        <v>0.1509</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1195</v>
+        <v>0.1161</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0611</v>
+        <v>0.0697</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,40 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>55.5 → 45.7</t>
-  </si>
-  <si>
-    <t>55.5</t>
-  </si>
-  <si>
-    <t>45.7</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -407,18 +374,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -930,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1178.9</v>
+        <v>1211.3</v>
       </c>
       <c r="D2">
-        <v>4.85</v>
+        <v>2.75</v>
       </c>
       <c r="E2">
         <v>1241.7</v>
@@ -942,46 +908,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-5.06</v>
+        <v>-2.45</v>
       </c>
       <c r="H2">
-        <v>57.53</v>
+        <v>61.86</v>
       </c>
       <c r="I2">
-        <v>9.640000000000001</v>
+        <v>17.4</v>
       </c>
       <c r="J2">
-        <v>3.63</v>
+        <v>3.55</v>
       </c>
       <c r="K2">
-        <v>-2.68</v>
+        <v>-0.08</v>
       </c>
       <c r="L2">
-        <v>17.92</v>
+        <v>21.91</v>
       </c>
       <c r="M2">
-        <v>6.97</v>
+        <v>7.69</v>
       </c>
       <c r="N2">
         <v>85</v>
       </c>
       <c r="O2">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="P2">
-        <v>1094.06</v>
+        <v>1129.96</v>
       </c>
       <c r="Q2">
-        <v>1098.57</v>
+        <v>1103.03</v>
       </c>
       <c r="R2">
-        <v>1097.08</v>
+        <v>1099.85</v>
       </c>
       <c r="S2">
-        <v>960.95</v>
+        <v>962.54</v>
       </c>
       <c r="T2">
-        <v>22.68</v>
+        <v>25.84</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -996,43 +962,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>62.11</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Z2">
-        <v>0.79</v>
+        <v>9.42</v>
       </c>
       <c r="AA2">
-        <v>-4.86</v>
+        <v>-2</v>
       </c>
       <c r="AB2">
-        <v>5.65</v>
+        <v>11.42</v>
       </c>
       <c r="AC2">
-        <v>88.25</v>
+        <v>100</v>
       </c>
       <c r="AD2">
-        <v>60.81</v>
+        <v>84</v>
       </c>
       <c r="AE2">
-        <v>48.65</v>
+        <v>49.66</v>
       </c>
       <c r="AF2">
-        <v>1652.37</v>
+        <v>154.12</v>
       </c>
       <c r="AG2">
-        <v>1160.07</v>
+        <v>1182.12</v>
       </c>
       <c r="AH2">
-        <v>1037.08</v>
+        <v>1023.94</v>
       </c>
       <c r="AI2">
-        <v>1044.34</v>
+        <v>1059.41</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>26.33</v>
+        <v>30.69</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1043,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>910</v>
+        <v>896.1</v>
       </c>
       <c r="D3">
-        <v>2.02</v>
+        <v>-1.53</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1055,46 +1021,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-6.81</v>
+        <v>-8.23</v>
       </c>
       <c r="H3">
-        <v>71.87</v>
+        <v>69.23999999999999</v>
       </c>
       <c r="I3">
-        <v>0.11</v>
+        <v>4.44</v>
       </c>
       <c r="J3">
-        <v>3.85</v>
+        <v>3.36</v>
       </c>
       <c r="K3">
-        <v>-5.46</v>
+        <v>-5.72</v>
       </c>
       <c r="L3">
-        <v>15.12</v>
+        <v>13.4</v>
       </c>
       <c r="M3">
-        <v>57.03</v>
+        <v>55.04</v>
       </c>
       <c r="N3">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="O3">
         <v>68</v>
       </c>
       <c r="P3">
-        <v>878.3099999999999</v>
+        <v>885.9299999999999</v>
       </c>
       <c r="Q3">
-        <v>891.05</v>
+        <v>891.98</v>
       </c>
       <c r="R3">
-        <v>886.1900000000001</v>
+        <v>886</v>
       </c>
       <c r="S3">
-        <v>786.13</v>
+        <v>787.3</v>
       </c>
       <c r="T3">
-        <v>15.76</v>
+        <v>13.82</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1109,34 +1075,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>54.86</v>
+        <v>51.42</v>
       </c>
       <c r="Z3">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AA3">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB3">
-        <v>-0.16</v>
+        <v>0.12</v>
       </c>
       <c r="AC3">
-        <v>55.22</v>
+        <v>60.95</v>
       </c>
       <c r="AD3">
-        <v>32.93</v>
+        <v>48.94</v>
       </c>
       <c r="AE3">
-        <v>26.02</v>
+        <v>26.3</v>
       </c>
       <c r="AF3">
-        <v>19.31</v>
+        <v>-9.9</v>
       </c>
       <c r="AG3">
-        <v>931.08</v>
+        <v>931.55</v>
       </c>
       <c r="AH3">
-        <v>851.01</v>
+        <v>852.41</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1145,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>28.28</v>
+        <v>26.15</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1156,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1764</v>
+        <v>1759.1</v>
       </c>
       <c r="D4">
-        <v>-2</v>
+        <v>-0.28</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1168,46 +1134,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-9.07</v>
+        <v>-9.32</v>
       </c>
       <c r="H4">
-        <v>30.21</v>
+        <v>29.85</v>
       </c>
       <c r="I4">
-        <v>-4.44</v>
+        <v>-1.81</v>
       </c>
       <c r="J4">
-        <v>-6.61</v>
+        <v>-5.57</v>
       </c>
       <c r="K4">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="L4">
-        <v>11.51</v>
+        <v>11.89</v>
       </c>
       <c r="M4">
-        <v>25.21</v>
+        <v>25.46</v>
       </c>
       <c r="N4">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="O4">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P4">
-        <v>1777.14</v>
+        <v>1770.64</v>
       </c>
       <c r="Q4">
-        <v>1830.18</v>
+        <v>1825.8</v>
       </c>
       <c r="R4">
-        <v>1833.43</v>
+        <v>1832.39</v>
       </c>
       <c r="S4">
-        <v>1682.94</v>
+        <v>1683.39</v>
       </c>
       <c r="T4">
-        <v>4.82</v>
+        <v>4.5</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1222,34 +1188,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>39.74</v>
+        <v>39.1</v>
       </c>
       <c r="Z4">
-        <v>-17.61</v>
+        <v>-20.12</v>
       </c>
       <c r="AA4">
-        <v>-7.81</v>
+        <v>-10.27</v>
       </c>
       <c r="AB4">
-        <v>-9.800000000000001</v>
+        <v>-9.85</v>
       </c>
       <c r="AC4">
-        <v>21.2</v>
+        <v>24.72</v>
       </c>
       <c r="AD4">
-        <v>12.48</v>
+        <v>20.72</v>
       </c>
       <c r="AE4">
-        <v>46.46</v>
+        <v>44.75</v>
       </c>
       <c r="AF4">
-        <v>-22.17</v>
+        <v>-24.44</v>
       </c>
       <c r="AG4">
-        <v>1902.46</v>
+        <v>1904.22</v>
       </c>
       <c r="AH4">
-        <v>1757.9</v>
+        <v>1747.38</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1258,7 +1224,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>21.53</v>
+        <v>22.69</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1269,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1940.8</v>
+        <v>1944.9</v>
       </c>
       <c r="D5">
-        <v>-2.94</v>
+        <v>0.21</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1281,46 +1247,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-19.09</v>
+        <v>-18.92</v>
       </c>
       <c r="H5">
-        <v>11.18</v>
+        <v>11.42</v>
       </c>
       <c r="I5">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="J5">
-        <v>-3.19</v>
+        <v>-2.56</v>
       </c>
       <c r="K5">
-        <v>-2.36</v>
+        <v>-2.4</v>
       </c>
       <c r="L5">
-        <v>-14</v>
+        <v>-16.11</v>
       </c>
       <c r="M5">
-        <v>20.2</v>
+        <v>19.88</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="P5">
-        <v>1949.4</v>
+        <v>1950.56</v>
       </c>
       <c r="Q5">
-        <v>1938.59</v>
+        <v>1939.51</v>
       </c>
       <c r="R5">
-        <v>2008.75</v>
+        <v>2006.44</v>
       </c>
       <c r="S5">
-        <v>2074.39</v>
+        <v>2072.57</v>
       </c>
       <c r="T5">
-        <v>-6.44</v>
+        <v>-6.16</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1335,34 +1301,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>45.66</v>
+        <v>46.38</v>
       </c>
       <c r="Z5">
-        <v>-14.94</v>
+        <v>-14.35</v>
       </c>
       <c r="AA5">
-        <v>-20.24</v>
+        <v>-19.06</v>
       </c>
       <c r="AB5">
-        <v>5.31</v>
+        <v>4.72</v>
       </c>
       <c r="AC5">
-        <v>69.09</v>
+        <v>68.26000000000001</v>
       </c>
       <c r="AD5">
-        <v>68.87</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="AE5">
-        <v>47.07</v>
+        <v>45.02</v>
       </c>
       <c r="AF5">
-        <v>-38.94</v>
+        <v>-46.37</v>
       </c>
       <c r="AG5">
-        <v>1984.52</v>
+        <v>1985.16</v>
       </c>
       <c r="AH5">
-        <v>1892.66</v>
+        <v>1893.85</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1371,7 +1337,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>24.57</v>
+        <v>25.56</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1382,58 +1348,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>700.9</v>
+        <v>695.55</v>
       </c>
       <c r="D6">
-        <v>0.03</v>
+        <v>-0.76</v>
       </c>
       <c r="E6">
-        <v>1095.8</v>
+        <v>1094.1</v>
       </c>
       <c r="F6">
-        <v>700.7</v>
+        <v>695.55</v>
       </c>
       <c r="G6">
-        <v>-36.04</v>
+        <v>-36.43</v>
       </c>
       <c r="H6">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>-2.79</v>
+        <v>-1.02</v>
       </c>
       <c r="J6">
-        <v>-13.5</v>
+        <v>-12.76</v>
       </c>
       <c r="K6">
-        <v>-2.1</v>
+        <v>-2.08</v>
       </c>
       <c r="L6">
-        <v>-35.58</v>
+        <v>-36.53</v>
       </c>
       <c r="M6">
-        <v>11.61</v>
+        <v>10.56</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P6">
-        <v>702.1</v>
+        <v>700.66</v>
       </c>
       <c r="Q6">
-        <v>762.51</v>
+        <v>756.09</v>
       </c>
       <c r="R6">
-        <v>773.29</v>
+        <v>771.51</v>
       </c>
       <c r="S6">
-        <v>836.84</v>
+        <v>835.14</v>
       </c>
       <c r="T6">
-        <v>-16.24</v>
+        <v>-16.71</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1448,43 +1414,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>27.51</v>
+        <v>26.3</v>
       </c>
       <c r="Z6">
-        <v>-22.78</v>
+        <v>-23.83</v>
       </c>
       <c r="AA6">
-        <v>-13.84</v>
+        <v>-15.84</v>
       </c>
       <c r="AB6">
-        <v>-8.949999999999999</v>
+        <v>-8</v>
       </c>
       <c r="AC6">
-        <v>0.35</v>
+        <v>0.15</v>
       </c>
       <c r="AD6">
-        <v>0.36</v>
+        <v>0.29</v>
       </c>
       <c r="AE6">
-        <v>22.52</v>
+        <v>21.69</v>
       </c>
       <c r="AF6">
-        <v>-72.62</v>
+        <v>-75.03</v>
       </c>
       <c r="AG6">
-        <v>849.1799999999999</v>
+        <v>842.62</v>
       </c>
       <c r="AH6">
-        <v>675.83</v>
+        <v>669.55</v>
       </c>
       <c r="AI6">
-        <v>765.23</v>
+        <v>764.55</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>42.92</v>
+        <v>45.43</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1495,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3043.4</v>
+        <v>2983</v>
       </c>
       <c r="D7">
-        <v>-0.35</v>
+        <v>-1.98</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1507,46 +1473,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-11.91</v>
+        <v>-13.66</v>
       </c>
       <c r="H7">
-        <v>60.9</v>
+        <v>57.71</v>
       </c>
       <c r="I7">
-        <v>-6.36</v>
+        <v>-4.65</v>
       </c>
       <c r="J7">
-        <v>-4.9</v>
+        <v>-10.12</v>
       </c>
       <c r="K7">
-        <v>17.68</v>
+        <v>14.06</v>
       </c>
       <c r="L7">
-        <v>25.02</v>
+        <v>21.11</v>
       </c>
       <c r="M7">
-        <v>30.42</v>
+        <v>30.07</v>
       </c>
       <c r="N7">
         <v>99</v>
       </c>
       <c r="O7">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P7">
-        <v>3078</v>
+        <v>3048.88</v>
       </c>
       <c r="Q7">
-        <v>3222.57</v>
+        <v>3199.66</v>
       </c>
       <c r="R7">
-        <v>2919.06</v>
+        <v>2929.41</v>
       </c>
       <c r="S7">
-        <v>2472.61</v>
+        <v>2476.05</v>
       </c>
       <c r="T7">
-        <v>23.08</v>
+        <v>20.47</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1561,43 +1527,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>45.5</v>
+        <v>41.38</v>
       </c>
       <c r="Z7">
-        <v>26.09</v>
+        <v>12.51</v>
       </c>
       <c r="AA7">
-        <v>71.04000000000001</v>
+        <v>59.34</v>
       </c>
       <c r="AB7">
-        <v>-44.95</v>
+        <v>-46.83</v>
       </c>
       <c r="AC7">
         <v>0.58</v>
       </c>
       <c r="AD7">
-        <v>0.38</v>
+        <v>0.58</v>
       </c>
       <c r="AE7">
-        <v>132.8</v>
+        <v>132.57</v>
       </c>
       <c r="AF7">
-        <v>-67.75</v>
+        <v>46.78</v>
       </c>
       <c r="AG7">
-        <v>3466.72</v>
+        <v>3443.4</v>
       </c>
       <c r="AH7">
-        <v>2978.42</v>
+        <v>2955.91</v>
       </c>
       <c r="AI7">
-        <v>3037.42</v>
+        <v>3398.57</v>
       </c>
       <c r="AJ7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK7">
-        <v>22.51</v>
+        <v>25.21</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1608,58 +1574,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8640.5</v>
+        <v>8627</v>
       </c>
       <c r="D8">
-        <v>-1.45</v>
+        <v>-0.16</v>
       </c>
       <c r="E8">
-        <v>9635.76</v>
+        <v>9631.77</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-10.33</v>
+        <v>-10.43</v>
       </c>
       <c r="H8">
-        <v>45.84</v>
+        <v>45.62</v>
       </c>
       <c r="I8">
-        <v>-1.95</v>
+        <v>0.55</v>
       </c>
       <c r="J8">
-        <v>6.55</v>
+        <v>5.43</v>
       </c>
       <c r="K8">
-        <v>11.18</v>
+        <v>10.48</v>
       </c>
       <c r="L8">
-        <v>-10.87</v>
+        <v>-10.47</v>
       </c>
       <c r="M8">
-        <v>15.09</v>
+        <v>15.08</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="P8">
-        <v>8683.299999999999</v>
+        <v>8692.700000000001</v>
       </c>
       <c r="Q8">
-        <v>8393.25</v>
+        <v>8410.299999999999</v>
       </c>
       <c r="R8">
-        <v>8135.67</v>
+        <v>8151.82</v>
       </c>
       <c r="S8">
-        <v>7421.2</v>
+        <v>7424.4</v>
       </c>
       <c r="T8">
-        <v>16.43</v>
+        <v>16.2</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1674,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>58.03</v>
+        <v>57.57</v>
       </c>
       <c r="Z8">
-        <v>176.11</v>
+        <v>169.08</v>
       </c>
       <c r="AA8">
-        <v>145.27</v>
+        <v>150.04</v>
       </c>
       <c r="AB8">
-        <v>30.84</v>
+        <v>19.04</v>
       </c>
       <c r="AC8">
-        <v>73.84</v>
+        <v>65.58</v>
       </c>
       <c r="AD8">
-        <v>74.20999999999999</v>
+        <v>72.38</v>
       </c>
       <c r="AE8">
-        <v>321.37</v>
+        <v>325.16</v>
       </c>
       <c r="AF8">
-        <v>-64.73</v>
+        <v>-5.11</v>
       </c>
       <c r="AG8">
-        <v>8900.290000000001</v>
+        <v>8925.030000000001</v>
       </c>
       <c r="AH8">
-        <v>7886.21</v>
+        <v>7895.57</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
@@ -1710,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>47.03</v>
+        <v>47.65</v>
       </c>
     </row>
   </sheetData>
@@ -1851,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1871,1134 +1837,1025 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>61</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>3.63</v>
+      </c>
+      <c r="D7" s="5">
+        <v>3.55</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.08</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>66</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3.85</v>
+      </c>
+      <c r="D8" s="5">
+        <v>3.36</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-6.61</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-5.57</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-3.19</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-2.56</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-13.5</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-12.76</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-4.9</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-10.12</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-5.22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>6.55</v>
+      </c>
+      <c r="D13" s="5">
+        <v>5.43</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>3.42</v>
-      </c>
-      <c r="D9" s="6">
-        <v>3.63</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="D14" s="5">
+        <v>17.4</v>
+      </c>
+      <c r="E14" s="7">
+        <v>7.76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>3.35</v>
-      </c>
-      <c r="D10" s="6">
-        <v>3.85</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0.11</v>
+      </c>
+      <c r="D15" s="5">
+        <v>4.44</v>
+      </c>
+      <c r="E15" s="7">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-3.92</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-6.61</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-2.69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-4.44</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-1.81</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-1.89</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-3.19</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>0.61</v>
+      </c>
+      <c r="D17" s="5">
+        <v>0.3</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-10.97</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-2.79</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-1.02</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-6.36</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-4.65</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-1.95</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0.55</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>17.92</v>
+      </c>
+      <c r="D21" s="5">
+        <v>21.91</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>15.12</v>
+      </c>
+      <c r="D22" s="5">
+        <v>13.4</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>11.51</v>
+      </c>
+      <c r="D23" s="5">
+        <v>11.89</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-14</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-16.11</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-35.58</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-36.53</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>25.02</v>
+      </c>
+      <c r="D26" s="5">
+        <v>21.11</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-3.91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-10.87</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-10.47</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-2.68</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-0.08</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-5.46</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-5.72</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>2.63</v>
+      </c>
+      <c r="D30" s="5">
+        <v>1.92</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-2.36</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-2.4</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-2.1</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-2.08</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>17.68</v>
+      </c>
+      <c r="D33" s="5">
+        <v>14.06</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-3.62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>11.18</v>
+      </c>
+      <c r="D34" s="5">
+        <v>10.48</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-5.06</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-2.45</v>
+      </c>
+      <c r="E35" s="7">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-6.81</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-8.23</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-9.07</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-9.32</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-19.09</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-18.92</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-36.04</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-36.43</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-11.91</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-13.66</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-10.33</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-10.43</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1178.9</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1211.3</v>
+      </c>
+      <c r="E42" s="7">
+        <v>32.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>910</v>
+      </c>
+      <c r="D43" s="5">
+        <v>896.1</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-13.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1764</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1759.1</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-4.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1940.8</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1944.9</v>
+      </c>
+      <c r="E45" s="7">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>700.9</v>
+      </c>
+      <c r="D46" s="5">
+        <v>695.55</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-5.35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>3043.4</v>
+      </c>
+      <c r="D47" s="5">
+        <v>2983</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-60.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>8640.5</v>
+      </c>
+      <c r="D48" s="5">
+        <v>8627</v>
+      </c>
+      <c r="E48" s="6">
         <v>-13.5</v>
       </c>
-      <c r="E13" s="8">
-        <v>-2.53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="5">
+        <v>71</v>
+      </c>
+      <c r="D49" s="5">
+        <v>57</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="5">
+        <v>57</v>
+      </c>
+      <c r="D50" s="5">
+        <v>71</v>
+      </c>
+      <c r="E50" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>62.11</v>
+      </c>
+      <c r="D51" s="5">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="E51" s="7">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>54.86</v>
+      </c>
+      <c r="D52" s="5">
+        <v>51.42</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-3.44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>39.74</v>
+      </c>
+      <c r="D53" s="5">
+        <v>39.1</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>45.66</v>
+      </c>
+      <c r="D54" s="5">
+        <v>46.38</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>27.51</v>
+      </c>
+      <c r="D55" s="5">
+        <v>26.3</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.35</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-4.9</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-2.55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>45.5</v>
+      </c>
+      <c r="D56" s="5">
+        <v>41.38</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-4.12</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>10.04</v>
-      </c>
-      <c r="D15" s="6">
-        <v>6.55</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-3.49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>58.03</v>
+      </c>
+      <c r="D57" s="5">
+        <v>57.57</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-0.46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>3.14</v>
-      </c>
-      <c r="D16" s="6">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="E16" s="7">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>1652.37</v>
+      </c>
+      <c r="D58" s="5">
+        <v>154.12</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-1498.25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-2.47</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.11</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>19.31</v>
+      </c>
+      <c r="D59" s="5">
+        <v>-9.9</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-29.21</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-3.17</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-4.44</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-22.17</v>
+      </c>
+      <c r="D60" s="5">
+        <v>-24.44</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>1.92</v>
-      </c>
-      <c r="D19" s="6">
-        <v>0.61</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-1.31</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-38.94</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-46.37</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-7.43</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-4.53</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-2.79</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="5">
+        <v>-72.62</v>
+      </c>
+      <c r="D62" s="5">
+        <v>-75.03</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-3.26</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-6.36</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>-67.75</v>
+      </c>
+      <c r="D63" s="5">
+        <v>46.78</v>
+      </c>
+      <c r="E63" s="7">
+        <v>114.53</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>1.13</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-1.95</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-3.08</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>15.03</v>
-      </c>
-      <c r="D23" s="6">
-        <v>17.92</v>
-      </c>
-      <c r="E23" s="7">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>12.97</v>
-      </c>
-      <c r="D24" s="6">
-        <v>15.12</v>
-      </c>
-      <c r="E24" s="7">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>18.69</v>
-      </c>
-      <c r="D25" s="6">
-        <v>11.51</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-7.18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-9.369999999999999</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-14</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-4.63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-34.84</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-35.58</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>25.22</v>
-      </c>
-      <c r="D28" s="6">
-        <v>25.02</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-8.529999999999999</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-10.87</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-2.34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-9.449999999999999</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-2.68</v>
-      </c>
-      <c r="E30" s="7">
-        <v>6.77</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-7.44</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-5.46</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>6.3</v>
-      </c>
-      <c r="D32" s="6">
-        <v>2.63</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-3.67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-0.78</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-2.36</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-0.48</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-2.1</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>16.72</v>
-      </c>
-      <c r="D35" s="6">
-        <v>17.68</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>10.85</v>
-      </c>
-      <c r="D36" s="6">
-        <v>11.18</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-9.449999999999999</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-5.06</v>
-      </c>
-      <c r="E37" s="7">
-        <v>4.39</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-8.65</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-6.81</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1.84</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-7.22</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-9.07</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-16.64</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-19.09</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-2.45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-36.06</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-36.04</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-11.6</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-11.91</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-9.56</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-10.33</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1124.4</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1178.9</v>
-      </c>
-      <c r="E44" s="7">
-        <v>54.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>892</v>
-      </c>
-      <c r="D45" s="6">
-        <v>910</v>
-      </c>
-      <c r="E45" s="7">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>1800</v>
-      </c>
-      <c r="D46" s="6">
-        <v>1764</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-36</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>1999.5</v>
-      </c>
-      <c r="D47" s="6">
-        <v>1940.8</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-58.7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>700.7</v>
-      </c>
-      <c r="D48" s="6">
-        <v>700.9</v>
-      </c>
-      <c r="E48" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>3054.1</v>
-      </c>
-      <c r="D49" s="6">
-        <v>3043.4</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-10.7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>8767.5</v>
-      </c>
-      <c r="D50" s="6">
-        <v>8640.5</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-127</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="6">
-        <v>57</v>
-      </c>
-      <c r="D51" s="6">
-        <v>85</v>
-      </c>
-      <c r="E51" s="7">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="6">
-        <v>43</v>
-      </c>
-      <c r="D52" s="6">
-        <v>71</v>
-      </c>
-      <c r="E52" s="7">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="6">
-        <v>85</v>
-      </c>
-      <c r="D53" s="6">
-        <v>57</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-28</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" s="6">
-        <v>71</v>
-      </c>
-      <c r="D54" s="6">
-        <v>43</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-28</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>54.96</v>
-      </c>
-      <c r="D55" s="6">
-        <v>62.11</v>
-      </c>
-      <c r="E55" s="7">
-        <v>7.15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>50.91</v>
-      </c>
-      <c r="D56" s="6">
-        <v>54.86</v>
-      </c>
-      <c r="E56" s="7">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>44.8</v>
-      </c>
-      <c r="D57" s="6">
-        <v>39.74</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-5.06</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>55.55</v>
-      </c>
-      <c r="D58" s="6">
-        <v>45.66</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-9.890000000000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>27.39</v>
-      </c>
-      <c r="D59" s="6">
-        <v>27.51</v>
-      </c>
-      <c r="E59" s="7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="6">
-        <v>46.25</v>
-      </c>
-      <c r="D60" s="6">
-        <v>45.5</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C61" s="6">
-        <v>62.32</v>
-      </c>
-      <c r="D61" s="6">
-        <v>58.03</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-4.29</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B62" s="5" t="s">
+      <c r="B64" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="6">
-        <v>170.12</v>
-      </c>
-      <c r="D62" s="6">
-        <v>1652.37</v>
-      </c>
-      <c r="E62" s="7">
-        <v>1482.25</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>21.7</v>
-      </c>
-      <c r="D63" s="6">
-        <v>19.31</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-2.39</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>32.41</v>
-      </c>
-      <c r="D64" s="6">
-        <v>-22.17</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-54.58</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>129.32</v>
-      </c>
-      <c r="D65" s="6">
-        <v>-38.94</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-168.26</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>5.86</v>
-      </c>
-      <c r="D66" s="6">
-        <v>-72.62</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-78.48</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="6">
-        <v>-18.29</v>
-      </c>
-      <c r="D67" s="6">
-        <v>-67.75</v>
-      </c>
-      <c r="E67" s="8">
-        <v>-49.46</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C68" s="6">
-        <v>0.36</v>
-      </c>
-      <c r="D68" s="6">
+      <c r="C64" s="5">
         <v>-64.73</v>
       </c>
-      <c r="E68" s="8">
-        <v>-65.09</v>
+      <c r="D64" s="5">
+        <v>-5.11</v>
+      </c>
+      <c r="E64" s="7">
+        <v>59.62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3018,60 +2875,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="10">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="11">
+        <v>7</v>
+      </c>
+      <c r="D2" s="10">
+        <v>46.8</v>
+      </c>
+      <c r="E2" s="10">
         <v>70</v>
       </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="11">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="12">
-        <v>7</v>
-      </c>
-      <c r="D2" s="11">
-        <v>47.6</v>
-      </c>
-      <c r="E2" s="11">
-        <v>70</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>2.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-2.7</v>
+      </c>
+      <c r="G2" s="10">
+        <v>2.3</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>60</v>
       </c>
     </row>
@@ -3173,49 +3030,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.5703</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3042</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2521</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.202</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1509</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1161</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0697</v>
+      <c r="A2" s="13">
+        <v>0.5504</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.3007</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.2546</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1988</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1508</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.1056</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.07690000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,49 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.5% → 0.0%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.5%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>65.6 → 70.4</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>65.6</t>
+  </si>
+  <si>
+    <t>70.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -224,7 +266,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,20 +300,27 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -298,13 +347,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,21 +429,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -397,7 +454,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -896,58 +953,58 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1211.3</v>
+        <v>1264.5</v>
       </c>
       <c r="D2">
-        <v>2.75</v>
+        <v>4.39</v>
       </c>
       <c r="E2">
-        <v>1241.7</v>
+        <v>1264.5</v>
       </c>
       <c r="F2">
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-2.45</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>61.86</v>
+        <v>68.97</v>
       </c>
       <c r="I2">
-        <v>17.4</v>
+        <v>20.25</v>
       </c>
       <c r="J2">
-        <v>3.55</v>
+        <v>12.68</v>
       </c>
       <c r="K2">
-        <v>-0.08</v>
+        <v>8.77</v>
       </c>
       <c r="L2">
-        <v>21.91</v>
+        <v>28.31</v>
       </c>
       <c r="M2">
-        <v>7.69</v>
+        <v>7.99</v>
       </c>
       <c r="N2">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="O2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="P2">
-        <v>1129.96</v>
+        <v>1172.54</v>
       </c>
       <c r="Q2">
-        <v>1103.03</v>
+        <v>1110.92</v>
       </c>
       <c r="R2">
-        <v>1099.85</v>
+        <v>1103.81</v>
       </c>
       <c r="S2">
-        <v>962.54</v>
+        <v>964.47</v>
       </c>
       <c r="T2">
-        <v>25.84</v>
+        <v>31.11</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,43 +1019,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>65.59999999999999</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="Z2">
-        <v>9.42</v>
+        <v>20.31</v>
       </c>
       <c r="AA2">
-        <v>-2</v>
+        <v>2.46</v>
       </c>
       <c r="AB2">
-        <v>11.42</v>
+        <v>17.85</v>
       </c>
       <c r="AC2">
         <v>100</v>
       </c>
       <c r="AD2">
-        <v>84</v>
+        <v>96.08</v>
       </c>
       <c r="AE2">
-        <v>49.66</v>
+        <v>50.52</v>
       </c>
       <c r="AF2">
-        <v>154.12</v>
+        <v>52.46</v>
       </c>
       <c r="AG2">
-        <v>1182.12</v>
+        <v>1218.06</v>
       </c>
       <c r="AH2">
-        <v>1023.94</v>
+        <v>1003.78</v>
       </c>
       <c r="AI2">
-        <v>1059.41</v>
+        <v>1091.15</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>30.69</v>
+        <v>35.29</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1066,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>896.1</v>
+        <v>895</v>
       </c>
       <c r="D3">
-        <v>-1.53</v>
+        <v>-0.12</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1021,46 +1078,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-8.23</v>
+        <v>-8.35</v>
       </c>
       <c r="H3">
-        <v>69.23999999999999</v>
+        <v>69.03</v>
       </c>
       <c r="I3">
-        <v>4.44</v>
+        <v>5.1</v>
       </c>
       <c r="J3">
-        <v>3.36</v>
+        <v>1.99</v>
       </c>
       <c r="K3">
-        <v>-5.72</v>
+        <v>-2.66</v>
       </c>
       <c r="L3">
-        <v>13.4</v>
+        <v>14.33</v>
       </c>
       <c r="M3">
-        <v>55.04</v>
+        <v>53.5</v>
       </c>
       <c r="N3">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="P3">
-        <v>885.9299999999999</v>
+        <v>894.62</v>
       </c>
       <c r="Q3">
-        <v>891.98</v>
+        <v>892.8</v>
       </c>
       <c r="R3">
-        <v>886</v>
+        <v>885.63</v>
       </c>
       <c r="S3">
-        <v>787.3</v>
+        <v>788.47</v>
       </c>
       <c r="T3">
-        <v>13.82</v>
+        <v>13.51</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1075,34 +1132,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>51.42</v>
+        <v>51.15</v>
       </c>
       <c r="Z3">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AA3">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AB3">
-        <v>0.12</v>
+        <v>0.21</v>
       </c>
       <c r="AC3">
-        <v>60.95</v>
+        <v>61.36</v>
       </c>
       <c r="AD3">
-        <v>48.94</v>
+        <v>59.18</v>
       </c>
       <c r="AE3">
-        <v>26.3</v>
+        <v>25.59</v>
       </c>
       <c r="AF3">
-        <v>-9.9</v>
+        <v>-48.87</v>
       </c>
       <c r="AG3">
-        <v>931.55</v>
+        <v>931.88</v>
       </c>
       <c r="AH3">
-        <v>852.41</v>
+        <v>853.73</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1111,7 +1168,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>26.15</v>
+        <v>23.43</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1179,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1759.1</v>
+        <v>1774</v>
       </c>
       <c r="D4">
-        <v>-0.28</v>
+        <v>0.85</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1134,46 +1191,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-9.32</v>
+        <v>-8.56</v>
       </c>
       <c r="H4">
-        <v>29.85</v>
+        <v>30.95</v>
       </c>
       <c r="I4">
-        <v>-1.81</v>
+        <v>0.48</v>
       </c>
       <c r="J4">
-        <v>-5.57</v>
+        <v>-3.94</v>
       </c>
       <c r="K4">
-        <v>1.92</v>
+        <v>-1.05</v>
       </c>
       <c r="L4">
-        <v>11.89</v>
+        <v>11.9</v>
       </c>
       <c r="M4">
-        <v>25.46</v>
+        <v>25.03</v>
       </c>
       <c r="N4">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="O4">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P4">
-        <v>1770.64</v>
+        <v>1772.32</v>
       </c>
       <c r="Q4">
-        <v>1825.8</v>
+        <v>1820.85</v>
       </c>
       <c r="R4">
-        <v>1832.39</v>
+        <v>1832.44</v>
       </c>
       <c r="S4">
-        <v>1683.39</v>
+        <v>1683.89</v>
       </c>
       <c r="T4">
-        <v>4.5</v>
+        <v>5.35</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1188,34 +1245,34 @@
         <v>2</v>
       </c>
       <c r="Y4">
-        <v>39.1</v>
+        <v>42.18</v>
       </c>
       <c r="Z4">
-        <v>-20.12</v>
+        <v>-20.67</v>
       </c>
       <c r="AA4">
-        <v>-10.27</v>
+        <v>-12.35</v>
       </c>
       <c r="AB4">
-        <v>-9.85</v>
+        <v>-8.32</v>
       </c>
       <c r="AC4">
-        <v>24.72</v>
+        <v>18.87</v>
       </c>
       <c r="AD4">
-        <v>20.72</v>
+        <v>21.59</v>
       </c>
       <c r="AE4">
-        <v>44.75</v>
+        <v>43.37</v>
       </c>
       <c r="AF4">
-        <v>-24.44</v>
+        <v>2.24</v>
       </c>
       <c r="AG4">
-        <v>1904.22</v>
+        <v>1899.22</v>
       </c>
       <c r="AH4">
-        <v>1747.38</v>
+        <v>1742.48</v>
       </c>
       <c r="AI4">
         <v>1758.5</v>
@@ -1224,7 +1281,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>22.69</v>
+        <v>22.79</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1292,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1944.9</v>
+        <v>1956</v>
       </c>
       <c r="D5">
-        <v>0.21</v>
+        <v>0.57</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1247,46 +1304,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-18.92</v>
+        <v>-18.46</v>
       </c>
       <c r="H5">
-        <v>11.42</v>
+        <v>12.05</v>
       </c>
       <c r="I5">
-        <v>0.3</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J5">
-        <v>-2.56</v>
+        <v>1.53</v>
       </c>
       <c r="K5">
-        <v>-2.4</v>
+        <v>-1.38</v>
       </c>
       <c r="L5">
-        <v>-16.11</v>
+        <v>-14.8</v>
       </c>
       <c r="M5">
-        <v>19.88</v>
+        <v>20.39</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P5">
-        <v>1950.56</v>
+        <v>1954.2</v>
       </c>
       <c r="Q5">
-        <v>1939.51</v>
+        <v>1941.63</v>
       </c>
       <c r="R5">
-        <v>2006.44</v>
+        <v>2004.13</v>
       </c>
       <c r="S5">
-        <v>2072.57</v>
+        <v>2070.87</v>
       </c>
       <c r="T5">
-        <v>-6.16</v>
+        <v>-5.55</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1301,34 +1358,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>46.38</v>
+        <v>48.37</v>
       </c>
       <c r="Z5">
-        <v>-14.35</v>
+        <v>-12.84</v>
       </c>
       <c r="AA5">
-        <v>-19.06</v>
+        <v>-17.82</v>
       </c>
       <c r="AB5">
-        <v>4.72</v>
+        <v>4.98</v>
       </c>
       <c r="AC5">
-        <v>68.26000000000001</v>
+        <v>53.51</v>
       </c>
       <c r="AD5">
-        <v>70.51000000000001</v>
+        <v>63.62</v>
       </c>
       <c r="AE5">
-        <v>45.02</v>
+        <v>45.58</v>
       </c>
       <c r="AF5">
-        <v>-46.37</v>
+        <v>-0.75</v>
       </c>
       <c r="AG5">
-        <v>1985.16</v>
+        <v>1986.14</v>
       </c>
       <c r="AH5">
-        <v>1893.85</v>
+        <v>1897.11</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1337,7 +1394,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>25.56</v>
+        <v>28.78</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,58 +1405,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>695.55</v>
+        <v>701.4</v>
       </c>
       <c r="D6">
-        <v>-0.76</v>
+        <v>0.84</v>
       </c>
       <c r="E6">
-        <v>1094.1</v>
+        <v>1089.8</v>
       </c>
       <c r="F6">
         <v>695.55</v>
       </c>
       <c r="G6">
-        <v>-36.43</v>
+        <v>-35.64</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="I6">
-        <v>-1.02</v>
+        <v>-0.23</v>
       </c>
       <c r="J6">
-        <v>-12.76</v>
+        <v>-14.87</v>
       </c>
       <c r="K6">
-        <v>-2.08</v>
+        <v>-1.27</v>
       </c>
       <c r="L6">
-        <v>-36.53</v>
+        <v>-35.89</v>
       </c>
       <c r="M6">
-        <v>10.56</v>
+        <v>11.21</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P6">
-        <v>700.66</v>
+        <v>700.33</v>
       </c>
       <c r="Q6">
-        <v>756.09</v>
+        <v>750.64</v>
       </c>
       <c r="R6">
-        <v>771.51</v>
+        <v>769.96</v>
       </c>
       <c r="S6">
-        <v>835.14</v>
+        <v>833.47</v>
       </c>
       <c r="T6">
-        <v>-16.71</v>
+        <v>-15.85</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1414,43 +1471,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>26.3</v>
+        <v>29.91</v>
       </c>
       <c r="Z6">
-        <v>-23.83</v>
+        <v>-23.92</v>
       </c>
       <c r="AA6">
-        <v>-15.84</v>
+        <v>-17.45</v>
       </c>
       <c r="AB6">
-        <v>-8</v>
+        <v>-6.46</v>
       </c>
       <c r="AC6">
-        <v>0.15</v>
+        <v>5.9</v>
       </c>
       <c r="AD6">
-        <v>0.29</v>
+        <v>2.13</v>
       </c>
       <c r="AE6">
-        <v>21.69</v>
+        <v>21.26</v>
       </c>
       <c r="AF6">
-        <v>-75.03</v>
+        <v>-66.56999999999999</v>
       </c>
       <c r="AG6">
-        <v>842.62</v>
+        <v>836.5</v>
       </c>
       <c r="AH6">
-        <v>669.55</v>
+        <v>664.78</v>
       </c>
       <c r="AI6">
-        <v>764.55</v>
+        <v>764.15</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>45.43</v>
+        <v>46.43</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1518,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2983</v>
+        <v>3019.9</v>
       </c>
       <c r="D7">
-        <v>-1.98</v>
+        <v>1.24</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1473,46 +1530,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-13.66</v>
+        <v>-12.59</v>
       </c>
       <c r="H7">
-        <v>57.71</v>
+        <v>59.66</v>
       </c>
       <c r="I7">
-        <v>-4.65</v>
+        <v>-3.03</v>
       </c>
       <c r="J7">
-        <v>-10.12</v>
+        <v>-12.25</v>
       </c>
       <c r="K7">
-        <v>14.06</v>
+        <v>14.32</v>
       </c>
       <c r="L7">
-        <v>21.11</v>
+        <v>22.96</v>
       </c>
       <c r="M7">
-        <v>30.07</v>
+        <v>30.35</v>
       </c>
       <c r="N7">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="O7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P7">
-        <v>3048.88</v>
+        <v>3030.02</v>
       </c>
       <c r="Q7">
-        <v>3199.66</v>
+        <v>3177.91</v>
       </c>
       <c r="R7">
-        <v>2929.41</v>
+        <v>2940.47</v>
       </c>
       <c r="S7">
-        <v>2476.05</v>
+        <v>2479.81</v>
       </c>
       <c r="T7">
-        <v>20.47</v>
+        <v>21.78</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,34 +1584,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>41.38</v>
+        <v>44.67</v>
       </c>
       <c r="Z7">
-        <v>12.51</v>
+        <v>4.67</v>
       </c>
       <c r="AA7">
-        <v>59.34</v>
+        <v>48.4</v>
       </c>
       <c r="AB7">
-        <v>-46.83</v>
+        <v>-43.74</v>
       </c>
       <c r="AC7">
-        <v>0.58</v>
+        <v>4.75</v>
       </c>
       <c r="AD7">
-        <v>0.58</v>
+        <v>1.97</v>
       </c>
       <c r="AE7">
-        <v>132.57</v>
+        <v>135.41</v>
       </c>
       <c r="AF7">
-        <v>46.78</v>
+        <v>19.49</v>
       </c>
       <c r="AG7">
-        <v>3443.4</v>
+        <v>3402.64</v>
       </c>
       <c r="AH7">
-        <v>2955.91</v>
+        <v>2953.17</v>
       </c>
       <c r="AI7">
         <v>3398.57</v>
@@ -1563,7 +1620,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>25.21</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,58 +1631,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8627</v>
+        <v>8678.5</v>
       </c>
       <c r="D8">
-        <v>-0.16</v>
+        <v>0.6</v>
       </c>
       <c r="E8">
-        <v>9631.77</v>
+        <v>9581.42</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-10.43</v>
+        <v>-9.42</v>
       </c>
       <c r="H8">
-        <v>45.62</v>
+        <v>46.48</v>
       </c>
       <c r="I8">
-        <v>0.55</v>
+        <v>0.17</v>
       </c>
       <c r="J8">
-        <v>5.43</v>
+        <v>4.74</v>
       </c>
       <c r="K8">
-        <v>10.48</v>
+        <v>13.4</v>
       </c>
       <c r="L8">
-        <v>-10.47</v>
+        <v>-9.9</v>
       </c>
       <c r="M8">
-        <v>15.08</v>
+        <v>15.53</v>
       </c>
       <c r="N8">
         <v>43</v>
       </c>
       <c r="O8">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P8">
-        <v>8692.700000000001</v>
+        <v>8695.700000000001</v>
       </c>
       <c r="Q8">
-        <v>8410.299999999999</v>
+        <v>8434.780000000001</v>
       </c>
       <c r="R8">
-        <v>8151.82</v>
+        <v>8168.86</v>
       </c>
       <c r="S8">
-        <v>7424.4</v>
+        <v>7428.04</v>
       </c>
       <c r="T8">
-        <v>16.2</v>
+        <v>16.83</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1640,34 +1697,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>57.57</v>
+        <v>58.89</v>
       </c>
       <c r="Z8">
-        <v>169.08</v>
+        <v>165.75</v>
       </c>
       <c r="AA8">
-        <v>150.04</v>
+        <v>153.18</v>
       </c>
       <c r="AB8">
-        <v>19.04</v>
+        <v>12.57</v>
       </c>
       <c r="AC8">
-        <v>65.58</v>
+        <v>54.64</v>
       </c>
       <c r="AD8">
-        <v>72.38</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AE8">
-        <v>325.16</v>
+        <v>318.15</v>
       </c>
       <c r="AF8">
-        <v>-5.11</v>
+        <v>-51.56</v>
       </c>
       <c r="AG8">
-        <v>8925.030000000001</v>
+        <v>8951.74</v>
       </c>
       <c r="AH8">
-        <v>7895.57</v>
+        <v>7917.81</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
@@ -1676,7 +1733,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>47.65</v>
+        <v>48.2</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1874,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1837,1025 +1894,1114 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>3.63</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="7">
         <v>3.55</v>
       </c>
-      <c r="E7" s="6">
+      <c r="D8" s="7">
+        <v>12.68</v>
+      </c>
+      <c r="E8" s="8">
+        <v>9.130000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>3.36</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1.99</v>
+      </c>
+      <c r="E9" s="9">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-5.57</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-3.94</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-2.56</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.53</v>
+      </c>
+      <c r="E11" s="8">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-12.76</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-14.87</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-2.11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-10.12</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-12.25</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-2.13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>5.43</v>
+      </c>
+      <c r="D14" s="7">
+        <v>4.74</v>
+      </c>
+      <c r="E14" s="9">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="7">
+        <v>17.4</v>
+      </c>
+      <c r="D15" s="7">
+        <v>20.25</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7">
+        <v>4.44</v>
+      </c>
+      <c r="D16" s="7">
+        <v>5.1</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-1.81</v>
+      </c>
+      <c r="D17" s="7">
+        <v>0.48</v>
+      </c>
+      <c r="E17" s="8">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.3</v>
+      </c>
+      <c r="D18" s="7">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-1.02</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-0.23</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-4.65</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-3.03</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>0.55</v>
+      </c>
+      <c r="D21" s="7">
+        <v>0.17</v>
+      </c>
+      <c r="E21" s="9">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>21.91</v>
+      </c>
+      <c r="D22" s="7">
+        <v>28.31</v>
+      </c>
+      <c r="E22" s="8">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7">
+        <v>13.4</v>
+      </c>
+      <c r="D23" s="7">
+        <v>14.33</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>11.89</v>
+      </c>
+      <c r="D24" s="7">
+        <v>11.9</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-16.11</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-14.8</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-36.53</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-35.89</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>21.11</v>
+      </c>
+      <c r="D27" s="7">
+        <v>22.96</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-10.47</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-9.9</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="7">
         <v>-0.08</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D29" s="7">
+        <v>8.77</v>
+      </c>
+      <c r="E29" s="8">
+        <v>8.85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="5">
-        <v>3.85</v>
-      </c>
-      <c r="D8" s="5">
-        <v>3.36</v>
-      </c>
-      <c r="E8" s="6">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="B30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-5.72</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-2.66</v>
+      </c>
+      <c r="E30" s="8">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="5">
-        <v>-6.61</v>
-      </c>
-      <c r="D9" s="5">
-        <v>-5.57</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>1.92</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-1.05</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-2.97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-3.19</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-2.56</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-2.4</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-1.38</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-13.5</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-12.76</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-2.08</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-1.27</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-4.9</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-10.12</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-5.22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>14.06</v>
+      </c>
+      <c r="D34" s="7">
+        <v>14.32</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>6.55</v>
-      </c>
-      <c r="D13" s="5">
-        <v>5.43</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>10.48</v>
+      </c>
+      <c r="D35" s="7">
+        <v>13.4</v>
+      </c>
+      <c r="E35" s="8">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="D14" s="5">
-        <v>17.4</v>
-      </c>
-      <c r="E14" s="7">
-        <v>7.76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-2.45</v>
+      </c>
+      <c r="D36" s="7">
+        <v>0</v>
+      </c>
+      <c r="E36" s="8">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>0.11</v>
-      </c>
-      <c r="D15" s="5">
-        <v>4.44</v>
-      </c>
-      <c r="E15" s="7">
-        <v>4.33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-8.23</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-8.35</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-4.44</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-1.81</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-9.32</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-8.56</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>0.61</v>
-      </c>
-      <c r="D17" s="5">
-        <v>0.3</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-18.92</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-18.46</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-2.79</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-1.02</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-36.43</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-35.64</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-6.36</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-4.65</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-13.66</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-12.59</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-1.95</v>
-      </c>
-      <c r="D20" s="5">
-        <v>0.55</v>
-      </c>
-      <c r="E20" s="7">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-10.43</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-9.42</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>17.92</v>
-      </c>
-      <c r="D21" s="5">
-        <v>21.91</v>
-      </c>
-      <c r="E21" s="7">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B43" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="7">
+        <v>1211.3</v>
+      </c>
+      <c r="D43" s="7">
+        <v>1264.5</v>
+      </c>
+      <c r="E43" s="8">
+        <v>53.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>15.12</v>
-      </c>
-      <c r="D22" s="5">
-        <v>13.4</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7">
+        <v>896.1</v>
+      </c>
+      <c r="D44" s="7">
+        <v>895</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>11.51</v>
-      </c>
-      <c r="D23" s="5">
-        <v>11.89</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>1759.1</v>
+      </c>
+      <c r="D45" s="7">
+        <v>1774</v>
+      </c>
+      <c r="E45" s="8">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>1944.9</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1956</v>
+      </c>
+      <c r="E46" s="8">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>695.55</v>
+      </c>
+      <c r="D47" s="7">
+        <v>701.4</v>
+      </c>
+      <c r="E47" s="8">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>2983</v>
+      </c>
+      <c r="D48" s="7">
+        <v>3019.9</v>
+      </c>
+      <c r="E48" s="8">
+        <v>36.9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>8627</v>
+      </c>
+      <c r="D49" s="7">
+        <v>8678.5</v>
+      </c>
+      <c r="E49" s="8">
+        <v>51.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="7">
+        <v>85</v>
+      </c>
+      <c r="D50" s="7">
+        <v>99</v>
+      </c>
+      <c r="E50" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="7">
+        <v>57</v>
+      </c>
+      <c r="D51" s="7">
+        <v>71</v>
+      </c>
+      <c r="E51" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="7">
+        <v>71</v>
+      </c>
+      <c r="D52" s="7">
+        <v>57</v>
+      </c>
+      <c r="E52" s="9">
         <v>-14</v>
       </c>
-      <c r="D24" s="5">
-        <v>-16.11</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="7">
+        <v>99</v>
+      </c>
+      <c r="D53" s="7">
+        <v>85</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="D54" s="7">
+        <v>70.43000000000001</v>
+      </c>
+      <c r="E54" s="8">
+        <v>4.83</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>51.42</v>
+      </c>
+      <c r="D55" s="7">
+        <v>51.15</v>
+      </c>
+      <c r="E55" s="9">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>39.1</v>
+      </c>
+      <c r="D56" s="7">
+        <v>42.18</v>
+      </c>
+      <c r="E56" s="8">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>46.38</v>
+      </c>
+      <c r="D57" s="7">
+        <v>48.37</v>
+      </c>
+      <c r="E57" s="8">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-35.58</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-36.53</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>26.3</v>
+      </c>
+      <c r="D58" s="7">
+        <v>29.91</v>
+      </c>
+      <c r="E58" s="8">
+        <v>3.61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>25.02</v>
-      </c>
-      <c r="D26" s="5">
-        <v>21.11</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-3.91</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="7">
+        <v>41.38</v>
+      </c>
+      <c r="D59" s="7">
+        <v>44.67</v>
+      </c>
+      <c r="E59" s="8">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-10.87</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-10.47</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="7">
+        <v>57.57</v>
+      </c>
+      <c r="D60" s="7">
+        <v>58.89</v>
+      </c>
+      <c r="E60" s="8">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-2.68</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-0.08</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>154.12</v>
+      </c>
+      <c r="D61" s="7">
+        <v>52.46</v>
+      </c>
+      <c r="E61" s="9">
+        <v>-101.66</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-5.46</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-5.72</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>-9.9</v>
+      </c>
+      <c r="D62" s="7">
+        <v>-48.87</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-38.97</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>2.63</v>
-      </c>
-      <c r="D30" s="5">
-        <v>1.92</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7">
+        <v>-24.44</v>
+      </c>
+      <c r="D63" s="7">
+        <v>2.24</v>
+      </c>
+      <c r="E63" s="8">
+        <v>26.68</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-2.36</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-2.4</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="7">
+        <v>-46.37</v>
+      </c>
+      <c r="D64" s="7">
+        <v>-0.75</v>
+      </c>
+      <c r="E64" s="8">
+        <v>45.62</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-2.1</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-2.08</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="7">
+        <v>-75.03</v>
+      </c>
+      <c r="D65" s="7">
+        <v>-66.56999999999999</v>
+      </c>
+      <c r="E65" s="8">
+        <v>8.460000000000001</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>17.68</v>
-      </c>
-      <c r="D33" s="5">
-        <v>14.06</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-3.62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B66" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="7">
+        <v>46.78</v>
+      </c>
+      <c r="D66" s="7">
+        <v>19.49</v>
+      </c>
+      <c r="E66" s="9">
+        <v>-27.29</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>11.18</v>
-      </c>
-      <c r="D34" s="5">
-        <v>10.48</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-5.06</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-2.45</v>
-      </c>
-      <c r="E35" s="7">
-        <v>2.61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-6.81</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-8.23</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-9.07</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-9.32</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-19.09</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-18.92</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-36.04</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-36.43</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-11.91</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-13.66</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-10.33</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-10.43</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1178.9</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1211.3</v>
-      </c>
-      <c r="E42" s="7">
-        <v>32.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>910</v>
-      </c>
-      <c r="D43" s="5">
-        <v>896.1</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-13.9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>1764</v>
-      </c>
-      <c r="D44" s="5">
-        <v>1759.1</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-4.9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1940.8</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1944.9</v>
-      </c>
-      <c r="E45" s="7">
-        <v>4.1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>700.9</v>
-      </c>
-      <c r="D46" s="5">
-        <v>695.55</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-5.35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>3043.4</v>
-      </c>
-      <c r="D47" s="5">
-        <v>2983</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-60.4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>8640.5</v>
-      </c>
-      <c r="D48" s="5">
-        <v>8627</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-13.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="5">
-        <v>71</v>
-      </c>
-      <c r="D49" s="5">
-        <v>57</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="5">
-        <v>57</v>
-      </c>
-      <c r="D50" s="5">
-        <v>71</v>
-      </c>
-      <c r="E50" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>62.11</v>
-      </c>
-      <c r="D51" s="5">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="E51" s="7">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>54.86</v>
-      </c>
-      <c r="D52" s="5">
-        <v>51.42</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>39.74</v>
-      </c>
-      <c r="D53" s="5">
-        <v>39.1</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>45.66</v>
-      </c>
-      <c r="D54" s="5">
-        <v>46.38</v>
-      </c>
-      <c r="E54" s="7">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>27.51</v>
-      </c>
-      <c r="D55" s="5">
-        <v>26.3</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>45.5</v>
-      </c>
-      <c r="D56" s="5">
-        <v>41.38</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-4.12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>58.03</v>
-      </c>
-      <c r="D57" s="5">
-        <v>57.57</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-0.46</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="3" t="s">
+      <c r="B67" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="5">
-        <v>1652.37</v>
-      </c>
-      <c r="D58" s="5">
-        <v>154.12</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-1498.25</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>19.31</v>
-      </c>
-      <c r="D59" s="5">
-        <v>-9.9</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-29.21</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>-22.17</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-24.44</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>-38.94</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-46.37</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-7.43</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-72.62</v>
-      </c>
-      <c r="D62" s="5">
-        <v>-75.03</v>
-      </c>
-      <c r="E62" s="6">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>-67.75</v>
-      </c>
-      <c r="D63" s="5">
-        <v>46.78</v>
-      </c>
-      <c r="E63" s="7">
-        <v>114.53</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>-64.73</v>
-      </c>
-      <c r="D64" s="5">
+      <c r="C67" s="7">
         <v>-5.11</v>
       </c>
-      <c r="E64" s="7">
-        <v>59.62</v>
+      <c r="D67" s="7">
+        <v>-51.56</v>
+      </c>
+      <c r="E67" s="9">
+        <v>-46.45</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2875,60 +3021,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="12">
+        <v>60.8</v>
+      </c>
+      <c r="C2" s="13">
+        <v>7</v>
+      </c>
+      <c r="D2" s="12">
+        <v>49.4</v>
+      </c>
+      <c r="E2" s="12">
+        <v>70</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-1.4</v>
+      </c>
+      <c r="G2" s="12">
+        <v>4.3</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>46.8</v>
-      </c>
-      <c r="E2" s="10">
-        <v>70</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-2.7</v>
-      </c>
-      <c r="G2" s="10">
-        <v>2.3</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>60</v>
       </c>
     </row>
@@ -3030,49 +3176,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.5504</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.3007</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2546</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1988</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1508</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.1056</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.07690000000000001</v>
+      <c r="A2" s="15">
+        <v>0.535</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3035</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2503</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2039</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1553</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1121</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0799</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,34 +187,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.5% → 0.0%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.5%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>RSI Overbought Entry</t>
-  </si>
-  <si>
-    <t>65.6 → 70.4</t>
-  </si>
-  <si>
-    <t>⚠️ CAUTION</t>
-  </si>
-  <si>
-    <t>65.6</t>
-  </si>
-  <si>
-    <t>70.4</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.1 → 49.0</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.1</t>
+  </si>
+  <si>
+    <t>49.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -266,7 +251,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,27 +285,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -347,19 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -437,15 +409,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -454,7 +425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -953,13 +924,13 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1264.5</v>
+        <v>1296.5</v>
       </c>
       <c r="D2">
-        <v>4.39</v>
+        <v>2.53</v>
       </c>
       <c r="E2">
-        <v>1264.5</v>
+        <v>1296.5</v>
       </c>
       <c r="F2">
         <v>748.35</v>
@@ -968,43 +939,43 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>68.97</v>
+        <v>73.25</v>
       </c>
       <c r="I2">
-        <v>20.25</v>
+        <v>19.65</v>
       </c>
       <c r="J2">
-        <v>12.68</v>
+        <v>17.15</v>
       </c>
       <c r="K2">
-        <v>8.77</v>
+        <v>13.4</v>
       </c>
       <c r="L2">
-        <v>28.31</v>
+        <v>35.49</v>
       </c>
       <c r="M2">
-        <v>7.99</v>
+        <v>8.6</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="P2">
-        <v>1172.54</v>
+        <v>1215.12</v>
       </c>
       <c r="Q2">
-        <v>1110.92</v>
+        <v>1120.46</v>
       </c>
       <c r="R2">
-        <v>1103.81</v>
+        <v>1108.11</v>
       </c>
       <c r="S2">
-        <v>964.47</v>
+        <v>966.61</v>
       </c>
       <c r="T2">
-        <v>31.11</v>
+        <v>34.13</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1019,43 +990,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>70.43000000000001</v>
+        <v>72.89</v>
       </c>
       <c r="Z2">
-        <v>20.31</v>
+        <v>31.16</v>
       </c>
       <c r="AA2">
-        <v>2.46</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB2">
-        <v>17.85</v>
+        <v>22.96</v>
       </c>
       <c r="AC2">
         <v>100</v>
       </c>
       <c r="AD2">
-        <v>96.08</v>
+        <v>100</v>
       </c>
       <c r="AE2">
-        <v>50.52</v>
+        <v>54.89</v>
       </c>
       <c r="AF2">
-        <v>52.46</v>
+        <v>761.08</v>
       </c>
       <c r="AG2">
-        <v>1218.06</v>
+        <v>1255.89</v>
       </c>
       <c r="AH2">
-        <v>1003.78</v>
+        <v>985.03</v>
       </c>
       <c r="AI2">
-        <v>1091.15</v>
+        <v>1148.32</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>35.29</v>
+        <v>40.82</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1066,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>895</v>
+        <v>886.7</v>
       </c>
       <c r="D3">
-        <v>-0.12</v>
+        <v>-0.93</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1078,46 +1049,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-8.35</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="H3">
-        <v>69.03</v>
+        <v>67.47</v>
       </c>
       <c r="I3">
-        <v>5.1</v>
+        <v>0.76</v>
       </c>
       <c r="J3">
-        <v>1.99</v>
+        <v>0.93</v>
       </c>
       <c r="K3">
-        <v>-2.66</v>
+        <v>-5.88</v>
       </c>
       <c r="L3">
-        <v>14.33</v>
+        <v>14.02</v>
       </c>
       <c r="M3">
-        <v>53.5</v>
+        <v>51.77</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P3">
-        <v>894.62</v>
+        <v>895.96</v>
       </c>
       <c r="Q3">
-        <v>892.8</v>
+        <v>893.89</v>
       </c>
       <c r="R3">
-        <v>885.63</v>
+        <v>884.78</v>
       </c>
       <c r="S3">
-        <v>788.47</v>
+        <v>789.6</v>
       </c>
       <c r="T3">
-        <v>13.51</v>
+        <v>12.3</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1132,34 +1103,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>51.15</v>
+        <v>49.03</v>
       </c>
       <c r="Z3">
-        <v>1.66</v>
+        <v>1.09</v>
       </c>
       <c r="AA3">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AB3">
-        <v>0.21</v>
+        <v>-0.29</v>
       </c>
       <c r="AC3">
-        <v>61.36</v>
+        <v>51.3</v>
       </c>
       <c r="AD3">
-        <v>59.18</v>
+        <v>57.87</v>
       </c>
       <c r="AE3">
-        <v>25.59</v>
+        <v>25.14</v>
       </c>
       <c r="AF3">
-        <v>-48.87</v>
+        <v>-48.48</v>
       </c>
       <c r="AG3">
-        <v>931.88</v>
+        <v>930.87</v>
       </c>
       <c r="AH3">
-        <v>853.73</v>
+        <v>856.9</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1168,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>23.43</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1179,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1774</v>
+        <v>1681.7</v>
       </c>
       <c r="D4">
-        <v>0.85</v>
+        <v>-5.2</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1191,46 +1162,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-8.56</v>
+        <v>-13.31</v>
       </c>
       <c r="H4">
-        <v>30.95</v>
+        <v>24.14</v>
       </c>
       <c r="I4">
-        <v>0.48</v>
+        <v>-4.69</v>
       </c>
       <c r="J4">
-        <v>-3.94</v>
+        <v>-10.21</v>
       </c>
       <c r="K4">
-        <v>-1.05</v>
+        <v>-6.53</v>
       </c>
       <c r="L4">
-        <v>11.9</v>
+        <v>5.79</v>
       </c>
       <c r="M4">
-        <v>25.03</v>
+        <v>24.12</v>
       </c>
       <c r="N4">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O4">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="P4">
-        <v>1772.32</v>
+        <v>1755.76</v>
       </c>
       <c r="Q4">
-        <v>1820.85</v>
+        <v>1811.53</v>
       </c>
       <c r="R4">
-        <v>1832.44</v>
+        <v>1830</v>
       </c>
       <c r="S4">
-        <v>1683.89</v>
+        <v>1683.65</v>
       </c>
       <c r="T4">
-        <v>5.35</v>
+        <v>-0.12</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1242,46 +1213,46 @@
         <v>46</v>
       </c>
       <c r="X4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4">
-        <v>42.18</v>
+        <v>31.53</v>
       </c>
       <c r="Z4">
-        <v>-20.67</v>
+        <v>-28.22</v>
       </c>
       <c r="AA4">
-        <v>-12.35</v>
+        <v>-15.53</v>
       </c>
       <c r="AB4">
-        <v>-8.32</v>
+        <v>-12.7</v>
       </c>
       <c r="AC4">
-        <v>18.87</v>
+        <v>13.91</v>
       </c>
       <c r="AD4">
-        <v>21.59</v>
+        <v>19.16</v>
       </c>
       <c r="AE4">
-        <v>43.37</v>
+        <v>50.56</v>
       </c>
       <c r="AF4">
-        <v>2.24</v>
+        <v>240.81</v>
       </c>
       <c r="AG4">
-        <v>1899.22</v>
+        <v>1908.4</v>
       </c>
       <c r="AH4">
-        <v>1742.48</v>
+        <v>1714.66</v>
       </c>
       <c r="AI4">
-        <v>1758.5</v>
+        <v>1822.63</v>
       </c>
       <c r="AJ4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK4">
-        <v>22.79</v>
+        <v>29.26</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1292,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1956</v>
+        <v>1942.5</v>
       </c>
       <c r="D5">
-        <v>0.57</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1304,46 +1275,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-18.46</v>
+        <v>-19.02</v>
       </c>
       <c r="H5">
-        <v>12.05</v>
+        <v>11.28</v>
       </c>
       <c r="I5">
-        <v>0.9399999999999999</v>
+        <v>0.66</v>
       </c>
       <c r="J5">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="K5">
-        <v>-1.38</v>
+        <v>-2.89</v>
       </c>
       <c r="L5">
-        <v>-14.8</v>
+        <v>-13.77</v>
       </c>
       <c r="M5">
-        <v>20.39</v>
+        <v>20.19</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="P5">
-        <v>1954.2</v>
+        <v>1956.74</v>
       </c>
       <c r="Q5">
-        <v>1941.63</v>
+        <v>1941.27</v>
       </c>
       <c r="R5">
-        <v>2004.13</v>
+        <v>2001.86</v>
       </c>
       <c r="S5">
-        <v>2070.87</v>
+        <v>2069.13</v>
       </c>
       <c r="T5">
-        <v>-5.55</v>
+        <v>-6.12</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1358,34 +1329,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>48.37</v>
+        <v>46.12</v>
       </c>
       <c r="Z5">
-        <v>-12.84</v>
+        <v>-12.59</v>
       </c>
       <c r="AA5">
-        <v>-17.82</v>
+        <v>-16.77</v>
       </c>
       <c r="AB5">
-        <v>4.98</v>
+        <v>4.18</v>
       </c>
       <c r="AC5">
-        <v>53.51</v>
+        <v>48.39</v>
       </c>
       <c r="AD5">
-        <v>63.62</v>
+        <v>56.72</v>
       </c>
       <c r="AE5">
-        <v>45.58</v>
+        <v>44.84</v>
       </c>
       <c r="AF5">
-        <v>-0.75</v>
+        <v>166.74</v>
       </c>
       <c r="AG5">
-        <v>1986.14</v>
+        <v>1985.62</v>
       </c>
       <c r="AH5">
-        <v>1897.11</v>
+        <v>1896.91</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1394,7 +1365,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>28.78</v>
+        <v>29.47</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1405,58 +1376,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>701.4</v>
+        <v>689.55</v>
       </c>
       <c r="D6">
-        <v>0.84</v>
+        <v>-1.69</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
       </c>
       <c r="F6">
-        <v>695.55</v>
+        <v>689.55</v>
       </c>
       <c r="G6">
-        <v>-35.64</v>
+        <v>-36.73</v>
       </c>
       <c r="H6">
-        <v>0.84</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>-0.23</v>
+        <v>-1.93</v>
       </c>
       <c r="J6">
-        <v>-14.87</v>
+        <v>-14.91</v>
       </c>
       <c r="K6">
-        <v>-1.27</v>
+        <v>-2.85</v>
       </c>
       <c r="L6">
-        <v>-35.89</v>
+        <v>-35.33</v>
       </c>
       <c r="M6">
-        <v>11.21</v>
+        <v>11.15</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P6">
-        <v>700.33</v>
+        <v>697.62</v>
       </c>
       <c r="Q6">
-        <v>750.64</v>
+        <v>745.3</v>
       </c>
       <c r="R6">
-        <v>769.96</v>
+        <v>768.17</v>
       </c>
       <c r="S6">
-        <v>833.47</v>
+        <v>831.75</v>
       </c>
       <c r="T6">
-        <v>-15.85</v>
+        <v>-17.1</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1471,43 +1442,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>29.91</v>
+        <v>27.02</v>
       </c>
       <c r="Z6">
-        <v>-23.92</v>
+        <v>-24.65</v>
       </c>
       <c r="AA6">
-        <v>-17.45</v>
+        <v>-18.89</v>
       </c>
       <c r="AB6">
-        <v>-6.46</v>
+        <v>-5.76</v>
       </c>
       <c r="AC6">
-        <v>5.9</v>
+        <v>6.91</v>
       </c>
       <c r="AD6">
-        <v>2.13</v>
+        <v>4.32</v>
       </c>
       <c r="AE6">
-        <v>21.26</v>
+        <v>20.85</v>
       </c>
       <c r="AF6">
-        <v>-66.56999999999999</v>
+        <v>-57.63</v>
       </c>
       <c r="AG6">
-        <v>836.5</v>
+        <v>832.46</v>
       </c>
       <c r="AH6">
-        <v>664.78</v>
+        <v>658.13</v>
       </c>
       <c r="AI6">
-        <v>764.15</v>
+        <v>757.9400000000001</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>46.43</v>
+        <v>47.84</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1518,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3019.9</v>
+        <v>3033.1</v>
       </c>
       <c r="D7">
-        <v>1.24</v>
+        <v>0.44</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1530,46 +1501,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-12.59</v>
+        <v>-12.21</v>
       </c>
       <c r="H7">
-        <v>59.66</v>
+        <v>60.36</v>
       </c>
       <c r="I7">
-        <v>-3.03</v>
+        <v>-0.54</v>
       </c>
       <c r="J7">
-        <v>-12.25</v>
+        <v>-12.21</v>
       </c>
       <c r="K7">
-        <v>14.32</v>
+        <v>18.53</v>
       </c>
       <c r="L7">
-        <v>22.96</v>
+        <v>21.27</v>
       </c>
       <c r="M7">
-        <v>30.35</v>
+        <v>30.33</v>
       </c>
       <c r="N7">
         <v>85</v>
       </c>
       <c r="O7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P7">
-        <v>3030.02</v>
+        <v>3026.7</v>
       </c>
       <c r="Q7">
-        <v>3177.91</v>
+        <v>3160.23</v>
       </c>
       <c r="R7">
-        <v>2940.47</v>
+        <v>2951.36</v>
       </c>
       <c r="S7">
-        <v>2479.81</v>
+        <v>2483.68</v>
       </c>
       <c r="T7">
-        <v>21.78</v>
+        <v>22.12</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1584,34 +1555,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>44.67</v>
+        <v>45.85</v>
       </c>
       <c r="Z7">
-        <v>4.67</v>
+        <v>-0.48</v>
       </c>
       <c r="AA7">
-        <v>48.4</v>
+        <v>38.63</v>
       </c>
       <c r="AB7">
-        <v>-43.74</v>
+        <v>-39.1</v>
       </c>
       <c r="AC7">
-        <v>4.75</v>
+        <v>12.36</v>
       </c>
       <c r="AD7">
-        <v>1.97</v>
+        <v>5.9</v>
       </c>
       <c r="AE7">
-        <v>135.41</v>
+        <v>134.5</v>
       </c>
       <c r="AF7">
-        <v>19.49</v>
+        <v>-30.35</v>
       </c>
       <c r="AG7">
-        <v>3402.64</v>
+        <v>3371.03</v>
       </c>
       <c r="AH7">
-        <v>2953.17</v>
+        <v>2949.43</v>
       </c>
       <c r="AI7">
         <v>3398.57</v>
@@ -1620,7 +1591,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>22.89</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1631,58 +1602,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8678.5</v>
+        <v>8525.5</v>
       </c>
       <c r="D8">
-        <v>0.6</v>
+        <v>-1.76</v>
       </c>
       <c r="E8">
-        <v>9581.42</v>
+        <v>9426.9</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-9.42</v>
+        <v>-9.56</v>
       </c>
       <c r="H8">
-        <v>46.48</v>
+        <v>43.9</v>
       </c>
       <c r="I8">
-        <v>0.17</v>
+        <v>-2.73</v>
       </c>
       <c r="J8">
-        <v>4.74</v>
+        <v>4.11</v>
       </c>
       <c r="K8">
-        <v>13.4</v>
+        <v>12.78</v>
       </c>
       <c r="L8">
-        <v>-9.9</v>
+        <v>-11.02</v>
       </c>
       <c r="M8">
-        <v>15.53</v>
+        <v>15.23</v>
       </c>
       <c r="N8">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="O8">
         <v>62</v>
       </c>
       <c r="P8">
-        <v>8695.700000000001</v>
+        <v>8647.799999999999</v>
       </c>
       <c r="Q8">
-        <v>8434.780000000001</v>
+        <v>8453.620000000001</v>
       </c>
       <c r="R8">
-        <v>8168.86</v>
+        <v>8183.8</v>
       </c>
       <c r="S8">
-        <v>7428.04</v>
+        <v>7431.94</v>
       </c>
       <c r="T8">
-        <v>16.83</v>
+        <v>14.71</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1697,34 +1668,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>58.89</v>
+        <v>53.56</v>
       </c>
       <c r="Z8">
-        <v>165.75</v>
+        <v>149.05</v>
       </c>
       <c r="AA8">
-        <v>153.18</v>
+        <v>152.35</v>
       </c>
       <c r="AB8">
-        <v>12.57</v>
+        <v>-3.3</v>
       </c>
       <c r="AC8">
-        <v>54.64</v>
+        <v>38.08</v>
       </c>
       <c r="AD8">
-        <v>64.68000000000001</v>
+        <v>52.76</v>
       </c>
       <c r="AE8">
-        <v>318.15</v>
+        <v>309.75</v>
       </c>
       <c r="AF8">
-        <v>-51.56</v>
+        <v>-56.65</v>
       </c>
       <c r="AG8">
-        <v>8951.74</v>
+        <v>8953.870000000001</v>
       </c>
       <c r="AH8">
-        <v>7917.81</v>
+        <v>7953.38</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
@@ -1733,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>48.2</v>
+        <v>45.43</v>
       </c>
     </row>
   </sheetData>
@@ -1874,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1914,7 +1885,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1932,1076 +1903,1005 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>12.68</v>
+      </c>
+      <c r="D7" s="6">
+        <v>17.15</v>
+      </c>
+      <c r="E7" s="7">
+        <v>4.47</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>1.99</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0.93</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-3.94</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-10.21</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-6.27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>1.53</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1.51</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-14.87</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-14.91</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-12.25</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-12.21</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>4.74</v>
+      </c>
+      <c r="D13" s="6">
+        <v>4.11</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>3.55</v>
-      </c>
-      <c r="D8" s="7">
-        <v>12.68</v>
-      </c>
-      <c r="E8" s="8">
-        <v>9.130000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>20.25</v>
+      </c>
+      <c r="D14" s="6">
+        <v>19.65</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>3.36</v>
-      </c>
-      <c r="D9" s="7">
-        <v>1.99</v>
-      </c>
-      <c r="E9" s="9">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>5.1</v>
+      </c>
+      <c r="D15" s="6">
+        <v>0.76</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-4.34</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-5.57</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-3.94</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.48</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-4.69</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-5.17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-2.56</v>
-      </c>
-      <c r="D11" s="7">
-        <v>1.53</v>
-      </c>
-      <c r="E11" s="8">
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.66</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-12.76</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-14.87</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-2.11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-0.23</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-1.93</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-10.12</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-12.25</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-2.13</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3.03</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-0.54</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>5.43</v>
-      </c>
-      <c r="D14" s="7">
-        <v>4.74</v>
-      </c>
-      <c r="E14" s="9">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.17</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-2.73</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>17.4</v>
-      </c>
-      <c r="D15" s="7">
-        <v>20.25</v>
-      </c>
-      <c r="E15" s="8">
-        <v>2.85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>28.31</v>
+      </c>
+      <c r="D21" s="6">
+        <v>35.49</v>
+      </c>
+      <c r="E21" s="7">
+        <v>7.18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>4.44</v>
-      </c>
-      <c r="D16" s="7">
-        <v>5.1</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>14.33</v>
+      </c>
+      <c r="D22" s="6">
+        <v>14.02</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1.81</v>
-      </c>
-      <c r="D17" s="7">
-        <v>0.48</v>
-      </c>
-      <c r="E17" s="8">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>11.9</v>
+      </c>
+      <c r="D23" s="6">
+        <v>5.79</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-6.11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="D18" s="7">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-14.8</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-13.77</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-1.02</v>
-      </c>
-      <c r="D19" s="7">
-        <v>-0.23</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-35.89</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-35.33</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-4.65</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-3.03</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>22.96</v>
+      </c>
+      <c r="D26" s="6">
+        <v>21.27</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>0.55</v>
-      </c>
-      <c r="D21" s="7">
-        <v>0.17</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-9.9</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-11.02</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>21.91</v>
-      </c>
-      <c r="D22" s="7">
-        <v>28.31</v>
-      </c>
-      <c r="E22" s="8">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>8.77</v>
+      </c>
+      <c r="D28" s="6">
+        <v>13.4</v>
+      </c>
+      <c r="E28" s="7">
+        <v>4.63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-2.66</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-5.88</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-3.22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-1.05</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-6.53</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-5.48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-1.38</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-2.89</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-1.27</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-2.85</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.58</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>14.32</v>
+      </c>
+      <c r="D33" s="6">
+        <v>18.53</v>
+      </c>
+      <c r="E33" s="7">
+        <v>4.21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
         <v>13.4</v>
       </c>
-      <c r="D23" s="7">
-        <v>14.33</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.93</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="D34" s="6">
+        <v>12.78</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-8.35</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>11.89</v>
-      </c>
-      <c r="D24" s="7">
-        <v>11.9</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-8.56</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-13.31</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-4.75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-16.11</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-14.8</v>
-      </c>
-      <c r="E25" s="8">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-18.46</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-19.02</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-36.53</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-35.89</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-35.64</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-36.73</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>21.11</v>
-      </c>
-      <c r="D27" s="7">
-        <v>22.96</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-12.59</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-12.21</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-10.47</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-9.9</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-9.42</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-9.56</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-0.08</v>
-      </c>
-      <c r="D29" s="7">
-        <v>8.77</v>
-      </c>
-      <c r="E29" s="8">
-        <v>8.85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="6">
+        <v>1264.5</v>
+      </c>
+      <c r="D41" s="6">
+        <v>1296.5</v>
+      </c>
+      <c r="E41" s="7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-5.72</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-2.66</v>
-      </c>
-      <c r="E30" s="8">
-        <v>3.06</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>895</v>
+      </c>
+      <c r="D42" s="6">
+        <v>886.7</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-8.300000000000001</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>1.92</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-1.05</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-2.97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>1774</v>
+      </c>
+      <c r="D43" s="6">
+        <v>1681.7</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-92.3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-2.4</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-1.38</v>
-      </c>
-      <c r="E32" s="8">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>1956</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1942.5</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-13.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-2.08</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-1.27</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>701.4</v>
+      </c>
+      <c r="D45" s="6">
+        <v>689.55</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-11.85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>14.06</v>
-      </c>
-      <c r="D34" s="7">
-        <v>14.32</v>
-      </c>
-      <c r="E34" s="8">
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>3019.9</v>
+      </c>
+      <c r="D46" s="6">
+        <v>3033.1</v>
+      </c>
+      <c r="E46" s="7">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>10.48</v>
-      </c>
-      <c r="D35" s="7">
-        <v>13.4</v>
-      </c>
-      <c r="E35" s="8">
-        <v>2.92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>8678.5</v>
+      </c>
+      <c r="D47" s="6">
+        <v>8525.5</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-153</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="6">
+        <v>57</v>
+      </c>
+      <c r="D48" s="6">
+        <v>43</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="6">
+        <v>43</v>
+      </c>
+      <c r="D49" s="6">
+        <v>57</v>
+      </c>
+      <c r="E49" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-2.45</v>
-      </c>
-      <c r="D36" s="7">
-        <v>0</v>
-      </c>
-      <c r="E36" s="8">
-        <v>2.45</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>70.43000000000001</v>
+      </c>
+      <c r="D50" s="6">
+        <v>72.89</v>
+      </c>
+      <c r="E50" s="7">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-8.23</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-8.35</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>51.15</v>
+      </c>
+      <c r="D51" s="6">
+        <v>49.03</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-2.12</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-9.32</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-8.56</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>42.18</v>
+      </c>
+      <c r="D52" s="6">
+        <v>31.53</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-10.65</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-18.92</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-18.46</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>48.37</v>
+      </c>
+      <c r="D53" s="6">
+        <v>46.12</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-36.43</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-35.64</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>29.91</v>
+      </c>
+      <c r="D54" s="6">
+        <v>27.02</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-2.89</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-13.66</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-12.59</v>
-      </c>
-      <c r="E41" s="8">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>44.67</v>
+      </c>
+      <c r="D55" s="6">
+        <v>45.85</v>
+      </c>
+      <c r="E55" s="7">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-10.43</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-9.42</v>
-      </c>
-      <c r="E42" s="8">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>58.89</v>
+      </c>
+      <c r="D56" s="6">
+        <v>53.56</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-5.33</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>1211.3</v>
-      </c>
-      <c r="D43" s="7">
-        <v>1264.5</v>
-      </c>
-      <c r="E43" s="8">
-        <v>53.2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>52.46</v>
+      </c>
+      <c r="D57" s="6">
+        <v>761.08</v>
+      </c>
+      <c r="E57" s="7">
+        <v>708.62</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="7">
-        <v>896.1</v>
-      </c>
-      <c r="D44" s="7">
-        <v>895</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-48.87</v>
+      </c>
+      <c r="D58" s="6">
+        <v>-48.48</v>
+      </c>
+      <c r="E58" s="7">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>1759.1</v>
-      </c>
-      <c r="D45" s="7">
-        <v>1774</v>
-      </c>
-      <c r="E45" s="8">
-        <v>14.9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>2.24</v>
+      </c>
+      <c r="D59" s="6">
+        <v>240.81</v>
+      </c>
+      <c r="E59" s="7">
+        <v>238.57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>1944.9</v>
-      </c>
-      <c r="D46" s="7">
-        <v>1956</v>
-      </c>
-      <c r="E46" s="8">
-        <v>11.1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-0.75</v>
+      </c>
+      <c r="D60" s="6">
+        <v>166.74</v>
+      </c>
+      <c r="E60" s="7">
+        <v>167.49</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>695.55</v>
-      </c>
-      <c r="D47" s="7">
-        <v>701.4</v>
-      </c>
-      <c r="E47" s="8">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-66.56999999999999</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-57.63</v>
+      </c>
+      <c r="E61" s="7">
+        <v>8.94</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>2983</v>
-      </c>
-      <c r="D48" s="7">
-        <v>3019.9</v>
-      </c>
-      <c r="E48" s="8">
-        <v>36.9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
+        <v>19.49</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-30.35</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-49.84</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>8627</v>
-      </c>
-      <c r="D49" s="7">
-        <v>8678.5</v>
-      </c>
-      <c r="E49" s="8">
-        <v>51.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="7">
-        <v>85</v>
-      </c>
-      <c r="D50" s="7">
-        <v>99</v>
-      </c>
-      <c r="E50" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="7">
-        <v>57</v>
-      </c>
-      <c r="D51" s="7">
-        <v>71</v>
-      </c>
-      <c r="E51" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="7">
-        <v>71</v>
-      </c>
-      <c r="D52" s="7">
-        <v>57</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C53" s="7">
-        <v>99</v>
-      </c>
-      <c r="D53" s="7">
-        <v>85</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="D54" s="7">
-        <v>70.43000000000001</v>
-      </c>
-      <c r="E54" s="8">
-        <v>4.83</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>51.42</v>
-      </c>
-      <c r="D55" s="7">
-        <v>51.15</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>39.1</v>
-      </c>
-      <c r="D56" s="7">
-        <v>42.18</v>
-      </c>
-      <c r="E56" s="8">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>46.38</v>
-      </c>
-      <c r="D57" s="7">
-        <v>48.37</v>
-      </c>
-      <c r="E57" s="8">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>26.3</v>
-      </c>
-      <c r="D58" s="7">
-        <v>29.91</v>
-      </c>
-      <c r="E58" s="8">
-        <v>3.61</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="7">
-        <v>41.38</v>
-      </c>
-      <c r="D59" s="7">
-        <v>44.67</v>
-      </c>
-      <c r="E59" s="8">
-        <v>3.29</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C60" s="7">
-        <v>57.57</v>
-      </c>
-      <c r="D60" s="7">
-        <v>58.89</v>
-      </c>
-      <c r="E60" s="8">
-        <v>1.32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B61" s="6" t="s">
+      <c r="B63" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="7">
-        <v>154.12</v>
-      </c>
-      <c r="D61" s="7">
-        <v>52.46</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-101.66</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-9.9</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-48.87</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-38.97</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-24.44</v>
-      </c>
-      <c r="D63" s="7">
-        <v>2.24</v>
+      <c r="C63" s="6">
+        <v>-51.56</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-56.65</v>
       </c>
       <c r="E63" s="8">
-        <v>26.68</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>-46.37</v>
-      </c>
-      <c r="D64" s="7">
-        <v>-0.75</v>
-      </c>
-      <c r="E64" s="8">
-        <v>45.62</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>-75.03</v>
-      </c>
-      <c r="D65" s="7">
-        <v>-66.56999999999999</v>
-      </c>
-      <c r="E65" s="8">
-        <v>8.460000000000001</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="7">
-        <v>46.78</v>
-      </c>
-      <c r="D66" s="7">
-        <v>19.49</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-27.29</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="7">
-        <v>-5.11</v>
-      </c>
-      <c r="D67" s="7">
-        <v>-51.56</v>
-      </c>
-      <c r="E67" s="9">
-        <v>-46.45</v>
+        <v>-5.09</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3021,60 +2921,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
-        <v>60.8</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="11">
+        <v>56.8</v>
+      </c>
+      <c r="C2" s="12">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>49.4</v>
-      </c>
-      <c r="E2" s="12">
-        <v>70</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-1.4</v>
-      </c>
-      <c r="G2" s="12">
-        <v>4.3</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="11">
+        <v>46.6</v>
+      </c>
+      <c r="E2" s="11">
+        <v>60</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-1.9</v>
+      </c>
+      <c r="G2" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>60</v>
       </c>
     </row>
@@ -3176,49 +3076,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.535</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.3035</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2503</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.2039</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1553</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1121</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0799</v>
+      <c r="A2" s="14">
+        <v>0.5177</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.3033</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2412</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.2019</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1523</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1115</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.08599999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="82">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,16 +190,43 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>51.1 → 49.0</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.1</t>
-  </si>
-  <si>
-    <t>49.0</t>
+    <t>46.1 → 50.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>46.1</t>
+  </si>
+  <si>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>27.0 → 35.6</t>
+  </si>
+  <si>
+    <t>27.0</t>
+  </si>
+  <si>
+    <t>35.6</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>72.9 → 69.4</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>72.9</t>
+  </si>
+  <si>
+    <t>69.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -251,7 +278,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -285,20 +312,27 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -325,13 +359,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,7 +441,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -409,14 +449,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -425,7 +466,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -924,10 +965,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1296.5</v>
+        <v>1278.5</v>
       </c>
       <c r="D2">
-        <v>2.53</v>
+        <v>-1.39</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -936,46 +977,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>-1.39</v>
       </c>
       <c r="H2">
-        <v>73.25</v>
+        <v>70.84</v>
       </c>
       <c r="I2">
-        <v>19.65</v>
+        <v>13.71</v>
       </c>
       <c r="J2">
-        <v>17.15</v>
+        <v>15.63</v>
       </c>
       <c r="K2">
-        <v>13.4</v>
+        <v>7.27</v>
       </c>
       <c r="L2">
-        <v>35.49</v>
+        <v>34.65</v>
       </c>
       <c r="M2">
-        <v>8.6</v>
+        <v>8.23</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="P2">
-        <v>1215.12</v>
+        <v>1245.94</v>
       </c>
       <c r="Q2">
-        <v>1120.46</v>
+        <v>1129.22</v>
       </c>
       <c r="R2">
-        <v>1108.11</v>
+        <v>1111.97</v>
       </c>
       <c r="S2">
-        <v>966.61</v>
+        <v>968.77</v>
       </c>
       <c r="T2">
-        <v>34.13</v>
+        <v>31.97</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +1031,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>72.89</v>
+        <v>69.39</v>
       </c>
       <c r="Z2">
-        <v>31.16</v>
+        <v>37.88</v>
       </c>
       <c r="AA2">
-        <v>8.199999999999999</v>
+        <v>14.14</v>
       </c>
       <c r="AB2">
-        <v>22.96</v>
+        <v>23.74</v>
       </c>
       <c r="AC2">
-        <v>100</v>
+        <v>96.72</v>
       </c>
       <c r="AD2">
-        <v>100</v>
+        <v>98.91</v>
       </c>
       <c r="AE2">
-        <v>54.89</v>
+        <v>54.15</v>
       </c>
       <c r="AF2">
-        <v>761.08</v>
+        <v>-37.3</v>
       </c>
       <c r="AG2">
-        <v>1255.89</v>
+        <v>1281.58</v>
       </c>
       <c r="AH2">
-        <v>985.03</v>
+        <v>976.87</v>
       </c>
       <c r="AI2">
         <v>1148.32</v>
@@ -1026,7 +1067,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>40.82</v>
+        <v>45.14</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1078,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>886.7</v>
+        <v>886</v>
       </c>
       <c r="D3">
-        <v>-0.93</v>
+        <v>-0.08</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1049,46 +1090,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-9.199999999999999</v>
+        <v>-9.27</v>
       </c>
       <c r="H3">
-        <v>67.47</v>
+        <v>67.33</v>
       </c>
       <c r="I3">
-        <v>0.76</v>
+        <v>-0.67</v>
       </c>
       <c r="J3">
-        <v>0.93</v>
+        <v>2.42</v>
       </c>
       <c r="K3">
-        <v>-5.88</v>
+        <v>-7.35</v>
       </c>
       <c r="L3">
-        <v>14.02</v>
+        <v>15.29</v>
       </c>
       <c r="M3">
-        <v>51.77</v>
+        <v>52.85</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="P3">
-        <v>895.96</v>
+        <v>894.76</v>
       </c>
       <c r="Q3">
-        <v>893.89</v>
+        <v>893.29</v>
       </c>
       <c r="R3">
-        <v>884.78</v>
+        <v>884.0599999999999</v>
       </c>
       <c r="S3">
-        <v>789.6</v>
+        <v>790.8099999999999</v>
       </c>
       <c r="T3">
-        <v>12.3</v>
+        <v>12.04</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1103,34 +1144,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>49.03</v>
+        <v>48.85</v>
       </c>
       <c r="Z3">
-        <v>1.09</v>
+        <v>0.58</v>
       </c>
       <c r="AA3">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AB3">
-        <v>-0.29</v>
+        <v>-0.64</v>
       </c>
       <c r="AC3">
-        <v>51.3</v>
+        <v>46.85</v>
       </c>
       <c r="AD3">
-        <v>57.87</v>
+        <v>53.17</v>
       </c>
       <c r="AE3">
-        <v>25.14</v>
+        <v>24.66</v>
       </c>
       <c r="AF3">
-        <v>-48.48</v>
+        <v>-62.74</v>
       </c>
       <c r="AG3">
-        <v>930.87</v>
+        <v>930.38</v>
       </c>
       <c r="AH3">
-        <v>856.9</v>
+        <v>856.2</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1139,7 +1180,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>21.5</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1191,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1681.7</v>
+        <v>1662.7</v>
       </c>
       <c r="D4">
-        <v>-5.2</v>
+        <v>-1.13</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1162,46 +1203,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-13.31</v>
+        <v>-14.29</v>
       </c>
       <c r="H4">
-        <v>24.14</v>
+        <v>22.74</v>
       </c>
       <c r="I4">
-        <v>-4.69</v>
+        <v>-7.63</v>
       </c>
       <c r="J4">
-        <v>-10.21</v>
+        <v>-11</v>
       </c>
       <c r="K4">
-        <v>-6.53</v>
+        <v>-6.27</v>
       </c>
       <c r="L4">
-        <v>5.79</v>
+        <v>2.08</v>
       </c>
       <c r="M4">
-        <v>24.12</v>
+        <v>24.04</v>
       </c>
       <c r="N4">
         <v>43</v>
       </c>
       <c r="O4">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P4">
-        <v>1755.76</v>
+        <v>1728.3</v>
       </c>
       <c r="Q4">
-        <v>1811.53</v>
+        <v>1800.89</v>
       </c>
       <c r="R4">
-        <v>1830</v>
+        <v>1827.47</v>
       </c>
       <c r="S4">
-        <v>1683.65</v>
+        <v>1683.35</v>
       </c>
       <c r="T4">
-        <v>-0.12</v>
+        <v>-1.23</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1216,43 +1257,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>31.53</v>
+        <v>29.86</v>
       </c>
       <c r="Z4">
-        <v>-28.22</v>
+        <v>-35.34</v>
       </c>
       <c r="AA4">
-        <v>-15.53</v>
+        <v>-19.49</v>
       </c>
       <c r="AB4">
-        <v>-12.7</v>
+        <v>-15.85</v>
       </c>
       <c r="AC4">
-        <v>13.91</v>
+        <v>10.39</v>
       </c>
       <c r="AD4">
-        <v>19.16</v>
+        <v>14.39</v>
       </c>
       <c r="AE4">
-        <v>50.56</v>
+        <v>50.11</v>
       </c>
       <c r="AF4">
-        <v>240.81</v>
+        <v>106.25</v>
       </c>
       <c r="AG4">
-        <v>1908.4</v>
+        <v>1913.64</v>
       </c>
       <c r="AH4">
-        <v>1714.66</v>
+        <v>1688.15</v>
       </c>
       <c r="AI4">
-        <v>1822.63</v>
+        <v>1810.09</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>29.26</v>
+        <v>34.86</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1304,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1942.5</v>
+        <v>1963.9</v>
       </c>
       <c r="D5">
-        <v>-0.6899999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1275,46 +1316,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-19.02</v>
+        <v>-18.13</v>
       </c>
       <c r="H5">
-        <v>11.28</v>
+        <v>12.51</v>
       </c>
       <c r="I5">
-        <v>0.66</v>
+        <v>-1.78</v>
       </c>
       <c r="J5">
-        <v>1.51</v>
+        <v>0.73</v>
       </c>
       <c r="K5">
-        <v>-2.89</v>
+        <v>2.61</v>
       </c>
       <c r="L5">
-        <v>-13.77</v>
+        <v>-13.26</v>
       </c>
       <c r="M5">
-        <v>20.19</v>
+        <v>20.78</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="P5">
-        <v>1956.74</v>
+        <v>1949.62</v>
       </c>
       <c r="Q5">
-        <v>1941.27</v>
+        <v>1943.04</v>
       </c>
       <c r="R5">
-        <v>2001.86</v>
+        <v>2000.69</v>
       </c>
       <c r="S5">
-        <v>2069.13</v>
+        <v>2067.42</v>
       </c>
       <c r="T5">
-        <v>-6.12</v>
+        <v>-5.01</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,34 +1370,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>46.12</v>
+        <v>50.07</v>
       </c>
       <c r="Z5">
-        <v>-12.59</v>
+        <v>-10.54</v>
       </c>
       <c r="AA5">
-        <v>-16.77</v>
+        <v>-15.53</v>
       </c>
       <c r="AB5">
-        <v>4.18</v>
+        <v>4.99</v>
       </c>
       <c r="AC5">
-        <v>48.39</v>
+        <v>51.09</v>
       </c>
       <c r="AD5">
-        <v>56.72</v>
+        <v>50.99</v>
       </c>
       <c r="AE5">
-        <v>44.84</v>
+        <v>44.56</v>
       </c>
       <c r="AF5">
-        <v>166.74</v>
+        <v>-62.9</v>
       </c>
       <c r="AG5">
-        <v>1985.62</v>
+        <v>1988.06</v>
       </c>
       <c r="AH5">
-        <v>1896.91</v>
+        <v>1898.02</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1365,7 +1406,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>29.47</v>
+        <v>31.23</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1417,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>689.55</v>
+        <v>704.75</v>
       </c>
       <c r="D6">
-        <v>-1.69</v>
+        <v>2.2</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1388,46 +1429,46 @@
         <v>689.55</v>
       </c>
       <c r="G6">
-        <v>-36.73</v>
+        <v>-35.33</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I6">
-        <v>-1.93</v>
+        <v>0.58</v>
       </c>
       <c r="J6">
-        <v>-14.91</v>
+        <v>-11.5</v>
       </c>
       <c r="K6">
-        <v>-2.85</v>
+        <v>-1.3</v>
       </c>
       <c r="L6">
-        <v>-35.33</v>
+        <v>-34.41</v>
       </c>
       <c r="M6">
-        <v>11.15</v>
+        <v>11.82</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P6">
-        <v>697.62</v>
+        <v>698.4299999999999</v>
       </c>
       <c r="Q6">
-        <v>745.3</v>
+        <v>740.77</v>
       </c>
       <c r="R6">
-        <v>768.17</v>
+        <v>766.86</v>
       </c>
       <c r="S6">
-        <v>831.75</v>
+        <v>830.23</v>
       </c>
       <c r="T6">
-        <v>-17.1</v>
+        <v>-15.11</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1442,34 +1483,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>27.02</v>
+        <v>35.62</v>
       </c>
       <c r="Z6">
-        <v>-24.65</v>
+        <v>-23.74</v>
       </c>
       <c r="AA6">
-        <v>-18.89</v>
+        <v>-19.86</v>
       </c>
       <c r="AB6">
-        <v>-5.76</v>
+        <v>-3.88</v>
       </c>
       <c r="AC6">
-        <v>6.91</v>
+        <v>22.64</v>
       </c>
       <c r="AD6">
-        <v>4.32</v>
+        <v>11.82</v>
       </c>
       <c r="AE6">
-        <v>20.85</v>
+        <v>20.98</v>
       </c>
       <c r="AF6">
-        <v>-57.63</v>
+        <v>-12.99</v>
       </c>
       <c r="AG6">
-        <v>832.46</v>
+        <v>826.39</v>
       </c>
       <c r="AH6">
-        <v>658.13</v>
+        <v>655.15</v>
       </c>
       <c r="AI6">
         <v>757.9400000000001</v>
@@ -1478,7 +1519,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>47.84</v>
+        <v>46.49</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1530,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3033.1</v>
+        <v>3003.4</v>
       </c>
       <c r="D7">
-        <v>0.44</v>
+        <v>-0.98</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1501,46 +1542,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-12.21</v>
+        <v>-13.07</v>
       </c>
       <c r="H7">
-        <v>60.36</v>
+        <v>58.79</v>
       </c>
       <c r="I7">
-        <v>-0.54</v>
+        <v>-1.66</v>
       </c>
       <c r="J7">
-        <v>-12.21</v>
+        <v>-11.32</v>
       </c>
       <c r="K7">
-        <v>18.53</v>
+        <v>14.75</v>
       </c>
       <c r="L7">
-        <v>21.27</v>
+        <v>22.03</v>
       </c>
       <c r="M7">
-        <v>30.33</v>
+        <v>30.07</v>
       </c>
       <c r="N7">
         <v>85</v>
       </c>
       <c r="O7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P7">
-        <v>3026.7</v>
+        <v>3016.56</v>
       </c>
       <c r="Q7">
-        <v>3160.23</v>
+        <v>3143.99</v>
       </c>
       <c r="R7">
-        <v>2951.36</v>
+        <v>2962.35</v>
       </c>
       <c r="S7">
-        <v>2483.68</v>
+        <v>2487.73</v>
       </c>
       <c r="T7">
-        <v>22.12</v>
+        <v>20.73</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1555,34 +1596,34 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>45.85</v>
+        <v>43.61</v>
       </c>
       <c r="Z7">
-        <v>-0.48</v>
+        <v>-6.87</v>
       </c>
       <c r="AA7">
-        <v>38.63</v>
+        <v>29.53</v>
       </c>
       <c r="AB7">
-        <v>-39.1</v>
+        <v>-36.4</v>
       </c>
       <c r="AC7">
-        <v>12.36</v>
+        <v>16.16</v>
       </c>
       <c r="AD7">
-        <v>5.9</v>
+        <v>11.09</v>
       </c>
       <c r="AE7">
-        <v>134.5</v>
+        <v>130.63</v>
       </c>
       <c r="AF7">
-        <v>-30.35</v>
+        <v>-22.88</v>
       </c>
       <c r="AG7">
-        <v>3371.03</v>
+        <v>3350.32</v>
       </c>
       <c r="AH7">
-        <v>2949.43</v>
+        <v>2937.67</v>
       </c>
       <c r="AI7">
         <v>3398.57</v>
@@ -1591,7 +1632,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>21.25</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,37 +1643,37 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8525.5</v>
+        <v>8646</v>
       </c>
       <c r="D8">
-        <v>-1.76</v>
+        <v>1.41</v>
       </c>
       <c r="E8">
-        <v>9426.9</v>
+        <v>9393</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-9.56</v>
+        <v>-7.95</v>
       </c>
       <c r="H8">
-        <v>43.9</v>
+        <v>45.94</v>
       </c>
       <c r="I8">
-        <v>-2.73</v>
+        <v>-1.39</v>
       </c>
       <c r="J8">
-        <v>4.11</v>
+        <v>6.11</v>
       </c>
       <c r="K8">
-        <v>12.78</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="L8">
-        <v>-11.02</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="M8">
-        <v>15.23</v>
+        <v>15.16</v>
       </c>
       <c r="N8">
         <v>57</v>
@@ -1641,19 +1682,19 @@
         <v>62</v>
       </c>
       <c r="P8">
-        <v>8647.799999999999</v>
+        <v>8623.5</v>
       </c>
       <c r="Q8">
-        <v>8453.620000000001</v>
+        <v>8467.120000000001</v>
       </c>
       <c r="R8">
-        <v>8183.8</v>
+        <v>8201.09</v>
       </c>
       <c r="S8">
-        <v>7431.94</v>
+        <v>7437.03</v>
       </c>
       <c r="T8">
-        <v>14.71</v>
+        <v>16.26</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1668,34 +1709,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>53.56</v>
+        <v>56.87</v>
       </c>
       <c r="Z8">
-        <v>149.05</v>
+        <v>143.88</v>
       </c>
       <c r="AA8">
-        <v>152.35</v>
+        <v>150.66</v>
       </c>
       <c r="AB8">
-        <v>-3.3</v>
+        <v>-6.78</v>
       </c>
       <c r="AC8">
-        <v>38.08</v>
+        <v>29.45</v>
       </c>
       <c r="AD8">
-        <v>52.76</v>
+        <v>40.72</v>
       </c>
       <c r="AE8">
-        <v>309.75</v>
+        <v>308.19</v>
       </c>
       <c r="AF8">
-        <v>-56.65</v>
+        <v>-49.54</v>
       </c>
       <c r="AG8">
-        <v>8953.870000000001</v>
+        <v>8973.09</v>
       </c>
       <c r="AH8">
-        <v>7953.38</v>
+        <v>7961.16</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
@@ -1704,7 +1745,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>45.43</v>
+        <v>44.97</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1886,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1885,7 +1926,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1903,1005 +1944,1028 @@
         <v>59</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A5" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>12.68</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C9" s="7">
         <v>17.15</v>
       </c>
-      <c r="E7" s="7">
-        <v>4.47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D9" s="7">
+        <v>15.63</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>1.99</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C10" s="7">
         <v>0.93</v>
       </c>
-      <c r="E8" s="8">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D10" s="7">
+        <v>2.42</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-3.94</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C11" s="7">
         <v>-10.21</v>
       </c>
-      <c r="E9" s="8">
+      <c r="D11" s="7">
+        <v>-11</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1.51</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.73</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-14.91</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-11.5</v>
+      </c>
+      <c r="E13" s="9">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-12.21</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-11.32</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>4.11</v>
+      </c>
+      <c r="D15" s="7">
+        <v>6.11</v>
+      </c>
+      <c r="E15" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7">
+        <v>19.65</v>
+      </c>
+      <c r="D16" s="7">
+        <v>13.71</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-5.94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-0.67</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>-4.69</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-7.63</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-2.94</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>0.66</v>
+      </c>
+      <c r="D19" s="7">
+        <v>-1.78</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-2.44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-1.93</v>
+      </c>
+      <c r="D20" s="7">
+        <v>0.58</v>
+      </c>
+      <c r="E20" s="9">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-0.54</v>
+      </c>
+      <c r="D21" s="7">
+        <v>-1.66</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-2.73</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-1.39</v>
+      </c>
+      <c r="E22" s="9">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="7">
+        <v>35.49</v>
+      </c>
+      <c r="D23" s="7">
+        <v>34.65</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>14.02</v>
+      </c>
+      <c r="D24" s="7">
+        <v>15.29</v>
+      </c>
+      <c r="E24" s="9">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>5.79</v>
+      </c>
+      <c r="D25" s="7">
+        <v>2.08</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-3.71</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-13.77</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-13.26</v>
+      </c>
+      <c r="E26" s="9">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-35.33</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-34.41</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>21.27</v>
+      </c>
+      <c r="D28" s="7">
+        <v>22.03</v>
+      </c>
+      <c r="E28" s="9">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-11.02</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="E29" s="9">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7">
+        <v>13.4</v>
+      </c>
+      <c r="D30" s="7">
+        <v>7.27</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-6.13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-5.88</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-7.35</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-6.53</v>
+      </c>
+      <c r="D32" s="7">
         <v>-6.27</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="E32" s="9">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>1.53</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1.51</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-2.89</v>
+      </c>
+      <c r="D33" s="7">
+        <v>2.61</v>
+      </c>
+      <c r="E33" s="9">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-14.87</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-14.91</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-2.85</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-1.3</v>
+      </c>
+      <c r="E34" s="9">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-12.25</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>18.53</v>
+      </c>
+      <c r="D35" s="7">
+        <v>14.75</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-3.78</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>12.78</v>
+      </c>
+      <c r="D36" s="7">
+        <v>9.640000000000001</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-3.14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-1.39</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-9.27</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-13.31</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-14.29</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-19.02</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-18.13</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-36.73</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-35.33</v>
+      </c>
+      <c r="E41" s="9">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
         <v>-12.21</v>
       </c>
-      <c r="E12" s="7">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D42" s="7">
+        <v>-13.07</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>4.74</v>
-      </c>
-      <c r="D13" s="6">
-        <v>4.11</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-9.56</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-7.95</v>
+      </c>
+      <c r="E43" s="9">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>20.25</v>
-      </c>
-      <c r="D14" s="6">
-        <v>19.65</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7">
+        <v>1296.5</v>
+      </c>
+      <c r="D44" s="7">
+        <v>1278.5</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>5.1</v>
-      </c>
-      <c r="D15" s="6">
-        <v>0.76</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-4.34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>886.7</v>
+      </c>
+      <c r="D45" s="7">
+        <v>886</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.48</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-4.69</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-5.17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>1681.7</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1662.7</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.66</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>1942.5</v>
+      </c>
+      <c r="D47" s="7">
+        <v>1963.9</v>
+      </c>
+      <c r="E47" s="9">
+        <v>21.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-0.23</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-1.93</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>689.55</v>
+      </c>
+      <c r="D48" s="7">
+        <v>704.75</v>
+      </c>
+      <c r="E48" s="9">
+        <v>15.2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3.03</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-0.54</v>
-      </c>
-      <c r="E19" s="7">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>3033.1</v>
+      </c>
+      <c r="D49" s="7">
+        <v>3003.4</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-29.7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.17</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-2.73</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7">
+        <v>8525.5</v>
+      </c>
+      <c r="D50" s="7">
+        <v>8646</v>
+      </c>
+      <c r="E50" s="9">
+        <v>120.5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>28.31</v>
-      </c>
-      <c r="D21" s="6">
-        <v>35.49</v>
-      </c>
-      <c r="E21" s="7">
-        <v>7.18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B51" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="7">
+        <v>72.89</v>
+      </c>
+      <c r="D51" s="7">
+        <v>69.39</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>14.33</v>
-      </c>
-      <c r="D22" s="6">
-        <v>14.02</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="7">
+        <v>49.03</v>
+      </c>
+      <c r="D52" s="7">
+        <v>48.85</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>11.9</v>
-      </c>
-      <c r="D23" s="6">
-        <v>5.79</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-6.11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="7">
+        <v>31.53</v>
+      </c>
+      <c r="D53" s="7">
+        <v>29.86</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-14.8</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-13.77</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>46.12</v>
+      </c>
+      <c r="D54" s="7">
+        <v>50.07</v>
+      </c>
+      <c r="E54" s="9">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-35.89</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-35.33</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>27.02</v>
+      </c>
+      <c r="D55" s="7">
+        <v>35.62</v>
+      </c>
+      <c r="E55" s="9">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>22.96</v>
-      </c>
-      <c r="D26" s="6">
-        <v>21.27</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>45.85</v>
+      </c>
+      <c r="D56" s="7">
+        <v>43.61</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-2.24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-9.9</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-11.02</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>53.56</v>
+      </c>
+      <c r="D57" s="7">
+        <v>56.87</v>
+      </c>
+      <c r="E57" s="9">
+        <v>3.31</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>8.77</v>
-      </c>
-      <c r="D28" s="6">
-        <v>13.4</v>
-      </c>
-      <c r="E28" s="7">
-        <v>4.63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B58" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="7">
+        <v>761.08</v>
+      </c>
+      <c r="D58" s="7">
+        <v>-37.3</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-798.38</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-2.66</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-5.88</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-3.22</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B59" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="7">
+        <v>-48.48</v>
+      </c>
+      <c r="D59" s="7">
+        <v>-62.74</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-14.26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-1.05</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-6.53</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-5.48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="7">
+        <v>240.81</v>
+      </c>
+      <c r="D60" s="7">
+        <v>106.25</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-134.56</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-1.38</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-2.89</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>166.74</v>
+      </c>
+      <c r="D61" s="7">
+        <v>-62.9</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-229.64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-1.27</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-2.85</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.58</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>-57.63</v>
+      </c>
+      <c r="D62" s="7">
+        <v>-12.99</v>
+      </c>
+      <c r="E62" s="9">
+        <v>44.64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>14.32</v>
-      </c>
-      <c r="D33" s="6">
-        <v>18.53</v>
-      </c>
-      <c r="E33" s="7">
-        <v>4.21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7">
+        <v>-30.35</v>
+      </c>
+      <c r="D63" s="7">
+        <v>-22.88</v>
+      </c>
+      <c r="E63" s="9">
+        <v>7.47</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>13.4</v>
-      </c>
-      <c r="D34" s="6">
-        <v>12.78</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.62</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-8.35</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-8.56</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-13.31</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-4.75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-18.46</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-19.02</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-35.64</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-36.73</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-1.09</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-12.59</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-12.21</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-9.42</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-9.56</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="6">
-        <v>1264.5</v>
-      </c>
-      <c r="D41" s="6">
-        <v>1296.5</v>
-      </c>
-      <c r="E41" s="7">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>895</v>
-      </c>
-      <c r="D42" s="6">
-        <v>886.7</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-8.300000000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>1774</v>
-      </c>
-      <c r="D43" s="6">
-        <v>1681.7</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-92.3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1956</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1942.5</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-13.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>701.4</v>
-      </c>
-      <c r="D45" s="6">
-        <v>689.55</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-11.85</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>3019.9</v>
-      </c>
-      <c r="D46" s="6">
-        <v>3033.1</v>
-      </c>
-      <c r="E46" s="7">
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>8678.5</v>
-      </c>
-      <c r="D47" s="6">
-        <v>8525.5</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-153</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" s="6">
-        <v>57</v>
-      </c>
-      <c r="D48" s="6">
-        <v>43</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="6">
-        <v>43</v>
-      </c>
-      <c r="D49" s="6">
-        <v>57</v>
-      </c>
-      <c r="E49" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>70.43000000000001</v>
-      </c>
-      <c r="D50" s="6">
-        <v>72.89</v>
-      </c>
-      <c r="E50" s="7">
-        <v>2.46</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>51.15</v>
-      </c>
-      <c r="D51" s="6">
-        <v>49.03</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-2.12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>42.18</v>
-      </c>
-      <c r="D52" s="6">
-        <v>31.53</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-10.65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>48.37</v>
-      </c>
-      <c r="D53" s="6">
-        <v>46.12</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>29.91</v>
-      </c>
-      <c r="D54" s="6">
-        <v>27.02</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-2.89</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>44.67</v>
-      </c>
-      <c r="D55" s="6">
-        <v>45.85</v>
-      </c>
-      <c r="E55" s="7">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>58.89</v>
-      </c>
-      <c r="D56" s="6">
-        <v>53.56</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-5.33</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="5" t="s">
+      <c r="B64" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="6">
-        <v>52.46</v>
-      </c>
-      <c r="D57" s="6">
-        <v>761.08</v>
-      </c>
-      <c r="E57" s="7">
-        <v>708.62</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="6">
-        <v>-48.87</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-48.48</v>
-      </c>
-      <c r="E58" s="7">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>2.24</v>
-      </c>
-      <c r="D59" s="6">
-        <v>240.81</v>
-      </c>
-      <c r="E59" s="7">
-        <v>238.57</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-0.75</v>
-      </c>
-      <c r="D60" s="6">
-        <v>166.74</v>
-      </c>
-      <c r="E60" s="7">
-        <v>167.49</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-66.56999999999999</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-57.63</v>
-      </c>
-      <c r="E61" s="7">
-        <v>8.94</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>19.49</v>
-      </c>
-      <c r="D62" s="6">
-        <v>-30.35</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-49.84</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-51.56</v>
-      </c>
-      <c r="D63" s="6">
+      <c r="C64" s="7">
         <v>-56.65</v>
       </c>
-      <c r="E63" s="8">
-        <v>-5.09</v>
+      <c r="D64" s="7">
+        <v>-49.54</v>
+      </c>
+      <c r="E64" s="9">
+        <v>7.11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2921,60 +2985,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
+      <c r="B1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>56.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>46.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>47.8</v>
+      </c>
+      <c r="E2" s="12">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-1.9</v>
-      </c>
-      <c r="G2" s="11">
-        <v>3.8</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-1.3</v>
+      </c>
+      <c r="G2" s="12">
+        <v>2.8</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>60</v>
       </c>
     </row>
@@ -3076,49 +3140,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.5177</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.3033</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2412</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.2019</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1523</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1115</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.08599999999999999</v>
+      <c r="A2" s="15">
+        <v>0.5285</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.3007</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2404</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.2078</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1516</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1182</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0823</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,46 +187,34 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.4% → -3.8%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.4%</t>
+  </si>
+  <si>
+    <t>-3.8%</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>46.1 → 50.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>46.1</t>
+    <t>50.1 → 40.4</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.1</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>27.0 → 35.6</t>
-  </si>
-  <si>
-    <t>27.0</t>
-  </si>
-  <si>
-    <t>35.6</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>72.9 → 69.4</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>72.9</t>
-  </si>
-  <si>
-    <t>69.4</t>
+    <t>40.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -312,13 +300,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -327,6 +308,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -359,12 +347,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -372,6 +354,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,8 +440,8 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -965,10 +953,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1278.5</v>
+        <v>1247.8</v>
       </c>
       <c r="D2">
-        <v>-1.39</v>
+        <v>-2.4</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -977,46 +965,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-1.39</v>
+        <v>-3.76</v>
       </c>
       <c r="H2">
-        <v>70.84</v>
+        <v>66.73999999999999</v>
       </c>
       <c r="I2">
-        <v>13.71</v>
+        <v>5.84</v>
       </c>
       <c r="J2">
-        <v>15.63</v>
+        <v>13.11</v>
       </c>
       <c r="K2">
-        <v>7.27</v>
+        <v>5.91</v>
       </c>
       <c r="L2">
-        <v>34.65</v>
+        <v>28.62</v>
       </c>
       <c r="M2">
-        <v>8.23</v>
+        <v>7.94</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P2">
-        <v>1245.94</v>
+        <v>1259.72</v>
       </c>
       <c r="Q2">
-        <v>1129.22</v>
+        <v>1135.78</v>
       </c>
       <c r="R2">
-        <v>1111.97</v>
+        <v>1115.73</v>
       </c>
       <c r="S2">
-        <v>968.77</v>
+        <v>970.66</v>
       </c>
       <c r="T2">
-        <v>31.97</v>
+        <v>28.55</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1031,34 +1019,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>69.39</v>
+        <v>63.77</v>
       </c>
       <c r="Z2">
-        <v>37.88</v>
+        <v>40.26</v>
       </c>
       <c r="AA2">
-        <v>14.14</v>
+        <v>19.36</v>
       </c>
       <c r="AB2">
-        <v>23.74</v>
+        <v>20.9</v>
       </c>
       <c r="AC2">
-        <v>96.72</v>
+        <v>88.17</v>
       </c>
       <c r="AD2">
-        <v>98.91</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="AE2">
-        <v>54.15</v>
+        <v>53.76</v>
       </c>
       <c r="AF2">
-        <v>-37.3</v>
+        <v>-59.53</v>
       </c>
       <c r="AG2">
-        <v>1281.58</v>
+        <v>1296.9</v>
       </c>
       <c r="AH2">
-        <v>976.87</v>
+        <v>974.65</v>
       </c>
       <c r="AI2">
         <v>1148.32</v>
@@ -1067,7 +1055,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>45.14</v>
+        <v>47.44</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1078,10 +1066,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>886</v>
+        <v>865</v>
       </c>
       <c r="D3">
-        <v>-0.08</v>
+        <v>-2.37</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1090,46 +1078,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-9.27</v>
+        <v>-11.42</v>
       </c>
       <c r="H3">
-        <v>67.33</v>
+        <v>63.37</v>
       </c>
       <c r="I3">
-        <v>-0.67</v>
+        <v>-4.95</v>
       </c>
       <c r="J3">
-        <v>2.42</v>
+        <v>-3.66</v>
       </c>
       <c r="K3">
-        <v>-7.35</v>
+        <v>-9.15</v>
       </c>
       <c r="L3">
-        <v>15.29</v>
+        <v>12.08</v>
       </c>
       <c r="M3">
-        <v>52.85</v>
+        <v>51.01</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P3">
-        <v>894.76</v>
+        <v>885.76</v>
       </c>
       <c r="Q3">
-        <v>893.29</v>
+        <v>892.09</v>
       </c>
       <c r="R3">
-        <v>884.0599999999999</v>
+        <v>883.26</v>
       </c>
       <c r="S3">
-        <v>790.8099999999999</v>
+        <v>791.8</v>
       </c>
       <c r="T3">
-        <v>12.04</v>
+        <v>9.24</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1144,34 +1132,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>48.85</v>
+        <v>43.58</v>
       </c>
       <c r="Z3">
-        <v>0.58</v>
+        <v>-1.51</v>
       </c>
       <c r="AA3">
-        <v>1.22</v>
+        <v>0.67</v>
       </c>
       <c r="AB3">
-        <v>-0.64</v>
+        <v>-2.18</v>
       </c>
       <c r="AC3">
-        <v>46.85</v>
+        <v>33.78</v>
       </c>
       <c r="AD3">
-        <v>53.17</v>
+        <v>43.98</v>
       </c>
       <c r="AE3">
-        <v>24.66</v>
+        <v>24.52</v>
       </c>
       <c r="AF3">
-        <v>-62.74</v>
+        <v>-27.45</v>
       </c>
       <c r="AG3">
-        <v>930.38</v>
+        <v>931.26</v>
       </c>
       <c r="AH3">
-        <v>856.2</v>
+        <v>852.92</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1180,7 +1168,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>19.84</v>
+        <v>20.38</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1191,10 +1179,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1662.7</v>
+        <v>1634.2</v>
       </c>
       <c r="D4">
-        <v>-1.13</v>
+        <v>-1.71</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1203,46 +1191,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-14.29</v>
+        <v>-15.76</v>
       </c>
       <c r="H4">
-        <v>22.74</v>
+        <v>20.63</v>
       </c>
       <c r="I4">
-        <v>-7.63</v>
+        <v>-7.36</v>
       </c>
       <c r="J4">
-        <v>-11</v>
+        <v>-12.86</v>
       </c>
       <c r="K4">
-        <v>-6.27</v>
+        <v>-8.69</v>
       </c>
       <c r="L4">
-        <v>2.08</v>
+        <v>0.72</v>
       </c>
       <c r="M4">
-        <v>24.04</v>
+        <v>24.35</v>
       </c>
       <c r="N4">
         <v>43</v>
       </c>
       <c r="O4">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P4">
-        <v>1728.3</v>
+        <v>1702.34</v>
       </c>
       <c r="Q4">
-        <v>1800.89</v>
+        <v>1789.46</v>
       </c>
       <c r="R4">
-        <v>1827.47</v>
+        <v>1824.06</v>
       </c>
       <c r="S4">
-        <v>1683.35</v>
+        <v>1682.87</v>
       </c>
       <c r="T4">
-        <v>-1.23</v>
+        <v>-2.89</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1257,43 +1245,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>29.86</v>
+        <v>27.51</v>
       </c>
       <c r="Z4">
-        <v>-35.34</v>
+        <v>-42.78</v>
       </c>
       <c r="AA4">
-        <v>-19.49</v>
+        <v>-24.15</v>
       </c>
       <c r="AB4">
-        <v>-15.85</v>
+        <v>-18.64</v>
       </c>
       <c r="AC4">
-        <v>10.39</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>14.39</v>
+        <v>8.1</v>
       </c>
       <c r="AE4">
-        <v>50.11</v>
+        <v>49.56</v>
       </c>
       <c r="AF4">
-        <v>106.25</v>
+        <v>-18.64</v>
       </c>
       <c r="AG4">
-        <v>1913.64</v>
+        <v>1920.61</v>
       </c>
       <c r="AH4">
-        <v>1688.15</v>
+        <v>1658.31</v>
       </c>
       <c r="AI4">
-        <v>1810.09</v>
+        <v>1789.07</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>34.86</v>
+        <v>40.1</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1304,10 +1292,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1963.9</v>
+        <v>1899.1</v>
       </c>
       <c r="D5">
-        <v>1.1</v>
+        <v>-3.3</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1316,46 +1304,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-18.13</v>
+        <v>-20.83</v>
       </c>
       <c r="H5">
-        <v>12.51</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="I5">
-        <v>-1.78</v>
+        <v>-2.15</v>
       </c>
       <c r="J5">
-        <v>0.73</v>
+        <v>-1.52</v>
       </c>
       <c r="K5">
-        <v>2.61</v>
+        <v>-5.28</v>
       </c>
       <c r="L5">
-        <v>-13.26</v>
+        <v>-15.48</v>
       </c>
       <c r="M5">
-        <v>20.78</v>
+        <v>19.9</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="P5">
-        <v>1949.62</v>
+        <v>1941.28</v>
       </c>
       <c r="Q5">
-        <v>1943.04</v>
+        <v>1942.31</v>
       </c>
       <c r="R5">
-        <v>2000.69</v>
+        <v>1997.99</v>
       </c>
       <c r="S5">
-        <v>2067.42</v>
+        <v>2065.12</v>
       </c>
       <c r="T5">
-        <v>-5.01</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1370,34 +1358,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>50.07</v>
+        <v>40.41</v>
       </c>
       <c r="Z5">
-        <v>-10.54</v>
+        <v>-13.99</v>
       </c>
       <c r="AA5">
-        <v>-15.53</v>
+        <v>-15.22</v>
       </c>
       <c r="AB5">
-        <v>4.99</v>
+        <v>1.23</v>
       </c>
       <c r="AC5">
-        <v>51.09</v>
+        <v>32.51</v>
       </c>
       <c r="AD5">
-        <v>50.99</v>
+        <v>43.99</v>
       </c>
       <c r="AE5">
-        <v>44.56</v>
+        <v>46.37</v>
       </c>
       <c r="AF5">
-        <v>-62.9</v>
+        <v>-51.97</v>
       </c>
       <c r="AG5">
-        <v>1988.06</v>
+        <v>1989.75</v>
       </c>
       <c r="AH5">
-        <v>1898.02</v>
+        <v>1894.87</v>
       </c>
       <c r="AI5">
         <v>2050.28</v>
@@ -1406,7 +1394,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>31.23</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1417,10 +1405,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>704.75</v>
+        <v>706.45</v>
       </c>
       <c r="D6">
-        <v>2.2</v>
+        <v>0.24</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1429,46 +1417,46 @@
         <v>689.55</v>
       </c>
       <c r="G6">
-        <v>-35.33</v>
+        <v>-35.18</v>
       </c>
       <c r="H6">
-        <v>2.2</v>
+        <v>2.45</v>
       </c>
       <c r="I6">
-        <v>0.58</v>
+        <v>0.79</v>
       </c>
       <c r="J6">
-        <v>-11.5</v>
+        <v>-11.17</v>
       </c>
       <c r="K6">
-        <v>-1.3</v>
+        <v>-1.05</v>
       </c>
       <c r="L6">
-        <v>-34.41</v>
+        <v>-33.8</v>
       </c>
       <c r="M6">
-        <v>11.82</v>
+        <v>12.14</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="P6">
-        <v>698.4299999999999</v>
+        <v>699.54</v>
       </c>
       <c r="Q6">
-        <v>740.77</v>
+        <v>735.83</v>
       </c>
       <c r="R6">
-        <v>766.86</v>
+        <v>765.97</v>
       </c>
       <c r="S6">
-        <v>830.23</v>
+        <v>828.72</v>
       </c>
       <c r="T6">
-        <v>-15.11</v>
+        <v>-14.75</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1483,34 +1471,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>35.62</v>
+        <v>36.52</v>
       </c>
       <c r="Z6">
-        <v>-23.74</v>
+        <v>-22.62</v>
       </c>
       <c r="AA6">
-        <v>-19.86</v>
+        <v>-20.41</v>
       </c>
       <c r="AB6">
-        <v>-3.88</v>
+        <v>-2.2</v>
       </c>
       <c r="AC6">
-        <v>22.64</v>
+        <v>39.02</v>
       </c>
       <c r="AD6">
-        <v>11.82</v>
+        <v>22.85</v>
       </c>
       <c r="AE6">
-        <v>20.98</v>
+        <v>20.5</v>
       </c>
       <c r="AF6">
-        <v>-12.99</v>
+        <v>-11.01</v>
       </c>
       <c r="AG6">
-        <v>826.39</v>
+        <v>817.0599999999999</v>
       </c>
       <c r="AH6">
-        <v>655.15</v>
+        <v>654.59</v>
       </c>
       <c r="AI6">
         <v>757.9400000000001</v>
@@ -1519,7 +1507,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>46.49</v>
+        <v>45.31</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1530,10 +1518,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>3003.4</v>
+        <v>2929.4</v>
       </c>
       <c r="D7">
-        <v>-0.98</v>
+        <v>-2.46</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1542,25 +1530,25 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-13.07</v>
+        <v>-15.21</v>
       </c>
       <c r="H7">
-        <v>58.79</v>
+        <v>54.88</v>
       </c>
       <c r="I7">
-        <v>-1.66</v>
+        <v>-3.75</v>
       </c>
       <c r="J7">
-        <v>-11.32</v>
+        <v>-11.98</v>
       </c>
       <c r="K7">
-        <v>14.75</v>
+        <v>14.21</v>
       </c>
       <c r="L7">
-        <v>22.03</v>
+        <v>19.76</v>
       </c>
       <c r="M7">
-        <v>30.07</v>
+        <v>29.12</v>
       </c>
       <c r="N7">
         <v>85</v>
@@ -1569,19 +1557,19 @@
         <v>78</v>
       </c>
       <c r="P7">
-        <v>3016.56</v>
+        <v>2993.76</v>
       </c>
       <c r="Q7">
-        <v>3143.99</v>
+        <v>3125.83</v>
       </c>
       <c r="R7">
-        <v>2962.35</v>
+        <v>2970.17</v>
       </c>
       <c r="S7">
-        <v>2487.73</v>
+        <v>2491.65</v>
       </c>
       <c r="T7">
-        <v>20.73</v>
+        <v>17.57</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1596,43 +1584,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>43.61</v>
+        <v>38.56</v>
       </c>
       <c r="Z7">
-        <v>-6.87</v>
+        <v>-17.71</v>
       </c>
       <c r="AA7">
-        <v>29.53</v>
+        <v>20.08</v>
       </c>
       <c r="AB7">
-        <v>-36.4</v>
+        <v>-37.79</v>
       </c>
       <c r="AC7">
-        <v>16.16</v>
+        <v>11.41</v>
       </c>
       <c r="AD7">
-        <v>11.09</v>
+        <v>13.31</v>
       </c>
       <c r="AE7">
-        <v>130.63</v>
+        <v>127.97</v>
       </c>
       <c r="AF7">
-        <v>-22.88</v>
+        <v>-50.45</v>
       </c>
       <c r="AG7">
-        <v>3350.32</v>
+        <v>3340.84</v>
       </c>
       <c r="AH7">
-        <v>2937.67</v>
+        <v>2910.83</v>
       </c>
       <c r="AI7">
-        <v>3398.57</v>
+        <v>3342.65</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>20.03</v>
+        <v>21.63</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1643,58 +1631,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8646</v>
+        <v>8459</v>
       </c>
       <c r="D8">
-        <v>1.41</v>
+        <v>-2.16</v>
       </c>
       <c r="E8">
-        <v>9393</v>
+        <v>9238.98</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-7.95</v>
+        <v>-8.44</v>
       </c>
       <c r="H8">
-        <v>45.94</v>
+        <v>42.78</v>
       </c>
       <c r="I8">
-        <v>-1.39</v>
+        <v>-2.1</v>
       </c>
       <c r="J8">
-        <v>6.11</v>
+        <v>0.99</v>
       </c>
       <c r="K8">
-        <v>9.640000000000001</v>
+        <v>2.58</v>
       </c>
       <c r="L8">
-        <v>-8.279999999999999</v>
+        <v>-9.94</v>
       </c>
       <c r="M8">
-        <v>15.16</v>
+        <v>14.87</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="P8">
-        <v>8623.5</v>
+        <v>8587.200000000001</v>
       </c>
       <c r="Q8">
-        <v>8467.120000000001</v>
+        <v>8477.9</v>
       </c>
       <c r="R8">
-        <v>8201.09</v>
+        <v>8218.6</v>
       </c>
       <c r="S8">
-        <v>7437.03</v>
+        <v>7439.96</v>
       </c>
       <c r="T8">
-        <v>16.26</v>
+        <v>13.7</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1709,34 +1697,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>56.87</v>
+        <v>50.82</v>
       </c>
       <c r="Z8">
-        <v>143.88</v>
+        <v>123.27</v>
       </c>
       <c r="AA8">
-        <v>150.66</v>
+        <v>145.18</v>
       </c>
       <c r="AB8">
-        <v>-6.78</v>
+        <v>-21.91</v>
       </c>
       <c r="AC8">
-        <v>29.45</v>
+        <v>13.23</v>
       </c>
       <c r="AD8">
-        <v>40.72</v>
+        <v>26.92</v>
       </c>
       <c r="AE8">
-        <v>308.19</v>
+        <v>300.47</v>
       </c>
       <c r="AF8">
-        <v>-49.54</v>
+        <v>-66.27</v>
       </c>
       <c r="AG8">
-        <v>8973.09</v>
+        <v>8972.870000000001</v>
       </c>
       <c r="AH8">
-        <v>7961.16</v>
+        <v>7982.93</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
@@ -1745,7 +1733,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>44.97</v>
+        <v>42.82</v>
       </c>
     </row>
   </sheetData>
@@ -1886,7 +1874,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1926,7 +1914,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1945,1027 +1933,1007 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="F4" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>73</v>
+      <c r="B8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="7">
+        <v>15.63</v>
+      </c>
+      <c r="D8" s="7">
+        <v>13.11</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-2.52</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="7">
-        <v>17.15</v>
+        <v>2.42</v>
       </c>
       <c r="D9" s="7">
-        <v>15.63</v>
+        <v>-3.66</v>
       </c>
       <c r="E9" s="8">
-        <v>-1.52</v>
+        <v>-6.08</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>0.93</v>
+        <v>-11</v>
       </c>
       <c r="D10" s="7">
-        <v>2.42</v>
-      </c>
-      <c r="E10" s="9">
-        <v>1.49</v>
+        <v>-12.86</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>-10.21</v>
+        <v>0.73</v>
       </c>
       <c r="D11" s="7">
-        <v>-11</v>
+        <v>-1.52</v>
       </c>
       <c r="E11" s="8">
-        <v>-0.79</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>1.51</v>
+        <v>-11.5</v>
       </c>
       <c r="D12" s="7">
-        <v>0.73</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.78</v>
+        <v>-11.17</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0.33</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-14.91</v>
+        <v>-11.32</v>
       </c>
       <c r="D13" s="7">
-        <v>-11.5</v>
-      </c>
-      <c r="E13" s="9">
-        <v>3.41</v>
+        <v>-11.98</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="7">
-        <v>-12.21</v>
+        <v>6.11</v>
       </c>
       <c r="D14" s="7">
-        <v>-11.32</v>
-      </c>
-      <c r="E14" s="9">
-        <v>0.89</v>
+        <v>0.99</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-5.12</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="7">
-        <v>4.11</v>
+        <v>13.71</v>
       </c>
       <c r="D15" s="7">
-        <v>6.11</v>
-      </c>
-      <c r="E15" s="9">
-        <v>2</v>
+        <v>5.84</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-7.87</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="7">
-        <v>19.65</v>
+        <v>-0.67</v>
       </c>
       <c r="D16" s="7">
-        <v>13.71</v>
+        <v>-4.95</v>
       </c>
       <c r="E16" s="8">
-        <v>-5.94</v>
+        <v>-4.28</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="7">
-        <v>0.76</v>
+        <v>-7.63</v>
       </c>
       <c r="D17" s="7">
-        <v>-0.67</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.43</v>
+        <v>-7.36</v>
+      </c>
+      <c r="E17" s="9">
+        <v>0.27</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>-4.69</v>
+        <v>-1.78</v>
       </c>
       <c r="D18" s="7">
-        <v>-7.63</v>
+        <v>-2.15</v>
       </c>
       <c r="E18" s="8">
-        <v>-2.94</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C19" s="7">
-        <v>0.66</v>
+        <v>0.58</v>
       </c>
       <c r="D19" s="7">
-        <v>-1.78</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-2.44</v>
+        <v>0.79</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.21</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="7">
-        <v>-1.93</v>
+        <v>-1.66</v>
       </c>
       <c r="D20" s="7">
-        <v>0.58</v>
-      </c>
-      <c r="E20" s="9">
-        <v>2.51</v>
+        <v>-3.75</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.09</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="7">
-        <v>-0.54</v>
+        <v>-1.39</v>
       </c>
       <c r="D21" s="7">
-        <v>-1.66</v>
+        <v>-2.1</v>
       </c>
       <c r="E21" s="8">
-        <v>-1.12</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C22" s="7">
-        <v>-2.73</v>
+        <v>34.65</v>
       </c>
       <c r="D22" s="7">
-        <v>-1.39</v>
-      </c>
-      <c r="E22" s="9">
-        <v>1.34</v>
+        <v>28.62</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-6.03</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C23" s="7">
-        <v>35.49</v>
+        <v>15.29</v>
       </c>
       <c r="D23" s="7">
-        <v>34.65</v>
+        <v>12.08</v>
       </c>
       <c r="E23" s="8">
-        <v>-0.84</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C24" s="7">
-        <v>14.02</v>
+        <v>2.08</v>
       </c>
       <c r="D24" s="7">
-        <v>15.29</v>
-      </c>
-      <c r="E24" s="9">
-        <v>1.27</v>
+        <v>0.72</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C25" s="7">
-        <v>5.79</v>
+        <v>-13.26</v>
       </c>
       <c r="D25" s="7">
-        <v>2.08</v>
+        <v>-15.48</v>
       </c>
       <c r="E25" s="8">
-        <v>-3.71</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C26" s="7">
-        <v>-13.77</v>
+        <v>-34.41</v>
       </c>
       <c r="D26" s="7">
-        <v>-13.26</v>
+        <v>-33.8</v>
       </c>
       <c r="E26" s="9">
-        <v>0.51</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C27" s="7">
-        <v>-35.33</v>
+        <v>22.03</v>
       </c>
       <c r="D27" s="7">
-        <v>-34.41</v>
-      </c>
-      <c r="E27" s="9">
-        <v>0.92</v>
+        <v>19.76</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="7">
-        <v>21.27</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="D28" s="7">
-        <v>22.03</v>
-      </c>
-      <c r="E28" s="9">
-        <v>0.76</v>
+        <v>-9.94</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29" s="7">
-        <v>-11.02</v>
+        <v>7.27</v>
       </c>
       <c r="D29" s="7">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="E29" s="9">
-        <v>2.74</v>
+        <v>5.91</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="7">
-        <v>13.4</v>
+        <v>-7.35</v>
       </c>
       <c r="D30" s="7">
-        <v>7.27</v>
+        <v>-9.15</v>
       </c>
       <c r="E30" s="8">
-        <v>-6.13</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="7">
-        <v>-5.88</v>
+        <v>-6.27</v>
       </c>
       <c r="D31" s="7">
-        <v>-7.35</v>
+        <v>-8.69</v>
       </c>
       <c r="E31" s="8">
-        <v>-1.47</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="7">
-        <v>-6.53</v>
+        <v>2.61</v>
       </c>
       <c r="D32" s="7">
-        <v>-6.27</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.26</v>
+        <v>-5.28</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-7.89</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="7">
-        <v>-2.89</v>
+        <v>-1.3</v>
       </c>
       <c r="D33" s="7">
-        <v>2.61</v>
+        <v>-1.05</v>
       </c>
       <c r="E33" s="9">
-        <v>5.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="7">
-        <v>-2.85</v>
+        <v>14.75</v>
       </c>
       <c r="D34" s="7">
-        <v>-1.3</v>
-      </c>
-      <c r="E34" s="9">
-        <v>1.55</v>
+        <v>14.21</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="7">
-        <v>18.53</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="D35" s="7">
-        <v>14.75</v>
+        <v>2.58</v>
       </c>
       <c r="E35" s="8">
-        <v>-3.78</v>
+        <v>-7.06</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C36" s="7">
-        <v>12.78</v>
+        <v>-1.39</v>
       </c>
       <c r="D36" s="7">
-        <v>9.640000000000001</v>
+        <v>-3.76</v>
       </c>
       <c r="E36" s="8">
-        <v>-3.14</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C37" s="7">
-        <v>0</v>
+        <v>-9.27</v>
       </c>
       <c r="D37" s="7">
-        <v>-1.39</v>
+        <v>-11.42</v>
       </c>
       <c r="E37" s="8">
-        <v>-1.39</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C38" s="7">
-        <v>-9.199999999999999</v>
+        <v>-14.29</v>
       </c>
       <c r="D38" s="7">
-        <v>-9.27</v>
+        <v>-15.76</v>
       </c>
       <c r="E38" s="8">
-        <v>-0.07000000000000001</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C39" s="7">
-        <v>-13.31</v>
+        <v>-18.13</v>
       </c>
       <c r="D39" s="7">
-        <v>-14.29</v>
+        <v>-20.83</v>
       </c>
       <c r="E39" s="8">
-        <v>-0.98</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C40" s="7">
-        <v>-19.02</v>
+        <v>-35.33</v>
       </c>
       <c r="D40" s="7">
-        <v>-18.13</v>
+        <v>-35.18</v>
       </c>
       <c r="E40" s="9">
-        <v>0.89</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C41" s="7">
-        <v>-36.73</v>
+        <v>-13.07</v>
       </c>
       <c r="D41" s="7">
-        <v>-35.33</v>
-      </c>
-      <c r="E41" s="9">
-        <v>1.4</v>
+        <v>-15.21</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C42" s="7">
-        <v>-12.21</v>
+        <v>-7.95</v>
       </c>
       <c r="D42" s="7">
-        <v>-13.07</v>
+        <v>-8.44</v>
       </c>
       <c r="E42" s="8">
-        <v>-0.86</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C43" s="7">
-        <v>-9.56</v>
+        <v>1278.5</v>
       </c>
       <c r="D43" s="7">
-        <v>-7.95</v>
-      </c>
-      <c r="E43" s="9">
-        <v>1.61</v>
+        <v>1247.8</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-30.7</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C44" s="7">
-        <v>1296.5</v>
+        <v>886</v>
       </c>
       <c r="D44" s="7">
-        <v>1278.5</v>
+        <v>865</v>
       </c>
       <c r="E44" s="8">
-        <v>-18</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C45" s="7">
-        <v>886.7</v>
+        <v>1662.7</v>
       </c>
       <c r="D45" s="7">
-        <v>886</v>
+        <v>1634.2</v>
       </c>
       <c r="E45" s="8">
-        <v>-0.7</v>
+        <v>-28.5</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C46" s="7">
-        <v>1681.7</v>
+        <v>1963.9</v>
       </c>
       <c r="D46" s="7">
-        <v>1662.7</v>
+        <v>1899.1</v>
       </c>
       <c r="E46" s="8">
-        <v>-19</v>
+        <v>-64.8</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C47" s="7">
-        <v>1942.5</v>
+        <v>704.75</v>
       </c>
       <c r="D47" s="7">
-        <v>1963.9</v>
+        <v>706.45</v>
       </c>
       <c r="E47" s="9">
-        <v>21.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C48" s="7">
-        <v>689.55</v>
+        <v>3003.4</v>
       </c>
       <c r="D48" s="7">
-        <v>704.75</v>
-      </c>
-      <c r="E48" s="9">
-        <v>15.2</v>
+        <v>2929.4</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-74</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C49" s="7">
-        <v>3033.1</v>
+        <v>8646</v>
       </c>
       <c r="D49" s="7">
-        <v>3003.4</v>
+        <v>8459</v>
       </c>
       <c r="E49" s="8">
-        <v>-29.7</v>
+        <v>-187</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C50" s="7">
-        <v>8525.5</v>
+        <v>69.39</v>
       </c>
       <c r="D50" s="7">
-        <v>8646</v>
-      </c>
-      <c r="E50" s="9">
-        <v>120.5</v>
+        <v>63.77</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-5.62</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="7">
-        <v>72.89</v>
+        <v>48.85</v>
       </c>
       <c r="D51" s="7">
-        <v>69.39</v>
+        <v>43.58</v>
       </c>
       <c r="E51" s="8">
-        <v>-3.5</v>
+        <v>-5.27</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="7">
-        <v>49.03</v>
+        <v>29.86</v>
       </c>
       <c r="D52" s="7">
-        <v>48.85</v>
+        <v>27.51</v>
       </c>
       <c r="E52" s="8">
-        <v>-0.18</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="7">
-        <v>31.53</v>
+        <v>50.07</v>
       </c>
       <c r="D53" s="7">
-        <v>29.86</v>
+        <v>40.41</v>
       </c>
       <c r="E53" s="8">
-        <v>-1.67</v>
+        <v>-9.66</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="7">
-        <v>46.12</v>
+        <v>35.62</v>
       </c>
       <c r="D54" s="7">
-        <v>50.07</v>
+        <v>36.52</v>
       </c>
       <c r="E54" s="9">
-        <v>3.95</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="7">
-        <v>27.02</v>
+        <v>43.61</v>
       </c>
       <c r="D55" s="7">
-        <v>35.62</v>
-      </c>
-      <c r="E55" s="9">
-        <v>8.6</v>
+        <v>38.56</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-5.05</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="7">
-        <v>45.85</v>
+        <v>56.87</v>
       </c>
       <c r="D56" s="7">
-        <v>43.61</v>
+        <v>50.82</v>
       </c>
       <c r="E56" s="8">
-        <v>-2.24</v>
+        <v>-6.05</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C57" s="7">
-        <v>53.56</v>
+        <v>-37.3</v>
       </c>
       <c r="D57" s="7">
-        <v>56.87</v>
-      </c>
-      <c r="E57" s="9">
-        <v>3.31</v>
+        <v>-59.53</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-22.23</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="7">
-        <v>761.08</v>
+        <v>-62.74</v>
       </c>
       <c r="D58" s="7">
-        <v>-37.3</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-798.38</v>
+        <v>-27.45</v>
+      </c>
+      <c r="E58" s="9">
+        <v>35.29</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="7">
-        <v>-48.48</v>
+        <v>106.25</v>
       </c>
       <c r="D59" s="7">
-        <v>-62.74</v>
+        <v>-18.64</v>
       </c>
       <c r="E59" s="8">
-        <v>-14.26</v>
+        <v>-124.89</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="7">
-        <v>240.81</v>
+        <v>-62.9</v>
       </c>
       <c r="D60" s="7">
-        <v>106.25</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-134.56</v>
+        <v>-51.97</v>
+      </c>
+      <c r="E60" s="9">
+        <v>10.93</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="7">
-        <v>166.74</v>
+        <v>-12.99</v>
       </c>
       <c r="D61" s="7">
-        <v>-62.9</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-229.64</v>
+        <v>-11.01</v>
+      </c>
+      <c r="E61" s="9">
+        <v>1.98</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="7">
-        <v>-57.63</v>
+        <v>-22.88</v>
       </c>
       <c r="D62" s="7">
-        <v>-12.99</v>
-      </c>
-      <c r="E62" s="9">
-        <v>44.64</v>
+        <v>-50.45</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-27.57</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C63" s="7">
-        <v>-30.35</v>
+        <v>-49.54</v>
       </c>
       <c r="D63" s="7">
-        <v>-22.88</v>
-      </c>
-      <c r="E63" s="9">
-        <v>7.47</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>-56.65</v>
-      </c>
-      <c r="D64" s="7">
-        <v>-49.54</v>
-      </c>
-      <c r="E64" s="9">
-        <v>7.11</v>
+        <v>-66.27</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-16.73</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2989,28 +2957,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -3024,16 +2992,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="12">
-        <v>47.8</v>
+        <v>43</v>
       </c>
       <c r="E2" s="12">
         <v>60</v>
       </c>
       <c r="F2" s="12">
-        <v>-1.3</v>
+        <v>-3.9</v>
       </c>
       <c r="G2" s="12">
-        <v>2.8</v>
+        <v>-0.2</v>
       </c>
       <c r="H2" s="12">
         <v>57</v>
@@ -3164,25 +3132,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="15">
-        <v>0.5285</v>
+        <v>0.5101</v>
       </c>
       <c r="B2" s="15">
-        <v>0.3007</v>
+        <v>0.2912</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2404</v>
+        <v>0.2435</v>
       </c>
       <c r="D2" s="15">
-        <v>0.2078</v>
+        <v>0.199</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1516</v>
+        <v>0.1487</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1182</v>
+        <v>0.1214</v>
       </c>
       <c r="G2" s="15">
-        <v>0.0823</v>
+        <v>0.0794</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,34 +187,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.4% → -3.8%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.4%</t>
-  </si>
-  <si>
-    <t>-3.8%</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.1 → 40.4</t>
+    <t>50.8 → 48.9</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>40.4</t>
+    <t>50.8</t>
+  </si>
+  <si>
+    <t>48.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -266,7 +251,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -300,13 +285,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -320,7 +298,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -342,12 +320,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -429,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -437,15 +409,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -454,7 +425,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -953,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1247.8</v>
+        <v>1200.5</v>
       </c>
       <c r="D2">
-        <v>-2.4</v>
+        <v>-3.79</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -965,46 +936,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-3.76</v>
+        <v>-7.4</v>
       </c>
       <c r="H2">
-        <v>66.73999999999999</v>
+        <v>60.42</v>
       </c>
       <c r="I2">
-        <v>5.84</v>
+        <v>-0.89</v>
       </c>
       <c r="J2">
-        <v>13.11</v>
+        <v>7.49</v>
       </c>
       <c r="K2">
-        <v>5.91</v>
+        <v>3.14</v>
       </c>
       <c r="L2">
-        <v>28.62</v>
+        <v>25.93</v>
       </c>
       <c r="M2">
-        <v>7.94</v>
+        <v>7.01</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="P2">
-        <v>1259.72</v>
+        <v>1257.56</v>
       </c>
       <c r="Q2">
-        <v>1135.78</v>
+        <v>1140.47</v>
       </c>
       <c r="R2">
-        <v>1115.73</v>
+        <v>1118</v>
       </c>
       <c r="S2">
-        <v>970.66</v>
+        <v>972.4</v>
       </c>
       <c r="T2">
-        <v>28.55</v>
+        <v>23.46</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1019,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>63.77</v>
+        <v>56.21</v>
       </c>
       <c r="Z2">
-        <v>40.26</v>
+        <v>37.89</v>
       </c>
       <c r="AA2">
-        <v>19.36</v>
+        <v>23.07</v>
       </c>
       <c r="AB2">
-        <v>20.9</v>
+        <v>14.82</v>
       </c>
       <c r="AC2">
-        <v>88.17</v>
+        <v>72.54000000000001</v>
       </c>
       <c r="AD2">
-        <v>94.95999999999999</v>
+        <v>85.81</v>
       </c>
       <c r="AE2">
-        <v>53.76</v>
+        <v>54.28</v>
       </c>
       <c r="AF2">
-        <v>-59.53</v>
+        <v>-52.1</v>
       </c>
       <c r="AG2">
-        <v>1296.9</v>
+        <v>1303.47</v>
       </c>
       <c r="AH2">
-        <v>974.65</v>
+        <v>977.47</v>
       </c>
       <c r="AI2">
         <v>1148.32</v>
@@ -1055,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>47.44</v>
+        <v>45.65</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1066,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>865</v>
+        <v>858.05</v>
       </c>
       <c r="D3">
-        <v>-2.37</v>
+        <v>-0.8</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1078,46 +1049,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-11.42</v>
+        <v>-12.13</v>
       </c>
       <c r="H3">
-        <v>63.37</v>
+        <v>62.06</v>
       </c>
       <c r="I3">
-        <v>-4.95</v>
+        <v>-4.25</v>
       </c>
       <c r="J3">
-        <v>-3.66</v>
+        <v>-3.48</v>
       </c>
       <c r="K3">
-        <v>-9.15</v>
+        <v>-12.13</v>
       </c>
       <c r="L3">
-        <v>12.08</v>
+        <v>11.67</v>
       </c>
       <c r="M3">
-        <v>51.01</v>
+        <v>49.31</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P3">
-        <v>885.76</v>
+        <v>878.15</v>
       </c>
       <c r="Q3">
-        <v>892.09</v>
+        <v>889.1900000000001</v>
       </c>
       <c r="R3">
-        <v>883.26</v>
+        <v>882.17</v>
       </c>
       <c r="S3">
-        <v>791.8</v>
+        <v>792.77</v>
       </c>
       <c r="T3">
-        <v>9.24</v>
+        <v>8.23</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1132,34 +1103,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>43.58</v>
+        <v>41.97</v>
       </c>
       <c r="Z3">
-        <v>-1.51</v>
+        <v>-3.68</v>
       </c>
       <c r="AA3">
-        <v>0.67</v>
+        <v>-0.2</v>
       </c>
       <c r="AB3">
-        <v>-2.18</v>
+        <v>-3.48</v>
       </c>
       <c r="AC3">
-        <v>33.78</v>
+        <v>21.58</v>
       </c>
       <c r="AD3">
-        <v>43.98</v>
+        <v>34.07</v>
       </c>
       <c r="AE3">
-        <v>24.52</v>
+        <v>24.05</v>
       </c>
       <c r="AF3">
-        <v>-27.45</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="AG3">
-        <v>931.26</v>
+        <v>929.47</v>
       </c>
       <c r="AH3">
-        <v>852.92</v>
+        <v>848.91</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1168,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>20.38</v>
+        <v>21.87</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1179,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1634.2</v>
+        <v>1627.3</v>
       </c>
       <c r="D4">
-        <v>-1.71</v>
+        <v>-0.42</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1191,46 +1162,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-15.76</v>
+        <v>-16.12</v>
       </c>
       <c r="H4">
-        <v>20.63</v>
+        <v>20.12</v>
       </c>
       <c r="I4">
-        <v>-7.36</v>
+        <v>-7.49</v>
       </c>
       <c r="J4">
-        <v>-12.86</v>
+        <v>-12.65</v>
       </c>
       <c r="K4">
-        <v>-8.69</v>
+        <v>-9.76</v>
       </c>
       <c r="L4">
-        <v>0.72</v>
+        <v>-0.1</v>
       </c>
       <c r="M4">
-        <v>24.35</v>
+        <v>23.42</v>
       </c>
       <c r="N4">
         <v>43</v>
       </c>
       <c r="O4">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P4">
-        <v>1702.34</v>
+        <v>1675.98</v>
       </c>
       <c r="Q4">
-        <v>1789.46</v>
+        <v>1777.95</v>
       </c>
       <c r="R4">
-        <v>1824.06</v>
+        <v>1820.95</v>
       </c>
       <c r="S4">
-        <v>1682.87</v>
+        <v>1682.3</v>
       </c>
       <c r="T4">
-        <v>-2.89</v>
+        <v>-3.27</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1245,43 +1216,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>27.51</v>
+        <v>26.95</v>
       </c>
       <c r="Z4">
-        <v>-42.78</v>
+        <v>-48.68</v>
       </c>
       <c r="AA4">
-        <v>-24.15</v>
+        <v>-29.05</v>
       </c>
       <c r="AB4">
-        <v>-18.64</v>
+        <v>-19.62</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>8.1</v>
+        <v>3.46</v>
       </c>
       <c r="AE4">
-        <v>49.56</v>
+        <v>49.14</v>
       </c>
       <c r="AF4">
-        <v>-18.64</v>
+        <v>0.47</v>
       </c>
       <c r="AG4">
-        <v>1920.61</v>
+        <v>1923.59</v>
       </c>
       <c r="AH4">
-        <v>1658.31</v>
+        <v>1632.32</v>
       </c>
       <c r="AI4">
-        <v>1789.07</v>
+        <v>1769.53</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>40.1</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1292,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1899.1</v>
+        <v>1792.9</v>
       </c>
       <c r="D5">
-        <v>-3.3</v>
+        <v>-5.59</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1304,46 +1275,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-20.83</v>
+        <v>-25.26</v>
       </c>
       <c r="H5">
-        <v>8.789999999999999</v>
+        <v>2.71</v>
       </c>
       <c r="I5">
-        <v>-2.15</v>
+        <v>-7.82</v>
       </c>
       <c r="J5">
-        <v>-1.52</v>
+        <v>-6.31</v>
       </c>
       <c r="K5">
-        <v>-5.28</v>
+        <v>-10.05</v>
       </c>
       <c r="L5">
-        <v>-15.48</v>
+        <v>-19.31</v>
       </c>
       <c r="M5">
-        <v>19.9</v>
+        <v>18.58</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="P5">
-        <v>1941.28</v>
+        <v>1910.88</v>
       </c>
       <c r="Q5">
-        <v>1942.31</v>
+        <v>1936.66</v>
       </c>
       <c r="R5">
-        <v>1997.99</v>
+        <v>1993.44</v>
       </c>
       <c r="S5">
-        <v>2065.12</v>
+        <v>2062.71</v>
       </c>
       <c r="T5">
-        <v>-8.039999999999999</v>
+        <v>-13.08</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1358,43 +1329,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>40.41</v>
+        <v>30.15</v>
       </c>
       <c r="Z5">
-        <v>-13.99</v>
+        <v>-25</v>
       </c>
       <c r="AA5">
-        <v>-15.22</v>
+        <v>-17.17</v>
       </c>
       <c r="AB5">
-        <v>1.23</v>
+        <v>-7.82</v>
       </c>
       <c r="AC5">
-        <v>32.51</v>
+        <v>20.76</v>
       </c>
       <c r="AD5">
-        <v>43.99</v>
+        <v>34.79</v>
       </c>
       <c r="AE5">
-        <v>46.37</v>
+        <v>52.2</v>
       </c>
       <c r="AF5">
-        <v>-51.97</v>
+        <v>214.23</v>
       </c>
       <c r="AG5">
-        <v>1989.75</v>
+        <v>2017.51</v>
       </c>
       <c r="AH5">
-        <v>1894.87</v>
+        <v>1855.81</v>
       </c>
       <c r="AI5">
-        <v>2050.28</v>
+        <v>1992.71</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>27.84</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1405,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>706.45</v>
+        <v>696.25</v>
       </c>
       <c r="D6">
-        <v>0.24</v>
+        <v>-1.44</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1417,46 +1388,46 @@
         <v>689.55</v>
       </c>
       <c r="G6">
-        <v>-35.18</v>
+        <v>-36.11</v>
       </c>
       <c r="H6">
-        <v>2.45</v>
+        <v>0.97</v>
       </c>
       <c r="I6">
-        <v>0.79</v>
+        <v>0.1</v>
       </c>
       <c r="J6">
-        <v>-11.17</v>
+        <v>-13.54</v>
       </c>
       <c r="K6">
-        <v>-1.05</v>
+        <v>-3.4</v>
       </c>
       <c r="L6">
-        <v>-33.8</v>
+        <v>-35.13</v>
       </c>
       <c r="M6">
-        <v>12.14</v>
+        <v>11.99</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="P6">
-        <v>699.54</v>
+        <v>699.6799999999999</v>
       </c>
       <c r="Q6">
-        <v>735.83</v>
+        <v>730.67</v>
       </c>
       <c r="R6">
-        <v>765.97</v>
+        <v>764.65</v>
       </c>
       <c r="S6">
-        <v>828.72</v>
+        <v>826.99</v>
       </c>
       <c r="T6">
-        <v>-14.75</v>
+        <v>-15.81</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1471,34 +1442,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>36.52</v>
+        <v>33.49</v>
       </c>
       <c r="Z6">
-        <v>-22.62</v>
+        <v>-22.29</v>
       </c>
       <c r="AA6">
-        <v>-20.41</v>
+        <v>-20.79</v>
       </c>
       <c r="AB6">
-        <v>-2.2</v>
+        <v>-1.5</v>
       </c>
       <c r="AC6">
-        <v>39.02</v>
+        <v>55.8</v>
       </c>
       <c r="AD6">
-        <v>22.85</v>
+        <v>39.15</v>
       </c>
       <c r="AE6">
-        <v>20.5</v>
+        <v>20.35</v>
       </c>
       <c r="AF6">
-        <v>-11.01</v>
+        <v>-28.54</v>
       </c>
       <c r="AG6">
-        <v>817.0599999999999</v>
+        <v>807.91</v>
       </c>
       <c r="AH6">
-        <v>654.59</v>
+        <v>653.4299999999999</v>
       </c>
       <c r="AI6">
         <v>757.9400000000001</v>
@@ -1507,7 +1478,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>45.31</v>
+        <v>45.04</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1518,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2929.4</v>
+        <v>2926.4</v>
       </c>
       <c r="D7">
-        <v>-2.46</v>
+        <v>-0.1</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1530,46 +1501,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-15.21</v>
+        <v>-15.3</v>
       </c>
       <c r="H7">
-        <v>54.88</v>
+        <v>54.72</v>
       </c>
       <c r="I7">
-        <v>-3.75</v>
+        <v>-1.9</v>
       </c>
       <c r="J7">
-        <v>-11.98</v>
+        <v>-11.12</v>
       </c>
       <c r="K7">
-        <v>14.21</v>
+        <v>14.6</v>
       </c>
       <c r="L7">
-        <v>19.76</v>
+        <v>21.92</v>
       </c>
       <c r="M7">
-        <v>29.12</v>
+        <v>29.41</v>
       </c>
       <c r="N7">
         <v>85</v>
       </c>
       <c r="O7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P7">
-        <v>2993.76</v>
+        <v>2982.44</v>
       </c>
       <c r="Q7">
-        <v>3125.83</v>
+        <v>3108.08</v>
       </c>
       <c r="R7">
-        <v>2970.17</v>
+        <v>2977.36</v>
       </c>
       <c r="S7">
-        <v>2491.65</v>
+        <v>2495.3</v>
       </c>
       <c r="T7">
-        <v>17.57</v>
+        <v>17.28</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1584,43 +1555,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>38.56</v>
+        <v>38.37</v>
       </c>
       <c r="Z7">
-        <v>-17.71</v>
+        <v>-26.23</v>
       </c>
       <c r="AA7">
-        <v>20.08</v>
+        <v>10.82</v>
       </c>
       <c r="AB7">
-        <v>-37.79</v>
+        <v>-37.05</v>
       </c>
       <c r="AC7">
-        <v>11.41</v>
+        <v>3.8</v>
       </c>
       <c r="AD7">
-        <v>13.31</v>
+        <v>10.46</v>
       </c>
       <c r="AE7">
-        <v>127.97</v>
+        <v>123.53</v>
       </c>
       <c r="AF7">
-        <v>-50.45</v>
+        <v>-31.27</v>
       </c>
       <c r="AG7">
-        <v>3340.84</v>
+        <v>3327.56</v>
       </c>
       <c r="AH7">
-        <v>2910.83</v>
+        <v>2888.6</v>
       </c>
       <c r="AI7">
-        <v>3342.65</v>
+        <v>3318.15</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>21.63</v>
+        <v>23.01</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1631,58 +1602,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8459</v>
+        <v>8395</v>
       </c>
       <c r="D8">
-        <v>-2.16</v>
+        <v>-0.76</v>
       </c>
       <c r="E8">
-        <v>9238.98</v>
+        <v>9108.879999999999</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-8.44</v>
+        <v>-7.84</v>
       </c>
       <c r="H8">
-        <v>42.78</v>
+        <v>41.7</v>
       </c>
       <c r="I8">
-        <v>-2.1</v>
+        <v>-2.69</v>
       </c>
       <c r="J8">
-        <v>0.99</v>
+        <v>1.84</v>
       </c>
       <c r="K8">
-        <v>2.58</v>
+        <v>3.6</v>
       </c>
       <c r="L8">
-        <v>-9.94</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="M8">
-        <v>14.87</v>
+        <v>14.71</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="P8">
-        <v>8587.200000000001</v>
+        <v>8540.799999999999</v>
       </c>
       <c r="Q8">
-        <v>8477.9</v>
+        <v>8489.120000000001</v>
       </c>
       <c r="R8">
-        <v>8218.6</v>
+        <v>8234.92</v>
       </c>
       <c r="S8">
-        <v>7439.96</v>
+        <v>7441.47</v>
       </c>
       <c r="T8">
-        <v>13.7</v>
+        <v>12.81</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1697,34 +1668,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>50.82</v>
+        <v>48.9</v>
       </c>
       <c r="Z8">
-        <v>123.27</v>
+        <v>100.62</v>
       </c>
       <c r="AA8">
-        <v>145.18</v>
+        <v>136.27</v>
       </c>
       <c r="AB8">
-        <v>-21.91</v>
+        <v>-35.65</v>
       </c>
       <c r="AC8">
-        <v>13.23</v>
+        <v>10.18</v>
       </c>
       <c r="AD8">
-        <v>26.92</v>
+        <v>17.62</v>
       </c>
       <c r="AE8">
-        <v>300.47</v>
+        <v>301.22</v>
       </c>
       <c r="AF8">
-        <v>-66.27</v>
+        <v>-44.26</v>
       </c>
       <c r="AG8">
-        <v>8972.870000000001</v>
+        <v>8964.540000000001</v>
       </c>
       <c r="AH8">
-        <v>7982.93</v>
+        <v>8013.71</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
@@ -1733,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>42.82</v>
+        <v>38.36</v>
       </c>
     </row>
   </sheetData>
@@ -1874,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1914,7 +1885,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1932,1008 +1903,988 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>13.11</v>
+      </c>
+      <c r="D7" s="6">
+        <v>7.49</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-5.62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-3.66</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-3.48</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-12.86</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-12.65</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-1.52</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-6.31</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-4.79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-11.17</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-13.54</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-2.37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-11.98</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-11.12</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.99</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1.84</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>15.63</v>
-      </c>
-      <c r="D8" s="7">
-        <v>13.11</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-2.52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>5.84</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-0.89</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-6.73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>2.42</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-3.66</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-6.08</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-4.95</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-4.25</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-11</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-12.86</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-7.36</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-7.49</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0.73</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-1.52</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-2.15</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-7.82</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-5.67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-11.5</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-11.17</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>0.79</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-11.32</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-11.98</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3.75</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-1.9</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>6.11</v>
-      </c>
-      <c r="D14" s="7">
-        <v>0.99</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-5.12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-2.1</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-2.69</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>13.71</v>
-      </c>
-      <c r="D15" s="7">
-        <v>5.84</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-7.87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>28.62</v>
+      </c>
+      <c r="D21" s="6">
+        <v>25.93</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-2.69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-0.67</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-4.95</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-4.28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>12.08</v>
+      </c>
+      <c r="D22" s="6">
+        <v>11.67</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-7.63</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-7.36</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.72</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-0.1</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1.78</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-2.15</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-15.48</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-19.31</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-3.83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>0.58</v>
-      </c>
-      <c r="D19" s="7">
-        <v>0.79</v>
-      </c>
-      <c r="E19" s="9">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-33.8</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-35.13</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-1.66</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-3.75</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-2.09</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>19.76</v>
+      </c>
+      <c r="D26" s="6">
+        <v>21.92</v>
+      </c>
+      <c r="E26" s="8">
+        <v>2.16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1.39</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-2.1</v>
-      </c>
-      <c r="E21" s="8">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-9.94</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-9.130000000000001</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>5.91</v>
+      </c>
+      <c r="D28" s="6">
+        <v>3.14</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-2.77</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-9.15</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-12.13</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-2.98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-8.69</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-9.76</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-5.28</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-10.05</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-4.77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-1.05</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-3.4</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>14.21</v>
+      </c>
+      <c r="D33" s="6">
+        <v>14.6</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>2.58</v>
+      </c>
+      <c r="D34" s="6">
+        <v>3.6</v>
+      </c>
+      <c r="E34" s="8">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-3.76</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-7.4</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-3.64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-11.42</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-12.13</v>
+      </c>
+      <c r="E36" s="7">
         <v>-0.71</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-15.76</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-16.12</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-20.83</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-25.26</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-4.43</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-35.18</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-36.11</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-15.21</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-15.3</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-8.44</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-7.84</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>34.65</v>
-      </c>
-      <c r="D22" s="7">
-        <v>28.62</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-6.03</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1247.8</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1200.5</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-47.3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>15.29</v>
-      </c>
-      <c r="D23" s="7">
-        <v>12.08</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-3.21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>865</v>
+      </c>
+      <c r="D43" s="6">
+        <v>858.05</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-6.95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>2.08</v>
-      </c>
-      <c r="D24" s="7">
-        <v>0.72</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>1634.2</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1627.3</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-6.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-13.26</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-15.48</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-2.22</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1899.1</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1792.9</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-106.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-34.41</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-33.8</v>
-      </c>
-      <c r="E26" s="9">
-        <v>0.61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>706.45</v>
+      </c>
+      <c r="D46" s="6">
+        <v>696.25</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-10.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>22.03</v>
-      </c>
-      <c r="D27" s="7">
-        <v>19.76</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>2929.4</v>
+      </c>
+      <c r="D47" s="6">
+        <v>2926.4</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-8.279999999999999</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-9.94</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>8459</v>
+      </c>
+      <c r="D48" s="6">
+        <v>8395</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>7.27</v>
-      </c>
-      <c r="D29" s="7">
-        <v>5.91</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.36</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>63.77</v>
+      </c>
+      <c r="D49" s="6">
+        <v>56.21</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-7.56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-7.35</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-9.15</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>43.58</v>
+      </c>
+      <c r="D50" s="6">
+        <v>41.97</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-1.61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-6.27</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-8.69</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-2.42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>27.51</v>
+      </c>
+      <c r="D51" s="6">
+        <v>26.95</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>2.61</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-5.28</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-7.89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>40.41</v>
+      </c>
+      <c r="D52" s="6">
+        <v>30.15</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-10.26</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-1.3</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-1.05</v>
-      </c>
-      <c r="E33" s="9">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>36.52</v>
+      </c>
+      <c r="D53" s="6">
+        <v>33.49</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-3.03</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>14.75</v>
-      </c>
-      <c r="D34" s="7">
-        <v>14.21</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>38.56</v>
+      </c>
+      <c r="D54" s="6">
+        <v>38.37</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>9.640000000000001</v>
-      </c>
-      <c r="D35" s="7">
-        <v>2.58</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-7.06</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>50.82</v>
+      </c>
+      <c r="D55" s="6">
+        <v>48.9</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-1.39</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-3.76</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-2.37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>-59.53</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-52.1</v>
+      </c>
+      <c r="E56" s="8">
+        <v>7.43</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-9.27</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-11.42</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>-27.45</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="E57" s="8">
+        <v>17.9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-14.29</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-15.76</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-1.47</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>-18.64</v>
+      </c>
+      <c r="D58" s="6">
+        <v>0.47</v>
+      </c>
+      <c r="E58" s="8">
+        <v>19.11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-18.13</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-20.83</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-2.7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>-51.97</v>
+      </c>
+      <c r="D59" s="6">
+        <v>214.23</v>
+      </c>
+      <c r="E59" s="8">
+        <v>266.2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-35.33</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-35.18</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-11.01</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-28.54</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-17.53</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-13.07</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-15.21</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-50.45</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-31.27</v>
+      </c>
+      <c r="E61" s="8">
+        <v>19.18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-7.95</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-8.44</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-0.49</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>1278.5</v>
-      </c>
-      <c r="D43" s="7">
-        <v>1247.8</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-30.7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="7">
-        <v>886</v>
-      </c>
-      <c r="D44" s="7">
-        <v>865</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-21</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>1662.7</v>
-      </c>
-      <c r="D45" s="7">
-        <v>1634.2</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-28.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>1963.9</v>
-      </c>
-      <c r="D46" s="7">
-        <v>1899.1</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-64.8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>704.75</v>
-      </c>
-      <c r="D47" s="7">
-        <v>706.45</v>
-      </c>
-      <c r="E47" s="9">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>3003.4</v>
-      </c>
-      <c r="D48" s="7">
-        <v>2929.4</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-74</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>8646</v>
-      </c>
-      <c r="D49" s="7">
-        <v>8459</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-187</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="7">
-        <v>69.39</v>
-      </c>
-      <c r="D50" s="7">
-        <v>63.77</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-5.62</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="7">
-        <v>48.85</v>
-      </c>
-      <c r="D51" s="7">
-        <v>43.58</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-5.27</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="7">
-        <v>29.86</v>
-      </c>
-      <c r="D52" s="7">
-        <v>27.51</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-2.35</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="7">
-        <v>50.07</v>
-      </c>
-      <c r="D53" s="7">
-        <v>40.41</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-9.66</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>35.62</v>
-      </c>
-      <c r="D54" s="7">
-        <v>36.52</v>
-      </c>
-      <c r="E54" s="9">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>43.61</v>
-      </c>
-      <c r="D55" s="7">
-        <v>38.56</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-5.05</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>56.87</v>
-      </c>
-      <c r="D56" s="7">
-        <v>50.82</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-6.05</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="7">
-        <v>-37.3</v>
-      </c>
-      <c r="D57" s="7">
-        <v>-59.53</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-22.23</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="7">
-        <v>-62.74</v>
-      </c>
-      <c r="D58" s="7">
-        <v>-27.45</v>
-      </c>
-      <c r="E58" s="9">
-        <v>35.29</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="7">
-        <v>106.25</v>
-      </c>
-      <c r="D59" s="7">
-        <v>-18.64</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-124.89</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="7">
-        <v>-62.9</v>
-      </c>
-      <c r="D60" s="7">
-        <v>-51.97</v>
-      </c>
-      <c r="E60" s="9">
-        <v>10.93</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="7">
-        <v>-12.99</v>
-      </c>
-      <c r="D61" s="7">
-        <v>-11.01</v>
-      </c>
-      <c r="E61" s="9">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>-22.88</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-50.45</v>
+      <c r="C62" s="6">
+        <v>-66.27</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-44.26</v>
       </c>
       <c r="E62" s="8">
-        <v>-27.57</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-49.54</v>
-      </c>
-      <c r="D63" s="7">
-        <v>-66.27</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-16.73</v>
+        <v>22.01</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2953,60 +2904,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>56.8</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>43</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>39.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F2" s="12">
-        <v>-3.9</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-0.2</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-5.4</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-2</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>60</v>
       </c>
     </row>
@@ -3108,49 +3059,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.5101</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.2912</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2435</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.199</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1487</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1214</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0794</v>
+      <c r="A2" s="14">
+        <v>0.4931</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2941</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2342</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1858</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1471</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1199</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0701</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,34 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.8 → 48.9</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.8</t>
-  </si>
-  <si>
-    <t>48.9</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,15 +374,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -924,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1200.5</v>
+        <v>1252.5</v>
       </c>
       <c r="D2">
-        <v>-3.79</v>
+        <v>4.33</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -936,46 +908,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-7.4</v>
+        <v>-3.39</v>
       </c>
       <c r="H2">
-        <v>60.42</v>
+        <v>67.37</v>
       </c>
       <c r="I2">
-        <v>-0.89</v>
+        <v>-0.95</v>
       </c>
       <c r="J2">
-        <v>7.49</v>
+        <v>13.18</v>
       </c>
       <c r="K2">
-        <v>3.14</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L2">
-        <v>25.93</v>
+        <v>31.95</v>
       </c>
       <c r="M2">
-        <v>7.01</v>
+        <v>7.48</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="P2">
-        <v>1257.56</v>
+        <v>1255.16</v>
       </c>
       <c r="Q2">
-        <v>1140.47</v>
+        <v>1148.07</v>
       </c>
       <c r="R2">
-        <v>1118</v>
+        <v>1121.36</v>
       </c>
       <c r="S2">
-        <v>972.4</v>
+        <v>974.33</v>
       </c>
       <c r="T2">
-        <v>23.46</v>
+        <v>28.55</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +962,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>56.21</v>
+        <v>61.6</v>
       </c>
       <c r="Z2">
-        <v>37.89</v>
+        <v>39.75</v>
       </c>
       <c r="AA2">
-        <v>23.07</v>
+        <v>26.4</v>
       </c>
       <c r="AB2">
-        <v>14.82</v>
+        <v>13.35</v>
       </c>
       <c r="AC2">
-        <v>72.54000000000001</v>
+        <v>65.23</v>
       </c>
       <c r="AD2">
-        <v>85.81</v>
+        <v>75.31</v>
       </c>
       <c r="AE2">
-        <v>54.28</v>
+        <v>55.36</v>
       </c>
       <c r="AF2">
-        <v>-52.1</v>
+        <v>-19.97</v>
       </c>
       <c r="AG2">
-        <v>1303.47</v>
+        <v>1317.28</v>
       </c>
       <c r="AH2">
-        <v>977.47</v>
+        <v>978.86</v>
       </c>
       <c r="AI2">
         <v>1148.32</v>
@@ -1026,7 +998,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>45.65</v>
+        <v>44.68</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>858.05</v>
+        <v>854.2</v>
       </c>
       <c r="D3">
-        <v>-0.8</v>
+        <v>-0.45</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1049,46 +1021,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-12.13</v>
+        <v>-12.52</v>
       </c>
       <c r="H3">
-        <v>62.06</v>
+        <v>61.33</v>
       </c>
       <c r="I3">
-        <v>-4.25</v>
+        <v>-4.56</v>
       </c>
       <c r="J3">
-        <v>-3.48</v>
+        <v>-6.75</v>
       </c>
       <c r="K3">
-        <v>-12.13</v>
+        <v>-10.97</v>
       </c>
       <c r="L3">
-        <v>11.67</v>
+        <v>12.78</v>
       </c>
       <c r="M3">
-        <v>49.31</v>
+        <v>47.72</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>878.15</v>
+        <v>869.99</v>
       </c>
       <c r="Q3">
-        <v>889.1900000000001</v>
+        <v>887.63</v>
       </c>
       <c r="R3">
-        <v>882.17</v>
+        <v>880.96</v>
       </c>
       <c r="S3">
-        <v>792.77</v>
+        <v>793.72</v>
       </c>
       <c r="T3">
-        <v>8.23</v>
+        <v>7.62</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1103,34 +1075,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>41.97</v>
+        <v>41.06</v>
       </c>
       <c r="Z3">
-        <v>-3.68</v>
+        <v>-5.65</v>
       </c>
       <c r="AA3">
-        <v>-0.2</v>
+        <v>-1.29</v>
       </c>
       <c r="AB3">
-        <v>-3.48</v>
+        <v>-4.36</v>
       </c>
       <c r="AC3">
-        <v>21.58</v>
+        <v>8.31</v>
       </c>
       <c r="AD3">
-        <v>34.07</v>
+        <v>21.22</v>
       </c>
       <c r="AE3">
-        <v>24.05</v>
+        <v>23.95</v>
       </c>
       <c r="AF3">
-        <v>-9.550000000000001</v>
+        <v>-0.59</v>
       </c>
       <c r="AG3">
-        <v>929.47</v>
+        <v>930.84</v>
       </c>
       <c r="AH3">
-        <v>848.91</v>
+        <v>844.42</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1139,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>21.87</v>
+        <v>22.28</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1627.3</v>
+        <v>1620</v>
       </c>
       <c r="D4">
-        <v>-0.42</v>
+        <v>-0.45</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1162,46 +1134,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-16.12</v>
+        <v>-16.49</v>
       </c>
       <c r="H4">
-        <v>20.12</v>
+        <v>19.58</v>
       </c>
       <c r="I4">
-        <v>-7.49</v>
+        <v>-8.68</v>
       </c>
       <c r="J4">
-        <v>-12.65</v>
+        <v>-12.78</v>
       </c>
       <c r="K4">
-        <v>-9.76</v>
+        <v>-9.42</v>
       </c>
       <c r="L4">
-        <v>-0.1</v>
+        <v>1.78</v>
       </c>
       <c r="M4">
-        <v>23.42</v>
+        <v>23.71</v>
       </c>
       <c r="N4">
         <v>43</v>
       </c>
       <c r="O4">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="P4">
-        <v>1675.98</v>
+        <v>1645.18</v>
       </c>
       <c r="Q4">
-        <v>1777.95</v>
+        <v>1768.22</v>
       </c>
       <c r="R4">
-        <v>1820.95</v>
+        <v>1818.17</v>
       </c>
       <c r="S4">
-        <v>1682.3</v>
+        <v>1681.81</v>
       </c>
       <c r="T4">
-        <v>-3.27</v>
+        <v>-3.67</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1216,43 +1188,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>26.95</v>
+        <v>26.35</v>
       </c>
       <c r="Z4">
-        <v>-48.68</v>
+        <v>-53.32</v>
       </c>
       <c r="AA4">
-        <v>-29.05</v>
+        <v>-33.91</v>
       </c>
       <c r="AB4">
-        <v>-19.62</v>
+        <v>-19.42</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>49.14</v>
+        <v>48.63</v>
       </c>
       <c r="AF4">
-        <v>0.47</v>
+        <v>23</v>
       </c>
       <c r="AG4">
-        <v>1923.59</v>
+        <v>1928.77</v>
       </c>
       <c r="AH4">
-        <v>1632.32</v>
+        <v>1607.67</v>
       </c>
       <c r="AI4">
-        <v>1769.53</v>
+        <v>1767</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>45.06</v>
+        <v>49.35</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1792.9</v>
+        <v>1758.2</v>
       </c>
       <c r="D5">
-        <v>-5.59</v>
+        <v>-1.94</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1275,46 +1247,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-25.26</v>
+        <v>-26.7</v>
       </c>
       <c r="H5">
-        <v>2.71</v>
+        <v>0.72</v>
       </c>
       <c r="I5">
-        <v>-7.82</v>
+        <v>-10.11</v>
       </c>
       <c r="J5">
-        <v>-6.31</v>
+        <v>-7.75</v>
       </c>
       <c r="K5">
-        <v>-10.05</v>
+        <v>-12.37</v>
       </c>
       <c r="L5">
-        <v>-19.31</v>
+        <v>-21.15</v>
       </c>
       <c r="M5">
-        <v>18.58</v>
+        <v>18.2</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="P5">
-        <v>1910.88</v>
+        <v>1871.32</v>
       </c>
       <c r="Q5">
-        <v>1936.66</v>
+        <v>1928.43</v>
       </c>
       <c r="R5">
-        <v>1993.44</v>
+        <v>1987.52</v>
       </c>
       <c r="S5">
-        <v>2062.71</v>
+        <v>2060.3</v>
       </c>
       <c r="T5">
-        <v>-13.08</v>
+        <v>-14.66</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,43 +1301,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>30.15</v>
+        <v>27.67</v>
       </c>
       <c r="Z5">
-        <v>-25</v>
+        <v>-36.11</v>
       </c>
       <c r="AA5">
-        <v>-17.17</v>
+        <v>-20.96</v>
       </c>
       <c r="AB5">
-        <v>-7.82</v>
+        <v>-15.15</v>
       </c>
       <c r="AC5">
-        <v>20.76</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>34.79</v>
+        <v>17.76</v>
       </c>
       <c r="AE5">
-        <v>52.2</v>
+        <v>54.84</v>
       </c>
       <c r="AF5">
-        <v>214.23</v>
+        <v>367.36</v>
       </c>
       <c r="AG5">
-        <v>2017.51</v>
+        <v>2042.07</v>
       </c>
       <c r="AH5">
-        <v>1855.81</v>
+        <v>1814.78</v>
       </c>
       <c r="AI5">
-        <v>1992.71</v>
+        <v>1951.96</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>30.07</v>
+        <v>32.85</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,58 +1348,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>696.25</v>
+        <v>685.9</v>
       </c>
       <c r="D6">
-        <v>-1.44</v>
+        <v>-1.49</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
       </c>
       <c r="F6">
-        <v>689.55</v>
+        <v>685.9</v>
       </c>
       <c r="G6">
-        <v>-36.11</v>
+        <v>-37.06</v>
       </c>
       <c r="H6">
-        <v>0.97</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.1</v>
+        <v>-2.21</v>
       </c>
       <c r="J6">
-        <v>-13.54</v>
+        <v>-14.2</v>
       </c>
       <c r="K6">
-        <v>-3.4</v>
+        <v>-6.71</v>
       </c>
       <c r="L6">
-        <v>-35.13</v>
+        <v>-35.4</v>
       </c>
       <c r="M6">
-        <v>11.99</v>
+        <v>11.37</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="P6">
-        <v>699.6799999999999</v>
+        <v>696.58</v>
       </c>
       <c r="Q6">
-        <v>730.67</v>
+        <v>725.1900000000001</v>
       </c>
       <c r="R6">
-        <v>764.65</v>
+        <v>763.01</v>
       </c>
       <c r="S6">
-        <v>826.99</v>
+        <v>825.27</v>
       </c>
       <c r="T6">
-        <v>-15.81</v>
+        <v>-16.89</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1442,43 +1414,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>33.49</v>
+        <v>30.71</v>
       </c>
       <c r="Z6">
-        <v>-22.29</v>
+        <v>-22.61</v>
       </c>
       <c r="AA6">
-        <v>-20.79</v>
+        <v>-21.15</v>
       </c>
       <c r="AB6">
-        <v>-1.5</v>
+        <v>-1.46</v>
       </c>
       <c r="AC6">
-        <v>55.8</v>
+        <v>54.45</v>
       </c>
       <c r="AD6">
-        <v>39.15</v>
+        <v>49.75</v>
       </c>
       <c r="AE6">
-        <v>20.35</v>
+        <v>20.83</v>
       </c>
       <c r="AF6">
-        <v>-28.54</v>
+        <v>26</v>
       </c>
       <c r="AG6">
-        <v>807.91</v>
+        <v>798.49</v>
       </c>
       <c r="AH6">
-        <v>653.4299999999999</v>
+        <v>651.88</v>
       </c>
       <c r="AI6">
-        <v>757.9400000000001</v>
+        <v>756.98</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>45.04</v>
+        <v>46.2</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2926.4</v>
+        <v>2900.9</v>
       </c>
       <c r="D7">
-        <v>-0.1</v>
+        <v>-0.87</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1501,22 +1473,22 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-15.3</v>
+        <v>-16.04</v>
       </c>
       <c r="H7">
-        <v>54.72</v>
+        <v>53.37</v>
       </c>
       <c r="I7">
-        <v>-1.9</v>
+        <v>-3.94</v>
       </c>
       <c r="J7">
-        <v>-11.12</v>
+        <v>-11.6</v>
       </c>
       <c r="K7">
-        <v>14.6</v>
+        <v>15.24</v>
       </c>
       <c r="L7">
-        <v>21.92</v>
+        <v>22.65</v>
       </c>
       <c r="M7">
         <v>29.41</v>
@@ -1525,22 +1497,22 @@
         <v>85</v>
       </c>
       <c r="O7">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P7">
-        <v>2982.44</v>
+        <v>2958.64</v>
       </c>
       <c r="Q7">
-        <v>3108.08</v>
+        <v>3089.75</v>
       </c>
       <c r="R7">
-        <v>2977.36</v>
+        <v>2982.85</v>
       </c>
       <c r="S7">
-        <v>2495.3</v>
+        <v>2498.88</v>
       </c>
       <c r="T7">
-        <v>17.28</v>
+        <v>16.09</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1555,43 +1527,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>38.37</v>
+        <v>36.68</v>
       </c>
       <c r="Z7">
-        <v>-26.23</v>
+        <v>-34.65</v>
       </c>
       <c r="AA7">
-        <v>10.82</v>
+        <v>1.72</v>
       </c>
       <c r="AB7">
-        <v>-37.05</v>
+        <v>-36.37</v>
       </c>
       <c r="AC7">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>10.46</v>
+        <v>5.07</v>
       </c>
       <c r="AE7">
-        <v>123.53</v>
+        <v>123.48</v>
       </c>
       <c r="AF7">
-        <v>-31.27</v>
+        <v>-13.71</v>
       </c>
       <c r="AG7">
-        <v>3327.56</v>
+        <v>3314.35</v>
       </c>
       <c r="AH7">
-        <v>2888.6</v>
+        <v>2865.15</v>
       </c>
       <c r="AI7">
-        <v>3318.15</v>
+        <v>3294.14</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>23.01</v>
+        <v>25.82</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8395</v>
+        <v>8351.5</v>
       </c>
       <c r="D8">
-        <v>-0.76</v>
+        <v>-0.52</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1614,46 +1586,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-7.84</v>
+        <v>-8.31</v>
       </c>
       <c r="H8">
-        <v>41.7</v>
+        <v>40.97</v>
       </c>
       <c r="I8">
-        <v>-2.69</v>
+        <v>-3.77</v>
       </c>
       <c r="J8">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="K8">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="L8">
-        <v>-9.130000000000001</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="M8">
-        <v>14.71</v>
+        <v>14.68</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P8">
-        <v>8540.799999999999</v>
+        <v>8475.4</v>
       </c>
       <c r="Q8">
-        <v>8489.120000000001</v>
+        <v>8501.450000000001</v>
       </c>
       <c r="R8">
-        <v>8234.92</v>
+        <v>8250.709999999999</v>
       </c>
       <c r="S8">
-        <v>7441.47</v>
+        <v>7441.81</v>
       </c>
       <c r="T8">
-        <v>12.81</v>
+        <v>12.22</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1668,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>48.9</v>
+        <v>47.58</v>
       </c>
       <c r="Z8">
-        <v>100.62</v>
+        <v>78.25</v>
       </c>
       <c r="AA8">
-        <v>136.27</v>
+        <v>124.67</v>
       </c>
       <c r="AB8">
-        <v>-35.65</v>
+        <v>-46.41</v>
       </c>
       <c r="AC8">
-        <v>10.18</v>
+        <v>0</v>
       </c>
       <c r="AD8">
-        <v>17.62</v>
+        <v>7.8</v>
       </c>
       <c r="AE8">
-        <v>301.22</v>
+        <v>303.2</v>
       </c>
       <c r="AF8">
-        <v>-44.26</v>
+        <v>-58.12</v>
       </c>
       <c r="AG8">
-        <v>8964.540000000001</v>
+        <v>8946.76</v>
       </c>
       <c r="AH8">
-        <v>8013.71</v>
+        <v>8056.14</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
@@ -1704,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>38.36</v>
+        <v>33.46</v>
       </c>
     </row>
   </sheetData>
@@ -1865,47 +1837,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1913,972 +1850,972 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
+      <c r="B6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>13.11</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>7.49</v>
       </c>
-      <c r="E7" s="7">
-        <v>-5.62</v>
+      <c r="D7" s="5">
+        <v>13.18</v>
+      </c>
+      <c r="E7" s="6">
+        <v>5.69</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-3.66</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-3.48</v>
       </c>
-      <c r="E8" s="8">
-        <v>0.18</v>
+      <c r="D8" s="5">
+        <v>-6.75</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-3.27</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-12.86</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-12.65</v>
       </c>
-      <c r="E9" s="8">
-        <v>0.21</v>
+      <c r="D9" s="5">
+        <v>-12.78</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-1.52</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-6.31</v>
       </c>
+      <c r="D10" s="5">
+        <v>-7.75</v>
+      </c>
       <c r="E10" s="7">
-        <v>-4.79</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-11.17</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-13.54</v>
       </c>
+      <c r="D11" s="5">
+        <v>-14.2</v>
+      </c>
       <c r="E11" s="7">
-        <v>-2.37</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-11.98</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-11.12</v>
       </c>
-      <c r="E12" s="8">
-        <v>0.86</v>
+      <c r="D12" s="5">
+        <v>-11.6</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
+        <v>1.84</v>
+      </c>
+      <c r="D13" s="5">
+        <v>2.22</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-0.89</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-0.95</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-4.25</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-4.56</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-7.49</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-8.68</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-7.82</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-10.11</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.1</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-2.21</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-1.9</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-3.94</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.04</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-2.69</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-3.77</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>25.93</v>
+      </c>
+      <c r="D21" s="5">
+        <v>31.95</v>
+      </c>
+      <c r="E21" s="6">
+        <v>6.02</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>11.67</v>
+      </c>
+      <c r="D22" s="5">
+        <v>12.78</v>
+      </c>
+      <c r="E22" s="6">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-0.1</v>
+      </c>
+      <c r="D23" s="5">
+        <v>1.78</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-19.31</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-21.15</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-35.13</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-35.4</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>21.92</v>
+      </c>
+      <c r="D26" s="5">
+        <v>22.65</v>
+      </c>
+      <c r="E26" s="6">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-9.130000000000001</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-8.140000000000001</v>
+      </c>
+      <c r="E27" s="6">
         <v>0.99</v>
       </c>
-      <c r="D13" s="6">
-        <v>1.84</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>5.84</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.89</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-6.73</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>3.14</v>
+      </c>
+      <c r="D28" s="5">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="E28" s="6">
+        <v>6.56</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-4.95</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-4.25</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-12.13</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-10.97</v>
+      </c>
+      <c r="E29" s="6">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-7.36</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-7.49</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-9.76</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-9.42</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-2.15</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-7.82</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-5.67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-10.05</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-12.37</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-2.32</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>0.79</v>
-      </c>
-      <c r="D18" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-3.4</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-6.71</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-3.31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-3.75</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.9</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>14.6</v>
+      </c>
+      <c r="D33" s="5">
+        <v>15.24</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-2.1</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-2.69</v>
-      </c>
-      <c r="E20" s="7">
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>3.6</v>
+      </c>
+      <c r="D34" s="5">
+        <v>2.97</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-7.4</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-3.39</v>
+      </c>
+      <c r="E35" s="6">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-12.13</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-12.52</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-16.12</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-16.49</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-25.26</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-26.7</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-36.11</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-37.06</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-15.3</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-16.04</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-7.84</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-8.31</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1200.5</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1252.5</v>
+      </c>
+      <c r="E42" s="6">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>858.05</v>
+      </c>
+      <c r="D43" s="5">
+        <v>854.2</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-3.85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1627.3</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1620</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-7.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1792.9</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1758.2</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-34.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>696.25</v>
+      </c>
+      <c r="D46" s="5">
+        <v>685.9</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-10.35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>2926.4</v>
+      </c>
+      <c r="D47" s="5">
+        <v>2900.9</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-25.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>8395</v>
+      </c>
+      <c r="D48" s="5">
+        <v>8351.5</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-43.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>56.21</v>
+      </c>
+      <c r="D49" s="5">
+        <v>61.6</v>
+      </c>
+      <c r="E49" s="6">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>41.97</v>
+      </c>
+      <c r="D50" s="5">
+        <v>41.06</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>26.95</v>
+      </c>
+      <c r="D51" s="5">
+        <v>26.35</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>30.15</v>
+      </c>
+      <c r="D52" s="5">
+        <v>27.67</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-2.48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>33.49</v>
+      </c>
+      <c r="D53" s="5">
+        <v>30.71</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-2.78</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>38.37</v>
+      </c>
+      <c r="D54" s="5">
+        <v>36.68</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>48.9</v>
+      </c>
+      <c r="D55" s="5">
+        <v>47.58</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
+        <v>-52.1</v>
+      </c>
+      <c r="D56" s="5">
+        <v>-19.97</v>
+      </c>
+      <c r="E56" s="6">
+        <v>32.13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5">
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="D57" s="5">
         <v>-0.59</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>28.62</v>
-      </c>
-      <c r="D21" s="6">
-        <v>25.93</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-2.69</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>12.08</v>
-      </c>
-      <c r="D22" s="6">
-        <v>11.67</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="E57" s="6">
+        <v>8.960000000000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>0.72</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-0.1</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.82</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>0.47</v>
+      </c>
+      <c r="D58" s="5">
+        <v>23</v>
+      </c>
+      <c r="E58" s="6">
+        <v>22.53</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-15.48</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-19.31</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-3.83</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>214.23</v>
+      </c>
+      <c r="D59" s="5">
+        <v>367.36</v>
+      </c>
+      <c r="E59" s="6">
+        <v>153.13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-33.8</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-35.13</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-28.54</v>
+      </c>
+      <c r="D60" s="5">
+        <v>26</v>
+      </c>
+      <c r="E60" s="6">
+        <v>54.54</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>19.76</v>
-      </c>
-      <c r="D26" s="6">
-        <v>21.92</v>
-      </c>
-      <c r="E26" s="8">
-        <v>2.16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-31.27</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-13.71</v>
+      </c>
+      <c r="E61" s="6">
+        <v>17.56</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-9.94</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-9.130000000000001</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>5.91</v>
-      </c>
-      <c r="D28" s="6">
-        <v>3.14</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-2.77</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-9.15</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-12.13</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-2.98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-8.69</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-9.76</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-5.28</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-10.05</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-4.77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-1.05</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-3.4</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-2.35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>14.21</v>
-      </c>
-      <c r="D33" s="6">
-        <v>14.6</v>
-      </c>
-      <c r="E33" s="8">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>2.58</v>
-      </c>
-      <c r="D34" s="6">
-        <v>3.6</v>
-      </c>
-      <c r="E34" s="8">
-        <v>1.02</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-3.76</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-7.4</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-3.64</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-11.42</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-12.13</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-15.76</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-16.12</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-20.83</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-25.26</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-4.43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-35.18</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-36.11</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.93</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-15.21</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-15.3</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-8.44</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-7.84</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1247.8</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1200.5</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-47.3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>865</v>
-      </c>
-      <c r="D43" s="6">
-        <v>858.05</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-6.95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1634.2</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1627.3</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-6.9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1899.1</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1792.9</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-106.2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>706.45</v>
-      </c>
-      <c r="D46" s="6">
-        <v>696.25</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-10.2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>2929.4</v>
-      </c>
-      <c r="D47" s="6">
-        <v>2926.4</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>8459</v>
-      </c>
-      <c r="D48" s="6">
-        <v>8395</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-64</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>63.77</v>
-      </c>
-      <c r="D49" s="6">
-        <v>56.21</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-7.56</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>43.58</v>
-      </c>
-      <c r="D50" s="6">
-        <v>41.97</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-1.61</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>27.51</v>
-      </c>
-      <c r="D51" s="6">
-        <v>26.95</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>40.41</v>
-      </c>
-      <c r="D52" s="6">
-        <v>30.15</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-10.26</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>36.52</v>
-      </c>
-      <c r="D53" s="6">
-        <v>33.49</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-3.03</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>38.56</v>
-      </c>
-      <c r="D54" s="6">
-        <v>38.37</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>50.82</v>
-      </c>
-      <c r="D55" s="6">
-        <v>48.9</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="5" t="s">
+      <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="6">
-        <v>-59.53</v>
-      </c>
-      <c r="D56" s="6">
-        <v>-52.1</v>
-      </c>
-      <c r="E56" s="8">
-        <v>7.43</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="6">
-        <v>-27.45</v>
-      </c>
-      <c r="D57" s="6">
-        <v>-9.550000000000001</v>
-      </c>
-      <c r="E57" s="8">
-        <v>17.9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="6">
-        <v>-18.64</v>
-      </c>
-      <c r="D58" s="6">
-        <v>0.47</v>
-      </c>
-      <c r="E58" s="8">
-        <v>19.11</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>-51.97</v>
-      </c>
-      <c r="D59" s="6">
-        <v>214.23</v>
-      </c>
-      <c r="E59" s="8">
-        <v>266.2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-11.01</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-28.54</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-17.53</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-50.45</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-31.27</v>
-      </c>
-      <c r="E61" s="8">
-        <v>19.18</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-66.27</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C62" s="5">
         <v>-44.26</v>
       </c>
-      <c r="E62" s="8">
-        <v>22.01</v>
+      <c r="D62" s="5">
+        <v>-58.12</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-13.86</v>
       </c>
     </row>
   </sheetData>
@@ -2904,60 +2841,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>56.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>39.4</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>38.8</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="10">
         <v>-5.4</v>
       </c>
-      <c r="G2" s="11">
-        <v>-2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="G2" s="10">
+        <v>-1.7</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>60</v>
       </c>
     </row>
@@ -3059,49 +2996,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.4931</v>
-      </c>
-      <c r="B2" s="14">
+      <c r="A2" s="13">
+        <v>0.4772</v>
+      </c>
+      <c r="B2" s="13">
         <v>0.2941</v>
       </c>
-      <c r="C2" s="14">
-        <v>0.2342</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1858</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1471</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1199</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0701</v>
+      <c r="C2" s="13">
+        <v>0.2371</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.182</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1468</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.1137</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.07480000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -258,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -298,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -896,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1252.5</v>
+        <v>1239.7</v>
       </c>
       <c r="D2">
-        <v>4.33</v>
+        <v>-1.02</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -908,25 +908,25 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-3.39</v>
+        <v>-4.38</v>
       </c>
       <c r="H2">
-        <v>67.37</v>
+        <v>65.66</v>
       </c>
       <c r="I2">
-        <v>-0.95</v>
+        <v>-4.38</v>
       </c>
       <c r="J2">
-        <v>13.18</v>
+        <v>12.65</v>
       </c>
       <c r="K2">
-        <v>9.699999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L2">
-        <v>31.95</v>
+        <v>35.02</v>
       </c>
       <c r="M2">
-        <v>7.48</v>
+        <v>7.62</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -935,19 +935,19 @@
         <v>84</v>
       </c>
       <c r="P2">
-        <v>1255.16</v>
+        <v>1243.8</v>
       </c>
       <c r="Q2">
-        <v>1148.07</v>
+        <v>1156.48</v>
       </c>
       <c r="R2">
-        <v>1121.36</v>
+        <v>1124.78</v>
       </c>
       <c r="S2">
-        <v>974.33</v>
+        <v>976.16</v>
       </c>
       <c r="T2">
-        <v>28.55</v>
+        <v>27</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,34 +962,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>61.6</v>
+        <v>59.65</v>
       </c>
       <c r="Z2">
-        <v>39.75</v>
+        <v>39.74</v>
       </c>
       <c r="AA2">
-        <v>26.4</v>
+        <v>29.07</v>
       </c>
       <c r="AB2">
-        <v>13.35</v>
+        <v>10.67</v>
       </c>
       <c r="AC2">
-        <v>65.23</v>
+        <v>61.38</v>
       </c>
       <c r="AD2">
-        <v>75.31</v>
+        <v>66.38</v>
       </c>
       <c r="AE2">
-        <v>55.36</v>
+        <v>54.88</v>
       </c>
       <c r="AF2">
-        <v>-19.97</v>
+        <v>-36.84</v>
       </c>
       <c r="AG2">
-        <v>1317.28</v>
+        <v>1326.39</v>
       </c>
       <c r="AH2">
-        <v>978.86</v>
+        <v>986.5700000000001</v>
       </c>
       <c r="AI2">
         <v>1148.32</v>
@@ -998,7 +998,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>44.68</v>
+        <v>43.84</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>854.2</v>
+        <v>879</v>
       </c>
       <c r="D3">
-        <v>-0.45</v>
+        <v>2.9</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1021,46 +1021,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-12.52</v>
+        <v>-9.98</v>
       </c>
       <c r="H3">
-        <v>61.33</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="I3">
-        <v>-4.56</v>
+        <v>-0.87</v>
       </c>
       <c r="J3">
-        <v>-6.75</v>
+        <v>-0.73</v>
       </c>
       <c r="K3">
-        <v>-10.97</v>
+        <v>-1.52</v>
       </c>
       <c r="L3">
-        <v>12.78</v>
+        <v>19.14</v>
       </c>
       <c r="M3">
-        <v>47.72</v>
+        <v>48.26</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="P3">
-        <v>869.99</v>
+        <v>868.45</v>
       </c>
       <c r="Q3">
-        <v>887.63</v>
+        <v>887.6900000000001</v>
       </c>
       <c r="R3">
-        <v>880.96</v>
+        <v>880.28</v>
       </c>
       <c r="S3">
-        <v>793.72</v>
+        <v>794.79</v>
       </c>
       <c r="T3">
-        <v>7.62</v>
+        <v>10.6</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1075,34 +1075,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>41.06</v>
+        <v>48.74</v>
       </c>
       <c r="Z3">
-        <v>-5.65</v>
+        <v>-5.14</v>
       </c>
       <c r="AA3">
-        <v>-1.29</v>
+        <v>-2.06</v>
       </c>
       <c r="AB3">
-        <v>-4.36</v>
+        <v>-3.09</v>
       </c>
       <c r="AC3">
-        <v>8.31</v>
+        <v>22.22</v>
       </c>
       <c r="AD3">
-        <v>21.22</v>
+        <v>17.37</v>
       </c>
       <c r="AE3">
-        <v>23.95</v>
+        <v>24.79</v>
       </c>
       <c r="AF3">
-        <v>-0.59</v>
+        <v>95.06</v>
       </c>
       <c r="AG3">
         <v>930.84</v>
       </c>
       <c r="AH3">
-        <v>844.42</v>
+        <v>844.54</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1111,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>22.28</v>
+        <v>19.87</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1620</v>
+        <v>1580</v>
       </c>
       <c r="D4">
-        <v>-0.45</v>
+        <v>-2.47</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1134,46 +1134,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-16.49</v>
+        <v>-18.56</v>
       </c>
       <c r="H4">
-        <v>19.58</v>
+        <v>16.63</v>
       </c>
       <c r="I4">
-        <v>-8.68</v>
+        <v>-6.05</v>
       </c>
       <c r="J4">
-        <v>-12.78</v>
+        <v>-12.93</v>
       </c>
       <c r="K4">
-        <v>-9.42</v>
+        <v>-11.72</v>
       </c>
       <c r="L4">
-        <v>1.78</v>
+        <v>0.72</v>
       </c>
       <c r="M4">
-        <v>23.71</v>
+        <v>23.34</v>
       </c>
       <c r="N4">
         <v>43</v>
       </c>
       <c r="O4">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="P4">
-        <v>1645.18</v>
+        <v>1624.84</v>
       </c>
       <c r="Q4">
-        <v>1768.22</v>
+        <v>1755.92</v>
       </c>
       <c r="R4">
-        <v>1818.17</v>
+        <v>1815.21</v>
       </c>
       <c r="S4">
-        <v>1681.81</v>
+        <v>1681.03</v>
       </c>
       <c r="T4">
-        <v>-3.67</v>
+        <v>-6.01</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1188,16 +1188,16 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>26.35</v>
+        <v>23.27</v>
       </c>
       <c r="Z4">
-        <v>-53.32</v>
+        <v>-59.55</v>
       </c>
       <c r="AA4">
-        <v>-33.91</v>
+        <v>-39.04</v>
       </c>
       <c r="AB4">
-        <v>-19.42</v>
+        <v>-20.51</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1206,25 +1206,25 @@
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>48.63</v>
+        <v>49.22</v>
       </c>
       <c r="AF4">
-        <v>23</v>
+        <v>10.34</v>
       </c>
       <c r="AG4">
-        <v>1928.77</v>
+        <v>1934.53</v>
       </c>
       <c r="AH4">
-        <v>1607.67</v>
+        <v>1577.32</v>
       </c>
       <c r="AI4">
-        <v>1767</v>
+        <v>1739.1</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>49.35</v>
+        <v>53.75</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1235,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1758.2</v>
+        <v>1763.6</v>
       </c>
       <c r="D5">
-        <v>-1.94</v>
+        <v>0.31</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1247,46 +1247,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-26.7</v>
+        <v>-26.48</v>
       </c>
       <c r="H5">
-        <v>0.72</v>
+        <v>1.03</v>
       </c>
       <c r="I5">
-        <v>-10.11</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="J5">
-        <v>-7.75</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="K5">
-        <v>-12.37</v>
+        <v>-13.31</v>
       </c>
       <c r="L5">
-        <v>-21.15</v>
+        <v>-19.03</v>
       </c>
       <c r="M5">
-        <v>18.2</v>
+        <v>18.11</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="P5">
-        <v>1871.32</v>
+        <v>1835.54</v>
       </c>
       <c r="Q5">
-        <v>1928.43</v>
+        <v>1920.88</v>
       </c>
       <c r="R5">
-        <v>1987.52</v>
+        <v>1982</v>
       </c>
       <c r="S5">
-        <v>2060.3</v>
+        <v>2057.54</v>
       </c>
       <c r="T5">
-        <v>-14.66</v>
+        <v>-14.29</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1301,43 +1301,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>27.67</v>
+        <v>28.65</v>
       </c>
       <c r="Z5">
-        <v>-36.11</v>
+        <v>-43.97</v>
       </c>
       <c r="AA5">
-        <v>-20.96</v>
+        <v>-25.56</v>
       </c>
       <c r="AB5">
-        <v>-15.15</v>
+        <v>-18.41</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD5">
-        <v>17.76</v>
+        <v>7.31</v>
       </c>
       <c r="AE5">
-        <v>54.84</v>
+        <v>56.27</v>
       </c>
       <c r="AF5">
-        <v>367.36</v>
+        <v>59.24</v>
       </c>
       <c r="AG5">
-        <v>2042.07</v>
+        <v>2056.36</v>
       </c>
       <c r="AH5">
-        <v>1814.78</v>
+        <v>1785.39</v>
       </c>
       <c r="AI5">
-        <v>1951.96</v>
+        <v>1907.26</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>32.85</v>
+        <v>36.33</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,37 +1348,37 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>685.9</v>
+        <v>674.55</v>
       </c>
       <c r="D6">
-        <v>-1.49</v>
+        <v>-1.65</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
       </c>
       <c r="F6">
-        <v>685.9</v>
+        <v>674.55</v>
       </c>
       <c r="G6">
-        <v>-37.06</v>
+        <v>-38.1</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-2.21</v>
+        <v>-2.18</v>
       </c>
       <c r="J6">
-        <v>-14.2</v>
+        <v>-15.21</v>
       </c>
       <c r="K6">
-        <v>-6.71</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="L6">
-        <v>-35.4</v>
+        <v>-34.61</v>
       </c>
       <c r="M6">
-        <v>11.37</v>
+        <v>10.61</v>
       </c>
       <c r="N6">
         <v>15</v>
@@ -1387,19 +1387,19 @@
         <v>19</v>
       </c>
       <c r="P6">
-        <v>696.58</v>
+        <v>693.58</v>
       </c>
       <c r="Q6">
-        <v>725.1900000000001</v>
+        <v>718.88</v>
       </c>
       <c r="R6">
-        <v>763.01</v>
+        <v>761.1900000000001</v>
       </c>
       <c r="S6">
-        <v>825.27</v>
+        <v>823.46</v>
       </c>
       <c r="T6">
-        <v>-16.89</v>
+        <v>-18.08</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1414,43 +1414,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>30.71</v>
+        <v>27.97</v>
       </c>
       <c r="Z6">
-        <v>-22.61</v>
+        <v>-23.51</v>
       </c>
       <c r="AA6">
-        <v>-21.15</v>
+        <v>-21.62</v>
       </c>
       <c r="AB6">
-        <v>-1.46</v>
+        <v>-1.88</v>
       </c>
       <c r="AC6">
-        <v>54.45</v>
+        <v>37.75</v>
       </c>
       <c r="AD6">
-        <v>49.75</v>
+        <v>49.33</v>
       </c>
       <c r="AE6">
-        <v>20.83</v>
+        <v>20.31</v>
       </c>
       <c r="AF6">
-        <v>26</v>
+        <v>-1.59</v>
       </c>
       <c r="AG6">
-        <v>798.49</v>
+        <v>786.3200000000001</v>
       </c>
       <c r="AH6">
-        <v>651.88</v>
+        <v>651.4400000000001</v>
       </c>
       <c r="AI6">
-        <v>756.98</v>
+        <v>739.76</v>
       </c>
       <c r="AJ6" t="s">
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>46.2</v>
+        <v>48.26</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2900.9</v>
+        <v>2893.8</v>
       </c>
       <c r="D7">
-        <v>-0.87</v>
+        <v>-0.24</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1473,46 +1473,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-16.04</v>
+        <v>-16.24</v>
       </c>
       <c r="H7">
-        <v>53.37</v>
+        <v>52.99</v>
       </c>
       <c r="I7">
-        <v>-3.94</v>
+        <v>-4.59</v>
       </c>
       <c r="J7">
-        <v>-11.6</v>
+        <v>-11.44</v>
       </c>
       <c r="K7">
-        <v>15.24</v>
+        <v>15.3</v>
       </c>
       <c r="L7">
-        <v>22.65</v>
+        <v>25.49</v>
       </c>
       <c r="M7">
-        <v>29.41</v>
+        <v>29.25</v>
       </c>
       <c r="N7">
         <v>85</v>
       </c>
       <c r="O7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P7">
-        <v>2958.64</v>
+        <v>2930.78</v>
       </c>
       <c r="Q7">
-        <v>3089.75</v>
+        <v>3071.34</v>
       </c>
       <c r="R7">
-        <v>2982.85</v>
+        <v>2990.13</v>
       </c>
       <c r="S7">
-        <v>2498.88</v>
+        <v>2502.47</v>
       </c>
       <c r="T7">
-        <v>16.09</v>
+        <v>15.64</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,43 +1527,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>36.68</v>
+        <v>36.2</v>
       </c>
       <c r="Z7">
-        <v>-34.65</v>
+        <v>-41.41</v>
       </c>
       <c r="AA7">
-        <v>1.72</v>
+        <v>-6.9</v>
       </c>
       <c r="AB7">
-        <v>-36.37</v>
+        <v>-34.51</v>
       </c>
       <c r="AC7">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>5.07</v>
+        <v>1.27</v>
       </c>
       <c r="AE7">
-        <v>123.48</v>
+        <v>122.02</v>
       </c>
       <c r="AF7">
-        <v>-13.71</v>
+        <v>-7</v>
       </c>
       <c r="AG7">
-        <v>3314.35</v>
+        <v>3296.85</v>
       </c>
       <c r="AH7">
-        <v>2865.15</v>
+        <v>2845.83</v>
       </c>
       <c r="AI7">
-        <v>3294.14</v>
+        <v>3239.55</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>25.82</v>
+        <v>29.27</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8351.5</v>
+        <v>8116</v>
       </c>
       <c r="D8">
-        <v>-0.52</v>
+        <v>-2.82</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1586,25 +1586,25 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-8.31</v>
+        <v>-10.9</v>
       </c>
       <c r="H8">
-        <v>40.97</v>
+        <v>36.99</v>
       </c>
       <c r="I8">
-        <v>-3.77</v>
+        <v>-4.8</v>
       </c>
       <c r="J8">
-        <v>2.22</v>
+        <v>0.14</v>
       </c>
       <c r="K8">
-        <v>2.97</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L8">
-        <v>-8.140000000000001</v>
+        <v>-8.02</v>
       </c>
       <c r="M8">
-        <v>14.68</v>
+        <v>14.26</v>
       </c>
       <c r="N8">
         <v>57</v>
@@ -1613,19 +1613,19 @@
         <v>58</v>
       </c>
       <c r="P8">
-        <v>8475.4</v>
+        <v>8393.5</v>
       </c>
       <c r="Q8">
-        <v>8501.450000000001</v>
+        <v>8507.67</v>
       </c>
       <c r="R8">
-        <v>8250.709999999999</v>
+        <v>8262.809999999999</v>
       </c>
       <c r="S8">
-        <v>7441.81</v>
+        <v>7441.9</v>
       </c>
       <c r="T8">
-        <v>12.22</v>
+        <v>9.06</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1640,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>47.58</v>
+        <v>41.13</v>
       </c>
       <c r="Z8">
-        <v>78.25</v>
+        <v>41.05</v>
       </c>
       <c r="AA8">
-        <v>124.67</v>
+        <v>107.94</v>
       </c>
       <c r="AB8">
-        <v>-46.41</v>
+        <v>-66.89</v>
       </c>
       <c r="AC8">
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>7.8</v>
+        <v>3.39</v>
       </c>
       <c r="AE8">
-        <v>303.2</v>
+        <v>310.22</v>
       </c>
       <c r="AF8">
-        <v>-58.12</v>
+        <v>-4.16</v>
       </c>
       <c r="AG8">
-        <v>8946.76</v>
+        <v>8925.610000000001</v>
       </c>
       <c r="AH8">
-        <v>8056.14</v>
+        <v>8089.74</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
@@ -1676,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>33.46</v>
+        <v>33.74</v>
       </c>
     </row>
   </sheetData>
@@ -1874,13 +1874,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>7.49</v>
+        <v>13.18</v>
       </c>
       <c r="D7" s="5">
-        <v>13.18</v>
+        <v>12.65</v>
       </c>
       <c r="E7" s="6">
-        <v>5.69</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1891,13 +1891,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-3.48</v>
+        <v>-6.75</v>
       </c>
       <c r="D8" s="5">
-        <v>-6.75</v>
+        <v>-0.73</v>
       </c>
       <c r="E8" s="7">
-        <v>-3.27</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1908,13 +1908,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-12.65</v>
+        <v>-12.78</v>
       </c>
       <c r="D9" s="5">
-        <v>-12.78</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.13</v>
+        <v>-12.93</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1925,13 +1925,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-6.31</v>
+        <v>-7.75</v>
       </c>
       <c r="D10" s="5">
-        <v>-7.75</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.44</v>
+        <v>-8.279999999999999</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1942,13 +1942,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-13.54</v>
+        <v>-14.2</v>
       </c>
       <c r="D11" s="5">
-        <v>-14.2</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.66</v>
+        <v>-15.21</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1959,13 +1959,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-11.12</v>
+        <v>-11.6</v>
       </c>
       <c r="D12" s="5">
-        <v>-11.6</v>
+        <v>-11.44</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.48</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1976,13 +1976,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="D13" s="5">
-        <v>2.22</v>
+        <v>0.14</v>
       </c>
       <c r="E13" s="6">
-        <v>0.38</v>
+        <v>-2.08</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1993,13 +1993,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-0.89</v>
+        <v>-0.95</v>
       </c>
       <c r="D14" s="5">
-        <v>-0.95</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.06</v>
+        <v>-4.38</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-3.43</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2010,13 +2010,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-4.25</v>
+        <v>-4.56</v>
       </c>
       <c r="D15" s="5">
-        <v>-4.56</v>
+        <v>-0.87</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.31</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2027,13 +2027,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-7.49</v>
+        <v>-8.68</v>
       </c>
       <c r="D16" s="5">
-        <v>-8.68</v>
+        <v>-6.05</v>
       </c>
       <c r="E16" s="7">
-        <v>-1.19</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2044,13 +2044,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>-7.82</v>
+        <v>-10.11</v>
       </c>
       <c r="D17" s="5">
-        <v>-10.11</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="E17" s="7">
-        <v>-2.29</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2061,13 +2061,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>0.1</v>
+        <v>-2.21</v>
       </c>
       <c r="D18" s="5">
-        <v>-2.21</v>
+        <v>-2.18</v>
       </c>
       <c r="E18" s="7">
-        <v>-2.31</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2078,13 +2078,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-1.9</v>
+        <v>-3.94</v>
       </c>
       <c r="D19" s="5">
-        <v>-3.94</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.04</v>
+        <v>-4.59</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2095,13 +2095,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>-2.69</v>
+        <v>-3.77</v>
       </c>
       <c r="D20" s="5">
-        <v>-3.77</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.08</v>
+        <v>-4.8</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2112,13 +2112,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>25.93</v>
+        <v>31.95</v>
       </c>
       <c r="D21" s="5">
-        <v>31.95</v>
-      </c>
-      <c r="E21" s="6">
-        <v>6.02</v>
+        <v>35.02</v>
+      </c>
+      <c r="E21" s="7">
+        <v>3.07</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2129,13 +2129,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>11.67</v>
+        <v>12.78</v>
       </c>
       <c r="D22" s="5">
-        <v>12.78</v>
-      </c>
-      <c r="E22" s="6">
-        <v>1.11</v>
+        <v>19.14</v>
+      </c>
+      <c r="E22" s="7">
+        <v>6.36</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2146,13 +2146,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-0.1</v>
+        <v>1.78</v>
       </c>
       <c r="D23" s="5">
-        <v>1.78</v>
+        <v>0.72</v>
       </c>
       <c r="E23" s="6">
-        <v>1.88</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2163,13 +2163,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-19.31</v>
+        <v>-21.15</v>
       </c>
       <c r="D24" s="5">
-        <v>-21.15</v>
+        <v>-19.03</v>
       </c>
       <c r="E24" s="7">
-        <v>-1.84</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2180,13 +2180,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-35.13</v>
+        <v>-35.4</v>
       </c>
       <c r="D25" s="5">
-        <v>-35.4</v>
+        <v>-34.61</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.27</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2197,13 +2197,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>21.92</v>
+        <v>22.65</v>
       </c>
       <c r="D26" s="5">
-        <v>22.65</v>
-      </c>
-      <c r="E26" s="6">
-        <v>0.73</v>
+        <v>25.49</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.84</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2214,13 +2214,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>-9.130000000000001</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="D27" s="5">
-        <v>-8.140000000000001</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.99</v>
+        <v>-8.02</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2231,13 +2231,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>3.14</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D28" s="5">
-        <v>9.699999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="E28" s="6">
-        <v>6.56</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2248,13 +2248,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-12.13</v>
+        <v>-10.97</v>
       </c>
       <c r="D29" s="5">
-        <v>-10.97</v>
-      </c>
-      <c r="E29" s="6">
-        <v>1.16</v>
+        <v>-1.52</v>
+      </c>
+      <c r="E29" s="7">
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2265,13 +2265,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>-9.76</v>
+        <v>-9.42</v>
       </c>
       <c r="D30" s="5">
-        <v>-9.42</v>
+        <v>-11.72</v>
       </c>
       <c r="E30" s="6">
-        <v>0.34</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2282,13 +2282,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>-10.05</v>
+        <v>-12.37</v>
       </c>
       <c r="D31" s="5">
-        <v>-12.37</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-2.32</v>
+        <v>-13.31</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2299,13 +2299,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>-3.4</v>
+        <v>-6.71</v>
       </c>
       <c r="D32" s="5">
-        <v>-6.71</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-3.31</v>
+        <v>-9.140000000000001</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-2.43</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2316,13 +2316,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>14.6</v>
+        <v>15.24</v>
       </c>
       <c r="D33" s="5">
-        <v>15.24</v>
-      </c>
-      <c r="E33" s="6">
-        <v>0.64</v>
+        <v>15.3</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.06</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2333,13 +2333,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>3.6</v>
+        <v>2.97</v>
       </c>
       <c r="D34" s="5">
-        <v>2.97</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.63</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-2.28</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2350,13 +2350,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-7.4</v>
+        <v>-3.39</v>
       </c>
       <c r="D35" s="5">
-        <v>-3.39</v>
+        <v>-4.38</v>
       </c>
       <c r="E35" s="6">
-        <v>4.01</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2367,13 +2367,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-12.13</v>
+        <v>-12.52</v>
       </c>
       <c r="D36" s="5">
-        <v>-12.52</v>
+        <v>-9.98</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.39</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2384,13 +2384,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="5">
-        <v>-16.12</v>
+        <v>-16.49</v>
       </c>
       <c r="D37" s="5">
-        <v>-16.49</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.37</v>
+        <v>-18.56</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-2.07</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2401,13 +2401,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="5">
-        <v>-25.26</v>
+        <v>-26.7</v>
       </c>
       <c r="D38" s="5">
-        <v>-26.7</v>
+        <v>-26.48</v>
       </c>
       <c r="E38" s="7">
-        <v>-1.44</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2418,13 +2418,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-36.11</v>
+        <v>-37.06</v>
       </c>
       <c r="D39" s="5">
-        <v>-37.06</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.95</v>
+        <v>-38.1</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2435,13 +2435,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-15.3</v>
+        <v>-16.04</v>
       </c>
       <c r="D40" s="5">
-        <v>-16.04</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-0.74</v>
+        <v>-16.24</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2452,13 +2452,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-7.84</v>
+        <v>-8.31</v>
       </c>
       <c r="D41" s="5">
-        <v>-8.31</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.47</v>
+        <v>-10.9</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-2.59</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2469,13 +2469,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>1200.5</v>
+        <v>1252.5</v>
       </c>
       <c r="D42" s="5">
-        <v>1252.5</v>
+        <v>1239.7</v>
       </c>
       <c r="E42" s="6">
-        <v>52</v>
+        <v>-12.8</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2486,13 +2486,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="5">
-        <v>858.05</v>
+        <v>854.2</v>
       </c>
       <c r="D43" s="5">
-        <v>854.2</v>
+        <v>879</v>
       </c>
       <c r="E43" s="7">
-        <v>-3.85</v>
+        <v>24.8</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2503,13 +2503,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="5">
-        <v>1627.3</v>
+        <v>1620</v>
       </c>
       <c r="D44" s="5">
-        <v>1620</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-7.3</v>
+        <v>1580</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-40</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2520,13 +2520,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="5">
-        <v>1792.9</v>
+        <v>1758.2</v>
       </c>
       <c r="D45" s="5">
-        <v>1758.2</v>
+        <v>1763.6</v>
       </c>
       <c r="E45" s="7">
-        <v>-34.7</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2537,13 +2537,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="5">
-        <v>696.25</v>
+        <v>685.9</v>
       </c>
       <c r="D46" s="5">
-        <v>685.9</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-10.35</v>
+        <v>674.55</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-11.35</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2554,13 +2554,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>2926.4</v>
+        <v>2900.9</v>
       </c>
       <c r="D47" s="5">
-        <v>2900.9</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-25.5</v>
+        <v>2893.8</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-7.1</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2571,13 +2571,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>8395</v>
+        <v>8351.5</v>
       </c>
       <c r="D48" s="5">
-        <v>8351.5</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-43.5</v>
+        <v>8116</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-235.5</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2588,13 +2588,13 @@
         <v>24</v>
       </c>
       <c r="C49" s="5">
-        <v>56.21</v>
+        <v>61.6</v>
       </c>
       <c r="D49" s="5">
-        <v>61.6</v>
+        <v>59.65</v>
       </c>
       <c r="E49" s="6">
-        <v>5.39</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2605,13 +2605,13 @@
         <v>24</v>
       </c>
       <c r="C50" s="5">
-        <v>41.97</v>
+        <v>41.06</v>
       </c>
       <c r="D50" s="5">
-        <v>41.06</v>
+        <v>48.74</v>
       </c>
       <c r="E50" s="7">
-        <v>-0.91</v>
+        <v>7.68</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2622,13 +2622,13 @@
         <v>24</v>
       </c>
       <c r="C51" s="5">
-        <v>26.95</v>
+        <v>26.35</v>
       </c>
       <c r="D51" s="5">
-        <v>26.35</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.6</v>
+        <v>23.27</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-3.08</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2639,13 +2639,13 @@
         <v>24</v>
       </c>
       <c r="C52" s="5">
-        <v>30.15</v>
+        <v>27.67</v>
       </c>
       <c r="D52" s="5">
-        <v>27.67</v>
+        <v>28.65</v>
       </c>
       <c r="E52" s="7">
-        <v>-2.48</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2656,13 +2656,13 @@
         <v>24</v>
       </c>
       <c r="C53" s="5">
-        <v>33.49</v>
+        <v>30.71</v>
       </c>
       <c r="D53" s="5">
-        <v>30.71</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-2.78</v>
+        <v>27.97</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-2.74</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2673,13 +2673,13 @@
         <v>24</v>
       </c>
       <c r="C54" s="5">
-        <v>38.37</v>
+        <v>36.68</v>
       </c>
       <c r="D54" s="5">
-        <v>36.68</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-1.69</v>
+        <v>36.2</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2690,13 +2690,13 @@
         <v>24</v>
       </c>
       <c r="C55" s="5">
-        <v>48.9</v>
+        <v>47.58</v>
       </c>
       <c r="D55" s="5">
-        <v>47.58</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-1.32</v>
+        <v>41.13</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-6.45</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2707,13 +2707,13 @@
         <v>31</v>
       </c>
       <c r="C56" s="5">
-        <v>-52.1</v>
+        <v>-19.97</v>
       </c>
       <c r="D56" s="5">
-        <v>-19.97</v>
+        <v>-36.84</v>
       </c>
       <c r="E56" s="6">
-        <v>32.13</v>
+        <v>-16.87</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2724,13 +2724,13 @@
         <v>31</v>
       </c>
       <c r="C57" s="5">
-        <v>-9.550000000000001</v>
+        <v>-0.59</v>
       </c>
       <c r="D57" s="5">
-        <v>-0.59</v>
-      </c>
-      <c r="E57" s="6">
-        <v>8.960000000000001</v>
+        <v>95.06</v>
+      </c>
+      <c r="E57" s="7">
+        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2741,13 +2741,13 @@
         <v>31</v>
       </c>
       <c r="C58" s="5">
-        <v>0.47</v>
+        <v>23</v>
       </c>
       <c r="D58" s="5">
-        <v>23</v>
+        <v>10.34</v>
       </c>
       <c r="E58" s="6">
-        <v>22.53</v>
+        <v>-12.66</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2758,13 +2758,13 @@
         <v>31</v>
       </c>
       <c r="C59" s="5">
-        <v>214.23</v>
+        <v>367.36</v>
       </c>
       <c r="D59" s="5">
-        <v>367.36</v>
+        <v>59.24</v>
       </c>
       <c r="E59" s="6">
-        <v>153.13</v>
+        <v>-308.12</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2775,13 +2775,13 @@
         <v>31</v>
       </c>
       <c r="C60" s="5">
-        <v>-28.54</v>
+        <v>26</v>
       </c>
       <c r="D60" s="5">
-        <v>26</v>
+        <v>-1.59</v>
       </c>
       <c r="E60" s="6">
-        <v>54.54</v>
+        <v>-27.59</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2792,13 +2792,13 @@
         <v>31</v>
       </c>
       <c r="C61" s="5">
-        <v>-31.27</v>
+        <v>-13.71</v>
       </c>
       <c r="D61" s="5">
-        <v>-13.71</v>
-      </c>
-      <c r="E61" s="6">
-        <v>17.56</v>
+        <v>-7</v>
+      </c>
+      <c r="E61" s="7">
+        <v>6.71</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2809,13 +2809,13 @@
         <v>31</v>
       </c>
       <c r="C62" s="5">
-        <v>-44.26</v>
+        <v>-58.12</v>
       </c>
       <c r="D62" s="5">
-        <v>-58.12</v>
+        <v>-4.16</v>
       </c>
       <c r="E62" s="7">
-        <v>-13.86</v>
+        <v>53.96</v>
       </c>
     </row>
   </sheetData>
@@ -2880,16 +2880,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="10">
-        <v>38.8</v>
+        <v>37.9</v>
       </c>
       <c r="E2" s="10">
         <v>60</v>
       </c>
       <c r="F2" s="10">
-        <v>-5.4</v>
+        <v>-5.1</v>
       </c>
       <c r="G2" s="10">
-        <v>-1.7</v>
+        <v>-1.6</v>
       </c>
       <c r="H2" s="10">
         <v>57</v>
@@ -3020,25 +3020,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="13">
-        <v>0.4772</v>
+        <v>0.4826</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2941</v>
+        <v>0.2925</v>
       </c>
       <c r="C2" s="13">
-        <v>0.2371</v>
+        <v>0.2334</v>
       </c>
       <c r="D2" s="13">
-        <v>0.182</v>
+        <v>0.1811</v>
       </c>
       <c r="E2" s="13">
-        <v>0.1468</v>
+        <v>0.1426</v>
       </c>
       <c r="F2" s="13">
-        <v>0.1137</v>
+        <v>0.1061</v>
       </c>
       <c r="G2" s="13">
-        <v>0.07480000000000001</v>
+        <v>0.0762</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,43 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>28.6 → 35.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>28.6</t>
+  </si>
+  <si>
+    <t>35.3</t>
+  </si>
+  <si>
+    <t>28.0 → 37.2</t>
+  </si>
+  <si>
+    <t>28.0</t>
+  </si>
+  <si>
+    <t>37.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -258,14 +294,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -298,13 +334,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,14 +410,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -896,10 +933,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1239.7</v>
+        <v>1267.6</v>
       </c>
       <c r="D2">
-        <v>-1.02</v>
+        <v>2.25</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -908,46 +945,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-4.38</v>
+        <v>-2.23</v>
       </c>
       <c r="H2">
-        <v>65.66</v>
+        <v>69.39</v>
       </c>
       <c r="I2">
-        <v>-4.38</v>
+        <v>-0.85</v>
       </c>
       <c r="J2">
-        <v>12.65</v>
+        <v>18.3</v>
       </c>
       <c r="K2">
-        <v>8.779999999999999</v>
+        <v>10.76</v>
       </c>
       <c r="L2">
-        <v>35.02</v>
+        <v>39.27</v>
       </c>
       <c r="M2">
-        <v>7.62</v>
+        <v>7.93</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P2">
-        <v>1243.8</v>
+        <v>1241.62</v>
       </c>
       <c r="Q2">
-        <v>1156.48</v>
+        <v>1165.96</v>
       </c>
       <c r="R2">
-        <v>1124.78</v>
+        <v>1129.01</v>
       </c>
       <c r="S2">
-        <v>976.16</v>
+        <v>978.16</v>
       </c>
       <c r="T2">
-        <v>27</v>
+        <v>29.59</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,34 +999,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>59.65</v>
+        <v>62.44</v>
       </c>
       <c r="Z2">
-        <v>39.74</v>
+        <v>41.5</v>
       </c>
       <c r="AA2">
-        <v>29.07</v>
+        <v>31.56</v>
       </c>
       <c r="AB2">
-        <v>10.67</v>
+        <v>9.94</v>
       </c>
       <c r="AC2">
-        <v>61.38</v>
+        <v>67.22</v>
       </c>
       <c r="AD2">
-        <v>66.38</v>
+        <v>64.61</v>
       </c>
       <c r="AE2">
-        <v>54.88</v>
+        <v>54.49</v>
       </c>
       <c r="AF2">
-        <v>-36.84</v>
+        <v>-56.28</v>
       </c>
       <c r="AG2">
-        <v>1326.39</v>
+        <v>1338.56</v>
       </c>
       <c r="AH2">
-        <v>986.5700000000001</v>
+        <v>993.36</v>
       </c>
       <c r="AI2">
         <v>1148.32</v>
@@ -998,7 +1035,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>43.84</v>
+        <v>43.82</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1046,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>879</v>
+        <v>882.3</v>
       </c>
       <c r="D3">
-        <v>2.9</v>
+        <v>0.38</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1021,46 +1058,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-9.98</v>
+        <v>-9.65</v>
       </c>
       <c r="H3">
-        <v>66.01000000000001</v>
+        <v>66.64</v>
       </c>
       <c r="I3">
-        <v>-0.87</v>
+        <v>-0.42</v>
       </c>
       <c r="J3">
-        <v>-0.73</v>
+        <v>0.52</v>
       </c>
       <c r="K3">
-        <v>-1.52</v>
+        <v>-4.62</v>
       </c>
       <c r="L3">
-        <v>19.14</v>
+        <v>18.33</v>
       </c>
       <c r="M3">
-        <v>48.26</v>
+        <v>49.27</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P3">
-        <v>868.45</v>
+        <v>867.71</v>
       </c>
       <c r="Q3">
-        <v>887.6900000000001</v>
+        <v>887.05</v>
       </c>
       <c r="R3">
-        <v>880.28</v>
+        <v>880.25</v>
       </c>
       <c r="S3">
-        <v>794.79</v>
+        <v>795.86</v>
       </c>
       <c r="T3">
-        <v>10.6</v>
+        <v>10.86</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1075,34 +1112,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>48.74</v>
+        <v>49.68</v>
       </c>
       <c r="Z3">
-        <v>-5.14</v>
+        <v>-4.43</v>
       </c>
       <c r="AA3">
-        <v>-2.06</v>
+        <v>-2.53</v>
       </c>
       <c r="AB3">
-        <v>-3.09</v>
+        <v>-1.9</v>
       </c>
       <c r="AC3">
-        <v>22.22</v>
+        <v>41.13</v>
       </c>
       <c r="AD3">
-        <v>17.37</v>
+        <v>23.89</v>
       </c>
       <c r="AE3">
-        <v>24.79</v>
+        <v>24.19</v>
       </c>
       <c r="AF3">
-        <v>95.06</v>
+        <v>-47.47</v>
       </c>
       <c r="AG3">
-        <v>930.84</v>
+        <v>930.13</v>
       </c>
       <c r="AH3">
-        <v>844.54</v>
+        <v>843.98</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1111,7 +1148,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>19.87</v>
+        <v>17.48</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1159,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1580</v>
+        <v>1605.4</v>
       </c>
       <c r="D4">
-        <v>-2.47</v>
+        <v>1.61</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1134,46 +1171,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-18.56</v>
+        <v>-17.25</v>
       </c>
       <c r="H4">
-        <v>16.63</v>
+        <v>18.51</v>
       </c>
       <c r="I4">
-        <v>-6.05</v>
+        <v>-3.45</v>
       </c>
       <c r="J4">
-        <v>-12.93</v>
+        <v>-12.08</v>
       </c>
       <c r="K4">
-        <v>-11.72</v>
+        <v>-13.25</v>
       </c>
       <c r="L4">
-        <v>0.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M4">
-        <v>23.34</v>
+        <v>23.73</v>
       </c>
       <c r="N4">
         <v>43</v>
       </c>
       <c r="O4">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P4">
-        <v>1624.84</v>
+        <v>1613.38</v>
       </c>
       <c r="Q4">
-        <v>1755.92</v>
+        <v>1743.73</v>
       </c>
       <c r="R4">
-        <v>1815.21</v>
+        <v>1812.97</v>
       </c>
       <c r="S4">
-        <v>1681.03</v>
+        <v>1680.4</v>
       </c>
       <c r="T4">
-        <v>-6.01</v>
+        <v>-4.46</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1188,34 +1225,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>23.27</v>
+        <v>28.95</v>
       </c>
       <c r="Z4">
-        <v>-59.55</v>
+        <v>-61.72</v>
       </c>
       <c r="AA4">
-        <v>-39.04</v>
+        <v>-43.57</v>
       </c>
       <c r="AB4">
-        <v>-20.51</v>
+        <v>-18.15</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="AE4">
-        <v>49.22</v>
+        <v>47.9</v>
       </c>
       <c r="AF4">
-        <v>10.34</v>
+        <v>-10.01</v>
       </c>
       <c r="AG4">
-        <v>1934.53</v>
+        <v>1928.68</v>
       </c>
       <c r="AH4">
-        <v>1577.32</v>
+        <v>1558.78</v>
       </c>
       <c r="AI4">
         <v>1739.1</v>
@@ -1224,7 +1261,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>53.75</v>
+        <v>57.57</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,10 +1272,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1763.6</v>
+        <v>1801.4</v>
       </c>
       <c r="D5">
-        <v>0.31</v>
+        <v>2.14</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1247,46 +1284,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-26.48</v>
+        <v>-24.9</v>
       </c>
       <c r="H5">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="I5">
-        <v>-9.210000000000001</v>
+        <v>-8.27</v>
       </c>
       <c r="J5">
-        <v>-8.279999999999999</v>
+        <v>-5.91</v>
       </c>
       <c r="K5">
-        <v>-13.31</v>
+        <v>-12.36</v>
       </c>
       <c r="L5">
-        <v>-19.03</v>
+        <v>-19.21</v>
       </c>
       <c r="M5">
-        <v>18.11</v>
+        <v>17.82</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P5">
-        <v>1835.54</v>
+        <v>1803.04</v>
       </c>
       <c r="Q5">
-        <v>1920.88</v>
+        <v>1914.38</v>
       </c>
       <c r="R5">
-        <v>1982</v>
+        <v>1977.57</v>
       </c>
       <c r="S5">
-        <v>2057.54</v>
+        <v>2054.97</v>
       </c>
       <c r="T5">
-        <v>-14.29</v>
+        <v>-12.34</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1301,34 +1338,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>28.65</v>
+        <v>35.27</v>
       </c>
       <c r="Z5">
-        <v>-43.97</v>
+        <v>-46.61</v>
       </c>
       <c r="AA5">
-        <v>-25.56</v>
+        <v>-29.77</v>
       </c>
       <c r="AB5">
-        <v>-18.41</v>
+        <v>-16.84</v>
       </c>
       <c r="AC5">
-        <v>1.17</v>
+        <v>10.26</v>
       </c>
       <c r="AD5">
-        <v>7.31</v>
+        <v>3.81</v>
       </c>
       <c r="AE5">
-        <v>56.27</v>
+        <v>56.39</v>
       </c>
       <c r="AF5">
-        <v>59.24</v>
+        <v>19.17</v>
       </c>
       <c r="AG5">
-        <v>2056.36</v>
+        <v>2059.84</v>
       </c>
       <c r="AH5">
-        <v>1785.39</v>
+        <v>1768.92</v>
       </c>
       <c r="AI5">
         <v>1907.26</v>
@@ -1337,7 +1374,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>36.33</v>
+        <v>36.56</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1385,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>674.55</v>
+        <v>691.95</v>
       </c>
       <c r="D6">
-        <v>-1.65</v>
+        <v>2.58</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1360,46 +1397,46 @@
         <v>674.55</v>
       </c>
       <c r="G6">
-        <v>-38.1</v>
+        <v>-36.51</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="I6">
-        <v>-2.18</v>
+        <v>-1.82</v>
       </c>
       <c r="J6">
-        <v>-15.21</v>
+        <v>-13.58</v>
       </c>
       <c r="K6">
-        <v>-9.140000000000001</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L6">
-        <v>-34.61</v>
+        <v>-31.68</v>
       </c>
       <c r="M6">
-        <v>10.61</v>
+        <v>10.65</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P6">
-        <v>693.58</v>
+        <v>691.02</v>
       </c>
       <c r="Q6">
-        <v>718.88</v>
+        <v>714.5700000000001</v>
       </c>
       <c r="R6">
-        <v>761.1900000000001</v>
+        <v>759.85</v>
       </c>
       <c r="S6">
-        <v>823.46</v>
+        <v>821.73</v>
       </c>
       <c r="T6">
-        <v>-18.08</v>
+        <v>-15.79</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1414,34 +1451,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>27.97</v>
+        <v>37.22</v>
       </c>
       <c r="Z6">
-        <v>-23.51</v>
+        <v>-22.56</v>
       </c>
       <c r="AA6">
-        <v>-21.62</v>
+        <v>-21.81</v>
       </c>
       <c r="AB6">
-        <v>-1.88</v>
+        <v>-0.74</v>
       </c>
       <c r="AC6">
-        <v>37.75</v>
+        <v>53.16</v>
       </c>
       <c r="AD6">
-        <v>49.33</v>
+        <v>48.45</v>
       </c>
       <c r="AE6">
-        <v>20.31</v>
+        <v>20.54</v>
       </c>
       <c r="AF6">
-        <v>-1.59</v>
+        <v>-45.17</v>
       </c>
       <c r="AG6">
-        <v>786.3200000000001</v>
+        <v>776.85</v>
       </c>
       <c r="AH6">
-        <v>651.4400000000001</v>
+        <v>652.28</v>
       </c>
       <c r="AI6">
         <v>739.76</v>
@@ -1450,7 +1487,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>48.26</v>
+        <v>45.25</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1498,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2893.8</v>
+        <v>2815.3</v>
       </c>
       <c r="D7">
-        <v>-0.24</v>
+        <v>-2.71</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1473,46 +1510,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-16.24</v>
+        <v>-18.51</v>
       </c>
       <c r="H7">
-        <v>52.99</v>
+        <v>48.84</v>
       </c>
       <c r="I7">
-        <v>-4.59</v>
+        <v>-6.26</v>
       </c>
       <c r="J7">
-        <v>-11.44</v>
+        <v>-13.69</v>
       </c>
       <c r="K7">
-        <v>15.3</v>
+        <v>12.86</v>
       </c>
       <c r="L7">
-        <v>25.49</v>
+        <v>30.1</v>
       </c>
       <c r="M7">
-        <v>29.25</v>
+        <v>28.47</v>
       </c>
       <c r="N7">
         <v>85</v>
       </c>
       <c r="O7">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="P7">
-        <v>2930.78</v>
+        <v>2893.16</v>
       </c>
       <c r="Q7">
-        <v>3071.34</v>
+        <v>3048.73</v>
       </c>
       <c r="R7">
-        <v>2990.13</v>
+        <v>2995.12</v>
       </c>
       <c r="S7">
-        <v>2502.47</v>
+        <v>2505.71</v>
       </c>
       <c r="T7">
-        <v>15.64</v>
+        <v>12.36</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1527,43 +1564,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>36.2</v>
+        <v>31.34</v>
       </c>
       <c r="Z7">
-        <v>-41.41</v>
+        <v>-52.5</v>
       </c>
       <c r="AA7">
-        <v>-6.9</v>
+        <v>-16.02</v>
       </c>
       <c r="AB7">
-        <v>-34.51</v>
+        <v>-36.48</v>
       </c>
       <c r="AC7">
         <v>0</v>
       </c>
       <c r="AD7">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>122.02</v>
+        <v>121.87</v>
       </c>
       <c r="AF7">
-        <v>-7</v>
+        <v>-58.74</v>
       </c>
       <c r="AG7">
-        <v>3296.85</v>
+        <v>3282</v>
       </c>
       <c r="AH7">
-        <v>2845.83</v>
+        <v>2815.47</v>
       </c>
       <c r="AI7">
-        <v>3239.55</v>
+        <v>3225.62</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>29.27</v>
+        <v>32.77</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1611,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8116</v>
+        <v>8016.5</v>
       </c>
       <c r="D8">
-        <v>-2.82</v>
+        <v>-1.23</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1586,46 +1623,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-10.9</v>
+        <v>-11.99</v>
       </c>
       <c r="H8">
-        <v>36.99</v>
+        <v>35.31</v>
       </c>
       <c r="I8">
-        <v>-4.8</v>
+        <v>-7.28</v>
       </c>
       <c r="J8">
-        <v>0.14</v>
+        <v>0.31</v>
       </c>
       <c r="K8">
-        <v>0.6899999999999999</v>
+        <v>-0.78</v>
       </c>
       <c r="L8">
-        <v>-8.02</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="M8">
-        <v>14.26</v>
+        <v>13.8</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P8">
-        <v>8393.5</v>
+        <v>8267.6</v>
       </c>
       <c r="Q8">
-        <v>8507.67</v>
+        <v>8493.15</v>
       </c>
       <c r="R8">
-        <v>8262.809999999999</v>
+        <v>8274.620000000001</v>
       </c>
       <c r="S8">
-        <v>7441.9</v>
+        <v>7440.47</v>
       </c>
       <c r="T8">
-        <v>9.06</v>
+        <v>7.74</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1640,34 +1677,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>41.13</v>
+        <v>38.74</v>
       </c>
       <c r="Z8">
-        <v>41.05</v>
+        <v>3.5</v>
       </c>
       <c r="AA8">
-        <v>107.94</v>
+        <v>87.05</v>
       </c>
       <c r="AB8">
-        <v>-66.89</v>
+        <v>-83.56</v>
       </c>
       <c r="AC8">
         <v>0</v>
       </c>
       <c r="AD8">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="AE8">
-        <v>310.22</v>
+        <v>306.21</v>
       </c>
       <c r="AF8">
-        <v>-4.16</v>
+        <v>-61.88</v>
       </c>
       <c r="AG8">
-        <v>8925.610000000001</v>
+        <v>8958.01</v>
       </c>
       <c r="AH8">
-        <v>8089.74</v>
+        <v>8028.29</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
@@ -1676,7 +1713,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>33.74</v>
+        <v>33.98</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1837,991 +1874,1046 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>13.18</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>12.65</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>18.3</v>
+      </c>
+      <c r="E8" s="7">
+        <v>5.65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-6.75</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>-0.73</v>
       </c>
-      <c r="E8" s="7">
-        <v>6.02</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>0.52</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-12.78</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-12.93</v>
       </c>
-      <c r="E9" s="6">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-12.08</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-7.75</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>-8.279999999999999</v>
       </c>
-      <c r="E10" s="6">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-5.91</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-14.2</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-15.21</v>
       </c>
-      <c r="E11" s="6">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-13.58</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-11.6</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>-11.44</v>
       </c>
-      <c r="E12" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-13.69</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>2.22</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>0.14</v>
       </c>
-      <c r="E13" s="6">
-        <v>-2.08</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>0.31</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-0.95</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>-4.38</v>
       </c>
-      <c r="E14" s="6">
-        <v>-3.43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-0.85</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-4.56</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-0.87</v>
       </c>
-      <c r="E15" s="7">
-        <v>3.69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-0.42</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-8.68</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>-6.05</v>
       </c>
-      <c r="E16" s="7">
-        <v>2.63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-3.45</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-10.11</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>-9.210000000000001</v>
       </c>
-      <c r="E17" s="7">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>-8.27</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>-2.21</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>-2.18</v>
       </c>
-      <c r="E18" s="7">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-1.82</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5">
-        <v>-3.94</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>-4.59</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-6.26</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="5">
-        <v>-3.77</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="6">
         <v>-4.8</v>
       </c>
-      <c r="E20" s="6">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D21" s="6">
+        <v>-7.28</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-2.48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>31.95</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="6">
         <v>35.02</v>
       </c>
-      <c r="E21" s="7">
-        <v>3.07</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="6">
+        <v>39.27</v>
+      </c>
+      <c r="E22" s="7">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="5">
-        <v>12.78</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="6">
         <v>19.14</v>
       </c>
-      <c r="E22" s="7">
-        <v>6.36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="6">
+        <v>18.33</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="5">
-        <v>1.78</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="6">
         <v>0.72</v>
       </c>
-      <c r="E23" s="6">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="6">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="5">
-        <v>-21.15</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="6">
         <v>-19.03</v>
       </c>
-      <c r="E24" s="7">
-        <v>2.12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D25" s="6">
+        <v>-19.21</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="5">
-        <v>-35.4</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C26" s="6">
         <v>-34.61</v>
       </c>
-      <c r="E25" s="7">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D26" s="6">
+        <v>-31.68</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="5">
-        <v>22.65</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="6">
         <v>25.49</v>
       </c>
-      <c r="E26" s="7">
-        <v>2.84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="6">
+        <v>30.1</v>
+      </c>
+      <c r="E27" s="7">
+        <v>4.61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="5">
-        <v>-8.140000000000001</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C28" s="6">
         <v>-8.02</v>
       </c>
-      <c r="E27" s="7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D28" s="6">
+        <v>-9.539999999999999</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="5">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C29" s="6">
         <v>8.779999999999999</v>
       </c>
-      <c r="E28" s="6">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D29" s="6">
+        <v>10.76</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="5">
-        <v>-10.97</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C30" s="6">
         <v>-1.52</v>
       </c>
-      <c r="E29" s="7">
-        <v>9.449999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D30" s="6">
+        <v>-4.62</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="5">
-        <v>-9.42</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C31" s="6">
         <v>-11.72</v>
       </c>
-      <c r="E30" s="6">
-        <v>-2.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="D31" s="6">
+        <v>-13.25</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="5">
-        <v>-12.37</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C32" s="6">
         <v>-13.31</v>
       </c>
-      <c r="E31" s="6">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="D32" s="6">
+        <v>-12.36</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="5">
-        <v>-6.71</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C33" s="6">
         <v>-9.140000000000001</v>
       </c>
-      <c r="E32" s="6">
-        <v>-2.43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="D33" s="6">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="5">
-        <v>15.24</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C34" s="6">
         <v>15.3</v>
       </c>
-      <c r="E33" s="7">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="D34" s="6">
+        <v>12.86</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-2.44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="5">
-        <v>2.97</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C35" s="6">
         <v>0.6899999999999999</v>
       </c>
-      <c r="E34" s="6">
-        <v>-2.28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="D35" s="6">
+        <v>-0.78</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="5">
-        <v>-3.39</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C36" s="6">
         <v>-4.38</v>
       </c>
-      <c r="E35" s="6">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="D36" s="6">
+        <v>-2.23</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="5">
-        <v>-12.52</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C37" s="6">
         <v>-9.98</v>
       </c>
-      <c r="E36" s="7">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="D37" s="6">
+        <v>-9.65</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="5">
-        <v>-16.49</v>
-      </c>
-      <c r="D37" s="5">
+      <c r="C38" s="6">
         <v>-18.56</v>
       </c>
-      <c r="E37" s="6">
-        <v>-2.07</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="D38" s="6">
+        <v>-17.25</v>
+      </c>
+      <c r="E38" s="7">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B39" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="5">
-        <v>-26.7</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="C39" s="6">
         <v>-26.48</v>
       </c>
-      <c r="E38" s="7">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="D39" s="6">
+        <v>-24.9</v>
+      </c>
+      <c r="E39" s="7">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="5">
-        <v>-37.06</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="C40" s="6">
         <v>-38.1</v>
       </c>
-      <c r="E39" s="6">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="D40" s="6">
+        <v>-36.51</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.59</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="5">
-        <v>-16.04</v>
-      </c>
-      <c r="D40" s="5">
+      <c r="C41" s="6">
         <v>-16.24</v>
       </c>
-      <c r="E40" s="6">
-        <v>-0.2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="D41" s="6">
+        <v>-18.51</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-2.27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B42" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C41" s="5">
-        <v>-8.31</v>
-      </c>
-      <c r="D41" s="5">
+      <c r="C42" s="6">
         <v>-10.9</v>
       </c>
-      <c r="E41" s="6">
-        <v>-2.59</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="D42" s="6">
+        <v>-11.99</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B43" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="5">
-        <v>1252.5</v>
-      </c>
-      <c r="D42" s="5">
+      <c r="C43" s="6">
         <v>1239.7</v>
       </c>
-      <c r="E42" s="6">
-        <v>-12.8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="D43" s="6">
+        <v>1267.6</v>
+      </c>
+      <c r="E43" s="7">
+        <v>27.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B44" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C43" s="5">
-        <v>854.2</v>
-      </c>
-      <c r="D43" s="5">
+      <c r="C44" s="6">
         <v>879</v>
       </c>
-      <c r="E43" s="7">
-        <v>24.8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="D44" s="6">
+        <v>882.3</v>
+      </c>
+      <c r="E44" s="7">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B45" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C44" s="5">
-        <v>1620</v>
-      </c>
-      <c r="D44" s="5">
+      <c r="C45" s="6">
         <v>1580</v>
       </c>
-      <c r="E44" s="6">
-        <v>-40</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="D45" s="6">
+        <v>1605.4</v>
+      </c>
+      <c r="E45" s="7">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="5">
-        <v>1758.2</v>
-      </c>
-      <c r="D45" s="5">
+      <c r="C46" s="6">
         <v>1763.6</v>
       </c>
-      <c r="E45" s="7">
-        <v>5.4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="D46" s="6">
+        <v>1801.4</v>
+      </c>
+      <c r="E46" s="7">
+        <v>37.8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C46" s="5">
-        <v>685.9</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C47" s="6">
         <v>674.55</v>
       </c>
-      <c r="E46" s="6">
-        <v>-11.35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="D47" s="6">
+        <v>691.95</v>
+      </c>
+      <c r="E47" s="7">
+        <v>17.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="5">
-        <v>2900.9</v>
-      </c>
-      <c r="D47" s="5">
+      <c r="C48" s="6">
         <v>2893.8</v>
       </c>
-      <c r="E47" s="6">
-        <v>-7.1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="D48" s="6">
+        <v>2815.3</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-78.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B49" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C48" s="5">
-        <v>8351.5</v>
-      </c>
-      <c r="D48" s="5">
+      <c r="C49" s="6">
         <v>8116</v>
       </c>
-      <c r="E48" s="6">
-        <v>-235.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
+      <c r="D49" s="6">
+        <v>8016.5</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-99.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B50" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C49" s="5">
-        <v>61.6</v>
-      </c>
-      <c r="D49" s="5">
+      <c r="C50" s="6">
         <v>59.65</v>
       </c>
-      <c r="E49" s="6">
-        <v>-1.95</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
+      <c r="D50" s="6">
+        <v>62.44</v>
+      </c>
+      <c r="E50" s="7">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="B51" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C50" s="5">
-        <v>41.06</v>
-      </c>
-      <c r="D50" s="5">
+      <c r="C51" s="6">
         <v>48.74</v>
       </c>
-      <c r="E50" s="7">
-        <v>7.68</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
+      <c r="D51" s="6">
+        <v>49.68</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="B52" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C51" s="5">
-        <v>26.35</v>
-      </c>
-      <c r="D51" s="5">
+      <c r="C52" s="6">
         <v>23.27</v>
       </c>
-      <c r="E51" s="6">
-        <v>-3.08</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
+      <c r="D52" s="6">
+        <v>28.95</v>
+      </c>
+      <c r="E52" s="7">
+        <v>5.68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C52" s="5">
-        <v>27.67</v>
-      </c>
-      <c r="D52" s="5">
+      <c r="C53" s="6">
         <v>28.65</v>
       </c>
-      <c r="E52" s="7">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
+      <c r="D53" s="6">
+        <v>35.27</v>
+      </c>
+      <c r="E53" s="7">
+        <v>6.62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C53" s="5">
-        <v>30.71</v>
-      </c>
-      <c r="D53" s="5">
+      <c r="C54" s="6">
         <v>27.97</v>
       </c>
-      <c r="E53" s="6">
-        <v>-2.74</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
+      <c r="D54" s="6">
+        <v>37.22</v>
+      </c>
+      <c r="E54" s="7">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="5">
-        <v>36.68</v>
-      </c>
-      <c r="D54" s="5">
+      <c r="C55" s="6">
         <v>36.2</v>
       </c>
-      <c r="E54" s="6">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
+      <c r="D55" s="6">
+        <v>31.34</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-4.86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B56" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C55" s="5">
-        <v>47.58</v>
-      </c>
-      <c r="D55" s="5">
+      <c r="C56" s="6">
         <v>41.13</v>
       </c>
-      <c r="E55" s="6">
-        <v>-6.45</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
+      <c r="D56" s="6">
+        <v>38.74</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-2.39</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="B57" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="5">
-        <v>-19.97</v>
-      </c>
-      <c r="D56" s="5">
+      <c r="C57" s="6">
         <v>-36.84</v>
       </c>
-      <c r="E56" s="6">
-        <v>-16.87</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
+      <c r="D57" s="6">
+        <v>-56.28</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-19.44</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B58" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="5">
-        <v>-0.59</v>
-      </c>
-      <c r="D57" s="5">
+      <c r="C58" s="6">
         <v>95.06</v>
       </c>
-      <c r="E57" s="7">
-        <v>95.65000000000001</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
+      <c r="D58" s="6">
+        <v>-47.47</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-142.53</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B59" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="5">
-        <v>23</v>
-      </c>
-      <c r="D58" s="5">
+      <c r="C59" s="6">
         <v>10.34</v>
       </c>
-      <c r="E58" s="6">
-        <v>-12.66</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
+      <c r="D59" s="6">
+        <v>-10.01</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-20.35</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="5">
-        <v>367.36</v>
-      </c>
-      <c r="D59" s="5">
+      <c r="C60" s="6">
         <v>59.24</v>
       </c>
-      <c r="E59" s="6">
-        <v>-308.12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
+      <c r="D60" s="6">
+        <v>19.17</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-40.07</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="5">
-        <v>26</v>
-      </c>
-      <c r="D60" s="5">
+      <c r="C61" s="6">
         <v>-1.59</v>
       </c>
-      <c r="E60" s="6">
-        <v>-27.59</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
+      <c r="D61" s="6">
+        <v>-45.17</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-43.58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="5">
-        <v>-13.71</v>
-      </c>
-      <c r="D61" s="5">
+      <c r="C62" s="6">
         <v>-7</v>
       </c>
-      <c r="E61" s="7">
-        <v>6.71</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
+      <c r="D62" s="6">
+        <v>-58.74</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-51.74</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B63" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="5">
-        <v>-58.12</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C63" s="6">
         <v>-4.16</v>
       </c>
-      <c r="E62" s="7">
-        <v>53.96</v>
+      <c r="D63" s="6">
+        <v>-61.88</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-57.72</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2841,60 +2933,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>56.8</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>40.5</v>
+      </c>
+      <c r="E2" s="11">
+        <v>60</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-3.7</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-2.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>56.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>37.9</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-5.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-1.6</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>60</v>
       </c>
     </row>
@@ -2996,49 +3088,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.4826</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2925</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2334</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1811</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1426</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.1061</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0762</v>
+      <c r="A2" s="14">
+        <v>0.4927</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2847</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2373</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1782</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.138</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1065</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0793</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="77">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,28 +187,31 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>49.7 → 57.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>49.7</t>
+  </si>
+  <si>
+    <t>57.3</t>
+  </si>
+  <si>
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>28.6 → 35.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>28.6</t>
-  </si>
-  <si>
-    <t>35.3</t>
-  </si>
-  <si>
-    <t>28.0 → 37.2</t>
-  </si>
-  <si>
-    <t>28.0</t>
-  </si>
-  <si>
-    <t>37.2</t>
+    <t>28.9 → 30.2</t>
+  </si>
+  <si>
+    <t>28.9</t>
+  </si>
+  <si>
+    <t>30.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -420,8 +423,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -933,10 +936,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1267.6</v>
+        <v>1269.6</v>
       </c>
       <c r="D2">
-        <v>2.25</v>
+        <v>0.16</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -945,46 +948,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-2.23</v>
+        <v>-2.07</v>
       </c>
       <c r="H2">
-        <v>69.39</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="I2">
-        <v>-0.85</v>
+        <v>1.75</v>
       </c>
       <c r="J2">
-        <v>18.3</v>
+        <v>17.77</v>
       </c>
       <c r="K2">
-        <v>10.76</v>
+        <v>14.78</v>
       </c>
       <c r="L2">
-        <v>39.27</v>
+        <v>37.57</v>
       </c>
       <c r="M2">
-        <v>7.93</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P2">
-        <v>1241.62</v>
+        <v>1245.98</v>
       </c>
       <c r="Q2">
-        <v>1165.96</v>
+        <v>1172.91</v>
       </c>
       <c r="R2">
-        <v>1129.01</v>
+        <v>1133.11</v>
       </c>
       <c r="S2">
-        <v>978.16</v>
+        <v>980.2</v>
       </c>
       <c r="T2">
-        <v>29.59</v>
+        <v>29.52</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -999,34 +1002,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>62.44</v>
+        <v>62.64</v>
       </c>
       <c r="Z2">
-        <v>41.5</v>
+        <v>42.56</v>
       </c>
       <c r="AA2">
-        <v>31.56</v>
+        <v>33.76</v>
       </c>
       <c r="AB2">
-        <v>9.94</v>
+        <v>8.81</v>
       </c>
       <c r="AC2">
-        <v>67.22</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="AD2">
-        <v>64.61</v>
+        <v>65.14</v>
       </c>
       <c r="AE2">
-        <v>54.49</v>
+        <v>53.15</v>
       </c>
       <c r="AF2">
-        <v>-56.28</v>
+        <v>-39.25</v>
       </c>
       <c r="AG2">
-        <v>1338.56</v>
+        <v>1350.64</v>
       </c>
       <c r="AH2">
-        <v>993.36</v>
+        <v>995.1799999999999</v>
       </c>
       <c r="AI2">
         <v>1148.32</v>
@@ -1035,7 +1038,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>43.82</v>
+        <v>44.46</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1046,10 +1049,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>882.3</v>
+        <v>912</v>
       </c>
       <c r="D3">
-        <v>0.38</v>
+        <v>3.37</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1058,46 +1061,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-9.65</v>
+        <v>-6.61</v>
       </c>
       <c r="H3">
-        <v>66.64</v>
+        <v>72.23999999999999</v>
       </c>
       <c r="I3">
-        <v>-0.42</v>
+        <v>5.43</v>
       </c>
       <c r="J3">
-        <v>0.52</v>
+        <v>1.9</v>
       </c>
       <c r="K3">
-        <v>-4.62</v>
+        <v>0.16</v>
       </c>
       <c r="L3">
-        <v>18.33</v>
+        <v>23.36</v>
       </c>
       <c r="M3">
-        <v>49.27</v>
+        <v>51.75</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="P3">
-        <v>867.71</v>
+        <v>877.11</v>
       </c>
       <c r="Q3">
-        <v>887.05</v>
+        <v>888.1</v>
       </c>
       <c r="R3">
-        <v>880.25</v>
+        <v>881.14</v>
       </c>
       <c r="S3">
-        <v>795.86</v>
+        <v>797.0599999999999</v>
       </c>
       <c r="T3">
-        <v>10.86</v>
+        <v>14.42</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1112,34 +1115,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>49.68</v>
+        <v>57.28</v>
       </c>
       <c r="Z3">
-        <v>-4.43</v>
+        <v>-1.45</v>
       </c>
       <c r="AA3">
-        <v>-2.53</v>
+        <v>-2.31</v>
       </c>
       <c r="AB3">
-        <v>-1.9</v>
+        <v>0.87</v>
       </c>
       <c r="AC3">
-        <v>41.13</v>
+        <v>73.55</v>
       </c>
       <c r="AD3">
-        <v>23.89</v>
+        <v>45.63</v>
       </c>
       <c r="AE3">
-        <v>24.19</v>
+        <v>24.68</v>
       </c>
       <c r="AF3">
-        <v>-47.47</v>
+        <v>5.06</v>
       </c>
       <c r="AG3">
-        <v>930.13</v>
+        <v>932.59</v>
       </c>
       <c r="AH3">
-        <v>843.98</v>
+        <v>843.62</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1148,7 +1151,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>17.48</v>
+        <v>18.46</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1159,10 +1162,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1605.4</v>
+        <v>1611</v>
       </c>
       <c r="D4">
-        <v>1.61</v>
+        <v>0.35</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1171,46 +1174,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-17.25</v>
+        <v>-16.96</v>
       </c>
       <c r="H4">
-        <v>18.51</v>
+        <v>18.92</v>
       </c>
       <c r="I4">
-        <v>-3.45</v>
+        <v>-1.42</v>
       </c>
       <c r="J4">
-        <v>-12.08</v>
+        <v>-12.89</v>
       </c>
       <c r="K4">
-        <v>-13.25</v>
+        <v>-13.08</v>
       </c>
       <c r="L4">
-        <v>0.9399999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="M4">
-        <v>23.73</v>
+        <v>23.75</v>
       </c>
       <c r="N4">
         <v>43</v>
       </c>
       <c r="O4">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="P4">
-        <v>1613.38</v>
+        <v>1608.74</v>
       </c>
       <c r="Q4">
-        <v>1743.73</v>
+        <v>1732.33</v>
       </c>
       <c r="R4">
-        <v>1812.97</v>
+        <v>1810.7</v>
       </c>
       <c r="S4">
-        <v>1680.4</v>
+        <v>1679.88</v>
       </c>
       <c r="T4">
-        <v>-4.46</v>
+        <v>-4.1</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1225,34 +1228,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>28.95</v>
+        <v>30.18</v>
       </c>
       <c r="Z4">
-        <v>-61.72</v>
+        <v>-62.27</v>
       </c>
       <c r="AA4">
-        <v>-43.57</v>
+        <v>-47.31</v>
       </c>
       <c r="AB4">
-        <v>-18.15</v>
+        <v>-14.96</v>
       </c>
       <c r="AC4">
-        <v>8.789999999999999</v>
+        <v>19.49</v>
       </c>
       <c r="AD4">
-        <v>2.93</v>
+        <v>9.43</v>
       </c>
       <c r="AE4">
-        <v>47.9</v>
+        <v>46.03</v>
       </c>
       <c r="AF4">
-        <v>-10.01</v>
+        <v>-39.02</v>
       </c>
       <c r="AG4">
-        <v>1928.68</v>
+        <v>1920.63</v>
       </c>
       <c r="AH4">
-        <v>1558.78</v>
+        <v>1544.03</v>
       </c>
       <c r="AI4">
         <v>1739.1</v>
@@ -1261,7 +1264,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>57.57</v>
+        <v>59.89</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1272,10 +1275,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1801.4</v>
+        <v>1788.3</v>
       </c>
       <c r="D5">
-        <v>2.14</v>
+        <v>-0.73</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1284,46 +1287,46 @@
         <v>1745.6</v>
       </c>
       <c r="G5">
-        <v>-24.9</v>
+        <v>-25.45</v>
       </c>
       <c r="H5">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="I5">
-        <v>-8.27</v>
+        <v>-5.83</v>
       </c>
       <c r="J5">
-        <v>-5.91</v>
+        <v>-7.4</v>
       </c>
       <c r="K5">
-        <v>-12.36</v>
+        <v>-13.79</v>
       </c>
       <c r="L5">
-        <v>-19.21</v>
+        <v>-20.15</v>
       </c>
       <c r="M5">
-        <v>17.82</v>
+        <v>16.81</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="P5">
-        <v>1803.04</v>
+        <v>1780.88</v>
       </c>
       <c r="Q5">
-        <v>1914.38</v>
+        <v>1906.86</v>
       </c>
       <c r="R5">
-        <v>1977.57</v>
+        <v>1973.72</v>
       </c>
       <c r="S5">
-        <v>2054.97</v>
+        <v>2052.39</v>
       </c>
       <c r="T5">
-        <v>-12.34</v>
+        <v>-12.87</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1338,34 +1341,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>35.27</v>
+        <v>34.09</v>
       </c>
       <c r="Z5">
-        <v>-46.61</v>
+        <v>-49.2</v>
       </c>
       <c r="AA5">
-        <v>-29.77</v>
+        <v>-33.66</v>
       </c>
       <c r="AB5">
-        <v>-16.84</v>
+        <v>-15.54</v>
       </c>
       <c r="AC5">
-        <v>10.26</v>
+        <v>17.94</v>
       </c>
       <c r="AD5">
-        <v>3.81</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="AE5">
-        <v>56.39</v>
+        <v>55.26</v>
       </c>
       <c r="AF5">
-        <v>19.17</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="AG5">
-        <v>2059.84</v>
+        <v>2062.23</v>
       </c>
       <c r="AH5">
-        <v>1768.92</v>
+        <v>1751.48</v>
       </c>
       <c r="AI5">
         <v>1907.26</v>
@@ -1374,7 +1377,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>36.56</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1385,10 +1388,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>691.95</v>
+        <v>699.2</v>
       </c>
       <c r="D6">
-        <v>2.58</v>
+        <v>1.05</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1397,46 +1400,46 @@
         <v>674.55</v>
       </c>
       <c r="G6">
-        <v>-36.51</v>
+        <v>-35.84</v>
       </c>
       <c r="H6">
-        <v>2.58</v>
+        <v>3.65</v>
       </c>
       <c r="I6">
-        <v>-1.82</v>
+        <v>-1.03</v>
       </c>
       <c r="J6">
-        <v>-13.58</v>
+        <v>-10.16</v>
       </c>
       <c r="K6">
-        <v>-9.800000000000001</v>
+        <v>-6.82</v>
       </c>
       <c r="L6">
-        <v>-31.68</v>
+        <v>-31.82</v>
       </c>
       <c r="M6">
-        <v>10.65</v>
+        <v>11.05</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P6">
-        <v>691.02</v>
+        <v>689.5700000000001</v>
       </c>
       <c r="Q6">
-        <v>714.5700000000001</v>
+        <v>710.46</v>
       </c>
       <c r="R6">
-        <v>759.85</v>
+        <v>758.67</v>
       </c>
       <c r="S6">
-        <v>821.73</v>
+        <v>820.09</v>
       </c>
       <c r="T6">
-        <v>-15.79</v>
+        <v>-14.74</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1451,34 +1454,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>37.22</v>
+        <v>40.64</v>
       </c>
       <c r="Z6">
-        <v>-22.56</v>
+        <v>-20.97</v>
       </c>
       <c r="AA6">
-        <v>-21.81</v>
+        <v>-21.64</v>
       </c>
       <c r="AB6">
-        <v>-0.74</v>
+        <v>0.67</v>
       </c>
       <c r="AC6">
-        <v>53.16</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="AD6">
-        <v>48.45</v>
+        <v>54.34</v>
       </c>
       <c r="AE6">
-        <v>20.54</v>
+        <v>20.41</v>
       </c>
       <c r="AF6">
-        <v>-45.17</v>
+        <v>-7.77</v>
       </c>
       <c r="AG6">
-        <v>776.85</v>
+        <v>764.49</v>
       </c>
       <c r="AH6">
-        <v>652.28</v>
+        <v>656.4299999999999</v>
       </c>
       <c r="AI6">
         <v>739.76</v>
@@ -1487,7 +1490,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>45.25</v>
+        <v>39.23</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1498,10 +1501,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2815.3</v>
+        <v>2819.1</v>
       </c>
       <c r="D7">
-        <v>-2.71</v>
+        <v>0.13</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1510,25 +1513,25 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-18.51</v>
+        <v>-18.4</v>
       </c>
       <c r="H7">
-        <v>48.84</v>
+        <v>49.04</v>
       </c>
       <c r="I7">
-        <v>-6.26</v>
+        <v>-3.77</v>
       </c>
       <c r="J7">
-        <v>-13.69</v>
+        <v>-13.72</v>
       </c>
       <c r="K7">
-        <v>12.86</v>
+        <v>11.19</v>
       </c>
       <c r="L7">
-        <v>30.1</v>
+        <v>28.87</v>
       </c>
       <c r="M7">
-        <v>28.47</v>
+        <v>28.08</v>
       </c>
       <c r="N7">
         <v>85</v>
@@ -1537,16 +1540,16 @@
         <v>77</v>
       </c>
       <c r="P7">
-        <v>2893.16</v>
+        <v>2871.1</v>
       </c>
       <c r="Q7">
-        <v>3048.73</v>
+        <v>3029.96</v>
       </c>
       <c r="R7">
-        <v>2995.12</v>
+        <v>3000.17</v>
       </c>
       <c r="S7">
-        <v>2505.71</v>
+        <v>2509.04</v>
       </c>
       <c r="T7">
         <v>12.36</v>
@@ -1564,43 +1567,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>31.34</v>
+        <v>31.82</v>
       </c>
       <c r="Z7">
-        <v>-52.5</v>
+        <v>-60.29</v>
       </c>
       <c r="AA7">
-        <v>-16.02</v>
+        <v>-24.88</v>
       </c>
       <c r="AB7">
-        <v>-36.48</v>
+        <v>-35.41</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>0.84</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="AE7">
-        <v>121.87</v>
+        <v>118.33</v>
       </c>
       <c r="AF7">
-        <v>-58.74</v>
+        <v>-38.76</v>
       </c>
       <c r="AG7">
-        <v>3282</v>
+        <v>3273.99</v>
       </c>
       <c r="AH7">
-        <v>2815.47</v>
+        <v>2785.93</v>
       </c>
       <c r="AI7">
-        <v>3225.62</v>
+        <v>3168.88</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>32.77</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1611,10 +1614,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8016.5</v>
+        <v>8097.5</v>
       </c>
       <c r="D8">
-        <v>-1.23</v>
+        <v>1.01</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1623,46 +1626,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-11.99</v>
+        <v>-11.1</v>
       </c>
       <c r="H8">
-        <v>35.31</v>
+        <v>36.68</v>
       </c>
       <c r="I8">
-        <v>-7.28</v>
+        <v>-4.27</v>
       </c>
       <c r="J8">
-        <v>0.31</v>
+        <v>-2.52</v>
       </c>
       <c r="K8">
-        <v>-0.78</v>
+        <v>2.45</v>
       </c>
       <c r="L8">
-        <v>-9.539999999999999</v>
+        <v>-7.61</v>
       </c>
       <c r="M8">
-        <v>13.8</v>
+        <v>14.29</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="P8">
-        <v>8267.6</v>
+        <v>8195.299999999999</v>
       </c>
       <c r="Q8">
-        <v>8493.15</v>
+        <v>8490.02</v>
       </c>
       <c r="R8">
-        <v>8274.620000000001</v>
+        <v>8275.08</v>
       </c>
       <c r="S8">
-        <v>7440.47</v>
+        <v>7440.18</v>
       </c>
       <c r="T8">
-        <v>7.74</v>
+        <v>8.83</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1677,34 +1680,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>38.74</v>
+        <v>41.71</v>
       </c>
       <c r="Z8">
-        <v>3.5</v>
+        <v>-19.5</v>
       </c>
       <c r="AA8">
-        <v>87.05</v>
+        <v>65.73999999999999</v>
       </c>
       <c r="AB8">
-        <v>-83.56</v>
+        <v>-85.25</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE8">
-        <v>306.21</v>
+        <v>293.98</v>
       </c>
       <c r="AF8">
-        <v>-61.88</v>
+        <v>-77.86</v>
       </c>
       <c r="AG8">
-        <v>8958.01</v>
+        <v>8965.040000000001</v>
       </c>
       <c r="AH8">
-        <v>8028.29</v>
+        <v>8015.01</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
@@ -1713,7 +1716,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>33.98</v>
+        <v>34.2</v>
       </c>
     </row>
   </sheetData>
@@ -1894,7 +1897,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1914,27 +1917,27 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1946,16 +1949,16 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1966,13 +1969,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>12.65</v>
+        <v>18.3</v>
       </c>
       <c r="D8" s="6">
-        <v>18.3</v>
+        <v>17.77</v>
       </c>
       <c r="E8" s="7">
-        <v>5.65</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1983,13 +1986,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-0.73</v>
+        <v>0.52</v>
       </c>
       <c r="D9" s="6">
-        <v>0.52</v>
-      </c>
-      <c r="E9" s="7">
-        <v>1.25</v>
+        <v>1.9</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.38</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2000,13 +2003,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-12.93</v>
+        <v>-12.08</v>
       </c>
       <c r="D10" s="6">
-        <v>-12.08</v>
+        <v>-12.89</v>
       </c>
       <c r="E10" s="7">
-        <v>0.85</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2017,13 +2020,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-8.279999999999999</v>
+        <v>-5.91</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.91</v>
+        <v>-7.4</v>
       </c>
       <c r="E11" s="7">
-        <v>2.37</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2034,13 +2037,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-15.21</v>
+        <v>-13.58</v>
       </c>
       <c r="D12" s="6">
-        <v>-13.58</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.63</v>
+        <v>-10.16</v>
+      </c>
+      <c r="E12" s="8">
+        <v>3.42</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2051,13 +2054,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-11.44</v>
+        <v>-13.69</v>
       </c>
       <c r="D13" s="6">
-        <v>-13.69</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-2.25</v>
+        <v>-13.72</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2068,13 +2071,13 @@
         <v>9</v>
       </c>
       <c r="C14" s="6">
-        <v>0.14</v>
+        <v>0.31</v>
       </c>
       <c r="D14" s="6">
-        <v>0.31</v>
+        <v>-2.52</v>
       </c>
       <c r="E14" s="7">
-        <v>0.17</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2085,13 +2088,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-4.38</v>
+        <v>-0.85</v>
       </c>
       <c r="D15" s="6">
-        <v>-0.85</v>
-      </c>
-      <c r="E15" s="7">
-        <v>3.53</v>
+        <v>1.75</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.6</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2102,13 +2105,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-0.87</v>
+        <v>-0.42</v>
       </c>
       <c r="D16" s="6">
-        <v>-0.42</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.45</v>
+        <v>5.43</v>
+      </c>
+      <c r="E16" s="8">
+        <v>5.85</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2119,13 +2122,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-6.05</v>
+        <v>-3.45</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.45</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2.6</v>
+        <v>-1.42</v>
+      </c>
+      <c r="E17" s="8">
+        <v>2.03</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2136,13 +2139,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-9.210000000000001</v>
+        <v>-8.27</v>
       </c>
       <c r="D18" s="6">
-        <v>-8.27</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.9399999999999999</v>
+        <v>-5.83</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.44</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2153,13 +2156,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-2.18</v>
+        <v>-1.82</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.82</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.36</v>
+        <v>-1.03</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.79</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2170,13 +2173,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-4.59</v>
+        <v>-6.26</v>
       </c>
       <c r="D20" s="6">
-        <v>-6.26</v>
+        <v>-3.77</v>
       </c>
       <c r="E20" s="8">
-        <v>-1.67</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2187,13 +2190,13 @@
         <v>8</v>
       </c>
       <c r="C21" s="6">
-        <v>-4.8</v>
+        <v>-7.28</v>
       </c>
       <c r="D21" s="6">
-        <v>-7.28</v>
+        <v>-4.27</v>
       </c>
       <c r="E21" s="8">
-        <v>-2.48</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2204,13 +2207,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>35.02</v>
+        <v>39.27</v>
       </c>
       <c r="D22" s="6">
-        <v>39.27</v>
+        <v>37.57</v>
       </c>
       <c r="E22" s="7">
-        <v>4.25</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2221,13 +2224,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>19.14</v>
+        <v>18.33</v>
       </c>
       <c r="D23" s="6">
-        <v>18.33</v>
+        <v>23.36</v>
       </c>
       <c r="E23" s="8">
-        <v>-0.8100000000000001</v>
+        <v>5.03</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2238,13 +2241,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>0.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D24" s="6">
-        <v>0.9399999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="E24" s="7">
-        <v>0.22</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2255,13 +2258,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-19.03</v>
+        <v>-19.21</v>
       </c>
       <c r="D25" s="6">
-        <v>-19.21</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.18</v>
+        <v>-20.15</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2272,13 +2275,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>-34.61</v>
+        <v>-31.68</v>
       </c>
       <c r="D26" s="6">
-        <v>-31.68</v>
+        <v>-31.82</v>
       </c>
       <c r="E26" s="7">
-        <v>2.93</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2289,13 +2292,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>25.49</v>
+        <v>30.1</v>
       </c>
       <c r="D27" s="6">
-        <v>30.1</v>
+        <v>28.87</v>
       </c>
       <c r="E27" s="7">
-        <v>4.61</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2306,13 +2309,13 @@
         <v>11</v>
       </c>
       <c r="C28" s="6">
-        <v>-8.02</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="D28" s="6">
-        <v>-9.539999999999999</v>
+        <v>-7.61</v>
       </c>
       <c r="E28" s="8">
-        <v>-1.52</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2323,13 +2326,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>8.779999999999999</v>
+        <v>10.76</v>
       </c>
       <c r="D29" s="6">
-        <v>10.76</v>
-      </c>
-      <c r="E29" s="7">
-        <v>1.98</v>
+        <v>14.78</v>
+      </c>
+      <c r="E29" s="8">
+        <v>4.02</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2340,13 +2343,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-1.52</v>
+        <v>-4.62</v>
       </c>
       <c r="D30" s="6">
-        <v>-4.62</v>
+        <v>0.16</v>
       </c>
       <c r="E30" s="8">
-        <v>-3.1</v>
+        <v>4.78</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2357,13 +2360,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-11.72</v>
+        <v>-13.25</v>
       </c>
       <c r="D31" s="6">
-        <v>-13.25</v>
+        <v>-13.08</v>
       </c>
       <c r="E31" s="8">
-        <v>-1.53</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2374,13 +2377,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-13.31</v>
+        <v>-12.36</v>
       </c>
       <c r="D32" s="6">
-        <v>-12.36</v>
+        <v>-13.79</v>
       </c>
       <c r="E32" s="7">
-        <v>0.95</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2391,13 +2394,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>-9.140000000000001</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="D33" s="6">
-        <v>-9.800000000000001</v>
+        <v>-6.82</v>
       </c>
       <c r="E33" s="8">
-        <v>-0.66</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2408,13 +2411,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>15.3</v>
+        <v>12.86</v>
       </c>
       <c r="D34" s="6">
-        <v>12.86</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-2.44</v>
+        <v>11.19</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.67</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2425,13 +2428,13 @@
         <v>10</v>
       </c>
       <c r="C35" s="6">
-        <v>0.6899999999999999</v>
+        <v>-0.78</v>
       </c>
       <c r="D35" s="6">
-        <v>-0.78</v>
+        <v>2.45</v>
       </c>
       <c r="E35" s="8">
-        <v>-1.47</v>
+        <v>3.23</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2442,13 +2445,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-4.38</v>
+        <v>-2.23</v>
       </c>
       <c r="D36" s="6">
-        <v>-2.23</v>
-      </c>
-      <c r="E36" s="7">
-        <v>2.15</v>
+        <v>-2.07</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.16</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2459,13 +2462,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-9.98</v>
+        <v>-9.65</v>
       </c>
       <c r="D37" s="6">
-        <v>-9.65</v>
-      </c>
-      <c r="E37" s="7">
-        <v>0.33</v>
+        <v>-6.61</v>
+      </c>
+      <c r="E37" s="8">
+        <v>3.04</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2476,13 +2479,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-18.56</v>
+        <v>-17.25</v>
       </c>
       <c r="D38" s="6">
-        <v>-17.25</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1.31</v>
+        <v>-16.96</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2493,13 +2496,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-26.48</v>
+        <v>-24.9</v>
       </c>
       <c r="D39" s="6">
-        <v>-24.9</v>
+        <v>-25.45</v>
       </c>
       <c r="E39" s="7">
-        <v>1.58</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2510,13 +2513,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-38.1</v>
+        <v>-36.51</v>
       </c>
       <c r="D40" s="6">
-        <v>-36.51</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.59</v>
+        <v>-35.84</v>
+      </c>
+      <c r="E40" s="8">
+        <v>0.67</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2527,13 +2530,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-16.24</v>
+        <v>-18.51</v>
       </c>
       <c r="D41" s="6">
-        <v>-18.51</v>
+        <v>-18.4</v>
       </c>
       <c r="E41" s="8">
-        <v>-2.27</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2544,13 +2547,13 @@
         <v>6</v>
       </c>
       <c r="C42" s="6">
-        <v>-10.9</v>
+        <v>-11.99</v>
       </c>
       <c r="D42" s="6">
-        <v>-11.99</v>
+        <v>-11.1</v>
       </c>
       <c r="E42" s="8">
-        <v>-1.09</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2561,13 +2564,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>1239.7</v>
+        <v>1267.6</v>
       </c>
       <c r="D43" s="6">
-        <v>1267.6</v>
-      </c>
-      <c r="E43" s="7">
-        <v>27.9</v>
+        <v>1269.6</v>
+      </c>
+      <c r="E43" s="8">
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2578,13 +2581,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>879</v>
+        <v>882.3</v>
       </c>
       <c r="D44" s="6">
-        <v>882.3</v>
-      </c>
-      <c r="E44" s="7">
-        <v>3.3</v>
+        <v>912</v>
+      </c>
+      <c r="E44" s="8">
+        <v>29.7</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2595,13 +2598,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>1580</v>
+        <v>1605.4</v>
       </c>
       <c r="D45" s="6">
-        <v>1605.4</v>
-      </c>
-      <c r="E45" s="7">
-        <v>25.4</v>
+        <v>1611</v>
+      </c>
+      <c r="E45" s="8">
+        <v>5.6</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2612,13 +2615,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>1763.6</v>
+        <v>1801.4</v>
       </c>
       <c r="D46" s="6">
-        <v>1801.4</v>
+        <v>1788.3</v>
       </c>
       <c r="E46" s="7">
-        <v>37.8</v>
+        <v>-13.1</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2629,13 +2632,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>674.55</v>
+        <v>691.95</v>
       </c>
       <c r="D47" s="6">
-        <v>691.95</v>
-      </c>
-      <c r="E47" s="7">
-        <v>17.4</v>
+        <v>699.2</v>
+      </c>
+      <c r="E47" s="8">
+        <v>7.25</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2646,13 +2649,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>2893.8</v>
+        <v>2815.3</v>
       </c>
       <c r="D48" s="6">
-        <v>2815.3</v>
+        <v>2819.1</v>
       </c>
       <c r="E48" s="8">
-        <v>-78.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2663,13 +2666,13 @@
         <v>2</v>
       </c>
       <c r="C49" s="6">
-        <v>8116</v>
+        <v>8016.5</v>
       </c>
       <c r="D49" s="6">
-        <v>8016.5</v>
+        <v>8097.5</v>
       </c>
       <c r="E49" s="8">
-        <v>-99.5</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2680,13 +2683,13 @@
         <v>24</v>
       </c>
       <c r="C50" s="6">
-        <v>59.65</v>
+        <v>62.44</v>
       </c>
       <c r="D50" s="6">
-        <v>62.44</v>
-      </c>
-      <c r="E50" s="7">
-        <v>2.79</v>
+        <v>62.64</v>
+      </c>
+      <c r="E50" s="8">
+        <v>0.2</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2697,13 +2700,13 @@
         <v>24</v>
       </c>
       <c r="C51" s="6">
-        <v>48.74</v>
+        <v>49.68</v>
       </c>
       <c r="D51" s="6">
-        <v>49.68</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.9399999999999999</v>
+        <v>57.28</v>
+      </c>
+      <c r="E51" s="8">
+        <v>7.6</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2714,13 +2717,13 @@
         <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>23.27</v>
+        <v>28.95</v>
       </c>
       <c r="D52" s="6">
-        <v>28.95</v>
-      </c>
-      <c r="E52" s="7">
-        <v>5.68</v>
+        <v>30.18</v>
+      </c>
+      <c r="E52" s="8">
+        <v>1.23</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2731,13 +2734,13 @@
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>28.65</v>
+        <v>35.27</v>
       </c>
       <c r="D53" s="6">
-        <v>35.27</v>
+        <v>34.09</v>
       </c>
       <c r="E53" s="7">
-        <v>6.62</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2748,13 +2751,13 @@
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>27.97</v>
+        <v>37.22</v>
       </c>
       <c r="D54" s="6">
-        <v>37.22</v>
-      </c>
-      <c r="E54" s="7">
-        <v>9.25</v>
+        <v>40.64</v>
+      </c>
+      <c r="E54" s="8">
+        <v>3.42</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2765,13 +2768,13 @@
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>36.2</v>
+        <v>31.34</v>
       </c>
       <c r="D55" s="6">
-        <v>31.34</v>
+        <v>31.82</v>
       </c>
       <c r="E55" s="8">
-        <v>-4.86</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2782,13 +2785,13 @@
         <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>41.13</v>
+        <v>38.74</v>
       </c>
       <c r="D56" s="6">
-        <v>38.74</v>
+        <v>41.71</v>
       </c>
       <c r="E56" s="8">
-        <v>-2.39</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2799,13 +2802,13 @@
         <v>31</v>
       </c>
       <c r="C57" s="6">
-        <v>-36.84</v>
+        <v>-56.28</v>
       </c>
       <c r="D57" s="6">
-        <v>-56.28</v>
+        <v>-39.25</v>
       </c>
       <c r="E57" s="8">
-        <v>-19.44</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2816,13 +2819,13 @@
         <v>31</v>
       </c>
       <c r="C58" s="6">
-        <v>95.06</v>
+        <v>-47.47</v>
       </c>
       <c r="D58" s="6">
-        <v>-47.47</v>
+        <v>5.06</v>
       </c>
       <c r="E58" s="8">
-        <v>-142.53</v>
+        <v>52.53</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2833,13 +2836,13 @@
         <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>10.34</v>
+        <v>-10.01</v>
       </c>
       <c r="D59" s="6">
-        <v>-10.01</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-20.35</v>
+        <v>-39.02</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-29.01</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2850,13 +2853,13 @@
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>59.24</v>
+        <v>19.17</v>
       </c>
       <c r="D60" s="6">
-        <v>19.17</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-40.07</v>
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-27.8</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2867,13 +2870,13 @@
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>-1.59</v>
+        <v>-45.17</v>
       </c>
       <c r="D61" s="6">
-        <v>-45.17</v>
+        <v>-7.77</v>
       </c>
       <c r="E61" s="8">
-        <v>-43.58</v>
+        <v>37.4</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2884,13 +2887,13 @@
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>-7</v>
+        <v>-58.74</v>
       </c>
       <c r="D62" s="6">
-        <v>-58.74</v>
+        <v>-38.76</v>
       </c>
       <c r="E62" s="8">
-        <v>-51.74</v>
+        <v>19.98</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -2901,13 +2904,13 @@
         <v>31</v>
       </c>
       <c r="C63" s="6">
-        <v>-4.16</v>
+        <v>-61.88</v>
       </c>
       <c r="D63" s="6">
-        <v>-61.88</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-57.72</v>
+        <v>-77.86</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-15.98</v>
       </c>
     </row>
   </sheetData>
@@ -2937,28 +2940,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2972,16 +2975,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>40.5</v>
+        <v>42.6</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.7</v>
+        <v>-3.9</v>
       </c>
       <c r="G2" s="11">
-        <v>-2.5</v>
+        <v>-0.7</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3112,25 +3115,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.4927</v>
+        <v>0.5175</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2847</v>
+        <v>0.2808</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2373</v>
+        <v>0.2375</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1782</v>
+        <v>0.1681</v>
       </c>
       <c r="E2" s="14">
-        <v>0.138</v>
+        <v>0.1429</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1065</v>
+        <v>0.1105</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0793</v>
+        <v>0.0828</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,46 +172,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>49.7 → 57.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.7</t>
-  </si>
-  <si>
-    <t>57.3</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.9 → 30.2</t>
-  </si>
-  <si>
-    <t>28.9</t>
-  </si>
-  <si>
-    <t>30.2</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -297,14 +258,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -337,13 +298,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -413,18 +374,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -936,10 +896,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1269.6</v>
+        <v>1256.7</v>
       </c>
       <c r="D2">
-        <v>0.16</v>
+        <v>-1.02</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -948,25 +908,25 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-2.07</v>
+        <v>-3.07</v>
       </c>
       <c r="H2">
-        <v>69.65000000000001</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="I2">
-        <v>1.75</v>
+        <v>4.68</v>
       </c>
       <c r="J2">
-        <v>17.77</v>
+        <v>11.15</v>
       </c>
       <c r="K2">
-        <v>14.78</v>
+        <v>16.31</v>
       </c>
       <c r="L2">
-        <v>37.57</v>
+        <v>37.39</v>
       </c>
       <c r="M2">
-        <v>8.279999999999999</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -975,19 +935,19 @@
         <v>85</v>
       </c>
       <c r="P2">
-        <v>1245.98</v>
+        <v>1257.22</v>
       </c>
       <c r="Q2">
-        <v>1172.91</v>
+        <v>1180.54</v>
       </c>
       <c r="R2">
-        <v>1133.11</v>
+        <v>1136.79</v>
       </c>
       <c r="S2">
-        <v>980.2</v>
+        <v>982.25</v>
       </c>
       <c r="T2">
-        <v>29.52</v>
+        <v>27.94</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1002,34 +962,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>62.64</v>
+        <v>60.41</v>
       </c>
       <c r="Z2">
-        <v>42.56</v>
+        <v>41.88</v>
       </c>
       <c r="AA2">
-        <v>33.76</v>
+        <v>35.38</v>
       </c>
       <c r="AB2">
-        <v>8.81</v>
+        <v>6.5</v>
       </c>
       <c r="AC2">
-        <v>66.81999999999999</v>
+        <v>62.4</v>
       </c>
       <c r="AD2">
-        <v>65.14</v>
+        <v>65.48</v>
       </c>
       <c r="AE2">
-        <v>53.15</v>
+        <v>51.59</v>
       </c>
       <c r="AF2">
-        <v>-39.25</v>
+        <v>-80.48999999999999</v>
       </c>
       <c r="AG2">
-        <v>1350.64</v>
+        <v>1358.93</v>
       </c>
       <c r="AH2">
-        <v>995.1799999999999</v>
+        <v>1002.16</v>
       </c>
       <c r="AI2">
         <v>1148.32</v>
@@ -1038,7 +998,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>44.46</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1049,10 +1009,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>912</v>
+        <v>894.5</v>
       </c>
       <c r="D3">
-        <v>3.37</v>
+        <v>-1.92</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1061,46 +1021,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-6.61</v>
+        <v>-8.4</v>
       </c>
       <c r="H3">
-        <v>72.23999999999999</v>
+        <v>68.94</v>
       </c>
       <c r="I3">
-        <v>5.43</v>
+        <v>4.25</v>
       </c>
       <c r="J3">
-        <v>1.9</v>
+        <v>0.39</v>
       </c>
       <c r="K3">
-        <v>0.16</v>
+        <v>-1.5</v>
       </c>
       <c r="L3">
-        <v>23.36</v>
+        <v>21.18</v>
       </c>
       <c r="M3">
-        <v>51.75</v>
+        <v>50.63</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="P3">
-        <v>877.11</v>
+        <v>884.4</v>
       </c>
       <c r="Q3">
-        <v>888.1</v>
+        <v>888.08</v>
       </c>
       <c r="R3">
-        <v>881.14</v>
+        <v>881.48</v>
       </c>
       <c r="S3">
-        <v>797.0599999999999</v>
+        <v>798.1900000000001</v>
       </c>
       <c r="T3">
-        <v>14.42</v>
+        <v>12.07</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1115,31 +1075,31 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>57.28</v>
+        <v>52.27</v>
       </c>
       <c r="Z3">
-        <v>-1.45</v>
+        <v>-0.49</v>
       </c>
       <c r="AA3">
-        <v>-2.31</v>
+        <v>-1.95</v>
       </c>
       <c r="AB3">
-        <v>0.87</v>
+        <v>1.46</v>
       </c>
       <c r="AC3">
-        <v>73.55</v>
+        <v>77.59</v>
       </c>
       <c r="AD3">
-        <v>45.63</v>
+        <v>64.09</v>
       </c>
       <c r="AE3">
-        <v>24.68</v>
+        <v>24.52</v>
       </c>
       <c r="AF3">
-        <v>5.06</v>
+        <v>-23.77</v>
       </c>
       <c r="AG3">
-        <v>932.59</v>
+        <v>932.54</v>
       </c>
       <c r="AH3">
         <v>843.62</v>
@@ -1151,7 +1111,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>18.46</v>
+        <v>19.3</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1162,10 +1122,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1611</v>
+        <v>1564.7</v>
       </c>
       <c r="D4">
-        <v>0.35</v>
+        <v>-2.87</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1174,46 +1134,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-16.96</v>
+        <v>-19.35</v>
       </c>
       <c r="H4">
-        <v>18.92</v>
+        <v>15.5</v>
       </c>
       <c r="I4">
-        <v>-1.42</v>
+        <v>-3.85</v>
       </c>
       <c r="J4">
-        <v>-12.89</v>
+        <v>-14.92</v>
       </c>
       <c r="K4">
-        <v>-13.08</v>
+        <v>-11.57</v>
       </c>
       <c r="L4">
-        <v>0.09</v>
+        <v>-2.46</v>
       </c>
       <c r="M4">
-        <v>23.75</v>
+        <v>22.02</v>
       </c>
       <c r="N4">
         <v>43</v>
       </c>
       <c r="O4">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="P4">
-        <v>1608.74</v>
+        <v>1596.22</v>
       </c>
       <c r="Q4">
-        <v>1732.33</v>
+        <v>1718.15</v>
       </c>
       <c r="R4">
-        <v>1810.7</v>
+        <v>1806.29</v>
       </c>
       <c r="S4">
-        <v>1679.88</v>
+        <v>1679.35</v>
       </c>
       <c r="T4">
-        <v>-4.1</v>
+        <v>-6.83</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1228,43 +1188,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>30.18</v>
+        <v>26.15</v>
       </c>
       <c r="Z4">
-        <v>-62.27</v>
+        <v>-65.69</v>
       </c>
       <c r="AA4">
-        <v>-47.31</v>
+        <v>-50.99</v>
       </c>
       <c r="AB4">
-        <v>-14.96</v>
+        <v>-14.7</v>
       </c>
       <c r="AC4">
-        <v>19.49</v>
+        <v>23.95</v>
       </c>
       <c r="AD4">
-        <v>9.43</v>
+        <v>17.41</v>
       </c>
       <c r="AE4">
-        <v>46.03</v>
+        <v>46.15</v>
       </c>
       <c r="AF4">
-        <v>-39.02</v>
+        <v>18.85</v>
       </c>
       <c r="AG4">
-        <v>1920.63</v>
+        <v>1912.32</v>
       </c>
       <c r="AH4">
-        <v>1544.03</v>
+        <v>1523.99</v>
       </c>
       <c r="AI4">
-        <v>1739.1</v>
+        <v>1727</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>59.89</v>
+        <v>62.61</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1275,58 +1235,58 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1788.3</v>
+        <v>1745.5</v>
       </c>
       <c r="D5">
-        <v>-0.73</v>
+        <v>-2.39</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
       </c>
       <c r="F5">
-        <v>1745.6</v>
+        <v>1745.5</v>
       </c>
       <c r="G5">
-        <v>-25.45</v>
+        <v>-27.23</v>
       </c>
       <c r="H5">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>-5.83</v>
+        <v>-2.64</v>
       </c>
       <c r="J5">
-        <v>-7.4</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="K5">
-        <v>-13.79</v>
+        <v>-13.12</v>
       </c>
       <c r="L5">
-        <v>-20.15</v>
+        <v>-22.15</v>
       </c>
       <c r="M5">
-        <v>16.81</v>
+        <v>16.23</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P5">
-        <v>1780.88</v>
+        <v>1771.4</v>
       </c>
       <c r="Q5">
-        <v>1906.86</v>
+        <v>1895.4</v>
       </c>
       <c r="R5">
-        <v>1973.72</v>
+        <v>1968.56</v>
       </c>
       <c r="S5">
-        <v>2052.39</v>
+        <v>2049.86</v>
       </c>
       <c r="T5">
-        <v>-12.87</v>
+        <v>-14.85</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1341,34 +1301,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>34.09</v>
+        <v>30.5</v>
       </c>
       <c r="Z5">
-        <v>-49.2</v>
+        <v>-54.08</v>
       </c>
       <c r="AA5">
-        <v>-33.66</v>
+        <v>-37.74</v>
       </c>
       <c r="AB5">
-        <v>-15.54</v>
+        <v>-16.34</v>
       </c>
       <c r="AC5">
-        <v>17.94</v>
+        <v>20.15</v>
       </c>
       <c r="AD5">
-        <v>9.789999999999999</v>
+        <v>16.11</v>
       </c>
       <c r="AE5">
-        <v>55.26</v>
+        <v>55.69</v>
       </c>
       <c r="AF5">
-        <v>-8.630000000000001</v>
+        <v>73.98</v>
       </c>
       <c r="AG5">
-        <v>2062.23</v>
+        <v>2063.04</v>
       </c>
       <c r="AH5">
-        <v>1751.48</v>
+        <v>1727.76</v>
       </c>
       <c r="AI5">
         <v>1907.26</v>
@@ -1377,7 +1337,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>36.52</v>
+        <v>38.07</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1388,10 +1348,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>699.2</v>
+        <v>699.55</v>
       </c>
       <c r="D6">
-        <v>1.05</v>
+        <v>0.05</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1400,46 +1360,46 @@
         <v>674.55</v>
       </c>
       <c r="G6">
-        <v>-35.84</v>
+        <v>-35.81</v>
       </c>
       <c r="H6">
-        <v>3.65</v>
+        <v>3.71</v>
       </c>
       <c r="I6">
-        <v>-1.03</v>
+        <v>0.47</v>
       </c>
       <c r="J6">
-        <v>-10.16</v>
+        <v>-10.47</v>
       </c>
       <c r="K6">
-        <v>-6.82</v>
+        <v>-3.11</v>
       </c>
       <c r="L6">
-        <v>-31.82</v>
+        <v>-32.41</v>
       </c>
       <c r="M6">
-        <v>11.05</v>
+        <v>11.03</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="P6">
-        <v>689.5700000000001</v>
+        <v>690.23</v>
       </c>
       <c r="Q6">
-        <v>710.46</v>
+        <v>706.55</v>
       </c>
       <c r="R6">
-        <v>758.67</v>
+        <v>757.24</v>
       </c>
       <c r="S6">
-        <v>820.09</v>
+        <v>818.52</v>
       </c>
       <c r="T6">
-        <v>-14.74</v>
+        <v>-14.54</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1454,34 +1414,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>40.64</v>
+        <v>40.81</v>
       </c>
       <c r="Z6">
-        <v>-20.97</v>
+        <v>-19.47</v>
       </c>
       <c r="AA6">
-        <v>-21.64</v>
+        <v>-21.21</v>
       </c>
       <c r="AB6">
-        <v>0.67</v>
+        <v>1.74</v>
       </c>
       <c r="AC6">
-        <v>72.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="AD6">
-        <v>54.34</v>
+        <v>75.09</v>
       </c>
       <c r="AE6">
-        <v>20.41</v>
+        <v>19.72</v>
       </c>
       <c r="AF6">
-        <v>-7.77</v>
+        <v>6.67</v>
       </c>
       <c r="AG6">
-        <v>764.49</v>
+        <v>750.46</v>
       </c>
       <c r="AH6">
-        <v>656.4299999999999</v>
+        <v>662.64</v>
       </c>
       <c r="AI6">
         <v>739.76</v>
@@ -1490,7 +1450,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>39.23</v>
+        <v>34.91</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1501,10 +1461,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2819.1</v>
+        <v>2715.4</v>
       </c>
       <c r="D7">
-        <v>0.13</v>
+        <v>-3.68</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1513,46 +1473,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-18.4</v>
+        <v>-21.4</v>
       </c>
       <c r="H7">
-        <v>49.04</v>
+        <v>43.56</v>
       </c>
       <c r="I7">
-        <v>-3.77</v>
+        <v>-7.21</v>
       </c>
       <c r="J7">
-        <v>-13.72</v>
+        <v>-15</v>
       </c>
       <c r="K7">
-        <v>11.19</v>
+        <v>7.98</v>
       </c>
       <c r="L7">
-        <v>28.87</v>
+        <v>21.06</v>
       </c>
       <c r="M7">
-        <v>28.08</v>
+        <v>26.92</v>
       </c>
       <c r="N7">
         <v>85</v>
       </c>
       <c r="O7">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="P7">
-        <v>2871.1</v>
+        <v>2828.9</v>
       </c>
       <c r="Q7">
-        <v>3029.96</v>
+        <v>3007.41</v>
       </c>
       <c r="R7">
-        <v>3000.17</v>
+        <v>3002.62</v>
       </c>
       <c r="S7">
-        <v>2509.04</v>
+        <v>2511.83</v>
       </c>
       <c r="T7">
-        <v>12.36</v>
+        <v>8.1</v>
       </c>
       <c r="U7" t="s">
         <v>45</v>
@@ -1567,43 +1527,43 @@
         <v>3</v>
       </c>
       <c r="Y7">
-        <v>31.82</v>
+        <v>26.42</v>
       </c>
       <c r="Z7">
-        <v>-60.29</v>
+        <v>-73.98</v>
       </c>
       <c r="AA7">
-        <v>-24.88</v>
+        <v>-34.7</v>
       </c>
       <c r="AB7">
-        <v>-35.41</v>
+        <v>-39.28</v>
       </c>
       <c r="AC7">
         <v>0.84</v>
       </c>
       <c r="AD7">
-        <v>0.28</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AE7">
-        <v>118.33</v>
+        <v>119.69</v>
       </c>
       <c r="AF7">
-        <v>-38.76</v>
+        <v>25.38</v>
       </c>
       <c r="AG7">
-        <v>3273.99</v>
+        <v>3280.03</v>
       </c>
       <c r="AH7">
-        <v>2785.93</v>
+        <v>2734.79</v>
       </c>
       <c r="AI7">
-        <v>3168.88</v>
+        <v>3115.86</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>36.3</v>
+        <v>40.89</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1614,10 +1574,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>8097.5</v>
+        <v>7991</v>
       </c>
       <c r="D8">
-        <v>1.01</v>
+        <v>-1.32</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1626,46 +1586,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-11.1</v>
+        <v>-12.27</v>
       </c>
       <c r="H8">
-        <v>36.68</v>
+        <v>34.88</v>
       </c>
       <c r="I8">
-        <v>-4.27</v>
+        <v>-4.81</v>
       </c>
       <c r="J8">
-        <v>-2.52</v>
+        <v>-2.07</v>
       </c>
       <c r="K8">
-        <v>2.45</v>
+        <v>4.26</v>
       </c>
       <c r="L8">
-        <v>-7.61</v>
+        <v>-9.76</v>
       </c>
       <c r="M8">
-        <v>14.29</v>
+        <v>14.01</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P8">
-        <v>8195.299999999999</v>
+        <v>8114.5</v>
       </c>
       <c r="Q8">
-        <v>8490.02</v>
+        <v>8472.58</v>
       </c>
       <c r="R8">
-        <v>8275.08</v>
+        <v>8268.85</v>
       </c>
       <c r="S8">
-        <v>7440.18</v>
+        <v>7439.96</v>
       </c>
       <c r="T8">
-        <v>8.83</v>
+        <v>7.41</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1680,34 +1640,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>41.71</v>
+        <v>39.03</v>
       </c>
       <c r="Z8">
-        <v>-19.5</v>
+        <v>-45.8</v>
       </c>
       <c r="AA8">
-        <v>65.73999999999999</v>
+        <v>43.43</v>
       </c>
       <c r="AB8">
-        <v>-85.25</v>
+        <v>-89.23</v>
       </c>
       <c r="AC8">
-        <v>4.2</v>
+        <v>4.61</v>
       </c>
       <c r="AD8">
-        <v>1.4</v>
+        <v>2.94</v>
       </c>
       <c r="AE8">
-        <v>293.98</v>
+        <v>285.91</v>
       </c>
       <c r="AF8">
-        <v>-77.86</v>
+        <v>-69.58</v>
       </c>
       <c r="AG8">
-        <v>8965.040000000001</v>
+        <v>8994.16</v>
       </c>
       <c r="AH8">
-        <v>8015.01</v>
+        <v>7950.99</v>
       </c>
       <c r="AI8">
         <v>7868.84</v>
@@ -1716,7 +1676,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>34.2</v>
+        <v>35.6</v>
       </c>
     </row>
   </sheetData>
@@ -1857,7 +1817,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1877,1046 +1837,991 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>68</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>17.77</v>
+      </c>
+      <c r="D7" s="5">
+        <v>11.15</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-6.62</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1.9</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.39</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-12.89</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-14.92</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-2.03</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-7.4</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-2.57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-10.16</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-10.47</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-13.72</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-15</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-2.52</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-2.07</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>18.3</v>
-      </c>
-      <c r="D8" s="6">
-        <v>17.77</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>1.75</v>
+      </c>
+      <c r="D14" s="5">
+        <v>4.68</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>0.52</v>
-      </c>
-      <c r="D9" s="6">
-        <v>1.9</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>5.43</v>
+      </c>
+      <c r="D15" s="5">
+        <v>4.25</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-12.08</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-12.89</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-1.42</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-3.85</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-5.91</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-7.4</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-5.83</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-2.64</v>
+      </c>
+      <c r="E17" s="7">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-13.58</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-10.16</v>
-      </c>
-      <c r="E12" s="8">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-1.03</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0.47</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-13.69</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-13.72</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-3.77</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-7.21</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-3.44</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>0.31</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-2.52</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-2.83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-4.27</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-4.81</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-0.85</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1.75</v>
-      </c>
-      <c r="E15" s="8">
-        <v>2.6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>37.57</v>
+      </c>
+      <c r="D21" s="5">
+        <v>37.39</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-0.42</v>
-      </c>
-      <c r="D16" s="6">
-        <v>5.43</v>
-      </c>
-      <c r="E16" s="8">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>23.36</v>
+      </c>
+      <c r="D22" s="5">
+        <v>21.18</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-2.18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-3.45</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-1.42</v>
-      </c>
-      <c r="E17" s="8">
-        <v>2.03</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0.09</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-2.46</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-2.55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-8.27</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-5.83</v>
-      </c>
-      <c r="E18" s="8">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-20.15</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-22.15</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-1.82</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-1.03</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-31.82</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-32.41</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-6.26</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-3.77</v>
-      </c>
-      <c r="E20" s="8">
-        <v>2.49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>28.87</v>
+      </c>
+      <c r="D26" s="5">
+        <v>21.06</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-7.81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-7.28</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-4.27</v>
-      </c>
-      <c r="E21" s="8">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-7.61</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-9.76</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-2.15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>39.27</v>
-      </c>
-      <c r="D22" s="6">
-        <v>37.57</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>14.78</v>
+      </c>
+      <c r="D28" s="5">
+        <v>16.31</v>
+      </c>
+      <c r="E28" s="7">
+        <v>1.53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>18.33</v>
-      </c>
-      <c r="D23" s="6">
-        <v>23.36</v>
-      </c>
-      <c r="E23" s="8">
-        <v>5.03</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>0.16</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-1.5</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-1.66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="D24" s="6">
-        <v>0.09</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-13.08</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-11.57</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-19.21</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-20.15</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-13.79</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-13.12</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-31.68</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-31.82</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-6.82</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-3.11</v>
+      </c>
+      <c r="E32" s="7">
+        <v>3.71</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>30.1</v>
-      </c>
-      <c r="D27" s="6">
-        <v>28.87</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>11.19</v>
+      </c>
+      <c r="D33" s="5">
+        <v>7.98</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-3.21</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-9.539999999999999</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-7.61</v>
-      </c>
-      <c r="E28" s="8">
-        <v>1.93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>2.45</v>
+      </c>
+      <c r="D34" s="5">
+        <v>4.26</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>10.76</v>
-      </c>
-      <c r="D29" s="6">
-        <v>14.78</v>
-      </c>
-      <c r="E29" s="8">
-        <v>4.02</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-2.07</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-3.07</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-4.62</v>
-      </c>
-      <c r="D30" s="6">
-        <v>0.16</v>
-      </c>
-      <c r="E30" s="8">
-        <v>4.78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-6.61</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-8.4</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-1.79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-13.25</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-13.08</v>
-      </c>
-      <c r="E31" s="8">
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-16.96</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-19.35</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-2.39</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-25.45</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-27.23</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-1.78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-35.84</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-35.81</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-18.4</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-21.4</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-11.1</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-12.27</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1269.6</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1256.7</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-12.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>912</v>
+      </c>
+      <c r="D43" s="5">
+        <v>894.5</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-17.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1611</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1564.7</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-46.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1788.3</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1745.5</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-42.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>699.2</v>
+      </c>
+      <c r="D46" s="5">
+        <v>699.55</v>
+      </c>
+      <c r="E46" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>2819.1</v>
+      </c>
+      <c r="D47" s="5">
+        <v>2715.4</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-103.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>8097.5</v>
+      </c>
+      <c r="D48" s="5">
+        <v>7991</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-106.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>62.64</v>
+      </c>
+      <c r="D49" s="5">
+        <v>60.41</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>57.28</v>
+      </c>
+      <c r="D50" s="5">
+        <v>52.27</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-5.01</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>30.18</v>
+      </c>
+      <c r="D51" s="5">
+        <v>26.15</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-4.03</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>34.09</v>
+      </c>
+      <c r="D52" s="5">
+        <v>30.5</v>
+      </c>
+      <c r="E52" s="6">
+        <v>-3.59</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>40.64</v>
+      </c>
+      <c r="D53" s="5">
+        <v>40.81</v>
+      </c>
+      <c r="E53" s="7">
         <v>0.17</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>31.82</v>
+      </c>
+      <c r="D54" s="5">
+        <v>26.42</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-5.4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>41.71</v>
+      </c>
+      <c r="D55" s="5">
+        <v>39.03</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-2.68</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
+        <v>-39.25</v>
+      </c>
+      <c r="D56" s="5">
+        <v>-80.48999999999999</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-41.24</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5">
+        <v>5.06</v>
+      </c>
+      <c r="D57" s="5">
+        <v>-23.77</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-28.83</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-39.02</v>
+      </c>
+      <c r="D58" s="5">
+        <v>18.85</v>
+      </c>
+      <c r="E58" s="7">
+        <v>57.87</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-12.36</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-13.79</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.43</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>-8.630000000000001</v>
+      </c>
+      <c r="D59" s="5">
+        <v>73.98</v>
+      </c>
+      <c r="E59" s="7">
+        <v>82.61</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-6.82</v>
-      </c>
-      <c r="E33" s="8">
-        <v>2.98</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-7.77</v>
+      </c>
+      <c r="D60" s="5">
+        <v>6.67</v>
+      </c>
+      <c r="E60" s="7">
+        <v>14.44</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>12.86</v>
-      </c>
-      <c r="D34" s="6">
-        <v>11.19</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-38.76</v>
+      </c>
+      <c r="D61" s="5">
+        <v>25.38</v>
+      </c>
+      <c r="E61" s="7">
+        <v>64.14</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-0.78</v>
-      </c>
-      <c r="D35" s="6">
-        <v>2.45</v>
-      </c>
-      <c r="E35" s="8">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-2.23</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-2.07</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-9.65</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-6.61</v>
-      </c>
-      <c r="E37" s="8">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-17.25</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-16.96</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.29</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-24.9</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-25.45</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-36.51</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-35.84</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-18.51</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-18.4</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-11.99</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-11.1</v>
-      </c>
-      <c r="E42" s="8">
-        <v>0.89</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>1267.6</v>
-      </c>
-      <c r="D43" s="6">
-        <v>1269.6</v>
-      </c>
-      <c r="E43" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>882.3</v>
-      </c>
-      <c r="D44" s="6">
-        <v>912</v>
-      </c>
-      <c r="E44" s="8">
-        <v>29.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1605.4</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1611</v>
-      </c>
-      <c r="E45" s="8">
-        <v>5.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>1801.4</v>
-      </c>
-      <c r="D46" s="6">
-        <v>1788.3</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-13.1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>691.95</v>
-      </c>
-      <c r="D47" s="6">
-        <v>699.2</v>
-      </c>
-      <c r="E47" s="8">
-        <v>7.25</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>2815.3</v>
-      </c>
-      <c r="D48" s="6">
-        <v>2819.1</v>
-      </c>
-      <c r="E48" s="8">
-        <v>3.8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>8016.5</v>
-      </c>
-      <c r="D49" s="6">
-        <v>8097.5</v>
-      </c>
-      <c r="E49" s="8">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>62.44</v>
-      </c>
-      <c r="D50" s="6">
-        <v>62.64</v>
-      </c>
-      <c r="E50" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>49.68</v>
-      </c>
-      <c r="D51" s="6">
-        <v>57.28</v>
-      </c>
-      <c r="E51" s="8">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>28.95</v>
-      </c>
-      <c r="D52" s="6">
-        <v>30.18</v>
-      </c>
-      <c r="E52" s="8">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>35.27</v>
-      </c>
-      <c r="D53" s="6">
-        <v>34.09</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>37.22</v>
-      </c>
-      <c r="D54" s="6">
-        <v>40.64</v>
-      </c>
-      <c r="E54" s="8">
-        <v>3.42</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>31.34</v>
-      </c>
-      <c r="D55" s="6">
-        <v>31.82</v>
-      </c>
-      <c r="E55" s="8">
-        <v>0.48</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>38.74</v>
-      </c>
-      <c r="D56" s="6">
-        <v>41.71</v>
-      </c>
-      <c r="E56" s="8">
-        <v>2.97</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B57" s="5" t="s">
+      <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="6">
-        <v>-56.28</v>
-      </c>
-      <c r="D57" s="6">
-        <v>-39.25</v>
-      </c>
-      <c r="E57" s="8">
-        <v>17.03</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="6">
-        <v>-47.47</v>
-      </c>
-      <c r="D58" s="6">
-        <v>5.06</v>
-      </c>
-      <c r="E58" s="8">
-        <v>52.53</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>-10.01</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-39.02</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-29.01</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>19.17</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-8.630000000000001</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-27.8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-45.17</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-7.77</v>
-      </c>
-      <c r="E61" s="8">
-        <v>37.4</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-58.74</v>
-      </c>
-      <c r="D62" s="6">
-        <v>-38.76</v>
-      </c>
-      <c r="E62" s="8">
-        <v>19.98</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-61.88</v>
-      </c>
-      <c r="D63" s="6">
+      <c r="C62" s="5">
         <v>-77.86</v>
       </c>
-      <c r="E63" s="7">
-        <v>-15.98</v>
+      <c r="D62" s="5">
+        <v>-69.58</v>
+      </c>
+      <c r="E62" s="7">
+        <v>8.279999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2936,60 +2841,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>76</v>
+      <c r="B1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>56.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>42.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>39.4</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-3.9</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-0.7</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-5.8</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-0.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>60</v>
       </c>
     </row>
@@ -3091,49 +2996,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.5175</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2808</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2375</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1681</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1429</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.1105</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0828</v>
+      <c r="A2" s="13">
+        <v>0.5063</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2692</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.2202</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1623</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1401</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.1103</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.0803</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,7 +172,40 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>52.3 → 44.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.3</t>
+  </si>
+  <si>
+    <t>44.5</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -374,14 +407,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -896,10 +930,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1256.7</v>
+        <v>1209.4</v>
       </c>
       <c r="D2">
-        <v>-1.02</v>
+        <v>-3.76</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -908,46 +942,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-3.07</v>
+        <v>-6.72</v>
       </c>
       <c r="H2">
-        <v>67.93000000000001</v>
+        <v>61.61</v>
       </c>
       <c r="I2">
-        <v>4.68</v>
+        <v>-3.44</v>
       </c>
       <c r="J2">
-        <v>11.15</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="K2">
-        <v>16.31</v>
+        <v>10.97</v>
       </c>
       <c r="L2">
-        <v>37.39</v>
+        <v>29.26</v>
       </c>
       <c r="M2">
-        <v>8.029999999999999</v>
+        <v>7.14</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P2">
-        <v>1257.22</v>
+        <v>1248.6</v>
       </c>
       <c r="Q2">
-        <v>1180.54</v>
+        <v>1186.22</v>
       </c>
       <c r="R2">
-        <v>1136.79</v>
+        <v>1139.74</v>
       </c>
       <c r="S2">
-        <v>982.25</v>
+        <v>984.05</v>
       </c>
       <c r="T2">
-        <v>27.94</v>
+        <v>22.9</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -962,34 +996,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>60.41</v>
+        <v>52.98</v>
       </c>
       <c r="Z2">
-        <v>41.88</v>
+        <v>37.1</v>
       </c>
       <c r="AA2">
-        <v>35.38</v>
+        <v>35.73</v>
       </c>
       <c r="AB2">
-        <v>6.5</v>
+        <v>1.37</v>
       </c>
       <c r="AC2">
-        <v>62.4</v>
+        <v>38.86</v>
       </c>
       <c r="AD2">
-        <v>65.48</v>
+        <v>56.03</v>
       </c>
       <c r="AE2">
-        <v>51.59</v>
+        <v>52.12</v>
       </c>
       <c r="AF2">
-        <v>-80.48999999999999</v>
+        <v>-72.41</v>
       </c>
       <c r="AG2">
-        <v>1358.93</v>
+        <v>1360.44</v>
       </c>
       <c r="AH2">
-        <v>1002.16</v>
+        <v>1012</v>
       </c>
       <c r="AI2">
         <v>1148.32</v>
@@ -998,7 +1032,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>43.4</v>
+        <v>38.49</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1009,10 +1043,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>894.5</v>
+        <v>862.05</v>
       </c>
       <c r="D3">
-        <v>-1.92</v>
+        <v>-3.63</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1021,25 +1055,25 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-8.4</v>
+        <v>-11.72</v>
       </c>
       <c r="H3">
-        <v>68.94</v>
+        <v>62.81</v>
       </c>
       <c r="I3">
-        <v>4.25</v>
+        <v>0.92</v>
       </c>
       <c r="J3">
-        <v>0.39</v>
+        <v>-3.68</v>
       </c>
       <c r="K3">
-        <v>-1.5</v>
+        <v>-5.36</v>
       </c>
       <c r="L3">
-        <v>21.18</v>
+        <v>15.58</v>
       </c>
       <c r="M3">
-        <v>50.63</v>
+        <v>50</v>
       </c>
       <c r="N3">
         <v>71</v>
@@ -1048,19 +1082,19 @@
         <v>71</v>
       </c>
       <c r="P3">
-        <v>884.4</v>
+        <v>885.97</v>
       </c>
       <c r="Q3">
-        <v>888.08</v>
+        <v>885.65</v>
       </c>
       <c r="R3">
-        <v>881.48</v>
+        <v>881.84</v>
       </c>
       <c r="S3">
-        <v>798.1900000000001</v>
+        <v>799.2</v>
       </c>
       <c r="T3">
-        <v>12.07</v>
+        <v>7.86</v>
       </c>
       <c r="U3" t="s">
         <v>45</v>
@@ -1075,34 +1109,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>52.27</v>
+        <v>44.5</v>
       </c>
       <c r="Z3">
-        <v>-0.49</v>
+        <v>-2.33</v>
       </c>
       <c r="AA3">
-        <v>-1.95</v>
+        <v>-2.03</v>
       </c>
       <c r="AB3">
-        <v>1.46</v>
+        <v>-0.3</v>
       </c>
       <c r="AC3">
-        <v>77.59</v>
+        <v>63.46</v>
       </c>
       <c r="AD3">
-        <v>64.09</v>
+        <v>71.53</v>
       </c>
       <c r="AE3">
-        <v>24.52</v>
+        <v>25.22</v>
       </c>
       <c r="AF3">
-        <v>-23.77</v>
+        <v>-35.82</v>
       </c>
       <c r="AG3">
-        <v>932.54</v>
+        <v>930.22</v>
       </c>
       <c r="AH3">
-        <v>843.62</v>
+        <v>841.0700000000001</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1111,7 +1145,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>19.3</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1122,10 +1156,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1564.7</v>
+        <v>1544</v>
       </c>
       <c r="D4">
-        <v>-2.87</v>
+        <v>-1.32</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1134,46 +1168,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-19.35</v>
+        <v>-20.41</v>
       </c>
       <c r="H4">
-        <v>15.5</v>
+        <v>13.97</v>
       </c>
       <c r="I4">
-        <v>-3.85</v>
+        <v>-4.69</v>
       </c>
       <c r="J4">
-        <v>-14.92</v>
+        <v>-16.46</v>
       </c>
       <c r="K4">
-        <v>-11.57</v>
+        <v>-13.83</v>
       </c>
       <c r="L4">
-        <v>-2.46</v>
+        <v>-1.64</v>
       </c>
       <c r="M4">
-        <v>22.02</v>
+        <v>22.31</v>
       </c>
       <c r="N4">
         <v>43</v>
       </c>
       <c r="O4">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="P4">
-        <v>1596.22</v>
+        <v>1581.02</v>
       </c>
       <c r="Q4">
-        <v>1718.15</v>
+        <v>1704.18</v>
       </c>
       <c r="R4">
-        <v>1806.29</v>
+        <v>1802.11</v>
       </c>
       <c r="S4">
-        <v>1679.35</v>
+        <v>1678.68</v>
       </c>
       <c r="T4">
-        <v>-6.83</v>
+        <v>-8.02</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1188,43 +1222,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>26.15</v>
+        <v>24.58</v>
       </c>
       <c r="Z4">
-        <v>-65.69</v>
+        <v>-69.27</v>
       </c>
       <c r="AA4">
-        <v>-50.99</v>
+        <v>-54.64</v>
       </c>
       <c r="AB4">
-        <v>-14.7</v>
+        <v>-14.62</v>
       </c>
       <c r="AC4">
-        <v>23.95</v>
+        <v>17.19</v>
       </c>
       <c r="AD4">
-        <v>17.41</v>
+        <v>20.21</v>
       </c>
       <c r="AE4">
-        <v>46.15</v>
+        <v>44.89</v>
       </c>
       <c r="AF4">
-        <v>18.85</v>
+        <v>-4.99</v>
       </c>
       <c r="AG4">
-        <v>1912.32</v>
+        <v>1906.5</v>
       </c>
       <c r="AH4">
-        <v>1523.99</v>
+        <v>1501.87</v>
       </c>
       <c r="AI4">
-        <v>1727</v>
+        <v>1692.02</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>62.61</v>
+        <v>65.34999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1235,58 +1269,58 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1745.5</v>
+        <v>1673.7</v>
       </c>
       <c r="D5">
-        <v>-2.39</v>
+        <v>-4.11</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
       </c>
       <c r="F5">
-        <v>1745.5</v>
+        <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-27.23</v>
+        <v>-30.23</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
-        <v>-2.64</v>
+        <v>-4.81</v>
       </c>
       <c r="J5">
-        <v>-9.970000000000001</v>
+        <v>-15.24</v>
       </c>
       <c r="K5">
-        <v>-13.12</v>
+        <v>-16.91</v>
       </c>
       <c r="L5">
-        <v>-22.15</v>
+        <v>-26.99</v>
       </c>
       <c r="M5">
-        <v>16.23</v>
+        <v>15.22</v>
       </c>
       <c r="N5">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="O5">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="P5">
-        <v>1771.4</v>
+        <v>1754.5</v>
       </c>
       <c r="Q5">
-        <v>1895.4</v>
+        <v>1881.53</v>
       </c>
       <c r="R5">
-        <v>1968.56</v>
+        <v>1961.49</v>
       </c>
       <c r="S5">
-        <v>2049.86</v>
+        <v>2047.03</v>
       </c>
       <c r="T5">
-        <v>-14.85</v>
+        <v>-18.24</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1301,43 +1335,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>30.5</v>
+        <v>25.62</v>
       </c>
       <c r="Z5">
-        <v>-54.08</v>
+        <v>-63.01</v>
       </c>
       <c r="AA5">
-        <v>-37.74</v>
+        <v>-42.8</v>
       </c>
       <c r="AB5">
-        <v>-16.34</v>
+        <v>-20.22</v>
       </c>
       <c r="AC5">
-        <v>20.15</v>
+        <v>11.06</v>
       </c>
       <c r="AD5">
-        <v>16.11</v>
+        <v>16.38</v>
       </c>
       <c r="AE5">
-        <v>55.69</v>
+        <v>57.9</v>
       </c>
       <c r="AF5">
-        <v>73.98</v>
+        <v>39.42</v>
       </c>
       <c r="AG5">
-        <v>2063.04</v>
+        <v>2073.86</v>
       </c>
       <c r="AH5">
-        <v>1727.76</v>
+        <v>1689.2</v>
       </c>
       <c r="AI5">
-        <v>1907.26</v>
+        <v>1879.19</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>38.07</v>
+        <v>41.05</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1348,10 +1382,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>699.55</v>
+        <v>677.15</v>
       </c>
       <c r="D6">
-        <v>0.05</v>
+        <v>-3.2</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1360,46 +1394,46 @@
         <v>674.55</v>
       </c>
       <c r="G6">
-        <v>-35.81</v>
+        <v>-37.86</v>
       </c>
       <c r="H6">
-        <v>3.71</v>
+        <v>0.39</v>
       </c>
       <c r="I6">
-        <v>0.47</v>
+        <v>-1.28</v>
       </c>
       <c r="J6">
-        <v>-10.47</v>
+        <v>-12.93</v>
       </c>
       <c r="K6">
-        <v>-3.11</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="L6">
-        <v>-32.41</v>
+        <v>-35.01</v>
       </c>
       <c r="M6">
-        <v>11.03</v>
+        <v>10.24</v>
       </c>
       <c r="N6">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="O6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="P6">
-        <v>690.23</v>
+        <v>688.48</v>
       </c>
       <c r="Q6">
-        <v>706.55</v>
+        <v>702.22</v>
       </c>
       <c r="R6">
-        <v>757.24</v>
+        <v>755.42</v>
       </c>
       <c r="S6">
-        <v>818.52</v>
+        <v>816.77</v>
       </c>
       <c r="T6">
-        <v>-14.54</v>
+        <v>-17.09</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1414,34 +1448,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>40.81</v>
+        <v>34.16</v>
       </c>
       <c r="Z6">
-        <v>-19.47</v>
+        <v>-19.85</v>
       </c>
       <c r="AA6">
-        <v>-21.21</v>
+        <v>-20.94</v>
       </c>
       <c r="AB6">
-        <v>1.74</v>
+        <v>1.09</v>
       </c>
       <c r="AC6">
-        <v>100</v>
+        <v>84.72</v>
       </c>
       <c r="AD6">
-        <v>75.09</v>
+        <v>85.61</v>
       </c>
       <c r="AE6">
-        <v>19.72</v>
+        <v>20.1</v>
       </c>
       <c r="AF6">
-        <v>6.67</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="AG6">
-        <v>750.46</v>
+        <v>738.88</v>
       </c>
       <c r="AH6">
-        <v>662.64</v>
+        <v>665.5599999999999</v>
       </c>
       <c r="AI6">
         <v>739.76</v>
@@ -1450,7 +1484,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>34.91</v>
+        <v>34.18</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1461,10 +1495,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2715.4</v>
+        <v>2581.9</v>
       </c>
       <c r="D7">
-        <v>-3.68</v>
+        <v>-4.92</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1473,97 +1507,97 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-21.4</v>
+        <v>-25.27</v>
       </c>
       <c r="H7">
-        <v>43.56</v>
+        <v>36.5</v>
       </c>
       <c r="I7">
-        <v>-7.21</v>
+        <v>-11</v>
       </c>
       <c r="J7">
-        <v>-15</v>
+        <v>-18.46</v>
       </c>
       <c r="K7">
-        <v>7.98</v>
+        <v>3.29</v>
       </c>
       <c r="L7">
-        <v>21.06</v>
+        <v>15.19</v>
       </c>
       <c r="M7">
-        <v>26.92</v>
+        <v>25.67</v>
       </c>
       <c r="N7">
         <v>85</v>
       </c>
       <c r="O7">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P7">
-        <v>2828.9</v>
+        <v>2765.1</v>
       </c>
       <c r="Q7">
-        <v>3007.41</v>
+        <v>2979.45</v>
       </c>
       <c r="R7">
-        <v>3002.62</v>
+        <v>3002.81</v>
       </c>
       <c r="S7">
-        <v>2511.83</v>
+        <v>2513.55</v>
       </c>
       <c r="T7">
-        <v>8.1</v>
+        <v>2.72</v>
       </c>
       <c r="U7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V7" t="s">
         <v>45</v>
       </c>
       <c r="W7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y7">
-        <v>26.42</v>
+        <v>21.39</v>
       </c>
       <c r="Z7">
-        <v>-73.98</v>
+        <v>-94.51000000000001</v>
       </c>
       <c r="AA7">
-        <v>-34.7</v>
+        <v>-46.66</v>
       </c>
       <c r="AB7">
-        <v>-39.28</v>
+        <v>-47.85</v>
       </c>
       <c r="AC7">
         <v>0.84</v>
       </c>
       <c r="AD7">
-        <v>0.5600000000000001</v>
+        <v>0.84</v>
       </c>
       <c r="AE7">
-        <v>119.69</v>
+        <v>121.57</v>
       </c>
       <c r="AF7">
-        <v>25.38</v>
+        <v>18.34</v>
       </c>
       <c r="AG7">
-        <v>3280.03</v>
+        <v>3304.09</v>
       </c>
       <c r="AH7">
-        <v>2734.79</v>
+        <v>2654.82</v>
       </c>
       <c r="AI7">
-        <v>3115.86</v>
+        <v>3011.7</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>40.89</v>
+        <v>46.01</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1574,10 +1608,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7991</v>
+        <v>7712</v>
       </c>
       <c r="D8">
-        <v>-1.32</v>
+        <v>-3.49</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1586,46 +1620,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-12.27</v>
+        <v>-15.34</v>
       </c>
       <c r="H8">
-        <v>34.88</v>
+        <v>30.17</v>
       </c>
       <c r="I8">
-        <v>-4.81</v>
+        <v>-7.66</v>
       </c>
       <c r="J8">
-        <v>-2.07</v>
+        <v>-7.53</v>
       </c>
       <c r="K8">
-        <v>4.26</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L8">
-        <v>-9.76</v>
+        <v>-15.23</v>
       </c>
       <c r="M8">
-        <v>14.01</v>
+        <v>13.1</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="P8">
-        <v>8114.5</v>
+        <v>7986.6</v>
       </c>
       <c r="Q8">
-        <v>8472.58</v>
+        <v>8437.219999999999</v>
       </c>
       <c r="R8">
-        <v>8268.85</v>
+        <v>8257.1</v>
       </c>
       <c r="S8">
-        <v>7439.96</v>
+        <v>7438.54</v>
       </c>
       <c r="T8">
-        <v>7.41</v>
+        <v>3.68</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1640,43 +1674,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>39.03</v>
+        <v>33.04</v>
       </c>
       <c r="Z8">
-        <v>-45.8</v>
+        <v>-88.13</v>
       </c>
       <c r="AA8">
-        <v>43.43</v>
+        <v>17.12</v>
       </c>
       <c r="AB8">
-        <v>-89.23</v>
+        <v>-105.25</v>
       </c>
       <c r="AC8">
         <v>4.61</v>
       </c>
       <c r="AD8">
-        <v>2.94</v>
+        <v>4.47</v>
       </c>
       <c r="AE8">
-        <v>285.91</v>
+        <v>288.66</v>
       </c>
       <c r="AF8">
-        <v>-69.58</v>
+        <v>-35.64</v>
       </c>
       <c r="AG8">
-        <v>8994.16</v>
+        <v>9060.09</v>
       </c>
       <c r="AH8">
-        <v>7950.99</v>
+        <v>7814.36</v>
       </c>
       <c r="AI8">
-        <v>7868.84</v>
+        <v>8699.24</v>
       </c>
       <c r="AJ8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK8">
-        <v>35.6</v>
+        <v>39.15</v>
       </c>
     </row>
   </sheetData>
@@ -1817,7 +1851,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1837,991 +1871,1100 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>55</v>
+      <c r="A5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>17.77</v>
-      </c>
-      <c r="D7" s="5">
-        <v>11.15</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-6.62</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>11.15</v>
+      </c>
+      <c r="D9" s="6">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>1.9</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C10" s="6">
         <v>0.39</v>
       </c>
-      <c r="E8" s="6">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-3.68</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-4.07</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-12.89</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C11" s="6">
         <v>-14.92</v>
       </c>
-      <c r="E9" s="6">
-        <v>-2.03</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D11" s="6">
+        <v>-16.46</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-7.4</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C12" s="6">
         <v>-9.970000000000001</v>
       </c>
-      <c r="E10" s="6">
-        <v>-2.57</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-15.24</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-5.27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-10.16</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C13" s="6">
         <v>-10.47</v>
       </c>
-      <c r="E11" s="6">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-12.93</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-2.46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-13.72</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C14" s="6">
         <v>-15</v>
       </c>
-      <c r="E12" s="6">
+      <c r="D14" s="6">
+        <v>-18.46</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-3.46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-2.07</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-7.53</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-5.46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>4.68</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-3.44</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-8.119999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>4.25</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.92</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-3.33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-3.85</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-4.69</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-2.64</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-4.81</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-2.17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.47</v>
+      </c>
+      <c r="D20" s="6">
         <v>-1.28</v>
       </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="E20" s="7">
+        <v>-1.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-7.21</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-11</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-3.79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-2.52</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-2.07</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6">
+        <v>-4.81</v>
+      </c>
+      <c r="D22" s="6">
+        <v>-7.66</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>1.75</v>
-      </c>
-      <c r="D14" s="5">
-        <v>4.68</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>37.39</v>
+      </c>
+      <c r="D23" s="6">
+        <v>29.26</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-8.130000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>5.43</v>
-      </c>
-      <c r="D15" s="5">
-        <v>4.25</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>21.18</v>
+      </c>
+      <c r="D24" s="6">
+        <v>15.58</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-5.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-1.42</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-3.85</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-2.43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-2.46</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-1.64</v>
+      </c>
+      <c r="E25" s="8">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-5.83</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-2.64</v>
-      </c>
-      <c r="E17" s="7">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-22.15</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-26.99</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-4.84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-1.03</v>
-      </c>
-      <c r="D18" s="5">
-        <v>0.47</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-32.41</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-35.01</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-3.77</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-7.21</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-3.44</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="6">
+        <v>21.06</v>
+      </c>
+      <c r="D28" s="6">
+        <v>15.19</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-5.87</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="5">
-        <v>-4.27</v>
-      </c>
-      <c r="D20" s="5">
-        <v>-4.81</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-0.54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-9.76</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-15.23</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-5.47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>37.57</v>
-      </c>
-      <c r="D21" s="5">
-        <v>37.39</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>16.31</v>
+      </c>
+      <c r="D30" s="6">
+        <v>10.97</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-5.34</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>23.36</v>
-      </c>
-      <c r="D22" s="5">
-        <v>21.18</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-2.18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-1.5</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-5.36</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-3.86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-2.46</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-2.55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-11.57</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-13.83</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-2.26</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-20.15</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-22.15</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-13.12</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-16.91</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-3.79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-31.82</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-32.41</v>
-      </c>
-      <c r="E25" s="6">
-        <v>-0.59</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-3.11</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-9.619999999999999</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-6.51</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>28.87</v>
-      </c>
-      <c r="D26" s="5">
-        <v>21.06</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-7.81</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="6">
+        <v>7.98</v>
+      </c>
+      <c r="D35" s="6">
+        <v>3.29</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-4.69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-7.61</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-9.76</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-2.15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="6">
+        <v>4.26</v>
+      </c>
+      <c r="D36" s="6">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-4.19</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>14.78</v>
-      </c>
-      <c r="D28" s="5">
-        <v>16.31</v>
-      </c>
-      <c r="E28" s="7">
-        <v>1.53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-3.07</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-6.72</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-3.65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>0.16</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-1.5</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-8.4</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-11.72</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-3.32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-13.08</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-11.57</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-19.35</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-20.41</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-13.79</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-13.12</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-27.23</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-30.23</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-6.82</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-3.11</v>
-      </c>
-      <c r="E32" s="7">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-35.81</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-37.86</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-2.05</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>11.19</v>
-      </c>
-      <c r="D33" s="5">
-        <v>7.98</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-3.21</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-21.4</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-25.27</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-3.87</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>2.45</v>
-      </c>
-      <c r="D34" s="5">
-        <v>4.26</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-12.27</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-15.34</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-3.07</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-2.07</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-3.07</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>1256.7</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1209.4</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-47.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-6.61</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-8.4</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-1.79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>894.5</v>
+      </c>
+      <c r="D45" s="6">
+        <v>862.05</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-32.45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-16.96</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-19.35</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-2.39</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>1564.7</v>
+      </c>
+      <c r="D46" s="6">
+        <v>1544</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-20.7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-25.45</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-27.23</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-1.78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>1745.5</v>
+      </c>
+      <c r="D47" s="6">
+        <v>1673.7</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-71.8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-35.84</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-35.81</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>699.55</v>
+      </c>
+      <c r="D48" s="6">
+        <v>677.15</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-22.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-18.4</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-21.4</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B49" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="6">
+        <v>2715.4</v>
+      </c>
+      <c r="D49" s="6">
+        <v>2581.9</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-133.5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-11.1</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-12.27</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B50" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="6">
+        <v>7991</v>
+      </c>
+      <c r="D50" s="6">
+        <v>7712</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-279</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="6">
+        <v>29</v>
+      </c>
+      <c r="D51" s="6">
+        <v>15</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="6">
+        <v>15</v>
+      </c>
+      <c r="D52" s="6">
+        <v>29</v>
+      </c>
+      <c r="E52" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1269.6</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1256.7</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-12.9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>60.41</v>
+      </c>
+      <c r="D53" s="6">
+        <v>52.98</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-7.43</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>912</v>
-      </c>
-      <c r="D43" s="5">
-        <v>894.5</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-17.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>52.27</v>
+      </c>
+      <c r="D54" s="6">
+        <v>44.5</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-7.77</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>1611</v>
-      </c>
-      <c r="D44" s="5">
-        <v>1564.7</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-46.3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>26.15</v>
+      </c>
+      <c r="D55" s="6">
+        <v>24.58</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-1.57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1788.3</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1745.5</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-42.8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>30.5</v>
+      </c>
+      <c r="D56" s="6">
+        <v>25.62</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-4.88</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>699.2</v>
-      </c>
-      <c r="D46" s="5">
-        <v>699.55</v>
-      </c>
-      <c r="E46" s="7">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>40.81</v>
+      </c>
+      <c r="D57" s="6">
+        <v>34.16</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-6.65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>2819.1</v>
-      </c>
-      <c r="D47" s="5">
-        <v>2715.4</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-103.7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="6">
+        <v>26.42</v>
+      </c>
+      <c r="D58" s="6">
+        <v>21.39</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-5.03</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>8097.5</v>
-      </c>
-      <c r="D48" s="5">
-        <v>7991</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-106.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>39.03</v>
+      </c>
+      <c r="D59" s="6">
+        <v>33.04</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-5.99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>62.64</v>
-      </c>
-      <c r="D49" s="5">
-        <v>60.41</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-2.23</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-80.48999999999999</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-72.41</v>
+      </c>
+      <c r="E60" s="8">
+        <v>8.08</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>57.28</v>
-      </c>
-      <c r="D50" s="5">
-        <v>52.27</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-5.01</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-23.77</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-35.82</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-12.05</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>30.18</v>
-      </c>
-      <c r="D51" s="5">
-        <v>26.15</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-4.03</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
+        <v>18.85</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-4.99</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-23.84</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>34.09</v>
-      </c>
-      <c r="D52" s="5">
-        <v>30.5</v>
-      </c>
-      <c r="E52" s="6">
-        <v>-3.59</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>73.98</v>
+      </c>
+      <c r="D63" s="6">
+        <v>39.42</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-34.56</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>40.64</v>
-      </c>
-      <c r="D53" s="5">
-        <v>40.81</v>
-      </c>
-      <c r="E53" s="7">
-        <v>0.17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>6.67</v>
+      </c>
+      <c r="D64" s="6">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-15.63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>31.82</v>
-      </c>
-      <c r="D54" s="5">
-        <v>26.42</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-5.4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>25.38</v>
+      </c>
+      <c r="D65" s="6">
+        <v>18.34</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-7.04</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>41.71</v>
-      </c>
-      <c r="D55" s="5">
-        <v>39.03</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-2.68</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="3" t="s">
+      <c r="B66" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="5">
-        <v>-39.25</v>
-      </c>
-      <c r="D56" s="5">
-        <v>-80.48999999999999</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-41.24</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5">
-        <v>5.06</v>
-      </c>
-      <c r="D57" s="5">
-        <v>-23.77</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-28.83</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5">
-        <v>-39.02</v>
-      </c>
-      <c r="D58" s="5">
-        <v>18.85</v>
-      </c>
-      <c r="E58" s="7">
-        <v>57.87</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>-8.630000000000001</v>
-      </c>
-      <c r="D59" s="5">
-        <v>73.98</v>
-      </c>
-      <c r="E59" s="7">
-        <v>82.61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>-7.77</v>
-      </c>
-      <c r="D60" s="5">
-        <v>6.67</v>
-      </c>
-      <c r="E60" s="7">
-        <v>14.44</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>-38.76</v>
-      </c>
-      <c r="D61" s="5">
-        <v>25.38</v>
-      </c>
-      <c r="E61" s="7">
-        <v>64.14</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-77.86</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C66" s="6">
         <v>-69.58</v>
       </c>
-      <c r="E62" s="7">
-        <v>8.279999999999999</v>
+      <c r="D66" s="6">
+        <v>-35.64</v>
+      </c>
+      <c r="E66" s="8">
+        <v>33.94</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2841,61 +2984,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>56.8</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>33.8</v>
+      </c>
+      <c r="E2" s="11">
+        <v>60</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-4.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>56.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>39.4</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-5.8</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-0.1</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
-        <v>60</v>
+      <c r="I2" s="11">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2996,49 +3139,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.5063</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2692</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2202</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1623</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1401</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.1103</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0803</v>
+      <c r="A2" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2567</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2231</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1522</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.131</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.1024</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.07139999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="61">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,55 +172,13 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>52.3 → 44.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.3</t>
-  </si>
-  <si>
-    <t>44.5</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Previous</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>Delta</t>
+    <t>No numeric changes detected since last run.</t>
   </si>
   <si>
     <t>Rank</t>
@@ -251,13 +209,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.00"/>
-    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
-    <numFmt numFmtId="166" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.00%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,22 +245,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -320,24 +262,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,34 +331,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1851,7 +1768,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1871,1100 +1788,27 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>46</v>
-      </c>
+      <c r="A5" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>11.15</v>
-      </c>
-      <c r="D9" s="6">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.39</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-3.68</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-4.07</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-14.92</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-16.46</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-15.24</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-5.27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-10.47</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-12.93</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-2.46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-15</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-18.46</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-2.07</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-7.53</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-5.46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>4.68</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-3.44</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-8.119999999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>4.25</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0.92</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-3.33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-3.85</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-4.69</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-2.64</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-4.81</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>0.47</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-1.28</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-7.21</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-11</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-3.79</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-4.81</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-7.66</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>37.39</v>
-      </c>
-      <c r="D23" s="6">
-        <v>29.26</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-8.130000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>21.18</v>
-      </c>
-      <c r="D24" s="6">
-        <v>15.58</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-5.6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-2.46</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-1.64</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>-22.15</v>
-      </c>
-      <c r="D26" s="6">
-        <v>-26.99</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-4.84</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-32.41</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-35.01</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="6">
-        <v>21.06</v>
-      </c>
-      <c r="D28" s="6">
-        <v>15.19</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-5.87</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-9.76</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-15.23</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-5.47</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>16.31</v>
-      </c>
-      <c r="D30" s="6">
-        <v>10.97</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-5.34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-1.5</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-5.36</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-3.86</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-11.57</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-13.83</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-2.26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-13.12</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-16.91</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-3.79</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-3.11</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-9.619999999999999</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-6.51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="6">
-        <v>7.98</v>
-      </c>
-      <c r="D35" s="6">
-        <v>3.29</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-4.69</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="6">
-        <v>4.26</v>
-      </c>
-      <c r="D36" s="6">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-4.19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-3.07</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-6.72</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-3.65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-8.4</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-11.72</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-3.32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-19.35</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-20.41</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-27.23</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-30.23</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-35.81</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-37.86</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-2.05</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="6">
-        <v>-21.4</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-25.27</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-3.87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-12.27</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-15.34</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1256.7</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1209.4</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-47.3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>894.5</v>
-      </c>
-      <c r="D45" s="6">
-        <v>862.05</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-32.45</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>1564.7</v>
-      </c>
-      <c r="D46" s="6">
-        <v>1544</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-20.7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>1745.5</v>
-      </c>
-      <c r="D47" s="6">
-        <v>1673.7</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-71.8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>699.55</v>
-      </c>
-      <c r="D48" s="6">
-        <v>677.15</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-22.4</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="6">
-        <v>2715.4</v>
-      </c>
-      <c r="D49" s="6">
-        <v>2581.9</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-133.5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="6">
-        <v>7991</v>
-      </c>
-      <c r="D50" s="6">
-        <v>7712</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-279</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="6">
-        <v>29</v>
-      </c>
-      <c r="D51" s="6">
-        <v>15</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="6">
-        <v>15</v>
-      </c>
-      <c r="D52" s="6">
-        <v>29</v>
-      </c>
-      <c r="E52" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>60.41</v>
-      </c>
-      <c r="D53" s="6">
-        <v>52.98</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-7.43</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>52.27</v>
-      </c>
-      <c r="D54" s="6">
-        <v>44.5</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-7.77</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>26.15</v>
-      </c>
-      <c r="D55" s="6">
-        <v>24.58</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-1.57</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>30.5</v>
-      </c>
-      <c r="D56" s="6">
-        <v>25.62</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-4.88</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>40.81</v>
-      </c>
-      <c r="D57" s="6">
-        <v>34.16</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-6.65</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>26.42</v>
-      </c>
-      <c r="D58" s="6">
-        <v>21.39</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-5.03</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>39.03</v>
-      </c>
-      <c r="D59" s="6">
-        <v>33.04</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-5.99</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-80.48999999999999</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-72.41</v>
-      </c>
-      <c r="E60" s="8">
-        <v>8.08</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-23.77</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-35.82</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-12.05</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>18.85</v>
-      </c>
-      <c r="D62" s="6">
-        <v>-4.99</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-23.84</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>73.98</v>
-      </c>
-      <c r="D63" s="6">
-        <v>39.42</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-34.56</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>6.67</v>
-      </c>
-      <c r="D64" s="6">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-15.63</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>25.38</v>
-      </c>
-      <c r="D65" s="6">
-        <v>18.34</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-7.04</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>-69.58</v>
-      </c>
-      <c r="D66" s="6">
-        <v>-35.64</v>
-      </c>
-      <c r="E66" s="8">
-        <v>33.94</v>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2984,60 +1828,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>74</v>
+      <c r="B1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="6">
         <v>56.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="7">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
+      <c r="D2" s="6">
         <v>33.8</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="6">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="6">
         <v>-9.199999999999999</v>
       </c>
-      <c r="G2" s="11">
+      <c r="G2" s="6">
         <v>-4.5</v>
       </c>
-      <c r="H2" s="11">
+      <c r="H2" s="6">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="6">
         <v>40</v>
       </c>
     </row>
@@ -3139,48 +1983,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="8" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
+      <c r="A2" s="9">
         <v>0.5</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="9">
         <v>0.2567</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="9">
         <v>0.2231</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="9">
         <v>0.1522</v>
       </c>
-      <c r="E2" s="14">
+      <c r="E2" s="9">
         <v>0.131</v>
       </c>
-      <c r="F2" s="14">
+      <c r="F2" s="9">
         <v>0.1024</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="9">
         <v>0.07139999999999999</v>
       </c>
     </row>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="79">
   <si>
     <t>Symbol</t>
   </si>
@@ -172,13 +172,67 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>24.6 → 33.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>24.6</t>
+  </si>
+  <si>
+    <t>33.6</t>
+  </si>
+  <si>
+    <t>25.6 → 30.6</t>
+  </si>
+  <si>
+    <t>25.6</t>
+  </si>
+  <si>
+    <t>30.6</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
   </si>
   <si>
-    <t>No numeric changes detected since last run.</t>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Previous</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>Delta</t>
   </si>
   <si>
     <t>Rank</t>
@@ -209,11 +263,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.00%"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.00"/>
+    <numFmt numFmtId="165" formatCode="+0.00;-0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,8 +301,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,6 +332,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2E4057"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -331,27 +419,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -714,7 +810,7 @@
     <col min="23" max="23" width="16.7109375" customWidth="1"/>
     <col min="24" max="24" width="13.7109375" customWidth="1"/>
     <col min="25" max="25" width="7.7109375" customWidth="1"/>
-    <col min="26" max="26" width="8.7109375" customWidth="1"/>
+    <col min="26" max="26" width="9.7109375" customWidth="1"/>
     <col min="27" max="27" width="13.7109375" customWidth="1"/>
     <col min="28" max="28" width="11.7109375" customWidth="1"/>
     <col min="29" max="30" width="13.7109375" customWidth="1"/>
@@ -847,10 +943,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1209.4</v>
+        <v>1202.6</v>
       </c>
       <c r="D2">
-        <v>-3.76</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -859,25 +955,25 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-6.72</v>
+        <v>-7.24</v>
       </c>
       <c r="H2">
-        <v>61.61</v>
+        <v>60.7</v>
       </c>
       <c r="I2">
-        <v>-3.44</v>
+        <v>-2.99</v>
       </c>
       <c r="J2">
-        <v>9.550000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="K2">
-        <v>10.97</v>
+        <v>10.21</v>
       </c>
       <c r="L2">
-        <v>29.26</v>
+        <v>31.16</v>
       </c>
       <c r="M2">
-        <v>7.14</v>
+        <v>6.71</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -886,19 +982,19 @@
         <v>86</v>
       </c>
       <c r="P2">
-        <v>1248.6</v>
+        <v>1241.18</v>
       </c>
       <c r="Q2">
-        <v>1186.22</v>
+        <v>1191.64</v>
       </c>
       <c r="R2">
-        <v>1139.74</v>
+        <v>1142.68</v>
       </c>
       <c r="S2">
-        <v>984.05</v>
+        <v>985.79</v>
       </c>
       <c r="T2">
-        <v>22.9</v>
+        <v>21.99</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -913,34 +1009,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>52.98</v>
+        <v>51.99</v>
       </c>
       <c r="Z2">
-        <v>37.1</v>
+        <v>32.39</v>
       </c>
       <c r="AA2">
-        <v>35.73</v>
+        <v>35.06</v>
       </c>
       <c r="AB2">
-        <v>1.37</v>
+        <v>-2.67</v>
       </c>
       <c r="AC2">
-        <v>38.86</v>
+        <v>16.51</v>
       </c>
       <c r="AD2">
-        <v>56.03</v>
+        <v>39.26</v>
       </c>
       <c r="AE2">
-        <v>52.12</v>
+        <v>51.49</v>
       </c>
       <c r="AF2">
-        <v>-72.41</v>
+        <v>-72.56</v>
       </c>
       <c r="AG2">
-        <v>1360.44</v>
+        <v>1360.46</v>
       </c>
       <c r="AH2">
-        <v>1012</v>
+        <v>1022.83</v>
       </c>
       <c r="AI2">
         <v>1148.32</v>
@@ -949,7 +1045,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>38.49</v>
+        <v>34.21</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -960,10 +1056,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>862.05</v>
+        <v>855.55</v>
       </c>
       <c r="D3">
-        <v>-3.63</v>
+        <v>-0.75</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -972,88 +1068,88 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-11.72</v>
+        <v>-12.39</v>
       </c>
       <c r="H3">
-        <v>62.81</v>
+        <v>61.58</v>
       </c>
       <c r="I3">
-        <v>0.92</v>
+        <v>-2.67</v>
       </c>
       <c r="J3">
-        <v>-3.68</v>
+        <v>-6.06</v>
       </c>
       <c r="K3">
-        <v>-5.36</v>
+        <v>-6.66</v>
       </c>
       <c r="L3">
-        <v>15.58</v>
+        <v>15.03</v>
       </c>
       <c r="M3">
-        <v>50</v>
+        <v>48.64</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>885.97</v>
+        <v>881.28</v>
       </c>
       <c r="Q3">
-        <v>885.65</v>
+        <v>882.08</v>
       </c>
       <c r="R3">
-        <v>881.84</v>
+        <v>882.36</v>
       </c>
       <c r="S3">
-        <v>799.2</v>
+        <v>800.12</v>
       </c>
       <c r="T3">
-        <v>7.86</v>
+        <v>6.93</v>
       </c>
       <c r="U3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V3" t="s">
         <v>45</v>
       </c>
       <c r="W3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y3">
-        <v>44.5</v>
+        <v>43.12</v>
       </c>
       <c r="Z3">
-        <v>-2.33</v>
+        <v>-4.26</v>
       </c>
       <c r="AA3">
-        <v>-2.03</v>
+        <v>-2.47</v>
       </c>
       <c r="AB3">
-        <v>-0.3</v>
+        <v>-1.78</v>
       </c>
       <c r="AC3">
-        <v>63.46</v>
+        <v>34.36</v>
       </c>
       <c r="AD3">
-        <v>71.53</v>
+        <v>58.47</v>
       </c>
       <c r="AE3">
-        <v>25.22</v>
+        <v>25.24</v>
       </c>
       <c r="AF3">
-        <v>-35.82</v>
+        <v>0.31</v>
       </c>
       <c r="AG3">
-        <v>930.22</v>
+        <v>924.09</v>
       </c>
       <c r="AH3">
-        <v>841.0700000000001</v>
+        <v>840.0700000000001</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1062,7 +1158,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>18.64</v>
+        <v>20.58</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1073,10 +1169,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1544</v>
+        <v>1587.6</v>
       </c>
       <c r="D4">
-        <v>-1.32</v>
+        <v>2.82</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1085,46 +1181,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-20.41</v>
+        <v>-18.16</v>
       </c>
       <c r="H4">
-        <v>13.97</v>
+        <v>17.19</v>
       </c>
       <c r="I4">
-        <v>-4.69</v>
+        <v>0.48</v>
       </c>
       <c r="J4">
-        <v>-16.46</v>
+        <v>-12.93</v>
       </c>
       <c r="K4">
-        <v>-13.83</v>
+        <v>-12.18</v>
       </c>
       <c r="L4">
-        <v>-1.64</v>
+        <v>-2.77</v>
       </c>
       <c r="M4">
-        <v>22.31</v>
+        <v>22.97</v>
       </c>
       <c r="N4">
         <v>43</v>
       </c>
       <c r="O4">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="P4">
-        <v>1581.02</v>
+        <v>1582.54</v>
       </c>
       <c r="Q4">
-        <v>1704.18</v>
+        <v>1692.11</v>
       </c>
       <c r="R4">
-        <v>1802.11</v>
+        <v>1797.81</v>
       </c>
       <c r="S4">
-        <v>1678.68</v>
+        <v>1678.38</v>
       </c>
       <c r="T4">
-        <v>-8.02</v>
+        <v>-5.41</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1139,34 +1235,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>24.58</v>
+        <v>33.65</v>
       </c>
       <c r="Z4">
-        <v>-69.27</v>
+        <v>-67.8</v>
       </c>
       <c r="AA4">
-        <v>-54.64</v>
+        <v>-57.27</v>
       </c>
       <c r="AB4">
-        <v>-14.62</v>
+        <v>-10.53</v>
       </c>
       <c r="AC4">
-        <v>17.19</v>
+        <v>24.8</v>
       </c>
       <c r="AD4">
-        <v>20.21</v>
+        <v>21.98</v>
       </c>
       <c r="AE4">
-        <v>44.89</v>
+        <v>45.53</v>
       </c>
       <c r="AF4">
-        <v>-4.99</v>
+        <v>0.48</v>
       </c>
       <c r="AG4">
-        <v>1906.5</v>
+        <v>1891.87</v>
       </c>
       <c r="AH4">
-        <v>1501.87</v>
+        <v>1492.36</v>
       </c>
       <c r="AI4">
         <v>1692.02</v>
@@ -1175,7 +1271,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>65.34999999999999</v>
+        <v>63.55</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1186,10 +1282,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1673.7</v>
+        <v>1703.4</v>
       </c>
       <c r="D5">
-        <v>-4.11</v>
+        <v>1.77</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1198,46 +1294,46 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-30.23</v>
+        <v>-28.99</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="I5">
-        <v>-4.81</v>
+        <v>-3.41</v>
       </c>
       <c r="J5">
-        <v>-15.24</v>
+        <v>-12.7</v>
       </c>
       <c r="K5">
-        <v>-16.91</v>
+        <v>-17.62</v>
       </c>
       <c r="L5">
-        <v>-26.99</v>
+        <v>-27.24</v>
       </c>
       <c r="M5">
-        <v>15.22</v>
+        <v>15.7</v>
       </c>
       <c r="N5">
         <v>15</v>
       </c>
       <c r="O5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P5">
-        <v>1754.5</v>
+        <v>1742.46</v>
       </c>
       <c r="Q5">
-        <v>1881.53</v>
+        <v>1868.57</v>
       </c>
       <c r="R5">
-        <v>1961.49</v>
+        <v>1954.81</v>
       </c>
       <c r="S5">
-        <v>2047.03</v>
+        <v>2043.8</v>
       </c>
       <c r="T5">
-        <v>-18.24</v>
+        <v>-16.66</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1252,43 +1348,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>25.62</v>
+        <v>30.57</v>
       </c>
       <c r="Z5">
-        <v>-63.01</v>
+        <v>-66.92</v>
       </c>
       <c r="AA5">
-        <v>-42.8</v>
+        <v>-47.62</v>
       </c>
       <c r="AB5">
-        <v>-20.22</v>
+        <v>-19.3</v>
       </c>
       <c r="AC5">
-        <v>11.06</v>
+        <v>10.12</v>
       </c>
       <c r="AD5">
-        <v>16.38</v>
+        <v>13.78</v>
       </c>
       <c r="AE5">
         <v>57.9</v>
       </c>
       <c r="AF5">
-        <v>39.42</v>
+        <v>28.14</v>
       </c>
       <c r="AG5">
-        <v>2073.86</v>
+        <v>2072.46</v>
       </c>
       <c r="AH5">
-        <v>1689.2</v>
+        <v>1664.67</v>
       </c>
       <c r="AI5">
-        <v>1879.19</v>
+        <v>1853.75</v>
       </c>
       <c r="AJ5" t="s">
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>41.05</v>
+        <v>43.86</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1299,10 +1395,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>677.15</v>
+        <v>688.9</v>
       </c>
       <c r="D6">
-        <v>-3.2</v>
+        <v>1.74</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1311,46 +1407,46 @@
         <v>674.55</v>
       </c>
       <c r="G6">
-        <v>-37.86</v>
+        <v>-36.79</v>
       </c>
       <c r="H6">
-        <v>0.39</v>
+        <v>2.13</v>
       </c>
       <c r="I6">
-        <v>-1.28</v>
+        <v>2.13</v>
       </c>
       <c r="J6">
-        <v>-12.93</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="K6">
-        <v>-9.619999999999999</v>
+        <v>-9.19</v>
       </c>
       <c r="L6">
-        <v>-35.01</v>
+        <v>-34.13</v>
       </c>
       <c r="M6">
-        <v>10.24</v>
+        <v>10.67</v>
       </c>
       <c r="N6">
         <v>29</v>
       </c>
       <c r="O6">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P6">
-        <v>688.48</v>
+        <v>691.35</v>
       </c>
       <c r="Q6">
-        <v>702.22</v>
+        <v>698.83</v>
       </c>
       <c r="R6">
-        <v>755.42</v>
+        <v>753.62</v>
       </c>
       <c r="S6">
-        <v>816.77</v>
+        <v>815.22</v>
       </c>
       <c r="T6">
-        <v>-17.09</v>
+        <v>-15.49</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1365,34 +1461,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>34.16</v>
+        <v>39.71</v>
       </c>
       <c r="Z6">
-        <v>-19.85</v>
+        <v>-18.99</v>
       </c>
       <c r="AA6">
-        <v>-20.94</v>
+        <v>-20.55</v>
       </c>
       <c r="AB6">
-        <v>1.09</v>
+        <v>1.56</v>
       </c>
       <c r="AC6">
-        <v>84.72</v>
+        <v>82.19</v>
       </c>
       <c r="AD6">
-        <v>85.61</v>
+        <v>88.97</v>
       </c>
       <c r="AE6">
-        <v>20.1</v>
+        <v>19.94</v>
       </c>
       <c r="AF6">
-        <v>-8.960000000000001</v>
+        <v>-52.35</v>
       </c>
       <c r="AG6">
-        <v>738.88</v>
+        <v>725.4400000000001</v>
       </c>
       <c r="AH6">
-        <v>665.5599999999999</v>
+        <v>672.22</v>
       </c>
       <c r="AI6">
         <v>739.76</v>
@@ -1401,7 +1497,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>34.18</v>
+        <v>33.85</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1412,10 +1508,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2581.9</v>
+        <v>2631.1</v>
       </c>
       <c r="D7">
-        <v>-4.92</v>
+        <v>1.91</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1424,22 +1520,22 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-25.27</v>
+        <v>-23.84</v>
       </c>
       <c r="H7">
-        <v>36.5</v>
+        <v>39.1</v>
       </c>
       <c r="I7">
-        <v>-11</v>
+        <v>-9.08</v>
       </c>
       <c r="J7">
-        <v>-18.46</v>
+        <v>-16.23</v>
       </c>
       <c r="K7">
-        <v>3.29</v>
+        <v>6.13</v>
       </c>
       <c r="L7">
-        <v>15.19</v>
+        <v>19.06</v>
       </c>
       <c r="M7">
         <v>25.67</v>
@@ -1448,22 +1544,22 @@
         <v>85</v>
       </c>
       <c r="O7">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="P7">
-        <v>2765.1</v>
+        <v>2712.56</v>
       </c>
       <c r="Q7">
-        <v>2979.45</v>
+        <v>2952.5</v>
       </c>
       <c r="R7">
-        <v>3002.81</v>
+        <v>3004.55</v>
       </c>
       <c r="S7">
-        <v>2513.55</v>
+        <v>2515.53</v>
       </c>
       <c r="T7">
-        <v>2.72</v>
+        <v>4.59</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1478,43 +1574,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>21.39</v>
+        <v>26.91</v>
       </c>
       <c r="Z7">
-        <v>-94.51000000000001</v>
+        <v>-105.59</v>
       </c>
       <c r="AA7">
-        <v>-46.66</v>
+        <v>-58.44</v>
       </c>
       <c r="AB7">
-        <v>-47.85</v>
+        <v>-47.14</v>
       </c>
       <c r="AC7">
-        <v>0.84</v>
+        <v>7.53</v>
       </c>
       <c r="AD7">
-        <v>0.84</v>
+        <v>3.07</v>
       </c>
       <c r="AE7">
-        <v>121.57</v>
+        <v>120.26</v>
       </c>
       <c r="AF7">
-        <v>18.34</v>
+        <v>-5.11</v>
       </c>
       <c r="AG7">
-        <v>3304.09</v>
+        <v>3299.23</v>
       </c>
       <c r="AH7">
-        <v>2654.82</v>
+        <v>2605.77</v>
       </c>
       <c r="AI7">
-        <v>3011.7</v>
+        <v>2994.17</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>46.01</v>
+        <v>50.45</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1525,10 +1621,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7712</v>
+        <v>7748.5</v>
       </c>
       <c r="D8">
-        <v>-3.49</v>
+        <v>0.47</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1537,25 +1633,25 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-15.34</v>
+        <v>-14.93</v>
       </c>
       <c r="H8">
-        <v>30.17</v>
+        <v>30.79</v>
       </c>
       <c r="I8">
-        <v>-7.66</v>
+        <v>-4.53</v>
       </c>
       <c r="J8">
-        <v>-7.53</v>
+        <v>-7.96</v>
       </c>
       <c r="K8">
-        <v>0.07000000000000001</v>
+        <v>-1.19</v>
       </c>
       <c r="L8">
-        <v>-15.23</v>
+        <v>-13.75</v>
       </c>
       <c r="M8">
-        <v>13.1</v>
+        <v>12.95</v>
       </c>
       <c r="N8">
         <v>57</v>
@@ -1564,19 +1660,19 @@
         <v>52</v>
       </c>
       <c r="P8">
-        <v>7986.6</v>
+        <v>7913.1</v>
       </c>
       <c r="Q8">
-        <v>8437.219999999999</v>
+        <v>8413.120000000001</v>
       </c>
       <c r="R8">
-        <v>8257.1</v>
+        <v>8247.49</v>
       </c>
       <c r="S8">
-        <v>7438.54</v>
+        <v>7436.79</v>
       </c>
       <c r="T8">
-        <v>3.68</v>
+        <v>4.19</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1591,43 +1687,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>33.04</v>
+        <v>34.46</v>
       </c>
       <c r="Z8">
-        <v>-88.13</v>
+        <v>-117.38</v>
       </c>
       <c r="AA8">
-        <v>17.12</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="AB8">
-        <v>-105.25</v>
+        <v>-107.6</v>
       </c>
       <c r="AC8">
-        <v>4.61</v>
+        <v>2.24</v>
       </c>
       <c r="AD8">
-        <v>4.47</v>
+        <v>3.82</v>
       </c>
       <c r="AE8">
-        <v>288.66</v>
+        <v>284.62</v>
       </c>
       <c r="AF8">
-        <v>-35.64</v>
+        <v>-66.34</v>
       </c>
       <c r="AG8">
-        <v>9060.09</v>
+        <v>9103.33</v>
       </c>
       <c r="AH8">
-        <v>7814.36</v>
+        <v>7722.92</v>
       </c>
       <c r="AI8">
-        <v>8699.24</v>
+        <v>8581.85</v>
       </c>
       <c r="AJ8" t="s">
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>39.15</v>
+        <v>42.59</v>
       </c>
     </row>
   </sheetData>
@@ -1768,7 +1864,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1788,27 +1884,1086 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>52</v>
+      <c r="A6" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="D10" s="7">
+        <v>9.74</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-3.68</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-6.06</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-2.38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>-16.46</v>
+      </c>
+      <c r="D12" s="7">
+        <v>-12.93</v>
+      </c>
+      <c r="E12" s="8">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-15.24</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-12.7</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-12.93</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-9.789999999999999</v>
+      </c>
+      <c r="E14" s="8">
+        <v>3.14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-18.46</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-16.23</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-7.53</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-7.96</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-3.44</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-2.99</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="7">
+        <v>0.92</v>
+      </c>
+      <c r="D18" s="7">
+        <v>-2.67</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-3.59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="7">
+        <v>-4.69</v>
+      </c>
+      <c r="D19" s="7">
+        <v>0.48</v>
+      </c>
+      <c r="E19" s="8">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-4.81</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-3.41</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="7">
+        <v>-1.28</v>
+      </c>
+      <c r="D21" s="7">
+        <v>2.13</v>
+      </c>
+      <c r="E21" s="8">
+        <v>3.41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-11</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-9.08</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="7">
+        <v>-7.66</v>
+      </c>
+      <c r="D23" s="7">
+        <v>-4.53</v>
+      </c>
+      <c r="E23" s="8">
+        <v>3.13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="7">
+        <v>29.26</v>
+      </c>
+      <c r="D24" s="7">
+        <v>31.16</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="7">
+        <v>15.58</v>
+      </c>
+      <c r="D25" s="7">
+        <v>15.03</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="7">
+        <v>-1.64</v>
+      </c>
+      <c r="D26" s="7">
+        <v>-2.77</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-1.13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="7">
+        <v>-26.99</v>
+      </c>
+      <c r="D27" s="7">
+        <v>-27.24</v>
+      </c>
+      <c r="E27" s="9">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-35.01</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-34.13</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="7">
+        <v>15.19</v>
+      </c>
+      <c r="D29" s="7">
+        <v>19.06</v>
+      </c>
+      <c r="E29" s="8">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-15.23</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-13.75</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>10.97</v>
+      </c>
+      <c r="D31" s="7">
+        <v>10.21</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-5.36</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-6.66</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-13.83</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-12.18</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-16.91</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-17.62</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-9.619999999999999</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-9.19</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>3.29</v>
+      </c>
+      <c r="D36" s="7">
+        <v>6.13</v>
+      </c>
+      <c r="E36" s="8">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-1.19</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-6.72</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-7.24</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-0.52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-11.72</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-12.39</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-20.41</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-18.16</v>
+      </c>
+      <c r="E40" s="8">
+        <v>2.25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-30.23</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-28.99</v>
+      </c>
+      <c r="E41" s="8">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-37.86</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-36.79</v>
+      </c>
+      <c r="E42" s="8">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-25.27</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-23.84</v>
+      </c>
+      <c r="E43" s="8">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-15.34</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-14.93</v>
+      </c>
+      <c r="E44" s="8">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>1209.4</v>
+      </c>
+      <c r="D45" s="7">
+        <v>1202.6</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-6.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>862.05</v>
+      </c>
+      <c r="D46" s="7">
+        <v>855.55</v>
+      </c>
+      <c r="E46" s="9">
+        <v>-6.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>1544</v>
+      </c>
+      <c r="D47" s="7">
+        <v>1587.6</v>
+      </c>
+      <c r="E47" s="8">
+        <v>43.6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>1673.7</v>
+      </c>
+      <c r="D48" s="7">
+        <v>1703.4</v>
+      </c>
+      <c r="E48" s="8">
+        <v>29.7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>677.15</v>
+      </c>
+      <c r="D49" s="7">
+        <v>688.9</v>
+      </c>
+      <c r="E49" s="8">
+        <v>11.75</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7">
+        <v>2581.9</v>
+      </c>
+      <c r="D50" s="7">
+        <v>2631.1</v>
+      </c>
+      <c r="E50" s="8">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7">
+        <v>7712</v>
+      </c>
+      <c r="D51" s="7">
+        <v>7748.5</v>
+      </c>
+      <c r="E51" s="8">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="7">
+        <v>52.98</v>
+      </c>
+      <c r="D52" s="7">
+        <v>51.99</v>
+      </c>
+      <c r="E52" s="9">
+        <v>-0.99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="7">
+        <v>44.5</v>
+      </c>
+      <c r="D53" s="7">
+        <v>43.12</v>
+      </c>
+      <c r="E53" s="9">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>24.58</v>
+      </c>
+      <c r="D54" s="7">
+        <v>33.65</v>
+      </c>
+      <c r="E54" s="8">
+        <v>9.07</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>25.62</v>
+      </c>
+      <c r="D55" s="7">
+        <v>30.57</v>
+      </c>
+      <c r="E55" s="8">
+        <v>4.95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>34.16</v>
+      </c>
+      <c r="D56" s="7">
+        <v>39.71</v>
+      </c>
+      <c r="E56" s="8">
+        <v>5.55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>21.39</v>
+      </c>
+      <c r="D57" s="7">
+        <v>26.91</v>
+      </c>
+      <c r="E57" s="8">
+        <v>5.52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>33.04</v>
+      </c>
+      <c r="D58" s="7">
+        <v>34.46</v>
+      </c>
+      <c r="E58" s="8">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="7">
+        <v>-72.41</v>
+      </c>
+      <c r="D59" s="7">
+        <v>-72.56</v>
+      </c>
+      <c r="E59" s="9">
+        <v>-0.15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="7">
+        <v>-35.82</v>
+      </c>
+      <c r="D60" s="7">
+        <v>0.31</v>
+      </c>
+      <c r="E60" s="8">
+        <v>36.13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>-4.99</v>
+      </c>
+      <c r="D61" s="7">
+        <v>0.48</v>
+      </c>
+      <c r="E61" s="8">
+        <v>5.47</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>39.42</v>
+      </c>
+      <c r="D62" s="7">
+        <v>28.14</v>
+      </c>
+      <c r="E62" s="9">
+        <v>-11.28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="D63" s="7">
+        <v>-52.35</v>
+      </c>
+      <c r="E63" s="9">
+        <v>-43.39</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="7">
+        <v>18.34</v>
+      </c>
+      <c r="D64" s="7">
+        <v>-5.11</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-23.45</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="7">
+        <v>-35.64</v>
+      </c>
+      <c r="D65" s="7">
+        <v>-66.34</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-30.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1828,61 +2983,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="B1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="12">
+        <v>56.8</v>
+      </c>
+      <c r="C2" s="13">
+        <v>7</v>
+      </c>
+      <c r="D2" s="12">
+        <v>37.2</v>
+      </c>
+      <c r="E2" s="12">
+        <v>60</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-8</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-4.4</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="6">
-        <v>56.8</v>
-      </c>
-      <c r="C2" s="7">
-        <v>7</v>
-      </c>
-      <c r="D2" s="6">
-        <v>33.8</v>
-      </c>
-      <c r="E2" s="6">
-        <v>60</v>
-      </c>
-      <c r="F2" s="6">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="G2" s="6">
-        <v>-4.5</v>
-      </c>
-      <c r="H2" s="6">
-        <v>57</v>
-      </c>
-      <c r="I2" s="6">
-        <v>40</v>
+      <c r="I2" s="12">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1983,49 +3138,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="B2" s="9">
+      <c r="A2" s="15">
+        <v>0.4864</v>
+      </c>
+      <c r="B2" s="15">
         <v>0.2567</v>
       </c>
-      <c r="C2" s="9">
-        <v>0.2231</v>
-      </c>
-      <c r="D2" s="9">
-        <v>0.1522</v>
-      </c>
-      <c r="E2" s="9">
-        <v>0.131</v>
-      </c>
-      <c r="F2" s="9">
-        <v>0.1024</v>
-      </c>
-      <c r="G2" s="9">
-        <v>0.07139999999999999</v>
+      <c r="C2" s="15">
+        <v>0.2297</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.157</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1295</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.1067</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.06709999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,34 +190,16 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>24.6 → 33.6</t>
+    <t>26.9 → 30.9</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>24.6</t>
-  </si>
-  <si>
-    <t>33.6</t>
-  </si>
-  <si>
-    <t>25.6 → 30.6</t>
-  </si>
-  <si>
-    <t>25.6</t>
-  </si>
-  <si>
-    <t>30.6</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>26.9</t>
+  </si>
+  <si>
+    <t>30.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -419,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -427,11 +409,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -943,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1202.6</v>
+        <v>1196.2</v>
       </c>
       <c r="D2">
-        <v>-0.5600000000000001</v>
+        <v>-0.53</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -955,46 +936,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-7.24</v>
+        <v>-7.74</v>
       </c>
       <c r="H2">
-        <v>60.7</v>
+        <v>59.84</v>
       </c>
       <c r="I2">
-        <v>-2.99</v>
+        <v>-5.63</v>
       </c>
       <c r="J2">
-        <v>9.74</v>
+        <v>9.33</v>
       </c>
       <c r="K2">
-        <v>10.21</v>
+        <v>11.48</v>
       </c>
       <c r="L2">
-        <v>31.16</v>
+        <v>30.37</v>
       </c>
       <c r="M2">
-        <v>6.71</v>
+        <v>6.35</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="P2">
-        <v>1241.18</v>
+        <v>1226.9</v>
       </c>
       <c r="Q2">
-        <v>1191.64</v>
+        <v>1196.94</v>
       </c>
       <c r="R2">
-        <v>1142.68</v>
+        <v>1145.58</v>
       </c>
       <c r="S2">
-        <v>985.79</v>
+        <v>987.52</v>
       </c>
       <c r="T2">
-        <v>21.99</v>
+        <v>21.13</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1009,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>51.99</v>
+        <v>51.02</v>
       </c>
       <c r="Z2">
-        <v>32.39</v>
+        <v>27.82</v>
       </c>
       <c r="AA2">
-        <v>35.06</v>
+        <v>33.61</v>
       </c>
       <c r="AB2">
-        <v>-2.67</v>
+        <v>-5.79</v>
       </c>
       <c r="AC2">
-        <v>16.51</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>39.26</v>
+        <v>18.46</v>
       </c>
       <c r="AE2">
-        <v>51.49</v>
+        <v>50.78</v>
       </c>
       <c r="AF2">
-        <v>-72.56</v>
+        <v>-86.62</v>
       </c>
       <c r="AG2">
-        <v>1360.46</v>
+        <v>1358.86</v>
       </c>
       <c r="AH2">
-        <v>1022.83</v>
+        <v>1035.03</v>
       </c>
       <c r="AI2">
         <v>1148.32</v>
@@ -1045,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>34.21</v>
+        <v>30.24</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1056,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>855.55</v>
+        <v>867.5</v>
       </c>
       <c r="D3">
-        <v>-0.75</v>
+        <v>1.4</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1068,46 +1049,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-12.39</v>
+        <v>-11.16</v>
       </c>
       <c r="H3">
-        <v>61.58</v>
+        <v>63.84</v>
       </c>
       <c r="I3">
-        <v>-2.67</v>
+        <v>-1.68</v>
       </c>
       <c r="J3">
-        <v>-6.06</v>
+        <v>-6.41</v>
       </c>
       <c r="K3">
-        <v>-6.66</v>
+        <v>-4.2</v>
       </c>
       <c r="L3">
-        <v>15.03</v>
+        <v>16.23</v>
       </c>
       <c r="M3">
-        <v>48.64</v>
+        <v>49.68</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P3">
-        <v>881.28</v>
+        <v>878.3200000000001</v>
       </c>
       <c r="Q3">
-        <v>882.08</v>
+        <v>879.72</v>
       </c>
       <c r="R3">
-        <v>882.36</v>
+        <v>883.0599999999999</v>
       </c>
       <c r="S3">
-        <v>800.12</v>
+        <v>801.11</v>
       </c>
       <c r="T3">
-        <v>6.93</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1122,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>43.12</v>
+        <v>46.42</v>
       </c>
       <c r="Z3">
-        <v>-4.26</v>
+        <v>-4.77</v>
       </c>
       <c r="AA3">
-        <v>-2.47</v>
+        <v>-2.93</v>
       </c>
       <c r="AB3">
-        <v>-1.78</v>
+        <v>-1.84</v>
       </c>
       <c r="AC3">
-        <v>34.36</v>
+        <v>22.33</v>
       </c>
       <c r="AD3">
-        <v>58.47</v>
+        <v>40.05</v>
       </c>
       <c r="AE3">
-        <v>25.24</v>
+        <v>25.04</v>
       </c>
       <c r="AF3">
-        <v>0.31</v>
+        <v>-34.03</v>
       </c>
       <c r="AG3">
-        <v>924.09</v>
+        <v>919.28</v>
       </c>
       <c r="AH3">
-        <v>840.0700000000001</v>
+        <v>840.17</v>
       </c>
       <c r="AI3">
         <v>926.39</v>
@@ -1158,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>20.58</v>
+        <v>20.04</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1169,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1587.6</v>
+        <v>1580.7</v>
       </c>
       <c r="D4">
-        <v>2.82</v>
+        <v>-0.43</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1181,46 +1162,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-18.16</v>
+        <v>-18.52</v>
       </c>
       <c r="H4">
-        <v>17.19</v>
+        <v>16.68</v>
       </c>
       <c r="I4">
-        <v>0.48</v>
+        <v>-1.54</v>
       </c>
       <c r="J4">
-        <v>-12.93</v>
+        <v>-13.58</v>
       </c>
       <c r="K4">
-        <v>-12.18</v>
+        <v>-12.71</v>
       </c>
       <c r="L4">
-        <v>-2.77</v>
+        <v>-3.05</v>
       </c>
       <c r="M4">
-        <v>22.97</v>
+        <v>22.72</v>
       </c>
       <c r="N4">
         <v>43</v>
       </c>
       <c r="O4">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P4">
-        <v>1582.54</v>
+        <v>1577.6</v>
       </c>
       <c r="Q4">
-        <v>1692.11</v>
+        <v>1678.2</v>
       </c>
       <c r="R4">
-        <v>1797.81</v>
+        <v>1793.95</v>
       </c>
       <c r="S4">
-        <v>1678.38</v>
+        <v>1678.37</v>
       </c>
       <c r="T4">
-        <v>-5.41</v>
+        <v>-5.82</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1235,34 +1216,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>33.65</v>
+        <v>32.98</v>
       </c>
       <c r="Z4">
-        <v>-67.8</v>
+        <v>-66.43000000000001</v>
       </c>
       <c r="AA4">
-        <v>-57.27</v>
+        <v>-59.11</v>
       </c>
       <c r="AB4">
-        <v>-10.53</v>
+        <v>-7.33</v>
       </c>
       <c r="AC4">
-        <v>24.8</v>
+        <v>37.44</v>
       </c>
       <c r="AD4">
-        <v>21.98</v>
+        <v>26.48</v>
       </c>
       <c r="AE4">
-        <v>45.53</v>
+        <v>44.74</v>
       </c>
       <c r="AF4">
-        <v>0.48</v>
+        <v>-30.81</v>
       </c>
       <c r="AG4">
-        <v>1891.87</v>
+        <v>1867.5</v>
       </c>
       <c r="AH4">
-        <v>1492.36</v>
+        <v>1488.9</v>
       </c>
       <c r="AI4">
         <v>1692.02</v>
@@ -1271,7 +1252,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>63.55</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1282,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1703.4</v>
+        <v>1690</v>
       </c>
       <c r="D5">
-        <v>1.77</v>
+        <v>-0.79</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1294,25 +1275,25 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-28.99</v>
+        <v>-29.55</v>
       </c>
       <c r="H5">
-        <v>1.77</v>
+        <v>0.97</v>
       </c>
       <c r="I5">
-        <v>-3.41</v>
+        <v>-6.18</v>
       </c>
       <c r="J5">
-        <v>-12.7</v>
+        <v>-13.89</v>
       </c>
       <c r="K5">
-        <v>-17.62</v>
+        <v>-17.97</v>
       </c>
       <c r="L5">
-        <v>-27.24</v>
+        <v>-25.86</v>
       </c>
       <c r="M5">
-        <v>15.7</v>
+        <v>15.61</v>
       </c>
       <c r="N5">
         <v>15</v>
@@ -1321,19 +1302,19 @@
         <v>22</v>
       </c>
       <c r="P5">
-        <v>1742.46</v>
+        <v>1720.18</v>
       </c>
       <c r="Q5">
-        <v>1868.57</v>
+        <v>1854.97</v>
       </c>
       <c r="R5">
-        <v>1954.81</v>
+        <v>1947.53</v>
       </c>
       <c r="S5">
-        <v>2043.8</v>
+        <v>2040.32</v>
       </c>
       <c r="T5">
-        <v>-16.66</v>
+        <v>-17.17</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1348,34 +1329,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>30.57</v>
+        <v>29.61</v>
       </c>
       <c r="Z5">
-        <v>-66.92</v>
+        <v>-70.29000000000001</v>
       </c>
       <c r="AA5">
-        <v>-47.62</v>
+        <v>-52.16</v>
       </c>
       <c r="AB5">
-        <v>-19.3</v>
+        <v>-18.14</v>
       </c>
       <c r="AC5">
-        <v>10.12</v>
+        <v>12.18</v>
       </c>
       <c r="AD5">
-        <v>13.78</v>
+        <v>11.12</v>
       </c>
       <c r="AE5">
-        <v>57.9</v>
+        <v>58.09</v>
       </c>
       <c r="AF5">
-        <v>28.14</v>
+        <v>-56.63</v>
       </c>
       <c r="AG5">
-        <v>2072.46</v>
+        <v>2068.69</v>
       </c>
       <c r="AH5">
-        <v>1664.67</v>
+        <v>1641.25</v>
       </c>
       <c r="AI5">
         <v>1853.75</v>
@@ -1384,7 +1365,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>43.86</v>
+        <v>44.32</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1395,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>688.9</v>
+        <v>699.35</v>
       </c>
       <c r="D6">
-        <v>1.74</v>
+        <v>1.52</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1407,46 +1388,46 @@
         <v>674.55</v>
       </c>
       <c r="G6">
-        <v>-36.79</v>
+        <v>-35.83</v>
       </c>
       <c r="H6">
-        <v>2.13</v>
+        <v>3.68</v>
       </c>
       <c r="I6">
-        <v>2.13</v>
+        <v>1.07</v>
       </c>
       <c r="J6">
-        <v>-9.789999999999999</v>
+        <v>-7.58</v>
       </c>
       <c r="K6">
-        <v>-9.19</v>
+        <v>-10.88</v>
       </c>
       <c r="L6">
-        <v>-34.13</v>
+        <v>-33.08</v>
       </c>
       <c r="M6">
-        <v>10.67</v>
+        <v>9.23</v>
       </c>
       <c r="N6">
         <v>29</v>
       </c>
       <c r="O6">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P6">
-        <v>691.35</v>
+        <v>692.83</v>
       </c>
       <c r="Q6">
-        <v>698.83</v>
+        <v>697.1</v>
       </c>
       <c r="R6">
-        <v>753.62</v>
+        <v>752.34</v>
       </c>
       <c r="S6">
-        <v>815.22</v>
+        <v>813.52</v>
       </c>
       <c r="T6">
-        <v>-15.49</v>
+        <v>-14.03</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1461,34 +1442,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>39.71</v>
+        <v>44.22</v>
       </c>
       <c r="Z6">
-        <v>-18.99</v>
+        <v>-17.26</v>
       </c>
       <c r="AA6">
-        <v>-20.55</v>
+        <v>-19.89</v>
       </c>
       <c r="AB6">
-        <v>1.56</v>
+        <v>2.63</v>
       </c>
       <c r="AC6">
         <v>82.19</v>
       </c>
       <c r="AD6">
-        <v>88.97</v>
+        <v>83.03</v>
       </c>
       <c r="AE6">
-        <v>19.94</v>
+        <v>19.58</v>
       </c>
       <c r="AF6">
-        <v>-52.35</v>
+        <v>-33.59</v>
       </c>
       <c r="AG6">
-        <v>725.4400000000001</v>
+        <v>717.98</v>
       </c>
       <c r="AH6">
-        <v>672.22</v>
+        <v>676.23</v>
       </c>
       <c r="AI6">
         <v>739.76</v>
@@ -1497,7 +1478,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>33.85</v>
+        <v>30.45</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1508,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2631.1</v>
+        <v>2668.1</v>
       </c>
       <c r="D7">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1520,46 +1501,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-23.84</v>
+        <v>-22.77</v>
       </c>
       <c r="H7">
-        <v>39.1</v>
+        <v>41.06</v>
       </c>
       <c r="I7">
-        <v>-9.08</v>
+        <v>-5.23</v>
       </c>
       <c r="J7">
-        <v>-16.23</v>
+        <v>-15.84</v>
       </c>
       <c r="K7">
-        <v>6.13</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L7">
-        <v>19.06</v>
+        <v>22.13</v>
       </c>
       <c r="M7">
-        <v>25.67</v>
+        <v>24.32</v>
       </c>
       <c r="N7">
         <v>85</v>
       </c>
       <c r="O7">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="P7">
-        <v>2712.56</v>
+        <v>2683.12</v>
       </c>
       <c r="Q7">
-        <v>2952.5</v>
+        <v>2928.05</v>
       </c>
       <c r="R7">
-        <v>3004.55</v>
+        <v>3006.79</v>
       </c>
       <c r="S7">
-        <v>2515.53</v>
+        <v>2517.66</v>
       </c>
       <c r="T7">
-        <v>4.59</v>
+        <v>5.98</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1574,34 +1555,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>26.91</v>
+        <v>30.85</v>
       </c>
       <c r="Z7">
-        <v>-105.59</v>
+        <v>-110.12</v>
       </c>
       <c r="AA7">
-        <v>-58.44</v>
+        <v>-68.78</v>
       </c>
       <c r="AB7">
-        <v>-47.14</v>
+        <v>-41.34</v>
       </c>
       <c r="AC7">
-        <v>7.53</v>
+        <v>20.42</v>
       </c>
       <c r="AD7">
-        <v>3.07</v>
+        <v>9.6</v>
       </c>
       <c r="AE7">
-        <v>120.26</v>
+        <v>116.37</v>
       </c>
       <c r="AF7">
-        <v>-5.11</v>
+        <v>-52.61</v>
       </c>
       <c r="AG7">
-        <v>3299.23</v>
+        <v>3282.9</v>
       </c>
       <c r="AH7">
-        <v>2605.77</v>
+        <v>2573.2</v>
       </c>
       <c r="AI7">
         <v>2994.17</v>
@@ -1610,7 +1591,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>50.45</v>
+        <v>53.36</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1621,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7748.5</v>
+        <v>7685</v>
       </c>
       <c r="D8">
-        <v>0.47</v>
+        <v>-0.82</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1633,25 +1614,25 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-14.93</v>
+        <v>-15.63</v>
       </c>
       <c r="H8">
-        <v>30.79</v>
+        <v>29.72</v>
       </c>
       <c r="I8">
-        <v>-4.53</v>
+        <v>-4.14</v>
       </c>
       <c r="J8">
-        <v>-7.96</v>
+        <v>-6.63</v>
       </c>
       <c r="K8">
-        <v>-1.19</v>
+        <v>-1.72</v>
       </c>
       <c r="L8">
-        <v>-13.75</v>
+        <v>-14.28</v>
       </c>
       <c r="M8">
-        <v>12.95</v>
+        <v>11.58</v>
       </c>
       <c r="N8">
         <v>57</v>
@@ -1660,19 +1641,19 @@
         <v>52</v>
       </c>
       <c r="P8">
-        <v>7913.1</v>
+        <v>7846.8</v>
       </c>
       <c r="Q8">
-        <v>8413.120000000001</v>
+        <v>8363.9</v>
       </c>
       <c r="R8">
-        <v>8247.49</v>
+        <v>8239.110000000001</v>
       </c>
       <c r="S8">
-        <v>7436.79</v>
+        <v>7434.67</v>
       </c>
       <c r="T8">
-        <v>4.19</v>
+        <v>3.37</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1687,34 +1668,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>34.46</v>
+        <v>33.14</v>
       </c>
       <c r="Z8">
-        <v>-117.38</v>
+        <v>-144.03</v>
       </c>
       <c r="AA8">
-        <v>-9.779999999999999</v>
+        <v>-36.63</v>
       </c>
       <c r="AB8">
-        <v>-107.6</v>
+        <v>-107.4</v>
       </c>
       <c r="AC8">
-        <v>2.24</v>
+        <v>1.96</v>
       </c>
       <c r="AD8">
-        <v>3.82</v>
+        <v>2.94</v>
       </c>
       <c r="AE8">
-        <v>284.62</v>
+        <v>292.79</v>
       </c>
       <c r="AF8">
-        <v>-66.34</v>
+        <v>-20.03</v>
       </c>
       <c r="AG8">
-        <v>9103.33</v>
+        <v>9114.870000000001</v>
       </c>
       <c r="AH8">
-        <v>7722.92</v>
+        <v>7612.93</v>
       </c>
       <c r="AI8">
         <v>8581.85</v>
@@ -1723,7 +1704,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>42.59</v>
+        <v>40.7</v>
       </c>
     </row>
   </sheetData>
@@ -1864,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1904,7 +1885,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1922,1048 +1903,988 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>9.74</v>
+      </c>
+      <c r="D7" s="6">
+        <v>9.33</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-6.06</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-6.41</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-12.93</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-13.58</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.65</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-12.7</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-13.89</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-9.789999999999999</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-7.58</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-16.23</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-15.84</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-7.96</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-6.63</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-2.99</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-5.63</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5" t="s">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-2.67</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-1.68</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.48</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-1.54</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.02</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-3.41</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-6.18</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.77</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2.13</v>
+      </c>
+      <c r="D18" s="6">
+        <v>1.07</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-9.08</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-5.23</v>
+      </c>
+      <c r="E19" s="8">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-4.53</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-4.14</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>31.16</v>
+      </c>
+      <c r="D21" s="6">
+        <v>30.37</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>15.03</v>
+      </c>
+      <c r="D22" s="6">
+        <v>16.23</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-2.77</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-3.05</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-27.24</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-25.86</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-34.13</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-33.08</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>19.06</v>
+      </c>
+      <c r="D26" s="6">
+        <v>22.13</v>
+      </c>
+      <c r="E26" s="8">
+        <v>3.07</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-13.75</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-14.28</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="D10" s="7">
-        <v>9.74</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>10.21</v>
+      </c>
+      <c r="D28" s="6">
+        <v>11.48</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-3.68</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-6.06</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-2.38</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-6.66</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-4.2</v>
+      </c>
+      <c r="E29" s="8">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-16.46</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-12.93</v>
-      </c>
-      <c r="E12" s="8">
-        <v>3.53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-12.18</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-12.71</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-15.24</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-12.7</v>
-      </c>
-      <c r="E13" s="8">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-17.62</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-17.97</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-12.93</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-9.789999999999999</v>
-      </c>
-      <c r="E14" s="8">
-        <v>3.14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-9.19</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-10.88</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.69</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-18.46</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-16.23</v>
-      </c>
-      <c r="E15" s="8">
-        <v>2.23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>6.13</v>
+      </c>
+      <c r="D33" s="6">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="E33" s="8">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-7.53</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-7.96</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-1.19</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-1.72</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-3.44</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-2.99</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-7.24</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-7.74</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0.92</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-2.67</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-3.59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-12.39</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-11.16</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>-4.69</v>
-      </c>
-      <c r="D19" s="7">
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-18.16</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-18.52</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-28.99</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-29.55</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-36.79</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-35.83</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-23.84</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-22.77</v>
+      </c>
+      <c r="E40" s="8">
+        <v>1.07</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-14.93</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-15.63</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1202.6</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1196.2</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-6.4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>855.55</v>
+      </c>
+      <c r="D43" s="6">
+        <v>867.5</v>
+      </c>
+      <c r="E43" s="8">
+        <v>11.95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>1587.6</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1580.7</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-6.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1703.4</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1690</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-13.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>688.9</v>
+      </c>
+      <c r="D46" s="6">
+        <v>699.35</v>
+      </c>
+      <c r="E46" s="8">
+        <v>10.45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>2631.1</v>
+      </c>
+      <c r="D47" s="6">
+        <v>2668.1</v>
+      </c>
+      <c r="E47" s="8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>7748.5</v>
+      </c>
+      <c r="D48" s="6">
+        <v>7685</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-63.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>51.99</v>
+      </c>
+      <c r="D49" s="6">
+        <v>51.02</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>43.12</v>
+      </c>
+      <c r="D50" s="6">
+        <v>46.42</v>
+      </c>
+      <c r="E50" s="8">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>33.65</v>
+      </c>
+      <c r="D51" s="6">
+        <v>32.98</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>30.57</v>
+      </c>
+      <c r="D52" s="6">
+        <v>29.61</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>39.71</v>
+      </c>
+      <c r="D53" s="6">
+        <v>44.22</v>
+      </c>
+      <c r="E53" s="8">
+        <v>4.51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>26.91</v>
+      </c>
+      <c r="D54" s="6">
+        <v>30.85</v>
+      </c>
+      <c r="E54" s="8">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>34.46</v>
+      </c>
+      <c r="D55" s="6">
+        <v>33.14</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>-72.56</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-86.62</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-14.06</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>0.31</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-34.03</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-34.34</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
         <v>0.48</v>
       </c>
-      <c r="E19" s="8">
-        <v>5.17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="D58" s="6">
+        <v>-30.81</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-31.29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-4.81</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-3.41</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>28.14</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-56.63</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-84.77</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-1.28</v>
-      </c>
-      <c r="D21" s="7">
-        <v>2.13</v>
-      </c>
-      <c r="E21" s="8">
-        <v>3.41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-52.35</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-33.59</v>
+      </c>
+      <c r="E60" s="8">
+        <v>18.76</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-11</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-9.08</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.92</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-5.11</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-52.61</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-47.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-7.66</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-4.53</v>
-      </c>
-      <c r="E23" s="8">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>29.26</v>
-      </c>
-      <c r="D24" s="7">
-        <v>31.16</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>15.58</v>
-      </c>
-      <c r="D25" s="7">
-        <v>15.03</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-1.64</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-2.77</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-1.13</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-26.99</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-27.24</v>
-      </c>
-      <c r="E27" s="9">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-35.01</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-34.13</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>15.19</v>
-      </c>
-      <c r="D29" s="7">
-        <v>19.06</v>
-      </c>
-      <c r="E29" s="8">
-        <v>3.87</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-15.23</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-13.75</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>10.97</v>
-      </c>
-      <c r="D31" s="7">
-        <v>10.21</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-0.76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-5.36</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-6.66</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-13.83</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-12.18</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-16.91</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-17.62</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-9.619999999999999</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-9.19</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.43</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>3.29</v>
-      </c>
-      <c r="D36" s="7">
-        <v>6.13</v>
-      </c>
-      <c r="E36" s="8">
-        <v>2.84</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-1.19</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-6.72</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-7.24</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-0.52</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-11.72</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-12.39</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-20.41</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-18.16</v>
-      </c>
-      <c r="E40" s="8">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-30.23</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-28.99</v>
-      </c>
-      <c r="E41" s="8">
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-37.86</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-36.79</v>
-      </c>
-      <c r="E42" s="8">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-25.27</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-23.84</v>
-      </c>
-      <c r="E43" s="8">
-        <v>1.43</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-15.34</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-14.93</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.41</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>1209.4</v>
-      </c>
-      <c r="D45" s="7">
-        <v>1202.6</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-6.8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>862.05</v>
-      </c>
-      <c r="D46" s="7">
-        <v>855.55</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-6.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>1544</v>
-      </c>
-      <c r="D47" s="7">
-        <v>1587.6</v>
-      </c>
-      <c r="E47" s="8">
-        <v>43.6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>1673.7</v>
-      </c>
-      <c r="D48" s="7">
-        <v>1703.4</v>
-      </c>
-      <c r="E48" s="8">
-        <v>29.7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>677.15</v>
-      </c>
-      <c r="D49" s="7">
-        <v>688.9</v>
-      </c>
-      <c r="E49" s="8">
-        <v>11.75</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>2581.9</v>
-      </c>
-      <c r="D50" s="7">
-        <v>2631.1</v>
-      </c>
-      <c r="E50" s="8">
-        <v>49.2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C51" s="7">
-        <v>7712</v>
-      </c>
-      <c r="D51" s="7">
-        <v>7748.5</v>
-      </c>
-      <c r="E51" s="8">
-        <v>36.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="7">
-        <v>52.98</v>
-      </c>
-      <c r="D52" s="7">
-        <v>51.99</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-0.99</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="7">
-        <v>44.5</v>
-      </c>
-      <c r="D53" s="7">
-        <v>43.12</v>
-      </c>
-      <c r="E53" s="9">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>24.58</v>
-      </c>
-      <c r="D54" s="7">
-        <v>33.65</v>
-      </c>
-      <c r="E54" s="8">
-        <v>9.07</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>25.62</v>
-      </c>
-      <c r="D55" s="7">
-        <v>30.57</v>
-      </c>
-      <c r="E55" s="8">
-        <v>4.95</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>34.16</v>
-      </c>
-      <c r="D56" s="7">
-        <v>39.71</v>
-      </c>
-      <c r="E56" s="8">
-        <v>5.55</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>21.39</v>
-      </c>
-      <c r="D57" s="7">
-        <v>26.91</v>
-      </c>
-      <c r="E57" s="8">
-        <v>5.52</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="7">
-        <v>33.04</v>
-      </c>
-      <c r="D58" s="7">
-        <v>34.46</v>
-      </c>
-      <c r="E58" s="8">
-        <v>1.42</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="7">
-        <v>-72.41</v>
-      </c>
-      <c r="D59" s="7">
-        <v>-72.56</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-0.15</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="7">
-        <v>-35.82</v>
-      </c>
-      <c r="D60" s="7">
-        <v>0.31</v>
-      </c>
-      <c r="E60" s="8">
-        <v>36.13</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="7">
-        <v>-4.99</v>
-      </c>
-      <c r="D61" s="7">
-        <v>0.48</v>
-      </c>
-      <c r="E61" s="8">
-        <v>5.47</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>39.42</v>
-      </c>
-      <c r="D62" s="7">
-        <v>28.14</v>
-      </c>
-      <c r="E62" s="9">
-        <v>-11.28</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="D63" s="7">
-        <v>-52.35</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-43.39</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>18.34</v>
-      </c>
-      <c r="D64" s="7">
-        <v>-5.11</v>
-      </c>
-      <c r="E64" s="9">
-        <v>-23.45</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="7">
-        <v>-35.64</v>
-      </c>
-      <c r="D65" s="7">
+      <c r="C62" s="6">
         <v>-66.34</v>
       </c>
-      <c r="E65" s="9">
-        <v>-30.7</v>
+      <c r="D62" s="6">
+        <v>-20.03</v>
+      </c>
+      <c r="E62" s="8">
+        <v>46.31</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2983,60 +2904,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>78</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>56.8</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>37.2</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>38.3</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F2" s="12">
-        <v>-8</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-4.4</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-7.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-4</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -3138,49 +3059,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.4864</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.2567</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2297</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.157</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1295</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.1067</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.06709999999999999</v>
+      <c r="A2" s="14">
+        <v>0.4968</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2432</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2272</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1561</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1158</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.09230000000000001</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0635</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="78">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,16 +190,31 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>26.9 → 30.9</t>
+    <t>29.6 → 35.0</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>26.9</t>
-  </si>
-  <si>
-    <t>30.9</t>
+    <t>29.6</t>
+  </si>
+  <si>
+    <t>35.0</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>51.0 → 49.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>51.0</t>
+  </si>
+  <si>
+    <t>49.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -401,7 +416,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -409,6 +424,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -924,10 +940,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1196.2</v>
+        <v>1184.7</v>
       </c>
       <c r="D2">
-        <v>-0.53</v>
+        <v>-0.96</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -936,46 +952,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-7.74</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="H2">
-        <v>59.84</v>
+        <v>58.31</v>
       </c>
       <c r="I2">
-        <v>-5.63</v>
+        <v>-6.69</v>
       </c>
       <c r="J2">
-        <v>9.33</v>
+        <v>8.67</v>
       </c>
       <c r="K2">
-        <v>11.48</v>
+        <v>11.11</v>
       </c>
       <c r="L2">
-        <v>30.37</v>
+        <v>29.32</v>
       </c>
       <c r="M2">
-        <v>6.35</v>
+        <v>5.96</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P2">
-        <v>1226.9</v>
+        <v>1209.92</v>
       </c>
       <c r="Q2">
-        <v>1196.94</v>
+        <v>1202.42</v>
       </c>
       <c r="R2">
-        <v>1145.58</v>
+        <v>1148</v>
       </c>
       <c r="S2">
-        <v>987.52</v>
+        <v>989.1900000000001</v>
       </c>
       <c r="T2">
-        <v>21.13</v>
+        <v>19.76</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +1006,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>51.02</v>
+        <v>49.25</v>
       </c>
       <c r="Z2">
-        <v>27.82</v>
+        <v>23</v>
       </c>
       <c r="AA2">
-        <v>33.61</v>
+        <v>31.49</v>
       </c>
       <c r="AB2">
-        <v>-5.79</v>
+        <v>-8.49</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>18.46</v>
+        <v>5.5</v>
       </c>
       <c r="AE2">
-        <v>50.78</v>
+        <v>50.09</v>
       </c>
       <c r="AF2">
-        <v>-86.62</v>
+        <v>-72.62</v>
       </c>
       <c r="AG2">
-        <v>1358.86</v>
+        <v>1354.08</v>
       </c>
       <c r="AH2">
-        <v>1035.03</v>
+        <v>1050.76</v>
       </c>
       <c r="AI2">
         <v>1148.32</v>
@@ -1026,7 +1042,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>30.24</v>
+        <v>29.14</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1053,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>867.5</v>
+        <v>854</v>
       </c>
       <c r="D3">
-        <v>1.4</v>
+        <v>-1.56</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1049,46 +1065,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-11.16</v>
+        <v>-12.54</v>
       </c>
       <c r="H3">
-        <v>63.84</v>
+        <v>61.29</v>
       </c>
       <c r="I3">
-        <v>-1.68</v>
+        <v>-6.36</v>
       </c>
       <c r="J3">
-        <v>-6.41</v>
+        <v>-6.62</v>
       </c>
       <c r="K3">
-        <v>-4.2</v>
+        <v>-6.55</v>
       </c>
       <c r="L3">
-        <v>16.23</v>
+        <v>15.05</v>
       </c>
       <c r="M3">
-        <v>49.68</v>
+        <v>49.64</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="P3">
-        <v>878.3200000000001</v>
+        <v>866.72</v>
       </c>
       <c r="Q3">
-        <v>879.72</v>
+        <v>876.97</v>
       </c>
       <c r="R3">
-        <v>883.0599999999999</v>
+        <v>882.87</v>
       </c>
       <c r="S3">
-        <v>801.11</v>
+        <v>802.0599999999999</v>
       </c>
       <c r="T3">
-        <v>8.289999999999999</v>
+        <v>6.48</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,43 +1119,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>46.42</v>
+        <v>43.36</v>
       </c>
       <c r="Z3">
-        <v>-4.77</v>
+        <v>-6.19</v>
       </c>
       <c r="AA3">
-        <v>-2.93</v>
+        <v>-3.58</v>
       </c>
       <c r="AB3">
-        <v>-1.84</v>
+        <v>-2.61</v>
       </c>
       <c r="AC3">
-        <v>22.33</v>
+        <v>19.98</v>
       </c>
       <c r="AD3">
-        <v>40.05</v>
+        <v>25.56</v>
       </c>
       <c r="AE3">
-        <v>25.04</v>
+        <v>25.62</v>
       </c>
       <c r="AF3">
-        <v>-34.03</v>
+        <v>13.38</v>
       </c>
       <c r="AG3">
-        <v>919.28</v>
+        <v>915.6</v>
       </c>
       <c r="AH3">
-        <v>840.17</v>
+        <v>838.35</v>
       </c>
       <c r="AI3">
-        <v>926.39</v>
+        <v>921.33</v>
       </c>
       <c r="AJ3" t="s">
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>20.04</v>
+        <v>22.06</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1166,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1580.7</v>
+        <v>1620.7</v>
       </c>
       <c r="D4">
-        <v>-0.43</v>
+        <v>2.53</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1162,46 +1178,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-18.52</v>
+        <v>-16.46</v>
       </c>
       <c r="H4">
-        <v>16.68</v>
+        <v>19.64</v>
       </c>
       <c r="I4">
-        <v>-1.54</v>
+        <v>0.6</v>
       </c>
       <c r="J4">
-        <v>-13.58</v>
+        <v>-12.82</v>
       </c>
       <c r="K4">
-        <v>-12.71</v>
+        <v>-8.51</v>
       </c>
       <c r="L4">
-        <v>-3.05</v>
+        <v>0.91</v>
       </c>
       <c r="M4">
-        <v>22.72</v>
+        <v>22.43</v>
       </c>
       <c r="N4">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="O4">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="P4">
-        <v>1577.6</v>
+        <v>1579.54</v>
       </c>
       <c r="Q4">
-        <v>1678.2</v>
+        <v>1666.94</v>
       </c>
       <c r="R4">
-        <v>1793.95</v>
+        <v>1789.36</v>
       </c>
       <c r="S4">
-        <v>1678.37</v>
+        <v>1678.08</v>
       </c>
       <c r="T4">
-        <v>-5.82</v>
+        <v>-3.42</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1216,34 +1232,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>32.98</v>
+        <v>40.45</v>
       </c>
       <c r="Z4">
-        <v>-66.43000000000001</v>
+        <v>-61.41</v>
       </c>
       <c r="AA4">
-        <v>-59.11</v>
+        <v>-59.57</v>
       </c>
       <c r="AB4">
-        <v>-7.33</v>
+        <v>-1.84</v>
       </c>
       <c r="AC4">
-        <v>37.44</v>
+        <v>65.7</v>
       </c>
       <c r="AD4">
-        <v>26.48</v>
+        <v>42.65</v>
       </c>
       <c r="AE4">
-        <v>44.74</v>
+        <v>45.08</v>
       </c>
       <c r="AF4">
-        <v>-30.81</v>
+        <v>4.54</v>
       </c>
       <c r="AG4">
-        <v>1867.5</v>
+        <v>1840.37</v>
       </c>
       <c r="AH4">
-        <v>1488.9</v>
+        <v>1493.51</v>
       </c>
       <c r="AI4">
         <v>1692.02</v>
@@ -1252,7 +1268,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>60.68</v>
+        <v>56.06</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1279,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1690</v>
+        <v>1723.2</v>
       </c>
       <c r="D5">
-        <v>-0.79</v>
+        <v>1.96</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1275,22 +1291,22 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-29.55</v>
+        <v>-28.16</v>
       </c>
       <c r="H5">
-        <v>0.97</v>
+        <v>2.96</v>
       </c>
       <c r="I5">
-        <v>-6.18</v>
+        <v>-3.64</v>
       </c>
       <c r="J5">
-        <v>-13.89</v>
+        <v>-12.17</v>
       </c>
       <c r="K5">
-        <v>-17.97</v>
+        <v>-16.82</v>
       </c>
       <c r="L5">
-        <v>-25.86</v>
+        <v>-22.85</v>
       </c>
       <c r="M5">
         <v>15.61</v>
@@ -1299,22 +1315,22 @@
         <v>15</v>
       </c>
       <c r="O5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P5">
-        <v>1720.18</v>
+        <v>1707.16</v>
       </c>
       <c r="Q5">
-        <v>1854.97</v>
+        <v>1844.68</v>
       </c>
       <c r="R5">
-        <v>1947.53</v>
+        <v>1940.52</v>
       </c>
       <c r="S5">
-        <v>2040.32</v>
+        <v>2036.94</v>
       </c>
       <c r="T5">
-        <v>-17.17</v>
+        <v>-15.4</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,34 +1345,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>29.61</v>
+        <v>35.04</v>
       </c>
       <c r="Z5">
-        <v>-70.29000000000001</v>
+        <v>-69.48999999999999</v>
       </c>
       <c r="AA5">
-        <v>-52.16</v>
+        <v>-55.62</v>
       </c>
       <c r="AB5">
-        <v>-18.14</v>
+        <v>-13.86</v>
       </c>
       <c r="AC5">
-        <v>12.18</v>
+        <v>25.01</v>
       </c>
       <c r="AD5">
-        <v>11.12</v>
+        <v>15.77</v>
       </c>
       <c r="AE5">
-        <v>58.09</v>
+        <v>57.83</v>
       </c>
       <c r="AF5">
-        <v>-56.63</v>
+        <v>-60.94</v>
       </c>
       <c r="AG5">
-        <v>2068.69</v>
+        <v>2063.15</v>
       </c>
       <c r="AH5">
-        <v>1641.25</v>
+        <v>1626.21</v>
       </c>
       <c r="AI5">
         <v>1853.75</v>
@@ -1365,7 +1381,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>44.32</v>
+        <v>44.72</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1392,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>699.35</v>
+        <v>706.85</v>
       </c>
       <c r="D6">
-        <v>1.52</v>
+        <v>1.07</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1388,46 +1404,46 @@
         <v>674.55</v>
       </c>
       <c r="G6">
-        <v>-35.83</v>
+        <v>-35.14</v>
       </c>
       <c r="H6">
-        <v>3.68</v>
+        <v>4.79</v>
       </c>
       <c r="I6">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="J6">
-        <v>-7.58</v>
+        <v>-3.69</v>
       </c>
       <c r="K6">
-        <v>-10.88</v>
+        <v>-9.26</v>
       </c>
       <c r="L6">
-        <v>-33.08</v>
+        <v>-33.1</v>
       </c>
       <c r="M6">
-        <v>9.23</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>29</v>
       </c>
       <c r="O6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P6">
-        <v>692.83</v>
+        <v>694.36</v>
       </c>
       <c r="Q6">
-        <v>697.1</v>
+        <v>696.39</v>
       </c>
       <c r="R6">
-        <v>752.34</v>
+        <v>751.28</v>
       </c>
       <c r="S6">
-        <v>813.52</v>
+        <v>811.74</v>
       </c>
       <c r="T6">
-        <v>-14.03</v>
+        <v>-12.92</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1442,34 +1458,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>44.22</v>
+        <v>47.26</v>
       </c>
       <c r="Z6">
-        <v>-17.26</v>
+        <v>-15.12</v>
       </c>
       <c r="AA6">
-        <v>-19.89</v>
+        <v>-18.94</v>
       </c>
       <c r="AB6">
-        <v>2.63</v>
+        <v>3.82</v>
       </c>
       <c r="AC6">
-        <v>82.19</v>
+        <v>97.47</v>
       </c>
       <c r="AD6">
-        <v>83.03</v>
+        <v>87.28</v>
       </c>
       <c r="AE6">
-        <v>19.58</v>
+        <v>19.14</v>
       </c>
       <c r="AF6">
-        <v>-33.59</v>
+        <v>5.47</v>
       </c>
       <c r="AG6">
-        <v>717.98</v>
+        <v>714.64</v>
       </c>
       <c r="AH6">
-        <v>676.23</v>
+        <v>678.15</v>
       </c>
       <c r="AI6">
         <v>739.76</v>
@@ -1478,7 +1494,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>30.45</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1505,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2668.1</v>
+        <v>2632.2</v>
       </c>
       <c r="D7">
-        <v>1.41</v>
+        <v>-1.35</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1501,46 +1517,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-22.77</v>
+        <v>-23.81</v>
       </c>
       <c r="H7">
-        <v>41.06</v>
+        <v>39.16</v>
       </c>
       <c r="I7">
-        <v>-5.23</v>
+        <v>-6.63</v>
       </c>
       <c r="J7">
-        <v>-15.84</v>
+        <v>-16.63</v>
       </c>
       <c r="K7">
-        <v>8.220000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="L7">
-        <v>22.13</v>
+        <v>19.42</v>
       </c>
       <c r="M7">
-        <v>24.32</v>
+        <v>24.97</v>
       </c>
       <c r="N7">
         <v>85</v>
       </c>
       <c r="O7">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="P7">
-        <v>2683.12</v>
+        <v>2645.74</v>
       </c>
       <c r="Q7">
-        <v>2928.05</v>
+        <v>2897.15</v>
       </c>
       <c r="R7">
-        <v>3006.79</v>
+        <v>3007.82</v>
       </c>
       <c r="S7">
-        <v>2517.66</v>
+        <v>2519.65</v>
       </c>
       <c r="T7">
-        <v>5.98</v>
+        <v>4.47</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1555,43 +1571,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>30.85</v>
+        <v>29.2</v>
       </c>
       <c r="Z7">
-        <v>-110.12</v>
+        <v>-115.27</v>
       </c>
       <c r="AA7">
-        <v>-68.78</v>
+        <v>-78.08</v>
       </c>
       <c r="AB7">
-        <v>-41.34</v>
+        <v>-37.2</v>
       </c>
       <c r="AC7">
-        <v>20.42</v>
+        <v>31.07</v>
       </c>
       <c r="AD7">
-        <v>9.6</v>
+        <v>19.67</v>
       </c>
       <c r="AE7">
-        <v>116.37</v>
+        <v>119.54</v>
       </c>
       <c r="AF7">
-        <v>-52.61</v>
+        <v>18.54</v>
       </c>
       <c r="AG7">
-        <v>3282.9</v>
+        <v>3241.35</v>
       </c>
       <c r="AH7">
-        <v>2573.2</v>
+        <v>2552.95</v>
       </c>
       <c r="AI7">
-        <v>2994.17</v>
+        <v>2967.97</v>
       </c>
       <c r="AJ7" t="s">
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>53.36</v>
+        <v>56.91</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1618,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7685</v>
+        <v>7791</v>
       </c>
       <c r="D8">
-        <v>-0.82</v>
+        <v>1.38</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1614,46 +1630,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-15.63</v>
+        <v>-14.47</v>
       </c>
       <c r="H8">
-        <v>29.72</v>
+        <v>31.5</v>
       </c>
       <c r="I8">
-        <v>-4.14</v>
+        <v>-3.79</v>
       </c>
       <c r="J8">
-        <v>-6.63</v>
+        <v>-10.13</v>
       </c>
       <c r="K8">
-        <v>-1.72</v>
+        <v>-0.45</v>
       </c>
       <c r="L8">
-        <v>-14.28</v>
+        <v>-12.22</v>
       </c>
       <c r="M8">
-        <v>11.58</v>
+        <v>12.22</v>
       </c>
       <c r="N8">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O8">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="P8">
-        <v>7846.8</v>
+        <v>7785.5</v>
       </c>
       <c r="Q8">
-        <v>8363.9</v>
+        <v>8312.83</v>
       </c>
       <c r="R8">
-        <v>8239.110000000001</v>
+        <v>8230.780000000001</v>
       </c>
       <c r="S8">
-        <v>7434.67</v>
+        <v>7433.35</v>
       </c>
       <c r="T8">
-        <v>3.37</v>
+        <v>4.81</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1668,34 +1684,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>33.14</v>
+        <v>37.43</v>
       </c>
       <c r="Z8">
-        <v>-144.03</v>
+        <v>-154.81</v>
       </c>
       <c r="AA8">
-        <v>-36.63</v>
+        <v>-60.27</v>
       </c>
       <c r="AB8">
-        <v>-107.4</v>
+        <v>-94.54000000000001</v>
       </c>
       <c r="AC8">
-        <v>1.96</v>
+        <v>7.62</v>
       </c>
       <c r="AD8">
-        <v>2.94</v>
+        <v>3.94</v>
       </c>
       <c r="AE8">
-        <v>292.79</v>
+        <v>283.55</v>
       </c>
       <c r="AF8">
-        <v>-20.03</v>
+        <v>-71.43000000000001</v>
       </c>
       <c r="AG8">
-        <v>9114.870000000001</v>
+        <v>9074.209999999999</v>
       </c>
       <c r="AH8">
-        <v>7612.93</v>
+        <v>7551.44</v>
       </c>
       <c r="AI8">
         <v>8581.85</v>
@@ -1704,7 +1720,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>40.7</v>
+        <v>39.06</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1861,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1885,7 +1901,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1903,988 +1919,1042 @@
         <v>59</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>9.74</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C8" s="7">
         <v>9.33</v>
       </c>
-      <c r="E7" s="7">
-        <v>-0.41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="D8" s="7">
+        <v>8.67</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-6.06</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C9" s="7">
         <v>-6.41</v>
       </c>
-      <c r="E8" s="7">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="D9" s="7">
+        <v>-6.62</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-12.93</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C10" s="7">
         <v>-13.58</v>
       </c>
-      <c r="E9" s="7">
-        <v>-0.65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="7">
+        <v>-12.82</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-12.7</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C11" s="7">
         <v>-13.89</v>
       </c>
-      <c r="E10" s="7">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="D11" s="7">
+        <v>-12.17</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1.72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-9.789999999999999</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C12" s="7">
         <v>-7.58</v>
       </c>
-      <c r="E11" s="8">
-        <v>2.21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="D12" s="7">
+        <v>-3.69</v>
+      </c>
+      <c r="E12" s="9">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-16.23</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C13" s="7">
         <v>-15.84</v>
       </c>
-      <c r="E12" s="8">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="D13" s="7">
+        <v>-16.63</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-7.96</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C14" s="7">
         <v>-6.63</v>
       </c>
-      <c r="E13" s="8">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="D14" s="7">
+        <v>-10.13</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>-2.99</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C15" s="7">
         <v>-5.63</v>
       </c>
-      <c r="E14" s="7">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="D15" s="7">
+        <v>-6.69</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-2.67</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C16" s="7">
         <v>-1.68</v>
       </c>
-      <c r="E15" s="8">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="D16" s="7">
+        <v>-6.36</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-4.68</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>0.48</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C17" s="7">
         <v>-1.54</v>
       </c>
-      <c r="E16" s="7">
-        <v>-2.02</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="D17" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="E17" s="9">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>-3.41</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C18" s="7">
         <v>-6.18</v>
       </c>
-      <c r="E17" s="7">
-        <v>-2.77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="D18" s="7">
+        <v>-3.64</v>
+      </c>
+      <c r="E18" s="9">
+        <v>2.54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>2.13</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C19" s="7">
         <v>1.07</v>
       </c>
-      <c r="E18" s="7">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="D19" s="7">
+        <v>1.09</v>
+      </c>
+      <c r="E19" s="9">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="6">
-        <v>-9.08</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C20" s="7">
         <v>-5.23</v>
       </c>
-      <c r="E19" s="8">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="D20" s="7">
+        <v>-6.63</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="6">
-        <v>-4.53</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C21" s="7">
         <v>-4.14</v>
       </c>
-      <c r="E20" s="8">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="D21" s="7">
+        <v>-3.79</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B22" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="6">
-        <v>31.16</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C22" s="7">
         <v>30.37</v>
       </c>
-      <c r="E21" s="7">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="D22" s="7">
+        <v>29.32</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.05</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="6">
-        <v>15.03</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C23" s="7">
         <v>16.23</v>
       </c>
-      <c r="E22" s="8">
-        <v>1.2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="D23" s="7">
+        <v>15.05</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.18</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B24" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="6">
-        <v>-2.77</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C24" s="7">
         <v>-3.05</v>
       </c>
-      <c r="E23" s="7">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="D24" s="7">
+        <v>0.91</v>
+      </c>
+      <c r="E24" s="9">
+        <v>3.96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="6">
-        <v>-27.24</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C25" s="7">
         <v>-25.86</v>
       </c>
-      <c r="E24" s="8">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="D25" s="7">
+        <v>-22.85</v>
+      </c>
+      <c r="E25" s="9">
+        <v>3.01</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="6">
-        <v>-34.13</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C26" s="7">
         <v>-33.08</v>
       </c>
-      <c r="E25" s="8">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="D26" s="7">
+        <v>-33.1</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="6">
-        <v>19.06</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C27" s="7">
         <v>22.13</v>
       </c>
-      <c r="E26" s="8">
-        <v>3.07</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="D27" s="7">
+        <v>19.42</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
-        <v>-13.75</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C28" s="7">
         <v>-14.28</v>
       </c>
-      <c r="E27" s="7">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="D28" s="7">
+        <v>-12.22</v>
+      </c>
+      <c r="E28" s="9">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B29" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="6">
-        <v>10.21</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C29" s="7">
         <v>11.48</v>
       </c>
-      <c r="E28" s="8">
+      <c r="D29" s="7">
+        <v>11.11</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-4.2</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-6.55</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-12.71</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-8.51</v>
+      </c>
+      <c r="E31" s="9">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-17.97</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-16.82</v>
+      </c>
+      <c r="E32" s="9">
+        <v>1.15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-10.88</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-9.26</v>
+      </c>
+      <c r="E33" s="9">
+        <v>1.62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="D34" s="7">
+        <v>6.7</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>-1.72</v>
+      </c>
+      <c r="D35" s="7">
+        <v>-0.45</v>
+      </c>
+      <c r="E35" s="9">
         <v>1.27</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-7.74</v>
+      </c>
+      <c r="D36" s="7">
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-6.66</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-4.2</v>
-      </c>
-      <c r="E29" s="8">
-        <v>2.46</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-11.16</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-12.54</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-12.18</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-12.71</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-18.52</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-16.46</v>
+      </c>
+      <c r="E38" s="9">
+        <v>2.06</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-17.62</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-17.97</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-29.55</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-28.16</v>
+      </c>
+      <c r="E39" s="9">
+        <v>1.39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-9.19</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-10.88</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.69</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-35.83</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-35.14</v>
+      </c>
+      <c r="E40" s="9">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>6.13</v>
-      </c>
-      <c r="D33" s="6">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="E33" s="8">
-        <v>2.09</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-22.77</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-23.81</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-1.19</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-1.72</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-15.63</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-14.47</v>
+      </c>
+      <c r="E42" s="9">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-7.24</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-7.74</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="7">
+        <v>1196.2</v>
+      </c>
+      <c r="D43" s="7">
+        <v>1184.7</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-11.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-12.39</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-11.16</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.23</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="7">
+        <v>867.5</v>
+      </c>
+      <c r="D44" s="7">
+        <v>854</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-13.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-18.16</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-18.52</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.36</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>1580.7</v>
+      </c>
+      <c r="D45" s="7">
+        <v>1620.7</v>
+      </c>
+      <c r="E45" s="9">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-28.99</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-29.55</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>1690</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1723.2</v>
+      </c>
+      <c r="E46" s="9">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-36.79</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-35.83</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>699.35</v>
+      </c>
+      <c r="D47" s="7">
+        <v>706.85</v>
+      </c>
+      <c r="E47" s="9">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-23.84</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-22.77</v>
-      </c>
-      <c r="E40" s="8">
-        <v>1.07</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>2668.1</v>
+      </c>
+      <c r="D48" s="7">
+        <v>2632.2</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-35.9</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-14.93</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-15.63</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>7685</v>
+      </c>
+      <c r="D49" s="7">
+        <v>7791</v>
+      </c>
+      <c r="E49" s="9">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="7">
+        <v>43</v>
+      </c>
+      <c r="D50" s="7">
+        <v>57</v>
+      </c>
+      <c r="E50" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="7">
+        <v>57</v>
+      </c>
+      <c r="D51" s="7">
+        <v>43</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1202.6</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1196.2</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-6.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="7">
+        <v>51.02</v>
+      </c>
+      <c r="D52" s="7">
+        <v>49.25</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-1.77</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>855.55</v>
-      </c>
-      <c r="D43" s="6">
-        <v>867.5</v>
-      </c>
-      <c r="E43" s="8">
-        <v>11.95</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="B53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="7">
+        <v>46.42</v>
+      </c>
+      <c r="D53" s="7">
+        <v>43.36</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-3.06</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1587.6</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1580.7</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-6.9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>32.98</v>
+      </c>
+      <c r="D54" s="7">
+        <v>40.45</v>
+      </c>
+      <c r="E54" s="9">
+        <v>7.47</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1703.4</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1690</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-13.4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>29.61</v>
+      </c>
+      <c r="D55" s="7">
+        <v>35.04</v>
+      </c>
+      <c r="E55" s="9">
+        <v>5.43</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>688.9</v>
-      </c>
-      <c r="D46" s="6">
-        <v>699.35</v>
-      </c>
-      <c r="E46" s="8">
-        <v>10.45</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>44.22</v>
+      </c>
+      <c r="D56" s="7">
+        <v>47.26</v>
+      </c>
+      <c r="E56" s="9">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>2631.1</v>
-      </c>
-      <c r="D47" s="6">
-        <v>2668.1</v>
-      </c>
-      <c r="E47" s="8">
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>30.85</v>
+      </c>
+      <c r="D57" s="7">
+        <v>29.2</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="7">
+        <v>33.14</v>
+      </c>
+      <c r="D58" s="7">
+        <v>37.43</v>
+      </c>
+      <c r="E58" s="9">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="B59" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="7">
+        <v>-86.62</v>
+      </c>
+      <c r="D59" s="7">
+        <v>-72.62</v>
+      </c>
+      <c r="E59" s="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="7">
+        <v>-34.03</v>
+      </c>
+      <c r="D60" s="7">
+        <v>13.38</v>
+      </c>
+      <c r="E60" s="9">
+        <v>47.41</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>-30.81</v>
+      </c>
+      <c r="D61" s="7">
+        <v>4.54</v>
+      </c>
+      <c r="E61" s="9">
+        <v>35.35</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>-56.63</v>
+      </c>
+      <c r="D62" s="7">
+        <v>-60.94</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-4.31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7">
+        <v>-33.59</v>
+      </c>
+      <c r="D63" s="7">
+        <v>5.47</v>
+      </c>
+      <c r="E63" s="9">
+        <v>39.06</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="7">
+        <v>-52.61</v>
+      </c>
+      <c r="D64" s="7">
+        <v>18.54</v>
+      </c>
+      <c r="E64" s="9">
+        <v>71.15000000000001</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>7748.5</v>
-      </c>
-      <c r="D48" s="6">
-        <v>7685</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-63.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="6">
-        <v>51.99</v>
-      </c>
-      <c r="D49" s="6">
-        <v>51.02</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="6">
-        <v>43.12</v>
-      </c>
-      <c r="D50" s="6">
-        <v>46.42</v>
-      </c>
-      <c r="E50" s="8">
-        <v>3.3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="6">
-        <v>33.65</v>
-      </c>
-      <c r="D51" s="6">
-        <v>32.98</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-0.67</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="6">
-        <v>30.57</v>
-      </c>
-      <c r="D52" s="6">
-        <v>29.61</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>39.71</v>
-      </c>
-      <c r="D53" s="6">
-        <v>44.22</v>
-      </c>
-      <c r="E53" s="8">
-        <v>4.51</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>26.91</v>
-      </c>
-      <c r="D54" s="6">
-        <v>30.85</v>
-      </c>
-      <c r="E54" s="8">
-        <v>3.94</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>34.46</v>
-      </c>
-      <c r="D55" s="6">
-        <v>33.14</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="5" t="s">
+      <c r="B65" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="6">
-        <v>-72.56</v>
-      </c>
-      <c r="D56" s="6">
-        <v>-86.62</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-14.06</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="6">
-        <v>0.31</v>
-      </c>
-      <c r="D57" s="6">
-        <v>-34.03</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-34.34</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="6">
-        <v>0.48</v>
-      </c>
-      <c r="D58" s="6">
-        <v>-30.81</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-31.29</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="6">
-        <v>28.14</v>
-      </c>
-      <c r="D59" s="6">
-        <v>-56.63</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-84.77</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="6">
-        <v>-52.35</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-33.59</v>
-      </c>
-      <c r="E60" s="8">
-        <v>18.76</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>-5.11</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-52.61</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-47.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-66.34</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C65" s="7">
         <v>-20.03</v>
       </c>
-      <c r="E62" s="8">
-        <v>46.31</v>
+      <c r="D65" s="7">
+        <v>-71.43000000000001</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-51.4</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2904,60 +2974,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>72</v>
       </c>
+      <c r="E1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="12">
         <v>56.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="13">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>38.3</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="12">
+        <v>40.3</v>
+      </c>
+      <c r="E2" s="12">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-7.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-4</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="12">
+        <v>-7.6</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-3.4</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>30</v>
       </c>
     </row>
@@ -3059,49 +3129,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.4968</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2432</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2272</v>
-      </c>
-      <c r="D2" s="14">
+      <c r="A2" s="15">
+        <v>0.4964</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.2497</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2243</v>
+      </c>
+      <c r="D2" s="15">
         <v>0.1561</v>
       </c>
-      <c r="E2" s="14">
-        <v>0.1158</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.09230000000000001</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0635</v>
+      <c r="E2" s="15">
+        <v>0.1222</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.09</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.0596</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -190,31 +190,16 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>29.6 → 35.0</t>
+    <t>29.2 → 33.2</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>29.6</t>
-  </si>
-  <si>
-    <t>35.0</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>51.0 → 49.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>51.0</t>
-  </si>
-  <si>
-    <t>49.2</t>
+    <t>29.2</t>
+  </si>
+  <si>
+    <t>33.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -416,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -424,11 +409,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -940,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1184.7</v>
+        <v>1171</v>
       </c>
       <c r="D2">
-        <v>-0.96</v>
+        <v>-1.16</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -952,25 +936,25 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-8.619999999999999</v>
+        <v>-9.68</v>
       </c>
       <c r="H2">
-        <v>58.31</v>
+        <v>56.48</v>
       </c>
       <c r="I2">
-        <v>-6.69</v>
+        <v>-6.82</v>
       </c>
       <c r="J2">
-        <v>8.67</v>
+        <v>8.91</v>
       </c>
       <c r="K2">
-        <v>11.11</v>
+        <v>8.25</v>
       </c>
       <c r="L2">
-        <v>29.32</v>
+        <v>28.35</v>
       </c>
       <c r="M2">
-        <v>5.96</v>
+        <v>6.15</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -979,19 +963,19 @@
         <v>83</v>
       </c>
       <c r="P2">
-        <v>1209.92</v>
+        <v>1192.78</v>
       </c>
       <c r="Q2">
-        <v>1202.42</v>
+        <v>1209.38</v>
       </c>
       <c r="R2">
-        <v>1148</v>
+        <v>1149.51</v>
       </c>
       <c r="S2">
-        <v>989.1900000000001</v>
+        <v>990.8099999999999</v>
       </c>
       <c r="T2">
-        <v>19.76</v>
+        <v>18.19</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -1006,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>49.25</v>
+        <v>47.15</v>
       </c>
       <c r="Z2">
-        <v>23</v>
+        <v>17.87</v>
       </c>
       <c r="AA2">
-        <v>31.49</v>
+        <v>28.76</v>
       </c>
       <c r="AB2">
-        <v>-8.49</v>
+        <v>-10.89</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>50.09</v>
+        <v>48.91</v>
       </c>
       <c r="AF2">
-        <v>-72.62</v>
+        <v>-82.78</v>
       </c>
       <c r="AG2">
-        <v>1354.08</v>
+        <v>1339.29</v>
       </c>
       <c r="AH2">
-        <v>1050.76</v>
+        <v>1079.47</v>
       </c>
       <c r="AI2">
         <v>1148.32</v>
@@ -1042,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>29.14</v>
+        <v>28.19</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1053,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>854</v>
+        <v>863</v>
       </c>
       <c r="D3">
-        <v>-1.56</v>
+        <v>1.05</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1065,46 +1049,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-12.54</v>
+        <v>-11.62</v>
       </c>
       <c r="H3">
-        <v>61.29</v>
+        <v>62.99</v>
       </c>
       <c r="I3">
-        <v>-6.36</v>
+        <v>-3.52</v>
       </c>
       <c r="J3">
-        <v>-6.62</v>
+        <v>-5.06</v>
       </c>
       <c r="K3">
-        <v>-6.55</v>
+        <v>-7.12</v>
       </c>
       <c r="L3">
-        <v>15.05</v>
+        <v>13.63</v>
       </c>
       <c r="M3">
-        <v>49.64</v>
+        <v>49.19</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="P3">
-        <v>866.72</v>
+        <v>860.42</v>
       </c>
       <c r="Q3">
-        <v>876.97</v>
+        <v>877.22</v>
       </c>
       <c r="R3">
-        <v>882.87</v>
+        <v>883.61</v>
       </c>
       <c r="S3">
-        <v>802.0599999999999</v>
+        <v>803.08</v>
       </c>
       <c r="T3">
-        <v>6.48</v>
+        <v>7.46</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1119,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>43.36</v>
+        <v>45.92</v>
       </c>
       <c r="Z3">
-        <v>-6.19</v>
+        <v>-6.51</v>
       </c>
       <c r="AA3">
-        <v>-3.58</v>
+        <v>-4.17</v>
       </c>
       <c r="AB3">
-        <v>-2.61</v>
+        <v>-2.35</v>
       </c>
       <c r="AC3">
-        <v>19.98</v>
+        <v>25.73</v>
       </c>
       <c r="AD3">
-        <v>25.56</v>
+        <v>22.68</v>
       </c>
       <c r="AE3">
-        <v>25.62</v>
+        <v>25.14</v>
       </c>
       <c r="AF3">
-        <v>13.38</v>
+        <v>-22.27</v>
       </c>
       <c r="AG3">
-        <v>915.6</v>
+        <v>915.39</v>
       </c>
       <c r="AH3">
-        <v>838.35</v>
+        <v>839.0599999999999</v>
       </c>
       <c r="AI3">
         <v>921.33</v>
@@ -1155,7 +1139,7 @@
         <v>48</v>
       </c>
       <c r="AK3">
-        <v>22.06</v>
+        <v>21.46</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1166,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1620.7</v>
+        <v>1563</v>
       </c>
       <c r="D4">
-        <v>2.53</v>
+        <v>-3.56</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1178,46 +1162,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-16.46</v>
+        <v>-19.43</v>
       </c>
       <c r="H4">
-        <v>19.64</v>
+        <v>15.38</v>
       </c>
       <c r="I4">
-        <v>0.6</v>
+        <v>-0.11</v>
       </c>
       <c r="J4">
-        <v>-12.82</v>
+        <v>-15.33</v>
       </c>
       <c r="K4">
-        <v>-8.51</v>
+        <v>-13.35</v>
       </c>
       <c r="L4">
-        <v>0.91</v>
+        <v>-3.53</v>
       </c>
       <c r="M4">
-        <v>22.43</v>
+        <v>21.57</v>
       </c>
       <c r="N4">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O4">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="P4">
-        <v>1579.54</v>
+        <v>1579.2</v>
       </c>
       <c r="Q4">
-        <v>1666.94</v>
+        <v>1655.51</v>
       </c>
       <c r="R4">
-        <v>1789.36</v>
+        <v>1782.86</v>
       </c>
       <c r="S4">
-        <v>1678.08</v>
+        <v>1677.42</v>
       </c>
       <c r="T4">
-        <v>-3.42</v>
+        <v>-6.82</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1232,34 +1216,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>40.45</v>
+        <v>34.48</v>
       </c>
       <c r="Z4">
-        <v>-61.41</v>
+        <v>-61.38</v>
       </c>
       <c r="AA4">
-        <v>-59.57</v>
+        <v>-59.93</v>
       </c>
       <c r="AB4">
-        <v>-1.84</v>
+        <v>-1.45</v>
       </c>
       <c r="AC4">
-        <v>65.7</v>
+        <v>69.14</v>
       </c>
       <c r="AD4">
-        <v>42.65</v>
+        <v>57.43</v>
       </c>
       <c r="AE4">
-        <v>45.08</v>
+        <v>46.73</v>
       </c>
       <c r="AF4">
-        <v>4.54</v>
+        <v>58.8</v>
       </c>
       <c r="AG4">
-        <v>1840.37</v>
+        <v>1824.42</v>
       </c>
       <c r="AH4">
-        <v>1493.51</v>
+        <v>1486.6</v>
       </c>
       <c r="AI4">
         <v>1692.02</v>
@@ -1268,7 +1252,7 @@
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>56.06</v>
+        <v>53.47</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1279,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1723.2</v>
+        <v>1747</v>
       </c>
       <c r="D5">
-        <v>1.96</v>
+        <v>1.38</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1291,46 +1275,46 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-28.16</v>
+        <v>-27.17</v>
       </c>
       <c r="H5">
-        <v>2.96</v>
+        <v>4.38</v>
       </c>
       <c r="I5">
-        <v>-3.64</v>
+        <v>0.09</v>
       </c>
       <c r="J5">
-        <v>-12.17</v>
+        <v>-9.43</v>
       </c>
       <c r="K5">
-        <v>-16.82</v>
+        <v>-15.03</v>
       </c>
       <c r="L5">
-        <v>-22.85</v>
+        <v>-21.83</v>
       </c>
       <c r="M5">
-        <v>15.61</v>
+        <v>16.1</v>
       </c>
       <c r="N5">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="O5">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="P5">
-        <v>1707.16</v>
+        <v>1707.46</v>
       </c>
       <c r="Q5">
-        <v>1844.68</v>
+        <v>1835.08</v>
       </c>
       <c r="R5">
-        <v>1940.52</v>
+        <v>1933.15</v>
       </c>
       <c r="S5">
-        <v>2036.94</v>
+        <v>2033.72</v>
       </c>
       <c r="T5">
-        <v>-15.4</v>
+        <v>-14.1</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1345,34 +1329,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>35.04</v>
+        <v>38.69</v>
       </c>
       <c r="Z5">
-        <v>-69.48999999999999</v>
+        <v>-66.16</v>
       </c>
       <c r="AA5">
-        <v>-55.62</v>
+        <v>-57.73</v>
       </c>
       <c r="AB5">
-        <v>-13.86</v>
+        <v>-8.43</v>
       </c>
       <c r="AC5">
-        <v>25.01</v>
+        <v>36.08</v>
       </c>
       <c r="AD5">
-        <v>15.77</v>
+        <v>24.42</v>
       </c>
       <c r="AE5">
-        <v>57.83</v>
+        <v>57.7</v>
       </c>
       <c r="AF5">
-        <v>-60.94</v>
+        <v>123.24</v>
       </c>
       <c r="AG5">
-        <v>2063.15</v>
+        <v>2052.96</v>
       </c>
       <c r="AH5">
-        <v>1626.21</v>
+        <v>1617.19</v>
       </c>
       <c r="AI5">
         <v>1853.75</v>
@@ -1381,7 +1365,7 @@
         <v>48</v>
       </c>
       <c r="AK5">
-        <v>44.72</v>
+        <v>41.85</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1392,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>706.85</v>
+        <v>691.6</v>
       </c>
       <c r="D6">
-        <v>1.07</v>
+        <v>-2.16</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1404,46 +1388,46 @@
         <v>674.55</v>
       </c>
       <c r="G6">
-        <v>-35.14</v>
+        <v>-36.54</v>
       </c>
       <c r="H6">
-        <v>4.79</v>
+        <v>2.53</v>
       </c>
       <c r="I6">
-        <v>1.09</v>
+        <v>-1.14</v>
       </c>
       <c r="J6">
-        <v>-3.69</v>
+        <v>-4.08</v>
       </c>
       <c r="K6">
-        <v>-9.26</v>
+        <v>-11.18</v>
       </c>
       <c r="L6">
-        <v>-33.1</v>
+        <v>-33.33</v>
       </c>
       <c r="M6">
-        <v>9</v>
+        <v>8.43</v>
       </c>
       <c r="N6">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="O6">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P6">
-        <v>694.36</v>
+        <v>692.77</v>
       </c>
       <c r="Q6">
-        <v>696.39</v>
+        <v>695.84</v>
       </c>
       <c r="R6">
-        <v>751.28</v>
+        <v>749.51</v>
       </c>
       <c r="S6">
-        <v>811.74</v>
+        <v>809.89</v>
       </c>
       <c r="T6">
-        <v>-12.92</v>
+        <v>-14.61</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1458,34 +1442,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>47.26</v>
+        <v>42.21</v>
       </c>
       <c r="Z6">
-        <v>-15.12</v>
+        <v>-14.48</v>
       </c>
       <c r="AA6">
-        <v>-18.94</v>
+        <v>-18.04</v>
       </c>
       <c r="AB6">
-        <v>3.82</v>
+        <v>3.57</v>
       </c>
       <c r="AC6">
-        <v>97.47</v>
+        <v>91.69</v>
       </c>
       <c r="AD6">
-        <v>87.28</v>
+        <v>90.45</v>
       </c>
       <c r="AE6">
-        <v>19.14</v>
+        <v>19.73</v>
       </c>
       <c r="AF6">
-        <v>5.47</v>
+        <v>59.9</v>
       </c>
       <c r="AG6">
-        <v>714.64</v>
+        <v>713.9400000000001</v>
       </c>
       <c r="AH6">
-        <v>678.15</v>
+        <v>677.73</v>
       </c>
       <c r="AI6">
         <v>739.76</v>
@@ -1494,7 +1478,7 @@
         <v>48</v>
       </c>
       <c r="AK6">
-        <v>26.94</v>
+        <v>25.66</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1505,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2632.2</v>
+        <v>2669.5</v>
       </c>
       <c r="D7">
-        <v>-1.35</v>
+        <v>1.42</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1517,46 +1501,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-23.81</v>
+        <v>-22.73</v>
       </c>
       <c r="H7">
-        <v>39.16</v>
+        <v>41.14</v>
       </c>
       <c r="I7">
-        <v>-6.63</v>
+        <v>-1.69</v>
       </c>
       <c r="J7">
-        <v>-16.63</v>
+        <v>-17.87</v>
       </c>
       <c r="K7">
-        <v>6.7</v>
+        <v>7.27</v>
       </c>
       <c r="L7">
-        <v>19.42</v>
+        <v>16.84</v>
       </c>
       <c r="M7">
-        <v>24.97</v>
+        <v>24.55</v>
       </c>
       <c r="N7">
         <v>85</v>
       </c>
       <c r="O7">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P7">
-        <v>2645.74</v>
+        <v>2636.56</v>
       </c>
       <c r="Q7">
-        <v>2897.15</v>
+        <v>2874.19</v>
       </c>
       <c r="R7">
-        <v>3007.82</v>
+        <v>3008.65</v>
       </c>
       <c r="S7">
-        <v>2519.65</v>
+        <v>2521.92</v>
       </c>
       <c r="T7">
-        <v>4.47</v>
+        <v>5.85</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1571,34 +1555,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>29.2</v>
+        <v>33.19</v>
       </c>
       <c r="Z7">
-        <v>-115.27</v>
+        <v>-115.02</v>
       </c>
       <c r="AA7">
-        <v>-78.08</v>
+        <v>-85.47</v>
       </c>
       <c r="AB7">
-        <v>-37.2</v>
+        <v>-29.56</v>
       </c>
       <c r="AC7">
-        <v>31.07</v>
+        <v>39.62</v>
       </c>
       <c r="AD7">
-        <v>19.67</v>
+        <v>30.37</v>
       </c>
       <c r="AE7">
-        <v>119.54</v>
+        <v>118.06</v>
       </c>
       <c r="AF7">
-        <v>18.54</v>
+        <v>-11.53</v>
       </c>
       <c r="AG7">
-        <v>3241.35</v>
+        <v>3214.62</v>
       </c>
       <c r="AH7">
-        <v>2552.95</v>
+        <v>2533.77</v>
       </c>
       <c r="AI7">
         <v>2967.97</v>
@@ -1607,7 +1591,7 @@
         <v>48</v>
       </c>
       <c r="AK7">
-        <v>56.91</v>
+        <v>59.23</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1618,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7791</v>
+        <v>7897</v>
       </c>
       <c r="D8">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1630,46 +1614,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-14.47</v>
+        <v>-13.3</v>
       </c>
       <c r="H8">
-        <v>31.5</v>
+        <v>33.29</v>
       </c>
       <c r="I8">
-        <v>-3.79</v>
+        <v>-1.18</v>
       </c>
       <c r="J8">
-        <v>-10.13</v>
+        <v>-10.39</v>
       </c>
       <c r="K8">
-        <v>-0.45</v>
+        <v>1.52</v>
       </c>
       <c r="L8">
-        <v>-12.22</v>
+        <v>-10.4</v>
       </c>
       <c r="M8">
-        <v>12.22</v>
+        <v>12.92</v>
       </c>
       <c r="N8">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="O8">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="P8">
-        <v>7785.5</v>
+        <v>7766.7</v>
       </c>
       <c r="Q8">
-        <v>8312.83</v>
+        <v>8278.67</v>
       </c>
       <c r="R8">
-        <v>8230.780000000001</v>
+        <v>8224.6</v>
       </c>
       <c r="S8">
-        <v>7433.35</v>
+        <v>7432.87</v>
       </c>
       <c r="T8">
-        <v>4.81</v>
+        <v>6.24</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1684,34 +1668,34 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>37.43</v>
+        <v>41.48</v>
       </c>
       <c r="Z8">
-        <v>-154.81</v>
+        <v>-153.03</v>
       </c>
       <c r="AA8">
-        <v>-60.27</v>
+        <v>-78.81999999999999</v>
       </c>
       <c r="AB8">
-        <v>-94.54000000000001</v>
+        <v>-74.20999999999999</v>
       </c>
       <c r="AC8">
-        <v>7.62</v>
+        <v>17.59</v>
       </c>
       <c r="AD8">
-        <v>3.94</v>
+        <v>9.06</v>
       </c>
       <c r="AE8">
-        <v>283.55</v>
+        <v>274.55</v>
       </c>
       <c r="AF8">
-        <v>-71.43000000000001</v>
+        <v>-54.99</v>
       </c>
       <c r="AG8">
-        <v>9074.209999999999</v>
+        <v>9050.790000000001</v>
       </c>
       <c r="AH8">
-        <v>7551.44</v>
+        <v>7506.56</v>
       </c>
       <c r="AI8">
         <v>8581.85</v>
@@ -1720,7 +1704,7 @@
         <v>48</v>
       </c>
       <c r="AK8">
-        <v>39.06</v>
+        <v>35.3</v>
       </c>
     </row>
   </sheetData>
@@ -1861,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1901,7 +1885,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>55</v>
@@ -1919,1042 +1903,1056 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>69</v>
+      <c r="B7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6">
+        <v>8.67</v>
+      </c>
+      <c r="D7" s="6">
+        <v>8.91</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.24</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-6.62</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-5.06</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-12.82</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-15.33</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-2.51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-12.17</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-9.43</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-3.69</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-4.08</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-16.63</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-17.87</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-10.13</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-10.39</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-6.69</v>
+      </c>
+      <c r="D14" s="6">
+        <v>-6.82</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-6.36</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-3.52</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>0.6</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-0.11</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-3.64</v>
+      </c>
+      <c r="D17" s="6">
+        <v>0.09</v>
+      </c>
+      <c r="E17" s="7">
+        <v>3.73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>1.09</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-1.14</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-6.63</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-1.69</v>
+      </c>
+      <c r="E19" s="7">
+        <v>4.94</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-3.79</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-1.18</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.61</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>29.32</v>
+      </c>
+      <c r="D21" s="6">
+        <v>28.35</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>15.05</v>
+      </c>
+      <c r="D22" s="6">
+        <v>13.63</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-3.53</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-4.44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-22.85</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-21.83</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-33.1</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-33.33</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>19.42</v>
+      </c>
+      <c r="D26" s="6">
+        <v>16.84</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-12.22</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-10.4</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.82</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>11.11</v>
+      </c>
+      <c r="D28" s="6">
+        <v>8.25</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-2.86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-6.55</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-7.12</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-8.51</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-13.35</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-4.84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-16.82</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-15.03</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-9.26</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-11.18</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>6.7</v>
+      </c>
+      <c r="D33" s="6">
+        <v>7.27</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-0.45</v>
+      </c>
+      <c r="D34" s="6">
+        <v>1.52</v>
+      </c>
+      <c r="E34" s="7">
+        <v>1.97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-9.68</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.06</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-12.54</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-11.62</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-16.46</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-19.43</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-2.97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-28.16</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-27.17</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-35.14</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-36.54</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-1.4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-23.81</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-22.73</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-14.47</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-13.3</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1184.7</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1171</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-13.7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>854</v>
+      </c>
+      <c r="D43" s="6">
+        <v>863</v>
+      </c>
+      <c r="E43" s="7">
         <v>9</v>
       </c>
-      <c r="C8" s="7">
-        <v>9.33</v>
-      </c>
-      <c r="D8" s="7">
-        <v>8.67</v>
-      </c>
-      <c r="E8" s="8">
-        <v>-0.66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-6.41</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-6.62</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-13.58</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-12.82</v>
-      </c>
-      <c r="E10" s="9">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>1620.7</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1563</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-57.7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-13.89</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-12.17</v>
-      </c>
-      <c r="E11" s="9">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1723.2</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1747</v>
+      </c>
+      <c r="E45" s="7">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-7.58</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-3.69</v>
-      </c>
-      <c r="E12" s="9">
-        <v>3.89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>706.85</v>
+      </c>
+      <c r="D46" s="6">
+        <v>691.6</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-15.25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-15.84</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-16.63</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>2632.2</v>
+      </c>
+      <c r="D47" s="6">
+        <v>2669.5</v>
+      </c>
+      <c r="E47" s="7">
+        <v>37.3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-6.63</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-10.13</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-3.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-5.63</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-6.69</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-1.68</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-6.36</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-4.68</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>7791</v>
+      </c>
+      <c r="D48" s="6">
+        <v>7897</v>
+      </c>
+      <c r="E48" s="7">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1.54</v>
-      </c>
-      <c r="D17" s="7">
-        <v>0.6</v>
-      </c>
-      <c r="E17" s="9">
-        <v>2.14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="6">
+        <v>57</v>
+      </c>
+      <c r="D49" s="6">
+        <v>43</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-6.18</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-3.64</v>
-      </c>
-      <c r="E18" s="9">
-        <v>2.54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="6">
+        <v>15</v>
+      </c>
+      <c r="D50" s="6">
+        <v>29</v>
+      </c>
+      <c r="E50" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>1.07</v>
-      </c>
-      <c r="D19" s="7">
-        <v>1.09</v>
-      </c>
-      <c r="E19" s="9">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-5.23</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-6.63</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-4.14</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-3.79</v>
-      </c>
-      <c r="E21" s="9">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>30.37</v>
-      </c>
-      <c r="D22" s="7">
-        <v>29.32</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-1.05</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>16.23</v>
-      </c>
-      <c r="D23" s="7">
-        <v>15.05</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-3.05</v>
-      </c>
-      <c r="D24" s="7">
-        <v>0.91</v>
-      </c>
-      <c r="E24" s="9">
-        <v>3.96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-25.86</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-22.85</v>
-      </c>
-      <c r="E25" s="9">
-        <v>3.01</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-33.08</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-33.1</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>22.13</v>
-      </c>
-      <c r="D27" s="7">
-        <v>19.42</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-14.28</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-12.22</v>
-      </c>
-      <c r="E28" s="9">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7">
-        <v>11.48</v>
-      </c>
-      <c r="D29" s="7">
-        <v>11.11</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-4.2</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-6.55</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-2.35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-12.71</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-8.51</v>
-      </c>
-      <c r="E31" s="9">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-17.97</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-16.82</v>
-      </c>
-      <c r="E32" s="9">
-        <v>1.15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-10.88</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-9.26</v>
-      </c>
-      <c r="E33" s="9">
-        <v>1.62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="D34" s="7">
-        <v>6.7</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>-1.72</v>
-      </c>
-      <c r="D35" s="7">
-        <v>-0.45</v>
-      </c>
-      <c r="E35" s="9">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-7.74</v>
-      </c>
-      <c r="D36" s="7">
-        <v>-8.619999999999999</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.88</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-11.16</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-12.54</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-18.52</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-16.46</v>
-      </c>
-      <c r="E38" s="9">
-        <v>2.06</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-29.55</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-28.16</v>
-      </c>
-      <c r="E39" s="9">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-35.83</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-35.14</v>
-      </c>
-      <c r="E40" s="9">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-22.77</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-23.81</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-1.04</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-15.63</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-14.47</v>
-      </c>
-      <c r="E42" s="9">
-        <v>1.16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="7">
-        <v>1196.2</v>
-      </c>
-      <c r="D43" s="7">
-        <v>1184.7</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-11.5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="7">
-        <v>867.5</v>
-      </c>
-      <c r="D44" s="7">
-        <v>854</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-13.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>1580.7</v>
-      </c>
-      <c r="D45" s="7">
-        <v>1620.7</v>
-      </c>
-      <c r="E45" s="9">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>1690</v>
-      </c>
-      <c r="D46" s="7">
-        <v>1723.2</v>
-      </c>
-      <c r="E46" s="9">
-        <v>33.2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>699.35</v>
-      </c>
-      <c r="D47" s="7">
-        <v>706.85</v>
-      </c>
-      <c r="E47" s="9">
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>2668.1</v>
-      </c>
-      <c r="D48" s="7">
-        <v>2632.2</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-35.9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>7685</v>
-      </c>
-      <c r="D49" s="7">
-        <v>7791</v>
-      </c>
-      <c r="E49" s="9">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" s="6" t="s">
+      <c r="B51" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C50" s="7">
-        <v>43</v>
-      </c>
-      <c r="D50" s="7">
-        <v>57</v>
-      </c>
-      <c r="E50" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="7">
-        <v>57</v>
-      </c>
-      <c r="D51" s="7">
-        <v>43</v>
+      <c r="C51" s="6">
+        <v>29</v>
+      </c>
+      <c r="D51" s="6">
+        <v>15</v>
       </c>
       <c r="E51" s="8">
         <v>-14</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="6">
+        <v>43</v>
+      </c>
+      <c r="D52" s="6">
+        <v>57</v>
+      </c>
+      <c r="E52" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B53" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C52" s="7">
-        <v>51.02</v>
-      </c>
-      <c r="D52" s="7">
+      <c r="C53" s="6">
         <v>49.25</v>
       </c>
-      <c r="E52" s="8">
-        <v>-1.77</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
+      <c r="D53" s="6">
+        <v>47.15</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-2.1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C53" s="7">
-        <v>46.42</v>
-      </c>
-      <c r="D53" s="7">
+      <c r="C54" s="6">
         <v>43.36</v>
       </c>
-      <c r="E53" s="8">
-        <v>-3.06</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
+      <c r="D54" s="6">
+        <v>45.92</v>
+      </c>
+      <c r="E54" s="7">
+        <v>2.56</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="7">
-        <v>32.98</v>
-      </c>
-      <c r="D54" s="7">
+      <c r="C55" s="6">
         <v>40.45</v>
       </c>
-      <c r="E54" s="9">
-        <v>7.47</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
+      <c r="D55" s="6">
+        <v>34.48</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-5.97</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B56" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C55" s="7">
-        <v>29.61</v>
-      </c>
-      <c r="D55" s="7">
+      <c r="C56" s="6">
         <v>35.04</v>
       </c>
-      <c r="E55" s="9">
-        <v>5.43</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
+      <c r="D56" s="6">
+        <v>38.69</v>
+      </c>
+      <c r="E56" s="7">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B57" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="7">
-        <v>44.22</v>
-      </c>
-      <c r="D56" s="7">
+      <c r="C57" s="6">
         <v>47.26</v>
       </c>
-      <c r="E56" s="9">
-        <v>3.04</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
+      <c r="D57" s="6">
+        <v>42.21</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-5.05</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B58" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C57" s="7">
-        <v>30.85</v>
-      </c>
-      <c r="D57" s="7">
+      <c r="C58" s="6">
         <v>29.2</v>
       </c>
-      <c r="E57" s="8">
-        <v>-1.65</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
+      <c r="D58" s="6">
+        <v>33.19</v>
+      </c>
+      <c r="E58" s="7">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B59" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C58" s="7">
-        <v>33.14</v>
-      </c>
-      <c r="D58" s="7">
+      <c r="C59" s="6">
         <v>37.43</v>
       </c>
-      <c r="E58" s="9">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
+      <c r="D59" s="6">
+        <v>41.48</v>
+      </c>
+      <c r="E59" s="7">
+        <v>4.05</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="7">
-        <v>-86.62</v>
-      </c>
-      <c r="D59" s="7">
+      <c r="C60" s="6">
         <v>-72.62</v>
       </c>
-      <c r="E59" s="9">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
+      <c r="D60" s="6">
+        <v>-82.78</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-10.16</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="7">
-        <v>-34.03</v>
-      </c>
-      <c r="D60" s="7">
+      <c r="C61" s="6">
         <v>13.38</v>
       </c>
-      <c r="E60" s="9">
-        <v>47.41</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
+      <c r="D61" s="6">
+        <v>-22.27</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-35.65</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="7">
-        <v>-30.81</v>
-      </c>
-      <c r="D61" s="7">
+      <c r="C62" s="6">
         <v>4.54</v>
       </c>
-      <c r="E61" s="9">
-        <v>35.35</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
+      <c r="D62" s="6">
+        <v>58.8</v>
+      </c>
+      <c r="E62" s="7">
+        <v>54.26</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B63" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="7">
-        <v>-56.63</v>
-      </c>
-      <c r="D62" s="7">
+      <c r="C63" s="6">
         <v>-60.94</v>
       </c>
-      <c r="E62" s="8">
-        <v>-4.31</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
+      <c r="D63" s="6">
+        <v>123.24</v>
+      </c>
+      <c r="E63" s="7">
+        <v>184.18</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="7">
-        <v>-33.59</v>
-      </c>
-      <c r="D63" s="7">
+      <c r="C64" s="6">
         <v>5.47</v>
       </c>
-      <c r="E63" s="9">
-        <v>39.06</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
+      <c r="D64" s="6">
+        <v>59.9</v>
+      </c>
+      <c r="E64" s="7">
+        <v>54.43</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B65" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C64" s="7">
-        <v>-52.61</v>
-      </c>
-      <c r="D64" s="7">
+      <c r="C65" s="6">
         <v>18.54</v>
       </c>
-      <c r="E64" s="9">
-        <v>71.15000000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="6" t="s">
+      <c r="D65" s="6">
+        <v>-11.53</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-30.07</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B66" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C65" s="7">
-        <v>-20.03</v>
-      </c>
-      <c r="D65" s="7">
+      <c r="C66" s="6">
         <v>-71.43000000000001</v>
       </c>
-      <c r="E65" s="8">
-        <v>-51.4</v>
+      <c r="D66" s="6">
+        <v>-54.99</v>
+      </c>
+      <c r="E66" s="7">
+        <v>16.44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2974,60 +2972,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>77</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>56.8</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>40.3</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>40.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="11">
         <v>-7.6</v>
       </c>
-      <c r="G2" s="12">
-        <v>-3.4</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="G2" s="11">
+        <v>-4.2</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>30</v>
       </c>
     </row>
@@ -3129,49 +3127,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.4964</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.2497</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2243</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1561</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1222</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.09</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.0596</v>
+      <c r="A2" s="14">
+        <v>0.4919</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2455</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2157</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.161</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.1292</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0843</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.06150000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -163,43 +163,13 @@
     <t>No</t>
   </si>
   <si>
-    <t>UP</t>
-  </si>
-  <si>
     <t>DOWN</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.2 → 33.2</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.2</t>
-  </si>
-  <si>
-    <t>33.2</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +255,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +295,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,15 +371,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -924,10 +893,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1171</v>
+        <v>1104.4</v>
       </c>
       <c r="D2">
-        <v>-1.16</v>
+        <v>-5.69</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -936,46 +905,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-9.68</v>
+        <v>-14.82</v>
       </c>
       <c r="H2">
-        <v>56.48</v>
+        <v>47.58</v>
       </c>
       <c r="I2">
-        <v>-6.82</v>
+        <v>-8.68</v>
       </c>
       <c r="J2">
-        <v>8.91</v>
+        <v>7.04</v>
       </c>
       <c r="K2">
-        <v>8.25</v>
+        <v>1.76</v>
       </c>
       <c r="L2">
-        <v>28.35</v>
+        <v>18.02</v>
       </c>
       <c r="M2">
-        <v>6.15</v>
+        <v>4.54</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="P2">
-        <v>1192.78</v>
+        <v>1171.78</v>
       </c>
       <c r="Q2">
-        <v>1209.38</v>
+        <v>1212.02</v>
       </c>
       <c r="R2">
-        <v>1149.51</v>
+        <v>1150.03</v>
       </c>
       <c r="S2">
-        <v>990.8099999999999</v>
+        <v>992.1</v>
       </c>
       <c r="T2">
-        <v>18.19</v>
+        <v>11.32</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,16 +959,16 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>47.15</v>
+        <v>38.55</v>
       </c>
       <c r="Z2">
-        <v>17.87</v>
+        <v>8.34</v>
       </c>
       <c r="AA2">
-        <v>28.76</v>
+        <v>24.68</v>
       </c>
       <c r="AB2">
-        <v>-10.89</v>
+        <v>-16.34</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -1008,25 +977,25 @@
         <v>0</v>
       </c>
       <c r="AE2">
-        <v>48.91</v>
+        <v>50.93</v>
       </c>
       <c r="AF2">
-        <v>-82.78</v>
+        <v>-69.92</v>
       </c>
       <c r="AG2">
-        <v>1339.29</v>
+        <v>1330.03</v>
       </c>
       <c r="AH2">
-        <v>1079.47</v>
+        <v>1094.01</v>
       </c>
       <c r="AI2">
-        <v>1148.32</v>
+        <v>1282.33</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>28.19</v>
+        <v>30.86</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1006,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>863</v>
+        <v>818</v>
       </c>
       <c r="D3">
-        <v>1.05</v>
+        <v>-5.21</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1049,46 +1018,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-11.62</v>
+        <v>-16.23</v>
       </c>
       <c r="H3">
-        <v>62.99</v>
+        <v>54.49</v>
       </c>
       <c r="I3">
-        <v>-3.52</v>
+        <v>-5.11</v>
       </c>
       <c r="J3">
-        <v>-5.06</v>
+        <v>-4.66</v>
       </c>
       <c r="K3">
-        <v>-7.12</v>
+        <v>-11.28</v>
       </c>
       <c r="L3">
-        <v>13.63</v>
+        <v>8.81</v>
       </c>
       <c r="M3">
-        <v>49.19</v>
+        <v>46.26</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="P3">
-        <v>860.42</v>
+        <v>851.61</v>
       </c>
       <c r="Q3">
-        <v>877.22</v>
+        <v>875.55</v>
       </c>
       <c r="R3">
-        <v>883.61</v>
+        <v>882.37</v>
       </c>
       <c r="S3">
-        <v>803.08</v>
+        <v>803.89</v>
       </c>
       <c r="T3">
-        <v>7.46</v>
+        <v>1.75</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1103,43 +1072,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>45.92</v>
+        <v>36.94</v>
       </c>
       <c r="Z3">
-        <v>-6.51</v>
+        <v>-10.28</v>
       </c>
       <c r="AA3">
-        <v>-4.17</v>
+        <v>-5.39</v>
       </c>
       <c r="AB3">
-        <v>-2.35</v>
+        <v>-4.89</v>
       </c>
       <c r="AC3">
-        <v>25.73</v>
+        <v>14.71</v>
       </c>
       <c r="AD3">
-        <v>22.68</v>
+        <v>20.14</v>
       </c>
       <c r="AE3">
-        <v>25.14</v>
+        <v>26.74</v>
       </c>
       <c r="AF3">
-        <v>-22.27</v>
+        <v>125.13</v>
       </c>
       <c r="AG3">
-        <v>915.39</v>
+        <v>920.76</v>
       </c>
       <c r="AH3">
-        <v>839.0599999999999</v>
+        <v>830.33</v>
       </c>
       <c r="AI3">
-        <v>921.33</v>
+        <v>910.9299999999999</v>
       </c>
       <c r="AJ3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK3">
-        <v>21.46</v>
+        <v>23.87</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1119,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1563</v>
+        <v>1586</v>
       </c>
       <c r="D4">
-        <v>-3.56</v>
+        <v>1.47</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1162,46 +1131,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-19.43</v>
+        <v>-18.25</v>
       </c>
       <c r="H4">
-        <v>15.38</v>
+        <v>17.07</v>
       </c>
       <c r="I4">
-        <v>-0.11</v>
+        <v>2.72</v>
       </c>
       <c r="J4">
-        <v>-15.33</v>
+        <v>-11.48</v>
       </c>
       <c r="K4">
-        <v>-13.35</v>
+        <v>-11.35</v>
       </c>
       <c r="L4">
-        <v>-3.53</v>
+        <v>-1.67</v>
       </c>
       <c r="M4">
-        <v>21.57</v>
+        <v>21.77</v>
       </c>
       <c r="N4">
         <v>43</v>
       </c>
       <c r="O4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P4">
-        <v>1579.2</v>
+        <v>1587.6</v>
       </c>
       <c r="Q4">
-        <v>1655.51</v>
+        <v>1646.53</v>
       </c>
       <c r="R4">
-        <v>1782.86</v>
+        <v>1777.08</v>
       </c>
       <c r="S4">
-        <v>1677.42</v>
+        <v>1676.86</v>
       </c>
       <c r="T4">
-        <v>-6.82</v>
+        <v>-5.42</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1216,43 +1185,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>34.48</v>
+        <v>38.38</v>
       </c>
       <c r="Z4">
-        <v>-61.38</v>
+        <v>-58.82</v>
       </c>
       <c r="AA4">
-        <v>-59.93</v>
+        <v>-59.71</v>
       </c>
       <c r="AB4">
-        <v>-1.45</v>
+        <v>0.89</v>
       </c>
       <c r="AC4">
-        <v>69.14</v>
+        <v>81.36</v>
       </c>
       <c r="AD4">
-        <v>57.43</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="AE4">
-        <v>46.73</v>
+        <v>47.22</v>
       </c>
       <c r="AF4">
-        <v>58.8</v>
+        <v>1.99</v>
       </c>
       <c r="AG4">
-        <v>1824.42</v>
+        <v>1809.8</v>
       </c>
       <c r="AH4">
-        <v>1486.6</v>
+        <v>1483.26</v>
       </c>
       <c r="AI4">
         <v>1692.02</v>
       </c>
       <c r="AJ4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK4">
-        <v>53.47</v>
+        <v>51.77</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1232,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1747</v>
+        <v>1765.3</v>
       </c>
       <c r="D5">
-        <v>1.38</v>
+        <v>1.05</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1275,46 +1244,46 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-27.17</v>
+        <v>-26.41</v>
       </c>
       <c r="H5">
-        <v>4.38</v>
+        <v>5.47</v>
       </c>
       <c r="I5">
-        <v>0.09</v>
+        <v>5.47</v>
       </c>
       <c r="J5">
-        <v>-9.43</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="K5">
-        <v>-15.03</v>
+        <v>-12.7</v>
       </c>
       <c r="L5">
-        <v>-21.83</v>
+        <v>-20.19</v>
       </c>
       <c r="M5">
-        <v>16.1</v>
+        <v>16.53</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="P5">
-        <v>1707.46</v>
+        <v>1725.78</v>
       </c>
       <c r="Q5">
-        <v>1835.08</v>
+        <v>1826.45</v>
       </c>
       <c r="R5">
-        <v>1933.15</v>
+        <v>1926.15</v>
       </c>
       <c r="S5">
-        <v>2033.72</v>
+        <v>2030.82</v>
       </c>
       <c r="T5">
-        <v>-14.1</v>
+        <v>-13.07</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,43 +1298,43 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>38.69</v>
+        <v>41.41</v>
       </c>
       <c r="Z5">
-        <v>-66.16</v>
+        <v>-61.35</v>
       </c>
       <c r="AA5">
-        <v>-57.73</v>
+        <v>-58.45</v>
       </c>
       <c r="AB5">
-        <v>-8.43</v>
+        <v>-2.89</v>
       </c>
       <c r="AC5">
-        <v>36.08</v>
+        <v>52.16</v>
       </c>
       <c r="AD5">
-        <v>24.42</v>
+        <v>37.75</v>
       </c>
       <c r="AE5">
-        <v>57.7</v>
+        <v>56.28</v>
       </c>
       <c r="AF5">
-        <v>123.24</v>
+        <v>-21.67</v>
       </c>
       <c r="AG5">
-        <v>2052.96</v>
+        <v>2040.84</v>
       </c>
       <c r="AH5">
-        <v>1617.19</v>
+        <v>1612.06</v>
       </c>
       <c r="AI5">
         <v>1853.75</v>
       </c>
       <c r="AJ5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK5">
-        <v>41.85</v>
+        <v>38.59</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,10 +1345,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>691.6</v>
+        <v>701.95</v>
       </c>
       <c r="D6">
-        <v>-2.16</v>
+        <v>1.5</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1388,46 +1357,46 @@
         <v>674.55</v>
       </c>
       <c r="G6">
-        <v>-36.54</v>
+        <v>-35.59</v>
       </c>
       <c r="H6">
-        <v>2.53</v>
+        <v>4.06</v>
       </c>
       <c r="I6">
-        <v>-1.14</v>
+        <v>3.66</v>
       </c>
       <c r="J6">
-        <v>-4.08</v>
+        <v>-0.11</v>
       </c>
       <c r="K6">
-        <v>-11.18</v>
+        <v>-8.9</v>
       </c>
       <c r="L6">
-        <v>-33.33</v>
+        <v>-31.62</v>
       </c>
       <c r="M6">
-        <v>8.43</v>
+        <v>8.33</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="P6">
-        <v>692.77</v>
+        <v>697.73</v>
       </c>
       <c r="Q6">
-        <v>695.84</v>
+        <v>695.78</v>
       </c>
       <c r="R6">
-        <v>749.51</v>
+        <v>747.48</v>
       </c>
       <c r="S6">
-        <v>809.89</v>
+        <v>808.05</v>
       </c>
       <c r="T6">
-        <v>-14.61</v>
+        <v>-13.13</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1442,43 +1411,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>42.21</v>
+        <v>46.4</v>
       </c>
       <c r="Z6">
-        <v>-14.48</v>
+        <v>-12.99</v>
       </c>
       <c r="AA6">
-        <v>-18.04</v>
+        <v>-17.03</v>
       </c>
       <c r="AB6">
-        <v>3.57</v>
+        <v>4.04</v>
       </c>
       <c r="AC6">
-        <v>91.69</v>
+        <v>90.19</v>
       </c>
       <c r="AD6">
-        <v>90.45</v>
+        <v>93.12</v>
       </c>
       <c r="AE6">
-        <v>19.73</v>
+        <v>19.6</v>
       </c>
       <c r="AF6">
-        <v>59.9</v>
+        <v>20.84</v>
       </c>
       <c r="AG6">
-        <v>713.9400000000001</v>
+        <v>713.8</v>
       </c>
       <c r="AH6">
-        <v>677.73</v>
+        <v>677.76</v>
       </c>
       <c r="AI6">
         <v>739.76</v>
       </c>
       <c r="AJ6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK6">
-        <v>25.66</v>
+        <v>24.17</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1458,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2669.5</v>
+        <v>2585.3</v>
       </c>
       <c r="D7">
-        <v>1.42</v>
+        <v>-3.15</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1501,46 +1470,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-22.73</v>
+        <v>-25.17</v>
       </c>
       <c r="H7">
-        <v>41.14</v>
+        <v>36.68</v>
       </c>
       <c r="I7">
-        <v>-1.69</v>
+        <v>0.13</v>
       </c>
       <c r="J7">
-        <v>-17.87</v>
+        <v>-17.37</v>
       </c>
       <c r="K7">
-        <v>7.27</v>
+        <v>5.35</v>
       </c>
       <c r="L7">
-        <v>16.84</v>
+        <v>9.07</v>
       </c>
       <c r="M7">
-        <v>24.55</v>
+        <v>23.66</v>
       </c>
       <c r="N7">
         <v>85</v>
       </c>
       <c r="O7">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="P7">
-        <v>2636.56</v>
+        <v>2637.24</v>
       </c>
       <c r="Q7">
-        <v>2874.19</v>
+        <v>2847.75</v>
       </c>
       <c r="R7">
-        <v>3008.65</v>
+        <v>3007.58</v>
       </c>
       <c r="S7">
-        <v>2521.92</v>
+        <v>2523.79</v>
       </c>
       <c r="T7">
-        <v>5.85</v>
+        <v>2.44</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1555,43 +1524,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>33.19</v>
+        <v>29.19</v>
       </c>
       <c r="Z7">
-        <v>-115.02</v>
+        <v>-120.24</v>
       </c>
       <c r="AA7">
-        <v>-85.47</v>
+        <v>-92.42</v>
       </c>
       <c r="AB7">
-        <v>-29.56</v>
+        <v>-27.81</v>
       </c>
       <c r="AC7">
-        <v>39.62</v>
+        <v>38.44</v>
       </c>
       <c r="AD7">
-        <v>30.37</v>
+        <v>36.38</v>
       </c>
       <c r="AE7">
-        <v>118.06</v>
+        <v>119.87</v>
       </c>
       <c r="AF7">
-        <v>-11.53</v>
+        <v>38.48</v>
       </c>
       <c r="AG7">
-        <v>3214.62</v>
+        <v>3191.83</v>
       </c>
       <c r="AH7">
-        <v>2533.77</v>
+        <v>2503.67</v>
       </c>
       <c r="AI7">
         <v>2967.97</v>
       </c>
       <c r="AJ7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK7">
-        <v>59.23</v>
+        <v>61.74</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1571,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7897</v>
+        <v>7728.5</v>
       </c>
       <c r="D8">
-        <v>1.36</v>
+        <v>-2.13</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1614,46 +1583,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-13.3</v>
+        <v>-15.15</v>
       </c>
       <c r="H8">
-        <v>33.29</v>
+        <v>30.45</v>
       </c>
       <c r="I8">
-        <v>-1.18</v>
+        <v>0.21</v>
       </c>
       <c r="J8">
-        <v>-10.39</v>
+        <v>-9.92</v>
       </c>
       <c r="K8">
-        <v>1.52</v>
+        <v>-0.68</v>
       </c>
       <c r="L8">
-        <v>-10.4</v>
+        <v>-13.01</v>
       </c>
       <c r="M8">
-        <v>12.92</v>
+        <v>12.46</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="P8">
-        <v>7766.7</v>
+        <v>7770</v>
       </c>
       <c r="Q8">
-        <v>8278.67</v>
+        <v>8231.92</v>
       </c>
       <c r="R8">
-        <v>8224.6</v>
+        <v>8217.129999999999</v>
       </c>
       <c r="S8">
-        <v>7432.87</v>
+        <v>7431.83</v>
       </c>
       <c r="T8">
-        <v>6.24</v>
+        <v>3.99</v>
       </c>
       <c r="U8" t="s">
         <v>45</v>
@@ -1668,43 +1637,43 @@
         <v>3</v>
       </c>
       <c r="Y8">
-        <v>41.48</v>
+        <v>37.34</v>
       </c>
       <c r="Z8">
-        <v>-153.03</v>
+        <v>-163.34</v>
       </c>
       <c r="AA8">
-        <v>-78.81999999999999</v>
+        <v>-95.72</v>
       </c>
       <c r="AB8">
-        <v>-74.20999999999999</v>
+        <v>-67.62</v>
       </c>
       <c r="AC8">
-        <v>17.59</v>
+        <v>23.48</v>
       </c>
       <c r="AD8">
-        <v>9.06</v>
+        <v>16.23</v>
       </c>
       <c r="AE8">
-        <v>274.55</v>
+        <v>268.97</v>
       </c>
       <c r="AF8">
-        <v>-54.99</v>
+        <v>-73.44</v>
       </c>
       <c r="AG8">
-        <v>9050.790000000001</v>
+        <v>9019.02</v>
       </c>
       <c r="AH8">
-        <v>7506.56</v>
+        <v>7444.83</v>
       </c>
       <c r="AI8">
         <v>8581.85</v>
       </c>
       <c r="AJ8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AK8">
-        <v>35.3</v>
+        <v>33.4</v>
       </c>
     </row>
   </sheetData>
@@ -1845,7 +1814,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1855,7 +1824,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1865,47 +1834,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1913,1040 +1847,972 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>64</v>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>8.67</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>8.91</v>
       </c>
-      <c r="E7" s="7">
-        <v>0.24</v>
+      <c r="D7" s="5">
+        <v>7.04</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.87</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-6.62</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-5.06</v>
       </c>
+      <c r="D8" s="5">
+        <v>-4.66</v>
+      </c>
       <c r="E8" s="7">
-        <v>1.56</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-12.82</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-15.33</v>
       </c>
-      <c r="E9" s="8">
-        <v>-2.51</v>
+      <c r="D9" s="5">
+        <v>-11.48</v>
+      </c>
+      <c r="E9" s="7">
+        <v>3.85</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-12.17</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-9.43</v>
       </c>
+      <c r="D10" s="5">
+        <v>-8.960000000000001</v>
+      </c>
       <c r="E10" s="7">
-        <v>2.74</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-3.69</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-4.08</v>
       </c>
-      <c r="E11" s="8">
-        <v>-0.39</v>
+      <c r="D11" s="5">
+        <v>-0.11</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3.97</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-16.63</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-17.87</v>
       </c>
-      <c r="E12" s="8">
-        <v>-1.24</v>
+      <c r="D12" s="5">
+        <v>-17.37</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.5</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-10.13</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-10.39</v>
       </c>
-      <c r="E13" s="8">
-        <v>-0.26</v>
+      <c r="D13" s="5">
+        <v>-9.92</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.47</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>-6.69</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>-6.82</v>
       </c>
-      <c r="E14" s="8">
-        <v>-0.13</v>
+      <c r="D14" s="5">
+        <v>-8.68</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-6.36</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-3.52</v>
       </c>
-      <c r="E15" s="7">
-        <v>2.84</v>
+      <c r="D15" s="5">
+        <v>-5.11</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>0.6</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-0.11</v>
       </c>
-      <c r="E16" s="8">
-        <v>-0.71</v>
+      <c r="D16" s="5">
+        <v>2.72</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.83</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>-3.64</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>0.09</v>
       </c>
+      <c r="D17" s="5">
+        <v>5.47</v>
+      </c>
       <c r="E17" s="7">
-        <v>3.73</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>1.09</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-1.14</v>
       </c>
-      <c r="E18" s="8">
-        <v>-2.23</v>
+      <c r="D18" s="5">
+        <v>3.66</v>
+      </c>
+      <c r="E18" s="7">
+        <v>4.8</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="6">
-        <v>-6.63</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>-1.69</v>
       </c>
+      <c r="D19" s="5">
+        <v>0.13</v>
+      </c>
       <c r="E19" s="7">
-        <v>4.94</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="6">
-        <v>-3.79</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-1.18</v>
       </c>
+      <c r="D20" s="5">
+        <v>0.21</v>
+      </c>
       <c r="E20" s="7">
-        <v>2.61</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="6">
-        <v>29.32</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>28.35</v>
       </c>
-      <c r="E21" s="8">
-        <v>-0.97</v>
+      <c r="D21" s="5">
+        <v>18.02</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-10.33</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="6">
-        <v>15.05</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>13.63</v>
       </c>
-      <c r="E22" s="8">
-        <v>-1.42</v>
+      <c r="D22" s="5">
+        <v>8.81</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-4.82</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>-3.53</v>
       </c>
-      <c r="E23" s="8">
-        <v>-4.44</v>
+      <c r="D23" s="5">
+        <v>-1.67</v>
+      </c>
+      <c r="E23" s="7">
+        <v>1.86</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="6">
-        <v>-22.85</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>-21.83</v>
       </c>
+      <c r="D24" s="5">
+        <v>-20.19</v>
+      </c>
       <c r="E24" s="7">
-        <v>1.02</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="6">
-        <v>-33.1</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>-33.33</v>
       </c>
-      <c r="E25" s="8">
-        <v>-0.23</v>
+      <c r="D25" s="5">
+        <v>-31.62</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.71</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="6">
-        <v>19.42</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>16.84</v>
       </c>
-      <c r="E26" s="8">
-        <v>-2.58</v>
+      <c r="D26" s="5">
+        <v>9.07</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-7.77</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
-        <v>-12.22</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>-10.4</v>
       </c>
-      <c r="E27" s="7">
-        <v>1.82</v>
+      <c r="D27" s="5">
+        <v>-13.01</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-2.61</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="6">
-        <v>11.11</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>8.25</v>
       </c>
-      <c r="E28" s="8">
-        <v>-2.86</v>
+      <c r="D28" s="5">
+        <v>1.76</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-6.49</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="6">
-        <v>-6.55</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>-7.12</v>
       </c>
-      <c r="E29" s="8">
-        <v>-0.57</v>
+      <c r="D29" s="5">
+        <v>-11.28</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-4.16</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="6">
-        <v>-8.51</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-13.35</v>
       </c>
-      <c r="E30" s="8">
-        <v>-4.84</v>
+      <c r="D30" s="5">
+        <v>-11.35</v>
+      </c>
+      <c r="E30" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="6">
-        <v>-16.82</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C31" s="5">
         <v>-15.03</v>
       </c>
+      <c r="D31" s="5">
+        <v>-12.7</v>
+      </c>
       <c r="E31" s="7">
-        <v>1.79</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="6">
-        <v>-9.26</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C32" s="5">
         <v>-11.18</v>
       </c>
-      <c r="E32" s="8">
+      <c r="D32" s="5">
+        <v>-8.9</v>
+      </c>
+      <c r="E32" s="7">
+        <v>2.28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>7.27</v>
+      </c>
+      <c r="D33" s="5">
+        <v>5.35</v>
+      </c>
+      <c r="E33" s="6">
         <v>-1.92</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>1.52</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-0.68</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-2.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-9.68</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-14.82</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-5.14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-11.62</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-16.23</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-4.61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-19.43</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-18.25</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-27.17</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-26.41</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.76</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-36.54</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-35.59</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>6.7</v>
-      </c>
-      <c r="D33" s="6">
-        <v>7.27</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.57</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-22.73</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-25.17</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-2.44</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-0.45</v>
-      </c>
-      <c r="D34" s="6">
-        <v>1.52</v>
-      </c>
-      <c r="E34" s="7">
-        <v>1.97</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-13.3</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-15.15</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-8.619999999999999</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-9.68</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1171</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1104.4</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-66.59999999999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-12.54</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-11.62</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>863</v>
+      </c>
+      <c r="D43" s="5">
+        <v>818</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-16.46</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-19.43</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-2.97</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1563</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1586</v>
+      </c>
+      <c r="E44" s="7">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-28.16</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-27.17</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1747</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1765.3</v>
+      </c>
+      <c r="E45" s="7">
+        <v>18.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-35.14</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-36.54</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-1.4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>691.6</v>
+      </c>
+      <c r="D46" s="5">
+        <v>701.95</v>
+      </c>
+      <c r="E46" s="7">
+        <v>10.35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-23.81</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-22.73</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>2669.5</v>
+      </c>
+      <c r="D47" s="5">
+        <v>2585.3</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-84.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-14.47</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-13.3</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>7897</v>
+      </c>
+      <c r="D48" s="5">
+        <v>7728.5</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-168.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1184.7</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1171</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-13.7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>47.15</v>
+      </c>
+      <c r="D49" s="5">
+        <v>38.55</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-8.6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>854</v>
-      </c>
-      <c r="D43" s="6">
-        <v>863</v>
-      </c>
-      <c r="E43" s="7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>45.92</v>
+      </c>
+      <c r="D50" s="5">
+        <v>36.94</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-8.98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1620.7</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1563</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-57.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>34.48</v>
+      </c>
+      <c r="D51" s="5">
+        <v>38.38</v>
+      </c>
+      <c r="E51" s="7">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1723.2</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1747</v>
-      </c>
-      <c r="E45" s="7">
-        <v>23.8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>38.69</v>
+      </c>
+      <c r="D52" s="5">
+        <v>41.41</v>
+      </c>
+      <c r="E52" s="7">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>706.85</v>
-      </c>
-      <c r="D46" s="6">
-        <v>691.6</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-15.25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>42.21</v>
+      </c>
+      <c r="D53" s="5">
+        <v>46.4</v>
+      </c>
+      <c r="E53" s="7">
+        <v>4.19</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>2632.2</v>
-      </c>
-      <c r="D47" s="6">
-        <v>2669.5</v>
-      </c>
-      <c r="E47" s="7">
-        <v>37.3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>33.19</v>
+      </c>
+      <c r="D54" s="5">
+        <v>29.19</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>7791</v>
-      </c>
-      <c r="D48" s="6">
-        <v>7897</v>
-      </c>
-      <c r="E48" s="7">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>41.48</v>
+      </c>
+      <c r="D55" s="5">
+        <v>37.34</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-4.14</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
+        <v>-82.78</v>
+      </c>
+      <c r="D56" s="5">
+        <v>-69.92</v>
+      </c>
+      <c r="E56" s="7">
+        <v>12.86</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5">
+        <v>-22.27</v>
+      </c>
+      <c r="D57" s="5">
+        <v>125.13</v>
+      </c>
+      <c r="E57" s="7">
+        <v>147.4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="6">
-        <v>57</v>
-      </c>
-      <c r="D49" s="6">
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>58.8</v>
+      </c>
+      <c r="D58" s="5">
+        <v>1.99</v>
+      </c>
+      <c r="E58" s="6">
+        <v>-56.81</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>123.24</v>
+      </c>
+      <c r="D59" s="5">
+        <v>-21.67</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-144.91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>59.9</v>
+      </c>
+      <c r="D60" s="5">
+        <v>20.84</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-39.06</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>-11.53</v>
+      </c>
+      <c r="D61" s="5">
+        <v>38.48</v>
+      </c>
+      <c r="E61" s="7">
+        <v>50.01</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E49" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="6">
-        <v>15</v>
-      </c>
-      <c r="D50" s="6">
-        <v>29</v>
-      </c>
-      <c r="E50" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="6">
-        <v>29</v>
-      </c>
-      <c r="D51" s="6">
-        <v>15</v>
-      </c>
-      <c r="E51" s="8">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="6">
-        <v>43</v>
-      </c>
-      <c r="D52" s="6">
-        <v>57</v>
-      </c>
-      <c r="E52" s="7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>49.25</v>
-      </c>
-      <c r="D53" s="6">
-        <v>47.15</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-2.1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>43.36</v>
-      </c>
-      <c r="D54" s="6">
-        <v>45.92</v>
-      </c>
-      <c r="E54" s="7">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>40.45</v>
-      </c>
-      <c r="D55" s="6">
-        <v>34.48</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-5.97</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>35.04</v>
-      </c>
-      <c r="D56" s="6">
-        <v>38.69</v>
-      </c>
-      <c r="E56" s="7">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>47.26</v>
-      </c>
-      <c r="D57" s="6">
-        <v>42.21</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-5.05</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>29.2</v>
-      </c>
-      <c r="D58" s="6">
-        <v>33.19</v>
-      </c>
-      <c r="E58" s="7">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>37.43</v>
-      </c>
-      <c r="D59" s="6">
-        <v>41.48</v>
-      </c>
-      <c r="E59" s="7">
-        <v>4.05</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="5" t="s">
+      <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="6">
-        <v>-72.62</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-82.78</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-10.16</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>13.38</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-22.27</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-35.65</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>4.54</v>
-      </c>
-      <c r="D62" s="6">
-        <v>58.8</v>
-      </c>
-      <c r="E62" s="7">
-        <v>54.26</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-60.94</v>
-      </c>
-      <c r="D63" s="6">
-        <v>123.24</v>
-      </c>
-      <c r="E63" s="7">
-        <v>184.18</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>5.47</v>
-      </c>
-      <c r="D64" s="6">
-        <v>59.9</v>
-      </c>
-      <c r="E64" s="7">
-        <v>54.43</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>18.54</v>
-      </c>
-      <c r="D65" s="6">
-        <v>-11.53</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-30.07</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>-71.43000000000001</v>
-      </c>
-      <c r="D66" s="6">
+      <c r="C62" s="5">
         <v>-54.99</v>
       </c>
-      <c r="E66" s="7">
-        <v>16.44</v>
+      <c r="D62" s="5">
+        <v>-73.44</v>
+      </c>
+      <c r="E62" s="6">
+        <v>-18.45</v>
       </c>
     </row>
   </sheetData>
@@ -2972,60 +2838,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>56.8</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>40.4</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>38.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-7.6</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-4.2</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-6.5</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-5.4</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>30</v>
       </c>
     </row>
@@ -3127,49 +2993,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.4919</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2455</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.2157</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.161</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1292</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0843</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.06150000000000001</v>
+      <c r="A2" s="13">
+        <v>0.4626</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2366</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.2177</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1653</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1246</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0833</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.0454</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="75">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,43 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.2 → 33.8</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.2</t>
+  </si>
+  <si>
+    <t>33.8</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -255,14 +291,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,13 +331,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,17 +407,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -893,10 +931,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1104.4</v>
+        <v>1110.1</v>
       </c>
       <c r="D2">
-        <v>-5.69</v>
+        <v>0.52</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -905,46 +943,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-14.82</v>
+        <v>-14.38</v>
       </c>
       <c r="H2">
-        <v>47.58</v>
+        <v>48.34</v>
       </c>
       <c r="I2">
-        <v>-8.68</v>
+        <v>-7.69</v>
       </c>
       <c r="J2">
-        <v>7.04</v>
+        <v>5.56</v>
       </c>
       <c r="K2">
-        <v>1.76</v>
+        <v>4.75</v>
       </c>
       <c r="L2">
-        <v>18.02</v>
+        <v>19.82</v>
       </c>
       <c r="M2">
-        <v>4.54</v>
+        <v>4.65</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P2">
-        <v>1171.78</v>
+        <v>1153.28</v>
       </c>
       <c r="Q2">
-        <v>1212.02</v>
+        <v>1213.34</v>
       </c>
       <c r="R2">
-        <v>1150.03</v>
+        <v>1150.59</v>
       </c>
       <c r="S2">
-        <v>992.1</v>
+        <v>993.47</v>
       </c>
       <c r="T2">
-        <v>11.32</v>
+        <v>11.74</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -959,43 +997,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>38.55</v>
+        <v>39.56</v>
       </c>
       <c r="Z2">
-        <v>8.34</v>
+        <v>1.23</v>
       </c>
       <c r="AA2">
-        <v>24.68</v>
+        <v>19.99</v>
       </c>
       <c r="AB2">
-        <v>-16.34</v>
+        <v>-18.76</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AE2">
-        <v>50.93</v>
+        <v>49.43</v>
       </c>
       <c r="AF2">
-        <v>-69.92</v>
+        <v>-73.7</v>
       </c>
       <c r="AG2">
-        <v>1330.03</v>
+        <v>1325.75</v>
       </c>
       <c r="AH2">
-        <v>1094.01</v>
+        <v>1100.94</v>
       </c>
       <c r="AI2">
-        <v>1282.33</v>
+        <v>1253.3</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>30.86</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,10 +1044,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>818</v>
+        <v>846</v>
       </c>
       <c r="D3">
-        <v>-5.21</v>
+        <v>3.42</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1018,46 +1056,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-16.23</v>
+        <v>-13.36</v>
       </c>
       <c r="H3">
-        <v>54.49</v>
+        <v>59.78</v>
       </c>
       <c r="I3">
-        <v>-5.11</v>
+        <v>-1.12</v>
       </c>
       <c r="J3">
-        <v>-4.66</v>
+        <v>-0.65</v>
       </c>
       <c r="K3">
-        <v>-11.28</v>
+        <v>-6.52</v>
       </c>
       <c r="L3">
-        <v>8.81</v>
+        <v>13.5</v>
       </c>
       <c r="M3">
-        <v>46.26</v>
+        <v>47.22</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="P3">
-        <v>851.61</v>
+        <v>849.7</v>
       </c>
       <c r="Q3">
-        <v>875.55</v>
+        <v>873.85</v>
       </c>
       <c r="R3">
-        <v>882.37</v>
+        <v>881.5</v>
       </c>
       <c r="S3">
-        <v>803.89</v>
+        <v>804.89</v>
       </c>
       <c r="T3">
-        <v>1.75</v>
+        <v>5.11</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1072,34 +1110,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>36.94</v>
+        <v>44.24</v>
       </c>
       <c r="Z3">
-        <v>-10.28</v>
+        <v>-10.89</v>
       </c>
       <c r="AA3">
-        <v>-5.39</v>
+        <v>-6.49</v>
       </c>
       <c r="AB3">
-        <v>-4.89</v>
+        <v>-4.4</v>
       </c>
       <c r="AC3">
-        <v>14.71</v>
+        <v>21.96</v>
       </c>
       <c r="AD3">
-        <v>20.14</v>
+        <v>20.8</v>
       </c>
       <c r="AE3">
-        <v>26.74</v>
+        <v>28.39</v>
       </c>
       <c r="AF3">
-        <v>125.13</v>
+        <v>245.39</v>
       </c>
       <c r="AG3">
-        <v>920.76</v>
+        <v>920.88</v>
       </c>
       <c r="AH3">
-        <v>830.33</v>
+        <v>826.8200000000001</v>
       </c>
       <c r="AI3">
         <v>910.9299999999999</v>
@@ -1108,7 +1146,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>23.87</v>
+        <v>24.14</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,10 +1157,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1586</v>
+        <v>1574.4</v>
       </c>
       <c r="D4">
-        <v>1.47</v>
+        <v>-0.73</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1131,25 +1169,25 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-18.25</v>
+        <v>-18.85</v>
       </c>
       <c r="H4">
-        <v>17.07</v>
+        <v>16.22</v>
       </c>
       <c r="I4">
-        <v>2.72</v>
+        <v>-0.83</v>
       </c>
       <c r="J4">
-        <v>-11.48</v>
+        <v>-10.83</v>
       </c>
       <c r="K4">
-        <v>-11.35</v>
+        <v>-12.77</v>
       </c>
       <c r="L4">
-        <v>-1.67</v>
+        <v>-4.35</v>
       </c>
       <c r="M4">
-        <v>21.77</v>
+        <v>21.58</v>
       </c>
       <c r="N4">
         <v>43</v>
@@ -1158,19 +1196,19 @@
         <v>45</v>
       </c>
       <c r="P4">
-        <v>1587.6</v>
+        <v>1584.96</v>
       </c>
       <c r="Q4">
-        <v>1646.53</v>
+        <v>1637.02</v>
       </c>
       <c r="R4">
-        <v>1777.08</v>
+        <v>1770.97</v>
       </c>
       <c r="S4">
-        <v>1676.86</v>
+        <v>1676.25</v>
       </c>
       <c r="T4">
-        <v>-5.42</v>
+        <v>-6.08</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1185,34 +1223,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>38.38</v>
+        <v>37.18</v>
       </c>
       <c r="Z4">
-        <v>-58.82</v>
+        <v>-57.07</v>
       </c>
       <c r="AA4">
-        <v>-59.71</v>
+        <v>-59.18</v>
       </c>
       <c r="AB4">
-        <v>0.89</v>
+        <v>2.11</v>
       </c>
       <c r="AC4">
-        <v>81.36</v>
+        <v>78.06</v>
       </c>
       <c r="AD4">
-        <v>72.06999999999999</v>
+        <v>76.19</v>
       </c>
       <c r="AE4">
-        <v>47.22</v>
+        <v>45.89</v>
       </c>
       <c r="AF4">
-        <v>1.99</v>
+        <v>-40.21</v>
       </c>
       <c r="AG4">
-        <v>1809.8</v>
+        <v>1793.36</v>
       </c>
       <c r="AH4">
-        <v>1483.26</v>
+        <v>1480.69</v>
       </c>
       <c r="AI4">
         <v>1692.02</v>
@@ -1221,7 +1259,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>51.77</v>
+        <v>50.29</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1270,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1765.3</v>
+        <v>1758.6</v>
       </c>
       <c r="D5">
-        <v>1.05</v>
+        <v>-0.38</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1244,46 +1282,46 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-26.41</v>
+        <v>-26.69</v>
       </c>
       <c r="H5">
-        <v>5.47</v>
+        <v>5.07</v>
       </c>
       <c r="I5">
-        <v>5.47</v>
+        <v>3.24</v>
       </c>
       <c r="J5">
-        <v>-8.960000000000001</v>
+        <v>-9.25</v>
       </c>
       <c r="K5">
-        <v>-12.7</v>
+        <v>-13.55</v>
       </c>
       <c r="L5">
-        <v>-20.19</v>
+        <v>-20.44</v>
       </c>
       <c r="M5">
-        <v>16.53</v>
+        <v>16.43</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="P5">
-        <v>1725.78</v>
+        <v>1736.82</v>
       </c>
       <c r="Q5">
-        <v>1826.45</v>
+        <v>1817.89</v>
       </c>
       <c r="R5">
-        <v>1926.15</v>
+        <v>1919.59</v>
       </c>
       <c r="S5">
-        <v>2030.82</v>
+        <v>2027.84</v>
       </c>
       <c r="T5">
-        <v>-13.07</v>
+        <v>-13.28</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1298,34 +1336,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>41.41</v>
+        <v>40.7</v>
       </c>
       <c r="Z5">
-        <v>-61.35</v>
+        <v>-57.41</v>
       </c>
       <c r="AA5">
-        <v>-58.45</v>
+        <v>-58.24</v>
       </c>
       <c r="AB5">
-        <v>-2.89</v>
+        <v>0.84</v>
       </c>
       <c r="AC5">
-        <v>52.16</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="AD5">
-        <v>37.75</v>
+        <v>53.13</v>
       </c>
       <c r="AE5">
-        <v>56.28</v>
+        <v>55.41</v>
       </c>
       <c r="AF5">
-        <v>-21.67</v>
+        <v>18.25</v>
       </c>
       <c r="AG5">
-        <v>2040.84</v>
+        <v>2028.55</v>
       </c>
       <c r="AH5">
-        <v>1612.06</v>
+        <v>1607.23</v>
       </c>
       <c r="AI5">
         <v>1853.75</v>
@@ -1334,7 +1372,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>38.59</v>
+        <v>36.12</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,10 +1383,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>701.95</v>
+        <v>694.15</v>
       </c>
       <c r="D6">
-        <v>1.5</v>
+        <v>-1.11</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1357,46 +1395,46 @@
         <v>674.55</v>
       </c>
       <c r="G6">
-        <v>-35.59</v>
+        <v>-36.3</v>
       </c>
       <c r="H6">
-        <v>4.06</v>
+        <v>2.91</v>
       </c>
       <c r="I6">
-        <v>3.66</v>
+        <v>0.76</v>
       </c>
       <c r="J6">
-        <v>-0.11</v>
+        <v>-1.27</v>
       </c>
       <c r="K6">
-        <v>-8.9</v>
+        <v>-7.57</v>
       </c>
       <c r="L6">
-        <v>-31.62</v>
+        <v>-33</v>
       </c>
       <c r="M6">
-        <v>8.33</v>
+        <v>8.09</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="P6">
-        <v>697.73</v>
+        <v>698.78</v>
       </c>
       <c r="Q6">
-        <v>695.78</v>
+        <v>695.33</v>
       </c>
       <c r="R6">
-        <v>747.48</v>
+        <v>744.9</v>
       </c>
       <c r="S6">
-        <v>808.05</v>
+        <v>806.23</v>
       </c>
       <c r="T6">
-        <v>-13.13</v>
+        <v>-13.9</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1411,34 +1449,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>46.4</v>
+        <v>43.82</v>
       </c>
       <c r="Z6">
-        <v>-12.99</v>
+        <v>-12.29</v>
       </c>
       <c r="AA6">
-        <v>-17.03</v>
+        <v>-16.09</v>
       </c>
       <c r="AB6">
-        <v>4.04</v>
+        <v>3.79</v>
       </c>
       <c r="AC6">
-        <v>90.19</v>
+        <v>84.25</v>
       </c>
       <c r="AD6">
-        <v>93.12</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="AE6">
-        <v>19.6</v>
+        <v>19.13</v>
       </c>
       <c r="AF6">
-        <v>20.84</v>
+        <v>-31.38</v>
       </c>
       <c r="AG6">
-        <v>713.8</v>
+        <v>713.03</v>
       </c>
       <c r="AH6">
-        <v>677.76</v>
+        <v>677.63</v>
       </c>
       <c r="AI6">
         <v>739.76</v>
@@ -1447,7 +1485,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>24.17</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,10 +1496,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2585.3</v>
+        <v>2630.4</v>
       </c>
       <c r="D7">
-        <v>-3.15</v>
+        <v>1.74</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1470,46 +1508,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-25.17</v>
+        <v>-23.86</v>
       </c>
       <c r="H7">
-        <v>36.68</v>
+        <v>39.07</v>
       </c>
       <c r="I7">
-        <v>0.13</v>
+        <v>-0.03</v>
       </c>
       <c r="J7">
-        <v>-17.37</v>
+        <v>-15.54</v>
       </c>
       <c r="K7">
-        <v>5.35</v>
+        <v>3.63</v>
       </c>
       <c r="L7">
-        <v>9.07</v>
+        <v>13.39</v>
       </c>
       <c r="M7">
-        <v>23.66</v>
+        <v>24.07</v>
       </c>
       <c r="N7">
         <v>85</v>
       </c>
       <c r="O7">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P7">
-        <v>2637.24</v>
+        <v>2637.1</v>
       </c>
       <c r="Q7">
-        <v>2847.75</v>
+        <v>2826.78</v>
       </c>
       <c r="R7">
-        <v>3007.58</v>
+        <v>3007.62</v>
       </c>
       <c r="S7">
-        <v>2523.79</v>
+        <v>2525.75</v>
       </c>
       <c r="T7">
-        <v>2.44</v>
+        <v>4.14</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1524,43 +1562,43 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>29.19</v>
+        <v>33.79</v>
       </c>
       <c r="Z7">
-        <v>-120.24</v>
+        <v>-119.35</v>
       </c>
       <c r="AA7">
-        <v>-92.42</v>
+        <v>-97.81</v>
       </c>
       <c r="AB7">
-        <v>-27.81</v>
+        <v>-21.54</v>
       </c>
       <c r="AC7">
-        <v>38.44</v>
+        <v>51.86</v>
       </c>
       <c r="AD7">
-        <v>36.38</v>
+        <v>43.31</v>
       </c>
       <c r="AE7">
-        <v>119.87</v>
+        <v>116.52</v>
       </c>
       <c r="AF7">
-        <v>38.48</v>
+        <v>-59.72</v>
       </c>
       <c r="AG7">
-        <v>3191.83</v>
+        <v>3170.15</v>
       </c>
       <c r="AH7">
-        <v>2503.67</v>
+        <v>2483.42</v>
       </c>
       <c r="AI7">
-        <v>2967.97</v>
+        <v>2961.01</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>61.74</v>
+        <v>63.91</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1571,10 +1609,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7728.5</v>
+        <v>7871.5</v>
       </c>
       <c r="D8">
-        <v>-2.13</v>
+        <v>1.85</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1583,88 +1621,88 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-15.15</v>
+        <v>-13.58</v>
       </c>
       <c r="H8">
-        <v>30.45</v>
+        <v>32.86</v>
       </c>
       <c r="I8">
-        <v>0.21</v>
+        <v>1.59</v>
       </c>
       <c r="J8">
-        <v>-9.92</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="K8">
-        <v>-0.68</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
-        <v>-13.01</v>
+        <v>-10.68</v>
       </c>
       <c r="M8">
-        <v>12.46</v>
+        <v>12.86</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="P8">
-        <v>7770</v>
+        <v>7794.6</v>
       </c>
       <c r="Q8">
-        <v>8231.92</v>
+        <v>8187.25</v>
       </c>
       <c r="R8">
-        <v>8217.129999999999</v>
+        <v>8213.52</v>
       </c>
       <c r="S8">
-        <v>7431.83</v>
+        <v>7431.93</v>
       </c>
       <c r="T8">
-        <v>3.99</v>
+        <v>5.91</v>
       </c>
       <c r="U8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V8" t="s">
         <v>45</v>
       </c>
       <c r="W8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y8">
-        <v>37.34</v>
+        <v>42.57</v>
       </c>
       <c r="Z8">
-        <v>-163.34</v>
+        <v>-158.15</v>
       </c>
       <c r="AA8">
-        <v>-95.72</v>
+        <v>-108.21</v>
       </c>
       <c r="AB8">
-        <v>-67.62</v>
+        <v>-49.94</v>
       </c>
       <c r="AC8">
-        <v>23.48</v>
+        <v>35.69</v>
       </c>
       <c r="AD8">
-        <v>16.23</v>
+        <v>25.59</v>
       </c>
       <c r="AE8">
-        <v>268.97</v>
+        <v>266.73</v>
       </c>
       <c r="AF8">
-        <v>-73.44</v>
+        <v>-51.33</v>
       </c>
       <c r="AG8">
-        <v>9019.02</v>
+        <v>8947.93</v>
       </c>
       <c r="AH8">
-        <v>7444.83</v>
+        <v>7426.57</v>
       </c>
       <c r="AI8">
         <v>8581.85</v>
@@ -1673,7 +1711,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>33.4</v>
+        <v>30.82</v>
       </c>
     </row>
   </sheetData>
@@ -1814,7 +1852,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1834,991 +1872,1066 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
+      <c r="A5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="5">
-        <v>8.91</v>
-      </c>
-      <c r="D7" s="5">
-        <v>7.04</v>
-      </c>
-      <c r="E7" s="6">
-        <v>-1.87</v>
-      </c>
+      <c r="A7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>7.04</v>
+      </c>
+      <c r="D9" s="7">
+        <v>5.56</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-1.48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-5.06</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C10" s="7">
         <v>-4.66</v>
       </c>
-      <c r="E8" s="7">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D10" s="7">
+        <v>-0.65</v>
+      </c>
+      <c r="E10" s="9">
+        <v>4.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-15.33</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C11" s="7">
         <v>-11.48</v>
       </c>
-      <c r="E9" s="7">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D11" s="7">
+        <v>-10.83</v>
+      </c>
+      <c r="E11" s="9">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-9.43</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C12" s="7">
         <v>-8.960000000000001</v>
       </c>
-      <c r="E10" s="7">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D12" s="7">
+        <v>-9.25</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-4.08</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C13" s="7">
         <v>-0.11</v>
       </c>
-      <c r="E11" s="7">
-        <v>3.97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D13" s="7">
+        <v>-1.27</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-17.87</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C14" s="7">
         <v>-17.37</v>
       </c>
-      <c r="E12" s="7">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D14" s="7">
+        <v>-15.54</v>
+      </c>
+      <c r="E14" s="9">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-10.39</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C15" s="7">
         <v>-9.92</v>
       </c>
-      <c r="E13" s="7">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D15" s="7">
+        <v>-9.140000000000001</v>
+      </c>
+      <c r="E15" s="9">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-6.82</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C16" s="7">
         <v>-8.68</v>
       </c>
-      <c r="E14" s="6">
-        <v>-1.86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D16" s="7">
+        <v>-7.69</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-3.52</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C17" s="7">
         <v>-5.11</v>
       </c>
-      <c r="E15" s="6">
-        <v>-1.59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D17" s="7">
+        <v>-1.12</v>
+      </c>
+      <c r="E17" s="9">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B18" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-0.11</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C18" s="7">
         <v>2.72</v>
       </c>
-      <c r="E16" s="7">
-        <v>2.83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D18" s="7">
+        <v>-0.83</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-3.55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>0.09</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C19" s="7">
         <v>5.47</v>
       </c>
-      <c r="E17" s="7">
-        <v>5.38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D19" s="7">
+        <v>3.24</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B20" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>-1.14</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C20" s="7">
         <v>3.66</v>
       </c>
-      <c r="E18" s="7">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D20" s="7">
+        <v>0.76</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-2.9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B21" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5">
-        <v>-1.69</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C21" s="7">
         <v>0.13</v>
       </c>
-      <c r="E19" s="7">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D21" s="7">
+        <v>-0.03</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B22" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="5">
-        <v>-1.18</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C22" s="7">
         <v>0.21</v>
       </c>
-      <c r="E20" s="7">
-        <v>1.39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D22" s="7">
+        <v>1.59</v>
+      </c>
+      <c r="E22" s="9">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B23" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>28.35</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C23" s="7">
         <v>18.02</v>
       </c>
-      <c r="E21" s="6">
-        <v>-10.33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D23" s="7">
+        <v>19.82</v>
+      </c>
+      <c r="E23" s="9">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B24" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="5">
-        <v>13.63</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C24" s="7">
         <v>8.81</v>
       </c>
-      <c r="E22" s="6">
-        <v>-4.82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D24" s="7">
+        <v>13.5</v>
+      </c>
+      <c r="E24" s="9">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B25" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="5">
-        <v>-3.53</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C25" s="7">
         <v>-1.67</v>
       </c>
-      <c r="E23" s="7">
-        <v>1.86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D25" s="7">
+        <v>-4.35</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-2.68</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B26" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="5">
-        <v>-21.83</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C26" s="7">
         <v>-20.19</v>
       </c>
-      <c r="E24" s="7">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D26" s="7">
+        <v>-20.44</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B27" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="5">
-        <v>-33.33</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C27" s="7">
         <v>-31.62</v>
       </c>
-      <c r="E25" s="7">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D27" s="7">
+        <v>-33</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B28" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="5">
-        <v>16.84</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C28" s="7">
         <v>9.07</v>
       </c>
-      <c r="E26" s="6">
-        <v>-7.77</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D28" s="7">
+        <v>13.39</v>
+      </c>
+      <c r="E28" s="9">
+        <v>4.32</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B29" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="5">
-        <v>-10.4</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C29" s="7">
         <v>-13.01</v>
       </c>
-      <c r="E27" s="6">
-        <v>-2.61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D29" s="7">
+        <v>-10.68</v>
+      </c>
+      <c r="E29" s="9">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B30" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="5">
-        <v>8.25</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C30" s="7">
         <v>1.76</v>
       </c>
-      <c r="E28" s="6">
-        <v>-6.49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D30" s="7">
+        <v>4.75</v>
+      </c>
+      <c r="E30" s="9">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B31" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="5">
-        <v>-7.12</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C31" s="7">
         <v>-11.28</v>
       </c>
-      <c r="E29" s="6">
-        <v>-4.16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D31" s="7">
+        <v>-6.52</v>
+      </c>
+      <c r="E31" s="9">
+        <v>4.76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B32" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="5">
-        <v>-13.35</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C32" s="7">
         <v>-11.35</v>
       </c>
-      <c r="E30" s="7">
+      <c r="D32" s="7">
+        <v>-12.77</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.42</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7">
+        <v>-12.7</v>
+      </c>
+      <c r="D33" s="7">
+        <v>-13.55</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="7">
+        <v>-8.9</v>
+      </c>
+      <c r="D34" s="7">
+        <v>-7.57</v>
+      </c>
+      <c r="E34" s="9">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C35" s="7">
+        <v>5.35</v>
+      </c>
+      <c r="D35" s="7">
+        <v>3.63</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36" s="7">
+        <v>-0.68</v>
+      </c>
+      <c r="D36" s="7">
+        <v>3.8</v>
+      </c>
+      <c r="E36" s="9">
+        <v>4.48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="7">
+        <v>-14.82</v>
+      </c>
+      <c r="D37" s="7">
+        <v>-14.38</v>
+      </c>
+      <c r="E37" s="9">
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="7">
+        <v>-16.23</v>
+      </c>
+      <c r="D38" s="7">
+        <v>-13.36</v>
+      </c>
+      <c r="E38" s="9">
+        <v>2.87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="7">
+        <v>-18.25</v>
+      </c>
+      <c r="D39" s="7">
+        <v>-18.85</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="7">
+        <v>-26.41</v>
+      </c>
+      <c r="D40" s="7">
+        <v>-26.69</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="7">
+        <v>-35.59</v>
+      </c>
+      <c r="D41" s="7">
+        <v>-36.3</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="7">
+        <v>-25.17</v>
+      </c>
+      <c r="D42" s="7">
+        <v>-23.86</v>
+      </c>
+      <c r="E42" s="9">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-15.15</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-13.58</v>
+      </c>
+      <c r="E43" s="9">
+        <v>1.57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="6" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="C44" s="7">
+        <v>1104.4</v>
+      </c>
+      <c r="D44" s="7">
+        <v>1110.1</v>
+      </c>
+      <c r="E44" s="9">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7">
+        <v>818</v>
+      </c>
+      <c r="D45" s="7">
+        <v>846</v>
+      </c>
+      <c r="E45" s="9">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7">
+        <v>1586</v>
+      </c>
+      <c r="D46" s="7">
+        <v>1574.4</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-11.6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-15.03</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-12.7</v>
-      </c>
-      <c r="E31" s="7">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B47" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7">
+        <v>1765.3</v>
+      </c>
+      <c r="D47" s="7">
+        <v>1758.6</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-6.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-11.18</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-8.9</v>
-      </c>
-      <c r="E32" s="7">
-        <v>2.28</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B48" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7">
+        <v>701.95</v>
+      </c>
+      <c r="D48" s="7">
+        <v>694.15</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-7.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>7.27</v>
-      </c>
-      <c r="D33" s="5">
-        <v>5.35</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B49" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C49" s="7">
+        <v>2585.3</v>
+      </c>
+      <c r="D49" s="7">
+        <v>2630.4</v>
+      </c>
+      <c r="E49" s="9">
+        <v>45.1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>1.52</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-0.68</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-2.2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="7">
+        <v>7728.5</v>
+      </c>
+      <c r="D50" s="7">
+        <v>7871.5</v>
+      </c>
+      <c r="E50" s="9">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-9.68</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-14.82</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-5.14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B51" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="7">
+        <v>38.55</v>
+      </c>
+      <c r="D51" s="7">
+        <v>39.56</v>
+      </c>
+      <c r="E51" s="9">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-11.62</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-16.23</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-4.61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="7">
+        <v>36.94</v>
+      </c>
+      <c r="D52" s="7">
+        <v>44.24</v>
+      </c>
+      <c r="E52" s="9">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-19.43</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-18.25</v>
-      </c>
-      <c r="E37" s="7">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="7">
+        <v>38.38</v>
+      </c>
+      <c r="D53" s="7">
+        <v>37.18</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-27.17</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-26.41</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="7">
+        <v>41.41</v>
+      </c>
+      <c r="D54" s="7">
+        <v>40.7</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-36.54</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-35.59</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="7">
+        <v>46.4</v>
+      </c>
+      <c r="D55" s="7">
+        <v>43.82</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-2.58</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-22.73</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-25.17</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-2.44</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="7">
+        <v>29.19</v>
+      </c>
+      <c r="D56" s="7">
+        <v>33.79</v>
+      </c>
+      <c r="E56" s="9">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-13.3</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-15.15</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="7">
+        <v>37.34</v>
+      </c>
+      <c r="D57" s="7">
+        <v>42.57</v>
+      </c>
+      <c r="E57" s="9">
+        <v>5.23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1171</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1104.4</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-66.59999999999999</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B58" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="7">
+        <v>-69.92</v>
+      </c>
+      <c r="D58" s="7">
+        <v>-73.7</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-3.78</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>863</v>
-      </c>
-      <c r="D43" s="5">
-        <v>818</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-45</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="B59" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="7">
+        <v>125.13</v>
+      </c>
+      <c r="D59" s="7">
+        <v>245.39</v>
+      </c>
+      <c r="E59" s="9">
+        <v>120.26</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>1563</v>
-      </c>
-      <c r="D44" s="5">
-        <v>1586</v>
-      </c>
-      <c r="E44" s="7">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="B60" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="7">
+        <v>1.99</v>
+      </c>
+      <c r="D60" s="7">
+        <v>-40.21</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-42.2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1747</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1765.3</v>
-      </c>
-      <c r="E45" s="7">
-        <v>18.3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="B61" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="7">
+        <v>-21.67</v>
+      </c>
+      <c r="D61" s="7">
+        <v>18.25</v>
+      </c>
+      <c r="E61" s="9">
+        <v>39.92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>691.6</v>
-      </c>
-      <c r="D46" s="5">
-        <v>701.95</v>
-      </c>
-      <c r="E46" s="7">
-        <v>10.35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="B62" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="7">
+        <v>20.84</v>
+      </c>
+      <c r="D62" s="7">
+        <v>-31.38</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-52.22</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>2669.5</v>
-      </c>
-      <c r="D47" s="5">
-        <v>2585.3</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-84.2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
+      <c r="B63" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7">
+        <v>38.48</v>
+      </c>
+      <c r="D63" s="7">
+        <v>-59.72</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-98.2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>7897</v>
-      </c>
-      <c r="D48" s="5">
-        <v>7728.5</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-168.5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>47.15</v>
-      </c>
-      <c r="D49" s="5">
-        <v>38.55</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-8.6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>45.92</v>
-      </c>
-      <c r="D50" s="5">
-        <v>36.94</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-8.98</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>34.48</v>
-      </c>
-      <c r="D51" s="5">
-        <v>38.38</v>
-      </c>
-      <c r="E51" s="7">
-        <v>3.9</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>38.69</v>
-      </c>
-      <c r="D52" s="5">
-        <v>41.41</v>
-      </c>
-      <c r="E52" s="7">
-        <v>2.72</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>42.21</v>
-      </c>
-      <c r="D53" s="5">
-        <v>46.4</v>
-      </c>
-      <c r="E53" s="7">
-        <v>4.19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>33.19</v>
-      </c>
-      <c r="D54" s="5">
-        <v>29.19</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>41.48</v>
-      </c>
-      <c r="D55" s="5">
-        <v>37.34</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-4.14</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="3" t="s">
+      <c r="B64" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="5">
-        <v>-82.78</v>
-      </c>
-      <c r="D56" s="5">
-        <v>-69.92</v>
-      </c>
-      <c r="E56" s="7">
-        <v>12.86</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5">
-        <v>-22.27</v>
-      </c>
-      <c r="D57" s="5">
-        <v>125.13</v>
-      </c>
-      <c r="E57" s="7">
-        <v>147.4</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5">
-        <v>58.8</v>
-      </c>
-      <c r="D58" s="5">
-        <v>1.99</v>
-      </c>
-      <c r="E58" s="6">
-        <v>-56.81</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>123.24</v>
-      </c>
-      <c r="D59" s="5">
-        <v>-21.67</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-144.91</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>59.9</v>
-      </c>
-      <c r="D60" s="5">
-        <v>20.84</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-39.06</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>-11.53</v>
-      </c>
-      <c r="D61" s="5">
-        <v>38.48</v>
-      </c>
-      <c r="E61" s="7">
-        <v>50.01</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-54.99</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C64" s="7">
         <v>-73.44</v>
       </c>
-      <c r="E62" s="6">
-        <v>-18.45</v>
+      <c r="D64" s="7">
+        <v>-51.33</v>
+      </c>
+      <c r="E64" s="9">
+        <v>22.11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2838,61 +2951,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="12">
+        <v>56.8</v>
+      </c>
+      <c r="C2" s="13">
+        <v>7</v>
+      </c>
+      <c r="D2" s="12">
+        <v>40.3</v>
+      </c>
+      <c r="E2" s="12">
+        <v>60</v>
+      </c>
+      <c r="F2" s="12">
+        <v>-5.9</v>
+      </c>
+      <c r="G2" s="12">
+        <v>-4</v>
+      </c>
+      <c r="H2" s="12">
         <v>57</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>56.8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>38.3</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-6.5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-5.4</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
-        <v>30</v>
+      <c r="I2" s="12">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2993,49 +3106,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="14" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.4626</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2366</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2177</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1653</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1246</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.0833</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0454</v>
+      <c r="A2" s="15">
+        <v>0.4722</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.2407</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.2158</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.1643</v>
+      </c>
+      <c r="E2" s="15">
+        <v>0.1286</v>
+      </c>
+      <c r="F2" s="15">
+        <v>0.0809</v>
+      </c>
+      <c r="G2" s="15">
+        <v>0.04650000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,43 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.2 → 33.8</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>29.2</t>
-  </si>
-  <si>
-    <t>33.8</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -291,14 +255,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -331,13 +295,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -407,19 +371,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -931,10 +893,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1110.1</v>
+        <v>1089</v>
       </c>
       <c r="D2">
-        <v>0.52</v>
+        <v>-1.9</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -943,46 +905,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-14.38</v>
+        <v>-16</v>
       </c>
       <c r="H2">
-        <v>48.34</v>
+        <v>45.52</v>
       </c>
       <c r="I2">
-        <v>-7.69</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="J2">
-        <v>5.56</v>
+        <v>0.5</v>
       </c>
       <c r="K2">
-        <v>4.75</v>
+        <v>0.17</v>
       </c>
       <c r="L2">
-        <v>19.82</v>
+        <v>19.35</v>
       </c>
       <c r="M2">
-        <v>4.65</v>
+        <v>4.79</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P2">
-        <v>1153.28</v>
+        <v>1131.84</v>
       </c>
       <c r="Q2">
-        <v>1213.34</v>
+        <v>1211.57</v>
       </c>
       <c r="R2">
-        <v>1150.59</v>
+        <v>1150.99</v>
       </c>
       <c r="S2">
-        <v>993.47</v>
+        <v>994.78</v>
       </c>
       <c r="T2">
-        <v>11.74</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -997,43 +959,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>39.56</v>
+        <v>37.11</v>
       </c>
       <c r="Z2">
-        <v>1.23</v>
+        <v>-6.04</v>
       </c>
       <c r="AA2">
-        <v>19.99</v>
+        <v>14.78</v>
       </c>
       <c r="AB2">
-        <v>-18.76</v>
+        <v>-20.82</v>
       </c>
       <c r="AC2">
         <v>1.34</v>
       </c>
       <c r="AD2">
-        <v>0.45</v>
+        <v>0.9</v>
       </c>
       <c r="AE2">
-        <v>49.43</v>
+        <v>48.31</v>
       </c>
       <c r="AF2">
-        <v>-73.7</v>
+        <v>-67.01000000000001</v>
       </c>
       <c r="AG2">
-        <v>1325.75</v>
+        <v>1330.78</v>
       </c>
       <c r="AH2">
-        <v>1100.94</v>
+        <v>1092.37</v>
       </c>
       <c r="AI2">
-        <v>1253.3</v>
+        <v>1242.27</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>33.33</v>
+        <v>35.87</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1044,10 +1006,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>846</v>
+        <v>855</v>
       </c>
       <c r="D3">
-        <v>3.42</v>
+        <v>1.06</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1056,46 +1018,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-13.36</v>
+        <v>-12.44</v>
       </c>
       <c r="H3">
-        <v>59.78</v>
+        <v>61.48</v>
       </c>
       <c r="I3">
-        <v>-1.12</v>
+        <v>-1.44</v>
       </c>
       <c r="J3">
-        <v>-0.65</v>
+        <v>-2.84</v>
       </c>
       <c r="K3">
-        <v>-6.52</v>
+        <v>-6.3</v>
       </c>
       <c r="L3">
-        <v>13.5</v>
+        <v>14.87</v>
       </c>
       <c r="M3">
-        <v>47.22</v>
+        <v>46.03</v>
       </c>
       <c r="N3">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O3">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>849.7</v>
+        <v>847.2</v>
       </c>
       <c r="Q3">
-        <v>873.85</v>
+        <v>872</v>
       </c>
       <c r="R3">
-        <v>881.5</v>
+        <v>881.08</v>
       </c>
       <c r="S3">
-        <v>804.89</v>
+        <v>805.97</v>
       </c>
       <c r="T3">
-        <v>5.11</v>
+        <v>6.08</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1110,34 +1072,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>44.24</v>
+        <v>46.39</v>
       </c>
       <c r="Z3">
-        <v>-10.89</v>
+        <v>-10.52</v>
       </c>
       <c r="AA3">
-        <v>-6.49</v>
+        <v>-7.3</v>
       </c>
       <c r="AB3">
-        <v>-4.4</v>
+        <v>-3.22</v>
       </c>
       <c r="AC3">
-        <v>21.96</v>
+        <v>27.47</v>
       </c>
       <c r="AD3">
-        <v>20.8</v>
+        <v>21.38</v>
       </c>
       <c r="AE3">
-        <v>28.39</v>
+        <v>27.95</v>
       </c>
       <c r="AF3">
-        <v>245.39</v>
+        <v>55.55</v>
       </c>
       <c r="AG3">
-        <v>920.88</v>
+        <v>918.9299999999999</v>
       </c>
       <c r="AH3">
-        <v>826.8200000000001</v>
+        <v>825.0599999999999</v>
       </c>
       <c r="AI3">
         <v>910.9299999999999</v>
@@ -1146,7 +1108,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>24.14</v>
+        <v>23.33</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1157,10 +1119,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1574.4</v>
+        <v>1553</v>
       </c>
       <c r="D4">
-        <v>-0.73</v>
+        <v>-1.36</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1169,25 +1131,25 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-18.85</v>
+        <v>-19.95</v>
       </c>
       <c r="H4">
-        <v>16.22</v>
+        <v>14.64</v>
       </c>
       <c r="I4">
-        <v>-0.83</v>
+        <v>-1.75</v>
       </c>
       <c r="J4">
-        <v>-10.83</v>
+        <v>-11.99</v>
       </c>
       <c r="K4">
-        <v>-12.77</v>
+        <v>-12.89</v>
       </c>
       <c r="L4">
-        <v>-4.35</v>
+        <v>-5.56</v>
       </c>
       <c r="M4">
-        <v>21.58</v>
+        <v>20.84</v>
       </c>
       <c r="N4">
         <v>43</v>
@@ -1196,19 +1158,19 @@
         <v>45</v>
       </c>
       <c r="P4">
-        <v>1584.96</v>
+        <v>1579.42</v>
       </c>
       <c r="Q4">
-        <v>1637.02</v>
+        <v>1624.67</v>
       </c>
       <c r="R4">
-        <v>1770.97</v>
+        <v>1763.23</v>
       </c>
       <c r="S4">
-        <v>1676.25</v>
+        <v>1675.51</v>
       </c>
       <c r="T4">
-        <v>-6.08</v>
+        <v>-7.31</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1223,34 +1185,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>37.18</v>
+        <v>35</v>
       </c>
       <c r="Z4">
-        <v>-57.07</v>
+        <v>-56.76</v>
       </c>
       <c r="AA4">
-        <v>-59.18</v>
+        <v>-58.7</v>
       </c>
       <c r="AB4">
-        <v>2.11</v>
+        <v>1.94</v>
       </c>
       <c r="AC4">
-        <v>78.06</v>
+        <v>79.06999999999999</v>
       </c>
       <c r="AD4">
-        <v>76.19</v>
+        <v>79.5</v>
       </c>
       <c r="AE4">
-        <v>45.89</v>
+        <v>45.63</v>
       </c>
       <c r="AF4">
-        <v>-40.21</v>
+        <v>-65.88</v>
       </c>
       <c r="AG4">
-        <v>1793.36</v>
+        <v>1765.01</v>
       </c>
       <c r="AH4">
-        <v>1480.69</v>
+        <v>1484.34</v>
       </c>
       <c r="AI4">
         <v>1692.02</v>
@@ -1259,7 +1221,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>50.29</v>
+        <v>50.07</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1270,10 +1232,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1758.6</v>
+        <v>1771.1</v>
       </c>
       <c r="D5">
-        <v>-0.38</v>
+        <v>0.71</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1282,46 +1244,46 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-26.69</v>
+        <v>-26.17</v>
       </c>
       <c r="H5">
-        <v>5.07</v>
+        <v>5.82</v>
       </c>
       <c r="I5">
-        <v>3.24</v>
+        <v>4.8</v>
       </c>
       <c r="J5">
-        <v>-9.25</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="K5">
-        <v>-13.55</v>
+        <v>-12.34</v>
       </c>
       <c r="L5">
-        <v>-20.44</v>
+        <v>-18.33</v>
       </c>
       <c r="M5">
-        <v>16.43</v>
+        <v>17.02</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="P5">
-        <v>1736.82</v>
+        <v>1753.04</v>
       </c>
       <c r="Q5">
-        <v>1817.89</v>
+        <v>1806.47</v>
       </c>
       <c r="R5">
-        <v>1919.59</v>
+        <v>1913.35</v>
       </c>
       <c r="S5">
-        <v>2027.84</v>
+        <v>2025.56</v>
       </c>
       <c r="T5">
-        <v>-13.28</v>
+        <v>-12.56</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1336,34 +1298,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>40.7</v>
+        <v>42.68</v>
       </c>
       <c r="Z5">
-        <v>-57.41</v>
+        <v>-52.67</v>
       </c>
       <c r="AA5">
-        <v>-58.24</v>
+        <v>-57.13</v>
       </c>
       <c r="AB5">
-        <v>0.84</v>
+        <v>4.46</v>
       </c>
       <c r="AC5">
-        <v>71.15000000000001</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="AD5">
-        <v>53.13</v>
+        <v>70</v>
       </c>
       <c r="AE5">
-        <v>55.41</v>
+        <v>53.88</v>
       </c>
       <c r="AF5">
-        <v>18.25</v>
+        <v>-55.39</v>
       </c>
       <c r="AG5">
-        <v>2028.55</v>
+        <v>1999.72</v>
       </c>
       <c r="AH5">
-        <v>1607.23</v>
+        <v>1613.22</v>
       </c>
       <c r="AI5">
         <v>1853.75</v>
@@ -1372,7 +1334,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>36.12</v>
+        <v>33.83</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1383,58 +1345,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>694.15</v>
+        <v>674.05</v>
       </c>
       <c r="D6">
-        <v>-1.11</v>
+        <v>-2.9</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
       </c>
       <c r="F6">
-        <v>674.55</v>
+        <v>674.05</v>
       </c>
       <c r="G6">
-        <v>-36.3</v>
+        <v>-38.15</v>
       </c>
       <c r="H6">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.76</v>
+        <v>-3.62</v>
       </c>
       <c r="J6">
-        <v>-1.27</v>
+        <v>-4.13</v>
       </c>
       <c r="K6">
-        <v>-7.57</v>
+        <v>-11.57</v>
       </c>
       <c r="L6">
-        <v>-33</v>
+        <v>-35.12</v>
       </c>
       <c r="M6">
-        <v>8.09</v>
+        <v>8.42</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="P6">
-        <v>698.78</v>
+        <v>693.72</v>
       </c>
       <c r="Q6">
-        <v>695.33</v>
+        <v>694</v>
       </c>
       <c r="R6">
-        <v>744.9</v>
+        <v>742.1900000000001</v>
       </c>
       <c r="S6">
-        <v>806.23</v>
+        <v>804.45</v>
       </c>
       <c r="T6">
-        <v>-13.9</v>
+        <v>-16.21</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1449,43 +1411,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>43.82</v>
+        <v>37.97</v>
       </c>
       <c r="Z6">
-        <v>-12.29</v>
+        <v>-13.21</v>
       </c>
       <c r="AA6">
-        <v>-16.09</v>
+        <v>-15.51</v>
       </c>
       <c r="AB6">
-        <v>3.79</v>
+        <v>2.3</v>
       </c>
       <c r="AC6">
-        <v>84.25</v>
+        <v>76.52</v>
       </c>
       <c r="AD6">
-        <v>88.70999999999999</v>
+        <v>83.66</v>
       </c>
       <c r="AE6">
-        <v>19.13</v>
+        <v>19.42</v>
       </c>
       <c r="AF6">
-        <v>-31.38</v>
+        <v>-11.8</v>
       </c>
       <c r="AG6">
-        <v>713.03</v>
+        <v>713.88</v>
       </c>
       <c r="AH6">
-        <v>677.63</v>
+        <v>674.12</v>
       </c>
       <c r="AI6">
-        <v>739.76</v>
+        <v>738.76</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>22.89</v>
+        <v>23.01</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1496,10 +1458,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2630.4</v>
+        <v>2555.2</v>
       </c>
       <c r="D7">
-        <v>1.74</v>
+        <v>-2.86</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1508,46 +1470,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-23.86</v>
+        <v>-26.04</v>
       </c>
       <c r="H7">
-        <v>39.07</v>
+        <v>35.09</v>
       </c>
       <c r="I7">
-        <v>-0.03</v>
+        <v>-4.23</v>
       </c>
       <c r="J7">
-        <v>-15.54</v>
+        <v>-16.21</v>
       </c>
       <c r="K7">
-        <v>3.63</v>
+        <v>-0.46</v>
       </c>
       <c r="L7">
-        <v>13.39</v>
+        <v>11.36</v>
       </c>
       <c r="M7">
-        <v>24.07</v>
+        <v>22.49</v>
       </c>
       <c r="N7">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O7">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="P7">
-        <v>2637.1</v>
+        <v>2614.52</v>
       </c>
       <c r="Q7">
-        <v>2826.78</v>
+        <v>2801.84</v>
       </c>
       <c r="R7">
-        <v>3007.62</v>
+        <v>3006.02</v>
       </c>
       <c r="S7">
-        <v>2525.75</v>
+        <v>2527.46</v>
       </c>
       <c r="T7">
-        <v>4.14</v>
+        <v>1.1</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1562,34 +1524,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>33.79</v>
+        <v>30.26</v>
       </c>
       <c r="Z7">
-        <v>-119.35</v>
+        <v>-123.29</v>
       </c>
       <c r="AA7">
-        <v>-97.81</v>
+        <v>-102.9</v>
       </c>
       <c r="AB7">
-        <v>-21.54</v>
+        <v>-20.39</v>
       </c>
       <c r="AC7">
-        <v>51.86</v>
+        <v>53.2</v>
       </c>
       <c r="AD7">
-        <v>43.31</v>
+        <v>47.83</v>
       </c>
       <c r="AE7">
-        <v>116.52</v>
+        <v>118.63</v>
       </c>
       <c r="AF7">
-        <v>-59.72</v>
+        <v>35.54</v>
       </c>
       <c r="AG7">
-        <v>3170.15</v>
+        <v>3148.14</v>
       </c>
       <c r="AH7">
-        <v>2483.42</v>
+        <v>2455.54</v>
       </c>
       <c r="AI7">
         <v>2961.01</v>
@@ -1598,7 +1560,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>63.91</v>
+        <v>62.49</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1609,10 +1571,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7871.5</v>
+        <v>7689</v>
       </c>
       <c r="D8">
-        <v>1.85</v>
+        <v>-2.32</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1621,46 +1583,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-13.58</v>
+        <v>-15.59</v>
       </c>
       <c r="H8">
-        <v>32.86</v>
+        <v>29.78</v>
       </c>
       <c r="I8">
-        <v>1.59</v>
+        <v>0.05</v>
       </c>
       <c r="J8">
-        <v>-9.140000000000001</v>
+        <v>-12.28</v>
       </c>
       <c r="K8">
-        <v>3.8</v>
+        <v>1.45</v>
       </c>
       <c r="L8">
-        <v>-10.68</v>
+        <v>-11.8</v>
       </c>
       <c r="M8">
-        <v>12.86</v>
+        <v>12.64</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="P8">
-        <v>7794.6</v>
+        <v>7795.4</v>
       </c>
       <c r="Q8">
-        <v>8187.25</v>
+        <v>8133.32</v>
       </c>
       <c r="R8">
-        <v>8213.52</v>
+        <v>8206.030000000001</v>
       </c>
       <c r="S8">
-        <v>7431.93</v>
+        <v>7431.87</v>
       </c>
       <c r="T8">
-        <v>5.91</v>
+        <v>3.46</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1675,48 +1637,108 @@
         <v>2</v>
       </c>
       <c r="Y8">
-        <v>42.57</v>
+        <v>38.19</v>
       </c>
       <c r="Z8">
-        <v>-158.15</v>
+        <v>-166.83</v>
       </c>
       <c r="AA8">
-        <v>-108.21</v>
+        <v>-119.93</v>
       </c>
       <c r="AB8">
-        <v>-49.94</v>
+        <v>-46.9</v>
       </c>
       <c r="AC8">
-        <v>35.69</v>
+        <v>34.72</v>
       </c>
       <c r="AD8">
-        <v>25.59</v>
+        <v>31.3</v>
       </c>
       <c r="AE8">
-        <v>266.73</v>
+        <v>266.1</v>
       </c>
       <c r="AF8">
-        <v>-51.33</v>
+        <v>-53.79</v>
       </c>
       <c r="AG8">
-        <v>8947.93</v>
+        <v>8873.440000000001</v>
       </c>
       <c r="AH8">
-        <v>7426.57</v>
+        <v>7393.21</v>
       </c>
       <c r="AI8">
-        <v>8581.85</v>
+        <v>8562.809999999999</v>
       </c>
       <c r="AJ8" t="s">
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>30.82</v>
+        <v>29.67</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AK8"/>
   <conditionalFormatting sqref="AF2:AF8">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D8">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I8">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J2:J8">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K8">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L8">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -1728,8 +1750,14 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D8">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="N2:N8">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="greaterThanOrEqual">
+      <formula>80</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="lessThanOrEqual">
+      <formula>20</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min" val="0"/>
         <cfvo type="percentile" val="50"/>
@@ -1738,72 +1766,6 @@
         <color rgb="FFFFFFFF"/>
         <color rgb="FF63BE7B"/>
       </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I8">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J8">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K8">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L8">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N8">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="greaterThanOrEqual">
-      <formula>80</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="19" operator="lessThanOrEqual">
-      <formula>20</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T8">
@@ -1815,26 +1777,26 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U8">
-    <cfRule type="containsText" dxfId="1" priority="12" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="13" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V8">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W8">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
+    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1872,1066 +1834,1025 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>46</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>5.56</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-5.06</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>66</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-0.65</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-2.84</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-10.83</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-11.99</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-9.25</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="E10" s="7">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-1.27</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-4.13</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-2.86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-15.54</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-16.21</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-9.140000000000001</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-12.28</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-3.14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-7.69</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-8.960000000000001</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-1.12</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-1.44</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-0.83</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-1.75</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3.24</v>
+      </c>
+      <c r="D17" s="5">
+        <v>4.8</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.76</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-3.62</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-4.38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-0.03</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-4.23</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-4.2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="5">
+        <v>1.59</v>
+      </c>
+      <c r="D20" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>19.82</v>
+      </c>
+      <c r="D21" s="5">
+        <v>19.35</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>13.5</v>
+      </c>
+      <c r="D22" s="5">
+        <v>14.87</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-4.35</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-5.56</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-20.44</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-18.33</v>
+      </c>
+      <c r="E24" s="7">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-33</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-35.12</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-2.12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>13.39</v>
+      </c>
+      <c r="D26" s="5">
+        <v>11.36</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-2.03</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-10.68</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-11.8</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>4.75</v>
+      </c>
+      <c r="D28" s="5">
+        <v>0.17</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-4.58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-6.52</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-6.3</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-12.77</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-12.89</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-13.55</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-12.34</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-7.57</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-11.57</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>3.63</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-0.46</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-4.09</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="5">
+        <v>3.8</v>
+      </c>
+      <c r="D34" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-2.35</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-14.38</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-16</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-13.36</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-12.44</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-18.85</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-19.95</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-26.69</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-26.17</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-36.3</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-38.15</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-23.86</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-26.04</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-2.18</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-13.58</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-15.59</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-2.01</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1110.1</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1089</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-21.1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>846</v>
+      </c>
+      <c r="D43" s="5">
+        <v>855</v>
+      </c>
+      <c r="E43" s="7">
         <v>9</v>
       </c>
-      <c r="C9" s="7">
-        <v>7.04</v>
-      </c>
-      <c r="D9" s="7">
-        <v>5.56</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-1.48</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1574.4</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1553</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-21.4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1758.6</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1771.1</v>
+      </c>
+      <c r="E45" s="7">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>694.15</v>
+      </c>
+      <c r="D46" s="5">
+        <v>674.05</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-20.1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="5">
+        <v>2630.4</v>
+      </c>
+      <c r="D47" s="5">
+        <v>2555.2</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-75.2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="5">
+        <v>7871.5</v>
+      </c>
+      <c r="D48" s="5">
+        <v>7689</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-182.5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-4.66</v>
-      </c>
-      <c r="D10" s="7">
-        <v>-0.65</v>
-      </c>
-      <c r="E10" s="9">
-        <v>4.01</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="5">
+        <v>71</v>
+      </c>
+      <c r="D49" s="5">
+        <v>85</v>
+      </c>
+      <c r="E49" s="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="5">
+        <v>85</v>
+      </c>
+      <c r="D50" s="5">
+        <v>71</v>
+      </c>
+      <c r="E50" s="6">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>39.56</v>
+      </c>
+      <c r="D51" s="5">
+        <v>37.11</v>
+      </c>
+      <c r="E51" s="6">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>44.24</v>
+      </c>
+      <c r="D52" s="5">
+        <v>46.39</v>
+      </c>
+      <c r="E52" s="7">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-11.48</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-10.83</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>37.18</v>
+      </c>
+      <c r="D53" s="5">
+        <v>35</v>
+      </c>
+      <c r="E53" s="6">
+        <v>-2.18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-9.25</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-0.29</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>40.7</v>
+      </c>
+      <c r="D54" s="5">
+        <v>42.68</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1.98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-0.11</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-1.27</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="5">
+        <v>43.82</v>
+      </c>
+      <c r="D55" s="5">
+        <v>37.97</v>
+      </c>
+      <c r="E55" s="6">
+        <v>-5.85</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-17.37</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-15.54</v>
-      </c>
-      <c r="E14" s="9">
-        <v>1.83</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B56" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="5">
+        <v>33.79</v>
+      </c>
+      <c r="D56" s="5">
+        <v>30.26</v>
+      </c>
+      <c r="E56" s="6">
+        <v>-3.53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="7">
-        <v>-9.92</v>
-      </c>
-      <c r="D15" s="7">
-        <v>-9.140000000000001</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="5">
+        <v>42.57</v>
+      </c>
+      <c r="D57" s="5">
+        <v>38.19</v>
+      </c>
+      <c r="E57" s="6">
+        <v>-4.38</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-8.68</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-7.69</v>
-      </c>
-      <c r="E16" s="9">
-        <v>0.99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-73.7</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-67.01000000000001</v>
+      </c>
+      <c r="E58" s="7">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-5.11</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-1.12</v>
-      </c>
-      <c r="E17" s="9">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>245.39</v>
+      </c>
+      <c r="D59" s="5">
+        <v>55.55</v>
+      </c>
+      <c r="E59" s="6">
+        <v>-189.84</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>2.72</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-0.83</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-3.55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-40.21</v>
+      </c>
+      <c r="D60" s="5">
+        <v>-65.88</v>
+      </c>
+      <c r="E60" s="6">
+        <v>-25.67</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="7">
-        <v>5.47</v>
-      </c>
-      <c r="D19" s="7">
-        <v>3.24</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-2.23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B61" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="5">
+        <v>18.25</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-55.39</v>
+      </c>
+      <c r="E61" s="6">
+        <v>-73.64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="7">
-        <v>3.66</v>
-      </c>
-      <c r="D20" s="7">
-        <v>0.76</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-2.9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B62" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="5">
+        <v>-31.38</v>
+      </c>
+      <c r="D62" s="5">
+        <v>-11.8</v>
+      </c>
+      <c r="E62" s="7">
+        <v>19.58</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="7">
-        <v>0.13</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-0.03</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B63" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="5">
+        <v>-59.72</v>
+      </c>
+      <c r="D63" s="5">
+        <v>35.54</v>
+      </c>
+      <c r="E63" s="7">
+        <v>95.26000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7">
-        <v>0.21</v>
-      </c>
-      <c r="D22" s="7">
-        <v>1.59</v>
-      </c>
-      <c r="E22" s="9">
-        <v>1.38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>18.02</v>
-      </c>
-      <c r="D23" s="7">
-        <v>19.82</v>
-      </c>
-      <c r="E23" s="9">
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="7">
-        <v>8.81</v>
-      </c>
-      <c r="D24" s="7">
-        <v>13.5</v>
-      </c>
-      <c r="E24" s="9">
-        <v>4.69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-1.67</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-4.35</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-2.68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-20.19</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-20.44</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="7">
-        <v>-31.62</v>
-      </c>
-      <c r="D27" s="7">
-        <v>-33</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-1.38</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="7">
-        <v>9.07</v>
-      </c>
-      <c r="D28" s="7">
-        <v>13.39</v>
-      </c>
-      <c r="E28" s="9">
-        <v>4.32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-13.01</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-10.68</v>
-      </c>
-      <c r="E29" s="9">
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7">
-        <v>1.76</v>
-      </c>
-      <c r="D30" s="7">
-        <v>4.75</v>
-      </c>
-      <c r="E30" s="9">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-11.28</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-6.52</v>
-      </c>
-      <c r="E31" s="9">
-        <v>4.76</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-11.35</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-12.77</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-12.7</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-13.55</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="7">
-        <v>-8.9</v>
-      </c>
-      <c r="D34" s="7">
-        <v>-7.57</v>
-      </c>
-      <c r="E34" s="9">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="7">
-        <v>5.35</v>
-      </c>
-      <c r="D35" s="7">
-        <v>3.63</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-1.72</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C36" s="7">
-        <v>-0.68</v>
-      </c>
-      <c r="D36" s="7">
-        <v>3.8</v>
-      </c>
-      <c r="E36" s="9">
-        <v>4.48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="7">
-        <v>-14.82</v>
-      </c>
-      <c r="D37" s="7">
-        <v>-14.38</v>
-      </c>
-      <c r="E37" s="9">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="7">
-        <v>-16.23</v>
-      </c>
-      <c r="D38" s="7">
-        <v>-13.36</v>
-      </c>
-      <c r="E38" s="9">
-        <v>2.87</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="7">
-        <v>-18.25</v>
-      </c>
-      <c r="D39" s="7">
-        <v>-18.85</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="7">
-        <v>-26.41</v>
-      </c>
-      <c r="D40" s="7">
-        <v>-26.69</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="7">
-        <v>-35.59</v>
-      </c>
-      <c r="D41" s="7">
-        <v>-36.3</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="7">
-        <v>-25.17</v>
-      </c>
-      <c r="D42" s="7">
-        <v>-23.86</v>
-      </c>
-      <c r="E42" s="9">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="7">
-        <v>-15.15</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-13.58</v>
-      </c>
-      <c r="E43" s="9">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="7">
-        <v>1104.4</v>
-      </c>
-      <c r="D44" s="7">
-        <v>1110.1</v>
-      </c>
-      <c r="E44" s="9">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="7">
-        <v>818</v>
-      </c>
-      <c r="D45" s="7">
-        <v>846</v>
-      </c>
-      <c r="E45" s="9">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="7">
-        <v>1586</v>
-      </c>
-      <c r="D46" s="7">
-        <v>1574.4</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-11.6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="7">
-        <v>1765.3</v>
-      </c>
-      <c r="D47" s="7">
-        <v>1758.6</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-6.7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="7">
-        <v>701.95</v>
-      </c>
-      <c r="D48" s="7">
-        <v>694.15</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-7.8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C49" s="7">
-        <v>2585.3</v>
-      </c>
-      <c r="D49" s="7">
-        <v>2630.4</v>
-      </c>
-      <c r="E49" s="9">
-        <v>45.1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C50" s="7">
-        <v>7728.5</v>
-      </c>
-      <c r="D50" s="7">
-        <v>7871.5</v>
-      </c>
-      <c r="E50" s="9">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="7">
-        <v>38.55</v>
-      </c>
-      <c r="D51" s="7">
-        <v>39.56</v>
-      </c>
-      <c r="E51" s="9">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="7">
-        <v>36.94</v>
-      </c>
-      <c r="D52" s="7">
-        <v>44.24</v>
-      </c>
-      <c r="E52" s="9">
-        <v>7.3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="7">
-        <v>38.38</v>
-      </c>
-      <c r="D53" s="7">
-        <v>37.18</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-1.2</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="7">
-        <v>41.41</v>
-      </c>
-      <c r="D54" s="7">
-        <v>40.7</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-0.71</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="7">
-        <v>46.4</v>
-      </c>
-      <c r="D55" s="7">
-        <v>43.82</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="7">
-        <v>29.19</v>
-      </c>
-      <c r="D56" s="7">
-        <v>33.79</v>
-      </c>
-      <c r="E56" s="9">
-        <v>4.6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="7">
-        <v>37.34</v>
-      </c>
-      <c r="D57" s="7">
-        <v>42.57</v>
-      </c>
-      <c r="E57" s="9">
-        <v>5.23</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B58" s="6" t="s">
+      <c r="B64" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C58" s="7">
-        <v>-69.92</v>
-      </c>
-      <c r="D58" s="7">
-        <v>-73.7</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-3.78</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="7">
-        <v>125.13</v>
-      </c>
-      <c r="D59" s="7">
-        <v>245.39</v>
-      </c>
-      <c r="E59" s="9">
-        <v>120.26</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="7">
-        <v>1.99</v>
-      </c>
-      <c r="D60" s="7">
-        <v>-40.21</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-42.2</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="7">
-        <v>-21.67</v>
-      </c>
-      <c r="D61" s="7">
-        <v>18.25</v>
-      </c>
-      <c r="E61" s="9">
-        <v>39.92</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="7">
-        <v>20.84</v>
-      </c>
-      <c r="D62" s="7">
-        <v>-31.38</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-52.22</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7">
-        <v>38.48</v>
-      </c>
-      <c r="D63" s="7">
-        <v>-59.72</v>
-      </c>
-      <c r="E63" s="8">
-        <v>-98.2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="7">
-        <v>-73.44</v>
-      </c>
-      <c r="D64" s="7">
+      <c r="C64" s="5">
         <v>-51.33</v>
       </c>
-      <c r="E64" s="9">
-        <v>22.11</v>
+      <c r="D64" s="5">
+        <v>-53.79</v>
+      </c>
+      <c r="E64" s="6">
+        <v>-2.46</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2951,61 +2872,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>74</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="12">
-        <v>56.8</v>
-      </c>
-      <c r="C2" s="13">
+      <c r="B2" s="10">
+        <v>55.64</v>
+      </c>
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="12">
-        <v>40.3</v>
-      </c>
-      <c r="E2" s="12">
-        <v>60</v>
-      </c>
-      <c r="F2" s="12">
-        <v>-5.9</v>
-      </c>
-      <c r="G2" s="12">
-        <v>-4</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="D2" s="10">
+        <v>38.2</v>
+      </c>
+      <c r="E2" s="10">
+        <v>57.1</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-7.9</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-6</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="12">
-        <v>10</v>
+      <c r="I2" s="10">
+        <v>14.3</v>
       </c>
     </row>
   </sheetData>
@@ -3106,49 +3027,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="15">
-        <v>0.4722</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.2407</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.2158</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.1643</v>
-      </c>
-      <c r="E2" s="15">
-        <v>0.1286</v>
-      </c>
-      <c r="F2" s="15">
-        <v>0.0809</v>
-      </c>
-      <c r="G2" s="15">
-        <v>0.04650000000000001</v>
+      <c r="A2" s="13">
+        <v>0.4603</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2249</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.2084</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1702</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.1264</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.0842</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.0479</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -893,10 +893,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1089</v>
+        <v>1059.9</v>
       </c>
       <c r="D2">
-        <v>-1.9</v>
+        <v>-2.67</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -905,46 +905,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-16</v>
+        <v>-18.25</v>
       </c>
       <c r="H2">
-        <v>45.52</v>
+        <v>41.63</v>
       </c>
       <c r="I2">
-        <v>-8.960000000000001</v>
+        <v>-10.53</v>
       </c>
       <c r="J2">
-        <v>0.5</v>
+        <v>-5.74</v>
       </c>
       <c r="K2">
-        <v>0.17</v>
+        <v>-2.24</v>
       </c>
       <c r="L2">
-        <v>19.35</v>
+        <v>16.82</v>
       </c>
       <c r="M2">
-        <v>4.79</v>
+        <v>4.03</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P2">
-        <v>1131.84</v>
+        <v>1106.88</v>
       </c>
       <c r="Q2">
-        <v>1211.57</v>
+        <v>1205.62</v>
       </c>
       <c r="R2">
-        <v>1150.99</v>
+        <v>1150.25</v>
       </c>
       <c r="S2">
-        <v>994.78</v>
+        <v>995.8</v>
       </c>
       <c r="T2">
-        <v>9.470000000000001</v>
+        <v>6.44</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -959,43 +959,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>37.11</v>
+        <v>33.99</v>
       </c>
       <c r="Z2">
-        <v>-6.04</v>
+        <v>-13.99</v>
       </c>
       <c r="AA2">
-        <v>14.78</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="AB2">
-        <v>-20.82</v>
+        <v>-23.02</v>
       </c>
       <c r="AC2">
         <v>1.34</v>
       </c>
       <c r="AD2">
-        <v>0.9</v>
+        <v>1.34</v>
       </c>
       <c r="AE2">
-        <v>48.31</v>
+        <v>48.25</v>
       </c>
       <c r="AF2">
-        <v>-67.01000000000001</v>
+        <v>-76.81999999999999</v>
       </c>
       <c r="AG2">
-        <v>1330.78</v>
+        <v>1342.3</v>
       </c>
       <c r="AH2">
-        <v>1092.37</v>
+        <v>1068.95</v>
       </c>
       <c r="AI2">
-        <v>1242.27</v>
+        <v>1209</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>35.87</v>
+        <v>39.45</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,10 +1006,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>855</v>
+        <v>821</v>
       </c>
       <c r="D3">
-        <v>1.06</v>
+        <v>-3.98</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1018,46 +1018,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-12.44</v>
+        <v>-15.92</v>
       </c>
       <c r="H3">
-        <v>61.48</v>
+        <v>55.06</v>
       </c>
       <c r="I3">
-        <v>-1.44</v>
+        <v>-3.86</v>
       </c>
       <c r="J3">
-        <v>-2.84</v>
+        <v>-7.96</v>
       </c>
       <c r="K3">
-        <v>-6.3</v>
+        <v>-10.26</v>
       </c>
       <c r="L3">
-        <v>14.87</v>
+        <v>8.65</v>
       </c>
       <c r="M3">
-        <v>46.03</v>
+        <v>43.23</v>
       </c>
       <c r="N3">
         <v>85</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P3">
-        <v>847.2</v>
+        <v>840.6</v>
       </c>
       <c r="Q3">
-        <v>872</v>
+        <v>867.55</v>
       </c>
       <c r="R3">
-        <v>881.08</v>
+        <v>879.92</v>
       </c>
       <c r="S3">
-        <v>805.97</v>
+        <v>806.84</v>
       </c>
       <c r="T3">
-        <v>6.08</v>
+        <v>1.75</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1072,34 +1072,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>46.39</v>
+        <v>40.1</v>
       </c>
       <c r="Z3">
-        <v>-10.52</v>
+        <v>-12.82</v>
       </c>
       <c r="AA3">
-        <v>-7.3</v>
+        <v>-8.4</v>
       </c>
       <c r="AB3">
-        <v>-3.22</v>
+        <v>-4.42</v>
       </c>
       <c r="AC3">
-        <v>27.47</v>
+        <v>32.65</v>
       </c>
       <c r="AD3">
-        <v>21.38</v>
+        <v>27.36</v>
       </c>
       <c r="AE3">
-        <v>27.95</v>
+        <v>29.48</v>
       </c>
       <c r="AF3">
-        <v>55.55</v>
+        <v>-1.36</v>
       </c>
       <c r="AG3">
-        <v>918.9299999999999</v>
+        <v>916.16</v>
       </c>
       <c r="AH3">
-        <v>825.0599999999999</v>
+        <v>818.9400000000001</v>
       </c>
       <c r="AI3">
         <v>910.9299999999999</v>
@@ -1108,7 +1108,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>23.33</v>
+        <v>25.18</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,10 +1119,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1553</v>
+        <v>1529.9</v>
       </c>
       <c r="D4">
-        <v>-1.36</v>
+        <v>-1.49</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1131,46 +1131,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-19.95</v>
+        <v>-21.14</v>
       </c>
       <c r="H4">
-        <v>14.64</v>
+        <v>12.93</v>
       </c>
       <c r="I4">
-        <v>-1.75</v>
+        <v>-5.6</v>
       </c>
       <c r="J4">
-        <v>-11.99</v>
+        <v>-15.01</v>
       </c>
       <c r="K4">
-        <v>-12.89</v>
+        <v>-13.01</v>
       </c>
       <c r="L4">
-        <v>-5.56</v>
+        <v>-9.85</v>
       </c>
       <c r="M4">
-        <v>20.84</v>
+        <v>20.24</v>
       </c>
       <c r="N4">
         <v>43</v>
       </c>
       <c r="O4">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="P4">
-        <v>1579.42</v>
+        <v>1561.26</v>
       </c>
       <c r="Q4">
-        <v>1624.67</v>
+        <v>1612.97</v>
       </c>
       <c r="R4">
-        <v>1763.23</v>
+        <v>1756.5</v>
       </c>
       <c r="S4">
-        <v>1675.51</v>
+        <v>1674.65</v>
       </c>
       <c r="T4">
-        <v>-7.31</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1185,43 +1185,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>35</v>
+        <v>32.77</v>
       </c>
       <c r="Z4">
-        <v>-56.76</v>
+        <v>-57.71</v>
       </c>
       <c r="AA4">
-        <v>-58.7</v>
+        <v>-58.5</v>
       </c>
       <c r="AB4">
-        <v>1.94</v>
+        <v>0.79</v>
       </c>
       <c r="AC4">
-        <v>79.06999999999999</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="AD4">
-        <v>79.5</v>
+        <v>75.11</v>
       </c>
       <c r="AE4">
-        <v>45.63</v>
+        <v>46.42</v>
       </c>
       <c r="AF4">
-        <v>-65.88</v>
+        <v>40.55</v>
       </c>
       <c r="AG4">
-        <v>1765.01</v>
+        <v>1743.05</v>
       </c>
       <c r="AH4">
-        <v>1484.34</v>
+        <v>1482.89</v>
       </c>
       <c r="AI4">
-        <v>1692.02</v>
+        <v>1676.2</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>50.07</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1232,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1771.1</v>
+        <v>1791.7</v>
       </c>
       <c r="D5">
-        <v>0.71</v>
+        <v>1.16</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1244,46 +1244,46 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-26.17</v>
+        <v>-25.31</v>
       </c>
       <c r="H5">
-        <v>5.82</v>
+        <v>7.05</v>
       </c>
       <c r="I5">
-        <v>4.8</v>
+        <v>3.98</v>
       </c>
       <c r="J5">
-        <v>-8.220000000000001</v>
+        <v>-10.39</v>
       </c>
       <c r="K5">
-        <v>-12.34</v>
+        <v>-12.78</v>
       </c>
       <c r="L5">
-        <v>-18.33</v>
+        <v>-18.17</v>
       </c>
       <c r="M5">
-        <v>17.02</v>
+        <v>17.59</v>
       </c>
       <c r="N5">
         <v>29</v>
       </c>
       <c r="O5">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="P5">
-        <v>1753.04</v>
+        <v>1766.74</v>
       </c>
       <c r="Q5">
-        <v>1806.47</v>
+        <v>1799.01</v>
       </c>
       <c r="R5">
-        <v>1913.35</v>
+        <v>1907.8</v>
       </c>
       <c r="S5">
-        <v>2025.56</v>
+        <v>2023.23</v>
       </c>
       <c r="T5">
-        <v>-12.56</v>
+        <v>-11.44</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1298,34 +1298,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>42.68</v>
+        <v>45.89</v>
       </c>
       <c r="Z5">
-        <v>-52.67</v>
+        <v>-46.71</v>
       </c>
       <c r="AA5">
-        <v>-57.13</v>
+        <v>-55.05</v>
       </c>
       <c r="AB5">
-        <v>4.46</v>
+        <v>8.33</v>
       </c>
       <c r="AC5">
-        <v>86.68000000000001</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="AD5">
-        <v>70</v>
+        <v>85.44</v>
       </c>
       <c r="AE5">
-        <v>53.88</v>
+        <v>57.46</v>
       </c>
       <c r="AF5">
-        <v>-55.39</v>
+        <v>-19.04</v>
       </c>
       <c r="AG5">
-        <v>1999.72</v>
+        <v>1981.65</v>
       </c>
       <c r="AH5">
-        <v>1613.22</v>
+        <v>1616.38</v>
       </c>
       <c r="AI5">
         <v>1853.75</v>
@@ -1334,7 +1334,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>33.83</v>
+        <v>32.54</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,37 +1345,37 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>674.05</v>
+        <v>657.1</v>
       </c>
       <c r="D6">
-        <v>-2.9</v>
+        <v>-2.51</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
       </c>
       <c r="F6">
-        <v>674.05</v>
+        <v>657.1</v>
       </c>
       <c r="G6">
-        <v>-38.15</v>
+        <v>-39.7</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-3.62</v>
+        <v>-7.04</v>
       </c>
       <c r="J6">
-        <v>-4.13</v>
+        <v>-6.22</v>
       </c>
       <c r="K6">
-        <v>-11.57</v>
+        <v>-14.42</v>
       </c>
       <c r="L6">
-        <v>-35.12</v>
+        <v>-36.48</v>
       </c>
       <c r="M6">
-        <v>8.42</v>
+        <v>7.6</v>
       </c>
       <c r="N6">
         <v>15</v>
@@ -1384,19 +1384,19 @@
         <v>20</v>
       </c>
       <c r="P6">
-        <v>693.72</v>
+        <v>683.77</v>
       </c>
       <c r="Q6">
-        <v>694</v>
+        <v>691.8099999999999</v>
       </c>
       <c r="R6">
-        <v>742.1900000000001</v>
+        <v>739.23</v>
       </c>
       <c r="S6">
-        <v>804.45</v>
+        <v>802.5599999999999</v>
       </c>
       <c r="T6">
-        <v>-16.21</v>
+        <v>-18.12</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1411,43 +1411,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>37.97</v>
+        <v>33.87</v>
       </c>
       <c r="Z6">
-        <v>-13.21</v>
+        <v>-15.14</v>
       </c>
       <c r="AA6">
-        <v>-15.51</v>
+        <v>-15.44</v>
       </c>
       <c r="AB6">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="AC6">
-        <v>76.52</v>
+        <v>54.88</v>
       </c>
       <c r="AD6">
-        <v>83.66</v>
+        <v>71.88</v>
       </c>
       <c r="AE6">
-        <v>19.42</v>
+        <v>19.82</v>
       </c>
       <c r="AF6">
-        <v>-11.8</v>
+        <v>33.45</v>
       </c>
       <c r="AG6">
-        <v>713.88</v>
+        <v>717.34</v>
       </c>
       <c r="AH6">
-        <v>674.12</v>
+        <v>666.28</v>
       </c>
       <c r="AI6">
-        <v>738.76</v>
+        <v>723.89</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>23.01</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,10 +1458,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2555.2</v>
+        <v>2435.2</v>
       </c>
       <c r="D7">
-        <v>-2.86</v>
+        <v>-4.7</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1470,46 +1470,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-26.04</v>
+        <v>-29.51</v>
       </c>
       <c r="H7">
-        <v>35.09</v>
+        <v>28.75</v>
       </c>
       <c r="I7">
-        <v>-4.23</v>
+        <v>-7.48</v>
       </c>
       <c r="J7">
-        <v>-16.21</v>
+        <v>-20.26</v>
       </c>
       <c r="K7">
-        <v>-0.46</v>
+        <v>-7.27</v>
       </c>
       <c r="L7">
-        <v>11.36</v>
+        <v>7.38</v>
       </c>
       <c r="M7">
-        <v>22.49</v>
+        <v>23.38</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P7">
-        <v>2614.52</v>
+        <v>2575.12</v>
       </c>
       <c r="Q7">
-        <v>2801.84</v>
+        <v>2771.43</v>
       </c>
       <c r="R7">
-        <v>3006.02</v>
+        <v>3000.85</v>
       </c>
       <c r="S7">
-        <v>2527.46</v>
+        <v>2528.47</v>
       </c>
       <c r="T7">
-        <v>1.1</v>
+        <v>-3.69</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1521,46 +1521,46 @@
         <v>46</v>
       </c>
       <c r="X7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>30.26</v>
+        <v>25.66</v>
       </c>
       <c r="Z7">
-        <v>-123.29</v>
+        <v>-134.55</v>
       </c>
       <c r="AA7">
-        <v>-102.9</v>
+        <v>-109.23</v>
       </c>
       <c r="AB7">
-        <v>-20.39</v>
+        <v>-25.32</v>
       </c>
       <c r="AC7">
-        <v>53.2</v>
+        <v>50.81</v>
       </c>
       <c r="AD7">
-        <v>47.83</v>
+        <v>51.96</v>
       </c>
       <c r="AE7">
-        <v>118.63</v>
+        <v>120.95</v>
       </c>
       <c r="AF7">
-        <v>35.54</v>
+        <v>38.98</v>
       </c>
       <c r="AG7">
-        <v>3148.14</v>
+        <v>3134.81</v>
       </c>
       <c r="AH7">
-        <v>2455.54</v>
+        <v>2408.05</v>
       </c>
       <c r="AI7">
-        <v>2961.01</v>
+        <v>2862.5</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>62.49</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1571,10 +1571,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7689</v>
+        <v>7406</v>
       </c>
       <c r="D8">
-        <v>-2.32</v>
+        <v>-3.68</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1583,46 +1583,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-15.59</v>
+        <v>-18.69</v>
       </c>
       <c r="H8">
-        <v>29.78</v>
+        <v>25.01</v>
       </c>
       <c r="I8">
-        <v>0.05</v>
+        <v>-4.94</v>
       </c>
       <c r="J8">
-        <v>-12.28</v>
+        <v>-15.53</v>
       </c>
       <c r="K8">
-        <v>1.45</v>
+        <v>-2.06</v>
       </c>
       <c r="L8">
-        <v>-11.8</v>
+        <v>-15.28</v>
       </c>
       <c r="M8">
-        <v>12.64</v>
+        <v>12.12</v>
       </c>
       <c r="N8">
         <v>57</v>
       </c>
       <c r="O8">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="P8">
-        <v>7795.4</v>
+        <v>7718.4</v>
       </c>
       <c r="Q8">
-        <v>8133.32</v>
+        <v>8071.6</v>
       </c>
       <c r="R8">
-        <v>8206.030000000001</v>
+        <v>8191.13</v>
       </c>
       <c r="S8">
-        <v>7431.87</v>
+        <v>7430.03</v>
       </c>
       <c r="T8">
-        <v>3.46</v>
+        <v>-0.32</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1634,37 +1634,37 @@
         <v>46</v>
       </c>
       <c r="X8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>38.19</v>
+        <v>32.59</v>
       </c>
       <c r="Z8">
-        <v>-166.83</v>
+        <v>-194.32</v>
       </c>
       <c r="AA8">
-        <v>-119.93</v>
+        <v>-134.81</v>
       </c>
       <c r="AB8">
-        <v>-46.9</v>
+        <v>-59.51</v>
       </c>
       <c r="AC8">
-        <v>34.72</v>
+        <v>28.7</v>
       </c>
       <c r="AD8">
-        <v>31.3</v>
+        <v>33.04</v>
       </c>
       <c r="AE8">
-        <v>266.1</v>
+        <v>301.7</v>
       </c>
       <c r="AF8">
-        <v>-53.79</v>
+        <v>681.5</v>
       </c>
       <c r="AG8">
-        <v>8873.440000000001</v>
+        <v>8839.030000000001</v>
       </c>
       <c r="AH8">
-        <v>7393.21</v>
+        <v>7304.17</v>
       </c>
       <c r="AI8">
         <v>8562.809999999999</v>
@@ -1673,7 +1673,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>29.67</v>
+        <v>32.29</v>
       </c>
     </row>
   </sheetData>
@@ -1814,7 +1814,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1871,13 +1871,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>5.56</v>
+        <v>0.5</v>
       </c>
       <c r="D7" s="5">
-        <v>0.5</v>
+        <v>-5.74</v>
       </c>
       <c r="E7" s="6">
-        <v>-5.06</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1888,13 +1888,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-0.65</v>
+        <v>-2.84</v>
       </c>
       <c r="D8" s="5">
-        <v>-2.84</v>
+        <v>-7.96</v>
       </c>
       <c r="E8" s="6">
-        <v>-2.19</v>
+        <v>-5.12</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1905,13 +1905,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-10.83</v>
+        <v>-11.99</v>
       </c>
       <c r="D9" s="5">
-        <v>-11.99</v>
+        <v>-15.01</v>
       </c>
       <c r="E9" s="6">
-        <v>-1.16</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1922,13 +1922,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-9.25</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="D10" s="5">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1.03</v>
+        <v>-10.39</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1939,13 +1939,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-1.27</v>
+        <v>-4.13</v>
       </c>
       <c r="D11" s="5">
-        <v>-4.13</v>
+        <v>-6.22</v>
       </c>
       <c r="E11" s="6">
-        <v>-2.86</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1956,13 +1956,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="5">
-        <v>-15.54</v>
+        <v>-16.21</v>
       </c>
       <c r="D12" s="5">
-        <v>-16.21</v>
+        <v>-20.26</v>
       </c>
       <c r="E12" s="6">
-        <v>-0.67</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1973,13 +1973,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="5">
-        <v>-9.140000000000001</v>
+        <v>-12.28</v>
       </c>
       <c r="D13" s="5">
-        <v>-12.28</v>
+        <v>-15.53</v>
       </c>
       <c r="E13" s="6">
-        <v>-3.14</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1990,13 +1990,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-7.69</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="D14" s="5">
-        <v>-8.960000000000001</v>
+        <v>-10.53</v>
       </c>
       <c r="E14" s="6">
-        <v>-1.27</v>
+        <v>-1.57</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2007,13 +2007,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-1.12</v>
+        <v>-1.44</v>
       </c>
       <c r="D15" s="5">
-        <v>-1.44</v>
+        <v>-3.86</v>
       </c>
       <c r="E15" s="6">
-        <v>-0.32</v>
+        <v>-2.42</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2024,13 +2024,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>-0.83</v>
+        <v>-1.75</v>
       </c>
       <c r="D16" s="5">
-        <v>-1.75</v>
+        <v>-5.6</v>
       </c>
       <c r="E16" s="6">
-        <v>-0.92</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2041,13 +2041,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="5">
-        <v>3.24</v>
+        <v>4.8</v>
       </c>
       <c r="D17" s="5">
-        <v>4.8</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.56</v>
+        <v>3.98</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2058,13 +2058,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="5">
-        <v>0.76</v>
+        <v>-3.62</v>
       </c>
       <c r="D18" s="5">
-        <v>-3.62</v>
+        <v>-7.04</v>
       </c>
       <c r="E18" s="6">
-        <v>-4.38</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2075,13 +2075,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="5">
-        <v>-0.03</v>
+        <v>-4.23</v>
       </c>
       <c r="D19" s="5">
-        <v>-4.23</v>
+        <v>-7.48</v>
       </c>
       <c r="E19" s="6">
-        <v>-4.2</v>
+        <v>-3.25</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2092,13 +2092,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="5">
-        <v>1.59</v>
+        <v>0.05</v>
       </c>
       <c r="D20" s="5">
-        <v>0.05</v>
+        <v>-4.94</v>
       </c>
       <c r="E20" s="6">
-        <v>-1.54</v>
+        <v>-4.99</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2109,13 +2109,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>19.82</v>
+        <v>19.35</v>
       </c>
       <c r="D21" s="5">
-        <v>19.35</v>
+        <v>16.82</v>
       </c>
       <c r="E21" s="6">
-        <v>-0.47</v>
+        <v>-2.53</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2126,13 +2126,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="5">
-        <v>13.5</v>
+        <v>14.87</v>
       </c>
       <c r="D22" s="5">
-        <v>14.87</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.37</v>
+        <v>8.65</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-6.22</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2143,13 +2143,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="5">
-        <v>-4.35</v>
+        <v>-5.56</v>
       </c>
       <c r="D23" s="5">
-        <v>-5.56</v>
+        <v>-9.85</v>
       </c>
       <c r="E23" s="6">
-        <v>-1.21</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2160,13 +2160,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="5">
-        <v>-20.44</v>
+        <v>-18.33</v>
       </c>
       <c r="D24" s="5">
-        <v>-18.33</v>
+        <v>-18.17</v>
       </c>
       <c r="E24" s="7">
-        <v>2.11</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2177,13 +2177,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="5">
-        <v>-33</v>
+        <v>-35.12</v>
       </c>
       <c r="D25" s="5">
-        <v>-35.12</v>
+        <v>-36.48</v>
       </c>
       <c r="E25" s="6">
-        <v>-2.12</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2194,13 +2194,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="5">
-        <v>13.39</v>
+        <v>11.36</v>
       </c>
       <c r="D26" s="5">
-        <v>11.36</v>
+        <v>7.38</v>
       </c>
       <c r="E26" s="6">
-        <v>-2.03</v>
+        <v>-3.98</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2211,13 +2211,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="5">
-        <v>-10.68</v>
+        <v>-11.8</v>
       </c>
       <c r="D27" s="5">
-        <v>-11.8</v>
+        <v>-15.28</v>
       </c>
       <c r="E27" s="6">
-        <v>-1.12</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2228,13 +2228,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="5">
-        <v>4.75</v>
+        <v>0.17</v>
       </c>
       <c r="D28" s="5">
-        <v>0.17</v>
+        <v>-2.24</v>
       </c>
       <c r="E28" s="6">
-        <v>-4.58</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2245,13 +2245,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="5">
-        <v>-6.52</v>
+        <v>-6.3</v>
       </c>
       <c r="D29" s="5">
-        <v>-6.3</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.22</v>
+        <v>-10.26</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-3.96</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2262,10 +2262,10 @@
         <v>10</v>
       </c>
       <c r="C30" s="5">
-        <v>-12.77</v>
+        <v>-12.89</v>
       </c>
       <c r="D30" s="5">
-        <v>-12.89</v>
+        <v>-13.01</v>
       </c>
       <c r="E30" s="6">
         <v>-0.12</v>
@@ -2279,13 +2279,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="5">
-        <v>-13.55</v>
+        <v>-12.34</v>
       </c>
       <c r="D31" s="5">
-        <v>-12.34</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.21</v>
+        <v>-12.78</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2296,13 +2296,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="5">
-        <v>-7.57</v>
+        <v>-11.57</v>
       </c>
       <c r="D32" s="5">
-        <v>-11.57</v>
+        <v>-14.42</v>
       </c>
       <c r="E32" s="6">
-        <v>-4</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2313,13 +2313,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="5">
-        <v>3.63</v>
+        <v>-0.46</v>
       </c>
       <c r="D33" s="5">
-        <v>-0.46</v>
+        <v>-7.27</v>
       </c>
       <c r="E33" s="6">
-        <v>-4.09</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2330,13 +2330,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="5">
-        <v>3.8</v>
+        <v>1.45</v>
       </c>
       <c r="D34" s="5">
-        <v>1.45</v>
+        <v>-2.06</v>
       </c>
       <c r="E34" s="6">
-        <v>-2.35</v>
+        <v>-3.51</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2347,13 +2347,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="5">
-        <v>-14.38</v>
+        <v>-16</v>
       </c>
       <c r="D35" s="5">
-        <v>-16</v>
+        <v>-18.25</v>
       </c>
       <c r="E35" s="6">
-        <v>-1.62</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2364,13 +2364,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="5">
-        <v>-13.36</v>
+        <v>-12.44</v>
       </c>
       <c r="D36" s="5">
-        <v>-12.44</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.92</v>
+        <v>-15.92</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-3.48</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2381,13 +2381,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="5">
-        <v>-18.85</v>
+        <v>-19.95</v>
       </c>
       <c r="D37" s="5">
-        <v>-19.95</v>
+        <v>-21.14</v>
       </c>
       <c r="E37" s="6">
-        <v>-1.1</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2398,13 +2398,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="5">
-        <v>-26.69</v>
+        <v>-26.17</v>
       </c>
       <c r="D38" s="5">
-        <v>-26.17</v>
+        <v>-25.31</v>
       </c>
       <c r="E38" s="7">
-        <v>0.52</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2415,13 +2415,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="5">
-        <v>-36.3</v>
+        <v>-38.15</v>
       </c>
       <c r="D39" s="5">
-        <v>-38.15</v>
+        <v>-39.7</v>
       </c>
       <c r="E39" s="6">
-        <v>-1.85</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2432,13 +2432,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="5">
-        <v>-23.86</v>
+        <v>-26.04</v>
       </c>
       <c r="D40" s="5">
-        <v>-26.04</v>
+        <v>-29.51</v>
       </c>
       <c r="E40" s="6">
-        <v>-2.18</v>
+        <v>-3.47</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2449,13 +2449,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="5">
-        <v>-13.58</v>
+        <v>-15.59</v>
       </c>
       <c r="D41" s="5">
-        <v>-15.59</v>
+        <v>-18.69</v>
       </c>
       <c r="E41" s="6">
-        <v>-2.01</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2466,13 +2466,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="5">
-        <v>1110.1</v>
+        <v>1089</v>
       </c>
       <c r="D42" s="5">
-        <v>1089</v>
+        <v>1059.9</v>
       </c>
       <c r="E42" s="6">
-        <v>-21.1</v>
+        <v>-29.1</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2483,13 +2483,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="5">
-        <v>846</v>
+        <v>855</v>
       </c>
       <c r="D43" s="5">
-        <v>855</v>
-      </c>
-      <c r="E43" s="7">
-        <v>9</v>
+        <v>821</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-34</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2500,13 +2500,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="5">
-        <v>1574.4</v>
+        <v>1553</v>
       </c>
       <c r="D44" s="5">
-        <v>1553</v>
+        <v>1529.9</v>
       </c>
       <c r="E44" s="6">
-        <v>-21.4</v>
+        <v>-23.1</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2517,13 +2517,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="5">
-        <v>1758.6</v>
+        <v>1771.1</v>
       </c>
       <c r="D45" s="5">
-        <v>1771.1</v>
+        <v>1791.7</v>
       </c>
       <c r="E45" s="7">
-        <v>12.5</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2534,13 +2534,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="5">
-        <v>694.15</v>
+        <v>674.05</v>
       </c>
       <c r="D46" s="5">
-        <v>674.05</v>
+        <v>657.1</v>
       </c>
       <c r="E46" s="6">
-        <v>-20.1</v>
+        <v>-16.95</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2551,13 +2551,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="5">
-        <v>2630.4</v>
+        <v>2555.2</v>
       </c>
       <c r="D47" s="5">
-        <v>2555.2</v>
+        <v>2435.2</v>
       </c>
       <c r="E47" s="6">
-        <v>-75.2</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2568,285 +2568,251 @@
         <v>2</v>
       </c>
       <c r="C48" s="5">
-        <v>7871.5</v>
+        <v>7689</v>
       </c>
       <c r="D48" s="5">
-        <v>7689</v>
+        <v>7406</v>
       </c>
       <c r="E48" s="6">
-        <v>-182.5</v>
+        <v>-283</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C49" s="5">
-        <v>71</v>
+        <v>37.11</v>
       </c>
       <c r="D49" s="5">
-        <v>85</v>
-      </c>
-      <c r="E49" s="7">
-        <v>14</v>
+        <v>33.99</v>
+      </c>
+      <c r="E49" s="6">
+        <v>-3.12</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C50" s="5">
-        <v>85</v>
+        <v>46.39</v>
       </c>
       <c r="D50" s="5">
-        <v>71</v>
+        <v>40.1</v>
       </c>
       <c r="E50" s="6">
-        <v>-14</v>
+        <v>-6.29</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C51" s="5">
-        <v>39.56</v>
+        <v>35</v>
       </c>
       <c r="D51" s="5">
-        <v>37.11</v>
+        <v>32.77</v>
       </c>
       <c r="E51" s="6">
-        <v>-2.45</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C52" s="5">
-        <v>44.24</v>
+        <v>42.68</v>
       </c>
       <c r="D52" s="5">
-        <v>46.39</v>
+        <v>45.89</v>
       </c>
       <c r="E52" s="7">
-        <v>2.15</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C53" s="5">
-        <v>37.18</v>
+        <v>37.97</v>
       </c>
       <c r="D53" s="5">
-        <v>35</v>
+        <v>33.87</v>
       </c>
       <c r="E53" s="6">
-        <v>-2.18</v>
+        <v>-4.1</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="5">
-        <v>40.7</v>
+        <v>30.26</v>
       </c>
       <c r="D54" s="5">
-        <v>42.68</v>
-      </c>
-      <c r="E54" s="7">
-        <v>1.98</v>
+        <v>25.66</v>
+      </c>
+      <c r="E54" s="6">
+        <v>-4.6</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="5">
-        <v>43.82</v>
+        <v>38.19</v>
       </c>
       <c r="D55" s="5">
-        <v>37.97</v>
+        <v>32.59</v>
       </c>
       <c r="E55" s="6">
-        <v>-5.85</v>
+        <v>-5.6</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C56" s="5">
-        <v>33.79</v>
+        <v>-67.01000000000001</v>
       </c>
       <c r="D56" s="5">
-        <v>30.26</v>
+        <v>-76.81999999999999</v>
       </c>
       <c r="E56" s="6">
-        <v>-3.53</v>
+        <v>-9.81</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C57" s="5">
-        <v>42.57</v>
+        <v>55.55</v>
       </c>
       <c r="D57" s="5">
-        <v>38.19</v>
+        <v>-1.36</v>
       </c>
       <c r="E57" s="6">
-        <v>-4.38</v>
+        <v>-56.91</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C58" s="5">
-        <v>-73.7</v>
+        <v>-65.88</v>
       </c>
       <c r="D58" s="5">
-        <v>-67.01000000000001</v>
+        <v>40.55</v>
       </c>
       <c r="E58" s="7">
-        <v>6.69</v>
+        <v>106.43</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C59" s="5">
-        <v>245.39</v>
+        <v>-55.39</v>
       </c>
       <c r="D59" s="5">
-        <v>55.55</v>
-      </c>
-      <c r="E59" s="6">
-        <v>-189.84</v>
+        <v>-19.04</v>
+      </c>
+      <c r="E59" s="7">
+        <v>36.35</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C60" s="5">
-        <v>-40.21</v>
+        <v>-11.8</v>
       </c>
       <c r="D60" s="5">
-        <v>-65.88</v>
-      </c>
-      <c r="E60" s="6">
-        <v>-25.67</v>
+        <v>33.45</v>
+      </c>
+      <c r="E60" s="7">
+        <v>45.25</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="3" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="5">
-        <v>18.25</v>
+        <v>35.54</v>
       </c>
       <c r="D61" s="5">
-        <v>-55.39</v>
-      </c>
-      <c r="E61" s="6">
-        <v>-73.64</v>
+        <v>38.98</v>
+      </c>
+      <c r="E61" s="7">
+        <v>3.44</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="5">
-        <v>-31.38</v>
+        <v>-53.79</v>
       </c>
       <c r="D62" s="5">
-        <v>-11.8</v>
+        <v>681.5</v>
       </c>
       <c r="E62" s="7">
-        <v>19.58</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>-59.72</v>
-      </c>
-      <c r="D63" s="5">
-        <v>35.54</v>
-      </c>
-      <c r="E63" s="7">
-        <v>95.26000000000001</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>-51.33</v>
-      </c>
-      <c r="D64" s="5">
-        <v>-53.79</v>
-      </c>
-      <c r="E64" s="6">
-        <v>-2.46</v>
+        <v>735.29</v>
       </c>
     </row>
   </sheetData>
@@ -2905,22 +2871,22 @@
         <v>44</v>
       </c>
       <c r="B2" s="10">
-        <v>55.64</v>
+        <v>44.24</v>
       </c>
       <c r="C2" s="11">
         <v>7</v>
       </c>
       <c r="D2" s="10">
-        <v>38.2</v>
+        <v>35</v>
       </c>
       <c r="E2" s="10">
-        <v>57.1</v>
+        <v>28.6</v>
       </c>
       <c r="F2" s="10">
-        <v>-7.9</v>
+        <v>-11.6</v>
       </c>
       <c r="G2" s="10">
-        <v>-6</v>
+        <v>-8.9</v>
       </c>
       <c r="H2" s="10">
         <v>57</v>
@@ -3051,25 +3017,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="13">
-        <v>0.4603</v>
+        <v>0.4323</v>
       </c>
       <c r="B2" s="13">
-        <v>0.2249</v>
+        <v>0.2338</v>
       </c>
       <c r="C2" s="13">
-        <v>0.2084</v>
+        <v>0.2024</v>
       </c>
       <c r="D2" s="13">
-        <v>0.1702</v>
+        <v>0.1759</v>
       </c>
       <c r="E2" s="13">
-        <v>0.1264</v>
+        <v>0.1212</v>
       </c>
       <c r="F2" s="13">
-        <v>0.0842</v>
+        <v>0.076</v>
       </c>
       <c r="G2" s="13">
-        <v>0.0479</v>
+        <v>0.0403</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>25.7 → 31.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>25.7</t>
+  </si>
+  <si>
+    <t>31.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -255,14 +282,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,13 +322,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,17 +398,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -893,10 +921,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1059.9</v>
+        <v>1054.7</v>
       </c>
       <c r="D2">
-        <v>-2.67</v>
+        <v>-0.49</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -905,46 +933,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-18.25</v>
+        <v>-18.65</v>
       </c>
       <c r="H2">
-        <v>41.63</v>
+        <v>40.94</v>
       </c>
       <c r="I2">
-        <v>-10.53</v>
+        <v>-9.93</v>
       </c>
       <c r="J2">
-        <v>-5.74</v>
+        <v>-10.54</v>
       </c>
       <c r="K2">
-        <v>-2.24</v>
+        <v>-1.33</v>
       </c>
       <c r="L2">
-        <v>16.82</v>
+        <v>15.29</v>
       </c>
       <c r="M2">
-        <v>4.03</v>
+        <v>4.88</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="P2">
-        <v>1106.88</v>
+        <v>1083.62</v>
       </c>
       <c r="Q2">
-        <v>1205.62</v>
+        <v>1197.79</v>
       </c>
       <c r="R2">
-        <v>1150.25</v>
+        <v>1148.92</v>
       </c>
       <c r="S2">
-        <v>995.8</v>
+        <v>996.79</v>
       </c>
       <c r="T2">
-        <v>6.44</v>
+        <v>5.81</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -959,43 +987,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>33.99</v>
+        <v>33.45</v>
       </c>
       <c r="Z2">
-        <v>-13.99</v>
+        <v>-20.47</v>
       </c>
       <c r="AA2">
-        <v>9.029999999999999</v>
+        <v>3.13</v>
       </c>
       <c r="AB2">
-        <v>-23.02</v>
+        <v>-23.6</v>
       </c>
       <c r="AC2">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>1.34</v>
+        <v>0.9</v>
       </c>
       <c r="AE2">
-        <v>48.25</v>
+        <v>47.48</v>
       </c>
       <c r="AF2">
-        <v>-76.81999999999999</v>
+        <v>-73.2</v>
       </c>
       <c r="AG2">
-        <v>1342.3</v>
+        <v>1350.15</v>
       </c>
       <c r="AH2">
-        <v>1068.95</v>
+        <v>1045.44</v>
       </c>
       <c r="AI2">
-        <v>1209</v>
+        <v>1202.4</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>39.45</v>
+        <v>42.57</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,10 +1034,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>821</v>
+        <v>817.1</v>
       </c>
       <c r="D3">
-        <v>-3.98</v>
+        <v>-0.48</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1018,46 +1046,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-15.92</v>
+        <v>-16.32</v>
       </c>
       <c r="H3">
-        <v>55.06</v>
+        <v>54.32</v>
       </c>
       <c r="I3">
-        <v>-3.86</v>
+        <v>-5.32</v>
       </c>
       <c r="J3">
-        <v>-7.96</v>
+        <v>-10.21</v>
       </c>
       <c r="K3">
-        <v>-10.26</v>
+        <v>-10.49</v>
       </c>
       <c r="L3">
-        <v>8.65</v>
+        <v>7.67</v>
       </c>
       <c r="M3">
-        <v>43.23</v>
+        <v>41.89</v>
       </c>
       <c r="N3">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O3">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="P3">
-        <v>840.6</v>
+        <v>831.42</v>
       </c>
       <c r="Q3">
-        <v>867.55</v>
+        <v>863.6</v>
       </c>
       <c r="R3">
-        <v>879.92</v>
+        <v>878.6799999999999</v>
       </c>
       <c r="S3">
-        <v>806.84</v>
+        <v>807.75</v>
       </c>
       <c r="T3">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1072,43 +1100,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>40.1</v>
+        <v>39.44</v>
       </c>
       <c r="Z3">
-        <v>-12.82</v>
+        <v>-14.79</v>
       </c>
       <c r="AA3">
-        <v>-8.4</v>
+        <v>-9.68</v>
       </c>
       <c r="AB3">
-        <v>-4.42</v>
+        <v>-5.11</v>
       </c>
       <c r="AC3">
-        <v>32.65</v>
+        <v>24.79</v>
       </c>
       <c r="AD3">
-        <v>27.36</v>
+        <v>28.3</v>
       </c>
       <c r="AE3">
-        <v>29.48</v>
+        <v>28.99</v>
       </c>
       <c r="AF3">
-        <v>-1.36</v>
+        <v>-35.54</v>
       </c>
       <c r="AG3">
-        <v>916.16</v>
+        <v>915.1900000000001</v>
       </c>
       <c r="AH3">
-        <v>818.9400000000001</v>
+        <v>812.01</v>
       </c>
       <c r="AI3">
-        <v>910.9299999999999</v>
+        <v>906.3099999999999</v>
       </c>
       <c r="AJ3" t="s">
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>25.18</v>
+        <v>27.11</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,10 +1147,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1529.9</v>
+        <v>1530.9</v>
       </c>
       <c r="D4">
-        <v>-1.49</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1131,46 +1159,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-21.14</v>
+        <v>-21.09</v>
       </c>
       <c r="H4">
-        <v>12.93</v>
+        <v>13.01</v>
       </c>
       <c r="I4">
-        <v>-5.6</v>
+        <v>-2.05</v>
       </c>
       <c r="J4">
-        <v>-15.01</v>
+        <v>-13.21</v>
       </c>
       <c r="K4">
-        <v>-13.01</v>
+        <v>-11.41</v>
       </c>
       <c r="L4">
-        <v>-9.85</v>
+        <v>-8.16</v>
       </c>
       <c r="M4">
-        <v>20.24</v>
+        <v>20.89</v>
       </c>
       <c r="N4">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="O4">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="P4">
-        <v>1561.26</v>
+        <v>1554.84</v>
       </c>
       <c r="Q4">
-        <v>1612.97</v>
+        <v>1601.56</v>
       </c>
       <c r="R4">
-        <v>1756.5</v>
+        <v>1748.72</v>
       </c>
       <c r="S4">
-        <v>1674.65</v>
+        <v>1673.7</v>
       </c>
       <c r="T4">
-        <v>-8.640000000000001</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1185,43 +1213,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>32.77</v>
+        <v>32.96</v>
       </c>
       <c r="Z4">
-        <v>-57.71</v>
+        <v>-57.72</v>
       </c>
       <c r="AA4">
-        <v>-58.5</v>
+        <v>-58.34</v>
       </c>
       <c r="AB4">
-        <v>0.79</v>
+        <v>0.63</v>
       </c>
       <c r="AC4">
-        <v>68.18000000000001</v>
+        <v>60</v>
       </c>
       <c r="AD4">
-        <v>75.11</v>
+        <v>69.08</v>
       </c>
       <c r="AE4">
-        <v>46.42</v>
+        <v>46.57</v>
       </c>
       <c r="AF4">
-        <v>40.55</v>
+        <v>-30.6</v>
       </c>
       <c r="AG4">
-        <v>1743.05</v>
+        <v>1716.87</v>
       </c>
       <c r="AH4">
-        <v>1482.89</v>
+        <v>1486.25</v>
       </c>
       <c r="AI4">
-        <v>1676.2</v>
+        <v>1651.55</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>51.88</v>
+        <v>54.18</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1260,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1791.7</v>
+        <v>1776.6</v>
       </c>
       <c r="D5">
-        <v>1.16</v>
+        <v>-0.84</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1244,46 +1272,46 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-25.31</v>
+        <v>-25.94</v>
       </c>
       <c r="H5">
-        <v>7.05</v>
+        <v>6.15</v>
       </c>
       <c r="I5">
-        <v>3.98</v>
+        <v>1.69</v>
       </c>
       <c r="J5">
-        <v>-10.39</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="K5">
-        <v>-12.78</v>
+        <v>-12.88</v>
       </c>
       <c r="L5">
-        <v>-18.17</v>
+        <v>-17.51</v>
       </c>
       <c r="M5">
-        <v>17.59</v>
+        <v>17.57</v>
       </c>
       <c r="N5">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="O5">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="P5">
-        <v>1766.74</v>
+        <v>1772.66</v>
       </c>
       <c r="Q5">
-        <v>1799.01</v>
+        <v>1790.6</v>
       </c>
       <c r="R5">
-        <v>1907.8</v>
+        <v>1901.37</v>
       </c>
       <c r="S5">
-        <v>2023.23</v>
+        <v>2020.84</v>
       </c>
       <c r="T5">
-        <v>-11.44</v>
+        <v>-12.09</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1298,34 +1326,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>45.89</v>
+        <v>43.95</v>
       </c>
       <c r="Z5">
-        <v>-46.71</v>
+        <v>-42.72</v>
       </c>
       <c r="AA5">
-        <v>-55.05</v>
+        <v>-52.58</v>
       </c>
       <c r="AB5">
-        <v>8.33</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="AC5">
-        <v>98.48999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="AD5">
-        <v>85.44</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="AE5">
-        <v>57.46</v>
+        <v>58.12</v>
       </c>
       <c r="AF5">
-        <v>-19.04</v>
+        <v>-33.54</v>
       </c>
       <c r="AG5">
-        <v>1981.65</v>
+        <v>1959.96</v>
       </c>
       <c r="AH5">
-        <v>1616.38</v>
+        <v>1621.24</v>
       </c>
       <c r="AI5">
         <v>1853.75</v>
@@ -1334,7 +1362,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>32.54</v>
+        <v>29.69</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,58 +1373,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>657.1</v>
+        <v>647.4</v>
       </c>
       <c r="D6">
-        <v>-2.51</v>
+        <v>-1.48</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
       </c>
       <c r="F6">
-        <v>657.1</v>
+        <v>647.4</v>
       </c>
       <c r="G6">
-        <v>-39.7</v>
+        <v>-40.59</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-7.04</v>
+        <v>-6.39</v>
       </c>
       <c r="J6">
-        <v>-6.22</v>
+        <v>-7.63</v>
       </c>
       <c r="K6">
-        <v>-14.42</v>
+        <v>-15.42</v>
       </c>
       <c r="L6">
-        <v>-36.48</v>
+        <v>-37.24</v>
       </c>
       <c r="M6">
-        <v>7.6</v>
+        <v>7.68</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P6">
-        <v>683.77</v>
+        <v>674.9299999999999</v>
       </c>
       <c r="Q6">
-        <v>691.8099999999999</v>
+        <v>689.4</v>
       </c>
       <c r="R6">
-        <v>739.23</v>
+        <v>736.35</v>
       </c>
       <c r="S6">
-        <v>802.5599999999999</v>
+        <v>800.7</v>
       </c>
       <c r="T6">
-        <v>-18.12</v>
+        <v>-19.15</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1411,43 +1439,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>33.87</v>
+        <v>31.75</v>
       </c>
       <c r="Z6">
-        <v>-15.14</v>
+        <v>-17.24</v>
       </c>
       <c r="AA6">
-        <v>-15.44</v>
+        <v>-15.8</v>
       </c>
       <c r="AB6">
-        <v>0.3</v>
+        <v>-1.45</v>
       </c>
       <c r="AC6">
-        <v>54.88</v>
+        <v>34.02</v>
       </c>
       <c r="AD6">
-        <v>71.88</v>
+        <v>55.14</v>
       </c>
       <c r="AE6">
-        <v>19.82</v>
+        <v>19.61</v>
       </c>
       <c r="AF6">
-        <v>33.45</v>
+        <v>-16.34</v>
       </c>
       <c r="AG6">
-        <v>717.34</v>
+        <v>721.64</v>
       </c>
       <c r="AH6">
-        <v>666.28</v>
+        <v>657.16</v>
       </c>
       <c r="AI6">
-        <v>723.89</v>
+        <v>711.25</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>25.79</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,10 +1486,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2435.2</v>
+        <v>2498</v>
       </c>
       <c r="D7">
-        <v>-4.7</v>
+        <v>2.58</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1470,46 +1498,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-29.51</v>
+        <v>-27.7</v>
       </c>
       <c r="H7">
-        <v>28.75</v>
+        <v>32.07</v>
       </c>
       <c r="I7">
-        <v>-7.48</v>
+        <v>-6.42</v>
       </c>
       <c r="J7">
-        <v>-20.26</v>
+        <v>-17.92</v>
       </c>
       <c r="K7">
-        <v>-7.27</v>
+        <v>-1.26</v>
       </c>
       <c r="L7">
-        <v>7.38</v>
+        <v>6.8</v>
       </c>
       <c r="M7">
-        <v>23.38</v>
+        <v>23.65</v>
       </c>
       <c r="N7">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O7">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="P7">
-        <v>2575.12</v>
+        <v>2540.82</v>
       </c>
       <c r="Q7">
-        <v>2771.43</v>
+        <v>2747.18</v>
       </c>
       <c r="R7">
-        <v>3000.85</v>
+        <v>2997.31</v>
       </c>
       <c r="S7">
-        <v>2528.47</v>
+        <v>2529.78</v>
       </c>
       <c r="T7">
-        <v>-3.69</v>
+        <v>-1.26</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1524,43 +1552,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>25.66</v>
+        <v>31.53</v>
       </c>
       <c r="Z7">
-        <v>-134.55</v>
+        <v>-136.83</v>
       </c>
       <c r="AA7">
-        <v>-109.23</v>
+        <v>-114.75</v>
       </c>
       <c r="AB7">
-        <v>-25.32</v>
+        <v>-22.08</v>
       </c>
       <c r="AC7">
-        <v>50.81</v>
+        <v>49.56</v>
       </c>
       <c r="AD7">
-        <v>51.96</v>
+        <v>51.19</v>
       </c>
       <c r="AE7">
-        <v>120.95</v>
+        <v>127.34</v>
       </c>
       <c r="AF7">
-        <v>38.98</v>
+        <v>231.79</v>
       </c>
       <c r="AG7">
-        <v>3134.81</v>
+        <v>3115.81</v>
       </c>
       <c r="AH7">
-        <v>2408.05</v>
+        <v>2378.55</v>
       </c>
       <c r="AI7">
-        <v>2862.5</v>
+        <v>2854.62</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>63.25</v>
+        <v>64.55</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1571,10 +1599,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7406</v>
+        <v>6887</v>
       </c>
       <c r="D8">
-        <v>-3.68</v>
+        <v>-7.01</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1583,46 +1611,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-18.69</v>
+        <v>-24.39</v>
       </c>
       <c r="H8">
-        <v>25.01</v>
+        <v>16.25</v>
       </c>
       <c r="I8">
-        <v>-4.94</v>
+        <v>-12.79</v>
       </c>
       <c r="J8">
-        <v>-15.53</v>
+        <v>-20.29</v>
       </c>
       <c r="K8">
-        <v>-2.06</v>
+        <v>-8.31</v>
       </c>
       <c r="L8">
-        <v>-15.28</v>
+        <v>-22.04</v>
       </c>
       <c r="M8">
-        <v>12.12</v>
+        <v>9.26</v>
       </c>
       <c r="N8">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="O8">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="P8">
-        <v>7718.4</v>
+        <v>7516.4</v>
       </c>
       <c r="Q8">
-        <v>8071.6</v>
+        <v>7984.6</v>
       </c>
       <c r="R8">
-        <v>8191.13</v>
+        <v>8166.38</v>
       </c>
       <c r="S8">
-        <v>7430.03</v>
+        <v>7425.63</v>
       </c>
       <c r="T8">
-        <v>-0.32</v>
+        <v>-7.25</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1637,43 +1665,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>32.59</v>
+        <v>25.27</v>
       </c>
       <c r="Z8">
-        <v>-194.32</v>
+        <v>-255.03</v>
       </c>
       <c r="AA8">
-        <v>-134.81</v>
+        <v>-158.85</v>
       </c>
       <c r="AB8">
-        <v>-59.51</v>
+        <v>-96.18000000000001</v>
       </c>
       <c r="AC8">
-        <v>28.7</v>
+        <v>10.83</v>
       </c>
       <c r="AD8">
-        <v>33.04</v>
+        <v>24.75</v>
       </c>
       <c r="AE8">
-        <v>301.7</v>
+        <v>320.44</v>
       </c>
       <c r="AF8">
-        <v>681.5</v>
+        <v>143.26</v>
       </c>
       <c r="AG8">
-        <v>8839.030000000001</v>
+        <v>8872.049999999999</v>
       </c>
       <c r="AH8">
-        <v>7304.17</v>
+        <v>7097.15</v>
       </c>
       <c r="AI8">
-        <v>8562.809999999999</v>
+        <v>8072.56</v>
       </c>
       <c r="AJ8" t="s">
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>32.29</v>
+        <v>37.07</v>
       </c>
     </row>
   </sheetData>
@@ -1814,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1834,12 +1862,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1847,972 +1910,1057 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-5.74</v>
       </c>
-      <c r="E7" s="6">
-        <v>-6.24</v>
+      <c r="D7" s="6">
+        <v>-10.54</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-4.8</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-2.84</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-7.96</v>
       </c>
-      <c r="E8" s="6">
-        <v>-5.12</v>
+      <c r="D8" s="6">
+        <v>-10.21</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-11.99</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-15.01</v>
       </c>
-      <c r="E9" s="6">
-        <v>-3.02</v>
+      <c r="D9" s="6">
+        <v>-13.21</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.8</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-10.39</v>
       </c>
-      <c r="E10" s="6">
-        <v>-2.17</v>
+      <c r="D10" s="6">
+        <v>-8.460000000000001</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.93</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-4.13</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-6.22</v>
       </c>
-      <c r="E11" s="6">
-        <v>-2.09</v>
+      <c r="D11" s="6">
+        <v>-7.63</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-16.21</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-20.26</v>
       </c>
-      <c r="E12" s="6">
-        <v>-4.05</v>
+      <c r="D12" s="6">
+        <v>-17.92</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2.34</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-12.28</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-15.53</v>
       </c>
-      <c r="E13" s="6">
-        <v>-3.25</v>
+      <c r="D13" s="6">
+        <v>-20.29</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-4.76</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-8.960000000000001</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-10.53</v>
       </c>
-      <c r="E14" s="6">
-        <v>-1.57</v>
+      <c r="D14" s="6">
+        <v>-9.93</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.6</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-1.44</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-3.86</v>
       </c>
-      <c r="E15" s="6">
-        <v>-2.42</v>
+      <c r="D15" s="6">
+        <v>-5.32</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-1.75</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-5.6</v>
       </c>
-      <c r="E16" s="6">
-        <v>-3.85</v>
+      <c r="D16" s="6">
+        <v>-2.05</v>
+      </c>
+      <c r="E16" s="8">
+        <v>3.55</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>4.8</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>3.98</v>
       </c>
-      <c r="E17" s="6">
-        <v>-0.82</v>
+      <c r="D17" s="6">
+        <v>1.69</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.29</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>-3.62</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-7.04</v>
       </c>
-      <c r="E18" s="6">
-        <v>-3.42</v>
+      <c r="D18" s="6">
+        <v>-6.39</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.65</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5">
-        <v>-4.23</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-7.48</v>
       </c>
-      <c r="E19" s="6">
-        <v>-3.25</v>
+      <c r="D19" s="6">
+        <v>-6.42</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.06</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="6">
+        <v>-4.94</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-12.79</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-7.85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>16.82</v>
+      </c>
+      <c r="D21" s="6">
+        <v>15.29</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-1.53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>8.65</v>
+      </c>
+      <c r="D22" s="6">
+        <v>7.67</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-9.85</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-8.16</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-18.17</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-17.51</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-36.48</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-37.24</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.76</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>7.38</v>
+      </c>
+      <c r="D26" s="6">
+        <v>6.8</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-15.28</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-22.04</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-6.76</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-2.24</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-1.33</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-10.26</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-10.49</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-13.01</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-11.41</v>
+      </c>
+      <c r="E30" s="8">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-12.78</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-12.88</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-14.42</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-15.42</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>-7.27</v>
+      </c>
+      <c r="D33" s="6">
+        <v>-1.26</v>
+      </c>
+      <c r="E33" s="8">
+        <v>6.01</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-2.06</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-8.31</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-6.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-18.25</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-18.65</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-15.92</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-16.32</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-21.14</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-21.09</v>
+      </c>
+      <c r="E37" s="8">
         <v>0.05</v>
       </c>
-      <c r="D20" s="5">
-        <v>-4.94</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-4.99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-25.31</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-25.94</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-39.7</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-40.59</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-29.51</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-27.7</v>
+      </c>
+      <c r="E40" s="8">
+        <v>1.81</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-18.69</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-24.39</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-5.7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>19.35</v>
-      </c>
-      <c r="D21" s="5">
-        <v>16.82</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-2.53</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1059.9</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1054.7</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-5.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>14.87</v>
-      </c>
-      <c r="D22" s="5">
-        <v>8.65</v>
-      </c>
-      <c r="E22" s="6">
-        <v>-6.22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>821</v>
+      </c>
+      <c r="D43" s="6">
+        <v>817.1</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-5.56</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-9.85</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-4.29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>1529.9</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1530.9</v>
+      </c>
+      <c r="E44" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-18.33</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-18.17</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1791.7</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1776.6</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-15.1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-35.12</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-36.48</v>
-      </c>
-      <c r="E25" s="6">
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>657.1</v>
+      </c>
+      <c r="D46" s="6">
+        <v>647.4</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-9.699999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>2435.2</v>
+      </c>
+      <c r="D47" s="6">
+        <v>2498</v>
+      </c>
+      <c r="E47" s="8">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>7406</v>
+      </c>
+      <c r="D48" s="6">
+        <v>6887</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-519</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="6">
+        <v>85</v>
+      </c>
+      <c r="D49" s="6">
+        <v>71</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="6">
+        <v>43</v>
+      </c>
+      <c r="D50" s="6">
+        <v>57</v>
+      </c>
+      <c r="E50" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="6">
+        <v>29</v>
+      </c>
+      <c r="D51" s="6">
+        <v>43</v>
+      </c>
+      <c r="E51" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="6">
+        <v>71</v>
+      </c>
+      <c r="D52" s="6">
+        <v>85</v>
+      </c>
+      <c r="E52" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C53" s="6">
+        <v>57</v>
+      </c>
+      <c r="D53" s="6">
+        <v>29</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>33.99</v>
+      </c>
+      <c r="D54" s="6">
+        <v>33.45</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-0.54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>40.1</v>
+      </c>
+      <c r="D55" s="6">
+        <v>39.44</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>32.77</v>
+      </c>
+      <c r="D56" s="6">
+        <v>32.96</v>
+      </c>
+      <c r="E56" s="8">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>45.89</v>
+      </c>
+      <c r="D57" s="6">
+        <v>43.95</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-1.94</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="6">
+        <v>33.87</v>
+      </c>
+      <c r="D58" s="6">
+        <v>31.75</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-2.12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>25.66</v>
+      </c>
+      <c r="D59" s="6">
+        <v>31.53</v>
+      </c>
+      <c r="E59" s="8">
+        <v>5.87</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C60" s="6">
+        <v>32.59</v>
+      </c>
+      <c r="D60" s="6">
+        <v>25.27</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-7.32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-76.81999999999999</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-73.2</v>
+      </c>
+      <c r="E61" s="8">
+        <v>3.62</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
         <v>-1.36</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D62" s="6">
+        <v>-35.54</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-34.18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>40.55</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-30.6</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-71.15000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>-19.04</v>
+      </c>
+      <c r="D64" s="6">
+        <v>-33.54</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-14.5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>33.45</v>
+      </c>
+      <c r="D65" s="6">
+        <v>-16.34</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-49.79</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>11.36</v>
-      </c>
-      <c r="D26" s="5">
-        <v>7.38</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-3.98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B66" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C66" s="6">
+        <v>38.98</v>
+      </c>
+      <c r="D66" s="6">
+        <v>231.79</v>
+      </c>
+      <c r="E66" s="8">
+        <v>192.81</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-11.8</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-15.28</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-3.48</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>0.17</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-2.24</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-2.41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-6.3</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-10.26</v>
-      </c>
-      <c r="E29" s="6">
-        <v>-3.96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-12.89</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-13.01</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-12.34</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-12.78</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-11.57</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-14.42</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>-0.46</v>
-      </c>
-      <c r="D33" s="5">
-        <v>-7.27</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-6.81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>1.45</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-2.06</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-3.51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-16</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-18.25</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-2.25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-12.44</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-15.92</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-3.48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-19.95</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-21.14</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-1.19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-26.17</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-25.31</v>
-      </c>
-      <c r="E38" s="7">
-        <v>0.86</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-38.15</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-39.7</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-26.04</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-29.51</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-3.47</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-15.59</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-18.69</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>1089</v>
-      </c>
-      <c r="D42" s="5">
-        <v>1059.9</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-29.1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>855</v>
-      </c>
-      <c r="D43" s="5">
-        <v>821</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-34</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>1553</v>
-      </c>
-      <c r="D44" s="5">
-        <v>1529.9</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-23.1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>1771.1</v>
-      </c>
-      <c r="D45" s="5">
-        <v>1791.7</v>
-      </c>
-      <c r="E45" s="7">
-        <v>20.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>674.05</v>
-      </c>
-      <c r="D46" s="5">
-        <v>657.1</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-16.95</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>2555.2</v>
-      </c>
-      <c r="D47" s="5">
-        <v>2435.2</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-120</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="5">
-        <v>7689</v>
-      </c>
-      <c r="D48" s="5">
-        <v>7406</v>
-      </c>
-      <c r="E48" s="6">
-        <v>-283</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>37.11</v>
-      </c>
-      <c r="D49" s="5">
-        <v>33.99</v>
-      </c>
-      <c r="E49" s="6">
-        <v>-3.12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>46.39</v>
-      </c>
-      <c r="D50" s="5">
-        <v>40.1</v>
-      </c>
-      <c r="E50" s="6">
-        <v>-6.29</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>35</v>
-      </c>
-      <c r="D51" s="5">
-        <v>32.77</v>
-      </c>
-      <c r="E51" s="6">
-        <v>-2.23</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>42.68</v>
-      </c>
-      <c r="D52" s="5">
-        <v>45.89</v>
-      </c>
-      <c r="E52" s="7">
-        <v>3.21</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>37.97</v>
-      </c>
-      <c r="D53" s="5">
-        <v>33.87</v>
-      </c>
-      <c r="E53" s="6">
-        <v>-4.1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>30.26</v>
-      </c>
-      <c r="D54" s="5">
-        <v>25.66</v>
-      </c>
-      <c r="E54" s="6">
-        <v>-4.6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>38.19</v>
-      </c>
-      <c r="D55" s="5">
-        <v>32.59</v>
-      </c>
-      <c r="E55" s="6">
-        <v>-5.6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="3" t="s">
+      <c r="B67" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C56" s="5">
-        <v>-67.01000000000001</v>
-      </c>
-      <c r="D56" s="5">
-        <v>-76.81999999999999</v>
-      </c>
-      <c r="E56" s="6">
-        <v>-9.81</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5">
-        <v>55.55</v>
-      </c>
-      <c r="D57" s="5">
-        <v>-1.36</v>
-      </c>
-      <c r="E57" s="6">
-        <v>-56.91</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5">
-        <v>-65.88</v>
-      </c>
-      <c r="D58" s="5">
-        <v>40.55</v>
-      </c>
-      <c r="E58" s="7">
-        <v>106.43</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>-55.39</v>
-      </c>
-      <c r="D59" s="5">
-        <v>-19.04</v>
-      </c>
-      <c r="E59" s="7">
-        <v>36.35</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>-11.8</v>
-      </c>
-      <c r="D60" s="5">
-        <v>33.45</v>
-      </c>
-      <c r="E60" s="7">
-        <v>45.25</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>35.54</v>
-      </c>
-      <c r="D61" s="5">
-        <v>38.98</v>
-      </c>
-      <c r="E61" s="7">
-        <v>3.44</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-53.79</v>
-      </c>
-      <c r="D62" s="5">
+      <c r="C67" s="6">
         <v>681.5</v>
       </c>
-      <c r="E62" s="7">
-        <v>735.29</v>
+      <c r="D67" s="6">
+        <v>143.26</v>
+      </c>
+      <c r="E67" s="7">
+        <v>-538.24</v>
       </c>
     </row>
   </sheetData>
@@ -2838,60 +2986,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>44.24</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>34</v>
+      </c>
+      <c r="E2" s="11">
+        <v>28.6</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-12.6</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>44.24</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>35</v>
-      </c>
-      <c r="E2" s="10">
-        <v>28.6</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-11.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-8.9</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>14.3</v>
       </c>
     </row>
@@ -2993,49 +3141,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.4323</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2338</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2024</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1759</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.1212</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.076</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0403</v>
+      <c r="A2" s="14">
+        <v>0.4189</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2365</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2089</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1757</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.0926</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0488</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -187,16 +187,16 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>25.7 → 31.5</t>
+    <t>25.3 → 31.8</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>25.7</t>
-  </si>
-  <si>
-    <t>31.5</t>
+    <t>25.3</t>
+  </si>
+  <si>
+    <t>31.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -921,10 +921,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1054.7</v>
+        <v>1028.8</v>
       </c>
       <c r="D2">
-        <v>-0.49</v>
+        <v>-2.46</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -933,46 +933,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-18.65</v>
+        <v>-20.65</v>
       </c>
       <c r="H2">
-        <v>40.94</v>
+        <v>37.48</v>
       </c>
       <c r="I2">
-        <v>-9.93</v>
+        <v>-6.85</v>
       </c>
       <c r="J2">
-        <v>-10.54</v>
+        <v>-15.07</v>
       </c>
       <c r="K2">
-        <v>-1.33</v>
+        <v>-2.58</v>
       </c>
       <c r="L2">
-        <v>15.29</v>
+        <v>13.99</v>
       </c>
       <c r="M2">
-        <v>4.88</v>
+        <v>4.34</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P2">
-        <v>1083.62</v>
+        <v>1068.5</v>
       </c>
       <c r="Q2">
-        <v>1197.79</v>
+        <v>1186.01</v>
       </c>
       <c r="R2">
-        <v>1148.92</v>
+        <v>1146.02</v>
       </c>
       <c r="S2">
-        <v>996.79</v>
+        <v>997.64</v>
       </c>
       <c r="T2">
-        <v>5.81</v>
+        <v>3.12</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -987,43 +987,43 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>33.45</v>
+        <v>30.81</v>
       </c>
       <c r="Z2">
-        <v>-20.47</v>
+        <v>-27.38</v>
       </c>
       <c r="AA2">
-        <v>3.13</v>
+        <v>-2.97</v>
       </c>
       <c r="AB2">
-        <v>-23.6</v>
+        <v>-24.41</v>
       </c>
       <c r="AC2">
         <v>0</v>
       </c>
       <c r="AD2">
-        <v>0.9</v>
+        <v>0.45</v>
       </c>
       <c r="AE2">
-        <v>47.48</v>
+        <v>48.93</v>
       </c>
       <c r="AF2">
-        <v>-73.2</v>
+        <v>-18.04</v>
       </c>
       <c r="AG2">
-        <v>1350.15</v>
+        <v>1352.45</v>
       </c>
       <c r="AH2">
-        <v>1045.44</v>
+        <v>1019.57</v>
       </c>
       <c r="AI2">
-        <v>1202.4</v>
+        <v>1168</v>
       </c>
       <c r="AJ2" t="s">
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>42.57</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +1034,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>817.1</v>
+        <v>813.35</v>
       </c>
       <c r="D3">
-        <v>-0.48</v>
+        <v>-0.46</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1046,46 +1046,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-16.32</v>
+        <v>-16.71</v>
       </c>
       <c r="H3">
-        <v>54.32</v>
+        <v>53.61</v>
       </c>
       <c r="I3">
-        <v>-5.32</v>
+        <v>-0.57</v>
       </c>
       <c r="J3">
-        <v>-10.21</v>
+        <v>-9.23</v>
       </c>
       <c r="K3">
-        <v>-10.49</v>
+        <v>-7.97</v>
       </c>
       <c r="L3">
-        <v>7.67</v>
+        <v>7.58</v>
       </c>
       <c r="M3">
-        <v>41.89</v>
+        <v>41.86</v>
       </c>
       <c r="N3">
         <v>71</v>
       </c>
       <c r="O3">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="P3">
-        <v>831.42</v>
+        <v>830.49</v>
       </c>
       <c r="Q3">
-        <v>863.6</v>
+        <v>859.51</v>
       </c>
       <c r="R3">
-        <v>878.6799999999999</v>
+        <v>877.33</v>
       </c>
       <c r="S3">
-        <v>807.75</v>
+        <v>808.5700000000001</v>
       </c>
       <c r="T3">
-        <v>1.16</v>
+        <v>0.59</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1100,43 +1100,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>39.44</v>
+        <v>38.78</v>
       </c>
       <c r="Z3">
-        <v>-14.79</v>
+        <v>-16.46</v>
       </c>
       <c r="AA3">
-        <v>-9.68</v>
+        <v>-11.04</v>
       </c>
       <c r="AB3">
-        <v>-5.11</v>
+        <v>-5.43</v>
       </c>
       <c r="AC3">
-        <v>24.79</v>
+        <v>12.31</v>
       </c>
       <c r="AD3">
-        <v>28.3</v>
+        <v>23.25</v>
       </c>
       <c r="AE3">
-        <v>28.99</v>
+        <v>30.47</v>
       </c>
       <c r="AF3">
-        <v>-35.54</v>
+        <v>265.13</v>
       </c>
       <c r="AG3">
-        <v>915.1900000000001</v>
+        <v>913.51</v>
       </c>
       <c r="AH3">
-        <v>812.01</v>
+        <v>805.52</v>
       </c>
       <c r="AI3">
-        <v>906.3099999999999</v>
+        <v>888.53</v>
       </c>
       <c r="AJ3" t="s">
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>27.11</v>
+        <v>30.87</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,10 +1147,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1530.9</v>
+        <v>1463.8</v>
       </c>
       <c r="D4">
-        <v>0.07000000000000001</v>
+        <v>-4.38</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1159,46 +1159,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-21.09</v>
+        <v>-24.55</v>
       </c>
       <c r="H4">
-        <v>13.01</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I4">
-        <v>-2.05</v>
+        <v>-7.7</v>
       </c>
       <c r="J4">
-        <v>-13.21</v>
+        <v>-16.79</v>
       </c>
       <c r="K4">
-        <v>-11.41</v>
+        <v>-14.76</v>
       </c>
       <c r="L4">
-        <v>-8.16</v>
+        <v>-11.45</v>
       </c>
       <c r="M4">
-        <v>20.89</v>
+        <v>20.7</v>
       </c>
       <c r="N4">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O4">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="P4">
-        <v>1554.84</v>
+        <v>1530.4</v>
       </c>
       <c r="Q4">
-        <v>1601.56</v>
+        <v>1586.05</v>
       </c>
       <c r="R4">
-        <v>1748.72</v>
+        <v>1739.71</v>
       </c>
       <c r="S4">
-        <v>1673.7</v>
+        <v>1672.12</v>
       </c>
       <c r="T4">
-        <v>-8.529999999999999</v>
+        <v>-12.46</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1213,43 +1213,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>32.96</v>
+        <v>27.15</v>
       </c>
       <c r="Z4">
-        <v>-57.72</v>
+        <v>-62.42</v>
       </c>
       <c r="AA4">
-        <v>-58.34</v>
+        <v>-59.16</v>
       </c>
       <c r="AB4">
-        <v>0.63</v>
+        <v>-3.26</v>
       </c>
       <c r="AC4">
-        <v>60</v>
+        <v>42.64</v>
       </c>
       <c r="AD4">
-        <v>69.08</v>
+        <v>56.94</v>
       </c>
       <c r="AE4">
-        <v>46.57</v>
+        <v>49.02</v>
       </c>
       <c r="AF4">
-        <v>-30.6</v>
+        <v>93.94</v>
       </c>
       <c r="AG4">
-        <v>1716.87</v>
+        <v>1686.14</v>
       </c>
       <c r="AH4">
-        <v>1486.25</v>
+        <v>1485.96</v>
       </c>
       <c r="AI4">
-        <v>1651.55</v>
+        <v>1622.2</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>54.18</v>
+        <v>57.16</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1260,10 +1260,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1776.6</v>
+        <v>1718</v>
       </c>
       <c r="D5">
-        <v>-0.84</v>
+        <v>-3.3</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1272,46 +1272,46 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-25.94</v>
+        <v>-28.38</v>
       </c>
       <c r="H5">
-        <v>6.15</v>
+        <v>2.65</v>
       </c>
       <c r="I5">
-        <v>1.69</v>
+        <v>-2.68</v>
       </c>
       <c r="J5">
-        <v>-8.460000000000001</v>
+        <v>-11.67</v>
       </c>
       <c r="K5">
-        <v>-12.88</v>
+        <v>-15.07</v>
       </c>
       <c r="L5">
-        <v>-17.51</v>
+        <v>-19.65</v>
       </c>
       <c r="M5">
-        <v>17.57</v>
+        <v>17.1</v>
       </c>
       <c r="N5">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="O5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P5">
-        <v>1772.66</v>
+        <v>1763.2</v>
       </c>
       <c r="Q5">
-        <v>1790.6</v>
+        <v>1778.7</v>
       </c>
       <c r="R5">
-        <v>1901.37</v>
+        <v>1894.02</v>
       </c>
       <c r="S5">
-        <v>2020.84</v>
+        <v>2018.08</v>
       </c>
       <c r="T5">
-        <v>-12.09</v>
+        <v>-14.87</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1326,34 +1326,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>43.95</v>
+        <v>37.34</v>
       </c>
       <c r="Z5">
-        <v>-42.72</v>
+        <v>-43.78</v>
       </c>
       <c r="AA5">
-        <v>-52.58</v>
+        <v>-50.82</v>
       </c>
       <c r="AB5">
-        <v>9.859999999999999</v>
+        <v>7.04</v>
       </c>
       <c r="AC5">
-        <v>96.8</v>
+        <v>82.73999999999999</v>
       </c>
       <c r="AD5">
-        <v>93.98999999999999</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="AE5">
-        <v>58.12</v>
+        <v>59.34</v>
       </c>
       <c r="AF5">
-        <v>-33.54</v>
+        <v>-61.63</v>
       </c>
       <c r="AG5">
-        <v>1959.96</v>
+        <v>1931.8</v>
       </c>
       <c r="AH5">
-        <v>1621.24</v>
+        <v>1625.6</v>
       </c>
       <c r="AI5">
         <v>1853.75</v>
@@ -1362,7 +1362,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>29.69</v>
+        <v>26.02</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1373,34 +1373,34 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>647.4</v>
+        <v>627.5</v>
       </c>
       <c r="D6">
-        <v>-1.48</v>
+        <v>-3.07</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
       </c>
       <c r="F6">
-        <v>647.4</v>
+        <v>627.5</v>
       </c>
       <c r="G6">
-        <v>-40.59</v>
+        <v>-42.42</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-6.39</v>
+        <v>-10.61</v>
       </c>
       <c r="J6">
-        <v>-7.63</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="K6">
-        <v>-15.42</v>
+        <v>-17.34</v>
       </c>
       <c r="L6">
-        <v>-37.24</v>
+        <v>-38.61</v>
       </c>
       <c r="M6">
         <v>7.68</v>
@@ -1409,22 +1409,22 @@
         <v>15</v>
       </c>
       <c r="O6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P6">
-        <v>674.9299999999999</v>
+        <v>660.04</v>
       </c>
       <c r="Q6">
-        <v>689.4</v>
+        <v>685.71</v>
       </c>
       <c r="R6">
-        <v>736.35</v>
+        <v>733.13</v>
       </c>
       <c r="S6">
-        <v>800.7</v>
+        <v>798.79</v>
       </c>
       <c r="T6">
-        <v>-19.15</v>
+        <v>-21.44</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1439,43 +1439,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>31.75</v>
+        <v>27.9</v>
       </c>
       <c r="Z6">
-        <v>-17.24</v>
+        <v>-20.29</v>
       </c>
       <c r="AA6">
-        <v>-15.8</v>
+        <v>-16.7</v>
       </c>
       <c r="AB6">
-        <v>-1.45</v>
+        <v>-3.59</v>
       </c>
       <c r="AC6">
-        <v>34.02</v>
+        <v>16.74</v>
       </c>
       <c r="AD6">
-        <v>55.14</v>
+        <v>35.21</v>
       </c>
       <c r="AE6">
-        <v>19.61</v>
+        <v>20.02</v>
       </c>
       <c r="AF6">
-        <v>-16.34</v>
+        <v>41.91</v>
       </c>
       <c r="AG6">
-        <v>721.64</v>
+        <v>727.64</v>
       </c>
       <c r="AH6">
-        <v>657.16</v>
+        <v>643.77</v>
       </c>
       <c r="AI6">
-        <v>711.25</v>
+        <v>694.78</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>29.05</v>
+        <v>33.62</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,10 +1486,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2498</v>
+        <v>2507.6</v>
       </c>
       <c r="D7">
-        <v>2.58</v>
+        <v>0.38</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1498,46 +1498,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-27.7</v>
+        <v>-27.42</v>
       </c>
       <c r="H7">
-        <v>32.07</v>
+        <v>32.58</v>
       </c>
       <c r="I7">
-        <v>-6.42</v>
+        <v>-3.01</v>
       </c>
       <c r="J7">
-        <v>-17.92</v>
+        <v>-15.94</v>
       </c>
       <c r="K7">
-        <v>-1.26</v>
+        <v>-2.27</v>
       </c>
       <c r="L7">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>23.65</v>
+        <v>24.14</v>
       </c>
       <c r="N7">
         <v>85</v>
       </c>
       <c r="O7">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="P7">
-        <v>2540.82</v>
+        <v>2525.28</v>
       </c>
       <c r="Q7">
-        <v>2747.18</v>
+        <v>2721.56</v>
       </c>
       <c r="R7">
-        <v>2997.31</v>
+        <v>2995.28</v>
       </c>
       <c r="S7">
-        <v>2529.78</v>
+        <v>2531</v>
       </c>
       <c r="T7">
-        <v>-1.26</v>
+        <v>-0.92</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1552,43 +1552,43 @@
         <v>1</v>
       </c>
       <c r="Y7">
-        <v>31.53</v>
+        <v>32.41</v>
       </c>
       <c r="Z7">
-        <v>-136.83</v>
+        <v>-136.29</v>
       </c>
       <c r="AA7">
-        <v>-114.75</v>
+        <v>-119.06</v>
       </c>
       <c r="AB7">
-        <v>-22.08</v>
+        <v>-17.23</v>
       </c>
       <c r="AC7">
-        <v>49.56</v>
+        <v>61.76</v>
       </c>
       <c r="AD7">
-        <v>51.19</v>
+        <v>54.04</v>
       </c>
       <c r="AE7">
-        <v>127.34</v>
+        <v>130.55</v>
       </c>
       <c r="AF7">
-        <v>231.79</v>
+        <v>22.11</v>
       </c>
       <c r="AG7">
-        <v>3115.81</v>
+        <v>3081.5</v>
       </c>
       <c r="AH7">
-        <v>2378.55</v>
+        <v>2361.63</v>
       </c>
       <c r="AI7">
-        <v>2854.62</v>
+        <v>2851.41</v>
       </c>
       <c r="AJ7" t="s">
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>64.55</v>
+        <v>65.68000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1599,10 +1599,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>6887</v>
+        <v>7092</v>
       </c>
       <c r="D8">
-        <v>-7.01</v>
+        <v>2.98</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1611,46 +1611,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-24.39</v>
+        <v>-22.14</v>
       </c>
       <c r="H8">
-        <v>16.25</v>
+        <v>19.71</v>
       </c>
       <c r="I8">
-        <v>-12.79</v>
+        <v>-8.24</v>
       </c>
       <c r="J8">
-        <v>-20.29</v>
+        <v>-17.79</v>
       </c>
       <c r="K8">
-        <v>-8.31</v>
+        <v>-4.5</v>
       </c>
       <c r="L8">
-        <v>-22.04</v>
+        <v>-18.33</v>
       </c>
       <c r="M8">
-        <v>9.26</v>
+        <v>10.83</v>
       </c>
       <c r="N8">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="O8">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="P8">
-        <v>7516.4</v>
+        <v>7389.1</v>
       </c>
       <c r="Q8">
-        <v>7984.6</v>
+        <v>7905.28</v>
       </c>
       <c r="R8">
-        <v>8166.38</v>
+        <v>8147.88</v>
       </c>
       <c r="S8">
-        <v>7425.63</v>
+        <v>7421.91</v>
       </c>
       <c r="T8">
-        <v>-7.25</v>
+        <v>-4.45</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1665,43 +1665,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>25.27</v>
+        <v>31.79</v>
       </c>
       <c r="Z8">
-        <v>-255.03</v>
+        <v>-283.34</v>
       </c>
       <c r="AA8">
-        <v>-158.85</v>
+        <v>-183.75</v>
       </c>
       <c r="AB8">
-        <v>-96.18000000000001</v>
+        <v>-99.59</v>
       </c>
       <c r="AC8">
-        <v>10.83</v>
+        <v>12.55</v>
       </c>
       <c r="AD8">
-        <v>24.75</v>
+        <v>17.36</v>
       </c>
       <c r="AE8">
-        <v>320.44</v>
+        <v>347.23</v>
       </c>
       <c r="AF8">
-        <v>143.26</v>
+        <v>139.5</v>
       </c>
       <c r="AG8">
-        <v>8872.049999999999</v>
+        <v>8814.91</v>
       </c>
       <c r="AH8">
-        <v>7097.15</v>
+        <v>6995.64</v>
       </c>
       <c r="AI8">
-        <v>8072.56</v>
+        <v>7963.93</v>
       </c>
       <c r="AJ8" t="s">
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>37.07</v>
+        <v>42.04</v>
       </c>
     </row>
   </sheetData>
@@ -1842,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1882,7 +1882,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>54</v>
@@ -1934,13 +1934,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-5.74</v>
+        <v>-10.54</v>
       </c>
       <c r="D7" s="6">
-        <v>-10.54</v>
+        <v>-15.07</v>
       </c>
       <c r="E7" s="7">
-        <v>-4.8</v>
+        <v>-4.53</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1951,13 +1951,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-7.96</v>
+        <v>-10.21</v>
       </c>
       <c r="D8" s="6">
-        <v>-10.21</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-2.25</v>
+        <v>-9.23</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.98</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1968,13 +1968,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-15.01</v>
+        <v>-13.21</v>
       </c>
       <c r="D9" s="6">
-        <v>-13.21</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.8</v>
+        <v>-16.79</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-3.58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1985,13 +1985,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-10.39</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="D10" s="6">
-        <v>-8.460000000000001</v>
-      </c>
-      <c r="E10" s="8">
-        <v>1.93</v>
+        <v>-11.67</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-3.21</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2002,13 +2002,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-6.22</v>
+        <v>-7.63</v>
       </c>
       <c r="D11" s="6">
-        <v>-7.63</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.41</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2019,13 +2019,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-20.26</v>
+        <v>-17.92</v>
       </c>
       <c r="D12" s="6">
-        <v>-17.92</v>
+        <v>-15.94</v>
       </c>
       <c r="E12" s="8">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2036,13 +2036,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-15.53</v>
+        <v>-20.29</v>
       </c>
       <c r="D13" s="6">
-        <v>-20.29</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-4.76</v>
+        <v>-17.79</v>
+      </c>
+      <c r="E13" s="8">
+        <v>2.5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2053,13 +2053,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-10.53</v>
+        <v>-9.93</v>
       </c>
       <c r="D14" s="6">
-        <v>-9.93</v>
+        <v>-6.85</v>
       </c>
       <c r="E14" s="8">
-        <v>0.6</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2070,13 +2070,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.86</v>
+        <v>-5.32</v>
       </c>
       <c r="D15" s="6">
-        <v>-5.32</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.46</v>
+        <v>-0.57</v>
+      </c>
+      <c r="E15" s="8">
+        <v>4.75</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2087,13 +2087,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-5.6</v>
+        <v>-2.05</v>
       </c>
       <c r="D16" s="6">
-        <v>-2.05</v>
-      </c>
-      <c r="E16" s="8">
-        <v>3.55</v>
+        <v>-7.7</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-5.65</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2104,13 +2104,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>3.98</v>
+        <v>1.69</v>
       </c>
       <c r="D17" s="6">
-        <v>1.69</v>
+        <v>-2.68</v>
       </c>
       <c r="E17" s="7">
-        <v>-2.29</v>
+        <v>-4.37</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2121,13 +2121,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-7.04</v>
+        <v>-6.39</v>
       </c>
       <c r="D18" s="6">
-        <v>-6.39</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.65</v>
+        <v>-10.61</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-4.22</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2138,13 +2138,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>-7.48</v>
+        <v>-6.42</v>
       </c>
       <c r="D19" s="6">
-        <v>-6.42</v>
+        <v>-3.01</v>
       </c>
       <c r="E19" s="8">
-        <v>1.06</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2155,13 +2155,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-4.94</v>
+        <v>-12.79</v>
       </c>
       <c r="D20" s="6">
-        <v>-12.79</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-7.85</v>
+        <v>-8.24</v>
+      </c>
+      <c r="E20" s="8">
+        <v>4.55</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2172,13 +2172,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>16.82</v>
+        <v>15.29</v>
       </c>
       <c r="D21" s="6">
-        <v>15.29</v>
+        <v>13.99</v>
       </c>
       <c r="E21" s="7">
-        <v>-1.53</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2189,13 +2189,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>8.65</v>
+        <v>7.67</v>
       </c>
       <c r="D22" s="6">
-        <v>7.67</v>
+        <v>7.58</v>
       </c>
       <c r="E22" s="7">
-        <v>-0.98</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2206,13 +2206,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-9.85</v>
+        <v>-8.16</v>
       </c>
       <c r="D23" s="6">
-        <v>-8.16</v>
-      </c>
-      <c r="E23" s="8">
-        <v>1.69</v>
+        <v>-11.45</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-3.29</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2223,13 +2223,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-18.17</v>
+        <v>-17.51</v>
       </c>
       <c r="D24" s="6">
-        <v>-17.51</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.66</v>
+        <v>-19.65</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2240,13 +2240,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-36.48</v>
+        <v>-37.24</v>
       </c>
       <c r="D25" s="6">
-        <v>-37.24</v>
+        <v>-38.61</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.76</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2257,13 +2257,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>7.38</v>
+        <v>6.8</v>
       </c>
       <c r="D26" s="6">
-        <v>6.8</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.58</v>
+        <v>7</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0.2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2274,13 +2274,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-15.28</v>
+        <v>-22.04</v>
       </c>
       <c r="D27" s="6">
-        <v>-22.04</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-6.76</v>
+        <v>-18.33</v>
+      </c>
+      <c r="E27" s="8">
+        <v>3.71</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2291,13 +2291,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-2.24</v>
+        <v>-1.33</v>
       </c>
       <c r="D28" s="6">
-        <v>-1.33</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.91</v>
+        <v>-2.58</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2308,13 +2308,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-10.26</v>
+        <v>-10.49</v>
       </c>
       <c r="D29" s="6">
-        <v>-10.49</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.23</v>
+        <v>-7.97</v>
+      </c>
+      <c r="E29" s="8">
+        <v>2.52</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2325,13 +2325,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-13.01</v>
+        <v>-11.41</v>
       </c>
       <c r="D30" s="6">
-        <v>-11.41</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.6</v>
+        <v>-14.76</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-3.35</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2342,13 +2342,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-12.78</v>
+        <v>-12.88</v>
       </c>
       <c r="D31" s="6">
-        <v>-12.88</v>
+        <v>-15.07</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.1</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2359,13 +2359,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-14.42</v>
+        <v>-15.42</v>
       </c>
       <c r="D32" s="6">
-        <v>-15.42</v>
+        <v>-17.34</v>
       </c>
       <c r="E32" s="7">
-        <v>-1</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2376,13 +2376,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>-7.27</v>
+        <v>-1.26</v>
       </c>
       <c r="D33" s="6">
-        <v>-1.26</v>
-      </c>
-      <c r="E33" s="8">
-        <v>6.01</v>
+        <v>-2.27</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2393,13 +2393,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-2.06</v>
+        <v>-8.31</v>
       </c>
       <c r="D34" s="6">
-        <v>-8.31</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-6.25</v>
+        <v>-4.5</v>
+      </c>
+      <c r="E34" s="8">
+        <v>3.81</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2410,13 +2410,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-18.25</v>
+        <v>-18.65</v>
       </c>
       <c r="D35" s="6">
-        <v>-18.65</v>
+        <v>-20.65</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2427,13 +2427,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-15.92</v>
+        <v>-16.32</v>
       </c>
       <c r="D36" s="6">
-        <v>-16.32</v>
+        <v>-16.71</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.4</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2444,13 +2444,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-21.14</v>
+        <v>-21.09</v>
       </c>
       <c r="D37" s="6">
-        <v>-21.09</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.05</v>
+        <v>-24.55</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-3.46</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2461,13 +2461,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-25.31</v>
+        <v>-25.94</v>
       </c>
       <c r="D38" s="6">
-        <v>-25.94</v>
+        <v>-28.38</v>
       </c>
       <c r="E38" s="7">
-        <v>-0.63</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2478,13 +2478,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-39.7</v>
+        <v>-40.59</v>
       </c>
       <c r="D39" s="6">
-        <v>-40.59</v>
+        <v>-42.42</v>
       </c>
       <c r="E39" s="7">
-        <v>-0.89</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2495,13 +2495,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-29.51</v>
+        <v>-27.7</v>
       </c>
       <c r="D40" s="6">
-        <v>-27.7</v>
+        <v>-27.42</v>
       </c>
       <c r="E40" s="8">
-        <v>1.81</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2512,13 +2512,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-18.69</v>
+        <v>-24.39</v>
       </c>
       <c r="D41" s="6">
-        <v>-24.39</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-5.7</v>
+        <v>-22.14</v>
+      </c>
+      <c r="E41" s="8">
+        <v>2.25</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2529,13 +2529,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>1059.9</v>
+        <v>1054.7</v>
       </c>
       <c r="D42" s="6">
-        <v>1054.7</v>
+        <v>1028.8</v>
       </c>
       <c r="E42" s="7">
-        <v>-5.2</v>
+        <v>-25.9</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2546,13 +2546,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>821</v>
+        <v>817.1</v>
       </c>
       <c r="D43" s="6">
-        <v>817.1</v>
+        <v>813.35</v>
       </c>
       <c r="E43" s="7">
-        <v>-3.9</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2563,13 +2563,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>1529.9</v>
+        <v>1530.9</v>
       </c>
       <c r="D44" s="6">
-        <v>1530.9</v>
-      </c>
-      <c r="E44" s="8">
-        <v>1</v>
+        <v>1463.8</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-67.09999999999999</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2580,13 +2580,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>1791.7</v>
+        <v>1776.6</v>
       </c>
       <c r="D45" s="6">
-        <v>1776.6</v>
+        <v>1718</v>
       </c>
       <c r="E45" s="7">
-        <v>-15.1</v>
+        <v>-58.6</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2597,13 +2597,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>657.1</v>
+        <v>647.4</v>
       </c>
       <c r="D46" s="6">
-        <v>647.4</v>
+        <v>627.5</v>
       </c>
       <c r="E46" s="7">
-        <v>-9.699999999999999</v>
+        <v>-19.9</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2614,13 +2614,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>2435.2</v>
+        <v>2498</v>
       </c>
       <c r="D47" s="6">
-        <v>2498</v>
+        <v>2507.6</v>
       </c>
       <c r="E47" s="8">
-        <v>62.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2631,27 +2631,27 @@
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>7406</v>
+        <v>6887</v>
       </c>
       <c r="D48" s="6">
-        <v>6887</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-519</v>
+        <v>7092</v>
+      </c>
+      <c r="E48" s="8">
+        <v>205</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C49" s="6">
-        <v>85</v>
+        <v>57</v>
       </c>
       <c r="D49" s="6">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="E49" s="7">
         <v>-14</v>
@@ -2659,7 +2659,7 @@
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>13</v>
@@ -2668,15 +2668,15 @@
         <v>43</v>
       </c>
       <c r="D50" s="6">
-        <v>57</v>
-      </c>
-      <c r="E50" s="8">
-        <v>14</v>
+        <v>29</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>13</v>
@@ -2685,282 +2685,248 @@
         <v>29</v>
       </c>
       <c r="D51" s="6">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="E51" s="8">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>71</v>
+        <v>33.45</v>
       </c>
       <c r="D52" s="6">
-        <v>85</v>
-      </c>
-      <c r="E52" s="8">
-        <v>14</v>
+        <v>30.81</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>57</v>
+        <v>39.44</v>
       </c>
       <c r="D53" s="6">
-        <v>29</v>
+        <v>38.78</v>
       </c>
       <c r="E53" s="7">
-        <v>-28</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>33.99</v>
+        <v>32.96</v>
       </c>
       <c r="D54" s="6">
-        <v>33.45</v>
+        <v>27.15</v>
       </c>
       <c r="E54" s="7">
-        <v>-0.54</v>
+        <v>-5.81</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>40.1</v>
+        <v>43.95</v>
       </c>
       <c r="D55" s="6">
-        <v>39.44</v>
+        <v>37.34</v>
       </c>
       <c r="E55" s="7">
-        <v>-0.66</v>
+        <v>-6.61</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C56" s="6">
-        <v>32.77</v>
+        <v>31.75</v>
       </c>
       <c r="D56" s="6">
-        <v>32.96</v>
-      </c>
-      <c r="E56" s="8">
-        <v>0.19</v>
+        <v>27.9</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-3.85</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C57" s="6">
-        <v>45.89</v>
+        <v>31.53</v>
       </c>
       <c r="D57" s="6">
-        <v>43.95</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-1.94</v>
+        <v>32.41</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0.88</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C58" s="6">
-        <v>33.87</v>
+        <v>25.27</v>
       </c>
       <c r="D58" s="6">
-        <v>31.75</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-2.12</v>
+        <v>31.79</v>
+      </c>
+      <c r="E58" s="8">
+        <v>6.52</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>25.66</v>
+        <v>-73.2</v>
       </c>
       <c r="D59" s="6">
-        <v>31.53</v>
+        <v>-18.04</v>
       </c>
       <c r="E59" s="8">
-        <v>5.87</v>
+        <v>55.16</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>32.59</v>
+        <v>-35.54</v>
       </c>
       <c r="D60" s="6">
-        <v>25.27</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-7.32</v>
+        <v>265.13</v>
+      </c>
+      <c r="E60" s="8">
+        <v>300.67</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>-76.81999999999999</v>
+        <v>-30.6</v>
       </c>
       <c r="D61" s="6">
-        <v>-73.2</v>
+        <v>93.94</v>
       </c>
       <c r="E61" s="8">
-        <v>3.62</v>
+        <v>124.54</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>-1.36</v>
+        <v>-33.54</v>
       </c>
       <c r="D62" s="6">
-        <v>-35.54</v>
+        <v>-61.63</v>
       </c>
       <c r="E62" s="7">
-        <v>-34.18</v>
+        <v>-28.09</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C63" s="6">
-        <v>40.55</v>
+        <v>-16.34</v>
       </c>
       <c r="D63" s="6">
-        <v>-30.6</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-71.15000000000001</v>
+        <v>41.91</v>
+      </c>
+      <c r="E63" s="8">
+        <v>58.25</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C64" s="6">
-        <v>-19.04</v>
+        <v>231.79</v>
       </c>
       <c r="D64" s="6">
-        <v>-33.54</v>
+        <v>22.11</v>
       </c>
       <c r="E64" s="7">
-        <v>-14.5</v>
+        <v>-209.68</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C65" s="6">
-        <v>33.45</v>
+        <v>143.26</v>
       </c>
       <c r="D65" s="6">
-        <v>-16.34</v>
+        <v>139.5</v>
       </c>
       <c r="E65" s="7">
-        <v>-49.79</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>38.98</v>
-      </c>
-      <c r="D66" s="6">
-        <v>231.79</v>
-      </c>
-      <c r="E66" s="8">
-        <v>192.81</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="6">
-        <v>681.5</v>
-      </c>
-      <c r="D67" s="6">
-        <v>143.26</v>
-      </c>
-      <c r="E67" s="7">
-        <v>-538.24</v>
+        <v>-3.76</v>
       </c>
     </row>
   </sheetData>
@@ -3025,16 +2991,16 @@
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>34</v>
+        <v>32.3</v>
       </c>
       <c r="E2" s="11">
         <v>28.6</v>
       </c>
       <c r="F2" s="11">
-        <v>-12.6</v>
+        <v>-13.8</v>
       </c>
       <c r="G2" s="11">
-        <v>-8.699999999999999</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3165,25 +3131,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.4189</v>
+        <v>0.4186</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2365</v>
+        <v>0.2414</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2089</v>
+        <v>0.207</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1757</v>
+        <v>0.171</v>
       </c>
       <c r="E2" s="14">
-        <v>0.0926</v>
+        <v>0.1083</v>
       </c>
       <c r="F2" s="14">
         <v>0.07679999999999999</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0488</v>
+        <v>0.0434</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,34 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>25.3 → 31.8</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>25.3</t>
-  </si>
-  <si>
-    <t>31.8</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -398,18 +371,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -921,10 +893,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1028.8</v>
+        <v>1129.2</v>
       </c>
       <c r="D2">
-        <v>-2.46</v>
+        <v>9.76</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -933,46 +905,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-20.65</v>
+        <v>-12.9</v>
       </c>
       <c r="H2">
-        <v>37.48</v>
+        <v>50.89</v>
       </c>
       <c r="I2">
-        <v>-6.85</v>
+        <v>1.72</v>
       </c>
       <c r="J2">
-        <v>-15.07</v>
+        <v>-10.7</v>
       </c>
       <c r="K2">
-        <v>-2.58</v>
+        <v>6.1</v>
       </c>
       <c r="L2">
-        <v>13.99</v>
+        <v>26.74</v>
       </c>
       <c r="M2">
-        <v>4.34</v>
+        <v>5.76</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="P2">
-        <v>1068.5</v>
+        <v>1072.32</v>
       </c>
       <c r="Q2">
-        <v>1186.01</v>
+        <v>1177.64</v>
       </c>
       <c r="R2">
-        <v>1146.02</v>
+        <v>1145.52</v>
       </c>
       <c r="S2">
-        <v>997.64</v>
+        <v>999</v>
       </c>
       <c r="T2">
-        <v>3.12</v>
+        <v>13.03</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -987,34 +959,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>30.81</v>
+        <v>47.93</v>
       </c>
       <c r="Z2">
-        <v>-27.38</v>
+        <v>-24.47</v>
       </c>
       <c r="AA2">
-        <v>-2.97</v>
+        <v>-7.27</v>
       </c>
       <c r="AB2">
-        <v>-24.41</v>
+        <v>-17.2</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>17.93</v>
       </c>
       <c r="AD2">
-        <v>0.45</v>
+        <v>5.98</v>
       </c>
       <c r="AE2">
-        <v>48.93</v>
+        <v>59.67</v>
       </c>
       <c r="AF2">
-        <v>-18.04</v>
+        <v>58.49</v>
       </c>
       <c r="AG2">
-        <v>1352.45</v>
+        <v>1337.38</v>
       </c>
       <c r="AH2">
-        <v>1019.57</v>
+        <v>1017.91</v>
       </c>
       <c r="AI2">
         <v>1168</v>
@@ -1023,7 +995,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>46.7</v>
+        <v>41.75</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +1006,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>813.35</v>
+        <v>833.25</v>
       </c>
       <c r="D3">
-        <v>-0.46</v>
+        <v>2.45</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1046,46 +1018,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-16.71</v>
+        <v>-14.67</v>
       </c>
       <c r="H3">
-        <v>53.61</v>
+        <v>57.37</v>
       </c>
       <c r="I3">
-        <v>-0.57</v>
+        <v>-1.51</v>
       </c>
       <c r="J3">
-        <v>-9.23</v>
+        <v>-6.9</v>
       </c>
       <c r="K3">
-        <v>-7.97</v>
+        <v>-3.97</v>
       </c>
       <c r="L3">
-        <v>7.58</v>
+        <v>12.83</v>
       </c>
       <c r="M3">
-        <v>41.86</v>
+        <v>41.11</v>
       </c>
       <c r="N3">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O3">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="P3">
-        <v>830.49</v>
+        <v>827.9400000000001</v>
       </c>
       <c r="Q3">
-        <v>859.51</v>
+        <v>856.84</v>
       </c>
       <c r="R3">
-        <v>877.33</v>
+        <v>876.23</v>
       </c>
       <c r="S3">
-        <v>808.5700000000001</v>
+        <v>809.52</v>
       </c>
       <c r="T3">
-        <v>0.59</v>
+        <v>2.93</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1100,34 +1072,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>38.78</v>
+        <v>44.14</v>
       </c>
       <c r="Z3">
-        <v>-16.46</v>
+        <v>-16</v>
       </c>
       <c r="AA3">
-        <v>-11.04</v>
+        <v>-12.03</v>
       </c>
       <c r="AB3">
-        <v>-5.43</v>
+        <v>-3.97</v>
       </c>
       <c r="AC3">
-        <v>12.31</v>
+        <v>18.92</v>
       </c>
       <c r="AD3">
-        <v>23.25</v>
+        <v>18.67</v>
       </c>
       <c r="AE3">
-        <v>30.47</v>
+        <v>31.29</v>
       </c>
       <c r="AF3">
-        <v>265.13</v>
+        <v>45.71</v>
       </c>
       <c r="AG3">
-        <v>913.51</v>
+        <v>910.46</v>
       </c>
       <c r="AH3">
-        <v>805.52</v>
+        <v>803.23</v>
       </c>
       <c r="AI3">
         <v>888.53</v>
@@ -1136,7 +1108,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>30.87</v>
+        <v>32.17</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,10 +1119,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1463.8</v>
+        <v>1447.9</v>
       </c>
       <c r="D4">
-        <v>-4.38</v>
+        <v>-1.09</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1159,46 +1131,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-24.55</v>
+        <v>-25.37</v>
       </c>
       <c r="H4">
-        <v>8.050000000000001</v>
+        <v>6.88</v>
       </c>
       <c r="I4">
-        <v>-7.7</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="J4">
-        <v>-16.79</v>
+        <v>-18.38</v>
       </c>
       <c r="K4">
-        <v>-14.76</v>
+        <v>-16.03</v>
       </c>
       <c r="L4">
-        <v>-11.45</v>
+        <v>-13.41</v>
       </c>
       <c r="M4">
-        <v>20.7</v>
+        <v>19.29</v>
       </c>
       <c r="N4">
         <v>43</v>
       </c>
       <c r="O4">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="P4">
-        <v>1530.4</v>
+        <v>1505.1</v>
       </c>
       <c r="Q4">
-        <v>1586.05</v>
+        <v>1574.36</v>
       </c>
       <c r="R4">
-        <v>1739.71</v>
+        <v>1730.31</v>
       </c>
       <c r="S4">
-        <v>1672.12</v>
+        <v>1670.5</v>
       </c>
       <c r="T4">
-        <v>-12.46</v>
+        <v>-13.33</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1213,43 +1185,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
+        <v>25.98</v>
+      </c>
+      <c r="Z4">
+        <v>-66.66</v>
+      </c>
+      <c r="AA4">
+        <v>-60.66</v>
+      </c>
+      <c r="AB4">
+        <v>-6</v>
+      </c>
+      <c r="AC4">
         <v>27.15</v>
       </c>
-      <c r="Z4">
-        <v>-62.42</v>
-      </c>
-      <c r="AA4">
-        <v>-59.16</v>
-      </c>
-      <c r="AB4">
-        <v>-3.26</v>
-      </c>
-      <c r="AC4">
-        <v>42.64</v>
-      </c>
       <c r="AD4">
-        <v>56.94</v>
+        <v>43.26</v>
       </c>
       <c r="AE4">
-        <v>49.02</v>
+        <v>49</v>
       </c>
       <c r="AF4">
-        <v>93.94</v>
+        <v>-3.04</v>
       </c>
       <c r="AG4">
-        <v>1686.14</v>
+        <v>1681.76</v>
       </c>
       <c r="AH4">
-        <v>1485.96</v>
+        <v>1466.96</v>
       </c>
       <c r="AI4">
-        <v>1622.2</v>
+        <v>1583.31</v>
       </c>
       <c r="AJ4" t="s">
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>57.16</v>
+        <v>60.38</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1260,10 +1232,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1718</v>
+        <v>1730.6</v>
       </c>
       <c r="D5">
-        <v>-3.3</v>
+        <v>0.73</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1272,46 +1244,46 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-28.38</v>
+        <v>-27.85</v>
       </c>
       <c r="H5">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="I5">
-        <v>-2.68</v>
+        <v>-1.59</v>
       </c>
       <c r="J5">
-        <v>-11.67</v>
+        <v>-11.52</v>
       </c>
       <c r="K5">
-        <v>-15.07</v>
+        <v>-12.63</v>
       </c>
       <c r="L5">
-        <v>-19.65</v>
+        <v>-20.12</v>
       </c>
       <c r="M5">
-        <v>17.1</v>
+        <v>17.43</v>
       </c>
       <c r="N5">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="O5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P5">
-        <v>1763.2</v>
+        <v>1757.6</v>
       </c>
       <c r="Q5">
-        <v>1778.7</v>
+        <v>1768.1</v>
       </c>
       <c r="R5">
-        <v>1894.02</v>
+        <v>1887.17</v>
       </c>
       <c r="S5">
-        <v>2018.08</v>
+        <v>2015.28</v>
       </c>
       <c r="T5">
-        <v>-14.87</v>
+        <v>-14.13</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1326,34 +1298,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>37.34</v>
+        <v>39.45</v>
       </c>
       <c r="Z5">
-        <v>-43.78</v>
+        <v>-43.1</v>
       </c>
       <c r="AA5">
-        <v>-50.82</v>
+        <v>-49.28</v>
       </c>
       <c r="AB5">
-        <v>7.04</v>
+        <v>6.17</v>
       </c>
       <c r="AC5">
-        <v>82.73999999999999</v>
+        <v>72.14</v>
       </c>
       <c r="AD5">
-        <v>92.68000000000001</v>
+        <v>83.89</v>
       </c>
       <c r="AE5">
-        <v>59.34</v>
+        <v>58.88</v>
       </c>
       <c r="AF5">
-        <v>-61.63</v>
+        <v>-67.48999999999999</v>
       </c>
       <c r="AG5">
-        <v>1931.8</v>
+        <v>1901.54</v>
       </c>
       <c r="AH5">
-        <v>1625.6</v>
+        <v>1634.67</v>
       </c>
       <c r="AI5">
         <v>1853.75</v>
@@ -1362,7 +1334,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>26.02</v>
+        <v>23.45</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1373,58 +1345,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>627.5</v>
+        <v>621.95</v>
       </c>
       <c r="D6">
-        <v>-3.07</v>
+        <v>-0.88</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
       </c>
       <c r="F6">
-        <v>627.5</v>
+        <v>621.95</v>
       </c>
       <c r="G6">
-        <v>-42.42</v>
+        <v>-42.93</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-10.61</v>
+        <v>-10.4</v>
       </c>
       <c r="J6">
-        <v>-9.779999999999999</v>
+        <v>-11.33</v>
       </c>
       <c r="K6">
-        <v>-17.34</v>
+        <v>-17.95</v>
       </c>
       <c r="L6">
-        <v>-38.61</v>
+        <v>-39.53</v>
       </c>
       <c r="M6">
-        <v>7.68</v>
+        <v>7.1</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P6">
-        <v>660.04</v>
+        <v>645.6</v>
       </c>
       <c r="Q6">
-        <v>685.71</v>
+        <v>682.33</v>
       </c>
       <c r="R6">
-        <v>733.13</v>
+        <v>730.12</v>
       </c>
       <c r="S6">
-        <v>798.79</v>
+        <v>796.86</v>
       </c>
       <c r="T6">
-        <v>-21.44</v>
+        <v>-21.95</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1439,43 +1411,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>27.9</v>
+        <v>26.92</v>
       </c>
       <c r="Z6">
-        <v>-20.29</v>
+        <v>-22.88</v>
       </c>
       <c r="AA6">
-        <v>-16.7</v>
+        <v>-17.93</v>
       </c>
       <c r="AB6">
-        <v>-3.59</v>
+        <v>-4.95</v>
       </c>
       <c r="AC6">
-        <v>16.74</v>
+        <v>6.54</v>
       </c>
       <c r="AD6">
-        <v>35.21</v>
+        <v>19.1</v>
       </c>
       <c r="AE6">
-        <v>20.02</v>
+        <v>20</v>
       </c>
       <c r="AF6">
-        <v>41.91</v>
+        <v>-26.96</v>
       </c>
       <c r="AG6">
-        <v>727.64</v>
+        <v>732.95</v>
       </c>
       <c r="AH6">
-        <v>643.77</v>
+        <v>631.7</v>
       </c>
       <c r="AI6">
-        <v>694.78</v>
+        <v>684.88</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>33.62</v>
+        <v>38.02</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,10 +1458,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2507.6</v>
+        <v>2538.6</v>
       </c>
       <c r="D7">
-        <v>0.38</v>
+        <v>1.24</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1498,46 +1470,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-27.42</v>
+        <v>-26.52</v>
       </c>
       <c r="H7">
-        <v>32.58</v>
+        <v>34.21</v>
       </c>
       <c r="I7">
-        <v>-3.01</v>
+        <v>-3.49</v>
       </c>
       <c r="J7">
         <v>-15.94</v>
       </c>
       <c r="K7">
-        <v>-2.27</v>
+        <v>-1.09</v>
       </c>
       <c r="L7">
-        <v>7</v>
+        <v>7.85</v>
       </c>
       <c r="M7">
-        <v>24.14</v>
+        <v>24.36</v>
       </c>
       <c r="N7">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O7">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P7">
-        <v>2525.28</v>
+        <v>2506.92</v>
       </c>
       <c r="Q7">
-        <v>2721.56</v>
+        <v>2696.84</v>
       </c>
       <c r="R7">
-        <v>2995.28</v>
+        <v>2988.49</v>
       </c>
       <c r="S7">
-        <v>2531</v>
+        <v>2532.43</v>
       </c>
       <c r="T7">
-        <v>-0.92</v>
+        <v>0.24</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1549,37 +1521,37 @@
         <v>46</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y7">
-        <v>32.41</v>
+        <v>35.29</v>
       </c>
       <c r="Z7">
-        <v>-136.29</v>
+        <v>-131.84</v>
       </c>
       <c r="AA7">
-        <v>-119.06</v>
+        <v>-121.62</v>
       </c>
       <c r="AB7">
-        <v>-17.23</v>
+        <v>-10.22</v>
       </c>
       <c r="AC7">
-        <v>61.76</v>
+        <v>85.78</v>
       </c>
       <c r="AD7">
-        <v>54.04</v>
+        <v>65.7</v>
       </c>
       <c r="AE7">
-        <v>130.55</v>
+        <v>132.98</v>
       </c>
       <c r="AF7">
-        <v>22.11</v>
+        <v>143.75</v>
       </c>
       <c r="AG7">
-        <v>3081.5</v>
+        <v>3033.88</v>
       </c>
       <c r="AH7">
-        <v>2361.63</v>
+        <v>2359.8</v>
       </c>
       <c r="AI7">
         <v>2851.41</v>
@@ -1588,7 +1560,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>65.68000000000001</v>
+        <v>63.51</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1599,10 +1571,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7092</v>
+        <v>7138</v>
       </c>
       <c r="D8">
-        <v>2.98</v>
+        <v>0.65</v>
       </c>
       <c r="E8">
         <v>9108.879999999999</v>
@@ -1611,46 +1583,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-22.14</v>
+        <v>-21.64</v>
       </c>
       <c r="H8">
-        <v>19.71</v>
+        <v>20.48</v>
       </c>
       <c r="I8">
-        <v>-8.24</v>
+        <v>-9.32</v>
       </c>
       <c r="J8">
-        <v>-17.79</v>
+        <v>-17.75</v>
       </c>
       <c r="K8">
-        <v>-4.5</v>
+        <v>-11.6</v>
       </c>
       <c r="L8">
-        <v>-18.33</v>
+        <v>-19.56</v>
       </c>
       <c r="M8">
-        <v>10.83</v>
+        <v>10.9</v>
       </c>
       <c r="N8">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="O8">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="P8">
-        <v>7389.1</v>
+        <v>7242.4</v>
       </c>
       <c r="Q8">
-        <v>7905.28</v>
+        <v>7835.9</v>
       </c>
       <c r="R8">
-        <v>8147.88</v>
+        <v>8131.55</v>
       </c>
       <c r="S8">
-        <v>7421.91</v>
+        <v>7418.76</v>
       </c>
       <c r="T8">
-        <v>-4.45</v>
+        <v>-3.78</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1665,34 +1637,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>31.79</v>
+        <v>33.2</v>
       </c>
       <c r="Z8">
-        <v>-283.34</v>
+        <v>-298.63</v>
       </c>
       <c r="AA8">
-        <v>-183.75</v>
+        <v>-206.73</v>
       </c>
       <c r="AB8">
-        <v>-99.59</v>
+        <v>-91.90000000000001</v>
       </c>
       <c r="AC8">
-        <v>12.55</v>
+        <v>27.82</v>
       </c>
       <c r="AD8">
-        <v>17.36</v>
+        <v>17.07</v>
       </c>
       <c r="AE8">
-        <v>347.23</v>
+        <v>350.89</v>
       </c>
       <c r="AF8">
-        <v>139.5</v>
+        <v>-49.72</v>
       </c>
       <c r="AG8">
-        <v>8814.91</v>
+        <v>8757.92</v>
       </c>
       <c r="AH8">
-        <v>6995.64</v>
+        <v>6913.88</v>
       </c>
       <c r="AI8">
         <v>7963.93</v>
@@ -1701,7 +1673,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>42.04</v>
+        <v>45.77</v>
       </c>
     </row>
   </sheetData>
@@ -1862,47 +1834,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1910,1023 +1847,1023 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-10.54</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-15.07</v>
       </c>
-      <c r="E7" s="7">
-        <v>-4.53</v>
+      <c r="D7" s="5">
+        <v>-10.7</v>
+      </c>
+      <c r="E7" s="6">
+        <v>4.37</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-10.21</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-9.23</v>
       </c>
-      <c r="E8" s="8">
-        <v>0.98</v>
+      <c r="D8" s="5">
+        <v>-6.9</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2.33</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-13.21</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-16.79</v>
       </c>
+      <c r="D9" s="5">
+        <v>-18.38</v>
+      </c>
       <c r="E9" s="7">
-        <v>-3.58</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-8.460000000000001</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-11.67</v>
       </c>
-      <c r="E10" s="7">
-        <v>-3.21</v>
+      <c r="D10" s="5">
+        <v>-11.52</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.15</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-7.63</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-9.779999999999999</v>
       </c>
+      <c r="D11" s="5">
+        <v>-11.33</v>
+      </c>
       <c r="E11" s="7">
-        <v>-2.15</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-17.79</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-17.75</v>
+      </c>
+      <c r="E12" s="6">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-6.85</v>
+      </c>
+      <c r="D13" s="5">
+        <v>1.72</v>
+      </c>
+      <c r="E13" s="6">
+        <v>8.57</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-0.57</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-1.51</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-7.7</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-8.029999999999999</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>-2.68</v>
+      </c>
+      <c r="D16" s="5">
+        <v>-1.59</v>
+      </c>
+      <c r="E16" s="6">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="5">
+        <v>-10.61</v>
+      </c>
+      <c r="D17" s="5">
+        <v>-10.4</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-17.92</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-15.94</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-3.01</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-3.49</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-20.29</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-17.79</v>
-      </c>
-      <c r="E13" s="8">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-8.24</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-9.32</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-9.93</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-6.85</v>
-      </c>
-      <c r="E14" s="8">
-        <v>3.08</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>13.99</v>
+      </c>
+      <c r="D20" s="5">
+        <v>26.74</v>
+      </c>
+      <c r="E20" s="6">
+        <v>12.75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-5.32</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-0.57</v>
-      </c>
-      <c r="E15" s="8">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>7.58</v>
+      </c>
+      <c r="D21" s="5">
+        <v>12.83</v>
+      </c>
+      <c r="E21" s="6">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-2.05</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-7.7</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-5.65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-11.45</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-13.41</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>1.69</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-2.68</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-4.37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="5">
+        <v>-19.65</v>
+      </c>
+      <c r="D23" s="5">
+        <v>-20.12</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="6">
-        <v>-6.39</v>
-      </c>
-      <c r="D18" s="6">
-        <v>-10.61</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-4.22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-38.61</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-39.53</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-6.42</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-3.01</v>
-      </c>
-      <c r="E19" s="8">
-        <v>3.41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="5">
+        <v>7</v>
+      </c>
+      <c r="D25" s="5">
+        <v>7.85</v>
+      </c>
+      <c r="E25" s="6">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-12.79</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-8.24</v>
-      </c>
-      <c r="E20" s="8">
-        <v>4.55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-18.33</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-19.56</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>15.29</v>
-      </c>
-      <c r="D21" s="6">
-        <v>13.99</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-1.3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-2.58</v>
+      </c>
+      <c r="D27" s="5">
+        <v>6.1</v>
+      </c>
+      <c r="E27" s="6">
+        <v>8.68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>7.67</v>
-      </c>
-      <c r="D22" s="6">
-        <v>7.58</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-7.97</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-3.97</v>
+      </c>
+      <c r="E28" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-8.16</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-11.45</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-3.29</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-14.76</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-16.03</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-17.51</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-19.65</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-15.07</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-12.63</v>
+      </c>
+      <c r="E30" s="6">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-37.24</v>
-      </c>
-      <c r="D25" s="6">
-        <v>-38.61</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-17.34</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-17.95</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="6">
-        <v>6.8</v>
-      </c>
-      <c r="D26" s="6">
-        <v>7</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5">
+        <v>-2.27</v>
+      </c>
+      <c r="D32" s="5">
+        <v>-1.09</v>
+      </c>
+      <c r="E32" s="6">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-22.04</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-18.33</v>
-      </c>
-      <c r="E27" s="8">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="5">
+        <v>-4.5</v>
+      </c>
+      <c r="D33" s="5">
+        <v>-11.6</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-7.1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-1.33</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-2.58</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="5">
+        <v>-20.65</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-12.9</v>
+      </c>
+      <c r="E34" s="6">
+        <v>7.75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-10.49</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-7.97</v>
-      </c>
-      <c r="E29" s="8">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-16.71</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-14.67</v>
+      </c>
+      <c r="E35" s="6">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-11.41</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-14.76</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-3.35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-24.55</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-25.37</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-12.88</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-15.07</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-2.19</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-28.38</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-27.85</v>
+      </c>
+      <c r="E37" s="6">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-15.42</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-17.34</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.92</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-42.42</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-42.93</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="6">
-        <v>-1.26</v>
-      </c>
-      <c r="D33" s="6">
-        <v>-2.27</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.01</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-27.42</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-26.52</v>
+      </c>
+      <c r="E39" s="6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="6">
-        <v>-8.31</v>
-      </c>
-      <c r="D34" s="6">
-        <v>-4.5</v>
-      </c>
-      <c r="E34" s="8">
-        <v>3.81</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-22.14</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-21.64</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-18.65</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-20.65</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>1028.8</v>
+      </c>
+      <c r="D41" s="5">
+        <v>1129.2</v>
+      </c>
+      <c r="E41" s="6">
+        <v>100.4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-16.32</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-16.71</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>813.35</v>
+      </c>
+      <c r="D42" s="5">
+        <v>833.25</v>
+      </c>
+      <c r="E42" s="6">
+        <v>19.9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-21.09</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-24.55</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-3.46</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>1463.8</v>
+      </c>
+      <c r="D43" s="5">
+        <v>1447.9</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-15.9</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-25.94</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-28.38</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-2.44</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1718</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1730.6</v>
+      </c>
+      <c r="E44" s="6">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-40.59</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-42.42</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.83</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>627.5</v>
+      </c>
+      <c r="D45" s="5">
+        <v>621.95</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-5.55</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-27.7</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-27.42</v>
-      </c>
-      <c r="E40" s="8">
-        <v>0.28</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>2507.6</v>
+      </c>
+      <c r="D46" s="5">
+        <v>2538.6</v>
+      </c>
+      <c r="E46" s="6">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-24.39</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-22.14</v>
-      </c>
-      <c r="E41" s="8">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
+      <c r="B47" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="6">
-        <v>1054.7</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1028.8</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-25.9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
+      <c r="C47" s="5">
+        <v>7092</v>
+      </c>
+      <c r="D47" s="5">
+        <v>7138</v>
+      </c>
+      <c r="E47" s="6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>817.1</v>
-      </c>
-      <c r="D43" s="6">
-        <v>813.35</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-3.75</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1530.9</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1463.8</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-67.09999999999999</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
+      <c r="B48" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="5">
+        <v>71</v>
+      </c>
+      <c r="D48" s="5">
+        <v>85</v>
+      </c>
+      <c r="E48" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1776.6</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1718</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-58.6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>647.4</v>
-      </c>
-      <c r="D46" s="6">
-        <v>627.5</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-19.9</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="5">
+        <v>29</v>
+      </c>
+      <c r="D49" s="5">
+        <v>57</v>
+      </c>
+      <c r="E49" s="6">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>2498</v>
-      </c>
-      <c r="D47" s="6">
-        <v>2507.6</v>
-      </c>
-      <c r="E47" s="8">
-        <v>9.6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>6887</v>
-      </c>
-      <c r="D48" s="6">
-        <v>7092</v>
-      </c>
-      <c r="E48" s="8">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B49" s="5" t="s">
+      <c r="B50" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C49" s="6">
-        <v>57</v>
-      </c>
-      <c r="D49" s="6">
-        <v>43</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="6">
-        <v>43</v>
-      </c>
-      <c r="D50" s="6">
-        <v>29</v>
+      <c r="C50" s="5">
+        <v>85</v>
+      </c>
+      <c r="D50" s="5">
+        <v>71</v>
       </c>
       <c r="E50" s="7">
         <v>-14</v>
       </c>
     </row>
     <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C51" s="6">
+      <c r="C51" s="5">
+        <v>57</v>
+      </c>
+      <c r="D51" s="5">
         <v>29</v>
       </c>
-      <c r="D51" s="6">
-        <v>57</v>
-      </c>
-      <c r="E51" s="8">
-        <v>28</v>
+      <c r="E51" s="7">
+        <v>-28</v>
       </c>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C52" s="6">
-        <v>33.45</v>
-      </c>
-      <c r="D52" s="6">
+      <c r="C52" s="5">
         <v>30.81</v>
       </c>
-      <c r="E52" s="7">
-        <v>-2.64</v>
+      <c r="D52" s="5">
+        <v>47.93</v>
+      </c>
+      <c r="E52" s="6">
+        <v>17.12</v>
       </c>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
+      <c r="A53" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C53" s="6">
-        <v>39.44</v>
-      </c>
-      <c r="D53" s="6">
+      <c r="C53" s="5">
         <v>38.78</v>
       </c>
-      <c r="E53" s="7">
-        <v>-0.66</v>
+      <c r="D53" s="5">
+        <v>44.14</v>
+      </c>
+      <c r="E53" s="6">
+        <v>5.36</v>
       </c>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C54" s="6">
-        <v>32.96</v>
-      </c>
-      <c r="D54" s="6">
+      <c r="C54" s="5">
         <v>27.15</v>
       </c>
+      <c r="D54" s="5">
+        <v>25.98</v>
+      </c>
       <c r="E54" s="7">
-        <v>-5.81</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
+      <c r="A55" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C55" s="6">
-        <v>43.95</v>
-      </c>
-      <c r="D55" s="6">
+      <c r="C55" s="5">
         <v>37.34</v>
       </c>
-      <c r="E55" s="7">
-        <v>-6.61</v>
+      <c r="D55" s="5">
+        <v>39.45</v>
+      </c>
+      <c r="E55" s="6">
+        <v>2.11</v>
       </c>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="6">
-        <v>31.75</v>
-      </c>
-      <c r="D56" s="6">
+      <c r="C56" s="5">
         <v>27.9</v>
       </c>
+      <c r="D56" s="5">
+        <v>26.92</v>
+      </c>
       <c r="E56" s="7">
-        <v>-3.85</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
+      <c r="A57" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C57" s="6">
-        <v>31.53</v>
-      </c>
-      <c r="D57" s="6">
+      <c r="C57" s="5">
         <v>32.41</v>
       </c>
-      <c r="E57" s="8">
-        <v>0.88</v>
+      <c r="D57" s="5">
+        <v>35.29</v>
+      </c>
+      <c r="E57" s="6">
+        <v>2.88</v>
       </c>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C58" s="6">
-        <v>25.27</v>
-      </c>
-      <c r="D58" s="6">
+      <c r="C58" s="5">
         <v>31.79</v>
       </c>
-      <c r="E58" s="8">
-        <v>6.52</v>
+      <c r="D58" s="5">
+        <v>33.2</v>
+      </c>
+      <c r="E58" s="6">
+        <v>1.41</v>
       </c>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
+      <c r="A59" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="6">
-        <v>-73.2</v>
-      </c>
-      <c r="D59" s="6">
+      <c r="C59" s="5">
         <v>-18.04</v>
       </c>
-      <c r="E59" s="8">
-        <v>55.16</v>
+      <c r="D59" s="5">
+        <v>58.49</v>
+      </c>
+      <c r="E59" s="6">
+        <v>76.53</v>
       </c>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="6">
-        <v>-35.54</v>
-      </c>
-      <c r="D60" s="6">
+      <c r="C60" s="5">
         <v>265.13</v>
       </c>
-      <c r="E60" s="8">
-        <v>300.67</v>
+      <c r="D60" s="5">
+        <v>45.71</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-219.42</v>
       </c>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C61" s="6">
-        <v>-30.6</v>
-      </c>
-      <c r="D61" s="6">
+      <c r="C61" s="5">
         <v>93.94</v>
       </c>
-      <c r="E61" s="8">
-        <v>124.54</v>
+      <c r="D61" s="5">
+        <v>-3.04</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-96.98</v>
       </c>
     </row>
     <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C62" s="6">
-        <v>-33.54</v>
-      </c>
-      <c r="D62" s="6">
+      <c r="C62" s="5">
         <v>-61.63</v>
       </c>
+      <c r="D62" s="5">
+        <v>-67.48999999999999</v>
+      </c>
       <c r="E62" s="7">
-        <v>-28.09</v>
+        <v>-5.86</v>
       </c>
     </row>
     <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C63" s="6">
-        <v>-16.34</v>
-      </c>
-      <c r="D63" s="6">
+      <c r="C63" s="5">
         <v>41.91</v>
       </c>
-      <c r="E63" s="8">
-        <v>58.25</v>
+      <c r="D63" s="5">
+        <v>-26.96</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-68.87</v>
       </c>
     </row>
     <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C64" s="6">
-        <v>231.79</v>
-      </c>
-      <c r="D64" s="6">
+      <c r="C64" s="5">
         <v>22.11</v>
       </c>
-      <c r="E64" s="7">
-        <v>-209.68</v>
+      <c r="D64" s="5">
+        <v>143.75</v>
+      </c>
+      <c r="E64" s="6">
+        <v>121.64</v>
       </c>
     </row>
     <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C65" s="6">
-        <v>143.26</v>
-      </c>
-      <c r="D65" s="6">
+      <c r="C65" s="5">
         <v>139.5</v>
       </c>
+      <c r="D65" s="5">
+        <v>-49.72</v>
+      </c>
       <c r="E65" s="7">
-        <v>-3.76</v>
+        <v>-189.22</v>
       </c>
     </row>
   </sheetData>
@@ -2952,60 +2889,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
-        <v>44.24</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="10">
+        <v>49.96</v>
+      </c>
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>32.3</v>
-      </c>
-      <c r="E2" s="11">
-        <v>28.6</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-13.8</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-9.199999999999999</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="10">
+        <v>36.1</v>
+      </c>
+      <c r="E2" s="10">
+        <v>42.9</v>
+      </c>
+      <c r="F2" s="10">
+        <v>-13.2</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>14.3</v>
       </c>
     </row>
@@ -3107,49 +3044,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.4186</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2414</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.207</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.171</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.1083</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.07679999999999999</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0434</v>
+      <c r="A2" s="13">
+        <v>0.4111</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2436</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.1929</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1743</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.109</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.0576</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="72">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,7 +169,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>26.0 → 30.3</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>26.0</t>
+  </si>
+  <si>
+    <t>30.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -371,17 +398,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -893,10 +921,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1129.2</v>
+        <v>1097.7</v>
       </c>
       <c r="D2">
-        <v>9.76</v>
+        <v>-2.79</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -905,46 +933,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-12.9</v>
+        <v>-15.33</v>
       </c>
       <c r="H2">
-        <v>50.89</v>
+        <v>46.68</v>
       </c>
       <c r="I2">
-        <v>1.72</v>
+        <v>0.8</v>
       </c>
       <c r="J2">
-        <v>-10.7</v>
+        <v>-15.33</v>
       </c>
       <c r="K2">
-        <v>6.1</v>
+        <v>2.29</v>
       </c>
       <c r="L2">
-        <v>26.74</v>
+        <v>20.87</v>
       </c>
       <c r="M2">
-        <v>5.76</v>
+        <v>5.33</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="P2">
-        <v>1072.32</v>
+        <v>1074.06</v>
       </c>
       <c r="Q2">
-        <v>1177.64</v>
+        <v>1168.6</v>
       </c>
       <c r="R2">
-        <v>1145.52</v>
+        <v>1143.79</v>
       </c>
       <c r="S2">
-        <v>999</v>
+        <v>1000.31</v>
       </c>
       <c r="T2">
-        <v>13.03</v>
+        <v>9.74</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -959,34 +987,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>47.93</v>
+        <v>44.24</v>
       </c>
       <c r="Z2">
-        <v>-24.47</v>
+        <v>-24.43</v>
       </c>
       <c r="AA2">
-        <v>-7.27</v>
+        <v>-10.7</v>
       </c>
       <c r="AB2">
-        <v>-17.2</v>
+        <v>-13.73</v>
       </c>
       <c r="AC2">
-        <v>17.93</v>
+        <v>33.05</v>
       </c>
       <c r="AD2">
-        <v>5.98</v>
+        <v>16.99</v>
       </c>
       <c r="AE2">
-        <v>59.67</v>
+        <v>60.11</v>
       </c>
       <c r="AF2">
-        <v>58.49</v>
+        <v>-14.39</v>
       </c>
       <c r="AG2">
-        <v>1337.38</v>
+        <v>1324.73</v>
       </c>
       <c r="AH2">
-        <v>1017.91</v>
+        <v>1012.48</v>
       </c>
       <c r="AI2">
         <v>1168</v>
@@ -995,7 +1023,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>41.75</v>
+        <v>37.45</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,10 +1034,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>833.25</v>
+        <v>835.4</v>
       </c>
       <c r="D3">
-        <v>2.45</v>
+        <v>0.26</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1018,46 +1046,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-14.67</v>
+        <v>-14.45</v>
       </c>
       <c r="H3">
-        <v>57.37</v>
+        <v>57.78</v>
       </c>
       <c r="I3">
-        <v>-1.51</v>
+        <v>-2.29</v>
       </c>
       <c r="J3">
-        <v>-6.9</v>
+        <v>-5.79</v>
       </c>
       <c r="K3">
-        <v>-3.97</v>
+        <v>-4.78</v>
       </c>
       <c r="L3">
-        <v>12.83</v>
+        <v>13.29</v>
       </c>
       <c r="M3">
-        <v>41.11</v>
+        <v>39.83</v>
       </c>
       <c r="N3">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O3">
         <v>79</v>
       </c>
       <c r="P3">
-        <v>827.9400000000001</v>
+        <v>824.02</v>
       </c>
       <c r="Q3">
-        <v>856.84</v>
+        <v>854.3099999999999</v>
       </c>
       <c r="R3">
-        <v>876.23</v>
+        <v>875.21</v>
       </c>
       <c r="S3">
-        <v>809.52</v>
+        <v>810.52</v>
       </c>
       <c r="T3">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1072,34 +1100,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>44.14</v>
+        <v>44.7</v>
       </c>
       <c r="Z3">
-        <v>-16</v>
+        <v>-15.28</v>
       </c>
       <c r="AA3">
-        <v>-12.03</v>
+        <v>-12.68</v>
       </c>
       <c r="AB3">
-        <v>-3.97</v>
+        <v>-2.6</v>
       </c>
       <c r="AC3">
-        <v>18.92</v>
+        <v>31.68</v>
       </c>
       <c r="AD3">
-        <v>18.67</v>
+        <v>20.97</v>
       </c>
       <c r="AE3">
-        <v>31.29</v>
+        <v>30.49</v>
       </c>
       <c r="AF3">
-        <v>45.71</v>
+        <v>-18.6</v>
       </c>
       <c r="AG3">
-        <v>910.46</v>
+        <v>906.9</v>
       </c>
       <c r="AH3">
-        <v>803.23</v>
+        <v>801.72</v>
       </c>
       <c r="AI3">
         <v>888.53</v>
@@ -1108,7 +1136,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>32.17</v>
+        <v>31.23</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,10 +1147,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1447.9</v>
+        <v>1469</v>
       </c>
       <c r="D4">
-        <v>-1.09</v>
+        <v>1.46</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1131,46 +1159,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-25.37</v>
+        <v>-24.28</v>
       </c>
       <c r="H4">
-        <v>6.88</v>
+        <v>8.44</v>
       </c>
       <c r="I4">
-        <v>-8.029999999999999</v>
+        <v>-5.41</v>
       </c>
       <c r="J4">
-        <v>-18.38</v>
+        <v>-12.65</v>
       </c>
       <c r="K4">
-        <v>-16.03</v>
+        <v>-17.71</v>
       </c>
       <c r="L4">
-        <v>-13.41</v>
+        <v>-11.99</v>
       </c>
       <c r="M4">
-        <v>19.29</v>
+        <v>18.91</v>
       </c>
       <c r="N4">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="O4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P4">
-        <v>1505.1</v>
+        <v>1488.3</v>
       </c>
       <c r="Q4">
-        <v>1574.36</v>
+        <v>1564.68</v>
       </c>
       <c r="R4">
-        <v>1730.31</v>
+        <v>1721.13</v>
       </c>
       <c r="S4">
-        <v>1670.5</v>
+        <v>1668.82</v>
       </c>
       <c r="T4">
-        <v>-13.33</v>
+        <v>-11.97</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1185,34 +1213,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>25.98</v>
+        <v>30.27</v>
       </c>
       <c r="Z4">
-        <v>-66.66</v>
+        <v>-67.54000000000001</v>
       </c>
       <c r="AA4">
-        <v>-60.66</v>
+        <v>-62.03</v>
       </c>
       <c r="AB4">
-        <v>-6</v>
+        <v>-5.5</v>
       </c>
       <c r="AC4">
-        <v>27.15</v>
+        <v>20.3</v>
       </c>
       <c r="AD4">
-        <v>43.26</v>
+        <v>30.03</v>
       </c>
       <c r="AE4">
-        <v>49</v>
+        <v>47.52</v>
       </c>
       <c r="AF4">
-        <v>-3.04</v>
+        <v>-4.36</v>
       </c>
       <c r="AG4">
-        <v>1681.76</v>
+        <v>1673.46</v>
       </c>
       <c r="AH4">
-        <v>1466.96</v>
+        <v>1455.89</v>
       </c>
       <c r="AI4">
         <v>1583.31</v>
@@ -1221,7 +1249,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>60.38</v>
+        <v>60.64</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1260,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1730.6</v>
+        <v>1738.4</v>
       </c>
       <c r="D5">
-        <v>0.73</v>
+        <v>0.45</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1244,46 +1272,46 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-27.85</v>
+        <v>-27.53</v>
       </c>
       <c r="H5">
-        <v>3.4</v>
+        <v>3.87</v>
       </c>
       <c r="I5">
-        <v>-1.59</v>
+        <v>-1.85</v>
       </c>
       <c r="J5">
-        <v>-11.52</v>
+        <v>-10.51</v>
       </c>
       <c r="K5">
-        <v>-12.63</v>
+        <v>-13.24</v>
       </c>
       <c r="L5">
-        <v>-20.12</v>
+        <v>-19.91</v>
       </c>
       <c r="M5">
-        <v>17.43</v>
+        <v>17.67</v>
       </c>
       <c r="N5">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="O5">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P5">
-        <v>1757.6</v>
+        <v>1751.06</v>
       </c>
       <c r="Q5">
-        <v>1768.1</v>
+        <v>1756.83</v>
       </c>
       <c r="R5">
-        <v>1887.17</v>
+        <v>1880.16</v>
       </c>
       <c r="S5">
-        <v>2015.28</v>
+        <v>2012.45</v>
       </c>
       <c r="T5">
-        <v>-14.13</v>
+        <v>-13.62</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1298,34 +1326,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>39.45</v>
+        <v>40.78</v>
       </c>
       <c r="Z5">
-        <v>-43.1</v>
+        <v>-41.46</v>
       </c>
       <c r="AA5">
-        <v>-49.28</v>
+        <v>-47.71</v>
       </c>
       <c r="AB5">
-        <v>6.17</v>
+        <v>6.25</v>
       </c>
       <c r="AC5">
-        <v>72.14</v>
+        <v>66.92</v>
       </c>
       <c r="AD5">
-        <v>83.89</v>
+        <v>73.93000000000001</v>
       </c>
       <c r="AE5">
-        <v>58.88</v>
+        <v>58.17</v>
       </c>
       <c r="AF5">
-        <v>-67.48999999999999</v>
+        <v>-57.25</v>
       </c>
       <c r="AG5">
-        <v>1901.54</v>
+        <v>1853.7</v>
       </c>
       <c r="AH5">
-        <v>1634.67</v>
+        <v>1659.96</v>
       </c>
       <c r="AI5">
         <v>1853.75</v>
@@ -1334,7 +1362,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>23.45</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,58 +1373,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>621.95</v>
+        <v>620.7</v>
       </c>
       <c r="D6">
-        <v>-0.88</v>
+        <v>-0.2</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
       </c>
       <c r="F6">
-        <v>621.95</v>
+        <v>620.7</v>
       </c>
       <c r="G6">
-        <v>-42.93</v>
+        <v>-43.04</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-10.4</v>
+        <v>-7.91</v>
       </c>
       <c r="J6">
-        <v>-11.33</v>
+        <v>-9.98</v>
       </c>
       <c r="K6">
-        <v>-17.95</v>
+        <v>-19.51</v>
       </c>
       <c r="L6">
-        <v>-39.53</v>
+        <v>-40.27</v>
       </c>
       <c r="M6">
-        <v>7.1</v>
+        <v>7.45</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="P6">
-        <v>645.6</v>
+        <v>634.9299999999999</v>
       </c>
       <c r="Q6">
-        <v>682.33</v>
+        <v>678.13</v>
       </c>
       <c r="R6">
-        <v>730.12</v>
+        <v>726.9299999999999</v>
       </c>
       <c r="S6">
-        <v>796.86</v>
+        <v>794.97</v>
       </c>
       <c r="T6">
-        <v>-21.95</v>
+        <v>-21.92</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1411,43 +1439,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>26.92</v>
+        <v>26.69</v>
       </c>
       <c r="Z6">
-        <v>-22.88</v>
+        <v>-24.75</v>
       </c>
       <c r="AA6">
-        <v>-17.93</v>
+        <v>-19.3</v>
       </c>
       <c r="AB6">
-        <v>-4.95</v>
+        <v>-5.46</v>
       </c>
       <c r="AC6">
-        <v>6.54</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>19.1</v>
+        <v>7.76</v>
       </c>
       <c r="AE6">
-        <v>20</v>
+        <v>19.56</v>
       </c>
       <c r="AF6">
-        <v>-26.96</v>
+        <v>-45.63</v>
       </c>
       <c r="AG6">
-        <v>732.95</v>
+        <v>734.54</v>
       </c>
       <c r="AH6">
-        <v>631.7</v>
+        <v>621.71</v>
       </c>
       <c r="AI6">
-        <v>684.88</v>
+        <v>682.24</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>38.02</v>
+        <v>41.83</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,10 +1486,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2538.6</v>
+        <v>2632.6</v>
       </c>
       <c r="D7">
-        <v>1.24</v>
+        <v>3.7</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1470,46 +1498,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-26.52</v>
+        <v>-23.8</v>
       </c>
       <c r="H7">
-        <v>34.21</v>
+        <v>39.18</v>
       </c>
       <c r="I7">
-        <v>-3.49</v>
+        <v>3.03</v>
       </c>
       <c r="J7">
-        <v>-15.94</v>
+        <v>-13.2</v>
       </c>
       <c r="K7">
-        <v>-1.09</v>
+        <v>1.53</v>
       </c>
       <c r="L7">
-        <v>7.85</v>
+        <v>10.83</v>
       </c>
       <c r="M7">
-        <v>24.36</v>
+        <v>25.48</v>
       </c>
       <c r="N7">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O7">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="P7">
-        <v>2506.92</v>
+        <v>2522.4</v>
       </c>
       <c r="Q7">
-        <v>2696.84</v>
+        <v>2678.3</v>
       </c>
       <c r="R7">
-        <v>2988.49</v>
+        <v>2983.39</v>
       </c>
       <c r="S7">
-        <v>2532.43</v>
+        <v>2534.43</v>
       </c>
       <c r="T7">
-        <v>0.24</v>
+        <v>3.87</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1524,34 +1552,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>35.29</v>
+        <v>43.21</v>
       </c>
       <c r="Z7">
-        <v>-131.84</v>
+        <v>-119.35</v>
       </c>
       <c r="AA7">
-        <v>-121.62</v>
+        <v>-121.16</v>
       </c>
       <c r="AB7">
-        <v>-10.22</v>
+        <v>1.81</v>
       </c>
       <c r="AC7">
-        <v>85.78</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="AD7">
-        <v>65.7</v>
+        <v>81.27</v>
       </c>
       <c r="AE7">
-        <v>132.98</v>
+        <v>131.22</v>
       </c>
       <c r="AF7">
-        <v>143.75</v>
+        <v>-29.93</v>
       </c>
       <c r="AG7">
-        <v>3033.88</v>
+        <v>2983.63</v>
       </c>
       <c r="AH7">
-        <v>2359.8</v>
+        <v>2372.97</v>
       </c>
       <c r="AI7">
         <v>2851.41</v>
@@ -1560,7 +1588,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>63.51</v>
+        <v>58.32</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1571,58 +1599,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>7138</v>
+        <v>6969</v>
       </c>
       <c r="D8">
-        <v>0.65</v>
+        <v>-2.37</v>
       </c>
       <c r="E8">
-        <v>9108.879999999999</v>
+        <v>9054.049999999999</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-21.64</v>
+        <v>-23.03</v>
       </c>
       <c r="H8">
-        <v>20.48</v>
+        <v>17.63</v>
       </c>
       <c r="I8">
-        <v>-9.32</v>
+        <v>-9.359999999999999</v>
       </c>
       <c r="J8">
-        <v>-17.75</v>
+        <v>-18.26</v>
       </c>
       <c r="K8">
-        <v>-11.6</v>
+        <v>-16.06</v>
       </c>
       <c r="L8">
-        <v>-19.56</v>
+        <v>-23.49</v>
       </c>
       <c r="M8">
-        <v>10.9</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="N8">
         <v>29</v>
       </c>
       <c r="O8">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="P8">
-        <v>7242.4</v>
+        <v>7098.4</v>
       </c>
       <c r="Q8">
-        <v>7835.9</v>
+        <v>7752.05</v>
       </c>
       <c r="R8">
-        <v>8131.55</v>
+        <v>8111.23</v>
       </c>
       <c r="S8">
-        <v>7418.76</v>
+        <v>7415.1</v>
       </c>
       <c r="T8">
-        <v>-3.78</v>
+        <v>-6.02</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1637,34 +1665,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>33.2</v>
+        <v>30.69</v>
       </c>
       <c r="Z8">
-        <v>-298.63</v>
+        <v>-320.68</v>
       </c>
       <c r="AA8">
-        <v>-206.73</v>
+        <v>-229.52</v>
       </c>
       <c r="AB8">
-        <v>-91.90000000000001</v>
+        <v>-91.16</v>
       </c>
       <c r="AC8">
-        <v>27.82</v>
+        <v>38.26</v>
       </c>
       <c r="AD8">
-        <v>17.07</v>
+        <v>26.21</v>
       </c>
       <c r="AE8">
-        <v>350.89</v>
+        <v>351.79</v>
       </c>
       <c r="AF8">
-        <v>-49.72</v>
+        <v>-32.9</v>
       </c>
       <c r="AG8">
-        <v>8757.92</v>
+        <v>8668.879999999999</v>
       </c>
       <c r="AH8">
-        <v>6913.88</v>
+        <v>6835.22</v>
       </c>
       <c r="AI8">
         <v>7963.93</v>
@@ -1673,7 +1701,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>45.77</v>
+        <v>49.01</v>
       </c>
     </row>
   </sheetData>
@@ -1814,7 +1842,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1834,12 +1862,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>49</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1847,1023 +1910,1040 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
+      <c r="B6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-15.07</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-10.7</v>
       </c>
-      <c r="E7" s="6">
-        <v>4.37</v>
+      <c r="D7" s="6">
+        <v>-15.33</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-4.63</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-9.23</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-6.9</v>
       </c>
-      <c r="E8" s="6">
-        <v>2.33</v>
+      <c r="D8" s="6">
+        <v>-5.79</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1.11</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-16.79</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-18.38</v>
       </c>
-      <c r="E9" s="7">
+      <c r="D9" s="6">
+        <v>-12.65</v>
+      </c>
+      <c r="E9" s="8">
+        <v>5.73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-11.52</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-10.51</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-11.33</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-9.98</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-15.94</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-13.2</v>
+      </c>
+      <c r="E12" s="8">
+        <v>2.74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-17.75</v>
+      </c>
+      <c r="D13" s="6">
+        <v>-18.26</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6">
+        <v>1.72</v>
+      </c>
+      <c r="D14" s="6">
+        <v>0.8</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-1.51</v>
+      </c>
+      <c r="D15" s="6">
+        <v>-2.29</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-8.029999999999999</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-5.41</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
         <v>-1.59</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D17" s="6">
+        <v>-1.85</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-10.4</v>
+      </c>
+      <c r="D18" s="6">
+        <v>-7.91</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-3.49</v>
+      </c>
+      <c r="D19" s="6">
+        <v>3.03</v>
+      </c>
+      <c r="E19" s="8">
+        <v>6.52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-9.32</v>
+      </c>
+      <c r="D20" s="6">
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.04</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>26.74</v>
+      </c>
+      <c r="D21" s="6">
+        <v>20.87</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-5.87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="6">
+        <v>12.83</v>
+      </c>
+      <c r="D22" s="6">
+        <v>13.29</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-13.41</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-11.99</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-11.67</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-11.52</v>
-      </c>
-      <c r="E10" s="6">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-20.12</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-19.91</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>-9.779999999999999</v>
-      </c>
-      <c r="D11" s="5">
-        <v>-11.33</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-39.53</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-40.27</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>7.85</v>
+      </c>
+      <c r="D26" s="6">
+        <v>10.83</v>
+      </c>
+      <c r="E26" s="8">
+        <v>2.98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5">
-        <v>-17.79</v>
-      </c>
-      <c r="D12" s="5">
-        <v>-17.75</v>
-      </c>
-      <c r="E12" s="6">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-19.56</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-23.49</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-3.93</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-6.85</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1.72</v>
-      </c>
-      <c r="E13" s="6">
-        <v>8.57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>6.1</v>
+      </c>
+      <c r="D28" s="6">
+        <v>2.29</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-3.81</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-0.57</v>
-      </c>
-      <c r="D14" s="5">
-        <v>-1.51</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-3.97</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-4.78</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-7.7</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-8.029999999999999</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-16.03</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-17.71</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.68</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>-2.68</v>
-      </c>
-      <c r="D16" s="5">
-        <v>-1.59</v>
-      </c>
-      <c r="E16" s="6">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="5">
-        <v>-10.61</v>
-      </c>
-      <c r="D17" s="5">
-        <v>-10.4</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="5">
-        <v>-3.01</v>
-      </c>
-      <c r="D18" s="5">
-        <v>-3.49</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-8.24</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-9.32</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.08</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>13.99</v>
-      </c>
-      <c r="D20" s="5">
-        <v>26.74</v>
-      </c>
-      <c r="E20" s="6">
-        <v>12.75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>7.58</v>
-      </c>
-      <c r="D21" s="5">
-        <v>12.83</v>
-      </c>
-      <c r="E21" s="6">
-        <v>5.25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="5">
-        <v>-11.45</v>
-      </c>
-      <c r="D22" s="5">
-        <v>-13.41</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-1.96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="5">
-        <v>-19.65</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-20.12</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-38.61</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-39.53</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>7</v>
-      </c>
-      <c r="D25" s="5">
-        <v>7.85</v>
-      </c>
-      <c r="E25" s="6">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-18.33</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-19.56</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="5">
-        <v>-2.58</v>
-      </c>
-      <c r="D27" s="5">
-        <v>6.1</v>
-      </c>
-      <c r="E27" s="6">
-        <v>8.68</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-7.97</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-3.97</v>
-      </c>
-      <c r="E28" s="6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-14.76</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-16.03</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-15.07</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C31" s="6">
         <v>-12.63</v>
       </c>
-      <c r="E30" s="6">
-        <v>2.44</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-17.34</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-17.95</v>
+      <c r="D31" s="6">
+        <v>-13.24</v>
       </c>
       <c r="E31" s="7">
         <v>-0.61</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-17.95</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-19.51</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="5">
-        <v>-2.27</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C33" s="6">
         <v>-1.09</v>
       </c>
-      <c r="E32" s="6">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="D33" s="6">
+        <v>1.53</v>
+      </c>
+      <c r="E33" s="8">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="5">
-        <v>-4.5</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C34" s="6">
         <v>-11.6</v>
       </c>
-      <c r="E33" s="7">
-        <v>-7.1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="D34" s="6">
+        <v>-16.06</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-4.46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="5">
-        <v>-20.65</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C35" s="6">
         <v>-12.9</v>
       </c>
-      <c r="E34" s="6">
-        <v>7.75</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="D35" s="6">
+        <v>-15.33</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C35" s="5">
-        <v>-16.71</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C36" s="6">
         <v>-14.67</v>
       </c>
-      <c r="E35" s="6">
-        <v>2.04</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="D36" s="6">
+        <v>-14.45</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C36" s="5">
-        <v>-24.55</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C37" s="6">
         <v>-25.37</v>
       </c>
-      <c r="E36" s="7">
-        <v>-0.82</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="D37" s="6">
+        <v>-24.28</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1.09</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B38" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="5">
-        <v>-28.38</v>
-      </c>
-      <c r="D37" s="5">
+      <c r="C38" s="6">
         <v>-27.85</v>
       </c>
-      <c r="E37" s="6">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="D38" s="6">
+        <v>-27.53</v>
+      </c>
+      <c r="E38" s="8">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B39" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="5">
-        <v>-42.42</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="C39" s="6">
         <v>-42.93</v>
       </c>
-      <c r="E38" s="7">
-        <v>-0.51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="D39" s="6">
+        <v>-43.04</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="5">
-        <v>-27.42</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="C40" s="6">
         <v>-26.52</v>
       </c>
-      <c r="E39" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="D40" s="6">
+        <v>-23.8</v>
+      </c>
+      <c r="E40" s="8">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C40" s="5">
-        <v>-22.14</v>
-      </c>
-      <c r="D40" s="5">
+      <c r="C41" s="6">
         <v>-21.64</v>
       </c>
-      <c r="E40" s="6">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="D41" s="6">
+        <v>-23.03</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B42" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="5">
-        <v>1028.8</v>
-      </c>
-      <c r="D41" s="5">
+      <c r="C42" s="6">
         <v>1129.2</v>
       </c>
-      <c r="E41" s="6">
-        <v>100.4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="D42" s="6">
+        <v>1097.7</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-31.5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B43" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="5">
-        <v>813.35</v>
-      </c>
-      <c r="D42" s="5">
+      <c r="C43" s="6">
         <v>833.25</v>
       </c>
-      <c r="E42" s="6">
-        <v>19.9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="D43" s="6">
+        <v>835.4</v>
+      </c>
+      <c r="E43" s="8">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B44" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C43" s="5">
-        <v>1463.8</v>
-      </c>
-      <c r="D43" s="5">
+      <c r="C44" s="6">
         <v>1447.9</v>
       </c>
-      <c r="E43" s="7">
-        <v>-15.9</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
+      <c r="D44" s="6">
+        <v>1469</v>
+      </c>
+      <c r="E44" s="8">
+        <v>21.1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B45" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C44" s="5">
-        <v>1718</v>
-      </c>
-      <c r="D44" s="5">
+      <c r="C45" s="6">
         <v>1730.6</v>
       </c>
-      <c r="E44" s="6">
-        <v>12.6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
+      <c r="D45" s="6">
+        <v>1738.4</v>
+      </c>
+      <c r="E45" s="8">
+        <v>7.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="5">
-        <v>627.5</v>
-      </c>
-      <c r="D45" s="5">
+      <c r="C46" s="6">
         <v>621.95</v>
       </c>
-      <c r="E45" s="7">
-        <v>-5.55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
+      <c r="D46" s="6">
+        <v>620.7</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B47" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C46" s="5">
-        <v>2507.6</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C47" s="6">
         <v>2538.6</v>
       </c>
-      <c r="E46" s="6">
+      <c r="D47" s="6">
+        <v>2632.6</v>
+      </c>
+      <c r="E47" s="8">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>7138</v>
+      </c>
+      <c r="D48" s="6">
+        <v>6969</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-169</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="6">
+        <v>85</v>
+      </c>
+      <c r="D49" s="6">
+        <v>71</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" s="6">
+        <v>43</v>
+      </c>
+      <c r="D50" s="6">
+        <v>57</v>
+      </c>
+      <c r="E50" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" s="6">
+        <v>57</v>
+      </c>
+      <c r="D51" s="6">
+        <v>43</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C52" s="6">
+        <v>71</v>
+      </c>
+      <c r="D52" s="6">
+        <v>85</v>
+      </c>
+      <c r="E52" s="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>47.93</v>
+      </c>
+      <c r="D53" s="6">
+        <v>44.24</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-3.69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>44.14</v>
+      </c>
+      <c r="D54" s="6">
+        <v>44.7</v>
+      </c>
+      <c r="E54" s="8">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>25.98</v>
+      </c>
+      <c r="D55" s="6">
+        <v>30.27</v>
+      </c>
+      <c r="E55" s="8">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C56" s="6">
+        <v>39.45</v>
+      </c>
+      <c r="D56" s="6">
+        <v>40.78</v>
+      </c>
+      <c r="E56" s="8">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C57" s="6">
+        <v>26.92</v>
+      </c>
+      <c r="D57" s="6">
+        <v>26.69</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="6">
+        <v>35.29</v>
+      </c>
+      <c r="D58" s="6">
+        <v>43.21</v>
+      </c>
+      <c r="E58" s="8">
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C59" s="6">
+        <v>33.2</v>
+      </c>
+      <c r="D59" s="6">
+        <v>30.69</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-2.51</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
+      <c r="C60" s="6">
+        <v>58.49</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-14.39</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-72.88</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>45.71</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-18.6</v>
+      </c>
+      <c r="E61" s="7">
+        <v>-64.31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C62" s="6">
+        <v>-3.04</v>
+      </c>
+      <c r="D62" s="6">
+        <v>-4.36</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="6">
+        <v>-67.48999999999999</v>
+      </c>
+      <c r="D63" s="6">
+        <v>-57.25</v>
+      </c>
+      <c r="E63" s="8">
+        <v>10.24</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64" s="6">
+        <v>-26.96</v>
+      </c>
+      <c r="D64" s="6">
+        <v>-45.63</v>
+      </c>
+      <c r="E64" s="7">
+        <v>-18.67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="6">
+        <v>143.75</v>
+      </c>
+      <c r="D65" s="6">
+        <v>-29.93</v>
+      </c>
+      <c r="E65" s="7">
+        <v>-173.68</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="5">
-        <v>7092</v>
-      </c>
-      <c r="D47" s="5">
-        <v>7138</v>
-      </c>
-      <c r="E47" s="6">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" s="5">
-        <v>71</v>
-      </c>
-      <c r="D48" s="5">
-        <v>85</v>
-      </c>
-      <c r="E48" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="5">
-        <v>29</v>
-      </c>
-      <c r="D49" s="5">
-        <v>57</v>
-      </c>
-      <c r="E49" s="6">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="5">
-        <v>85</v>
-      </c>
-      <c r="D50" s="5">
-        <v>71</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="5">
-        <v>57</v>
-      </c>
-      <c r="D51" s="5">
-        <v>29</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-28</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>30.81</v>
-      </c>
-      <c r="D52" s="5">
-        <v>47.93</v>
-      </c>
-      <c r="E52" s="6">
-        <v>17.12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>38.78</v>
-      </c>
-      <c r="D53" s="5">
-        <v>44.14</v>
-      </c>
-      <c r="E53" s="6">
-        <v>5.36</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>27.15</v>
-      </c>
-      <c r="D54" s="5">
-        <v>25.98</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-1.17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="5">
-        <v>37.34</v>
-      </c>
-      <c r="D55" s="5">
-        <v>39.45</v>
-      </c>
-      <c r="E55" s="6">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="5">
-        <v>27.9</v>
-      </c>
-      <c r="D56" s="5">
-        <v>26.92</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-0.98</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="5">
-        <v>32.41</v>
-      </c>
-      <c r="D57" s="5">
-        <v>35.29</v>
-      </c>
-      <c r="E57" s="6">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="5">
-        <v>31.79</v>
-      </c>
-      <c r="D58" s="5">
-        <v>33.2</v>
-      </c>
-      <c r="E58" s="6">
-        <v>1.41</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B59" s="3" t="s">
+      <c r="B66" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C59" s="5">
-        <v>-18.04</v>
-      </c>
-      <c r="D59" s="5">
-        <v>58.49</v>
-      </c>
-      <c r="E59" s="6">
-        <v>76.53</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>265.13</v>
-      </c>
-      <c r="D60" s="5">
-        <v>45.71</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-219.42</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>93.94</v>
-      </c>
-      <c r="D61" s="5">
-        <v>-3.04</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-96.98</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="5">
-        <v>-61.63</v>
-      </c>
-      <c r="D62" s="5">
-        <v>-67.48999999999999</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-5.86</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="5">
-        <v>41.91</v>
-      </c>
-      <c r="D63" s="5">
-        <v>-26.96</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-68.87</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="5">
-        <v>22.11</v>
-      </c>
-      <c r="D64" s="5">
-        <v>143.75</v>
-      </c>
-      <c r="E64" s="6">
-        <v>121.64</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="5">
-        <v>139.5</v>
-      </c>
-      <c r="D65" s="5">
+      <c r="C66" s="6">
         <v>-49.72</v>
       </c>
-      <c r="E65" s="7">
-        <v>-189.22</v>
+      <c r="D66" s="6">
+        <v>-32.9</v>
+      </c>
+      <c r="E66" s="8">
+        <v>16.82</v>
       </c>
     </row>
   </sheetData>
@@ -2889,60 +2969,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>49.96</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>37.2</v>
+      </c>
+      <c r="E2" s="11">
+        <v>42.9</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-12.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-9.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>49.96</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>36.1</v>
-      </c>
-      <c r="E2" s="10">
-        <v>42.9</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-13.2</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-8.199999999999999</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>14.3</v>
       </c>
     </row>
@@ -3044,49 +3124,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.4111</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2436</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.1929</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1743</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.109</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0576</v>
+      <c r="A2" s="14">
+        <v>0.3983</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2548</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.1891</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1767</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.09039999999999999</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.0745</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0533</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="63">
   <si>
     <t>Symbol</t>
   </si>
@@ -169,34 +169,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>26.0 → 30.3</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>26.0</t>
-  </si>
-  <si>
-    <t>30.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -398,18 +371,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -921,10 +893,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1097.7</v>
+        <v>1086.1</v>
       </c>
       <c r="D2">
-        <v>-2.79</v>
+        <v>-1.06</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -933,46 +905,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-15.33</v>
+        <v>-16.23</v>
       </c>
       <c r="H2">
-        <v>46.68</v>
+        <v>45.13</v>
       </c>
       <c r="I2">
-        <v>0.8</v>
+        <v>2.47</v>
       </c>
       <c r="J2">
-        <v>-15.33</v>
+        <v>-15.05</v>
       </c>
       <c r="K2">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="L2">
-        <v>20.87</v>
+        <v>20.02</v>
       </c>
       <c r="M2">
-        <v>5.33</v>
+        <v>5.47</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>1074.06</v>
+        <v>1079.3</v>
       </c>
       <c r="Q2">
-        <v>1168.6</v>
+        <v>1160.52</v>
       </c>
       <c r="R2">
-        <v>1143.79</v>
+        <v>1142.48</v>
       </c>
       <c r="S2">
-        <v>1000.31</v>
+        <v>1001.63</v>
       </c>
       <c r="T2">
-        <v>9.74</v>
+        <v>8.43</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -987,34 +959,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>44.24</v>
+        <v>42.92</v>
       </c>
       <c r="Z2">
-        <v>-24.43</v>
+        <v>-25.04</v>
       </c>
       <c r="AA2">
-        <v>-10.7</v>
+        <v>-13.57</v>
       </c>
       <c r="AB2">
-        <v>-13.73</v>
+        <v>-11.47</v>
       </c>
       <c r="AC2">
-        <v>33.05</v>
+        <v>51.25</v>
       </c>
       <c r="AD2">
-        <v>16.99</v>
+        <v>34.08</v>
       </c>
       <c r="AE2">
-        <v>60.11</v>
+        <v>57.23</v>
       </c>
       <c r="AF2">
-        <v>-14.39</v>
+        <v>-76.09</v>
       </c>
       <c r="AG2">
-        <v>1324.73</v>
+        <v>1316.13</v>
       </c>
       <c r="AH2">
-        <v>1012.48</v>
+        <v>1004.91</v>
       </c>
       <c r="AI2">
         <v>1168</v>
@@ -1023,7 +995,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>37.45</v>
+        <v>33.74</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1034,10 +1006,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>835.4</v>
+        <v>832.3</v>
       </c>
       <c r="D3">
-        <v>0.26</v>
+        <v>-0.37</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1046,46 +1018,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-14.45</v>
+        <v>-14.77</v>
       </c>
       <c r="H3">
-        <v>57.78</v>
+        <v>57.19</v>
       </c>
       <c r="I3">
-        <v>-2.29</v>
+        <v>1.38</v>
       </c>
       <c r="J3">
-        <v>-5.79</v>
+        <v>-6.06</v>
       </c>
       <c r="K3">
-        <v>-4.78</v>
+        <v>-1.4</v>
       </c>
       <c r="L3">
-        <v>13.29</v>
+        <v>13.82</v>
       </c>
       <c r="M3">
-        <v>39.83</v>
+        <v>41.15</v>
       </c>
       <c r="N3">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="O3">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P3">
-        <v>824.02</v>
+        <v>826.28</v>
       </c>
       <c r="Q3">
-        <v>854.3099999999999</v>
+        <v>852.6799999999999</v>
       </c>
       <c r="R3">
-        <v>875.21</v>
+        <v>874.05</v>
       </c>
       <c r="S3">
-        <v>810.52</v>
+        <v>811.5</v>
       </c>
       <c r="T3">
-        <v>3.07</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1100,34 +1072,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>44.7</v>
+        <v>44.01</v>
       </c>
       <c r="Z3">
-        <v>-15.28</v>
+        <v>-14.79</v>
       </c>
       <c r="AA3">
-        <v>-12.68</v>
+        <v>-13.1</v>
       </c>
       <c r="AB3">
-        <v>-2.6</v>
+        <v>-1.69</v>
       </c>
       <c r="AC3">
-        <v>31.68</v>
+        <v>53.53</v>
       </c>
       <c r="AD3">
-        <v>20.97</v>
+        <v>34.71</v>
       </c>
       <c r="AE3">
-        <v>30.49</v>
+        <v>29.11</v>
       </c>
       <c r="AF3">
-        <v>-18.6</v>
+        <v>-63.39</v>
       </c>
       <c r="AG3">
-        <v>906.9</v>
+        <v>905.9</v>
       </c>
       <c r="AH3">
-        <v>801.72</v>
+        <v>799.46</v>
       </c>
       <c r="AI3">
         <v>888.53</v>
@@ -1136,7 +1108,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>31.23</v>
+        <v>30.41</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1147,10 +1119,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1469</v>
+        <v>1545.2</v>
       </c>
       <c r="D4">
-        <v>1.46</v>
+        <v>5.19</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1159,46 +1131,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-24.28</v>
+        <v>-20.35</v>
       </c>
       <c r="H4">
-        <v>8.44</v>
+        <v>14.06</v>
       </c>
       <c r="I4">
-        <v>-5.41</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>-12.65</v>
+        <v>-7.07</v>
       </c>
       <c r="K4">
-        <v>-17.71</v>
+        <v>-11.85</v>
       </c>
       <c r="L4">
-        <v>-11.99</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="M4">
-        <v>18.91</v>
+        <v>20.69</v>
       </c>
       <c r="N4">
         <v>57</v>
       </c>
       <c r="O4">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="P4">
-        <v>1488.3</v>
+        <v>1491.36</v>
       </c>
       <c r="Q4">
-        <v>1564.68</v>
+        <v>1560.22</v>
       </c>
       <c r="R4">
-        <v>1721.13</v>
+        <v>1714.15</v>
       </c>
       <c r="S4">
-        <v>1668.82</v>
+        <v>1667.63</v>
       </c>
       <c r="T4">
-        <v>-11.97</v>
+        <v>-7.34</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1213,34 +1185,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>30.27</v>
+        <v>43.11</v>
       </c>
       <c r="Z4">
-        <v>-67.54000000000001</v>
+        <v>-61.38</v>
       </c>
       <c r="AA4">
-        <v>-62.03</v>
+        <v>-61.9</v>
       </c>
       <c r="AB4">
-        <v>-5.5</v>
+        <v>0.53</v>
       </c>
       <c r="AC4">
-        <v>20.3</v>
+        <v>48.24</v>
       </c>
       <c r="AD4">
-        <v>30.03</v>
+        <v>31.9</v>
       </c>
       <c r="AE4">
-        <v>47.52</v>
+        <v>51.69</v>
       </c>
       <c r="AF4">
-        <v>-4.36</v>
+        <v>88.61</v>
       </c>
       <c r="AG4">
-        <v>1673.46</v>
+        <v>1664.21</v>
       </c>
       <c r="AH4">
-        <v>1455.89</v>
+        <v>1456.24</v>
       </c>
       <c r="AI4">
         <v>1583.31</v>
@@ -1249,7 +1221,7 @@
         <v>47</v>
       </c>
       <c r="AK4">
-        <v>60.64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1260,10 +1232,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1738.4</v>
+        <v>1703.5</v>
       </c>
       <c r="D5">
-        <v>0.45</v>
+        <v>-2.01</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1272,46 +1244,46 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-27.53</v>
+        <v>-28.98</v>
       </c>
       <c r="H5">
-        <v>3.87</v>
+        <v>1.78</v>
       </c>
       <c r="I5">
-        <v>-1.85</v>
+        <v>-4.92</v>
       </c>
       <c r="J5">
-        <v>-10.51</v>
+        <v>-13.26</v>
       </c>
       <c r="K5">
-        <v>-13.24</v>
+        <v>-15.95</v>
       </c>
       <c r="L5">
-        <v>-19.91</v>
+        <v>-20.97</v>
       </c>
       <c r="M5">
-        <v>17.67</v>
+        <v>17.38</v>
       </c>
       <c r="N5">
         <v>43</v>
       </c>
       <c r="O5">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="P5">
-        <v>1751.06</v>
+        <v>1733.42</v>
       </c>
       <c r="Q5">
-        <v>1756.83</v>
+        <v>1747.05</v>
       </c>
       <c r="R5">
-        <v>1880.16</v>
+        <v>1872.32</v>
       </c>
       <c r="S5">
-        <v>2012.45</v>
+        <v>2009.43</v>
       </c>
       <c r="T5">
-        <v>-13.62</v>
+        <v>-15.22</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1326,34 +1298,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>40.78</v>
+        <v>36.88</v>
       </c>
       <c r="Z5">
-        <v>-41.46</v>
+        <v>-42.49</v>
       </c>
       <c r="AA5">
-        <v>-47.71</v>
+        <v>-46.67</v>
       </c>
       <c r="AB5">
-        <v>6.25</v>
+        <v>4.18</v>
       </c>
       <c r="AC5">
-        <v>66.92</v>
+        <v>66.16</v>
       </c>
       <c r="AD5">
-        <v>73.93000000000001</v>
+        <v>68.41</v>
       </c>
       <c r="AE5">
-        <v>58.17</v>
+        <v>58.62</v>
       </c>
       <c r="AF5">
-        <v>-57.25</v>
+        <v>-60.76</v>
       </c>
       <c r="AG5">
-        <v>1853.7</v>
+        <v>1819.98</v>
       </c>
       <c r="AH5">
-        <v>1659.96</v>
+        <v>1674.12</v>
       </c>
       <c r="AI5">
         <v>1853.75</v>
@@ -1362,7 +1334,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>21.35</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,7 +1348,7 @@
         <v>620.7</v>
       </c>
       <c r="D6">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1391,40 +1363,40 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>-7.91</v>
+        <v>-5.54</v>
       </c>
       <c r="J6">
-        <v>-9.98</v>
+        <v>-11.93</v>
       </c>
       <c r="K6">
-        <v>-19.51</v>
+        <v>-19.18</v>
       </c>
       <c r="L6">
-        <v>-40.27</v>
+        <v>-40.5</v>
       </c>
       <c r="M6">
-        <v>7.45</v>
+        <v>7.52</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P6">
-        <v>634.9299999999999</v>
+        <v>627.65</v>
       </c>
       <c r="Q6">
-        <v>678.13</v>
+        <v>673.84</v>
       </c>
       <c r="R6">
-        <v>726.9299999999999</v>
+        <v>723.84</v>
       </c>
       <c r="S6">
-        <v>794.97</v>
+        <v>793.1</v>
       </c>
       <c r="T6">
-        <v>-21.92</v>
+        <v>-21.74</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1442,40 +1414,40 @@
         <v>26.69</v>
       </c>
       <c r="Z6">
-        <v>-24.75</v>
+        <v>-25.94</v>
       </c>
       <c r="AA6">
-        <v>-19.3</v>
+        <v>-20.63</v>
       </c>
       <c r="AB6">
-        <v>-5.46</v>
+        <v>-5.31</v>
       </c>
       <c r="AC6">
         <v>0</v>
       </c>
       <c r="AD6">
-        <v>7.76</v>
+        <v>2.18</v>
       </c>
       <c r="AE6">
-        <v>19.56</v>
+        <v>18.88</v>
       </c>
       <c r="AF6">
-        <v>-45.63</v>
+        <v>-71.45</v>
       </c>
       <c r="AG6">
-        <v>734.54</v>
+        <v>734.09</v>
       </c>
       <c r="AH6">
-        <v>621.71</v>
+        <v>613.59</v>
       </c>
       <c r="AI6">
-        <v>682.24</v>
+        <v>676.99</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>41.83</v>
+        <v>45.23</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1486,10 +1458,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2632.6</v>
+        <v>2576.8</v>
       </c>
       <c r="D7">
-        <v>3.7</v>
+        <v>-2.12</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1498,46 +1470,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-23.8</v>
+        <v>-25.42</v>
       </c>
       <c r="H7">
-        <v>39.18</v>
+        <v>36.23</v>
       </c>
       <c r="I7">
-        <v>3.03</v>
+        <v>5.81</v>
       </c>
       <c r="J7">
-        <v>-13.2</v>
+        <v>-14.2</v>
       </c>
       <c r="K7">
-        <v>1.53</v>
+        <v>0.18</v>
       </c>
       <c r="L7">
-        <v>10.83</v>
+        <v>2.65</v>
       </c>
       <c r="M7">
-        <v>25.48</v>
+        <v>26.22</v>
       </c>
       <c r="N7">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O7">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="P7">
-        <v>2522.4</v>
+        <v>2550.72</v>
       </c>
       <c r="Q7">
-        <v>2678.3</v>
+        <v>2660.67</v>
       </c>
       <c r="R7">
-        <v>2983.39</v>
+        <v>2973.15</v>
       </c>
       <c r="S7">
-        <v>2534.43</v>
+        <v>2536.17</v>
       </c>
       <c r="T7">
-        <v>3.87</v>
+        <v>1.6</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1552,34 +1524,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>43.21</v>
+        <v>40.08</v>
       </c>
       <c r="Z7">
-        <v>-119.35</v>
+        <v>-112.66</v>
       </c>
       <c r="AA7">
-        <v>-121.16</v>
+        <v>-119.46</v>
       </c>
       <c r="AB7">
-        <v>1.81</v>
+        <v>6.8</v>
       </c>
       <c r="AC7">
-        <v>96.29000000000001</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="AD7">
-        <v>81.27</v>
+        <v>92.42</v>
       </c>
       <c r="AE7">
-        <v>131.22</v>
+        <v>127.8</v>
       </c>
       <c r="AF7">
-        <v>-29.93</v>
+        <v>-43.35</v>
       </c>
       <c r="AG7">
-        <v>2983.63</v>
+        <v>2944.95</v>
       </c>
       <c r="AH7">
-        <v>2372.97</v>
+        <v>2376.39</v>
       </c>
       <c r="AI7">
         <v>2851.41</v>
@@ -1588,7 +1560,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>58.32</v>
+        <v>53.82</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1599,58 +1571,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>6969</v>
+        <v>6862.5</v>
       </c>
       <c r="D8">
-        <v>-2.37</v>
+        <v>-1.53</v>
       </c>
       <c r="E8">
-        <v>9054.049999999999</v>
+        <v>8908.5</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-23.03</v>
+        <v>-22.97</v>
       </c>
       <c r="H8">
-        <v>17.63</v>
+        <v>15.83</v>
       </c>
       <c r="I8">
-        <v>-9.359999999999999</v>
+        <v>-7.34</v>
       </c>
       <c r="J8">
-        <v>-18.26</v>
+        <v>-20.63</v>
       </c>
       <c r="K8">
-        <v>-16.06</v>
+        <v>-17.31</v>
       </c>
       <c r="L8">
-        <v>-23.49</v>
+        <v>-24.21</v>
       </c>
       <c r="M8">
-        <v>9.039999999999999</v>
+        <v>9.51</v>
       </c>
       <c r="N8">
         <v>29</v>
       </c>
       <c r="O8">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="P8">
-        <v>7098.4</v>
+        <v>6989.7</v>
       </c>
       <c r="Q8">
-        <v>7752.05</v>
+        <v>7672.22</v>
       </c>
       <c r="R8">
-        <v>8111.23</v>
+        <v>8089.84</v>
       </c>
       <c r="S8">
-        <v>7415.1</v>
+        <v>7410.63</v>
       </c>
       <c r="T8">
-        <v>-6.02</v>
+        <v>-7.4</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1665,43 +1637,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>30.69</v>
+        <v>29.2</v>
       </c>
       <c r="Z8">
-        <v>-320.68</v>
+        <v>-342.8</v>
       </c>
       <c r="AA8">
-        <v>-229.52</v>
+        <v>-252.17</v>
       </c>
       <c r="AB8">
-        <v>-91.16</v>
+        <v>-90.62</v>
       </c>
       <c r="AC8">
-        <v>38.26</v>
+        <v>33.26</v>
       </c>
       <c r="AD8">
-        <v>26.21</v>
+        <v>33.11</v>
       </c>
       <c r="AE8">
-        <v>351.79</v>
+        <v>340.48</v>
       </c>
       <c r="AF8">
-        <v>-32.9</v>
+        <v>-43.63</v>
       </c>
       <c r="AG8">
-        <v>8668.879999999999</v>
+        <v>8607.700000000001</v>
       </c>
       <c r="AH8">
-        <v>6835.22</v>
+        <v>6736.75</v>
       </c>
       <c r="AI8">
-        <v>7963.93</v>
+        <v>7939.2</v>
       </c>
       <c r="AJ8" t="s">
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>49.01</v>
+        <v>52.18</v>
       </c>
     </row>
   </sheetData>
@@ -1842,7 +1814,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1862,47 +1834,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1910,1040 +1847,955 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>63</v>
+      <c r="B6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>-10.7</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>-15.33</v>
       </c>
-      <c r="E7" s="7">
-        <v>-4.63</v>
+      <c r="D7" s="5">
+        <v>-15.05</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0.28</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-6.9</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>-5.79</v>
       </c>
-      <c r="E8" s="8">
-        <v>1.11</v>
+      <c r="D8" s="5">
+        <v>-6.06</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.27</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
-        <v>-18.38</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
         <v>-12.65</v>
       </c>
-      <c r="E9" s="8">
-        <v>5.73</v>
+      <c r="D9" s="5">
+        <v>-7.07</v>
+      </c>
+      <c r="E9" s="6">
+        <v>5.58</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="6">
-        <v>-11.52</v>
-      </c>
-      <c r="D10" s="6">
+      <c r="C10" s="5">
         <v>-10.51</v>
       </c>
-      <c r="E10" s="8">
-        <v>1.01</v>
+      <c r="D10" s="5">
+        <v>-13.26</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="6">
-        <v>-11.33</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="5">
         <v>-9.98</v>
       </c>
-      <c r="E11" s="8">
-        <v>1.35</v>
+      <c r="D11" s="5">
+        <v>-11.93</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-1.95</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6">
-        <v>-15.94</v>
-      </c>
-      <c r="D12" s="6">
+      <c r="C12" s="5">
         <v>-13.2</v>
       </c>
-      <c r="E12" s="8">
-        <v>2.74</v>
+      <c r="D12" s="5">
+        <v>-14.2</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="6">
-        <v>-17.75</v>
-      </c>
-      <c r="D13" s="6">
+      <c r="C13" s="5">
         <v>-18.26</v>
       </c>
+      <c r="D13" s="5">
+        <v>-20.63</v>
+      </c>
       <c r="E13" s="7">
-        <v>-0.51</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="6">
-        <v>1.72</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="C14" s="5">
         <v>0.8</v>
       </c>
-      <c r="E14" s="7">
-        <v>-0.92</v>
+      <c r="D14" s="5">
+        <v>2.47</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1.67</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="6">
-        <v>-1.51</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="C15" s="5">
         <v>-2.29</v>
       </c>
-      <c r="E15" s="7">
-        <v>-0.78</v>
+      <c r="D15" s="5">
+        <v>1.38</v>
+      </c>
+      <c r="E15" s="6">
+        <v>3.67</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="6">
-        <v>-8.029999999999999</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
         <v>-5.41</v>
       </c>
-      <c r="E16" s="8">
-        <v>2.62</v>
+      <c r="D16" s="5">
+        <v>1</v>
+      </c>
+      <c r="E16" s="6">
+        <v>6.41</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6">
-        <v>-1.59</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="C17" s="5">
         <v>-1.85</v>
       </c>
+      <c r="D17" s="5">
+        <v>-4.92</v>
+      </c>
       <c r="E17" s="7">
-        <v>-0.26</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="6">
-        <v>-10.4</v>
-      </c>
-      <c r="D18" s="6">
+      <c r="C18" s="5">
         <v>-7.91</v>
       </c>
-      <c r="E18" s="8">
-        <v>2.49</v>
+      <c r="D18" s="5">
+        <v>-5.54</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2.37</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="6">
-        <v>-3.49</v>
-      </c>
-      <c r="D19" s="6">
+      <c r="C19" s="5">
         <v>3.03</v>
       </c>
-      <c r="E19" s="8">
-        <v>6.52</v>
+      <c r="D19" s="5">
+        <v>5.81</v>
+      </c>
+      <c r="E19" s="6">
+        <v>2.78</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="6">
-        <v>-9.32</v>
-      </c>
-      <c r="D20" s="6">
+      <c r="C20" s="5">
         <v>-9.359999999999999</v>
       </c>
-      <c r="E20" s="7">
-        <v>-0.04</v>
+      <c r="D20" s="5">
+        <v>-7.34</v>
+      </c>
+      <c r="E20" s="6">
+        <v>2.02</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="6">
-        <v>26.74</v>
-      </c>
-      <c r="D21" s="6">
+      <c r="C21" s="5">
         <v>20.87</v>
       </c>
+      <c r="D21" s="5">
+        <v>20.02</v>
+      </c>
       <c r="E21" s="7">
-        <v>-5.87</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="6">
-        <v>12.83</v>
-      </c>
-      <c r="D22" s="6">
+      <c r="C22" s="5">
         <v>13.29</v>
       </c>
-      <c r="E22" s="8">
-        <v>0.46</v>
+      <c r="D22" s="5">
+        <v>13.82</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.53</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="6">
-        <v>-13.41</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
         <v>-11.99</v>
       </c>
-      <c r="E23" s="8">
-        <v>1.42</v>
+      <c r="D23" s="5">
+        <v>-8.210000000000001</v>
+      </c>
+      <c r="E23" s="6">
+        <v>3.78</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="6">
-        <v>-20.12</v>
-      </c>
-      <c r="D24" s="6">
+      <c r="C24" s="5">
         <v>-19.91</v>
       </c>
-      <c r="E24" s="8">
-        <v>0.21</v>
+      <c r="D24" s="5">
+        <v>-20.97</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="6">
-        <v>-39.53</v>
-      </c>
-      <c r="D25" s="6">
+      <c r="C25" s="5">
         <v>-40.27</v>
       </c>
+      <c r="D25" s="5">
+        <v>-40.5</v>
+      </c>
       <c r="E25" s="7">
-        <v>-0.74</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="6">
-        <v>7.85</v>
-      </c>
-      <c r="D26" s="6">
+      <c r="C26" s="5">
         <v>10.83</v>
       </c>
-      <c r="E26" s="8">
-        <v>2.98</v>
+      <c r="D26" s="5">
+        <v>2.65</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-8.18</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C27" s="6">
-        <v>-19.56</v>
-      </c>
-      <c r="D27" s="6">
+      <c r="C27" s="5">
         <v>-23.49</v>
       </c>
+      <c r="D27" s="5">
+        <v>-24.21</v>
+      </c>
       <c r="E27" s="7">
-        <v>-3.93</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="6">
-        <v>6.1</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C28" s="5">
         <v>2.29</v>
       </c>
-      <c r="E28" s="7">
-        <v>-3.81</v>
+      <c r="D28" s="5">
+        <v>2.32</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.03</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="6">
-        <v>-3.97</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
         <v>-4.78</v>
       </c>
-      <c r="E29" s="7">
-        <v>-0.8100000000000001</v>
+      <c r="D29" s="5">
+        <v>-1.4</v>
+      </c>
+      <c r="E29" s="6">
+        <v>3.38</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="6">
-        <v>-16.03</v>
-      </c>
-      <c r="D30" s="6">
+      <c r="C30" s="5">
         <v>-17.71</v>
       </c>
-      <c r="E30" s="7">
-        <v>-1.68</v>
+      <c r="D30" s="5">
+        <v>-11.85</v>
+      </c>
+      <c r="E30" s="6">
+        <v>5.86</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="6">
-        <v>-12.63</v>
-      </c>
-      <c r="D31" s="6">
+      <c r="C31" s="5">
         <v>-13.24</v>
       </c>
+      <c r="D31" s="5">
+        <v>-15.95</v>
+      </c>
       <c r="E31" s="7">
-        <v>-0.61</v>
+        <v>-2.71</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="6">
-        <v>-17.95</v>
-      </c>
-      <c r="D32" s="6">
+      <c r="C32" s="5">
         <v>-19.51</v>
       </c>
-      <c r="E32" s="7">
-        <v>-1.56</v>
+      <c r="D32" s="5">
+        <v>-19.18</v>
+      </c>
+      <c r="E32" s="6">
+        <v>0.33</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="6">
-        <v>-1.09</v>
-      </c>
-      <c r="D33" s="6">
+      <c r="C33" s="5">
         <v>1.53</v>
       </c>
-      <c r="E33" s="8">
-        <v>2.62</v>
+      <c r="D33" s="5">
+        <v>0.18</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="6">
+      <c r="C34" s="5">
+        <v>-16.06</v>
+      </c>
+      <c r="D34" s="5">
+        <v>-17.31</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="5">
+        <v>-15.33</v>
+      </c>
+      <c r="D35" s="5">
+        <v>-16.23</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-14.45</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-14.77</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-24.28</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-20.35</v>
+      </c>
+      <c r="E37" s="6">
+        <v>3.93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-27.53</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-28.98</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-23.8</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-25.42</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-23.03</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-22.97</v>
+      </c>
+      <c r="E40" s="6">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="5">
+        <v>1097.7</v>
+      </c>
+      <c r="D41" s="5">
+        <v>1086.1</v>
+      </c>
+      <c r="E41" s="7">
         <v>-11.6</v>
       </c>
-      <c r="D34" s="6">
-        <v>-16.06</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-4.46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="5">
+        <v>835.4</v>
+      </c>
+      <c r="D42" s="5">
+        <v>832.3</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="5">
+        <v>1469</v>
+      </c>
+      <c r="D43" s="5">
+        <v>1545.2</v>
+      </c>
+      <c r="E43" s="6">
+        <v>76.2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1738.4</v>
+      </c>
+      <c r="D44" s="5">
+        <v>1703.5</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-34.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="5">
+        <v>2632.6</v>
+      </c>
+      <c r="D45" s="5">
+        <v>2576.8</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-55.8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="5">
+        <v>6969</v>
+      </c>
+      <c r="D46" s="5">
+        <v>6862.5</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-106.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C47" s="5">
+        <v>71</v>
+      </c>
+      <c r="D47" s="5">
+        <v>85</v>
+      </c>
+      <c r="E47" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C48" s="5">
+        <v>85</v>
+      </c>
+      <c r="D48" s="5">
+        <v>71</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="6">
-        <v>-12.9</v>
-      </c>
-      <c r="D35" s="6">
-        <v>-15.33</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-2.43</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="5">
+        <v>44.24</v>
+      </c>
+      <c r="D49" s="5">
+        <v>42.92</v>
+      </c>
+      <c r="E49" s="7">
+        <v>-1.32</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="6">
-        <v>-14.67</v>
-      </c>
-      <c r="D36" s="6">
-        <v>-14.45</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
+      <c r="B50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="5">
+        <v>44.7</v>
+      </c>
+      <c r="D50" s="5">
+        <v>44.01</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="6">
-        <v>-25.37</v>
-      </c>
-      <c r="D37" s="6">
-        <v>-24.28</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1.09</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
+      <c r="B51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="5">
+        <v>30.27</v>
+      </c>
+      <c r="D51" s="5">
+        <v>43.11</v>
+      </c>
+      <c r="E51" s="6">
+        <v>12.84</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="6">
-        <v>-27.85</v>
-      </c>
-      <c r="D38" s="6">
-        <v>-27.53</v>
-      </c>
-      <c r="E38" s="8">
-        <v>0.32</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
+      <c r="B52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="5">
+        <v>40.78</v>
+      </c>
+      <c r="D52" s="5">
+        <v>36.88</v>
+      </c>
+      <c r="E52" s="7">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="5">
+        <v>43.21</v>
+      </c>
+      <c r="D53" s="5">
+        <v>40.08</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-3.13</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="5">
+        <v>30.69</v>
+      </c>
+      <c r="D54" s="5">
+        <v>29.2</v>
+      </c>
+      <c r="E54" s="7">
+        <v>-1.49</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="5">
+        <v>-14.39</v>
+      </c>
+      <c r="D55" s="5">
+        <v>-76.09</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-61.7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="5">
+        <v>-18.6</v>
+      </c>
+      <c r="D56" s="5">
+        <v>-63.39</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-44.79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="5">
+        <v>-4.36</v>
+      </c>
+      <c r="D57" s="5">
+        <v>88.61</v>
+      </c>
+      <c r="E57" s="6">
+        <v>92.97</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="5">
+        <v>-57.25</v>
+      </c>
+      <c r="D58" s="5">
+        <v>-60.76</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-3.51</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="6">
-        <v>-42.93</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-43.04</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
+      <c r="B59" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="5">
+        <v>-45.63</v>
+      </c>
+      <c r="D59" s="5">
+        <v>-71.45</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-25.82</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="6">
-        <v>-26.52</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-23.8</v>
-      </c>
-      <c r="E40" s="8">
-        <v>2.72</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
+      <c r="B60" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="5">
+        <v>-29.93</v>
+      </c>
+      <c r="D60" s="5">
+        <v>-43.35</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-13.42</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="6">
-        <v>-21.64</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-23.03</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="6">
-        <v>1129.2</v>
-      </c>
-      <c r="D42" s="6">
-        <v>1097.7</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-31.5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6">
-        <v>833.25</v>
-      </c>
-      <c r="D43" s="6">
-        <v>835.4</v>
-      </c>
-      <c r="E43" s="8">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="6">
-        <v>1447.9</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1469</v>
-      </c>
-      <c r="E44" s="8">
-        <v>21.1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="6">
-        <v>1730.6</v>
-      </c>
-      <c r="D45" s="6">
-        <v>1738.4</v>
-      </c>
-      <c r="E45" s="8">
-        <v>7.8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="6">
-        <v>621.95</v>
-      </c>
-      <c r="D46" s="6">
-        <v>620.7</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C47" s="6">
-        <v>2538.6</v>
-      </c>
-      <c r="D47" s="6">
-        <v>2632.6</v>
-      </c>
-      <c r="E47" s="8">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="6">
-        <v>7138</v>
-      </c>
-      <c r="D48" s="6">
-        <v>6969</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-169</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" s="6">
-        <v>85</v>
-      </c>
-      <c r="D49" s="6">
-        <v>71</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" s="6">
-        <v>43</v>
-      </c>
-      <c r="D50" s="6">
-        <v>57</v>
-      </c>
-      <c r="E50" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C51" s="6">
-        <v>57</v>
-      </c>
-      <c r="D51" s="6">
-        <v>43</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C52" s="6">
-        <v>71</v>
-      </c>
-      <c r="D52" s="6">
-        <v>85</v>
-      </c>
-      <c r="E52" s="8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="6">
-        <v>47.93</v>
-      </c>
-      <c r="D53" s="6">
-        <v>44.24</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-3.69</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="6">
-        <v>44.14</v>
-      </c>
-      <c r="D54" s="6">
-        <v>44.7</v>
-      </c>
-      <c r="E54" s="8">
-        <v>0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="6">
-        <v>25.98</v>
-      </c>
-      <c r="D55" s="6">
-        <v>30.27</v>
-      </c>
-      <c r="E55" s="8">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C56" s="6">
-        <v>39.45</v>
-      </c>
-      <c r="D56" s="6">
-        <v>40.78</v>
-      </c>
-      <c r="E56" s="8">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C57" s="6">
-        <v>26.92</v>
-      </c>
-      <c r="D57" s="6">
-        <v>26.69</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C58" s="6">
-        <v>35.29</v>
-      </c>
-      <c r="D58" s="6">
-        <v>43.21</v>
-      </c>
-      <c r="E58" s="8">
-        <v>7.92</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C59" s="6">
-        <v>33.2</v>
-      </c>
-      <c r="D59" s="6">
-        <v>30.69</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-2.51</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="5" t="s">
+      <c r="B61" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C60" s="6">
-        <v>58.49</v>
-      </c>
-      <c r="D60" s="6">
-        <v>-14.39</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-72.88</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="6">
-        <v>45.71</v>
-      </c>
-      <c r="D61" s="6">
-        <v>-18.6</v>
+      <c r="C61" s="5">
+        <v>-32.9</v>
+      </c>
+      <c r="D61" s="5">
+        <v>-43.63</v>
       </c>
       <c r="E61" s="7">
-        <v>-64.31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5">
-      <c r="A62" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C62" s="6">
-        <v>-3.04</v>
-      </c>
-      <c r="D62" s="6">
-        <v>-4.36</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
-      <c r="A63" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="6">
-        <v>-67.48999999999999</v>
-      </c>
-      <c r="D63" s="6">
-        <v>-57.25</v>
-      </c>
-      <c r="E63" s="8">
-        <v>10.24</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C64" s="6">
-        <v>-26.96</v>
-      </c>
-      <c r="D64" s="6">
-        <v>-45.63</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-18.67</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C65" s="6">
-        <v>143.75</v>
-      </c>
-      <c r="D65" s="6">
-        <v>-29.93</v>
-      </c>
-      <c r="E65" s="7">
-        <v>-173.68</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C66" s="6">
-        <v>-49.72</v>
-      </c>
-      <c r="D66" s="6">
-        <v>-32.9</v>
-      </c>
-      <c r="E66" s="8">
-        <v>16.82</v>
+        <v>-10.73</v>
       </c>
     </row>
   </sheetData>
@@ -2969,60 +2821,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>71</v>
+      <c r="B1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>49.96</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>7</v>
       </c>
-      <c r="D2" s="11">
-        <v>37.2</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>37.6</v>
+      </c>
+      <c r="E2" s="10">
         <v>42.9</v>
       </c>
-      <c r="F2" s="11">
-        <v>-12.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>-9.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>-12.6</v>
+      </c>
+      <c r="G2" s="10">
+        <v>-9</v>
+      </c>
+      <c r="H2" s="10">
         <v>57</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>14.3</v>
       </c>
     </row>
@@ -3124,49 +2976,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="14">
-        <v>0.3983</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.2548</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.1891</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.1767</v>
-      </c>
-      <c r="E2" s="14">
-        <v>0.09039999999999999</v>
-      </c>
-      <c r="F2" s="14">
-        <v>0.0745</v>
-      </c>
-      <c r="G2" s="14">
-        <v>0.0533</v>
+      <c r="A2" s="13">
+        <v>0.4115</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.2622</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.2069</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.1738</v>
+      </c>
+      <c r="E2" s="13">
+        <v>0.0951</v>
+      </c>
+      <c r="F2" s="13">
+        <v>0.07519999999999999</v>
+      </c>
+      <c r="G2" s="13">
+        <v>0.0547</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,10 +166,40 @@
     <t>DOWN</t>
   </si>
   <si>
+    <t>UP</t>
+  </si>
+  <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>43.1 → 50.7</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>43.1</t>
+  </si>
+  <si>
+    <t>50.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -371,14 +401,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -893,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1086.1</v>
+        <v>1086.2</v>
       </c>
       <c r="D2">
-        <v>-1.06</v>
+        <v>0.01</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -905,46 +936,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-16.23</v>
+        <v>-16.22</v>
       </c>
       <c r="H2">
-        <v>45.13</v>
+        <v>45.15</v>
       </c>
       <c r="I2">
-        <v>2.47</v>
+        <v>2.99</v>
       </c>
       <c r="J2">
-        <v>-15.05</v>
+        <v>-12.95</v>
       </c>
       <c r="K2">
-        <v>2.32</v>
+        <v>2.86</v>
       </c>
       <c r="L2">
-        <v>20.02</v>
+        <v>21.28</v>
       </c>
       <c r="M2">
-        <v>5.47</v>
+        <v>5.64</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="P2">
-        <v>1079.3</v>
+        <v>1085.6</v>
       </c>
       <c r="Q2">
-        <v>1160.52</v>
+        <v>1154.8</v>
       </c>
       <c r="R2">
-        <v>1142.48</v>
+        <v>1141.75</v>
       </c>
       <c r="S2">
-        <v>1001.63</v>
+        <v>1002.98</v>
       </c>
       <c r="T2">
-        <v>8.43</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -959,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>42.92</v>
+        <v>42.94</v>
       </c>
       <c r="Z2">
-        <v>-25.04</v>
+        <v>-25.23</v>
       </c>
       <c r="AA2">
-        <v>-13.57</v>
+        <v>-15.9</v>
       </c>
       <c r="AB2">
-        <v>-11.47</v>
+        <v>-9.33</v>
       </c>
       <c r="AC2">
-        <v>51.25</v>
+        <v>52.41</v>
       </c>
       <c r="AD2">
-        <v>34.08</v>
+        <v>45.57</v>
       </c>
       <c r="AE2">
-        <v>57.23</v>
+        <v>55.74</v>
       </c>
       <c r="AF2">
-        <v>-76.09</v>
+        <v>-42.13</v>
       </c>
       <c r="AG2">
-        <v>1316.13</v>
+        <v>1312.61</v>
       </c>
       <c r="AH2">
-        <v>1004.91</v>
+        <v>997</v>
       </c>
       <c r="AI2">
         <v>1168</v>
@@ -995,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>33.74</v>
+        <v>29.26</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1006,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>832.3</v>
+        <v>829.8</v>
       </c>
       <c r="D3">
-        <v>-0.37</v>
+        <v>-0.3</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1018,46 +1049,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-14.77</v>
+        <v>-15.02</v>
       </c>
       <c r="H3">
-        <v>57.19</v>
+        <v>56.72</v>
       </c>
       <c r="I3">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="J3">
-        <v>-6.06</v>
+        <v>-4.07</v>
       </c>
       <c r="K3">
-        <v>-1.4</v>
+        <v>0.04</v>
       </c>
       <c r="L3">
-        <v>13.82</v>
+        <v>14.89</v>
       </c>
       <c r="M3">
-        <v>41.15</v>
+        <v>41.85</v>
       </c>
       <c r="N3">
         <v>85</v>
       </c>
       <c r="O3">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P3">
-        <v>826.28</v>
+        <v>828.8200000000001</v>
       </c>
       <c r="Q3">
-        <v>852.6799999999999</v>
+        <v>851.26</v>
       </c>
       <c r="R3">
-        <v>874.05</v>
+        <v>872.67</v>
       </c>
       <c r="S3">
-        <v>811.5</v>
+        <v>812.58</v>
       </c>
       <c r="T3">
-        <v>2.56</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1072,34 +1103,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>44.01</v>
+        <v>43.43</v>
       </c>
       <c r="Z3">
-        <v>-14.79</v>
+        <v>-14.44</v>
       </c>
       <c r="AA3">
-        <v>-13.1</v>
+        <v>-13.37</v>
       </c>
       <c r="AB3">
-        <v>-1.69</v>
+        <v>-1.07</v>
       </c>
       <c r="AC3">
-        <v>53.53</v>
+        <v>64.56</v>
       </c>
       <c r="AD3">
-        <v>34.71</v>
+        <v>49.93</v>
       </c>
       <c r="AE3">
-        <v>29.11</v>
+        <v>28.2</v>
       </c>
       <c r="AF3">
-        <v>-63.39</v>
+        <v>-38.77</v>
       </c>
       <c r="AG3">
-        <v>905.9</v>
+        <v>905.38</v>
       </c>
       <c r="AH3">
-        <v>799.46</v>
+        <v>797.15</v>
       </c>
       <c r="AI3">
         <v>888.53</v>
@@ -1108,7 +1139,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>30.41</v>
+        <v>30.87</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1119,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1545.2</v>
+        <v>1604.2</v>
       </c>
       <c r="D4">
-        <v>5.19</v>
+        <v>3.82</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1131,46 +1162,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-20.35</v>
+        <v>-17.31</v>
       </c>
       <c r="H4">
-        <v>14.06</v>
+        <v>18.42</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>4.79</v>
       </c>
       <c r="J4">
-        <v>-7.07</v>
+        <v>-1.84</v>
       </c>
       <c r="K4">
-        <v>-11.85</v>
+        <v>-11.02</v>
       </c>
       <c r="L4">
-        <v>-8.210000000000001</v>
+        <v>-7.39</v>
       </c>
       <c r="M4">
-        <v>20.69</v>
+        <v>21.37</v>
       </c>
       <c r="N4">
         <v>57</v>
       </c>
       <c r="O4">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="P4">
-        <v>1491.36</v>
+        <v>1506.02</v>
       </c>
       <c r="Q4">
-        <v>1560.22</v>
+        <v>1559.07</v>
       </c>
       <c r="R4">
-        <v>1714.15</v>
+        <v>1708.35</v>
       </c>
       <c r="S4">
-        <v>1667.63</v>
+        <v>1666.88</v>
       </c>
       <c r="T4">
-        <v>-7.34</v>
+        <v>-3.76</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1185,43 +1216,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>43.11</v>
+        <v>50.68</v>
       </c>
       <c r="Z4">
-        <v>-61.38</v>
+        <v>-51.15</v>
       </c>
       <c r="AA4">
-        <v>-61.9</v>
+        <v>-59.75</v>
       </c>
       <c r="AB4">
-        <v>0.53</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AC4">
-        <v>48.24</v>
+        <v>78.63</v>
       </c>
       <c r="AD4">
-        <v>31.9</v>
+        <v>49.05</v>
       </c>
       <c r="AE4">
-        <v>51.69</v>
+        <v>53.28</v>
       </c>
       <c r="AF4">
-        <v>88.61</v>
+        <v>174.69</v>
       </c>
       <c r="AG4">
-        <v>1664.21</v>
+        <v>1660.39</v>
       </c>
       <c r="AH4">
-        <v>1456.24</v>
+        <v>1457.75</v>
       </c>
       <c r="AI4">
-        <v>1583.31</v>
+        <v>1424.16</v>
       </c>
       <c r="AJ4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AK4">
-        <v>53</v>
+        <v>48.8</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1232,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1703.5</v>
+        <v>1719.8</v>
       </c>
       <c r="D5">
-        <v>-2.01</v>
+        <v>0.96</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1244,46 +1275,46 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-28.98</v>
+        <v>-28.3</v>
       </c>
       <c r="H5">
-        <v>1.78</v>
+        <v>2.75</v>
       </c>
       <c r="I5">
-        <v>-4.92</v>
+        <v>-3.2</v>
       </c>
       <c r="J5">
-        <v>-13.26</v>
+        <v>-9.44</v>
       </c>
       <c r="K5">
-        <v>-15.95</v>
+        <v>-15.6</v>
       </c>
       <c r="L5">
-        <v>-20.97</v>
+        <v>-20.18</v>
       </c>
       <c r="M5">
-        <v>17.38</v>
+        <v>17.94</v>
       </c>
       <c r="N5">
         <v>43</v>
       </c>
       <c r="O5">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P5">
-        <v>1733.42</v>
+        <v>1722.06</v>
       </c>
       <c r="Q5">
-        <v>1747.05</v>
+        <v>1743.39</v>
       </c>
       <c r="R5">
-        <v>1872.32</v>
+        <v>1864.81</v>
       </c>
       <c r="S5">
-        <v>2009.43</v>
+        <v>2006.71</v>
       </c>
       <c r="T5">
-        <v>-15.22</v>
+        <v>-14.3</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1298,34 +1329,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>36.88</v>
+        <v>39.77</v>
       </c>
       <c r="Z5">
-        <v>-42.49</v>
+        <v>-41.51</v>
       </c>
       <c r="AA5">
-        <v>-46.67</v>
+        <v>-45.64</v>
       </c>
       <c r="AB5">
-        <v>4.18</v>
+        <v>4.13</v>
       </c>
       <c r="AC5">
-        <v>66.16</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AD5">
-        <v>68.41</v>
+        <v>65.78</v>
       </c>
       <c r="AE5">
-        <v>58.62</v>
+        <v>56.79</v>
       </c>
       <c r="AF5">
-        <v>-60.76</v>
+        <v>-21.61</v>
       </c>
       <c r="AG5">
-        <v>1819.98</v>
+        <v>1813.94</v>
       </c>
       <c r="AH5">
-        <v>1674.12</v>
+        <v>1672.85</v>
       </c>
       <c r="AI5">
         <v>1853.75</v>
@@ -1334,7 +1365,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>18.94</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1345,10 +1376,10 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>620.7</v>
+        <v>626.65</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
@@ -1357,25 +1388,25 @@
         <v>620.7</v>
       </c>
       <c r="G6">
-        <v>-43.04</v>
+        <v>-42.5</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="I6">
-        <v>-5.54</v>
+        <v>-3.21</v>
       </c>
       <c r="J6">
-        <v>-11.93</v>
+        <v>-11.3</v>
       </c>
       <c r="K6">
-        <v>-19.18</v>
+        <v>-19.55</v>
       </c>
       <c r="L6">
-        <v>-40.5</v>
+        <v>-39.68</v>
       </c>
       <c r="M6">
-        <v>7.52</v>
+        <v>7.58</v>
       </c>
       <c r="N6">
         <v>15</v>
@@ -1384,19 +1415,19 @@
         <v>14</v>
       </c>
       <c r="P6">
-        <v>627.65</v>
+        <v>623.5</v>
       </c>
       <c r="Q6">
-        <v>673.84</v>
+        <v>670.36</v>
       </c>
       <c r="R6">
-        <v>723.84</v>
+        <v>720.53</v>
       </c>
       <c r="S6">
-        <v>793.1</v>
+        <v>791.4400000000001</v>
       </c>
       <c r="T6">
-        <v>-21.74</v>
+        <v>-20.82</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1411,34 +1442,34 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>26.69</v>
+        <v>29.96</v>
       </c>
       <c r="Z6">
-        <v>-25.94</v>
+        <v>-26.1</v>
       </c>
       <c r="AA6">
-        <v>-20.63</v>
+        <v>-21.72</v>
       </c>
       <c r="AB6">
-        <v>-5.31</v>
+        <v>-4.38</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD6">
-        <v>2.18</v>
+        <v>1.77</v>
       </c>
       <c r="AE6">
-        <v>18.88</v>
+        <v>18.31</v>
       </c>
       <c r="AF6">
-        <v>-71.45</v>
+        <v>-69.65000000000001</v>
       </c>
       <c r="AG6">
-        <v>734.09</v>
+        <v>733.14</v>
       </c>
       <c r="AH6">
-        <v>613.59</v>
+        <v>607.5700000000001</v>
       </c>
       <c r="AI6">
         <v>676.99</v>
@@ -1447,7 +1478,7 @@
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>45.23</v>
+        <v>46.57</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1458,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2576.8</v>
+        <v>2563.8</v>
       </c>
       <c r="D7">
-        <v>-2.12</v>
+        <v>-0.5</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1470,25 +1501,25 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-25.42</v>
+        <v>-25.79</v>
       </c>
       <c r="H7">
-        <v>36.23</v>
+        <v>35.55</v>
       </c>
       <c r="I7">
-        <v>5.81</v>
+        <v>2.63</v>
       </c>
       <c r="J7">
-        <v>-14.2</v>
+        <v>-12.48</v>
       </c>
       <c r="K7">
-        <v>0.18</v>
+        <v>0.77</v>
       </c>
       <c r="L7">
-        <v>2.65</v>
+        <v>3.78</v>
       </c>
       <c r="M7">
-        <v>26.22</v>
+        <v>26.21</v>
       </c>
       <c r="N7">
         <v>71</v>
@@ -1497,19 +1528,19 @@
         <v>71</v>
       </c>
       <c r="P7">
-        <v>2550.72</v>
+        <v>2563.88</v>
       </c>
       <c r="Q7">
-        <v>2660.67</v>
+        <v>2642.54</v>
       </c>
       <c r="R7">
-        <v>2973.15</v>
+        <v>2962.48</v>
       </c>
       <c r="S7">
-        <v>2536.17</v>
+        <v>2538.22</v>
       </c>
       <c r="T7">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1524,34 +1555,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>40.08</v>
+        <v>39.36</v>
       </c>
       <c r="Z7">
-        <v>-112.66</v>
+        <v>-107.17</v>
       </c>
       <c r="AA7">
-        <v>-119.46</v>
+        <v>-117</v>
       </c>
       <c r="AB7">
-        <v>6.8</v>
+        <v>9.83</v>
       </c>
       <c r="AC7">
-        <v>95.20999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="AD7">
-        <v>92.42</v>
+        <v>93.13</v>
       </c>
       <c r="AE7">
-        <v>127.8</v>
+        <v>121.79</v>
       </c>
       <c r="AF7">
-        <v>-43.35</v>
+        <v>-61.65</v>
       </c>
       <c r="AG7">
-        <v>2944.95</v>
+        <v>2900.5</v>
       </c>
       <c r="AH7">
-        <v>2376.39</v>
+        <v>2384.58</v>
       </c>
       <c r="AI7">
         <v>2851.41</v>
@@ -1560,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>53.82</v>
+        <v>49.92</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1571,58 +1602,58 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>6862.5</v>
+        <v>6856.5</v>
       </c>
       <c r="D8">
-        <v>-1.53</v>
+        <v>-0.09</v>
       </c>
       <c r="E8">
-        <v>8908.5</v>
+        <v>8812.5</v>
       </c>
       <c r="F8">
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-22.97</v>
+        <v>-22.2</v>
       </c>
       <c r="H8">
-        <v>15.83</v>
+        <v>15.73</v>
       </c>
       <c r="I8">
-        <v>-7.34</v>
+        <v>-0.44</v>
       </c>
       <c r="J8">
-        <v>-20.63</v>
+        <v>-18.94</v>
       </c>
       <c r="K8">
-        <v>-17.31</v>
+        <v>-16.68</v>
       </c>
       <c r="L8">
-        <v>-24.21</v>
+        <v>-23.03</v>
       </c>
       <c r="M8">
-        <v>9.51</v>
+        <v>9.66</v>
       </c>
       <c r="N8">
         <v>29</v>
       </c>
       <c r="O8">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P8">
-        <v>6989.7</v>
+        <v>6983.6</v>
       </c>
       <c r="Q8">
-        <v>7672.22</v>
+        <v>7595.3</v>
       </c>
       <c r="R8">
-        <v>8089.84</v>
+        <v>8068.33</v>
       </c>
       <c r="S8">
-        <v>7410.63</v>
+        <v>7406.98</v>
       </c>
       <c r="T8">
-        <v>-7.4</v>
+        <v>-7.43</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1637,34 +1668,34 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>29.2</v>
+        <v>29.11</v>
       </c>
       <c r="Z8">
-        <v>-342.8</v>
+        <v>-356.7</v>
       </c>
       <c r="AA8">
-        <v>-252.17</v>
+        <v>-273.08</v>
       </c>
       <c r="AB8">
-        <v>-90.62</v>
+        <v>-83.62</v>
       </c>
       <c r="AC8">
-        <v>33.26</v>
+        <v>25.39</v>
       </c>
       <c r="AD8">
-        <v>33.11</v>
+        <v>32.3</v>
       </c>
       <c r="AE8">
-        <v>340.48</v>
+        <v>337.2</v>
       </c>
       <c r="AF8">
-        <v>-43.63</v>
+        <v>-14.52</v>
       </c>
       <c r="AG8">
-        <v>8607.700000000001</v>
+        <v>8533.549999999999</v>
       </c>
       <c r="AH8">
-        <v>6736.75</v>
+        <v>6657.05</v>
       </c>
       <c r="AI8">
         <v>7939.2</v>
@@ -1673,7 +1704,7 @@
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>52.18</v>
+        <v>53.43</v>
       </c>
     </row>
   </sheetData>
@@ -1814,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1824,7 +1855,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1834,12 +1865,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1847,955 +1913,972 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>54</v>
+      <c r="B6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-15.33</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-15.05</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.28</v>
+      <c r="D7" s="6">
+        <v>-12.95</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2.1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-5.79</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-6.06</v>
       </c>
+      <c r="D8" s="6">
+        <v>-4.07</v>
+      </c>
       <c r="E8" s="7">
-        <v>-0.27</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-12.65</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-7.07</v>
       </c>
-      <c r="E9" s="6">
-        <v>5.58</v>
+      <c r="D9" s="6">
+        <v>-1.84</v>
+      </c>
+      <c r="E9" s="7">
+        <v>5.23</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-10.51</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-13.26</v>
       </c>
+      <c r="D10" s="6">
+        <v>-9.44</v>
+      </c>
       <c r="E10" s="7">
-        <v>-2.75</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-9.98</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-11.93</v>
       </c>
+      <c r="D11" s="6">
+        <v>-11.3</v>
+      </c>
       <c r="E11" s="7">
-        <v>-1.95</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="5">
-        <v>-13.2</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-14.2</v>
       </c>
+      <c r="D12" s="6">
+        <v>-12.48</v>
+      </c>
       <c r="E12" s="7">
-        <v>-1</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="5">
-        <v>-18.26</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-20.63</v>
       </c>
+      <c r="D13" s="6">
+        <v>-18.94</v>
+      </c>
       <c r="E13" s="7">
-        <v>-2.37</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>0.8</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>2.47</v>
       </c>
-      <c r="E14" s="6">
-        <v>1.67</v>
+      <c r="D14" s="6">
+        <v>2.99</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.52</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-2.29</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>1.38</v>
       </c>
-      <c r="E15" s="6">
-        <v>3.67</v>
+      <c r="D15" s="6">
+        <v>1.55</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.17</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-5.41</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>1</v>
       </c>
-      <c r="E16" s="6">
-        <v>6.41</v>
+      <c r="D16" s="6">
+        <v>4.79</v>
+      </c>
+      <c r="E16" s="7">
+        <v>3.79</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="5">
-        <v>-1.85</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>-4.92</v>
       </c>
+      <c r="D17" s="6">
+        <v>-3.2</v>
+      </c>
       <c r="E17" s="7">
-        <v>-3.07</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="5">
-        <v>-7.91</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>-5.54</v>
       </c>
-      <c r="E18" s="6">
-        <v>2.37</v>
+      <c r="D18" s="6">
+        <v>-3.21</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.33</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="5">
-        <v>3.03</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>5.81</v>
       </c>
-      <c r="E19" s="6">
-        <v>2.78</v>
+      <c r="D19" s="6">
+        <v>2.63</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-3.18</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="5">
-        <v>-9.359999999999999</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>-7.34</v>
       </c>
-      <c r="E20" s="6">
-        <v>2.02</v>
+      <c r="D20" s="6">
+        <v>-0.44</v>
+      </c>
+      <c r="E20" s="7">
+        <v>6.9</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>20.87</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>20.02</v>
       </c>
+      <c r="D21" s="6">
+        <v>21.28</v>
+      </c>
       <c r="E21" s="7">
-        <v>-0.85</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C22" s="5">
-        <v>13.29</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>13.82</v>
       </c>
-      <c r="E22" s="6">
-        <v>0.53</v>
+      <c r="D22" s="6">
+        <v>14.89</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.07</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="5">
-        <v>-11.99</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>-8.210000000000001</v>
       </c>
-      <c r="E23" s="6">
+      <c r="D23" s="6">
+        <v>-7.39</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-20.97</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-20.18</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="6">
+        <v>-40.5</v>
+      </c>
+      <c r="D25" s="6">
+        <v>-39.68</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2.65</v>
+      </c>
+      <c r="D26" s="6">
         <v>3.78</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="E26" s="7">
+        <v>1.13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-24.21</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-23.03</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="6">
+        <v>2.32</v>
+      </c>
+      <c r="D28" s="6">
+        <v>2.86</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-1.4</v>
+      </c>
+      <c r="D29" s="6">
+        <v>0.04</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-11.85</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-11.02</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-19.91</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-20.97</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.06</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-15.95</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-15.6</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="5">
-        <v>-40.27</v>
-      </c>
-      <c r="D25" s="5">
-        <v>-40.5</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="6">
+        <v>-19.18</v>
+      </c>
+      <c r="D32" s="6">
+        <v>-19.55</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="5">
-        <v>10.83</v>
-      </c>
-      <c r="D26" s="5">
-        <v>2.65</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-8.18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.18</v>
+      </c>
+      <c r="D33" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-23.49</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-24.21</v>
-      </c>
-      <c r="E27" s="7">
+      <c r="B34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C34" s="6">
+        <v>-17.31</v>
+      </c>
+      <c r="D34" s="6">
+        <v>-16.68</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-16.23</v>
+      </c>
+      <c r="D35" s="6">
+        <v>-16.22</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="6">
+        <v>-14.77</v>
+      </c>
+      <c r="D36" s="6">
+        <v>-15.02</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="6">
+        <v>-20.35</v>
+      </c>
+      <c r="D37" s="6">
+        <v>-17.31</v>
+      </c>
+      <c r="E37" s="7">
+        <v>3.04</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="6">
+        <v>-28.98</v>
+      </c>
+      <c r="D38" s="6">
+        <v>-28.3</v>
+      </c>
+      <c r="E38" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-43.04</v>
+      </c>
+      <c r="D39" s="6">
+        <v>-42.5</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="6">
+        <v>-25.42</v>
+      </c>
+      <c r="D40" s="6">
+        <v>-25.79</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="6">
+        <v>-22.97</v>
+      </c>
+      <c r="D41" s="6">
+        <v>-22.2</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C42" s="6">
+        <v>1086.1</v>
+      </c>
+      <c r="D42" s="6">
+        <v>1086.2</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6">
+        <v>832.3</v>
+      </c>
+      <c r="D43" s="6">
+        <v>829.8</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="6">
+        <v>1545.2</v>
+      </c>
+      <c r="D44" s="6">
+        <v>1604.2</v>
+      </c>
+      <c r="E44" s="7">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6">
+        <v>1703.5</v>
+      </c>
+      <c r="D45" s="6">
+        <v>1719.8</v>
+      </c>
+      <c r="E45" s="7">
+        <v>16.3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C46" s="6">
+        <v>620.7</v>
+      </c>
+      <c r="D46" s="6">
+        <v>626.65</v>
+      </c>
+      <c r="E46" s="7">
+        <v>5.95</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6">
+        <v>2576.8</v>
+      </c>
+      <c r="D47" s="6">
+        <v>2563.8</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C48" s="6">
+        <v>6862.5</v>
+      </c>
+      <c r="D48" s="6">
+        <v>6856.5</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" s="6">
+        <v>42.92</v>
+      </c>
+      <c r="D49" s="6">
+        <v>42.94</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C50" s="6">
+        <v>44.01</v>
+      </c>
+      <c r="D50" s="6">
+        <v>43.43</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="6">
+        <v>43.11</v>
+      </c>
+      <c r="D51" s="6">
+        <v>50.68</v>
+      </c>
+      <c r="E51" s="7">
+        <v>7.57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C52" s="6">
+        <v>36.88</v>
+      </c>
+      <c r="D52" s="6">
+        <v>39.77</v>
+      </c>
+      <c r="E52" s="7">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="6">
+        <v>26.69</v>
+      </c>
+      <c r="D53" s="6">
+        <v>29.96</v>
+      </c>
+      <c r="E53" s="7">
+        <v>3.27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" s="6">
+        <v>40.08</v>
+      </c>
+      <c r="D54" s="6">
+        <v>39.36</v>
+      </c>
+      <c r="E54" s="8">
         <v>-0.72</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+    <row r="55" spans="1:5">
+      <c r="A55" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="6">
+        <v>29.2</v>
+      </c>
+      <c r="D55" s="6">
+        <v>29.11</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="5">
-        <v>2.29</v>
-      </c>
-      <c r="D28" s="5">
-        <v>2.32</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B56" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="6">
+        <v>-76.09</v>
+      </c>
+      <c r="D56" s="6">
+        <v>-42.13</v>
+      </c>
+      <c r="E56" s="7">
+        <v>33.96</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-4.78</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-1.4</v>
-      </c>
-      <c r="E29" s="6">
-        <v>3.38</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B57" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="6">
+        <v>-63.39</v>
+      </c>
+      <c r="D57" s="6">
+        <v>-38.77</v>
+      </c>
+      <c r="E57" s="7">
+        <v>24.62</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-17.71</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-11.85</v>
-      </c>
-      <c r="E30" s="6">
-        <v>5.86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B58" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="6">
+        <v>88.61</v>
+      </c>
+      <c r="D58" s="6">
+        <v>174.69</v>
+      </c>
+      <c r="E58" s="7">
+        <v>86.08</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-13.24</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-15.95</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-2.71</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B59" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="6">
+        <v>-60.76</v>
+      </c>
+      <c r="D59" s="6">
+        <v>-21.61</v>
+      </c>
+      <c r="E59" s="7">
+        <v>39.15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5">
-        <v>-19.51</v>
-      </c>
-      <c r="D32" s="5">
-        <v>-19.18</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B60" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="6">
+        <v>-71.45</v>
+      </c>
+      <c r="D60" s="6">
+        <v>-69.65000000000001</v>
+      </c>
+      <c r="E60" s="7">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="5">
-        <v>1.53</v>
-      </c>
-      <c r="D33" s="5">
-        <v>0.18</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B61" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="6">
+        <v>-43.35</v>
+      </c>
+      <c r="D61" s="6">
+        <v>-61.65</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-18.3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="5">
-        <v>-16.06</v>
-      </c>
-      <c r="D34" s="5">
-        <v>-17.31</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="5">
-        <v>-15.33</v>
-      </c>
-      <c r="D35" s="5">
-        <v>-16.23</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="5">
-        <v>-14.45</v>
-      </c>
-      <c r="D36" s="5">
-        <v>-14.77</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.32</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="5">
-        <v>-24.28</v>
-      </c>
-      <c r="D37" s="5">
-        <v>-20.35</v>
-      </c>
-      <c r="E37" s="6">
-        <v>3.93</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="5">
-        <v>-27.53</v>
-      </c>
-      <c r="D38" s="5">
-        <v>-28.98</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="5">
-        <v>-23.8</v>
-      </c>
-      <c r="D39" s="5">
-        <v>-25.42</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-1.62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="5">
-        <v>-23.03</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-22.97</v>
-      </c>
-      <c r="E40" s="6">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="5">
-        <v>1097.7</v>
-      </c>
-      <c r="D41" s="5">
-        <v>1086.1</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-11.6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C42" s="5">
-        <v>835.4</v>
-      </c>
-      <c r="D42" s="5">
-        <v>832.3</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C43" s="5">
-        <v>1469</v>
-      </c>
-      <c r="D43" s="5">
-        <v>1545.2</v>
-      </c>
-      <c r="E43" s="6">
-        <v>76.2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C44" s="5">
-        <v>1738.4</v>
-      </c>
-      <c r="D44" s="5">
-        <v>1703.5</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-34.9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C45" s="5">
-        <v>2632.6</v>
-      </c>
-      <c r="D45" s="5">
-        <v>2576.8</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-55.8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C46" s="5">
-        <v>6969</v>
-      </c>
-      <c r="D46" s="5">
-        <v>6862.5</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-106.5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C47" s="5">
-        <v>71</v>
-      </c>
-      <c r="D47" s="5">
-        <v>85</v>
-      </c>
-      <c r="E47" s="6">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C48" s="5">
-        <v>85</v>
-      </c>
-      <c r="D48" s="5">
-        <v>71</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C49" s="5">
-        <v>44.24</v>
-      </c>
-      <c r="D49" s="5">
-        <v>42.92</v>
-      </c>
-      <c r="E49" s="7">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C50" s="5">
-        <v>44.7</v>
-      </c>
-      <c r="D50" s="5">
-        <v>44.01</v>
-      </c>
-      <c r="E50" s="7">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C51" s="5">
-        <v>30.27</v>
-      </c>
-      <c r="D51" s="5">
-        <v>43.11</v>
-      </c>
-      <c r="E51" s="6">
-        <v>12.84</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C52" s="5">
-        <v>40.78</v>
-      </c>
-      <c r="D52" s="5">
-        <v>36.88</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-3.9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C53" s="5">
-        <v>43.21</v>
-      </c>
-      <c r="D53" s="5">
-        <v>40.08</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-3.13</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C54" s="5">
-        <v>30.69</v>
-      </c>
-      <c r="D54" s="5">
-        <v>29.2</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-1.49</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
-      <c r="A55" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B55" s="3" t="s">
+      <c r="B62" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C55" s="5">
-        <v>-14.39</v>
-      </c>
-      <c r="D55" s="5">
-        <v>-76.09</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-61.7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
-      <c r="A56" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C56" s="5">
-        <v>-18.6</v>
-      </c>
-      <c r="D56" s="5">
-        <v>-63.39</v>
-      </c>
-      <c r="E56" s="7">
-        <v>-44.79</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5">
-      <c r="A57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C57" s="5">
-        <v>-4.36</v>
-      </c>
-      <c r="D57" s="5">
-        <v>88.61</v>
-      </c>
-      <c r="E57" s="6">
-        <v>92.97</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5">
-      <c r="A58" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C58" s="5">
-        <v>-57.25</v>
-      </c>
-      <c r="D58" s="5">
-        <v>-60.76</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-3.51</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C59" s="5">
-        <v>-45.63</v>
-      </c>
-      <c r="D59" s="5">
-        <v>-71.45</v>
-      </c>
-      <c r="E59" s="7">
-        <v>-25.82</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C60" s="5">
-        <v>-29.93</v>
-      </c>
-      <c r="D60" s="5">
-        <v>-43.35</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-13.42</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5">
-      <c r="A61" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C61" s="5">
-        <v>-32.9</v>
-      </c>
-      <c r="D61" s="5">
+      <c r="C62" s="6">
         <v>-43.63</v>
       </c>
-      <c r="E61" s="7">
-        <v>-10.73</v>
+      <c r="D62" s="6">
+        <v>-14.52</v>
+      </c>
+      <c r="E62" s="7">
+        <v>29.11</v>
       </c>
     </row>
   </sheetData>
@@ -2821,60 +2904,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="11">
+        <v>49.96</v>
+      </c>
+      <c r="C2" s="12">
+        <v>7</v>
+      </c>
+      <c r="D2" s="11">
+        <v>39.3</v>
+      </c>
+      <c r="E2" s="11">
+        <v>42.9</v>
+      </c>
+      <c r="F2" s="11">
+        <v>-10.1</v>
+      </c>
+      <c r="G2" s="11">
+        <v>-8.5</v>
+      </c>
+      <c r="H2" s="11">
         <v>57</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="10">
-        <v>49.96</v>
-      </c>
-      <c r="C2" s="11">
-        <v>7</v>
-      </c>
-      <c r="D2" s="10">
-        <v>37.6</v>
-      </c>
-      <c r="E2" s="10">
-        <v>42.9</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-12.6</v>
-      </c>
-      <c r="G2" s="10">
-        <v>-9</v>
-      </c>
-      <c r="H2" s="10">
-        <v>57</v>
-      </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>14.3</v>
       </c>
     </row>
@@ -2976,49 +3059,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="13">
-        <v>0.4115</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.2622</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.2069</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.1738</v>
-      </c>
-      <c r="E2" s="13">
-        <v>0.0951</v>
-      </c>
-      <c r="F2" s="13">
-        <v>0.07519999999999999</v>
-      </c>
-      <c r="G2" s="13">
-        <v>0.0547</v>
+      <c r="A2" s="14">
+        <v>0.4185</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.2621</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.2137</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.1794</v>
+      </c>
+      <c r="E2" s="14">
+        <v>0.09660000000000001</v>
+      </c>
+      <c r="F2" s="14">
+        <v>0.07580000000000001</v>
+      </c>
+      <c r="G2" s="14">
+        <v>0.0564</v>
       </c>
     </row>
   </sheetData>

--- a/MURUGAPPA_GROUP_Technical_Metrics.xlsx
+++ b/MURUGAPPA_GROUP_Technical_Metrics.xlsx
@@ -190,16 +190,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>43.1 → 50.7</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>43.1</t>
+    <t>50.7 → 48.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.7</t>
+  </si>
+  <si>
+    <t>48.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -924,10 +924,10 @@
         <v>44</v>
       </c>
       <c r="C2">
-        <v>1086.2</v>
+        <v>1030.3</v>
       </c>
       <c r="D2">
-        <v>0.01</v>
+        <v>-5.15</v>
       </c>
       <c r="E2">
         <v>1296.5</v>
@@ -936,46 +936,46 @@
         <v>748.35</v>
       </c>
       <c r="G2">
-        <v>-16.22</v>
+        <v>-20.53</v>
       </c>
       <c r="H2">
-        <v>45.15</v>
+        <v>37.68</v>
       </c>
       <c r="I2">
-        <v>2.99</v>
+        <v>0.15</v>
       </c>
       <c r="J2">
-        <v>-12.95</v>
+        <v>-14.18</v>
       </c>
       <c r="K2">
-        <v>2.86</v>
+        <v>-1.97</v>
       </c>
       <c r="L2">
-        <v>21.28</v>
+        <v>13.65</v>
       </c>
       <c r="M2">
-        <v>5.64</v>
+        <v>4.67</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="P2">
-        <v>1085.6</v>
+        <v>1085.9</v>
       </c>
       <c r="Q2">
-        <v>1154.8</v>
+        <v>1143.69</v>
       </c>
       <c r="R2">
-        <v>1141.75</v>
+        <v>1139.83</v>
       </c>
       <c r="S2">
-        <v>1002.98</v>
+        <v>1004.11</v>
       </c>
       <c r="T2">
-        <v>8.300000000000001</v>
+        <v>2.61</v>
       </c>
       <c r="U2" t="s">
         <v>45</v>
@@ -990,34 +990,34 @@
         <v>3</v>
       </c>
       <c r="Y2">
-        <v>42.94</v>
+        <v>36.83</v>
       </c>
       <c r="Z2">
-        <v>-25.23</v>
+        <v>-29.55</v>
       </c>
       <c r="AA2">
-        <v>-15.9</v>
+        <v>-18.63</v>
       </c>
       <c r="AB2">
-        <v>-9.33</v>
+        <v>-10.92</v>
       </c>
       <c r="AC2">
-        <v>52.41</v>
+        <v>47.21</v>
       </c>
       <c r="AD2">
-        <v>45.57</v>
+        <v>50.29</v>
       </c>
       <c r="AE2">
-        <v>55.74</v>
+        <v>56.33</v>
       </c>
       <c r="AF2">
-        <v>-42.13</v>
+        <v>-33.1</v>
       </c>
       <c r="AG2">
-        <v>1312.61</v>
+        <v>1303.81</v>
       </c>
       <c r="AH2">
-        <v>997</v>
+        <v>983.58</v>
       </c>
       <c r="AI2">
         <v>1168</v>
@@ -1026,7 +1026,7 @@
         <v>47</v>
       </c>
       <c r="AK2">
-        <v>29.26</v>
+        <v>27.33</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1037,10 +1037,10 @@
         <v>44</v>
       </c>
       <c r="C3">
-        <v>829.8</v>
+        <v>804</v>
       </c>
       <c r="D3">
-        <v>-0.3</v>
+        <v>-3.11</v>
       </c>
       <c r="E3">
         <v>976.5</v>
@@ -1049,46 +1049,46 @@
         <v>529.48</v>
       </c>
       <c r="G3">
-        <v>-15.02</v>
+        <v>-17.67</v>
       </c>
       <c r="H3">
-        <v>56.72</v>
+        <v>51.85</v>
       </c>
       <c r="I3">
-        <v>1.55</v>
+        <v>-1.15</v>
       </c>
       <c r="J3">
-        <v>-4.07</v>
+        <v>-6.3</v>
       </c>
       <c r="K3">
-        <v>0.04</v>
+        <v>-3.44</v>
       </c>
       <c r="L3">
-        <v>14.89</v>
+        <v>10.63</v>
       </c>
       <c r="M3">
-        <v>41.85</v>
+        <v>40.5</v>
       </c>
       <c r="N3">
         <v>85</v>
       </c>
       <c r="O3">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P3">
-        <v>828.8200000000001</v>
+        <v>826.95</v>
       </c>
       <c r="Q3">
-        <v>851.26</v>
+        <v>848.75</v>
       </c>
       <c r="R3">
-        <v>872.67</v>
+        <v>870.87</v>
       </c>
       <c r="S3">
-        <v>812.58</v>
+        <v>813.64</v>
       </c>
       <c r="T3">
-        <v>2.12</v>
+        <v>-1.18</v>
       </c>
       <c r="U3" t="s">
         <v>46</v>
@@ -1100,37 +1100,37 @@
         <v>46</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>43.43</v>
+        <v>37.87</v>
       </c>
       <c r="Z3">
-        <v>-14.44</v>
+        <v>-16.06</v>
       </c>
       <c r="AA3">
-        <v>-13.37</v>
+        <v>-13.91</v>
       </c>
       <c r="AB3">
-        <v>-1.07</v>
+        <v>-2.15</v>
       </c>
       <c r="AC3">
-        <v>64.56</v>
+        <v>50.98</v>
       </c>
       <c r="AD3">
-        <v>49.93</v>
+        <v>56.36</v>
       </c>
       <c r="AE3">
-        <v>28.2</v>
+        <v>28.24</v>
       </c>
       <c r="AF3">
-        <v>-38.77</v>
+        <v>-13.1</v>
       </c>
       <c r="AG3">
-        <v>905.38</v>
+        <v>906.8099999999999</v>
       </c>
       <c r="AH3">
-        <v>797.15</v>
+        <v>790.7</v>
       </c>
       <c r="AI3">
         <v>888.53</v>
@@ -1139,7 +1139,7 @@
         <v>47</v>
       </c>
       <c r="AK3">
-        <v>30.87</v>
+        <v>32.65</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1150,10 +1150,10 @@
         <v>44</v>
       </c>
       <c r="C4">
-        <v>1604.2</v>
+        <v>1586</v>
       </c>
       <c r="D4">
-        <v>3.82</v>
+        <v>-1.13</v>
       </c>
       <c r="E4">
         <v>1940</v>
@@ -1162,46 +1162,46 @@
         <v>1354.7</v>
       </c>
       <c r="G4">
-        <v>-17.31</v>
+        <v>-18.25</v>
       </c>
       <c r="H4">
-        <v>18.42</v>
+        <v>17.07</v>
       </c>
       <c r="I4">
-        <v>4.79</v>
+        <v>8.35</v>
       </c>
       <c r="J4">
-        <v>-1.84</v>
+        <v>-2.54</v>
       </c>
       <c r="K4">
-        <v>-11.02</v>
+        <v>-10.59</v>
       </c>
       <c r="L4">
-        <v>-7.39</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="M4">
-        <v>21.37</v>
+        <v>22.17</v>
       </c>
       <c r="N4">
         <v>57</v>
       </c>
       <c r="O4">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P4">
-        <v>1506.02</v>
+        <v>1530.46</v>
       </c>
       <c r="Q4">
-        <v>1559.07</v>
+        <v>1557.37</v>
       </c>
       <c r="R4">
-        <v>1708.35</v>
+        <v>1702.71</v>
       </c>
       <c r="S4">
-        <v>1666.88</v>
+        <v>1666.23</v>
       </c>
       <c r="T4">
-        <v>-3.76</v>
+        <v>-4.82</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
@@ -1216,43 +1216,43 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>50.68</v>
+        <v>48.54</v>
       </c>
       <c r="Z4">
-        <v>-51.15</v>
+        <v>-44</v>
       </c>
       <c r="AA4">
-        <v>-59.75</v>
+        <v>-56.6</v>
       </c>
       <c r="AB4">
-        <v>8.609999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="AC4">
-        <v>78.63</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AD4">
-        <v>49.05</v>
+        <v>74.66</v>
       </c>
       <c r="AE4">
-        <v>53.28</v>
+        <v>52.12</v>
       </c>
       <c r="AF4">
-        <v>174.69</v>
+        <v>88.17</v>
       </c>
       <c r="AG4">
-        <v>1660.39</v>
+        <v>1655.48</v>
       </c>
       <c r="AH4">
-        <v>1457.75</v>
+        <v>1459.26</v>
       </c>
       <c r="AI4">
-        <v>1424.16</v>
+        <v>1448.15</v>
       </c>
       <c r="AJ4" t="s">
         <v>48</v>
       </c>
       <c r="AK4">
-        <v>48.8</v>
+        <v>45.34</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1263,10 +1263,10 @@
         <v>44</v>
       </c>
       <c r="C5">
-        <v>1719.8</v>
+        <v>1696</v>
       </c>
       <c r="D5">
-        <v>0.96</v>
+        <v>-1.38</v>
       </c>
       <c r="E5">
         <v>2398.74</v>
@@ -1275,25 +1275,25 @@
         <v>1673.7</v>
       </c>
       <c r="G5">
-        <v>-28.3</v>
+        <v>-29.3</v>
       </c>
       <c r="H5">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="I5">
-        <v>-3.2</v>
+        <v>-1.28</v>
       </c>
       <c r="J5">
-        <v>-9.44</v>
+        <v>-5.4</v>
       </c>
       <c r="K5">
-        <v>-15.6</v>
+        <v>-17.44</v>
       </c>
       <c r="L5">
-        <v>-20.18</v>
+        <v>-24.15</v>
       </c>
       <c r="M5">
-        <v>17.94</v>
+        <v>17.66</v>
       </c>
       <c r="N5">
         <v>43</v>
@@ -1302,19 +1302,19 @@
         <v>35</v>
       </c>
       <c r="P5">
-        <v>1722.06</v>
+        <v>1717.66</v>
       </c>
       <c r="Q5">
-        <v>1743.39</v>
+        <v>1740.28</v>
       </c>
       <c r="R5">
-        <v>1864.81</v>
+        <v>1857.48</v>
       </c>
       <c r="S5">
-        <v>2006.71</v>
+        <v>2003.7</v>
       </c>
       <c r="T5">
-        <v>-14.3</v>
+        <v>-15.36</v>
       </c>
       <c r="U5" t="s">
         <v>46</v>
@@ -1329,34 +1329,34 @@
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>39.77</v>
+        <v>37.1</v>
       </c>
       <c r="Z5">
-        <v>-41.51</v>
+        <v>-42.16</v>
       </c>
       <c r="AA5">
-        <v>-45.64</v>
+        <v>-44.94</v>
       </c>
       <c r="AB5">
-        <v>4.13</v>
+        <v>2.78</v>
       </c>
       <c r="AC5">
-        <v>64.23999999999999</v>
+        <v>54.64</v>
       </c>
       <c r="AD5">
-        <v>65.78</v>
+        <v>61.68</v>
       </c>
       <c r="AE5">
-        <v>56.79</v>
+        <v>57.35</v>
       </c>
       <c r="AF5">
-        <v>-21.61</v>
+        <v>-6.45</v>
       </c>
       <c r="AG5">
-        <v>1813.94</v>
+        <v>1813.51</v>
       </c>
       <c r="AH5">
-        <v>1672.85</v>
+        <v>1667.06</v>
       </c>
       <c r="AI5">
         <v>1853.75</v>
@@ -1365,7 +1365,7 @@
         <v>47</v>
       </c>
       <c r="AK5">
-        <v>17</v>
+        <v>18.65</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1376,58 +1376,58 @@
         <v>44</v>
       </c>
       <c r="C6">
-        <v>626.65</v>
+        <v>600.45</v>
       </c>
       <c r="D6">
-        <v>0.96</v>
+        <v>-4.18</v>
       </c>
       <c r="E6">
         <v>1089.8</v>
       </c>
       <c r="F6">
-        <v>620.7</v>
+        <v>600.45</v>
       </c>
       <c r="G6">
-        <v>-42.5</v>
+        <v>-44.9</v>
       </c>
       <c r="H6">
-        <v>0.96</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>-3.21</v>
+        <v>-4.31</v>
       </c>
       <c r="J6">
-        <v>-11.3</v>
+        <v>-13.76</v>
       </c>
       <c r="K6">
-        <v>-19.55</v>
+        <v>-21.32</v>
       </c>
       <c r="L6">
-        <v>-39.68</v>
+        <v>-43.68</v>
       </c>
       <c r="M6">
-        <v>7.58</v>
+        <v>6.62</v>
       </c>
       <c r="N6">
         <v>15</v>
       </c>
       <c r="O6">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P6">
-        <v>623.5</v>
+        <v>618.09</v>
       </c>
       <c r="Q6">
-        <v>670.36</v>
+        <v>666.09</v>
       </c>
       <c r="R6">
-        <v>720.53</v>
+        <v>716.9299999999999</v>
       </c>
       <c r="S6">
-        <v>791.4400000000001</v>
+        <v>789.74</v>
       </c>
       <c r="T6">
-        <v>-20.82</v>
+        <v>-23.97</v>
       </c>
       <c r="U6" t="s">
         <v>46</v>
@@ -1442,43 +1442,43 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>29.96</v>
+        <v>24.73</v>
       </c>
       <c r="Z6">
-        <v>-26.1</v>
+        <v>-28.01</v>
       </c>
       <c r="AA6">
-        <v>-21.72</v>
+        <v>-22.98</v>
       </c>
       <c r="AB6">
-        <v>-4.38</v>
+        <v>-5.03</v>
       </c>
       <c r="AC6">
         <v>5.3</v>
       </c>
       <c r="AD6">
-        <v>1.77</v>
+        <v>3.53</v>
       </c>
       <c r="AE6">
-        <v>18.31</v>
+        <v>19.39</v>
       </c>
       <c r="AF6">
-        <v>-69.65000000000001</v>
+        <v>24.83</v>
       </c>
       <c r="AG6">
-        <v>733.14</v>
+        <v>735.6799999999999</v>
       </c>
       <c r="AH6">
-        <v>607.5700000000001</v>
+        <v>596.49</v>
       </c>
       <c r="AI6">
-        <v>676.99</v>
+        <v>669.1799999999999</v>
       </c>
       <c r="AJ6" t="s">
         <v>47</v>
       </c>
       <c r="AK6">
-        <v>46.57</v>
+        <v>49.71</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1489,10 +1489,10 @@
         <v>44</v>
       </c>
       <c r="C7">
-        <v>2563.8</v>
+        <v>2583.9</v>
       </c>
       <c r="D7">
-        <v>-0.5</v>
+        <v>0.78</v>
       </c>
       <c r="E7">
         <v>3454.9</v>
@@ -1501,46 +1501,46 @@
         <v>1891.45</v>
       </c>
       <c r="G7">
-        <v>-25.79</v>
+        <v>-25.21</v>
       </c>
       <c r="H7">
-        <v>35.55</v>
+        <v>36.61</v>
       </c>
       <c r="I7">
-        <v>2.63</v>
+        <v>3.04</v>
       </c>
       <c r="J7">
-        <v>-12.48</v>
+        <v>-11.7</v>
       </c>
       <c r="K7">
-        <v>0.77</v>
+        <v>1.08</v>
       </c>
       <c r="L7">
-        <v>3.78</v>
+        <v>4.85</v>
       </c>
       <c r="M7">
-        <v>26.21</v>
+        <v>25.86</v>
       </c>
       <c r="N7">
         <v>71</v>
       </c>
       <c r="O7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P7">
-        <v>2563.88</v>
+        <v>2579.14</v>
       </c>
       <c r="Q7">
-        <v>2642.54</v>
+        <v>2626.69</v>
       </c>
       <c r="R7">
-        <v>2962.48</v>
+        <v>2948.56</v>
       </c>
       <c r="S7">
-        <v>2538.22</v>
+        <v>2540.42</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U7" t="s">
         <v>46</v>
@@ -1555,34 +1555,34 @@
         <v>2</v>
       </c>
       <c r="Y7">
-        <v>39.36</v>
+        <v>41.11</v>
       </c>
       <c r="Z7">
-        <v>-107.17</v>
+        <v>-100.04</v>
       </c>
       <c r="AA7">
-        <v>-117</v>
+        <v>-113.61</v>
       </c>
       <c r="AB7">
-        <v>9.83</v>
+        <v>13.57</v>
       </c>
       <c r="AC7">
-        <v>87.90000000000001</v>
+        <v>83.91</v>
       </c>
       <c r="AD7">
-        <v>93.13</v>
+        <v>89.01000000000001</v>
       </c>
       <c r="AE7">
-        <v>121.79</v>
+        <v>118.59</v>
       </c>
       <c r="AF7">
-        <v>-61.65</v>
+        <v>-55.63</v>
       </c>
       <c r="AG7">
-        <v>2900.5</v>
+        <v>2855.06</v>
       </c>
       <c r="AH7">
-        <v>2384.58</v>
+        <v>2398.32</v>
       </c>
       <c r="AI7">
         <v>2851.41</v>
@@ -1591,7 +1591,7 @@
         <v>47</v>
       </c>
       <c r="AK7">
-        <v>49.92</v>
+        <v>47.75</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1602,10 +1602,10 @@
         <v>44</v>
       </c>
       <c r="C8">
-        <v>6856.5</v>
+        <v>6761</v>
       </c>
       <c r="D8">
-        <v>-0.09</v>
+        <v>-1.39</v>
       </c>
       <c r="E8">
         <v>8812.5</v>
@@ -1614,46 +1614,46 @@
         <v>5924.5</v>
       </c>
       <c r="G8">
-        <v>-22.2</v>
+        <v>-23.28</v>
       </c>
       <c r="H8">
-        <v>15.73</v>
+        <v>14.12</v>
       </c>
       <c r="I8">
-        <v>-0.44</v>
+        <v>-4.67</v>
       </c>
       <c r="J8">
-        <v>-18.94</v>
+        <v>-19.46</v>
       </c>
       <c r="K8">
-        <v>-16.68</v>
+        <v>-16.57</v>
       </c>
       <c r="L8">
-        <v>-23.03</v>
+        <v>-22.57</v>
       </c>
       <c r="M8">
-        <v>9.66</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="N8">
         <v>29</v>
       </c>
       <c r="O8">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="P8">
-        <v>6983.6</v>
+        <v>6917.4</v>
       </c>
       <c r="Q8">
-        <v>7595.3</v>
+        <v>7515.78</v>
       </c>
       <c r="R8">
-        <v>8068.33</v>
+        <v>8042.45</v>
       </c>
       <c r="S8">
-        <v>7406.98</v>
+        <v>7403.86</v>
       </c>
       <c r="T8">
-        <v>-7.43</v>
+        <v>-8.68</v>
       </c>
       <c r="U8" t="s">
         <v>46</v>
@@ -1668,43 +1668,43 @@
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>29.11</v>
+        <v>27.71</v>
       </c>
       <c r="Z8">
-        <v>-356.7</v>
+        <v>-371.14</v>
       </c>
       <c r="AA8">
-        <v>-273.08</v>
+        <v>-292.69</v>
       </c>
       <c r="AB8">
-        <v>-83.62</v>
+        <v>-78.45</v>
       </c>
       <c r="AC8">
-        <v>25.39</v>
+        <v>19.64</v>
       </c>
       <c r="AD8">
-        <v>32.3</v>
+        <v>26.1</v>
       </c>
       <c r="AE8">
-        <v>337.2</v>
+        <v>326.69</v>
       </c>
       <c r="AF8">
-        <v>-14.52</v>
+        <v>-67.86</v>
       </c>
       <c r="AG8">
-        <v>8533.549999999999</v>
+        <v>8453.77</v>
       </c>
       <c r="AH8">
-        <v>6657.05</v>
+        <v>6577.78</v>
       </c>
       <c r="AI8">
-        <v>7939.2</v>
+        <v>7825.06</v>
       </c>
       <c r="AJ8" t="s">
         <v>47</v>
       </c>
       <c r="AK8">
-        <v>53.43</v>
+        <v>54.71</v>
       </c>
     </row>
   </sheetData>
@@ -1808,27 +1808,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U8">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",U2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="16" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",U2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V8">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W8">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Y2:Y8">
@@ -1937,13 +1937,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-15.05</v>
+        <v>-12.95</v>
       </c>
       <c r="D7" s="6">
-        <v>-12.95</v>
+        <v>-14.18</v>
       </c>
       <c r="E7" s="7">
-        <v>2.1</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1954,13 +1954,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-6.06</v>
+        <v>-4.07</v>
       </c>
       <c r="D8" s="6">
-        <v>-4.07</v>
+        <v>-6.3</v>
       </c>
       <c r="E8" s="7">
-        <v>1.99</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1971,13 +1971,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-7.07</v>
+        <v>-1.84</v>
       </c>
       <c r="D9" s="6">
-        <v>-1.84</v>
+        <v>-2.54</v>
       </c>
       <c r="E9" s="7">
-        <v>5.23</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1988,13 +1988,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-13.26</v>
+        <v>-9.44</v>
       </c>
       <c r="D10" s="6">
-        <v>-9.44</v>
-      </c>
-      <c r="E10" s="7">
-        <v>3.82</v>
+        <v>-5.4</v>
+      </c>
+      <c r="E10" s="8">
+        <v>4.04</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -2005,13 +2005,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-11.93</v>
+        <v>-11.3</v>
       </c>
       <c r="D11" s="6">
-        <v>-11.3</v>
+        <v>-13.76</v>
       </c>
       <c r="E11" s="7">
-        <v>0.63</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -2022,13 +2022,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-14.2</v>
+        <v>-12.48</v>
       </c>
       <c r="D12" s="6">
-        <v>-12.48</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.72</v>
+        <v>-11.7</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.78</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -2039,13 +2039,13 @@
         <v>9</v>
       </c>
       <c r="C13" s="6">
-        <v>-20.63</v>
+        <v>-18.94</v>
       </c>
       <c r="D13" s="6">
-        <v>-18.94</v>
+        <v>-19.46</v>
       </c>
       <c r="E13" s="7">
-        <v>1.69</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -2056,13 +2056,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>2.47</v>
+        <v>2.99</v>
       </c>
       <c r="D14" s="6">
-        <v>2.99</v>
+        <v>0.15</v>
       </c>
       <c r="E14" s="7">
-        <v>0.52</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -2073,13 +2073,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="D15" s="6">
-        <v>1.55</v>
+        <v>-1.15</v>
       </c>
       <c r="E15" s="7">
-        <v>0.17</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -2090,13 +2090,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>1</v>
+        <v>4.79</v>
       </c>
       <c r="D16" s="6">
-        <v>4.79</v>
-      </c>
-      <c r="E16" s="7">
-        <v>3.79</v>
+        <v>8.35</v>
+      </c>
+      <c r="E16" s="8">
+        <v>3.56</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2107,13 +2107,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.92</v>
+        <v>-3.2</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.2</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.72</v>
+        <v>-1.28</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.92</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -2124,13 +2124,13 @@
         <v>8</v>
       </c>
       <c r="C18" s="6">
-        <v>-5.54</v>
+        <v>-3.21</v>
       </c>
       <c r="D18" s="6">
-        <v>-3.21</v>
+        <v>-4.31</v>
       </c>
       <c r="E18" s="7">
-        <v>2.33</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -2141,13 +2141,13 @@
         <v>8</v>
       </c>
       <c r="C19" s="6">
-        <v>5.81</v>
+        <v>2.63</v>
       </c>
       <c r="D19" s="6">
-        <v>2.63</v>
+        <v>3.04</v>
       </c>
       <c r="E19" s="8">
-        <v>-3.18</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -2158,13 +2158,13 @@
         <v>8</v>
       </c>
       <c r="C20" s="6">
-        <v>-7.34</v>
+        <v>-0.44</v>
       </c>
       <c r="D20" s="6">
-        <v>-0.44</v>
+        <v>-4.67</v>
       </c>
       <c r="E20" s="7">
-        <v>6.9</v>
+        <v>-4.23</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -2175,13 +2175,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>20.02</v>
+        <v>21.28</v>
       </c>
       <c r="D21" s="6">
-        <v>21.28</v>
+        <v>13.65</v>
       </c>
       <c r="E21" s="7">
-        <v>1.26</v>
+        <v>-7.63</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -2192,13 +2192,13 @@
         <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>13.82</v>
+        <v>14.89</v>
       </c>
       <c r="D22" s="6">
-        <v>14.89</v>
+        <v>10.63</v>
       </c>
       <c r="E22" s="7">
-        <v>1.07</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -2209,13 +2209,13 @@
         <v>11</v>
       </c>
       <c r="C23" s="6">
-        <v>-8.210000000000001</v>
+        <v>-7.39</v>
       </c>
       <c r="D23" s="6">
-        <v>-7.39</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="E23" s="7">
-        <v>0.82</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -2226,13 +2226,13 @@
         <v>11</v>
       </c>
       <c r="C24" s="6">
-        <v>-20.97</v>
+        <v>-20.18</v>
       </c>
       <c r="D24" s="6">
-        <v>-20.18</v>
+        <v>-24.15</v>
       </c>
       <c r="E24" s="7">
-        <v>0.79</v>
+        <v>-3.97</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2243,13 +2243,13 @@
         <v>11</v>
       </c>
       <c r="C25" s="6">
-        <v>-40.5</v>
+        <v>-39.68</v>
       </c>
       <c r="D25" s="6">
-        <v>-39.68</v>
+        <v>-43.68</v>
       </c>
       <c r="E25" s="7">
-        <v>0.82</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2260,13 +2260,13 @@
         <v>11</v>
       </c>
       <c r="C26" s="6">
-        <v>2.65</v>
+        <v>3.78</v>
       </c>
       <c r="D26" s="6">
-        <v>3.78</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.13</v>
+        <v>4.85</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.07</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2277,13 +2277,13 @@
         <v>11</v>
       </c>
       <c r="C27" s="6">
-        <v>-24.21</v>
+        <v>-23.03</v>
       </c>
       <c r="D27" s="6">
-        <v>-23.03</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.18</v>
+        <v>-22.57</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.46</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2294,13 +2294,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>2.32</v>
+        <v>2.86</v>
       </c>
       <c r="D28" s="6">
-        <v>2.86</v>
+        <v>-1.97</v>
       </c>
       <c r="E28" s="7">
-        <v>0.54</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2311,13 +2311,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-1.4</v>
+        <v>0.04</v>
       </c>
       <c r="D29" s="6">
-        <v>0.04</v>
+        <v>-3.44</v>
       </c>
       <c r="E29" s="7">
-        <v>1.44</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2328,13 +2328,13 @@
         <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-11.85</v>
+        <v>-11.02</v>
       </c>
       <c r="D30" s="6">
-        <v>-11.02</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.83</v>
+        <v>-10.59</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.43</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2345,13 +2345,13 @@
         <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-15.95</v>
+        <v>-15.6</v>
       </c>
       <c r="D31" s="6">
-        <v>-15.6</v>
+        <v>-17.44</v>
       </c>
       <c r="E31" s="7">
-        <v>0.35</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2362,13 +2362,13 @@
         <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-19.18</v>
+        <v>-19.55</v>
       </c>
       <c r="D32" s="6">
-        <v>-19.55</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.37</v>
+        <v>-21.32</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-1.77</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2379,13 +2379,13 @@
         <v>10</v>
       </c>
       <c r="C33" s="6">
-        <v>0.18</v>
+        <v>0.77</v>
       </c>
       <c r="D33" s="6">
-        <v>0.77</v>
-      </c>
-      <c r="E33" s="7">
-        <v>0.59</v>
+        <v>1.08</v>
+      </c>
+      <c r="E33" s="8">
+        <v>0.31</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2396,13 +2396,13 @@
         <v>10</v>
       </c>
       <c r="C34" s="6">
-        <v>-17.31</v>
+        <v>-16.68</v>
       </c>
       <c r="D34" s="6">
-        <v>-16.68</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.63</v>
+        <v>-16.57</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.11</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2413,13 +2413,13 @@
         <v>6</v>
       </c>
       <c r="C35" s="6">
-        <v>-16.23</v>
+        <v>-16.22</v>
       </c>
       <c r="D35" s="6">
-        <v>-16.22</v>
+        <v>-20.53</v>
       </c>
       <c r="E35" s="7">
-        <v>0.01</v>
+        <v>-4.31</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2430,13 +2430,13 @@
         <v>6</v>
       </c>
       <c r="C36" s="6">
-        <v>-14.77</v>
+        <v>-15.02</v>
       </c>
       <c r="D36" s="6">
-        <v>-15.02</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.25</v>
+        <v>-17.67</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-2.65</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2447,13 +2447,13 @@
         <v>6</v>
       </c>
       <c r="C37" s="6">
-        <v>-20.35</v>
+        <v>-17.31</v>
       </c>
       <c r="D37" s="6">
-        <v>-17.31</v>
+        <v>-18.25</v>
       </c>
       <c r="E37" s="7">
-        <v>3.04</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2464,13 +2464,13 @@
         <v>6</v>
       </c>
       <c r="C38" s="6">
-        <v>-28.98</v>
+        <v>-28.3</v>
       </c>
       <c r="D38" s="6">
-        <v>-28.3</v>
+        <v>-29.3</v>
       </c>
       <c r="E38" s="7">
-        <v>0.68</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2481,13 +2481,13 @@
         <v>6</v>
       </c>
       <c r="C39" s="6">
-        <v>-43.04</v>
+        <v>-42.5</v>
       </c>
       <c r="D39" s="6">
-        <v>-42.5</v>
+        <v>-44.9</v>
       </c>
       <c r="E39" s="7">
-        <v>0.54</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2498,13 +2498,13 @@
         <v>6</v>
       </c>
       <c r="C40" s="6">
-        <v>-25.42</v>
+        <v>-25.79</v>
       </c>
       <c r="D40" s="6">
-        <v>-25.79</v>
+        <v>-25.21</v>
       </c>
       <c r="E40" s="8">
-        <v>-0.37</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2515,13 +2515,13 @@
         <v>6</v>
       </c>
       <c r="C41" s="6">
-        <v>-22.97</v>
+        <v>-22.2</v>
       </c>
       <c r="D41" s="6">
-        <v>-22.2</v>
+        <v>-23.28</v>
       </c>
       <c r="E41" s="7">
-        <v>0.77</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2532,13 +2532,13 @@
         <v>2</v>
       </c>
       <c r="C42" s="6">
-        <v>1086.1</v>
+        <v>1086.2</v>
       </c>
       <c r="D42" s="6">
-        <v>1086.2</v>
+        <v>1030.3</v>
       </c>
       <c r="E42" s="7">
-        <v>0.1</v>
+        <v>-55.9</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2549,13 +2549,13 @@
         <v>2</v>
       </c>
       <c r="C43" s="6">
-        <v>832.3</v>
+        <v>829.8</v>
       </c>
       <c r="D43" s="6">
-        <v>829.8</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-2.5</v>
+        <v>804</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-25.8</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2566,13 +2566,13 @@
         <v>2</v>
       </c>
       <c r="C44" s="6">
-        <v>1545.2</v>
+        <v>1604.2</v>
       </c>
       <c r="D44" s="6">
-        <v>1604.2</v>
+        <v>1586</v>
       </c>
       <c r="E44" s="7">
-        <v>59</v>
+        <v>-18.2</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2583,13 +2583,13 @@
         <v>2</v>
       </c>
       <c r="C45" s="6">
-        <v>1703.5</v>
+        <v>1719.8</v>
       </c>
       <c r="D45" s="6">
-        <v>1719.8</v>
+        <v>1696</v>
       </c>
       <c r="E45" s="7">
-        <v>16.3</v>
+        <v>-23.8</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2600,13 +2600,13 @@
         <v>2</v>
       </c>
       <c r="C46" s="6">
-        <v>620.7</v>
+        <v>626.65</v>
       </c>
       <c r="D46" s="6">
-        <v>626.65</v>
+        <v>600.45</v>
       </c>
       <c r="E46" s="7">
-        <v>5.95</v>
+        <v>-26.2</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -2617,13 +2617,13 @@
         <v>2</v>
       </c>
       <c r="C47" s="6">
-        <v>2576.8</v>
+        <v>2563.8</v>
       </c>
       <c r="D47" s="6">
-        <v>2563.8</v>
+        <v>2583.9</v>
       </c>
       <c r="E47" s="8">
-        <v>-13</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -2634,13 +2634,13 @@
         <v>2</v>
       </c>
       <c r="C48" s="6">
-        <v>6862.5</v>
+        <v>6856.5</v>
       </c>
       <c r="D48" s="6">
-        <v>6856.5</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-6</v>
+        <v>6761</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-95.5</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -2651,13 +2651,13 @@
         <v>24</v>
       </c>
       <c r="C49" s="6">
-        <v>42.92</v>
+        <v>42.94</v>
       </c>
       <c r="D49" s="6">
-        <v>42.94</v>
+        <v>36.83</v>
       </c>
       <c r="E49" s="7">
-        <v>0.02</v>
+        <v>-6.11</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -2668,13 +2668,13 @@
         <v>24</v>
       </c>
       <c r="C50" s="6">
-        <v>44.01</v>
+        <v>43.43</v>
       </c>
       <c r="D50" s="6">
-        <v>43.43</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.58</v>
+        <v>37.87</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-5.56</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -2685,13 +2685,13 @@
         <v>24</v>
       </c>
       <c r="C51" s="6">
-        <v>43.11</v>
+        <v>50.68</v>
       </c>
       <c r="D51" s="6">
-        <v>50.68</v>
+        <v>48.54</v>
       </c>
       <c r="E51" s="7">
-        <v>7.57</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -2702,13 +2702,13 @@
         <v>24</v>
       </c>
       <c r="C52" s="6">
-        <v>36.88</v>
+        <v>39.77</v>
       </c>
       <c r="D52" s="6">
-        <v>39.77</v>
+        <v>37.1</v>
       </c>
       <c r="E52" s="7">
-        <v>2.89</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -2719,13 +2719,13 @@
         <v>24</v>
       </c>
       <c r="C53" s="6">
-        <v>26.69</v>
+        <v>29.96</v>
       </c>
       <c r="D53" s="6">
-        <v>29.96</v>
+        <v>24.73</v>
       </c>
       <c r="E53" s="7">
-        <v>3.27</v>
+        <v>-5.23</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -2736,13 +2736,13 @@
         <v>24</v>
       </c>
       <c r="C54" s="6">
-        <v>40.08</v>
+        <v>39.36</v>
       </c>
       <c r="D54" s="6">
-        <v>39.36</v>
+        <v>41.11</v>
       </c>
       <c r="E54" s="8">
-        <v>-0.72</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -2753,13 +2753,13 @@
         <v>24</v>
       </c>
       <c r="C55" s="6">
-        <v>29.2</v>
+        <v>29.11</v>
       </c>
       <c r="D55" s="6">
-        <v>29.11</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-0.09</v>
+        <v>27.71</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -2770,13 +2770,13 @@
         <v>31</v>
       </c>
       <c r="C56" s="6">
-        <v>-76.09</v>
+        <v>-42.13</v>
       </c>
       <c r="D56" s="6">
-        <v>-42.13</v>
-      </c>
-      <c r="E56" s="7">
-        <v>33.96</v>
+        <v>-33.1</v>
+      </c>
+      <c r="E56" s="8">
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -2787,13 +2787,13 @@
         <v>31</v>
       </c>
       <c r="C57" s="6">
-        <v>-63.39</v>
+        <v>-38.77</v>
       </c>
       <c r="D57" s="6">
-        <v>-38.77</v>
-      </c>
-      <c r="E57" s="7">
-        <v>24.62</v>
+        <v>-13.1</v>
+      </c>
+      <c r="E57" s="8">
+        <v>25.67</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -2804,13 +2804,13 @@
         <v>31</v>
       </c>
       <c r="C58" s="6">
-        <v>88.61</v>
+        <v>174.69</v>
       </c>
       <c r="D58" s="6">
-        <v>174.69</v>
+        <v>88.17</v>
       </c>
       <c r="E58" s="7">
-        <v>86.08</v>
+        <v>-86.52</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -2821,13 +2821,13 @@
         <v>31</v>
       </c>
       <c r="C59" s="6">
-        <v>-60.76</v>
+        <v>-21.61</v>
       </c>
       <c r="D59" s="6">
-        <v>-21.61</v>
-      </c>
-      <c r="E59" s="7">
-        <v>39.15</v>
+        <v>-6.45</v>
+      </c>
+      <c r="E59" s="8">
+        <v>15.16</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -2838,13 +2838,13 @@
         <v>31</v>
       </c>
       <c r="C60" s="6">
-        <v>-71.45</v>
+        <v>-69.65000000000001</v>
       </c>
       <c r="D60" s="6">
-        <v>-69.65000000000001</v>
-      </c>
-      <c r="E60" s="7">
-        <v>1.8</v>
+        <v>24.83</v>
+      </c>
+      <c r="E60" s="8">
+        <v>94.48</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -2855,13 +2855,13 @@
         <v>31</v>
       </c>
       <c r="C61" s="6">
-        <v>-43.35</v>
+        <v>-61.65</v>
       </c>
       <c r="D61" s="6">
-        <v>-61.65</v>
+        <v>-55.63</v>
       </c>
       <c r="E61" s="8">
-        <v>-18.3</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -2872,13 +2872,13 @@
         <v>31</v>
       </c>
       <c r="C62" s="6">
-        <v>-43.63</v>
+        <v>-14.52</v>
       </c>
       <c r="D62" s="6">
-        <v>-14.52</v>
+        <v>-67.86</v>
       </c>
       <c r="E62" s="7">
-        <v>29.11</v>
+        <v>-53.34</v>
       </c>
     </row>
   </sheetData>
@@ -2937,22 +2937,22 @@
         <v>44</v>
       </c>
       <c r="B2" s="11">
-        <v>49.96</v>
+        <v>44.2</v>
       </c>
       <c r="C2" s="12">
         <v>7</v>
       </c>
       <c r="D2" s="11">
-        <v>39.3</v>
+        <v>36.3</v>
       </c>
       <c r="E2" s="11">
-        <v>42.9</v>
+        <v>28.6</v>
       </c>
       <c r="F2" s="11">
-        <v>-10.1</v>
+        <v>-10.5</v>
       </c>
       <c r="G2" s="11">
-        <v>-8.5</v>
+        <v>-10</v>
       </c>
       <c r="H2" s="11">
         <v>57</v>
@@ -3083,25 +3083,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="14">
-        <v>0.4185</v>
+        <v>0.405</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2621</v>
+        <v>0.2586</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2137</v>
+        <v>0.2217</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1794</v>
+        <v>0.1766</v>
       </c>
       <c r="E2" s="14">
-        <v>0.09660000000000001</v>
+        <v>0.09119999999999999</v>
       </c>
       <c r="F2" s="14">
-        <v>0.07580000000000001</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0564</v>
+        <v>0.0467</v>
       </c>
     </row>
   </sheetData>
